--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899768DF-971A-45F2-A20A-B85B92ACC371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15A2125F-AD76-40EB-873C-DD295E338771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -19,9 +19,7 @@
     <sheet name="Deco" sheetId="9" r:id="rId4"/>
     <sheet name="Cant" sheetId="10" r:id="rId5"/>
     <sheet name="Taiere" sheetId="19" r:id="rId6"/>
-    <sheet name="Verificare" sheetId="11" r:id="rId7"/>
-    <sheet name="Tutorial Fisa" sheetId="12" r:id="rId8"/>
-    <sheet name="Parametri" sheetId="4" state="hidden" r:id="rId9"/>
+    <sheet name="Parametri" sheetId="4" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Proforma!$A$1:$B$202</definedName>
@@ -93,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="118">
   <si>
     <t>FIRMA:</t>
   </si>
@@ -437,21 +435,6 @@
     <t>S</t>
   </si>
   <si>
-    <t>Nr. crt.</t>
-  </si>
-  <si>
-    <t>Verficat</t>
-  </si>
-  <si>
-    <t>Corectare Preț EK la dublaje =&gt; buton "Piese"</t>
-  </si>
-  <si>
-    <t>Generare accesorii</t>
-  </si>
-  <si>
-    <t>Verificare cote țarcuri sertare</t>
-  </si>
-  <si>
     <t>Pasi</t>
   </si>
   <si>
@@ -462,232 +445,6 @@
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Calculați datele atelierului </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>- Rezolvați conflictele din RoomDesigner dacă se poate</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sertare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Adăugare cuplaje Movento/Tandem pe lista de componente</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Adăugare prelucrari</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Accesoriile necesare se adaugă la sfârșit, nu modificăm nr. de piese la accesoriile existente (balamale, minificși etc,)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sertare</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Șters Kartoane și DSK</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VB35</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Culoare material =&gt; culoare VB35</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Aventos HF,HK Top</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Șters găurile mecanismului de pe pereții laterali</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Plintele</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - corectat adaosuri Horatec, canturi 0,8 dacă e nevoie</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Blaturile</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Canturi de 1,5 nu de 0,8</t>
-    </r>
-  </si>
-  <si>
-    <t>Pași Verificare</t>
-  </si>
-  <si>
-    <t>Se uploadează PDF-ul în site și se selectează "Multiple Sheets"</t>
-  </si>
-  <si>
-    <t>Se accesează adresa https://www.ilovepdf.com/pdf_to_excel</t>
-  </si>
-  <si>
-    <t>Se downloadează fișierul convertit și se deschide (Dublu-Click)</t>
-  </si>
-  <si>
-    <t>Dai click pe "Enable Editing"</t>
-  </si>
-  <si>
-    <t>In coloana X din sheet-ul "Deco" pentru fiecare rând completat se selectează "N" sau "S" în funcție de valoarea validă (net sau standard)</t>
-  </si>
-  <si>
-    <t>Apoi din același sheet 3 se selectează valorile din tabelul "Bandarea Marginilor" până la coloana G și se copiază in sheet-ul "Cant" din Fișă pe rândul 2</t>
-  </si>
-  <si>
-    <t>Se selecteaza din sheet 3 coloanele pana la "J" din primul tabel de sus și se copiaza in sheet-ul "Deco" din Fișă pe rândul 2</t>
-  </si>
-  <si>
-    <t>In sheet-ul „Fisa” va trebui completat antetul și veți observa ca toate valorile au fost completate automat</t>
-  </si>
-  <si>
-    <t>Ultimul pas se află în sheet-ul „Verificare” unde au fost trecuți toți pașii de verificat cand se completează fișa</t>
-  </si>
-  <si>
-    <t>În coloana „Verificat” puteți selecta ”da” sau ”nu” în funcție de verificările facute la proiectul selectat.</t>
-  </si>
-  <si>
-    <t>Tutorial Fișă Prototip</t>
-  </si>
-  <si>
-    <t>Se exporta din RoomDesigner "Mengenkalkulation" in format PDF pentru proiectul dorit</t>
-  </si>
-  <si>
-    <t>De specificat că în funcție de ce ați selectat la „11” Fișa va aparea ca fiind validă sau invalidă</t>
   </si>
 </sst>
 </file>
@@ -701,7 +458,7 @@
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -791,36 +548,6 @@
       <name val="Times New Roman"/>
       <charset val="204"/>
     </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -878,7 +605,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="59">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -1497,79 +1224,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1626,7 +1290,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="299">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -2071,7 +1735,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2080,62 +1744,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="49" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="49" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="49" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="49" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="56" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="55" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
@@ -2163,8 +1778,8 @@
     <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
@@ -2181,14 +1796,235 @@
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="53" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2244,230 +2080,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2477,12 +2092,64 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3031,33 +2698,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="242" t="s">
+      <c r="A1" s="239" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="243"/>
-      <c r="C1" s="243"/>
-      <c r="D1" s="243"/>
-      <c r="E1" s="243"/>
-      <c r="F1" s="243"/>
-      <c r="G1" s="243"/>
-      <c r="H1" s="243"/>
-      <c r="I1" s="243"/>
-      <c r="J1" s="243"/>
-      <c r="K1" s="243"/>
-      <c r="L1" s="244"/>
+      <c r="B1" s="240"/>
+      <c r="C1" s="240"/>
+      <c r="D1" s="240"/>
+      <c r="E1" s="240"/>
+      <c r="F1" s="240"/>
+      <c r="G1" s="240"/>
+      <c r="H1" s="240"/>
+      <c r="I1" s="240"/>
+      <c r="J1" s="240"/>
+      <c r="K1" s="240"/>
+      <c r="L1" s="241"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="232" t="s">
+      <c r="O1" s="224" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
-      <c r="S1" s="234"/>
+      <c r="P1" s="225"/>
+      <c r="Q1" s="225"/>
+      <c r="R1" s="225"/>
+      <c r="S1" s="226"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -3076,165 +2743,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="85"/>
-      <c r="O2" s="235"/>
-      <c r="P2" s="236"/>
-      <c r="Q2" s="236"/>
-      <c r="R2" s="236"/>
-      <c r="S2" s="237"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="228"/>
+      <c r="Q2" s="228"/>
+      <c r="R2" s="228"/>
+      <c r="S2" s="229"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="252"/>
-      <c r="C3" s="253"/>
-      <c r="D3" s="254"/>
+      <c r="B3" s="247"/>
+      <c r="C3" s="248"/>
+      <c r="D3" s="249"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="256"/>
-      <c r="J3" s="257"/>
-      <c r="K3" s="258"/>
+      <c r="I3" s="180"/>
+      <c r="J3" s="181"/>
+      <c r="K3" s="182"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="77"/>
-      <c r="O3" s="245"/>
-      <c r="P3" s="230"/>
-      <c r="Q3" s="230"/>
-      <c r="R3" s="230"/>
-      <c r="S3" s="231"/>
+      <c r="O3" s="242"/>
+      <c r="P3" s="243"/>
+      <c r="Q3" s="243"/>
+      <c r="R3" s="243"/>
+      <c r="S3" s="244"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="288"/>
-      <c r="C4" s="289"/>
-      <c r="D4" s="290"/>
+      <c r="B4" s="218"/>
+      <c r="C4" s="219"/>
+      <c r="D4" s="220"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="291"/>
-      <c r="J4" s="292"/>
-      <c r="K4" s="293"/>
+      <c r="I4" s="221"/>
+      <c r="J4" s="222"/>
+      <c r="K4" s="223"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="77"/>
-      <c r="O4" s="245"/>
-      <c r="P4" s="230"/>
-      <c r="Q4" s="230"/>
-      <c r="R4" s="230"/>
-      <c r="S4" s="231"/>
+      <c r="O4" s="242"/>
+      <c r="P4" s="243"/>
+      <c r="Q4" s="243"/>
+      <c r="R4" s="243"/>
+      <c r="S4" s="244"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="215"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="217"/>
+      <c r="B5" s="257"/>
+      <c r="C5" s="258"/>
+      <c r="D5" s="259"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="229"/>
-      <c r="J5" s="230"/>
-      <c r="K5" s="231"/>
+      <c r="I5" s="266"/>
+      <c r="J5" s="243"/>
+      <c r="K5" s="244"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="77"/>
-      <c r="O5" s="245"/>
-      <c r="P5" s="230"/>
-      <c r="Q5" s="230"/>
-      <c r="R5" s="230"/>
-      <c r="S5" s="231"/>
+      <c r="O5" s="242"/>
+      <c r="P5" s="243"/>
+      <c r="Q5" s="243"/>
+      <c r="R5" s="243"/>
+      <c r="S5" s="244"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="220"/>
-      <c r="C6" s="221"/>
-      <c r="D6" s="222"/>
+      <c r="B6" s="262"/>
+      <c r="C6" s="263"/>
+      <c r="D6" s="264"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="223"/>
-      <c r="J6" s="224"/>
-      <c r="K6" s="225"/>
+      <c r="I6" s="265"/>
+      <c r="J6" s="231"/>
+      <c r="K6" s="232"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="78"/>
-      <c r="O6" s="238"/>
-      <c r="P6" s="224"/>
-      <c r="Q6" s="224"/>
-      <c r="R6" s="224"/>
-      <c r="S6" s="225"/>
+      <c r="O6" s="230"/>
+      <c r="P6" s="231"/>
+      <c r="Q6" s="231"/>
+      <c r="R6" s="231"/>
+      <c r="S6" s="232"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="260" t="s">
+      <c r="A8" s="186" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="261"/>
-      <c r="C8" s="261"/>
-      <c r="D8" s="262"/>
-      <c r="F8" s="226" t="s">
+      <c r="B8" s="187"/>
+      <c r="C8" s="187"/>
+      <c r="D8" s="188"/>
+      <c r="F8" s="233" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="227"/>
-      <c r="H8" s="227"/>
-      <c r="I8" s="227"/>
-      <c r="J8" s="227"/>
-      <c r="K8" s="227"/>
-      <c r="L8" s="227"/>
-      <c r="M8" s="227"/>
-      <c r="N8" s="227"/>
-      <c r="O8" s="227"/>
-      <c r="P8" s="227"/>
-      <c r="Q8" s="227"/>
-      <c r="R8" s="227"/>
-      <c r="S8" s="228"/>
+      <c r="G8" s="234"/>
+      <c r="H8" s="234"/>
+      <c r="I8" s="234"/>
+      <c r="J8" s="234"/>
+      <c r="K8" s="234"/>
+      <c r="L8" s="234"/>
+      <c r="M8" s="234"/>
+      <c r="N8" s="234"/>
+      <c r="O8" s="234"/>
+      <c r="P8" s="234"/>
+      <c r="Q8" s="234"/>
+      <c r="R8" s="234"/>
+      <c r="S8" s="235"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="263"/>
-      <c r="B9" s="264"/>
-      <c r="C9" s="264"/>
-      <c r="D9" s="265"/>
-      <c r="F9" s="284" t="s">
+      <c r="A9" s="189"/>
+      <c r="B9" s="190"/>
+      <c r="C9" s="190"/>
+      <c r="D9" s="191"/>
+      <c r="F9" s="214" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="285"/>
-      <c r="H9" s="218" t="s">
+      <c r="G9" s="215"/>
+      <c r="H9" s="260" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="219"/>
-      <c r="J9" s="282" t="s">
+      <c r="I9" s="261"/>
+      <c r="J9" s="212" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="283"/>
-      <c r="L9" s="213" t="s">
+      <c r="K9" s="213"/>
+      <c r="L9" s="255" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="214"/>
-      <c r="N9" s="250" t="s">
+      <c r="M9" s="256"/>
+      <c r="N9" s="192" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="251"/>
-      <c r="P9" s="277" t="s">
+      <c r="O9" s="193"/>
+      <c r="P9" s="207" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="278"/>
-      <c r="R9" s="250" t="s">
+      <c r="Q9" s="208"/>
+      <c r="R9" s="192" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="251"/>
+      <c r="S9" s="193"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="246" t="s">
+      <c r="A10" s="245" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -3291,7 +2958,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="247"/>
+      <c r="A11" s="184"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -3377,7 +3044,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="247"/>
+      <c r="A12" s="184"/>
       <c r="B12" s="135" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3455,7 +3122,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="247"/>
+      <c r="A13" s="184"/>
       <c r="B13" s="135" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3533,7 +3200,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="247"/>
+      <c r="A14" s="184"/>
       <c r="B14" s="135" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3619,7 +3286,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="247"/>
+      <c r="A15" s="184"/>
       <c r="B15" s="135" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3697,7 +3364,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="247"/>
+      <c r="A16" s="184"/>
       <c r="B16" s="135" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3775,7 +3442,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="247"/>
+      <c r="A17" s="184"/>
       <c r="B17" s="135" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3853,7 +3520,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="247"/>
+      <c r="A18" s="184"/>
       <c r="B18" s="135" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3931,7 +3598,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="247"/>
+      <c r="A19" s="184"/>
       <c r="B19" s="135" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -4009,7 +3676,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="247"/>
+      <c r="A20" s="184"/>
       <c r="B20" s="135" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -4087,7 +3754,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="247"/>
+      <c r="A21" s="184"/>
       <c r="B21" s="135" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -4165,7 +3832,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="248"/>
+      <c r="A22" s="246"/>
       <c r="B22" s="135" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -4285,7 +3952,7 @@
       <c r="S23" s="60"/>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="246" t="s">
+      <c r="A24" s="245" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -4373,7 +4040,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="247"/>
+      <c r="A25" s="184"/>
       <c r="B25" s="71" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4459,7 +4126,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="247"/>
+      <c r="A26" s="184"/>
       <c r="B26" s="71" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4545,7 +4212,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="247"/>
+      <c r="A27" s="184"/>
       <c r="B27" s="71" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4631,7 +4298,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="249"/>
+      <c r="A28" s="185"/>
       <c r="B28" s="71" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4792,7 +4459,7 @@
       <c r="S31" s="81"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="279" t="s">
+      <c r="A32" s="209" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4865,7 +4532,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="280"/>
+      <c r="A33" s="210"/>
       <c r="B33" s="71" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4936,7 +4603,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="281"/>
+      <c r="A34" s="211"/>
       <c r="B34" s="71" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -5028,7 +4695,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="279" t="s">
+      <c r="A36" s="209" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -5101,7 +4768,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="280"/>
+      <c r="A37" s="210"/>
       <c r="B37" s="71" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -5172,7 +4839,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="281"/>
+      <c r="A38" s="211"/>
       <c r="B38" s="72" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5257,7 +4924,7 @@
       <c r="Q39" s="65"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="246" t="s">
+      <c r="A40" s="245" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5269,25 +4936,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="239" t="s">
+      <c r="F40" s="236" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="240"/>
-      <c r="H40" s="240"/>
-      <c r="I40" s="240"/>
-      <c r="J40" s="240"/>
-      <c r="K40" s="240"/>
-      <c r="L40" s="240"/>
-      <c r="M40" s="240"/>
-      <c r="N40" s="240"/>
-      <c r="O40" s="240"/>
-      <c r="P40" s="240"/>
-      <c r="Q40" s="240"/>
-      <c r="R40" s="240"/>
-      <c r="S40" s="241"/>
+      <c r="G40" s="237"/>
+      <c r="H40" s="237"/>
+      <c r="I40" s="237"/>
+      <c r="J40" s="237"/>
+      <c r="K40" s="237"/>
+      <c r="L40" s="237"/>
+      <c r="M40" s="237"/>
+      <c r="N40" s="237"/>
+      <c r="O40" s="237"/>
+      <c r="P40" s="237"/>
+      <c r="Q40" s="237"/>
+      <c r="R40" s="237"/>
+      <c r="S40" s="238"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="247"/>
+      <c r="A41" s="184"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -5350,7 +5017,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="247"/>
+      <c r="A42" s="184"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5378,7 +5045,7 @@
       <c r="S42" s="84"/>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="247"/>
+      <c r="A43" s="184"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5390,25 +5057,25 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="226" t="s">
+      <c r="F43" s="233" t="s">
         <v>94</v>
       </c>
-      <c r="G43" s="227"/>
-      <c r="H43" s="227"/>
-      <c r="I43" s="227"/>
-      <c r="J43" s="227"/>
-      <c r="K43" s="227"/>
-      <c r="L43" s="227"/>
-      <c r="M43" s="227"/>
-      <c r="N43" s="227"/>
-      <c r="O43" s="227"/>
-      <c r="P43" s="227"/>
-      <c r="Q43" s="227"/>
-      <c r="R43" s="227"/>
-      <c r="S43" s="228"/>
+      <c r="G43" s="234"/>
+      <c r="H43" s="234"/>
+      <c r="I43" s="234"/>
+      <c r="J43" s="234"/>
+      <c r="K43" s="234"/>
+      <c r="L43" s="234"/>
+      <c r="M43" s="234"/>
+      <c r="N43" s="234"/>
+      <c r="O43" s="234"/>
+      <c r="P43" s="234"/>
+      <c r="Q43" s="234"/>
+      <c r="R43" s="234"/>
+      <c r="S43" s="235"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="247"/>
+      <c r="A44" s="184"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5464,7 +5131,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="247"/>
+      <c r="A45" s="184"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5535,7 +5202,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="247"/>
+      <c r="A46" s="184"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5549,7 +5216,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="247"/>
+      <c r="A47" s="184"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5560,34 +5227,34 @@
       <c r="D47" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="207" t="s">
+      <c r="F47" s="203" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="286" t="str">
+      <c r="G47" s="216" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="207" t="s">
+      <c r="J47" s="203" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="275">
+      <c r="K47" s="205">
         <v>1</v>
       </c>
-      <c r="N47" s="207" t="s">
+      <c r="N47" s="203" t="s">
         <v>111</v>
       </c>
-      <c r="O47" s="209"/>
-      <c r="P47" s="210"/>
-      <c r="R47" s="207" t="s">
-        <v>122</v>
-      </c>
-      <c r="S47" s="207" t="str">
-        <f>IF(Verificare!B20=2,"O","X")</f>
-        <v>X</v>
+      <c r="O47" s="251"/>
+      <c r="P47" s="252"/>
+      <c r="R47" s="203" t="s">
+        <v>117</v>
+      </c>
+      <c r="S47" s="203" t="e">
+        <f>IF(#REF!=2,"O","X")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="249"/>
+      <c r="A48" s="185"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5598,15 +5265,15 @@
       <c r="D48" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="255"/>
-      <c r="G48" s="287"/>
-      <c r="J48" s="255"/>
-      <c r="K48" s="276"/>
-      <c r="N48" s="208"/>
-      <c r="O48" s="211"/>
-      <c r="P48" s="212"/>
-      <c r="R48" s="208"/>
-      <c r="S48" s="255"/>
+      <c r="F48" s="204"/>
+      <c r="G48" s="217"/>
+      <c r="J48" s="204"/>
+      <c r="K48" s="206"/>
+      <c r="N48" s="250"/>
+      <c r="O48" s="253"/>
+      <c r="P48" s="254"/>
+      <c r="R48" s="250"/>
+      <c r="S48" s="204"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5615,177 +5282,202 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="259" t="s">
+      <c r="A50" s="183" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="266"/>
-      <c r="C50" s="267"/>
-      <c r="D50" s="267"/>
-      <c r="E50" s="267"/>
-      <c r="F50" s="267"/>
-      <c r="G50" s="267"/>
-      <c r="H50" s="267"/>
-      <c r="I50" s="267"/>
-      <c r="J50" s="267"/>
-      <c r="K50" s="267"/>
-      <c r="L50" s="267"/>
-      <c r="M50" s="267"/>
-      <c r="N50" s="267"/>
-      <c r="O50" s="267"/>
-      <c r="P50" s="267"/>
-      <c r="Q50" s="267"/>
-      <c r="R50" s="267"/>
-      <c r="S50" s="268"/>
+      <c r="B50" s="194"/>
+      <c r="C50" s="195"/>
+      <c r="D50" s="195"/>
+      <c r="E50" s="195"/>
+      <c r="F50" s="195"/>
+      <c r="G50" s="195"/>
+      <c r="H50" s="195"/>
+      <c r="I50" s="195"/>
+      <c r="J50" s="195"/>
+      <c r="K50" s="195"/>
+      <c r="L50" s="195"/>
+      <c r="M50" s="195"/>
+      <c r="N50" s="195"/>
+      <c r="O50" s="195"/>
+      <c r="P50" s="195"/>
+      <c r="Q50" s="195"/>
+      <c r="R50" s="195"/>
+      <c r="S50" s="196"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="247"/>
-      <c r="B51" s="269"/>
-      <c r="C51" s="270"/>
-      <c r="D51" s="270"/>
-      <c r="E51" s="270"/>
-      <c r="F51" s="270"/>
-      <c r="G51" s="270"/>
-      <c r="H51" s="270"/>
-      <c r="I51" s="270"/>
-      <c r="J51" s="270"/>
-      <c r="K51" s="270"/>
-      <c r="L51" s="270"/>
-      <c r="M51" s="270"/>
-      <c r="N51" s="270"/>
-      <c r="O51" s="270"/>
-      <c r="P51" s="270"/>
-      <c r="Q51" s="270"/>
-      <c r="R51" s="270"/>
-      <c r="S51" s="271"/>
+      <c r="A51" s="184"/>
+      <c r="B51" s="197"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="K51" s="198"/>
+      <c r="L51" s="198"/>
+      <c r="M51" s="198"/>
+      <c r="N51" s="198"/>
+      <c r="O51" s="198"/>
+      <c r="P51" s="198"/>
+      <c r="Q51" s="198"/>
+      <c r="R51" s="198"/>
+      <c r="S51" s="199"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="247"/>
-      <c r="B52" s="269"/>
-      <c r="C52" s="270"/>
-      <c r="D52" s="270"/>
-      <c r="E52" s="270"/>
-      <c r="F52" s="270"/>
-      <c r="G52" s="270"/>
-      <c r="H52" s="270"/>
-      <c r="I52" s="270"/>
-      <c r="J52" s="270"/>
-      <c r="K52" s="270"/>
-      <c r="L52" s="270"/>
-      <c r="M52" s="270"/>
-      <c r="N52" s="270"/>
-      <c r="O52" s="270"/>
-      <c r="P52" s="270"/>
-      <c r="Q52" s="270"/>
-      <c r="R52" s="270"/>
-      <c r="S52" s="271"/>
+      <c r="A52" s="184"/>
+      <c r="B52" s="197"/>
+      <c r="C52" s="198"/>
+      <c r="D52" s="198"/>
+      <c r="E52" s="198"/>
+      <c r="F52" s="198"/>
+      <c r="G52" s="198"/>
+      <c r="H52" s="198"/>
+      <c r="I52" s="198"/>
+      <c r="J52" s="198"/>
+      <c r="K52" s="198"/>
+      <c r="L52" s="198"/>
+      <c r="M52" s="198"/>
+      <c r="N52" s="198"/>
+      <c r="O52" s="198"/>
+      <c r="P52" s="198"/>
+      <c r="Q52" s="198"/>
+      <c r="R52" s="198"/>
+      <c r="S52" s="199"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="247"/>
-      <c r="B53" s="269"/>
-      <c r="C53" s="270"/>
-      <c r="D53" s="270"/>
-      <c r="E53" s="270"/>
-      <c r="F53" s="270"/>
-      <c r="G53" s="270"/>
-      <c r="H53" s="270"/>
-      <c r="I53" s="270"/>
-      <c r="J53" s="270"/>
-      <c r="K53" s="270"/>
-      <c r="L53" s="270"/>
-      <c r="M53" s="270"/>
-      <c r="N53" s="270"/>
-      <c r="O53" s="270"/>
-      <c r="P53" s="270"/>
-      <c r="Q53" s="270"/>
-      <c r="R53" s="270"/>
-      <c r="S53" s="271"/>
+      <c r="A53" s="184"/>
+      <c r="B53" s="197"/>
+      <c r="C53" s="198"/>
+      <c r="D53" s="198"/>
+      <c r="E53" s="198"/>
+      <c r="F53" s="198"/>
+      <c r="G53" s="198"/>
+      <c r="H53" s="198"/>
+      <c r="I53" s="198"/>
+      <c r="J53" s="198"/>
+      <c r="K53" s="198"/>
+      <c r="L53" s="198"/>
+      <c r="M53" s="198"/>
+      <c r="N53" s="198"/>
+      <c r="O53" s="198"/>
+      <c r="P53" s="198"/>
+      <c r="Q53" s="198"/>
+      <c r="R53" s="198"/>
+      <c r="S53" s="199"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="247"/>
-      <c r="B54" s="269"/>
-      <c r="C54" s="270"/>
-      <c r="D54" s="270"/>
-      <c r="E54" s="270"/>
-      <c r="F54" s="270"/>
-      <c r="G54" s="270"/>
-      <c r="H54" s="270"/>
-      <c r="I54" s="270"/>
-      <c r="J54" s="270"/>
-      <c r="K54" s="270"/>
-      <c r="L54" s="270"/>
-      <c r="M54" s="270"/>
-      <c r="N54" s="270"/>
-      <c r="O54" s="270"/>
-      <c r="P54" s="270"/>
-      <c r="Q54" s="270"/>
-      <c r="R54" s="270"/>
-      <c r="S54" s="271"/>
+      <c r="A54" s="184"/>
+      <c r="B54" s="197"/>
+      <c r="C54" s="198"/>
+      <c r="D54" s="198"/>
+      <c r="E54" s="198"/>
+      <c r="F54" s="198"/>
+      <c r="G54" s="198"/>
+      <c r="H54" s="198"/>
+      <c r="I54" s="198"/>
+      <c r="J54" s="198"/>
+      <c r="K54" s="198"/>
+      <c r="L54" s="198"/>
+      <c r="M54" s="198"/>
+      <c r="N54" s="198"/>
+      <c r="O54" s="198"/>
+      <c r="P54" s="198"/>
+      <c r="Q54" s="198"/>
+      <c r="R54" s="198"/>
+      <c r="S54" s="199"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="247"/>
-      <c r="B55" s="269"/>
-      <c r="C55" s="270"/>
-      <c r="D55" s="270"/>
-      <c r="E55" s="270"/>
-      <c r="F55" s="270"/>
-      <c r="G55" s="270"/>
-      <c r="H55" s="270"/>
-      <c r="I55" s="270"/>
-      <c r="J55" s="270"/>
-      <c r="K55" s="270"/>
-      <c r="L55" s="270"/>
-      <c r="M55" s="270"/>
-      <c r="N55" s="270"/>
-      <c r="O55" s="270"/>
-      <c r="P55" s="270"/>
-      <c r="Q55" s="270"/>
-      <c r="R55" s="270"/>
-      <c r="S55" s="271"/>
+      <c r="A55" s="184"/>
+      <c r="B55" s="197"/>
+      <c r="C55" s="198"/>
+      <c r="D55" s="198"/>
+      <c r="E55" s="198"/>
+      <c r="F55" s="198"/>
+      <c r="G55" s="198"/>
+      <c r="H55" s="198"/>
+      <c r="I55" s="198"/>
+      <c r="J55" s="198"/>
+      <c r="K55" s="198"/>
+      <c r="L55" s="198"/>
+      <c r="M55" s="198"/>
+      <c r="N55" s="198"/>
+      <c r="O55" s="198"/>
+      <c r="P55" s="198"/>
+      <c r="Q55" s="198"/>
+      <c r="R55" s="198"/>
+      <c r="S55" s="199"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="247"/>
-      <c r="B56" s="269"/>
-      <c r="C56" s="270"/>
-      <c r="D56" s="270"/>
-      <c r="E56" s="270"/>
-      <c r="F56" s="270"/>
-      <c r="G56" s="270"/>
-      <c r="H56" s="270"/>
-      <c r="I56" s="270"/>
-      <c r="J56" s="270"/>
-      <c r="K56" s="270"/>
-      <c r="L56" s="270"/>
-      <c r="M56" s="270"/>
-      <c r="N56" s="270"/>
-      <c r="O56" s="270"/>
-      <c r="P56" s="270"/>
-      <c r="Q56" s="270"/>
-      <c r="R56" s="270"/>
-      <c r="S56" s="271"/>
+      <c r="A56" s="184"/>
+      <c r="B56" s="197"/>
+      <c r="C56" s="198"/>
+      <c r="D56" s="198"/>
+      <c r="E56" s="198"/>
+      <c r="F56" s="198"/>
+      <c r="G56" s="198"/>
+      <c r="H56" s="198"/>
+      <c r="I56" s="198"/>
+      <c r="J56" s="198"/>
+      <c r="K56" s="198"/>
+      <c r="L56" s="198"/>
+      <c r="M56" s="198"/>
+      <c r="N56" s="198"/>
+      <c r="O56" s="198"/>
+      <c r="P56" s="198"/>
+      <c r="Q56" s="198"/>
+      <c r="R56" s="198"/>
+      <c r="S56" s="199"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="249"/>
-      <c r="B57" s="272"/>
-      <c r="C57" s="273"/>
-      <c r="D57" s="273"/>
-      <c r="E57" s="273"/>
-      <c r="F57" s="273"/>
-      <c r="G57" s="273"/>
-      <c r="H57" s="273"/>
-      <c r="I57" s="273"/>
-      <c r="J57" s="273"/>
-      <c r="K57" s="273"/>
-      <c r="L57" s="273"/>
-      <c r="M57" s="273"/>
-      <c r="N57" s="273"/>
-      <c r="O57" s="273"/>
-      <c r="P57" s="273"/>
-      <c r="Q57" s="273"/>
-      <c r="R57" s="273"/>
-      <c r="S57" s="274"/>
+      <c r="A57" s="185"/>
+      <c r="B57" s="200"/>
+      <c r="C57" s="201"/>
+      <c r="D57" s="201"/>
+      <c r="E57" s="201"/>
+      <c r="F57" s="201"/>
+      <c r="G57" s="201"/>
+      <c r="H57" s="201"/>
+      <c r="I57" s="201"/>
+      <c r="J57" s="201"/>
+      <c r="K57" s="201"/>
+      <c r="L57" s="201"/>
+      <c r="M57" s="201"/>
+      <c r="N57" s="201"/>
+      <c r="O57" s="201"/>
+      <c r="P57" s="201"/>
+      <c r="Q57" s="201"/>
+      <c r="R57" s="201"/>
+      <c r="S57" s="202"/>
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="F43:S43"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="F40:S40"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="A10:A22"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="S47:S48"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A57"/>
     <mergeCell ref="A8:D9"/>
@@ -5802,31 +5494,6 @@
     <mergeCell ref="G47:G48"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="F40:S40"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="A10:A22"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="F43:S43"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8990,18 +8657,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customFormat="1">
-      <c r="A1" s="294" t="s">
+      <c r="A1" s="267" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="294"/>
-      <c r="C1" s="294"/>
-      <c r="D1" s="294"/>
-      <c r="E1" s="294"/>
-      <c r="F1" s="294"/>
-      <c r="G1" s="294"/>
-      <c r="H1" s="294"/>
-      <c r="I1" s="294"/>
-      <c r="J1" s="294"/>
+      <c r="B1" s="267"/>
+      <c r="C1" s="267"/>
+      <c r="D1" s="267"/>
+      <c r="E1" s="267"/>
+      <c r="F1" s="267"/>
+      <c r="G1" s="267"/>
+      <c r="H1" s="267"/>
+      <c r="I1" s="267"/>
+      <c r="J1" s="267"/>
       <c r="K1" s="12"/>
       <c r="L1" s="5"/>
     </row>
@@ -9022,15 +8689,15 @@
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="295">
+      <c r="B3" s="268">
         <f>Fisa!B3:D3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="295"/>
-      <c r="D3" s="295"/>
-      <c r="E3" s="295"/>
-      <c r="F3" s="295"/>
-      <c r="G3" s="295"/>
+      <c r="C3" s="268"/>
+      <c r="D3" s="268"/>
+      <c r="E3" s="268"/>
+      <c r="F3" s="268"/>
+      <c r="G3" s="268"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -9041,11 +8708,11 @@
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="296">
+      <c r="B4" s="269">
         <f>Fisa!B6</f>
         <v>0</v>
       </c>
-      <c r="C4" s="296"/>
+      <c r="C4" s="269"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -11038,9 +10705,12 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="204"/>
-    <col min="24" max="24" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.140625" style="177"/>
+    <col min="20" max="20" width="9.140625" customWidth="1"/>
+    <col min="21" max="21" width="4.140625" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" style="270"/>
+    <col min="24" max="24" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -11059,7 +10729,7 @@
       <c r="E1" t="s">
         <v>104</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="270" t="s">
         <v>3</v>
       </c>
       <c r="W1" t="s">
@@ -11076,1006 +10746,1126 @@
       </c>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="186"/>
-      <c r="B2" s="184"/>
-      <c r="C2" s="184"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="184"/>
-      <c r="F2" s="184"/>
-      <c r="G2" s="184"/>
-      <c r="H2" s="184"/>
-      <c r="I2" s="184"/>
-      <c r="J2" s="184"/>
-      <c r="K2" s="184"/>
-      <c r="L2" s="202"/>
-      <c r="M2" s="184"/>
-      <c r="N2" s="184"/>
-      <c r="O2" s="184"/>
-      <c r="P2" s="184"/>
-      <c r="Q2" s="197"/>
-      <c r="R2" s="205"/>
-      <c r="S2" s="200"/>
+      <c r="A2" s="159"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="175"/>
+      <c r="M2" s="157"/>
+      <c r="N2" s="157"/>
+      <c r="O2" s="157"/>
+      <c r="P2" s="157"/>
+      <c r="Q2" s="170"/>
+      <c r="R2" s="178"/>
+      <c r="S2" s="173"/>
       <c r="T2" s="147"/>
       <c r="U2" s="147"/>
-      <c r="V2" s="129" t="e">
-        <f>Q2/P2</f>
-        <v>#DIV/0!</v>
+      <c r="V2" s="270" t="str">
+        <f>IFERROR(ROUND(Q2/P2,2),"")</f>
+        <v/>
       </c>
       <c r="W2" t="str">
-        <f>IF(OR(E2=1220,E2=1300,RIGHT(A2,2)="PM",RIGHT(A2,2)="PA",RIGHT(A2,2)="PG",RIGHT(A2,2)="TM/ST9",RIGHT(A2,2)="3D"),"MDF",
-IF(OR(AND(B2=18,D2=2800,E2=2070),AND(B2=18.6,D2=2800,E2=2070),AND(B2=16,D2=2800,E2=2070),AND(B2=8,D2=2800,E2=2070)),"PAL",
-IF(B2=2.7,"HDF", IF(B2=12, "LC",
-IF(OR(B2=8,E2=640),"PS",
-IF(OR(B2=38,B2=20,E2=600,E2=650,E2=920),"BLAT","DB"))))))</f>
+        <f>IF(AND(D2=2800, E2=2070, OR(B2=18, B2=18.6, B2=8, B2=10, B2=16)), "PAL",
+  IF(OR(AND(D2=2800, E2=2070, OR(B2=19, B2=19.3)),
+        AND(D2=2800, E2=1220, B2=18),
+        AND(D2=3050, E2=1300, B2=19.3)), "MDF",
+    IF(AND(D2=4100, OR(E2=600, E2=650, E2=920), OR(B2=38, B2=20)), "BLAT",
+      IF(AND(D2=4100, E2=640, OR(B2=9.2, B2=8)), "PS",
+        IF(B2=2.7, "HDF", "DB")))))</f>
         <v>DB</v>
       </c>
-      <c r="X2" t="e">
-        <f t="shared" ref="X2:X23" si="0">IF(ISNUMBER(--LEFT(TRIM(MID(A2,FIND("-",A2)+1,50)),1)),
+      <c r="X2" t="str">
+        <f>IFERROR(IF(ISNUMBER(--LEFT(TRIM(MID(A2,FIND("-",A2)+1,50)),1)),
 "AGT "&amp;TRIM(MID(A2,FIND("-",A2)+1,50)),
 TRIM(MID(A2,FIND("-",A2)+1,50)))
 &amp;IF(OR(E2=600,E2=650,E2=920)," /"&amp;E2,"")
-&amp;IF(E2=640," "&amp;"PS","")</f>
-        <v>#VALUE!</v>
+&amp;IF(E2=640," "&amp;"PS",""),"")</f>
+        <v/>
       </c>
       <c r="Y2" t="str">
-        <f t="shared" ref="Y2:Y15" si="1">IF(W2="DB", " ",IF(OR(ISNUMBER(FIND(" ST",X2)),ISNUMBER(FIND(" SM",X2)),ISNUMBER(FIND(" PM",X2)),ISNUMBER(FIND(" TM",X2)),ISNUMBER(FIND(" PG",X2)),ISNUMBER(FIND(" PA",X2))),SUBSTITUTE(X2," ","",1),X2))</f>
+        <f t="shared" ref="Y2:Y15" si="0">IF(W2="DB", " ",IF(OR(ISNUMBER(FIND(" ST",X2)),ISNUMBER(FIND(" SM",X2)),ISNUMBER(FIND(" PM",X2)),ISNUMBER(FIND(" TM",X2)),ISNUMBER(FIND(" PG",X2)),ISNUMBER(FIND(" PA",X2))),SUBSTITUTE(X2," ","",1),X2))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z2" t="e">
+      <c r="Z2" t="str">
         <f>IF(W2="DB",IF(OR(ISNUMBER(FIND(" ST",X2)),ISNUMBER(FIND(" SM",X2)),ISNUMBER(FIND(" PM",X2)),ISNUMBER(FIND("TM/ST7",X2)),ISNUMBER(FIND(" PG",X2)),ISNUMBER(FIND(" PA",X2))),SUBSTITUTE(X2," ","",1),X2)," ")</f>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="187"/>
-      <c r="B3" s="185"/>
-      <c r="C3" s="185"/>
-      <c r="D3" s="185"/>
-      <c r="E3" s="185"/>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
-      <c r="L3" s="203"/>
-      <c r="M3" s="185"/>
-      <c r="N3" s="185"/>
-      <c r="O3" s="185"/>
-      <c r="P3" s="185"/>
-      <c r="Q3" s="198"/>
-      <c r="R3" s="205"/>
-      <c r="S3" s="200"/>
+      <c r="A3" s="160"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="158"/>
+      <c r="I3" s="158"/>
+      <c r="J3" s="158"/>
+      <c r="K3" s="158"/>
+      <c r="L3" s="176"/>
+      <c r="M3" s="158"/>
+      <c r="N3" s="158"/>
+      <c r="O3" s="158"/>
+      <c r="P3" s="158"/>
+      <c r="Q3" s="171"/>
+      <c r="R3" s="178"/>
+      <c r="S3" s="173"/>
       <c r="T3" s="133"/>
       <c r="U3" s="147"/>
-      <c r="V3" s="129" t="e">
-        <f t="shared" ref="V3:V34" si="2">Q3/P3</f>
-        <v>#DIV/0!</v>
+      <c r="V3" s="270" t="str">
+        <f t="shared" ref="V3:V34" si="1">IFERROR(ROUND(Q3/P3,2),"")</f>
+        <v/>
       </c>
       <c r="W3" t="str">
-        <f t="shared" ref="W3:W23" si="3">IF(OR(E3=1220,E3=1300,RIGHT(A3,2)="PM",RIGHT(A3,2)="PA",RIGHT(A3,2)="PG",RIGHT(A3,2)="TM/ST9",RIGHT(A3,2)="3D"),"MDF",
-IF(OR(AND(B3=18,D3=2800,E3=2070),AND(B3=18.6,D3=2800,E3=2070),AND(B3=16,D3=2800,E3=2070),AND(B3=8,D3=2800,E3=2070)),"PAL",
-IF(B3=2.7,"HDF", IF(B3=12, "LC",
-IF(OR(B3=8,E3=640),"PS",
-IF(OR(B3=38,B3=20,E3=600,E3=650,E3=920),"BLAT","DB"))))))</f>
+        <f t="shared" ref="W3:W34" si="2">IF(AND(D3=2800, E3=2070, OR(B3=18, B3=18.6, B3=8, B3=10, B3=16)), "PAL",
+  IF(OR(AND(D3=2800, E3=2070, OR(B3=19, B3=19.3)),
+        AND(D3=2800, E3=1220, B3=18),
+        AND(D3=3050, E3=1300, B3=19.3)), "MDF",
+    IF(AND(D3=4100, OR(E3=600, E3=650, E3=920), OR(B3=38, B3=20)), "BLAT",
+      IF(AND(D3=4100, E3=640, OR(B3=9.2, B3=8)), "PS",
+        IF(B3=2.7, "HDF", "DB")))))</f>
         <v>DB</v>
       </c>
-      <c r="X3" t="e">
+      <c r="X3" t="str">
+        <f t="shared" ref="X3:X34" si="3">IFERROR(IF(ISNUMBER(--LEFT(TRIM(MID(A3,FIND("-",A3)+1,50)),1)),
+"AGT "&amp;TRIM(MID(A3,FIND("-",A3)+1,50)),
+TRIM(MID(A3,FIND("-",A3)+1,50)))
+&amp;IF(OR(E3=600,E3=650,E3=920)," /"&amp;E3,"")
+&amp;IF(E3=640," "&amp;"PS",""),"")</f>
+        <v/>
+      </c>
+      <c r="Y3" t="str">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y3" t="str">
-        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z3" t="e">
-        <f t="shared" ref="Z3:Z28" si="4">IF(W3="DB",IF(OR(ISNUMBER(FIND(" ST",X3)),ISNUMBER(FIND(" SM",X3)),ISNUMBER(FIND(" PM",X3)),ISNUMBER(FIND("TM/ST7",X3)),ISNUMBER(FIND(" PG",X3)),ISNUMBER(FIND(" PA",X3))),SUBSTITUTE(X3," ","",1),X3)," ")</f>
-        <v>#VALUE!</v>
+      <c r="Z3" t="str">
+        <f t="shared" ref="Z3:Z34" si="4">IF(W3="DB",IF(OR(ISNUMBER(FIND(" ST",X3)),ISNUMBER(FIND(" SM",X3)),ISNUMBER(FIND(" PM",X3)),ISNUMBER(FIND("TM/ST7",X3)),ISNUMBER(FIND(" PG",X3)),ISNUMBER(FIND(" PA",X3))),SUBSTITUTE(X3," ","",1),X3)," ")</f>
+        <v/>
       </c>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="186"/>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="202"/>
-      <c r="M4" s="184"/>
-      <c r="N4" s="184"/>
-      <c r="O4" s="184"/>
-      <c r="P4" s="184"/>
-      <c r="Q4" s="197"/>
-      <c r="R4" s="205"/>
-      <c r="S4" s="200"/>
+      <c r="A4" s="159"/>
+      <c r="B4" s="157"/>
+      <c r="C4" s="157"/>
+      <c r="D4" s="157"/>
+      <c r="E4" s="157"/>
+      <c r="F4" s="157"/>
+      <c r="G4" s="157"/>
+      <c r="H4" s="157"/>
+      <c r="I4" s="157"/>
+      <c r="J4" s="157"/>
+      <c r="K4" s="157"/>
+      <c r="L4" s="175"/>
+      <c r="M4" s="157"/>
+      <c r="N4" s="157"/>
+      <c r="O4" s="157"/>
+      <c r="P4" s="157"/>
+      <c r="Q4" s="170"/>
+      <c r="R4" s="178"/>
+      <c r="S4" s="173"/>
       <c r="T4" s="147"/>
       <c r="U4" s="133"/>
-      <c r="V4" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V4" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W4" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X4" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X4" t="e">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y4" t="str">
-        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z4" t="e">
+      <c r="Z4" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="187"/>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
-      <c r="F5" s="185"/>
-      <c r="G5" s="185"/>
-      <c r="H5" s="185"/>
-      <c r="I5" s="185"/>
-      <c r="J5" s="185"/>
-      <c r="K5" s="185"/>
-      <c r="L5" s="203"/>
-      <c r="M5" s="185"/>
-      <c r="N5" s="185"/>
-      <c r="O5" s="185"/>
-      <c r="P5" s="185"/>
-      <c r="Q5" s="198"/>
-      <c r="R5" s="205"/>
-      <c r="S5" s="200"/>
+      <c r="A5" s="160"/>
+      <c r="B5" s="158"/>
+      <c r="C5" s="158"/>
+      <c r="D5" s="158"/>
+      <c r="E5" s="158"/>
+      <c r="F5" s="158"/>
+      <c r="G5" s="158"/>
+      <c r="H5" s="158"/>
+      <c r="I5" s="158"/>
+      <c r="J5" s="158"/>
+      <c r="K5" s="158"/>
+      <c r="L5" s="176"/>
+      <c r="M5" s="158"/>
+      <c r="N5" s="158"/>
+      <c r="O5" s="158"/>
+      <c r="P5" s="158"/>
+      <c r="Q5" s="171"/>
+      <c r="R5" s="178"/>
+      <c r="S5" s="173"/>
       <c r="T5" s="147"/>
       <c r="U5" s="133"/>
-      <c r="V5" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V5" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W5" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X5" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X5" t="e">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y5" t="str">
-        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z5" t="e">
+      <c r="Z5" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="186"/>
-      <c r="B6" s="184"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
-      <c r="F6" s="184"/>
-      <c r="G6" s="184"/>
-      <c r="H6" s="184"/>
-      <c r="I6" s="184"/>
-      <c r="J6" s="184"/>
-      <c r="K6" s="184"/>
-      <c r="L6" s="203"/>
-      <c r="M6" s="184"/>
-      <c r="N6" s="184"/>
-      <c r="O6" s="184"/>
-      <c r="P6" s="184"/>
-      <c r="Q6" s="197"/>
-      <c r="R6" s="205"/>
-      <c r="S6" s="200"/>
+      <c r="A6" s="159"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="157"/>
+      <c r="D6" s="157"/>
+      <c r="E6" s="157"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="157"/>
+      <c r="H6" s="157"/>
+      <c r="I6" s="157"/>
+      <c r="J6" s="157"/>
+      <c r="K6" s="157"/>
+      <c r="L6" s="176"/>
+      <c r="M6" s="157"/>
+      <c r="N6" s="157"/>
+      <c r="O6" s="157"/>
+      <c r="P6" s="157"/>
+      <c r="Q6" s="170"/>
+      <c r="R6" s="178"/>
+      <c r="S6" s="173"/>
       <c r="T6" s="147"/>
       <c r="U6" s="133"/>
-      <c r="V6" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V6" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W6" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X6" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X6" t="e">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y6" t="str">
-        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z6" t="e">
+      <c r="Z6" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="187"/>
-      <c r="B7" s="185"/>
-      <c r="C7" s="185"/>
-      <c r="D7" s="185"/>
-      <c r="E7" s="185"/>
-      <c r="F7" s="185"/>
-      <c r="G7" s="185"/>
-      <c r="H7" s="185"/>
-      <c r="I7" s="185"/>
-      <c r="J7" s="185"/>
-      <c r="K7" s="185"/>
-      <c r="L7" s="203"/>
-      <c r="M7" s="185"/>
-      <c r="N7" s="185"/>
-      <c r="O7" s="185"/>
-      <c r="P7" s="185"/>
-      <c r="Q7" s="198"/>
-      <c r="R7" s="205"/>
-      <c r="S7" s="200"/>
+      <c r="A7" s="160"/>
+      <c r="B7" s="158"/>
+      <c r="C7" s="158"/>
+      <c r="D7" s="158"/>
+      <c r="E7" s="158"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="158"/>
+      <c r="H7" s="158"/>
+      <c r="I7" s="158"/>
+      <c r="J7" s="158"/>
+      <c r="K7" s="158"/>
+      <c r="L7" s="176"/>
+      <c r="M7" s="158"/>
+      <c r="N7" s="158"/>
+      <c r="O7" s="158"/>
+      <c r="P7" s="158"/>
+      <c r="Q7" s="171"/>
+      <c r="R7" s="178"/>
+      <c r="S7" s="173"/>
       <c r="T7" s="133"/>
       <c r="U7" s="133"/>
-      <c r="V7" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V7" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W7" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X7" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X7" t="e">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y7" t="str">
-        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z7" t="e">
+      <c r="Z7" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:26">
-      <c r="A8" s="186"/>
-      <c r="B8" s="184"/>
-      <c r="C8" s="184"/>
-      <c r="D8" s="184"/>
-      <c r="E8" s="184"/>
-      <c r="F8" s="184"/>
-      <c r="G8" s="184"/>
-      <c r="H8" s="184"/>
-      <c r="I8" s="184"/>
-      <c r="J8" s="184"/>
-      <c r="K8" s="184"/>
-      <c r="L8" s="203"/>
-      <c r="M8" s="184"/>
-      <c r="N8" s="184"/>
-      <c r="O8" s="184"/>
-      <c r="P8" s="184"/>
-      <c r="Q8" s="197"/>
-      <c r="R8" s="205"/>
-      <c r="S8" s="200"/>
+      <c r="A8" s="159"/>
+      <c r="B8" s="157"/>
+      <c r="C8" s="157"/>
+      <c r="D8" s="157"/>
+      <c r="E8" s="157"/>
+      <c r="F8" s="157"/>
+      <c r="G8" s="157"/>
+      <c r="H8" s="157"/>
+      <c r="I8" s="157"/>
+      <c r="J8" s="157"/>
+      <c r="K8" s="157"/>
+      <c r="L8" s="176"/>
+      <c r="M8" s="157"/>
+      <c r="N8" s="157"/>
+      <c r="O8" s="157"/>
+      <c r="P8" s="157"/>
+      <c r="Q8" s="170"/>
+      <c r="R8" s="178"/>
+      <c r="S8" s="173"/>
       <c r="T8" s="147"/>
       <c r="U8" s="133"/>
-      <c r="V8" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V8" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W8" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X8" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X8" t="e">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y8" t="str">
-        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z8" t="e">
+      <c r="Z8" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:26">
-      <c r="A9" s="187"/>
-      <c r="B9" s="185"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="185"/>
-      <c r="E9" s="185"/>
-      <c r="F9" s="185"/>
-      <c r="G9" s="185"/>
-      <c r="H9" s="185"/>
-      <c r="I9" s="185"/>
-      <c r="J9" s="185"/>
-      <c r="K9" s="185"/>
-      <c r="L9" s="202"/>
-      <c r="M9" s="185"/>
-      <c r="N9" s="185"/>
-      <c r="O9" s="185"/>
-      <c r="P9" s="185"/>
-      <c r="Q9" s="198"/>
-      <c r="R9" s="205"/>
-      <c r="S9" s="200"/>
+      <c r="A9" s="160"/>
+      <c r="B9" s="158"/>
+      <c r="C9" s="158"/>
+      <c r="D9" s="158"/>
+      <c r="E9" s="158"/>
+      <c r="F9" s="158"/>
+      <c r="G9" s="158"/>
+      <c r="H9" s="158"/>
+      <c r="I9" s="158"/>
+      <c r="J9" s="158"/>
+      <c r="K9" s="158"/>
+      <c r="L9" s="175"/>
+      <c r="M9" s="158"/>
+      <c r="N9" s="158"/>
+      <c r="O9" s="158"/>
+      <c r="P9" s="158"/>
+      <c r="Q9" s="171"/>
+      <c r="R9" s="178"/>
+      <c r="S9" s="173"/>
       <c r="T9" s="147"/>
       <c r="U9" s="131"/>
-      <c r="V9" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V9" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W9" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X9" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X9" t="e">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y9" t="str">
-        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z9" t="e">
+      <c r="Z9" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="186"/>
-      <c r="B10" s="184"/>
-      <c r="C10" s="184"/>
-      <c r="D10" s="184"/>
-      <c r="E10" s="184"/>
-      <c r="F10" s="184"/>
-      <c r="G10" s="184"/>
-      <c r="H10" s="184"/>
-      <c r="I10" s="184"/>
-      <c r="J10" s="184"/>
-      <c r="K10" s="184"/>
-      <c r="L10" s="203"/>
-      <c r="M10" s="184"/>
-      <c r="N10" s="184"/>
-      <c r="O10" s="184"/>
-      <c r="P10" s="184"/>
-      <c r="Q10" s="197"/>
-      <c r="R10" s="205"/>
-      <c r="S10" s="200"/>
+      <c r="A10" s="159"/>
+      <c r="B10" s="157"/>
+      <c r="C10" s="157"/>
+      <c r="D10" s="157"/>
+      <c r="E10" s="157"/>
+      <c r="F10" s="157"/>
+      <c r="G10" s="157"/>
+      <c r="H10" s="157"/>
+      <c r="I10" s="157"/>
+      <c r="J10" s="157"/>
+      <c r="K10" s="157"/>
+      <c r="L10" s="176"/>
+      <c r="M10" s="157"/>
+      <c r="N10" s="157"/>
+      <c r="O10" s="157"/>
+      <c r="P10" s="157"/>
+      <c r="Q10" s="170"/>
+      <c r="R10" s="178"/>
+      <c r="S10" s="173"/>
       <c r="T10" s="147"/>
       <c r="U10" s="147"/>
-      <c r="V10" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V10" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W10" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X10" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X10" t="e">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y10" t="str">
-        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z10" t="e">
+      <c r="Z10" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="187"/>
-      <c r="B11" s="185"/>
-      <c r="C11" s="185"/>
-      <c r="D11" s="185"/>
-      <c r="E11" s="185"/>
-      <c r="F11" s="185"/>
-      <c r="G11" s="185"/>
-      <c r="H11" s="185"/>
-      <c r="I11" s="185"/>
-      <c r="J11" s="185"/>
-      <c r="K11" s="185"/>
-      <c r="L11" s="203"/>
-      <c r="M11" s="185"/>
-      <c r="N11" s="185"/>
-      <c r="O11" s="185"/>
-      <c r="P11" s="185"/>
-      <c r="Q11" s="198"/>
-      <c r="R11" s="205"/>
-      <c r="S11" s="200"/>
+      <c r="A11" s="160"/>
+      <c r="B11" s="158"/>
+      <c r="C11" s="158"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="158"/>
+      <c r="F11" s="158"/>
+      <c r="G11" s="158"/>
+      <c r="H11" s="158"/>
+      <c r="I11" s="158"/>
+      <c r="J11" s="158"/>
+      <c r="K11" s="158"/>
+      <c r="L11" s="176"/>
+      <c r="M11" s="158"/>
+      <c r="N11" s="158"/>
+      <c r="O11" s="158"/>
+      <c r="P11" s="158"/>
+      <c r="Q11" s="171"/>
+      <c r="R11" s="178"/>
+      <c r="S11" s="173"/>
       <c r="T11" s="147"/>
       <c r="U11" s="147"/>
-      <c r="V11" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V11" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W11" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X11" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X11" t="e">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y11" t="str">
-        <f t="shared" si="1"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z11" t="e">
+      <c r="Z11" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="186"/>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
-      <c r="F12" s="184"/>
-      <c r="G12" s="184"/>
-      <c r="H12" s="184"/>
-      <c r="I12" s="184"/>
-      <c r="J12" s="184"/>
-      <c r="K12" s="184"/>
-      <c r="L12" s="203"/>
-      <c r="M12" s="184"/>
-      <c r="N12" s="184"/>
-      <c r="O12" s="184"/>
-      <c r="P12" s="184"/>
-      <c r="Q12" s="197"/>
-      <c r="R12" s="205"/>
+      <c r="A12" s="272"/>
+      <c r="B12" s="273"/>
+      <c r="C12" s="274"/>
+      <c r="D12" s="275"/>
+      <c r="E12" s="275"/>
+      <c r="F12" s="276"/>
+      <c r="G12" s="273"/>
+      <c r="H12" s="277"/>
+      <c r="I12" s="273"/>
+      <c r="J12" s="277"/>
+      <c r="K12" s="281"/>
+      <c r="L12" s="281"/>
+      <c r="M12" s="279"/>
+      <c r="N12" s="281"/>
+      <c r="O12" s="281"/>
+      <c r="P12" s="278"/>
+      <c r="Q12" s="281"/>
+      <c r="R12" s="178"/>
       <c r="S12" s="134"/>
       <c r="T12" s="134"/>
       <c r="U12" s="134"/>
-      <c r="V12" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V12" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W12" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X12" t="str">
         <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Y12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="Z12" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="A13" s="272"/>
+      <c r="B13" s="273"/>
+      <c r="C13" s="274"/>
+      <c r="D13" s="275"/>
+      <c r="E13" s="275"/>
+      <c r="F13" s="280"/>
+      <c r="G13" s="273"/>
+      <c r="H13" s="277"/>
+      <c r="I13" s="273"/>
+      <c r="J13" s="278"/>
+      <c r="K13" s="281"/>
+      <c r="L13" s="281"/>
+      <c r="M13" s="279"/>
+      <c r="N13" s="281"/>
+      <c r="O13" s="281"/>
+      <c r="P13" s="277"/>
+      <c r="Q13" s="281"/>
+      <c r="R13" s="178"/>
+      <c r="S13" s="167"/>
+      <c r="T13" s="166"/>
+      <c r="U13" s="174"/>
+      <c r="V13" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W13" t="str">
+        <f t="shared" si="2"/>
         <v>DB</v>
       </c>
-      <c r="X12" t="e">
+      <c r="X13" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Y13" t="str">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y12" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="Z13" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="A14" s="272"/>
+      <c r="B14" s="273"/>
+      <c r="C14" s="274"/>
+      <c r="D14" s="275"/>
+      <c r="E14" s="275"/>
+      <c r="F14" s="276"/>
+      <c r="G14" s="273"/>
+      <c r="H14" s="278"/>
+      <c r="I14" s="273"/>
+      <c r="J14" s="278"/>
+      <c r="K14" s="281"/>
+      <c r="L14" s="281"/>
+      <c r="M14" s="278"/>
+      <c r="N14" s="281"/>
+      <c r="O14" s="281"/>
+      <c r="P14" s="278"/>
+      <c r="Q14" s="281"/>
+      <c r="R14" s="178"/>
+      <c r="S14" s="166"/>
+      <c r="T14" s="167"/>
+      <c r="U14" s="174"/>
+      <c r="V14" s="270" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W14" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X14" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Y14" t="str">
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z12" t="e">
+      <c r="Z14" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="187"/>
-      <c r="B13" s="185"/>
-      <c r="C13" s="185"/>
-      <c r="D13" s="185"/>
-      <c r="E13" s="185"/>
-      <c r="F13" s="185"/>
-      <c r="G13" s="185"/>
-      <c r="H13" s="185"/>
-      <c r="I13" s="185"/>
-      <c r="J13" s="185"/>
-      <c r="K13" s="185"/>
-      <c r="L13" s="203"/>
-      <c r="M13" s="185"/>
-      <c r="N13" s="185"/>
-      <c r="O13" s="185"/>
-      <c r="P13" s="185"/>
-      <c r="Q13" s="198"/>
-      <c r="R13" s="205"/>
-      <c r="S13" s="194"/>
-      <c r="T13" s="193"/>
-      <c r="U13" s="201"/>
-      <c r="V13" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
+      <c r="A15" s="271"/>
+      <c r="B15" s="271"/>
+      <c r="C15" s="271"/>
+      <c r="D15" s="271"/>
+      <c r="E15" s="271"/>
+      <c r="F15" s="271"/>
+      <c r="G15" s="271"/>
+      <c r="H15" s="271"/>
+      <c r="I15" s="271"/>
+      <c r="J15" s="271"/>
+      <c r="K15" s="271"/>
+      <c r="L15" s="271"/>
+      <c r="M15" s="271"/>
+      <c r="N15" s="271"/>
+      <c r="O15" s="271"/>
+      <c r="P15" s="271"/>
+      <c r="Q15" s="271"/>
+      <c r="R15" s="178"/>
+      <c r="S15" s="167"/>
+      <c r="T15" s="167"/>
+      <c r="U15" s="134"/>
+      <c r="V15" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W15" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X15" t="str">
         <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Y15" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="Z15" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
+      <c r="A16" s="271"/>
+      <c r="B16" s="271"/>
+      <c r="C16" s="271"/>
+      <c r="D16" s="271"/>
+      <c r="E16" s="271"/>
+      <c r="F16" s="271"/>
+      <c r="G16" s="271"/>
+      <c r="H16" s="271"/>
+      <c r="I16" s="271"/>
+      <c r="J16" s="271"/>
+      <c r="K16" s="271"/>
+      <c r="L16" s="271"/>
+      <c r="M16" s="271"/>
+      <c r="N16" s="271"/>
+      <c r="O16" s="271"/>
+      <c r="P16" s="271"/>
+      <c r="Q16" s="271"/>
+      <c r="R16" s="179"/>
+      <c r="S16" s="167"/>
+      <c r="T16" s="167"/>
+      <c r="U16" s="133"/>
+      <c r="V16" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W16" t="str">
+        <f t="shared" si="2"/>
         <v>DB</v>
       </c>
-      <c r="X13" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y13" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="Z13" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="186"/>
-      <c r="B14" s="184"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="184"/>
-      <c r="E14" s="184"/>
-      <c r="F14" s="184"/>
-      <c r="G14" s="184"/>
-      <c r="H14" s="184"/>
-      <c r="I14" s="184"/>
-      <c r="J14" s="184"/>
-      <c r="K14" s="184"/>
-      <c r="L14" s="203"/>
-      <c r="M14" s="184"/>
-      <c r="N14" s="184"/>
-      <c r="O14" s="184"/>
-      <c r="P14" s="184"/>
-      <c r="Q14" s="197"/>
-      <c r="R14" s="205"/>
-      <c r="S14" s="193"/>
-      <c r="T14" s="194"/>
-      <c r="U14" s="201"/>
-      <c r="V14" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W14" t="str">
+      <c r="X16" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X14" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y14" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="Z14" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26">
-      <c r="A15" s="187"/>
-      <c r="B15" s="185"/>
-      <c r="C15" s="185"/>
-      <c r="D15" s="185"/>
-      <c r="E15" s="185"/>
-      <c r="F15" s="185"/>
-      <c r="G15" s="185"/>
-      <c r="H15" s="185"/>
-      <c r="I15" s="185"/>
-      <c r="J15" s="185"/>
-      <c r="K15" s="185"/>
-      <c r="L15" s="202"/>
-      <c r="M15" s="185"/>
-      <c r="N15" s="185"/>
-      <c r="O15" s="185"/>
-      <c r="P15" s="185"/>
-      <c r="Q15" s="198"/>
-      <c r="R15" s="205"/>
-      <c r="S15" s="194"/>
-      <c r="T15" s="194"/>
-      <c r="U15" s="134"/>
-      <c r="V15" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W15" t="str">
-        <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X15" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y15" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="Z15" t="e">
-        <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26">
-      <c r="A16" s="186"/>
-      <c r="B16" s="184"/>
-      <c r="C16" s="184"/>
-      <c r="D16" s="184"/>
-      <c r="E16" s="184"/>
-      <c r="F16" s="184"/>
-      <c r="G16" s="184"/>
-      <c r="H16" s="184"/>
-      <c r="I16" s="184"/>
-      <c r="J16" s="184"/>
-      <c r="K16" s="184"/>
-      <c r="L16" s="184"/>
-      <c r="M16" s="184"/>
-      <c r="N16" s="184"/>
-      <c r="O16" s="184"/>
-      <c r="P16" s="184"/>
-      <c r="Q16" s="197"/>
-      <c r="R16" s="206"/>
-      <c r="S16" s="194"/>
-      <c r="T16" s="194"/>
-      <c r="U16" s="133"/>
-      <c r="V16" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W16" t="str">
-        <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X16" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="Y16" t="str">
         <f t="shared" ref="Y16:Y24" si="5">IF(W16="DB", " ",IF(OR(ISNUMBER(FIND(" ST",X16)),ISNUMBER(FIND(" SM",X16)),ISNUMBER(FIND(" PM",X16)),ISNUMBER(FIND(" TM",X16)),ISNUMBER(FIND(" PG",X16)),ISNUMBER(FIND(" PA",X16))),SUBSTITUTE(X16," ","",1),X16))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z16" t="e">
+      <c r="Z16" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="17" spans="1:26">
-      <c r="A17" s="187"/>
-      <c r="B17" s="185"/>
-      <c r="C17" s="185"/>
-      <c r="D17" s="185"/>
-      <c r="E17" s="185"/>
-      <c r="F17" s="185"/>
-      <c r="G17" s="185"/>
-      <c r="H17" s="185"/>
-      <c r="I17" s="185"/>
-      <c r="J17" s="185"/>
-      <c r="K17" s="185"/>
-      <c r="L17" s="185"/>
-      <c r="M17" s="185"/>
-      <c r="N17" s="185"/>
-      <c r="O17" s="185"/>
-      <c r="P17" s="185"/>
-      <c r="Q17" s="198"/>
-      <c r="R17" s="206"/>
-      <c r="S17" s="194"/>
-      <c r="T17" s="194"/>
+      <c r="A17" s="283"/>
+      <c r="B17" s="282"/>
+      <c r="C17" s="282"/>
+      <c r="D17" s="282"/>
+      <c r="E17" s="282"/>
+      <c r="F17" s="282"/>
+      <c r="G17" s="282"/>
+      <c r="H17" s="282"/>
+      <c r="I17" s="282"/>
+      <c r="J17" s="282"/>
+      <c r="K17" s="282"/>
+      <c r="L17" s="285"/>
+      <c r="M17" s="282"/>
+      <c r="N17" s="282"/>
+      <c r="O17" s="282"/>
+      <c r="P17" s="282"/>
+      <c r="Q17" s="284"/>
+      <c r="R17" s="179"/>
+      <c r="S17" s="167"/>
+      <c r="T17" s="167"/>
       <c r="U17" s="133"/>
-      <c r="V17" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V17" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W17" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X17" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X17" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="Y17" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z17" t="e">
+      <c r="Z17" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="1:26">
-      <c r="A18" s="188"/>
-      <c r="B18" s="189"/>
-      <c r="C18" s="190"/>
-      <c r="D18" s="191"/>
-      <c r="E18" s="191"/>
-      <c r="F18" s="192"/>
-      <c r="G18" s="189"/>
-      <c r="H18" s="193"/>
-      <c r="I18" s="189"/>
-      <c r="J18" s="194"/>
-      <c r="K18" s="199"/>
-      <c r="L18" s="199"/>
-      <c r="M18" s="193"/>
-      <c r="N18" s="199"/>
-      <c r="O18" s="199"/>
-      <c r="P18" s="193"/>
-      <c r="Q18" s="199"/>
-      <c r="R18" s="206"/>
-      <c r="S18" s="194"/>
-      <c r="T18" s="194"/>
+      <c r="A18" s="161"/>
+      <c r="B18" s="162"/>
+      <c r="C18" s="163"/>
+      <c r="D18" s="164"/>
+      <c r="E18" s="164"/>
+      <c r="F18" s="165"/>
+      <c r="G18" s="162"/>
+      <c r="H18" s="166"/>
+      <c r="I18" s="162"/>
+      <c r="J18" s="167"/>
+      <c r="K18" s="172"/>
+      <c r="L18" s="172"/>
+      <c r="M18" s="166"/>
+      <c r="N18" s="172"/>
+      <c r="O18" s="172"/>
+      <c r="P18" s="166"/>
+      <c r="Q18" s="172"/>
+      <c r="R18" s="179"/>
+      <c r="S18" s="167"/>
+      <c r="T18" s="167"/>
       <c r="U18" s="133"/>
-      <c r="V18" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V18" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W18" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X18" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X18" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="Y18" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z18" t="e">
+      <c r="Z18" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="1:26">
-      <c r="A19" s="188"/>
-      <c r="B19" s="189"/>
-      <c r="C19" s="190"/>
-      <c r="D19" s="191"/>
-      <c r="E19" s="191"/>
-      <c r="F19" s="192"/>
-      <c r="G19" s="189"/>
-      <c r="H19" s="193"/>
-      <c r="I19" s="189"/>
-      <c r="J19" s="193"/>
-      <c r="K19" s="199"/>
-      <c r="L19" s="199"/>
-      <c r="M19" s="195"/>
-      <c r="N19" s="199"/>
-      <c r="O19" s="199"/>
-      <c r="P19" s="194"/>
-      <c r="Q19" s="199"/>
-      <c r="R19" s="206"/>
-      <c r="S19" s="194"/>
-      <c r="T19" s="194"/>
-      <c r="V19" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="A19" s="161"/>
+      <c r="B19" s="162"/>
+      <c r="C19" s="163"/>
+      <c r="D19" s="164"/>
+      <c r="E19" s="164"/>
+      <c r="F19" s="165"/>
+      <c r="G19" s="162"/>
+      <c r="H19" s="166"/>
+      <c r="I19" s="162"/>
+      <c r="J19" s="166"/>
+      <c r="K19" s="172"/>
+      <c r="L19" s="172"/>
+      <c r="M19" s="168"/>
+      <c r="N19" s="172"/>
+      <c r="O19" s="172"/>
+      <c r="P19" s="167"/>
+      <c r="Q19" s="172"/>
+      <c r="R19" s="179"/>
+      <c r="S19" s="167"/>
+      <c r="T19" s="167"/>
+      <c r="V19" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W19" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X19" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X19" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="Y19" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z19" t="e">
+      <c r="Z19" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:26">
-      <c r="A20" s="188"/>
-      <c r="B20" s="189"/>
-      <c r="C20" s="190"/>
-      <c r="D20" s="191"/>
-      <c r="E20" s="191"/>
-      <c r="F20" s="196"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="193"/>
-      <c r="I20" s="189"/>
-      <c r="J20" s="194"/>
-      <c r="K20" s="199"/>
-      <c r="L20" s="199"/>
-      <c r="M20" s="195"/>
-      <c r="N20" s="199"/>
-      <c r="O20" s="199"/>
-      <c r="P20" s="193"/>
-      <c r="Q20" s="199"/>
-      <c r="R20" s="206"/>
-      <c r="S20" s="193"/>
-      <c r="T20" s="189"/>
-      <c r="V20" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="A20" s="161"/>
+      <c r="B20" s="162"/>
+      <c r="C20" s="163"/>
+      <c r="D20" s="164"/>
+      <c r="E20" s="164"/>
+      <c r="F20" s="169"/>
+      <c r="G20" s="162"/>
+      <c r="H20" s="166"/>
+      <c r="I20" s="162"/>
+      <c r="J20" s="167"/>
+      <c r="K20" s="172"/>
+      <c r="L20" s="172"/>
+      <c r="M20" s="168"/>
+      <c r="N20" s="172"/>
+      <c r="O20" s="172"/>
+      <c r="P20" s="166"/>
+      <c r="Q20" s="172"/>
+      <c r="R20" s="179"/>
+      <c r="S20" s="166"/>
+      <c r="T20" s="162"/>
+      <c r="V20" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W20" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X20" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X20" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="Y20" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z20" t="e">
+      <c r="Z20" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:26">
-      <c r="A21" s="188"/>
-      <c r="B21" s="189"/>
-      <c r="C21" s="190"/>
-      <c r="D21" s="191"/>
-      <c r="E21" s="191"/>
-      <c r="F21" s="192"/>
-      <c r="G21" s="189"/>
-      <c r="H21" s="194"/>
-      <c r="I21" s="189"/>
-      <c r="J21" s="194"/>
-      <c r="K21" s="199"/>
-      <c r="L21" s="199"/>
-      <c r="M21" s="194"/>
-      <c r="N21" s="199"/>
-      <c r="O21" s="199"/>
-      <c r="P21" s="194"/>
-      <c r="Q21" s="199"/>
-      <c r="R21" s="206"/>
-      <c r="S21" s="194"/>
-      <c r="T21" s="193"/>
-      <c r="V21" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="A21" s="161"/>
+      <c r="B21" s="162"/>
+      <c r="C21" s="163"/>
+      <c r="D21" s="164"/>
+      <c r="E21" s="164"/>
+      <c r="F21" s="165"/>
+      <c r="G21" s="162"/>
+      <c r="H21" s="167"/>
+      <c r="I21" s="162"/>
+      <c r="J21" s="167"/>
+      <c r="K21" s="172"/>
+      <c r="L21" s="172"/>
+      <c r="M21" s="167"/>
+      <c r="N21" s="172"/>
+      <c r="O21" s="172"/>
+      <c r="P21" s="167"/>
+      <c r="Q21" s="172"/>
+      <c r="R21" s="179"/>
+      <c r="S21" s="167"/>
+      <c r="T21" s="166"/>
+      <c r="V21" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W21" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X21" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X21" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="Y21" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z21" t="e">
+      <c r="Z21" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:26">
-      <c r="V22" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V22" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W22" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X22" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X22" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="Y22" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z22" t="e">
+      <c r="Z22" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="23" spans="1:26">
-      <c r="V23" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V23" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
       <c r="W23" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X23" t="str">
         <f t="shared" si="3"/>
-        <v>DB</v>
-      </c>
-      <c r="X23" t="e">
-        <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
       <c r="Y23" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="Z23" t="e">
+      <c r="Z23" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:26">
-      <c r="V24" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y24">
+      <c r="V24" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W24" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X24" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Y24" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="Z24" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
     </row>
     <row r="25" spans="1:26">
-      <c r="V25" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V25" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W25" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X25" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="Z25" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
     </row>
     <row r="26" spans="1:26">
-      <c r="V26" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V26" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W26" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X26" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="Z26" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
     </row>
     <row r="27" spans="1:26">
-      <c r="V27" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V27" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W27" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X27" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="Z27" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:26">
-      <c r="V28" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V28" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W28" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X28" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
       <c r="Z28" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
     </row>
     <row r="29" spans="1:26">
-      <c r="V29" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V29" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W29" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X29" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Z29" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:26">
-      <c r="V30" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V30" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W30" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X30" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Z30" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
     </row>
     <row r="31" spans="1:26">
-      <c r="V31" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V31" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W31" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X31" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Z31" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
     </row>
     <row r="32" spans="1:26">
-      <c r="V32" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="33" spans="22:22">
-      <c r="V33" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="34" spans="22:22">
-      <c r="V34" s="129" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+      <c r="V32" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W32" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X32" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Z32" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="22:26">
+      <c r="V33" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W33" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X33" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Z33" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="22:26">
+      <c r="V34" s="270" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="W34" t="str">
+        <f t="shared" si="2"/>
+        <v>DB</v>
+      </c>
+      <c r="X34" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="Z34" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -12124,11 +11914,11 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="187"/>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
+      <c r="A2" s="160"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
       <c r="H2" t="str">
         <f>RIGHT(A2,3)</f>
         <v/>
@@ -12141,23 +11931,23 @@
         <f t="shared" ref="J2:J23" si="0">CONCATENATE(B2,"/",H2)</f>
         <v>/</v>
       </c>
-      <c r="L2" t="e">
-        <f>IF(ISNUMBER(VALUE(MID(A2,FIND("-",A2)+1,1))),
+      <c r="L2" t="str">
+        <f>IFERROR(IF(ISNUMBER(VALUE(MID(A2,FIND("-",A2)+1,1))),
 "AGT "&amp;TRIM(MID(A2,FIND("-",A2)+1,FIND("@",SUBSTITUTE(A2,"-","@",LEN(A2)-LEN(SUBSTITUTE(A2,"-",""))))-FIND("-",A2)-1)),
-TRIM(MID(A2,FIND("-",A2)+1,FIND("@",SUBSTITUTE(A2,"-","@",LEN(A2)-LEN(SUBSTITUTE(A2,"-",""))))-FIND("-",A2)-1)))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M2" t="e">
+TRIM(MID(A2,FIND("-",A2)+1,FIND("@",SUBSTITUTE(A2,"-","@",LEN(A2)-LEN(SUBSTITUTE(A2,"-",""))))-FIND("-",A2)-1))),"")</f>
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <f>IF(OR(ISNUMBER(FIND(" ST",L2)),ISNUMBER(FIND(" SM",L2)),ISNUMBER(FIND(" PM",L2)),ISNUMBER(FIND(" TM",L2)),ISNUMBER(FIND(" PG",L2)),ISNUMBER(FIND(" PA",L2))),SUBSTITUTE(L2," ","",1),L2)</f>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="186"/>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
+      <c r="A3" s="159"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
       <c r="H3" t="str">
         <f t="shared" ref="H3:H17" si="1">RIGHT(A3,3)</f>
         <v/>
@@ -12170,23 +11960,23 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L3" t="e">
-        <f>IF(ISNUMBER(VALUE(MID(A3,FIND("-",A3)+1,1))),
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L23" si="3">IFERROR(IF(ISNUMBER(VALUE(MID(A3,FIND("-",A3)+1,1))),
 "AGT "&amp;TRIM(MID(A3,FIND("-",A3)+1,FIND("@",SUBSTITUTE(A3,"-","@",LEN(A3)-LEN(SUBSTITUTE(A3,"-",""))))-FIND("-",A3)-1)),
-TRIM(MID(A3,FIND("-",A3)+1,FIND("@",SUBSTITUTE(A3,"-","@",LEN(A3)-LEN(SUBSTITUTE(A3,"-",""))))-FIND("-",A3)-1)))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M3" t="e">
-        <f t="shared" ref="M3:M23" si="3">IF(OR(ISNUMBER(FIND(" ST",L3)),ISNUMBER(FIND(" SM",L3)),ISNUMBER(FIND(" PM",L3)),ISNUMBER(FIND(" TM",L3)),ISNUMBER(FIND(" PG",L3)),ISNUMBER(FIND(" PA",L3))),SUBSTITUTE(L3," ","",1),L3)</f>
-        <v>#VALUE!</v>
+TRIM(MID(A3,FIND("-",A3)+1,FIND("@",SUBSTITUTE(A3,"-","@",LEN(A3)-LEN(SUBSTITUTE(A3,"-",""))))-FIND("-",A3)-1))),"")</f>
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <f t="shared" ref="M3:M23" si="4">IF(OR(ISNUMBER(FIND(" ST",L3)),ISNUMBER(FIND(" SM",L3)),ISNUMBER(FIND(" PM",L3)),ISNUMBER(FIND(" TM",L3)),ISNUMBER(FIND(" PG",L3)),ISNUMBER(FIND(" PA",L3))),SUBSTITUTE(L3," ","",1),L3)</f>
+        <v/>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="187"/>
-      <c r="B4" s="185"/>
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
       <c r="H4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12199,23 +11989,21 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L4" t="e">
-        <f t="shared" ref="L4:L23" si="4">IF(ISNUMBER(VALUE(MID(A4,FIND("-",A4)+1,1))),
-"AGT "&amp;TRIM(MID(A4,FIND("-",A4)+1,FIND("@",SUBSTITUTE(A4,"-","@",LEN(A4)-LEN(SUBSTITUTE(A4,"-",""))))-FIND("-",A4)-1)),
-TRIM(MID(A4,FIND("-",A4)+1,FIND("@",SUBSTITUTE(A4,"-","@",LEN(A4)-LEN(SUBSTITUTE(A4,"-",""))))-FIND("-",A4)-1)))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M4" t="e">
+      <c r="L4" t="str">
         <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="186"/>
-      <c r="B5" s="184"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
+      <c r="A5" s="159"/>
+      <c r="B5" s="157"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
       <c r="H5" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12228,21 +12016,21 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L5" t="e">
+      <c r="L5" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M5" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="187"/>
-      <c r="B6" s="185"/>
-      <c r="C6" s="185"/>
-      <c r="D6" s="185"/>
-      <c r="E6" s="185"/>
+      <c r="A6" s="160"/>
+      <c r="B6" s="158"/>
+      <c r="C6" s="158"/>
+      <c r="D6" s="158"/>
+      <c r="E6" s="158"/>
       <c r="H6" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12255,21 +12043,21 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L6" t="e">
+      <c r="L6" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M6" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="186"/>
-      <c r="B7" s="184"/>
-      <c r="C7" s="184"/>
-      <c r="D7" s="184"/>
-      <c r="E7" s="184"/>
+      <c r="A7" s="159"/>
+      <c r="B7" s="157"/>
+      <c r="C7" s="157"/>
+      <c r="D7" s="157"/>
+      <c r="E7" s="157"/>
       <c r="H7" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12282,21 +12070,21 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L7" t="e">
+      <c r="L7" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M7" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="187"/>
-      <c r="B8" s="185"/>
-      <c r="C8" s="185"/>
-      <c r="D8" s="185"/>
-      <c r="E8" s="185"/>
+      <c r="A8" s="160"/>
+      <c r="B8" s="158"/>
+      <c r="C8" s="158"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="158"/>
       <c r="H8" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12309,21 +12097,21 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L8" t="e">
+      <c r="L8" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M8" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="186"/>
-      <c r="B9" s="184"/>
-      <c r="C9" s="184"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="184"/>
+      <c r="A9" s="159"/>
+      <c r="B9" s="157"/>
+      <c r="C9" s="157"/>
+      <c r="D9" s="157"/>
+      <c r="E9" s="157"/>
       <c r="H9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12336,21 +12124,21 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L9" t="e">
+      <c r="L9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M9" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="187"/>
-      <c r="B10" s="185"/>
-      <c r="C10" s="185"/>
-      <c r="D10" s="185"/>
-      <c r="E10" s="185"/>
+      <c r="A10" s="160"/>
+      <c r="B10" s="158"/>
+      <c r="C10" s="158"/>
+      <c r="D10" s="158"/>
+      <c r="E10" s="158"/>
       <c r="H10" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12363,21 +12151,21 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L10" t="e">
+      <c r="L10" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M10" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="186"/>
-      <c r="B11" s="184"/>
-      <c r="C11" s="184"/>
-      <c r="D11" s="184"/>
-      <c r="E11" s="184"/>
+      <c r="A11" s="159"/>
+      <c r="B11" s="157"/>
+      <c r="C11" s="157"/>
+      <c r="D11" s="157"/>
+      <c r="E11" s="157"/>
       <c r="H11" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12390,13 +12178,13 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L11" t="e">
+      <c r="L11" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M11" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -12417,13 +12205,13 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L12" t="e">
+      <c r="L12" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M12" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -12444,21 +12232,21 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L13" t="e">
+      <c r="L13" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M13" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="161"/>
-      <c r="B14" s="162"/>
-      <c r="C14" s="163"/>
-      <c r="D14" s="164"/>
-      <c r="E14" s="165"/>
+      <c r="A14" s="286"/>
+      <c r="B14" s="287"/>
+      <c r="C14" s="288"/>
+      <c r="D14" s="288"/>
+      <c r="E14" s="289"/>
       <c r="H14" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12471,21 +12259,21 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L14" t="e">
+      <c r="L14" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M14" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="158"/>
-      <c r="B15" s="157"/>
-      <c r="C15" s="159"/>
-      <c r="D15" s="160"/>
-      <c r="E15" s="166"/>
+      <c r="A15" s="291"/>
+      <c r="B15" s="290"/>
+      <c r="C15" s="290"/>
+      <c r="D15" s="290"/>
+      <c r="E15" s="290"/>
       <c r="H15" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12498,13 +12286,13 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L15" t="e">
+      <c r="L15" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M15" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -12520,13 +12308,13 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L16" t="e">
+      <c r="L16" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M16" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="17" spans="8:13">
@@ -12542,13 +12330,13 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L17" t="e">
+      <c r="L17" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M17" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="8:13">
@@ -12560,13 +12348,13 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L18" t="e">
+      <c r="L18" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M18" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="8:13">
@@ -12578,13 +12366,13 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L19" t="e">
+      <c r="L19" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M19" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M19" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="8:13">
@@ -12596,13 +12384,13 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L20" t="e">
+      <c r="L20" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M20" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M20" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="8:13">
@@ -12614,13 +12402,13 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L21" t="e">
+      <c r="L21" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M21" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M21" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="8:13">
@@ -12632,13 +12420,13 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L22" t="e">
+      <c r="L22" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M22" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M22" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
     <row r="23" spans="8:13">
@@ -12650,13 +12438,13 @@
         <f t="shared" si="0"/>
         <v>/</v>
       </c>
-      <c r="L23" t="e">
+      <c r="L23" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M23" t="str">
         <f t="shared" si="4"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M23" t="e">
-        <f t="shared" si="3"/>
-        <v>#VALUE!</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -12673,182 +12461,224 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9">
-      <c r="A2" s="186"/>
-      <c r="B2" s="184"/>
-      <c r="C2" s="184"/>
+      <c r="A2" s="159"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
       <c r="I2" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A2)), "CLEAF", Deco!W2)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="187"/>
-      <c r="B3" s="185"/>
-      <c r="C3" s="185"/>
+      <c r="A3" s="160"/>
+      <c r="B3" s="158"/>
+      <c r="C3" s="158"/>
       <c r="I3" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A3)), "CLEAF", Deco!W3)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="186"/>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
+      <c r="A4" s="159"/>
+      <c r="B4" s="157"/>
+      <c r="C4" s="157"/>
       <c r="I4" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A4)), "CLEAF", Deco!W4)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="187"/>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
+      <c r="A5" s="160"/>
+      <c r="B5" s="158"/>
+      <c r="C5" s="158"/>
       <c r="I5" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A5)), "CLEAF", Deco!W5)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="186"/>
-      <c r="B6" s="184"/>
-      <c r="C6" s="184"/>
+      <c r="A6" s="159"/>
+      <c r="B6" s="157"/>
+      <c r="C6" s="157"/>
       <c r="I6" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A6)), "CLEAF", Deco!W6)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="187"/>
-      <c r="B7" s="185"/>
-      <c r="C7" s="185"/>
+      <c r="A7" s="160"/>
+      <c r="B7" s="158"/>
+      <c r="C7" s="158"/>
       <c r="I7" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A7)), "CLEAF", Deco!W7)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="186"/>
-      <c r="B8" s="184"/>
-      <c r="C8" s="184"/>
+      <c r="A8" s="159"/>
+      <c r="B8" s="157"/>
+      <c r="C8" s="157"/>
       <c r="I8" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A8)), "CLEAF", Deco!W8)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="187"/>
-      <c r="B9" s="185"/>
-      <c r="C9" s="185"/>
+      <c r="A9" s="160"/>
+      <c r="B9" s="158"/>
+      <c r="C9" s="158"/>
       <c r="I9" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A9)), "CLEAF", Deco!W9)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="186"/>
-      <c r="B10" s="184"/>
-      <c r="C10" s="184"/>
-      <c r="D10" s="184"/>
+      <c r="A10" s="159"/>
+      <c r="B10" s="157"/>
+      <c r="C10" s="157"/>
+      <c r="D10" s="157"/>
       <c r="I10" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A10)), "CLEAF", Deco!W10)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="187"/>
-      <c r="B11" s="185"/>
-      <c r="C11" s="185"/>
-      <c r="D11" s="185"/>
+      <c r="A11" s="160"/>
+      <c r="B11" s="158"/>
+      <c r="C11" s="158"/>
+      <c r="D11" s="158"/>
       <c r="I11" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A11)), "CLEAF", Deco!W11)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="186"/>
-      <c r="B12" s="184"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
+      <c r="A12" s="294"/>
+      <c r="B12" s="293"/>
+      <c r="C12" s="293"/>
+      <c r="D12" s="292"/>
       <c r="I12" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A12)), "CLEAF", Deco!W12)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="187"/>
-      <c r="B13" s="185"/>
-      <c r="C13" s="185"/>
-      <c r="D13" s="185"/>
+      <c r="A13" s="296"/>
+      <c r="B13" s="295"/>
+      <c r="C13" s="295"/>
+      <c r="D13" s="295"/>
       <c r="I13" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A13)), "CLEAF", Deco!W13)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="186"/>
-      <c r="B14" s="184"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="184"/>
+      <c r="A14" s="297"/>
+      <c r="B14" s="297"/>
+      <c r="C14" s="297"/>
+      <c r="D14" s="297"/>
       <c r="I14" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A14)), "CLEAF", Deco!W14)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="187"/>
-      <c r="B15" s="185"/>
-      <c r="C15" s="185"/>
-      <c r="D15" s="185"/>
+      <c r="A15" s="297"/>
+      <c r="B15" s="297"/>
+      <c r="C15" s="297"/>
+      <c r="D15" s="297"/>
       <c r="I15" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A15)), "CLEAF", Deco!W15)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="16" spans="1:9">
+      <c r="A16" s="297"/>
+      <c r="B16" s="297"/>
+      <c r="C16" s="297"/>
+      <c r="D16" s="297"/>
       <c r="I16" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A16)), "CLEAF", Deco!W16)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="17" spans="9:9">
+    <row r="17" spans="1:9">
+      <c r="A17" s="297"/>
+      <c r="B17" s="297"/>
+      <c r="C17" s="297"/>
+      <c r="D17" s="297"/>
       <c r="I17" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A17)), "CLEAF", Deco!W17)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="18" spans="9:9">
+    <row r="18" spans="1:9">
+      <c r="A18" s="297"/>
+      <c r="B18" s="297"/>
+      <c r="C18" s="297"/>
+      <c r="D18" s="297"/>
       <c r="I18" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A18)), "CLEAF", Deco!W18)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="19" spans="9:9">
+    <row r="19" spans="1:9">
       <c r="I19" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A19)), "CLEAF", Deco!W19)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="20" spans="9:9">
+    <row r="20" spans="1:9">
       <c r="I20" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A20)), "CLEAF", Deco!W20)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="21" spans="9:9">
+    <row r="21" spans="1:9">
       <c r="I21" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A21)), "CLEAF", Deco!W21)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="22" spans="9:9">
+    <row r="22" spans="1:9">
       <c r="I22" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A22)), "CLEAF", Deco!W22)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="23" spans="9:9">
+    <row r="23" spans="1:9">
       <c r="I23" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A23)), "CLEAF", Deco!W23)</f>
+        <v>DB</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="I24" t="str">
+        <f>IF(ISNUMBER(SEARCH("CLMEL", A24)), "CLEAF", Deco!W24)</f>
+        <v>DB</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="I25" t="str">
+        <f>IF(ISNUMBER(SEARCH("CLMEL", A25)), "CLEAF", Deco!W25)</f>
+        <v>DB</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="I26" t="str">
+        <f>IF(ISNUMBER(SEARCH("CLMEL", A26)), "CLEAF", Deco!W26)</f>
+        <v>DB</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="I27" t="str">
+        <f>IF(ISNUMBER(SEARCH("CLMEL", A27)), "CLEAF", Deco!W27)</f>
+        <v>DB</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="I28" t="str">
+        <f>IF(ISNUMBER(SEARCH("CLMEL", A28)), "CLEAF", Deco!W28)</f>
         <v>DB</v>
       </c>
     </row>
@@ -12864,336 +12694,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C73D6DF-483A-44BF-8CA8-51845992196D}">
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="155.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="25.5" customHeight="1">
-      <c r="A1" s="297" t="s">
-        <v>131</v>
-      </c>
-      <c r="B1" s="297"/>
-      <c r="C1" s="297"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1"/>
-    <row r="3" spans="1:3" ht="15.75" thickBot="1">
-      <c r="A3" s="177" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="178" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" s="84" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="18.75">
-      <c r="A4" s="167">
-        <v>1</v>
-      </c>
-      <c r="B4" s="168" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="169"/>
-    </row>
-    <row r="5" spans="1:3" ht="18.75">
-      <c r="A5" s="170">
-        <v>2</v>
-      </c>
-      <c r="B5" s="171" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5" s="172"/>
-    </row>
-    <row r="6" spans="1:3" ht="18.75">
-      <c r="A6" s="170">
-        <v>3</v>
-      </c>
-      <c r="B6" s="171" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="172"/>
-    </row>
-    <row r="7" spans="1:3" ht="18.75">
-      <c r="A7" s="170">
-        <v>4</v>
-      </c>
-      <c r="B7" s="171" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="172"/>
-    </row>
-    <row r="8" spans="1:3" ht="18.75">
-      <c r="A8" s="170">
-        <v>5</v>
-      </c>
-      <c r="B8" s="171" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="172"/>
-    </row>
-    <row r="9" spans="1:3" ht="18.75">
-      <c r="A9" s="170">
-        <v>6</v>
-      </c>
-      <c r="B9" s="171" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9" s="172"/>
-    </row>
-    <row r="10" spans="1:3" ht="18.75">
-      <c r="A10" s="170">
-        <v>7</v>
-      </c>
-      <c r="B10" s="171" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="172"/>
-    </row>
-    <row r="11" spans="1:3" ht="18.75">
-      <c r="A11" s="170">
-        <v>8</v>
-      </c>
-      <c r="B11" s="171" t="s">
-        <v>130</v>
-      </c>
-      <c r="C11" s="172"/>
-    </row>
-    <row r="12" spans="1:3" ht="18.75">
-      <c r="A12" s="170">
-        <v>9</v>
-      </c>
-      <c r="B12" s="173" t="s">
-        <v>116</v>
-      </c>
-      <c r="C12" s="172"/>
-    </row>
-    <row r="13" spans="1:3" ht="18.75">
-      <c r="A13" s="170">
-        <v>10</v>
-      </c>
-      <c r="B13" s="173" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="172"/>
-    </row>
-    <row r="14" spans="1:3" ht="19.5" thickBot="1">
-      <c r="A14" s="174">
-        <v>11</v>
-      </c>
-      <c r="B14" s="175" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="176"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="179" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="180">
-        <f>IF(AND(C4="Da",C5="Da",C6="Da",C7="Da",C8="Da",C9="Da",C10="Da",C11="Da",C12="Da",C13="Da",C14="Da"),2,IF(OR(C4="Nu",C5="Nu",C6="Nu",C7="Nu",C8="Nu",C9="nu",C10="Nu",C11="Nu",C12="Nu",C13="Nu",C14="Nu"),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="181"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="B20">
-    <cfRule type="iconSet" priority="1">
-      <iconSet>
-        <cfvo type="percent" val="0"/>
-        <cfvo type="num" val="1"/>
-        <cfvo type="num" val="2"/>
-      </iconSet>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E4C28A07-E9B0-4616-B938-E635BBCAEA09}">
-          <x14:formula1>
-            <xm:f>Parametri!$G$2:$G$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>C4:C15</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73BEC0EC-3A12-46E9-B4E0-C75D48E79ED4}">
-  <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="135.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1">
-      <c r="B1" s="298" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="183"/>
-      <c r="D1" s="183"/>
-      <c r="E1" s="183"/>
-      <c r="F1" s="183"/>
-      <c r="G1" s="183"/>
-      <c r="H1" s="183"/>
-      <c r="I1" s="183"/>
-      <c r="J1" s="183"/>
-      <c r="K1" s="183"/>
-      <c r="L1" s="183"/>
-      <c r="M1" s="183"/>
-      <c r="N1" s="183"/>
-      <c r="O1" s="183"/>
-      <c r="P1" s="183"/>
-    </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1">
-      <c r="B2" s="298"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
-      <c r="M2" s="183"/>
-      <c r="N2" s="183"/>
-      <c r="O2" s="183"/>
-      <c r="P2" s="183"/>
-    </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1">
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="182"/>
-      <c r="M3" s="182"/>
-      <c r="N3" s="182"/>
-      <c r="O3" s="182"/>
-      <c r="P3" s="182"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="A14">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="A15">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
-        <v>144</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:B2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1340A89A-E89E-466F-87D6-BAD428C7D38A}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -13225,7 +12725,7 @@
         <v>109</v>
       </c>
       <c r="G1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -13248,7 +12748,7 @@
         <v>112</v>
       </c>
       <c r="G2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -13262,7 +12762,7 @@
         <v>113</v>
       </c>
       <c r="G3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:7">

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15A2125F-AD76-40EB-873C-DD295E338771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54099AFB-E8E6-455C-A301-A34138B4FFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -375,9 +375,6 @@
     <t>Cant 43/1</t>
   </si>
   <si>
-    <t>Nr. Piese Dublaje</t>
-  </si>
-  <si>
     <t>CUT CLEAF</t>
   </si>
   <si>
@@ -445,6 +442,9 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Status  Dublaj</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1290,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="298">
+  <cellXfs count="271">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1802,6 +1802,7 @@
     <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2092,64 +2093,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2177,78 +2120,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>11205</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7844F070-EFAE-D559-F4AE-D02C99DA728E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="906555" y="8372475"/>
-          <a:ext cx="13657170" cy="1504950"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2698,37 +2569,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="239" t="s">
+      <c r="A1" s="240" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="240"/>
-      <c r="C1" s="240"/>
-      <c r="D1" s="240"/>
-      <c r="E1" s="240"/>
-      <c r="F1" s="240"/>
-      <c r="G1" s="240"/>
-      <c r="H1" s="240"/>
-      <c r="I1" s="240"/>
-      <c r="J1" s="240"/>
-      <c r="K1" s="240"/>
-      <c r="L1" s="241"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="241"/>
+      <c r="H1" s="241"/>
+      <c r="I1" s="241"/>
+      <c r="J1" s="241"/>
+      <c r="K1" s="241"/>
+      <c r="L1" s="242"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="224" t="s">
+      <c r="O1" s="225" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="225"/>
-      <c r="R1" s="225"/>
-      <c r="S1" s="226"/>
+      <c r="P1" s="226"/>
+      <c r="Q1" s="226"/>
+      <c r="R1" s="226"/>
+      <c r="S1" s="227"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
@@ -2743,165 +2614,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="85"/>
-      <c r="O2" s="227"/>
-      <c r="P2" s="228"/>
-      <c r="Q2" s="228"/>
-      <c r="R2" s="228"/>
-      <c r="S2" s="229"/>
+      <c r="O2" s="228"/>
+      <c r="P2" s="229"/>
+      <c r="Q2" s="229"/>
+      <c r="R2" s="229"/>
+      <c r="S2" s="230"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="247"/>
-      <c r="C3" s="248"/>
-      <c r="D3" s="249"/>
+      <c r="B3" s="248"/>
+      <c r="C3" s="249"/>
+      <c r="D3" s="250"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="180"/>
-      <c r="J3" s="181"/>
-      <c r="K3" s="182"/>
+      <c r="I3" s="181"/>
+      <c r="J3" s="182"/>
+      <c r="K3" s="183"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="77"/>
-      <c r="O3" s="242"/>
-      <c r="P3" s="243"/>
-      <c r="Q3" s="243"/>
-      <c r="R3" s="243"/>
-      <c r="S3" s="244"/>
+      <c r="O3" s="243"/>
+      <c r="P3" s="244"/>
+      <c r="Q3" s="244"/>
+      <c r="R3" s="244"/>
+      <c r="S3" s="245"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="218"/>
-      <c r="C4" s="219"/>
-      <c r="D4" s="220"/>
+      <c r="B4" s="219"/>
+      <c r="C4" s="220"/>
+      <c r="D4" s="221"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="221"/>
-      <c r="J4" s="222"/>
-      <c r="K4" s="223"/>
+      <c r="I4" s="222"/>
+      <c r="J4" s="223"/>
+      <c r="K4" s="224"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="77"/>
-      <c r="O4" s="242"/>
-      <c r="P4" s="243"/>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="244"/>
+      <c r="O4" s="243"/>
+      <c r="P4" s="244"/>
+      <c r="Q4" s="244"/>
+      <c r="R4" s="244"/>
+      <c r="S4" s="245"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="257"/>
-      <c r="C5" s="258"/>
-      <c r="D5" s="259"/>
+      <c r="B5" s="258"/>
+      <c r="C5" s="259"/>
+      <c r="D5" s="260"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="266"/>
-      <c r="J5" s="243"/>
-      <c r="K5" s="244"/>
+      <c r="I5" s="267"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="245"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="77"/>
-      <c r="O5" s="242"/>
-      <c r="P5" s="243"/>
-      <c r="Q5" s="243"/>
-      <c r="R5" s="243"/>
-      <c r="S5" s="244"/>
+      <c r="O5" s="243"/>
+      <c r="P5" s="244"/>
+      <c r="Q5" s="244"/>
+      <c r="R5" s="244"/>
+      <c r="S5" s="245"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="262"/>
-      <c r="C6" s="263"/>
-      <c r="D6" s="264"/>
+      <c r="B6" s="263"/>
+      <c r="C6" s="264"/>
+      <c r="D6" s="265"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="265"/>
-      <c r="J6" s="231"/>
-      <c r="K6" s="232"/>
+      <c r="I6" s="266"/>
+      <c r="J6" s="232"/>
+      <c r="K6" s="233"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="78"/>
-      <c r="O6" s="230"/>
-      <c r="P6" s="231"/>
-      <c r="Q6" s="231"/>
-      <c r="R6" s="231"/>
-      <c r="S6" s="232"/>
+      <c r="O6" s="231"/>
+      <c r="P6" s="232"/>
+      <c r="Q6" s="232"/>
+      <c r="R6" s="232"/>
+      <c r="S6" s="233"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="186" t="s">
+      <c r="A8" s="187" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="187"/>
-      <c r="C8" s="187"/>
-      <c r="D8" s="188"/>
-      <c r="F8" s="233" t="s">
+      <c r="B8" s="188"/>
+      <c r="C8" s="188"/>
+      <c r="D8" s="189"/>
+      <c r="F8" s="234" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="234"/>
-      <c r="H8" s="234"/>
-      <c r="I8" s="234"/>
-      <c r="J8" s="234"/>
-      <c r="K8" s="234"/>
-      <c r="L8" s="234"/>
-      <c r="M8" s="234"/>
-      <c r="N8" s="234"/>
-      <c r="O8" s="234"/>
-      <c r="P8" s="234"/>
-      <c r="Q8" s="234"/>
-      <c r="R8" s="234"/>
-      <c r="S8" s="235"/>
+      <c r="G8" s="235"/>
+      <c r="H8" s="235"/>
+      <c r="I8" s="235"/>
+      <c r="J8" s="235"/>
+      <c r="K8" s="235"/>
+      <c r="L8" s="235"/>
+      <c r="M8" s="235"/>
+      <c r="N8" s="235"/>
+      <c r="O8" s="235"/>
+      <c r="P8" s="235"/>
+      <c r="Q8" s="235"/>
+      <c r="R8" s="235"/>
+      <c r="S8" s="236"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="189"/>
-      <c r="B9" s="190"/>
-      <c r="C9" s="190"/>
-      <c r="D9" s="191"/>
-      <c r="F9" s="214" t="s">
+      <c r="A9" s="190"/>
+      <c r="B9" s="191"/>
+      <c r="C9" s="191"/>
+      <c r="D9" s="192"/>
+      <c r="F9" s="215" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="215"/>
-      <c r="H9" s="260" t="s">
+      <c r="G9" s="216"/>
+      <c r="H9" s="261" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="261"/>
-      <c r="J9" s="212" t="s">
+      <c r="I9" s="262"/>
+      <c r="J9" s="213" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="213"/>
-      <c r="L9" s="255" t="s">
+      <c r="K9" s="214"/>
+      <c r="L9" s="256" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="256"/>
-      <c r="N9" s="192" t="s">
+      <c r="M9" s="257"/>
+      <c r="N9" s="193" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="193"/>
-      <c r="P9" s="207" t="s">
+      <c r="O9" s="194"/>
+      <c r="P9" s="208" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="208"/>
-      <c r="R9" s="192" t="s">
+      <c r="Q9" s="209"/>
+      <c r="R9" s="193" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="193"/>
+      <c r="S9" s="194"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="245" t="s">
+      <c r="A10" s="246" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2958,7 +2829,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="184"/>
+      <c r="A11" s="185"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2973,11 +2844,11 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="87" t="str">
-        <f t="shared" ref="F11:F13" si="0" xml:space="preserve"> IF(OR(
+        <f xml:space="preserve"> IF(OR(
       ISNUMBER(--RIGHT(B11,1)),
       RIGHT(B11,2)="SM",
       RIGHT(B11,2)="PM",
-      RIGHT(B11,2)="PG",
+      RIGHT(B11,2)="PG", RIGHT(B11,2)="PA",
       RIGHT(B11,2)="mm",
       RIGHT(B11,2)="mp"
    ),B11,
@@ -3044,7 +2915,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="184"/>
+      <c r="A12" s="185"/>
       <c r="B12" s="135" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3059,7 +2930,15 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="87" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="F12:F23" si="0" xml:space="preserve"> IF(OR(
+      ISNUMBER(--RIGHT(B12,1)),
+      RIGHT(B12,2)="SM",
+      RIGHT(B12,2)="PM",
+      RIGHT(B12,2)="PG", RIGHT(B12,2)="PA",
+      RIGHT(B12,2)="mm",
+      RIGHT(B12,2)="mp"
+   ),B12,
+   LEFT(B12,7))</f>
         <v/>
       </c>
       <c r="G12" s="137" t="str">
@@ -3122,7 +3001,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="184"/>
+      <c r="A13" s="185"/>
       <c r="B13" s="135" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3200,7 +3079,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="184"/>
+      <c r="A14" s="185"/>
       <c r="B14" s="135" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3215,15 +3094,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="87" t="str">
-        <f t="shared" ref="F14:F22" si="7" xml:space="preserve"> IF(OR(
-      ISNUMBER(--RIGHT(B14,1)),
-      RIGHT(B14,2)="SM",
-      RIGHT(B14,2)="PM",
-      RIGHT(B14,2)="PG",
-      RIGHT(B14,2)="mm",
-      RIGHT(B14,2)="mp"
-   ),B14,
-   LEFT(B14,7))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G14" s="137" t="str">
@@ -3286,7 +3157,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="184"/>
+      <c r="A15" s="185"/>
       <c r="B15" s="135" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3301,7 +3172,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G15" s="137" t="str">
@@ -3364,7 +3235,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="184"/>
+      <c r="A16" s="185"/>
       <c r="B16" s="135" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3379,7 +3250,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G16" s="137" t="str">
@@ -3442,7 +3313,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="184"/>
+      <c r="A17" s="185"/>
       <c r="B17" s="135" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3457,7 +3328,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G17" s="137" t="str">
@@ -3520,7 +3391,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="184"/>
+      <c r="A18" s="185"/>
       <c r="B18" s="135" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3535,7 +3406,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G18" s="137" t="str">
@@ -3598,7 +3469,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="184"/>
+      <c r="A19" s="185"/>
       <c r="B19" s="135" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3613,7 +3484,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G19" s="137" t="str">
@@ -3676,7 +3547,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="184"/>
+      <c r="A20" s="185"/>
       <c r="B20" s="135" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3691,7 +3562,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G20" s="137" t="str">
@@ -3754,7 +3625,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="184"/>
+      <c r="A21" s="185"/>
       <c r="B21" s="135" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3769,7 +3640,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G21" s="137" t="str">
@@ -3832,7 +3703,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="246"/>
+      <c r="A22" s="247"/>
       <c r="B22" s="135" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3847,7 +3718,7 @@
       </c>
       <c r="E22" s="79"/>
       <c r="F22" s="87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="G22" s="137" t="str">
@@ -3918,7 +3789,10 @@
         <v>mp</v>
       </c>
       <c r="E23" s="49"/>
-      <c r="F23" s="89"/>
+      <c r="F23" s="87" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="G23" s="90"/>
       <c r="H23" s="102"/>
       <c r="I23" s="148" t="str">
@@ -3952,7 +3826,7 @@
       <c r="S23" s="60"/>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="245" t="s">
+      <c r="A24" s="246" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3973,7 +3847,7 @@
       ISNUMBER(--RIGHT(B24,1)),
       RIGHT(B24,2)="SM",
       RIGHT(B24,2)="PM",
-      RIGHT(B24,2)="PG",
+      RIGHT(B24,2)="PG",RIGHT(B24,2)="PA",
       RIGHT(B24,2)="mm",
       RIGHT(B24,2)="mp"
    ),B24,
@@ -4040,7 +3914,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="184"/>
+      <c r="A25" s="185"/>
       <c r="B25" s="71" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4059,7 +3933,7 @@
       ISNUMBER(--RIGHT(B25,1)),
       RIGHT(B25,2)="SM",
       RIGHT(B25,2)="PM",
-      RIGHT(B25,2)="PG",
+      RIGHT(B25,2)="PG",RIGHT(B25,2)="PA",
       RIGHT(B25,2)="mm",
       RIGHT(B25,2)="mp"
    ),B25,
@@ -4126,7 +4000,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="184"/>
+      <c r="A26" s="185"/>
       <c r="B26" s="71" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4141,11 +4015,11 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="87" t="str">
-        <f xml:space="preserve"> IF(OR(
+        <f t="shared" ref="F26:F28" si="7" xml:space="preserve"> IF(OR(
       ISNUMBER(--RIGHT(B26,1)),
       RIGHT(B26,2)="SM",
       RIGHT(B26,2)="PM",
-      RIGHT(B26,2)="PG",
+      RIGHT(B26,2)="PG",RIGHT(B26,2)="PA",
       RIGHT(B26,2)="mm",
       RIGHT(B26,2)="mp"
    ),B26,
@@ -4212,7 +4086,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="184"/>
+      <c r="A27" s="185"/>
       <c r="B27" s="71" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4227,15 +4101,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="87" t="str">
-        <f xml:space="preserve"> IF(OR(
-      ISNUMBER(--RIGHT(B27,1)),
-      RIGHT(B27,2)="SM",
-      RIGHT(B27,2)="PM",
-      RIGHT(B27,2)="PG",
-      RIGHT(B27,2)="mm",
-      RIGHT(B27,2)="mp"
-   ),B27,
-   LEFT(B27,7))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G27" s="88" t="str">
@@ -4298,7 +4164,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="185"/>
+      <c r="A28" s="186"/>
       <c r="B28" s="71" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4312,16 +4178,8 @@
         <v>mp</v>
       </c>
       <c r="E28" s="79"/>
-      <c r="F28" s="93" t="str">
-        <f xml:space="preserve"> IF(OR(
-      ISNUMBER(--RIGHT(B28,1)),
-      RIGHT(B28,2)="SM",
-      RIGHT(B28,2)="PM",
-      RIGHT(B28,2)="PG",
-      RIGHT(B28,2)="mm",
-      RIGHT(B28,2)="mp"
-   ),B28,
-   LEFT(B28,7))</f>
+      <c r="F28" s="87" t="str">
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G28" s="143" t="str">
@@ -4459,7 +4317,7 @@
       <c r="S31" s="81"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="209" t="s">
+      <c r="A32" s="210" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4532,7 +4390,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="210"/>
+      <c r="A33" s="211"/>
       <c r="B33" s="71" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4603,7 +4461,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="211"/>
+      <c r="A34" s="212"/>
       <c r="B34" s="71" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4695,7 +4553,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="209" t="s">
+      <c r="A36" s="210" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4768,7 +4626,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="210"/>
+      <c r="A37" s="211"/>
       <c r="B37" s="71" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4839,7 +4697,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="211"/>
+      <c r="A38" s="212"/>
       <c r="B38" s="72" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4924,7 +4782,7 @@
       <c r="Q39" s="65"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="245" t="s">
+      <c r="A40" s="246" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4936,25 +4794,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="236" t="s">
+      <c r="F40" s="237" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="237"/>
-      <c r="H40" s="237"/>
-      <c r="I40" s="237"/>
-      <c r="J40" s="237"/>
-      <c r="K40" s="237"/>
-      <c r="L40" s="237"/>
-      <c r="M40" s="237"/>
-      <c r="N40" s="237"/>
-      <c r="O40" s="237"/>
-      <c r="P40" s="237"/>
-      <c r="Q40" s="237"/>
-      <c r="R40" s="237"/>
-      <c r="S40" s="238"/>
+      <c r="G40" s="238"/>
+      <c r="H40" s="238"/>
+      <c r="I40" s="238"/>
+      <c r="J40" s="238"/>
+      <c r="K40" s="238"/>
+      <c r="L40" s="238"/>
+      <c r="M40" s="238"/>
+      <c r="N40" s="238"/>
+      <c r="O40" s="238"/>
+      <c r="P40" s="238"/>
+      <c r="Q40" s="238"/>
+      <c r="R40" s="238"/>
+      <c r="S40" s="239"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="184"/>
+      <c r="A41" s="185"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -5017,7 +4875,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="184"/>
+      <c r="A42" s="185"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5045,7 +4903,7 @@
       <c r="S42" s="84"/>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="184"/>
+      <c r="A43" s="185"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5057,25 +4915,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="233" t="s">
-        <v>94</v>
-      </c>
-      <c r="G43" s="234"/>
-      <c r="H43" s="234"/>
-      <c r="I43" s="234"/>
-      <c r="J43" s="234"/>
-      <c r="K43" s="234"/>
-      <c r="L43" s="234"/>
-      <c r="M43" s="234"/>
-      <c r="N43" s="234"/>
-      <c r="O43" s="234"/>
-      <c r="P43" s="234"/>
-      <c r="Q43" s="234"/>
-      <c r="R43" s="234"/>
-      <c r="S43" s="235"/>
+      <c r="F43" s="234" t="str">
+        <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
+        <v>Nr. Piese Dublaje</v>
+      </c>
+      <c r="G43" s="235"/>
+      <c r="H43" s="235"/>
+      <c r="I43" s="235"/>
+      <c r="J43" s="235"/>
+      <c r="K43" s="235"/>
+      <c r="L43" s="235"/>
+      <c r="M43" s="235"/>
+      <c r="N43" s="235"/>
+      <c r="O43" s="235"/>
+      <c r="P43" s="235"/>
+      <c r="Q43" s="235"/>
+      <c r="R43" s="235"/>
+      <c r="S43" s="236"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="184"/>
+      <c r="A44" s="185"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5131,7 +4990,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="184"/>
+      <c r="A45" s="185"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5202,7 +5061,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="184"/>
+      <c r="A46" s="185"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5216,7 +5075,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="184"/>
+      <c r="A47" s="185"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5227,34 +5086,34 @@
       <c r="D47" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="203" t="s">
+      <c r="F47" s="204" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="216" t="str">
+      <c r="G47" s="217" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="203" t="s">
+      <c r="J47" s="204" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="205">
+      <c r="K47" s="206">
         <v>1</v>
       </c>
-      <c r="N47" s="203" t="s">
-        <v>111</v>
-      </c>
-      <c r="O47" s="251"/>
-      <c r="P47" s="252"/>
-      <c r="R47" s="203" t="s">
-        <v>117</v>
-      </c>
-      <c r="S47" s="203" t="e">
+      <c r="N47" s="204" t="s">
+        <v>110</v>
+      </c>
+      <c r="O47" s="252"/>
+      <c r="P47" s="253"/>
+      <c r="R47" s="204" t="s">
+        <v>116</v>
+      </c>
+      <c r="S47" s="204" t="e">
         <f>IF(#REF!=2,"O","X")</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="185"/>
+      <c r="A48" s="186"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5265,15 +5124,15 @@
       <c r="D48" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="204"/>
-      <c r="G48" s="217"/>
-      <c r="J48" s="204"/>
-      <c r="K48" s="206"/>
-      <c r="N48" s="250"/>
-      <c r="O48" s="253"/>
-      <c r="P48" s="254"/>
-      <c r="R48" s="250"/>
-      <c r="S48" s="204"/>
+      <c r="F48" s="205"/>
+      <c r="G48" s="218"/>
+      <c r="J48" s="205"/>
+      <c r="K48" s="207"/>
+      <c r="N48" s="251"/>
+      <c r="O48" s="254"/>
+      <c r="P48" s="255"/>
+      <c r="R48" s="251"/>
+      <c r="S48" s="205"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5282,174 +5141,174 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="183" t="s">
+      <c r="A50" s="184" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="194"/>
-      <c r="C50" s="195"/>
-      <c r="D50" s="195"/>
-      <c r="E50" s="195"/>
-      <c r="F50" s="195"/>
-      <c r="G50" s="195"/>
-      <c r="H50" s="195"/>
-      <c r="I50" s="195"/>
-      <c r="J50" s="195"/>
-      <c r="K50" s="195"/>
-      <c r="L50" s="195"/>
-      <c r="M50" s="195"/>
-      <c r="N50" s="195"/>
-      <c r="O50" s="195"/>
-      <c r="P50" s="195"/>
-      <c r="Q50" s="195"/>
-      <c r="R50" s="195"/>
-      <c r="S50" s="196"/>
+      <c r="B50" s="195"/>
+      <c r="C50" s="196"/>
+      <c r="D50" s="196"/>
+      <c r="E50" s="196"/>
+      <c r="F50" s="196"/>
+      <c r="G50" s="196"/>
+      <c r="H50" s="196"/>
+      <c r="I50" s="196"/>
+      <c r="J50" s="196"/>
+      <c r="K50" s="196"/>
+      <c r="L50" s="196"/>
+      <c r="M50" s="196"/>
+      <c r="N50" s="196"/>
+      <c r="O50" s="196"/>
+      <c r="P50" s="196"/>
+      <c r="Q50" s="196"/>
+      <c r="R50" s="196"/>
+      <c r="S50" s="197"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="184"/>
-      <c r="B51" s="197"/>
-      <c r="C51" s="198"/>
-      <c r="D51" s="198"/>
-      <c r="E51" s="198"/>
-      <c r="F51" s="198"/>
-      <c r="G51" s="198"/>
-      <c r="H51" s="198"/>
-      <c r="I51" s="198"/>
-      <c r="J51" s="198"/>
-      <c r="K51" s="198"/>
-      <c r="L51" s="198"/>
-      <c r="M51" s="198"/>
-      <c r="N51" s="198"/>
-      <c r="O51" s="198"/>
-      <c r="P51" s="198"/>
-      <c r="Q51" s="198"/>
-      <c r="R51" s="198"/>
-      <c r="S51" s="199"/>
+      <c r="A51" s="185"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="199"/>
+      <c r="D51" s="199"/>
+      <c r="E51" s="199"/>
+      <c r="F51" s="199"/>
+      <c r="G51" s="199"/>
+      <c r="H51" s="199"/>
+      <c r="I51" s="199"/>
+      <c r="J51" s="199"/>
+      <c r="K51" s="199"/>
+      <c r="L51" s="199"/>
+      <c r="M51" s="199"/>
+      <c r="N51" s="199"/>
+      <c r="O51" s="199"/>
+      <c r="P51" s="199"/>
+      <c r="Q51" s="199"/>
+      <c r="R51" s="199"/>
+      <c r="S51" s="200"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="184"/>
-      <c r="B52" s="197"/>
-      <c r="C52" s="198"/>
-      <c r="D52" s="198"/>
-      <c r="E52" s="198"/>
-      <c r="F52" s="198"/>
-      <c r="G52" s="198"/>
-      <c r="H52" s="198"/>
-      <c r="I52" s="198"/>
-      <c r="J52" s="198"/>
-      <c r="K52" s="198"/>
-      <c r="L52" s="198"/>
-      <c r="M52" s="198"/>
-      <c r="N52" s="198"/>
-      <c r="O52" s="198"/>
-      <c r="P52" s="198"/>
-      <c r="Q52" s="198"/>
-      <c r="R52" s="198"/>
-      <c r="S52" s="199"/>
+      <c r="A52" s="185"/>
+      <c r="B52" s="198"/>
+      <c r="C52" s="199"/>
+      <c r="D52" s="199"/>
+      <c r="E52" s="199"/>
+      <c r="F52" s="199"/>
+      <c r="G52" s="199"/>
+      <c r="H52" s="199"/>
+      <c r="I52" s="199"/>
+      <c r="J52" s="199"/>
+      <c r="K52" s="199"/>
+      <c r="L52" s="199"/>
+      <c r="M52" s="199"/>
+      <c r="N52" s="199"/>
+      <c r="O52" s="199"/>
+      <c r="P52" s="199"/>
+      <c r="Q52" s="199"/>
+      <c r="R52" s="199"/>
+      <c r="S52" s="200"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="184"/>
-      <c r="B53" s="197"/>
-      <c r="C53" s="198"/>
-      <c r="D53" s="198"/>
-      <c r="E53" s="198"/>
-      <c r="F53" s="198"/>
-      <c r="G53" s="198"/>
-      <c r="H53" s="198"/>
-      <c r="I53" s="198"/>
-      <c r="J53" s="198"/>
-      <c r="K53" s="198"/>
-      <c r="L53" s="198"/>
-      <c r="M53" s="198"/>
-      <c r="N53" s="198"/>
-      <c r="O53" s="198"/>
-      <c r="P53" s="198"/>
-      <c r="Q53" s="198"/>
-      <c r="R53" s="198"/>
-      <c r="S53" s="199"/>
+      <c r="A53" s="185"/>
+      <c r="B53" s="198"/>
+      <c r="C53" s="199"/>
+      <c r="D53" s="199"/>
+      <c r="E53" s="199"/>
+      <c r="F53" s="199"/>
+      <c r="G53" s="199"/>
+      <c r="H53" s="199"/>
+      <c r="I53" s="199"/>
+      <c r="J53" s="199"/>
+      <c r="K53" s="199"/>
+      <c r="L53" s="199"/>
+      <c r="M53" s="199"/>
+      <c r="N53" s="199"/>
+      <c r="O53" s="199"/>
+      <c r="P53" s="199"/>
+      <c r="Q53" s="199"/>
+      <c r="R53" s="199"/>
+      <c r="S53" s="200"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="184"/>
-      <c r="B54" s="197"/>
-      <c r="C54" s="198"/>
-      <c r="D54" s="198"/>
-      <c r="E54" s="198"/>
-      <c r="F54" s="198"/>
-      <c r="G54" s="198"/>
-      <c r="H54" s="198"/>
-      <c r="I54" s="198"/>
-      <c r="J54" s="198"/>
-      <c r="K54" s="198"/>
-      <c r="L54" s="198"/>
-      <c r="M54" s="198"/>
-      <c r="N54" s="198"/>
-      <c r="O54" s="198"/>
-      <c r="P54" s="198"/>
-      <c r="Q54" s="198"/>
-      <c r="R54" s="198"/>
-      <c r="S54" s="199"/>
+      <c r="A54" s="185"/>
+      <c r="B54" s="198"/>
+      <c r="C54" s="199"/>
+      <c r="D54" s="199"/>
+      <c r="E54" s="199"/>
+      <c r="F54" s="199"/>
+      <c r="G54" s="199"/>
+      <c r="H54" s="199"/>
+      <c r="I54" s="199"/>
+      <c r="J54" s="199"/>
+      <c r="K54" s="199"/>
+      <c r="L54" s="199"/>
+      <c r="M54" s="199"/>
+      <c r="N54" s="199"/>
+      <c r="O54" s="199"/>
+      <c r="P54" s="199"/>
+      <c r="Q54" s="199"/>
+      <c r="R54" s="199"/>
+      <c r="S54" s="200"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="184"/>
-      <c r="B55" s="197"/>
-      <c r="C55" s="198"/>
-      <c r="D55" s="198"/>
-      <c r="E55" s="198"/>
-      <c r="F55" s="198"/>
-      <c r="G55" s="198"/>
-      <c r="H55" s="198"/>
-      <c r="I55" s="198"/>
-      <c r="J55" s="198"/>
-      <c r="K55" s="198"/>
-      <c r="L55" s="198"/>
-      <c r="M55" s="198"/>
-      <c r="N55" s="198"/>
-      <c r="O55" s="198"/>
-      <c r="P55" s="198"/>
-      <c r="Q55" s="198"/>
-      <c r="R55" s="198"/>
-      <c r="S55" s="199"/>
+      <c r="A55" s="185"/>
+      <c r="B55" s="198"/>
+      <c r="C55" s="199"/>
+      <c r="D55" s="199"/>
+      <c r="E55" s="199"/>
+      <c r="F55" s="199"/>
+      <c r="G55" s="199"/>
+      <c r="H55" s="199"/>
+      <c r="I55" s="199"/>
+      <c r="J55" s="199"/>
+      <c r="K55" s="199"/>
+      <c r="L55" s="199"/>
+      <c r="M55" s="199"/>
+      <c r="N55" s="199"/>
+      <c r="O55" s="199"/>
+      <c r="P55" s="199"/>
+      <c r="Q55" s="199"/>
+      <c r="R55" s="199"/>
+      <c r="S55" s="200"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="184"/>
-      <c r="B56" s="197"/>
-      <c r="C56" s="198"/>
-      <c r="D56" s="198"/>
-      <c r="E56" s="198"/>
-      <c r="F56" s="198"/>
-      <c r="G56" s="198"/>
-      <c r="H56" s="198"/>
-      <c r="I56" s="198"/>
-      <c r="J56" s="198"/>
-      <c r="K56" s="198"/>
-      <c r="L56" s="198"/>
-      <c r="M56" s="198"/>
-      <c r="N56" s="198"/>
-      <c r="O56" s="198"/>
-      <c r="P56" s="198"/>
-      <c r="Q56" s="198"/>
-      <c r="R56" s="198"/>
-      <c r="S56" s="199"/>
+      <c r="A56" s="185"/>
+      <c r="B56" s="198"/>
+      <c r="C56" s="199"/>
+      <c r="D56" s="199"/>
+      <c r="E56" s="199"/>
+      <c r="F56" s="199"/>
+      <c r="G56" s="199"/>
+      <c r="H56" s="199"/>
+      <c r="I56" s="199"/>
+      <c r="J56" s="199"/>
+      <c r="K56" s="199"/>
+      <c r="L56" s="199"/>
+      <c r="M56" s="199"/>
+      <c r="N56" s="199"/>
+      <c r="O56" s="199"/>
+      <c r="P56" s="199"/>
+      <c r="Q56" s="199"/>
+      <c r="R56" s="199"/>
+      <c r="S56" s="200"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="185"/>
-      <c r="B57" s="200"/>
-      <c r="C57" s="201"/>
-      <c r="D57" s="201"/>
-      <c r="E57" s="201"/>
-      <c r="F57" s="201"/>
-      <c r="G57" s="201"/>
-      <c r="H57" s="201"/>
-      <c r="I57" s="201"/>
-      <c r="J57" s="201"/>
-      <c r="K57" s="201"/>
-      <c r="L57" s="201"/>
-      <c r="M57" s="201"/>
-      <c r="N57" s="201"/>
-      <c r="O57" s="201"/>
-      <c r="P57" s="201"/>
-      <c r="Q57" s="201"/>
-      <c r="R57" s="201"/>
-      <c r="S57" s="202"/>
+      <c r="A57" s="186"/>
+      <c r="B57" s="201"/>
+      <c r="C57" s="202"/>
+      <c r="D57" s="202"/>
+      <c r="E57" s="202"/>
+      <c r="F57" s="202"/>
+      <c r="G57" s="202"/>
+      <c r="H57" s="202"/>
+      <c r="I57" s="202"/>
+      <c r="J57" s="202"/>
+      <c r="K57" s="202"/>
+      <c r="L57" s="202"/>
+      <c r="M57" s="202"/>
+      <c r="N57" s="202"/>
+      <c r="O57" s="202"/>
+      <c r="P57" s="202"/>
+      <c r="Q57" s="202"/>
+      <c r="R57" s="202"/>
+      <c r="S57" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="41">
@@ -5498,7 +5357,6 @@
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
@@ -8489,7 +8347,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B193">
         <f>Fisa!C42</f>
@@ -8657,18 +8515,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customFormat="1">
-      <c r="A1" s="267" t="s">
+      <c r="A1" s="268" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="267"/>
-      <c r="C1" s="267"/>
-      <c r="D1" s="267"/>
-      <c r="E1" s="267"/>
-      <c r="F1" s="267"/>
-      <c r="G1" s="267"/>
-      <c r="H1" s="267"/>
-      <c r="I1" s="267"/>
-      <c r="J1" s="267"/>
+      <c r="B1" s="268"/>
+      <c r="C1" s="268"/>
+      <c r="D1" s="268"/>
+      <c r="E1" s="268"/>
+      <c r="F1" s="268"/>
+      <c r="G1" s="268"/>
+      <c r="H1" s="268"/>
+      <c r="I1" s="268"/>
+      <c r="J1" s="268"/>
       <c r="K1" s="12"/>
       <c r="L1" s="5"/>
     </row>
@@ -8689,15 +8547,15 @@
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="268">
+      <c r="B3" s="269">
         <f>Fisa!B3:D3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="268"/>
-      <c r="D3" s="268"/>
-      <c r="E3" s="268"/>
-      <c r="F3" s="268"/>
-      <c r="G3" s="268"/>
+      <c r="C3" s="269"/>
+      <c r="D3" s="269"/>
+      <c r="E3" s="269"/>
+      <c r="F3" s="269"/>
+      <c r="G3" s="269"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -8708,11 +8566,11 @@
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="269">
+      <c r="B4" s="270">
         <f>Fisa!B6</f>
         <v>0</v>
       </c>
-      <c r="C4" s="269"/>
+      <c r="C4" s="270"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -9116,7 +8974,7 @@
         <v>76</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>4</v>
@@ -9125,7 +8983,7 @@
         <v>77</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H25" s="8" t="s">
         <v>78</v>
@@ -10139,7 +9997,7 @@
     </row>
     <row r="60" spans="1:29" customFormat="1">
       <c r="A60" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B60" s="10" t="str">
         <f>Fisa!B36</f>
@@ -10701,75 +10559,78 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94548918-A7C3-43E1-9261-72D16FD14B4A}">
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:AA34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.140625" style="177"/>
     <col min="20" max="20" width="9.140625" customWidth="1"/>
     <col min="21" max="21" width="4.140625" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" style="270"/>
+    <col min="22" max="22" width="9.140625" style="180"/>
     <col min="24" max="24" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" t="s">
         <v>68</v>
       </c>
       <c r="B1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" t="s">
         <v>101</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>102</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>103</v>
       </c>
-      <c r="E1" t="s">
-        <v>104</v>
-      </c>
-      <c r="V1" s="270" t="s">
+      <c r="V1" s="180" t="s">
         <v>3</v>
       </c>
       <c r="W1" t="s">
+        <v>105</v>
+      </c>
+      <c r="X1" t="s">
         <v>106</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>107</v>
       </c>
-      <c r="Y1" t="s">
-        <v>108</v>
-      </c>
       <c r="Z1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26">
-      <c r="A2" s="159"/>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
+        <v>109</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" s="160"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
       <c r="L2" s="175"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="170"/>
+      <c r="M2" s="158"/>
+      <c r="N2" s="158"/>
+      <c r="O2" s="158"/>
+      <c r="P2" s="158"/>
+      <c r="Q2" s="171"/>
       <c r="R2" s="178"/>
       <c r="S2" s="173"/>
       <c r="T2" s="147"/>
       <c r="U2" s="147"/>
-      <c r="V2" s="270" t="str">
-        <f>IFERROR(ROUND(Q2/P2,2),"")</f>
-        <v/>
+      <c r="V2" s="180">
+        <f>IFERROR(IF(W2="DB",Q2/13.5, ROUND(Q2/P2,2)),"")</f>
+        <v>0</v>
       </c>
       <c r="W2" t="str">
         <f>IF(AND(D2=2800, E2=2070, OR(B2=18, B2=18.6, B2=8, B2=10, B2=16)), "PAL",
@@ -10797,32 +10658,36 @@
         <f>IF(W2="DB",IF(OR(ISNUMBER(FIND(" ST",X2)),ISNUMBER(FIND(" SM",X2)),ISNUMBER(FIND(" PM",X2)),ISNUMBER(FIND("TM/ST7",X2)),ISNUMBER(FIND(" PG",X2)),ISNUMBER(FIND(" PA",X2))),SUBSTITUTE(X2," ","",1),X2)," ")</f>
         <v/>
       </c>
-    </row>
-    <row r="3" spans="1:26">
-      <c r="A3" s="160"/>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
-      <c r="D3" s="158"/>
-      <c r="E3" s="158"/>
-      <c r="F3" s="158"/>
-      <c r="G3" s="158"/>
-      <c r="H3" s="158"/>
-      <c r="I3" s="158"/>
-      <c r="J3" s="158"/>
-      <c r="K3" s="158"/>
+      <c r="AA2" t="str">
+        <f>IF(W2="DB", IF(V2=INT(V2),"OK", "Vezi EK"),"")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27">
+      <c r="A3" s="159"/>
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="157"/>
       <c r="L3" s="176"/>
-      <c r="M3" s="158"/>
-      <c r="N3" s="158"/>
-      <c r="O3" s="158"/>
-      <c r="P3" s="158"/>
-      <c r="Q3" s="171"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="157"/>
+      <c r="O3" s="157"/>
+      <c r="P3" s="157"/>
+      <c r="Q3" s="170"/>
       <c r="R3" s="178"/>
       <c r="S3" s="173"/>
       <c r="T3" s="133"/>
       <c r="U3" s="147"/>
-      <c r="V3" s="270" t="str">
-        <f t="shared" ref="V3:V34" si="1">IFERROR(ROUND(Q3/P3,2),"")</f>
-        <v/>
+      <c r="V3" s="180">
+        <f t="shared" ref="V3:V34" si="1">IFERROR(IF(W3="DB",Q3/13.5, ROUND(Q3/P3,2)),"")</f>
+        <v>0</v>
       </c>
       <c r="W3" t="str">
         <f t="shared" ref="W3:W34" si="2">IF(AND(D3=2800, E3=2070, OR(B3=18, B3=18.6, B3=8, B3=10, B3=16)), "PAL",
@@ -10850,32 +10715,36 @@
         <f t="shared" ref="Z3:Z34" si="4">IF(W3="DB",IF(OR(ISNUMBER(FIND(" ST",X3)),ISNUMBER(FIND(" SM",X3)),ISNUMBER(FIND(" PM",X3)),ISNUMBER(FIND("TM/ST7",X3)),ISNUMBER(FIND(" PG",X3)),ISNUMBER(FIND(" PA",X3))),SUBSTITUTE(X3," ","",1),X3)," ")</f>
         <v/>
       </c>
-    </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="159"/>
-      <c r="B4" s="157"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="157"/>
-      <c r="E4" s="157"/>
-      <c r="F4" s="157"/>
-      <c r="G4" s="157"/>
-      <c r="H4" s="157"/>
-      <c r="I4" s="157"/>
-      <c r="J4" s="157"/>
-      <c r="K4" s="157"/>
-      <c r="L4" s="175"/>
-      <c r="M4" s="157"/>
-      <c r="N4" s="157"/>
-      <c r="O4" s="157"/>
-      <c r="P4" s="157"/>
-      <c r="Q4" s="170"/>
+      <c r="AA3" t="str">
+        <f t="shared" ref="AA3:AA34" si="5">IF(W3="DB", IF(V3=INT(V3),"OK", "Vezi EK"),"")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4" s="160"/>
+      <c r="B4" s="158"/>
+      <c r="C4" s="158"/>
+      <c r="D4" s="158"/>
+      <c r="E4" s="158"/>
+      <c r="F4" s="158"/>
+      <c r="G4" s="158"/>
+      <c r="H4" s="158"/>
+      <c r="I4" s="158"/>
+      <c r="J4" s="158"/>
+      <c r="K4" s="158"/>
+      <c r="L4" s="176"/>
+      <c r="M4" s="158"/>
+      <c r="N4" s="158"/>
+      <c r="O4" s="158"/>
+      <c r="P4" s="158"/>
+      <c r="Q4" s="171"/>
       <c r="R4" s="178"/>
       <c r="S4" s="173"/>
       <c r="T4" s="147"/>
       <c r="U4" s="133"/>
-      <c r="V4" s="270" t="str">
+      <c r="V4" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W4" t="str">
         <f t="shared" si="2"/>
@@ -10893,32 +10762,36 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="160"/>
-      <c r="B5" s="158"/>
-      <c r="C5" s="158"/>
-      <c r="D5" s="158"/>
-      <c r="E5" s="158"/>
-      <c r="F5" s="158"/>
-      <c r="G5" s="158"/>
-      <c r="H5" s="158"/>
-      <c r="I5" s="158"/>
-      <c r="J5" s="158"/>
-      <c r="K5" s="158"/>
+      <c r="AA4" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27">
+      <c r="A5" s="159"/>
+      <c r="B5" s="157"/>
+      <c r="C5" s="157"/>
+      <c r="D5" s="157"/>
+      <c r="E5" s="157"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="157"/>
+      <c r="H5" s="157"/>
+      <c r="I5" s="157"/>
+      <c r="J5" s="157"/>
+      <c r="K5" s="157"/>
       <c r="L5" s="176"/>
-      <c r="M5" s="158"/>
-      <c r="N5" s="158"/>
-      <c r="O5" s="158"/>
-      <c r="P5" s="158"/>
-      <c r="Q5" s="171"/>
+      <c r="M5" s="157"/>
+      <c r="N5" s="157"/>
+      <c r="O5" s="157"/>
+      <c r="P5" s="157"/>
+      <c r="Q5" s="170"/>
       <c r="R5" s="178"/>
       <c r="S5" s="173"/>
       <c r="T5" s="147"/>
       <c r="U5" s="133"/>
-      <c r="V5" s="270" t="str">
+      <c r="V5" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="2"/>
@@ -10936,8 +10809,12 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="6" spans="1:26">
+      <c r="AA5" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
       <c r="A6" s="159"/>
       <c r="B6" s="157"/>
       <c r="C6" s="157"/>
@@ -10959,9 +10836,9 @@
       <c r="S6" s="173"/>
       <c r="T6" s="147"/>
       <c r="U6" s="133"/>
-      <c r="V6" s="270" t="str">
+      <c r="V6" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W6" t="str">
         <f t="shared" si="2"/>
@@ -10979,8 +10856,12 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="7" spans="1:26">
+      <c r="AA6" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
       <c r="A7" s="160"/>
       <c r="B7" s="158"/>
       <c r="C7" s="158"/>
@@ -11002,9 +10883,9 @@
       <c r="S7" s="173"/>
       <c r="T7" s="133"/>
       <c r="U7" s="133"/>
-      <c r="V7" s="270" t="str">
+      <c r="V7" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W7" t="str">
         <f t="shared" si="2"/>
@@ -11022,8 +10903,12 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="AA7" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
       <c r="A8" s="159"/>
       <c r="B8" s="157"/>
       <c r="C8" s="157"/>
@@ -11045,9 +10930,9 @@
       <c r="S8" s="173"/>
       <c r="T8" s="147"/>
       <c r="U8" s="133"/>
-      <c r="V8" s="270" t="str">
+      <c r="V8" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="2"/>
@@ -11065,8 +10950,12 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="AA8" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
       <c r="A9" s="160"/>
       <c r="B9" s="158"/>
       <c r="C9" s="158"/>
@@ -11088,9 +10977,9 @@
       <c r="S9" s="173"/>
       <c r="T9" s="147"/>
       <c r="U9" s="131"/>
-      <c r="V9" s="270" t="str">
+      <c r="V9" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="2"/>
@@ -11108,8 +10997,12 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="AA9" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
       <c r="A10" s="159"/>
       <c r="B10" s="157"/>
       <c r="C10" s="157"/>
@@ -11131,9 +11024,9 @@
       <c r="S10" s="173"/>
       <c r="T10" s="147"/>
       <c r="U10" s="147"/>
-      <c r="V10" s="270" t="str">
+      <c r="V10" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="2"/>
@@ -11151,8 +11044,12 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="AA10" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
       <c r="A11" s="160"/>
       <c r="B11" s="158"/>
       <c r="C11" s="158"/>
@@ -11174,9 +11071,9 @@
       <c r="S11" s="173"/>
       <c r="T11" s="147"/>
       <c r="U11" s="147"/>
-      <c r="V11" s="270" t="str">
+      <c r="V11" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="2"/>
@@ -11194,32 +11091,36 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="12" spans="1:26">
-      <c r="A12" s="272"/>
-      <c r="B12" s="273"/>
-      <c r="C12" s="274"/>
-      <c r="D12" s="275"/>
-      <c r="E12" s="275"/>
-      <c r="F12" s="276"/>
-      <c r="G12" s="273"/>
-      <c r="H12" s="277"/>
-      <c r="I12" s="273"/>
-      <c r="J12" s="277"/>
-      <c r="K12" s="281"/>
-      <c r="L12" s="281"/>
-      <c r="M12" s="279"/>
-      <c r="N12" s="281"/>
-      <c r="O12" s="281"/>
-      <c r="P12" s="278"/>
-      <c r="Q12" s="281"/>
+      <c r="AA11" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
+      <c r="A12" s="161"/>
+      <c r="B12" s="162"/>
+      <c r="C12" s="163"/>
+      <c r="D12" s="164"/>
+      <c r="E12" s="164"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="162"/>
+      <c r="H12" s="166"/>
+      <c r="I12" s="162"/>
+      <c r="J12" s="166"/>
+      <c r="K12" s="172"/>
+      <c r="L12" s="172"/>
+      <c r="M12" s="168"/>
+      <c r="N12" s="172"/>
+      <c r="O12" s="172"/>
+      <c r="P12" s="167"/>
+      <c r="Q12" s="172"/>
       <c r="R12" s="178"/>
       <c r="S12" s="134"/>
       <c r="T12" s="134"/>
       <c r="U12" s="134"/>
-      <c r="V12" s="270" t="str">
+      <c r="V12" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="2"/>
@@ -11237,32 +11138,36 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="13" spans="1:26">
-      <c r="A13" s="272"/>
-      <c r="B13" s="273"/>
-      <c r="C13" s="274"/>
-      <c r="D13" s="275"/>
-      <c r="E13" s="275"/>
-      <c r="F13" s="280"/>
-      <c r="G13" s="273"/>
-      <c r="H13" s="277"/>
-      <c r="I13" s="273"/>
-      <c r="J13" s="278"/>
-      <c r="K13" s="281"/>
-      <c r="L13" s="281"/>
-      <c r="M13" s="279"/>
-      <c r="N13" s="281"/>
-      <c r="O13" s="281"/>
-      <c r="P13" s="277"/>
-      <c r="Q13" s="281"/>
+      <c r="AA12" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
+      <c r="A13" s="161"/>
+      <c r="B13" s="162"/>
+      <c r="C13" s="163"/>
+      <c r="D13" s="164"/>
+      <c r="E13" s="164"/>
+      <c r="F13" s="169"/>
+      <c r="G13" s="162"/>
+      <c r="H13" s="166"/>
+      <c r="I13" s="162"/>
+      <c r="J13" s="167"/>
+      <c r="K13" s="172"/>
+      <c r="L13" s="172"/>
+      <c r="M13" s="168"/>
+      <c r="N13" s="172"/>
+      <c r="O13" s="172"/>
+      <c r="P13" s="166"/>
+      <c r="Q13" s="172"/>
       <c r="R13" s="178"/>
       <c r="S13" s="167"/>
       <c r="T13" s="166"/>
       <c r="U13" s="174"/>
-      <c r="V13" s="270" t="str">
+      <c r="V13" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="2"/>
@@ -11280,32 +11185,36 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="14" spans="1:26">
-      <c r="A14" s="272"/>
-      <c r="B14" s="273"/>
-      <c r="C14" s="274"/>
-      <c r="D14" s="275"/>
-      <c r="E14" s="275"/>
-      <c r="F14" s="276"/>
-      <c r="G14" s="273"/>
-      <c r="H14" s="278"/>
-      <c r="I14" s="273"/>
-      <c r="J14" s="278"/>
-      <c r="K14" s="281"/>
-      <c r="L14" s="281"/>
-      <c r="M14" s="278"/>
-      <c r="N14" s="281"/>
-      <c r="O14" s="281"/>
-      <c r="P14" s="278"/>
-      <c r="Q14" s="281"/>
+      <c r="AA13" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
+      <c r="A14" s="161"/>
+      <c r="B14" s="162"/>
+      <c r="C14" s="163"/>
+      <c r="D14" s="164"/>
+      <c r="E14" s="164"/>
+      <c r="F14" s="165"/>
+      <c r="G14" s="162"/>
+      <c r="H14" s="167"/>
+      <c r="I14" s="162"/>
+      <c r="J14" s="167"/>
+      <c r="K14" s="172"/>
+      <c r="L14" s="172"/>
+      <c r="M14" s="167"/>
+      <c r="N14" s="172"/>
+      <c r="O14" s="172"/>
+      <c r="P14" s="167"/>
+      <c r="Q14" s="172"/>
       <c r="R14" s="178"/>
       <c r="S14" s="166"/>
       <c r="T14" s="167"/>
       <c r="U14" s="174"/>
-      <c r="V14" s="270" t="str">
+      <c r="V14" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="2"/>
@@ -11323,32 +11232,19 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="15" spans="1:26">
-      <c r="A15" s="271"/>
-      <c r="B15" s="271"/>
-      <c r="C15" s="271"/>
-      <c r="D15" s="271"/>
-      <c r="E15" s="271"/>
-      <c r="F15" s="271"/>
-      <c r="G15" s="271"/>
-      <c r="H15" s="271"/>
-      <c r="I15" s="271"/>
-      <c r="J15" s="271"/>
-      <c r="K15" s="271"/>
-      <c r="L15" s="271"/>
-      <c r="M15" s="271"/>
-      <c r="N15" s="271"/>
-      <c r="O15" s="271"/>
-      <c r="P15" s="271"/>
-      <c r="Q15" s="271"/>
+      <c r="AA14" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
       <c r="R15" s="178"/>
       <c r="S15" s="167"/>
       <c r="T15" s="167"/>
       <c r="U15" s="134"/>
-      <c r="V15" s="270" t="str">
+      <c r="V15" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="2"/>
@@ -11366,32 +11262,19 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="16" spans="1:26">
-      <c r="A16" s="271"/>
-      <c r="B16" s="271"/>
-      <c r="C16" s="271"/>
-      <c r="D16" s="271"/>
-      <c r="E16" s="271"/>
-      <c r="F16" s="271"/>
-      <c r="G16" s="271"/>
-      <c r="H16" s="271"/>
-      <c r="I16" s="271"/>
-      <c r="J16" s="271"/>
-      <c r="K16" s="271"/>
-      <c r="L16" s="271"/>
-      <c r="M16" s="271"/>
-      <c r="N16" s="271"/>
-      <c r="O16" s="271"/>
-      <c r="P16" s="271"/>
-      <c r="Q16" s="271"/>
+      <c r="AA15" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
       <c r="R16" s="179"/>
       <c r="S16" s="167"/>
       <c r="T16" s="167"/>
       <c r="U16" s="133"/>
-      <c r="V16" s="270" t="str">
+      <c r="V16" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="2"/>
@@ -11402,39 +11285,43 @@
         <v/>
       </c>
       <c r="Y16" t="str">
-        <f t="shared" ref="Y16:Y24" si="5">IF(W16="DB", " ",IF(OR(ISNUMBER(FIND(" ST",X16)),ISNUMBER(FIND(" SM",X16)),ISNUMBER(FIND(" PM",X16)),ISNUMBER(FIND(" TM",X16)),ISNUMBER(FIND(" PG",X16)),ISNUMBER(FIND(" PA",X16))),SUBSTITUTE(X16," ","",1),X16))</f>
+        <f t="shared" ref="Y16:Y24" si="6">IF(W16="DB", " ",IF(OR(ISNUMBER(FIND(" ST",X16)),ISNUMBER(FIND(" SM",X16)),ISNUMBER(FIND(" PM",X16)),ISNUMBER(FIND(" TM",X16)),ISNUMBER(FIND(" PG",X16)),ISNUMBER(FIND(" PA",X16))),SUBSTITUTE(X16," ","",1),X16))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="Z16" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="17" spans="1:26">
-      <c r="A17" s="283"/>
-      <c r="B17" s="282"/>
-      <c r="C17" s="282"/>
-      <c r="D17" s="282"/>
-      <c r="E17" s="282"/>
-      <c r="F17" s="282"/>
-      <c r="G17" s="282"/>
-      <c r="H17" s="282"/>
-      <c r="I17" s="282"/>
-      <c r="J17" s="282"/>
-      <c r="K17" s="282"/>
-      <c r="L17" s="285"/>
-      <c r="M17" s="282"/>
-      <c r="N17" s="282"/>
-      <c r="O17" s="282"/>
-      <c r="P17" s="282"/>
-      <c r="Q17" s="284"/>
+      <c r="AA16" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
+      <c r="A17" s="159"/>
+      <c r="B17" s="157"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="157"/>
+      <c r="E17" s="157"/>
+      <c r="F17" s="157"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="157"/>
+      <c r="J17" s="157"/>
+      <c r="K17" s="157"/>
+      <c r="L17" s="176"/>
+      <c r="M17" s="157"/>
+      <c r="N17" s="157"/>
+      <c r="O17" s="157"/>
+      <c r="P17" s="157"/>
+      <c r="Q17" s="170"/>
       <c r="R17" s="179"/>
       <c r="S17" s="167"/>
       <c r="T17" s="167"/>
       <c r="U17" s="133"/>
-      <c r="V17" s="270" t="str">
+      <c r="V17" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="2"/>
@@ -11445,15 +11332,19 @@
         <v/>
       </c>
       <c r="Y17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="Z17" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="18" spans="1:26">
+      <c r="AA17" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
       <c r="A18" s="161"/>
       <c r="B18" s="162"/>
       <c r="C18" s="163"/>
@@ -11475,9 +11366,9 @@
       <c r="S18" s="167"/>
       <c r="T18" s="167"/>
       <c r="U18" s="133"/>
-      <c r="V18" s="270" t="str">
+      <c r="V18" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" si="2"/>
@@ -11488,15 +11379,19 @@
         <v/>
       </c>
       <c r="Y18" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="Z18" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="19" spans="1:26">
+      <c r="AA18" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
       <c r="A19" s="161"/>
       <c r="B19" s="162"/>
       <c r="C19" s="163"/>
@@ -11517,9 +11412,9 @@
       <c r="R19" s="179"/>
       <c r="S19" s="167"/>
       <c r="T19" s="167"/>
-      <c r="V19" s="270" t="str">
+      <c r="V19" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="2"/>
@@ -11530,15 +11425,19 @@
         <v/>
       </c>
       <c r="Y19" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="Z19" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="20" spans="1:26">
+      <c r="AA19" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20" s="161"/>
       <c r="B20" s="162"/>
       <c r="C20" s="163"/>
@@ -11559,9 +11458,9 @@
       <c r="R20" s="179"/>
       <c r="S20" s="166"/>
       <c r="T20" s="162"/>
-      <c r="V20" s="270" t="str">
+      <c r="V20" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" si="2"/>
@@ -11572,15 +11471,19 @@
         <v/>
       </c>
       <c r="Y20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="Z20" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="AA20" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21" s="161"/>
       <c r="B21" s="162"/>
       <c r="C21" s="163"/>
@@ -11601,9 +11504,9 @@
       <c r="R21" s="179"/>
       <c r="S21" s="167"/>
       <c r="T21" s="166"/>
-      <c r="V21" s="270" t="str">
+      <c r="V21" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="2"/>
@@ -11614,18 +11517,22 @@
         <v/>
       </c>
       <c r="Y21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="Z21" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="22" spans="1:26">
-      <c r="V22" s="270" t="str">
+      <c r="AA21" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
+      <c r="V22" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="2"/>
@@ -11636,18 +11543,22 @@
         <v/>
       </c>
       <c r="Y22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="Z22" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="23" spans="1:26">
-      <c r="V23" s="270" t="str">
+      <c r="AA22" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27">
+      <c r="V23" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="2"/>
@@ -11658,18 +11569,22 @@
         <v/>
       </c>
       <c r="Y23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="Z23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="24" spans="1:26">
-      <c r="V24" s="270" t="str">
+      <c r="AA23" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
+      <c r="V24" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W24" t="str">
         <f t="shared" si="2"/>
@@ -11680,18 +11595,22 @@
         <v/>
       </c>
       <c r="Y24" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="Z24" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="25" spans="1:26">
-      <c r="V25" s="270" t="str">
+      <c r="AA24" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
+      <c r="V25" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W25" t="str">
         <f t="shared" si="2"/>
@@ -11705,11 +11624,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="26" spans="1:26">
-      <c r="V26" s="270" t="str">
+      <c r="AA25" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
+      <c r="V26" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W26" t="str">
         <f t="shared" si="2"/>
@@ -11723,11 +11646,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="27" spans="1:26">
-      <c r="V27" s="270" t="str">
+      <c r="AA26" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
+      <c r="V27" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W27" t="str">
         <f t="shared" si="2"/>
@@ -11741,11 +11668,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="28" spans="1:26">
-      <c r="V28" s="270" t="str">
+      <c r="AA27" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
+      <c r="V28" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W28" t="str">
         <f t="shared" si="2"/>
@@ -11759,11 +11690,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="29" spans="1:26">
-      <c r="V29" s="270" t="str">
+      <c r="AA28" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
+      <c r="V29" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W29" t="str">
         <f t="shared" si="2"/>
@@ -11777,11 +11712,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="30" spans="1:26">
-      <c r="V30" s="270" t="str">
+      <c r="AA29" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="V30" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W30" t="str">
         <f t="shared" si="2"/>
@@ -11795,11 +11734,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="31" spans="1:26">
-      <c r="V31" s="270" t="str">
+      <c r="AA30" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
+      <c r="V31" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W31" t="str">
         <f t="shared" si="2"/>
@@ -11813,11 +11756,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="32" spans="1:26">
-      <c r="V32" s="270" t="str">
+      <c r="AA31" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
+      <c r="V32" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W32" t="str">
         <f t="shared" si="2"/>
@@ -11831,11 +11778,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="33" spans="22:26">
-      <c r="V33" s="270" t="str">
+      <c r="AA32" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="33" spans="22:27">
+      <c r="V33" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W33" t="str">
         <f t="shared" si="2"/>
@@ -11849,11 +11800,15 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-    </row>
-    <row r="34" spans="22:26">
-      <c r="V34" s="270" t="str">
+      <c r="AA33" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="34" spans="22:27">
+      <c r="V34" s="180">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="W34" t="str">
         <f t="shared" si="2"/>
@@ -11866,6 +11821,10 @@
       <c r="Z34" t="str">
         <f t="shared" si="4"/>
         <v/>
+      </c>
+      <c r="AA34" t="str">
+        <f t="shared" si="5"/>
+        <v>OK</v>
       </c>
     </row>
   </sheetData>
@@ -11889,28 +11848,28 @@
         <v>68</v>
       </c>
       <c r="B1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" t="s">
         <v>101</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>102</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>103</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>104</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>105</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>106</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>107</v>
-      </c>
-      <c r="M1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -12242,11 +12201,11 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="286"/>
-      <c r="B14" s="287"/>
-      <c r="C14" s="288"/>
-      <c r="D14" s="288"/>
-      <c r="E14" s="289"/>
+      <c r="A14" s="130"/>
+      <c r="B14" s="131"/>
+      <c r="C14" s="132"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="133"/>
       <c r="H14" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12269,11 +12228,11 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="291"/>
-      <c r="B15" s="290"/>
-      <c r="C15" s="290"/>
-      <c r="D15" s="290"/>
-      <c r="E15" s="290"/>
+      <c r="A15" s="160"/>
+      <c r="B15" s="158"/>
+      <c r="C15" s="158"/>
+      <c r="D15" s="158"/>
+      <c r="E15" s="158"/>
       <c r="H15" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12553,130 +12512,109 @@
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="294"/>
-      <c r="B12" s="293"/>
-      <c r="C12" s="293"/>
-      <c r="D12" s="292"/>
+      <c r="A12" s="159"/>
+      <c r="B12" s="157"/>
+      <c r="C12" s="157"/>
       <c r="I12" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A12)), "CLEAF", Deco!W12)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="296"/>
-      <c r="B13" s="295"/>
-      <c r="C13" s="295"/>
-      <c r="D13" s="295"/>
+      <c r="A13" s="159"/>
+      <c r="B13" s="157"/>
+      <c r="C13" s="157"/>
+      <c r="D13" s="157"/>
       <c r="I13" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A13)), "CLEAF", Deco!W13)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="297"/>
-      <c r="B14" s="297"/>
-      <c r="C14" s="297"/>
-      <c r="D14" s="297"/>
       <c r="I14" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A14)), "CLEAF", Deco!W14)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="297"/>
-      <c r="B15" s="297"/>
-      <c r="C15" s="297"/>
-      <c r="D15" s="297"/>
       <c r="I15" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A15)), "CLEAF", Deco!W15)</f>
         <v>DB</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="297"/>
-      <c r="B16" s="297"/>
-      <c r="C16" s="297"/>
-      <c r="D16" s="297"/>
       <c r="I16" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A16)), "CLEAF", Deco!W16)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="297"/>
-      <c r="B17" s="297"/>
-      <c r="C17" s="297"/>
-      <c r="D17" s="297"/>
+    <row r="17" spans="9:9">
       <c r="I17" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A17)), "CLEAF", Deco!W17)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="297"/>
-      <c r="B18" s="297"/>
-      <c r="C18" s="297"/>
-      <c r="D18" s="297"/>
+    <row r="18" spans="9:9">
       <c r="I18" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A18)), "CLEAF", Deco!W18)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="9:9">
       <c r="I19" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A19)), "CLEAF", Deco!W19)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="9:9">
       <c r="I20" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A20)), "CLEAF", Deco!W20)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="9:9">
       <c r="I21" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A21)), "CLEAF", Deco!W21)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="9:9">
       <c r="I22" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A22)), "CLEAF", Deco!W22)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="9:9">
       <c r="I23" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A23)), "CLEAF", Deco!W23)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="9:9">
       <c r="I24" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A24)), "CLEAF", Deco!W24)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="9:9">
       <c r="I25" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A25)), "CLEAF", Deco!W25)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="9:9">
       <c r="I26" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A26)), "CLEAF", Deco!W26)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="9:9">
       <c r="I27" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A27)), "CLEAF", Deco!W27)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="9:9">
       <c r="I28" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A28)), "CLEAF", Deco!W28)</f>
         <v>DB</v>
@@ -12722,10 +12660,10 @@
         <v>47</v>
       </c>
       <c r="F1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -12745,10 +12683,10 @@
         <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -12759,10 +12697,10 @@
         <v>46</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -12777,7 +12715,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54099AFB-E8E6-455C-A301-A34138B4FFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E95382-2466-4C7B-BAEC-C6BFE40F2221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="119">
   <si>
     <t>FIRMA:</t>
   </si>
@@ -446,6 +446,9 @@
   <si>
     <t>Status  Dublaj</t>
   </si>
+  <si>
+    <t>SHK-W 960 ST7-2.0</t>
+  </si>
 </sst>
 </file>
 
@@ -549,7 +552,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -598,14 +601,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor theme="9" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="54">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -1261,24 +1258,37 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </right>
-      <top style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="9" tint="0.39997558519241921"/>
       </left>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1290,7 +1300,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="271">
+  <cellXfs count="266">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1468,7 +1478,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1726,30 +1735,19 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
@@ -1778,8 +1776,6 @@
     <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" indent="2" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="52" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
@@ -1789,20 +1785,170 @@
     <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="53" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="52" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1818,12 +1964,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1842,12 +1982,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1874,12 +2008,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1946,144 +2074,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2091,6 +2081,21 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2548,7 +2553,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2" customWidth="1"/>
@@ -2569,33 +2574,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="206" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="241"/>
-      <c r="G1" s="241"/>
-      <c r="H1" s="241"/>
-      <c r="I1" s="241"/>
-      <c r="J1" s="241"/>
-      <c r="K1" s="241"/>
-      <c r="L1" s="242"/>
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="207"/>
+      <c r="J1" s="207"/>
+      <c r="K1" s="207"/>
+      <c r="L1" s="208"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="225" t="s">
+      <c r="O1" s="196" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="226"/>
-      <c r="Q1" s="226"/>
-      <c r="R1" s="226"/>
-      <c r="S1" s="227"/>
+      <c r="P1" s="197"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="198"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2613,166 +2618,166 @@
       <c r="M2" s="42">
         <v>1</v>
       </c>
-      <c r="N2" s="85"/>
-      <c r="O2" s="228"/>
-      <c r="P2" s="229"/>
-      <c r="Q2" s="229"/>
-      <c r="R2" s="229"/>
-      <c r="S2" s="230"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="199"/>
+      <c r="P2" s="200"/>
+      <c r="Q2" s="200"/>
+      <c r="R2" s="200"/>
+      <c r="S2" s="201"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="248"/>
-      <c r="C3" s="249"/>
-      <c r="D3" s="250"/>
+      <c r="B3" s="216"/>
+      <c r="C3" s="217"/>
+      <c r="D3" s="218"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="181"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="183"/>
+      <c r="I3" s="220"/>
+      <c r="J3" s="221"/>
+      <c r="K3" s="222"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
-      <c r="N3" s="77"/>
-      <c r="O3" s="243"/>
-      <c r="P3" s="244"/>
-      <c r="Q3" s="244"/>
-      <c r="R3" s="244"/>
-      <c r="S3" s="245"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="209"/>
+      <c r="P3" s="194"/>
+      <c r="Q3" s="194"/>
+      <c r="R3" s="194"/>
+      <c r="S3" s="195"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="219"/>
-      <c r="C4" s="220"/>
-      <c r="D4" s="221"/>
+      <c r="B4" s="252"/>
+      <c r="C4" s="253"/>
+      <c r="D4" s="254"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="222"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="224"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="256"/>
+      <c r="K4" s="257"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
-      <c r="N4" s="77"/>
-      <c r="O4" s="243"/>
-      <c r="P4" s="244"/>
-      <c r="Q4" s="244"/>
-      <c r="R4" s="244"/>
-      <c r="S4" s="245"/>
+      <c r="N4" s="76"/>
+      <c r="O4" s="209"/>
+      <c r="P4" s="194"/>
+      <c r="Q4" s="194"/>
+      <c r="R4" s="194"/>
+      <c r="S4" s="195"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="258"/>
-      <c r="C5" s="259"/>
-      <c r="D5" s="260"/>
+      <c r="B5" s="179"/>
+      <c r="C5" s="180"/>
+      <c r="D5" s="181"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="267"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="245"/>
+      <c r="I5" s="193"/>
+      <c r="J5" s="194"/>
+      <c r="K5" s="195"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
-      <c r="N5" s="77"/>
-      <c r="O5" s="243"/>
-      <c r="P5" s="244"/>
-      <c r="Q5" s="244"/>
-      <c r="R5" s="244"/>
-      <c r="S5" s="245"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="209"/>
+      <c r="P5" s="194"/>
+      <c r="Q5" s="194"/>
+      <c r="R5" s="194"/>
+      <c r="S5" s="195"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="263"/>
-      <c r="C6" s="264"/>
-      <c r="D6" s="265"/>
+      <c r="B6" s="184"/>
+      <c r="C6" s="185"/>
+      <c r="D6" s="186"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="266"/>
-      <c r="J6" s="232"/>
-      <c r="K6" s="233"/>
+      <c r="I6" s="187"/>
+      <c r="J6" s="188"/>
+      <c r="K6" s="189"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
-      <c r="N6" s="78"/>
-      <c r="O6" s="231"/>
-      <c r="P6" s="232"/>
-      <c r="Q6" s="232"/>
-      <c r="R6" s="232"/>
-      <c r="S6" s="233"/>
+      <c r="N6" s="77"/>
+      <c r="O6" s="202"/>
+      <c r="P6" s="188"/>
+      <c r="Q6" s="188"/>
+      <c r="R6" s="188"/>
+      <c r="S6" s="189"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="187" t="s">
+      <c r="A8" s="224" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="188"/>
-      <c r="C8" s="188"/>
-      <c r="D8" s="189"/>
-      <c r="F8" s="234" t="s">
+      <c r="B8" s="225"/>
+      <c r="C8" s="225"/>
+      <c r="D8" s="226"/>
+      <c r="F8" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="235"/>
-      <c r="H8" s="235"/>
-      <c r="I8" s="235"/>
-      <c r="J8" s="235"/>
-      <c r="K8" s="235"/>
-      <c r="L8" s="235"/>
-      <c r="M8" s="235"/>
-      <c r="N8" s="235"/>
-      <c r="O8" s="235"/>
-      <c r="P8" s="235"/>
-      <c r="Q8" s="235"/>
-      <c r="R8" s="235"/>
-      <c r="S8" s="236"/>
+      <c r="G8" s="191"/>
+      <c r="H8" s="191"/>
+      <c r="I8" s="191"/>
+      <c r="J8" s="191"/>
+      <c r="K8" s="191"/>
+      <c r="L8" s="191"/>
+      <c r="M8" s="191"/>
+      <c r="N8" s="191"/>
+      <c r="O8" s="191"/>
+      <c r="P8" s="191"/>
+      <c r="Q8" s="191"/>
+      <c r="R8" s="191"/>
+      <c r="S8" s="192"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="190"/>
-      <c r="B9" s="191"/>
-      <c r="C9" s="191"/>
-      <c r="D9" s="192"/>
-      <c r="F9" s="215" t="s">
+      <c r="A9" s="227"/>
+      <c r="B9" s="228"/>
+      <c r="C9" s="228"/>
+      <c r="D9" s="229"/>
+      <c r="F9" s="248" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="216"/>
-      <c r="H9" s="261" t="s">
+      <c r="G9" s="249"/>
+      <c r="H9" s="182" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="262"/>
-      <c r="J9" s="213" t="s">
+      <c r="I9" s="183"/>
+      <c r="J9" s="246" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="214"/>
-      <c r="L9" s="256" t="s">
+      <c r="K9" s="247"/>
+      <c r="L9" s="177" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="257"/>
-      <c r="N9" s="193" t="s">
+      <c r="M9" s="178"/>
+      <c r="N9" s="214" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="194"/>
-      <c r="P9" s="208" t="s">
+      <c r="O9" s="215"/>
+      <c r="P9" s="241" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="209"/>
-      <c r="R9" s="193" t="s">
+      <c r="Q9" s="242"/>
+      <c r="R9" s="214" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="194"/>
+      <c r="S9" s="215"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="246" t="s">
+      <c r="A10" s="210" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2785,28 +2790,28 @@
         <v>52</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="86" t="s">
+      <c r="F10" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="86" t="s">
+      <c r="G10" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="98" t="s">
+      <c r="H10" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="98" t="s">
+      <c r="I10" s="97" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="108" t="s">
+      <c r="J10" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="108" t="s">
+      <c r="K10" s="107" t="s">
         <v>72</v>
       </c>
-      <c r="L10" s="117" t="s">
+      <c r="L10" s="116" t="s">
         <v>64</v>
       </c>
-      <c r="M10" s="117" t="s">
+      <c r="M10" s="116" t="s">
         <v>72</v>
       </c>
       <c r="N10" s="23" t="s">
@@ -2829,12 +2834,12 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="185"/>
+      <c r="A11" s="211"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
       </c>
-      <c r="C11" s="62" t="str">
+      <c r="C11" s="61" t="str">
         <f>IF(D11="buc",IF(B11&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B11,Deco!$Y$2:$Y$99,0)),""),IF(B11&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B11,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -2843,27 +2848,38 @@
         <v>mp</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="87" t="str">
-        <f xml:space="preserve"> IF(OR(
+      <c r="F11" s="86" t="str">
+        <f>IF(
+   OR(
       ISNUMBER(--RIGHT(B11,1)),
       RIGHT(B11,2)="SM",
       RIGHT(B11,2)="PM",
-      RIGHT(B11,2)="PG", RIGHT(B11,2)="PA",
-      RIGHT(B11,2)="mm",
-      RIGHT(B11,2)="mp"
-   ),B11,
-   LEFT(B11,7))</f>
-        <v/>
-      </c>
-      <c r="G11" s="137" t="str">
+      RIGHT(B11,2)="PG",
+      RIGHT(B11,2)="PA",
+      RIGHT(B11,2)="MP"
+   ),
+   B11,
+   IF(
+      OR(RIGHT(B11,4)="16mm",RIGHT(B11,4)="10mm"),
+      LEFT(B11,LEN(B11)-5),
+      IF(
+         RIGHT(B11,4)=" 8mm",
+         LEFT(B11,LEN(B11)-4),
+         LEFT(B11,7)
+      )
+   )
+)</f>
+        <v/>
+      </c>
+      <c r="G11" s="136" t="str">
         <f>IFERROR(IF(AND(F11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F11,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F11,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
         <v/>
       </c>
-      <c r="H11" s="99" t="str">
+      <c r="H11" s="98" t="str">
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="I11" s="138" t="str">
+      <c r="I11" s="137" t="str">
         <f>IFERROR(
    IF(AND(H11&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H11,Cant!$J$2:$J$99,"22/1.0")
@@ -2873,19 +2889,19 @@
    ""),"")</f>
         <v/>
       </c>
-      <c r="J11" s="109" t="str">
+      <c r="J11" s="108" t="str">
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="K11" s="139" t="str">
+      <c r="K11" s="138" t="str">
         <f>IFERROR(IF(AND(J11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J11,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J11,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
         <v/>
       </c>
-      <c r="L11" s="118" t="str">
+      <c r="L11" s="117" t="str">
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="M11" s="140" t="str">
+      <c r="M11" s="139" t="str">
         <f>IFERROR(IF(AND(L11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L11,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L11,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
         <v/>
       </c>
@@ -2893,7 +2909,7 @@
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="O11" s="141" t="str">
+      <c r="O11" s="140" t="str">
         <f>IFERROR(IF(AND(N11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
         <v/>
       </c>
@@ -2901,7 +2917,7 @@
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="Q11" s="142" t="str">
+      <c r="Q11" s="141" t="str">
         <f>IFERROR(IF(AND(P11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
         <v/>
       </c>
@@ -2915,12 +2931,12 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="185"/>
-      <c r="B12" s="135" t="str" cm="1">
+      <c r="A12" s="211"/>
+      <c r="B12" s="134" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
       </c>
-      <c r="C12" s="136" t="str">
+      <c r="C12" s="135" t="str">
         <f>IF(D12="buc",IF(B12&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B12,Deco!$Y$2:$Y$99,0)),""),IF(B12&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B12,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -2929,84 +2945,95 @@
         <v>mp</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="87" t="str">
-        <f t="shared" ref="F12:F23" si="0" xml:space="preserve"> IF(OR(
+      <c r="F12" s="86" t="str">
+        <f>IF(
+   OR(
       ISNUMBER(--RIGHT(B12,1)),
       RIGHT(B12,2)="SM",
       RIGHT(B12,2)="PM",
-      RIGHT(B12,2)="PG", RIGHT(B12,2)="PA",
-      RIGHT(B12,2)="mm",
-      RIGHT(B12,2)="mp"
-   ),B12,
-   LEFT(B12,7))</f>
-        <v/>
-      </c>
-      <c r="G12" s="137" t="str">
-        <f>IFERROR(IF(AND(F12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F12,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F12,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="100" t="str">
+      RIGHT(B12,2)="PG",
+      RIGHT(B12,2)="PA",
+      RIGHT(B12,2)="MP"
+   ),
+   B12,
+   IF(
+      OR(RIGHT(B12,4)="16mm",RIGHT(B12,4)="10mm"),
+      LEFT(B12,LEN(B12)-5),
+      IF(
+         RIGHT(B12,4)=" 8mm",
+         LEFT(B12,LEN(B12)-4),
+         LEFT(B12,7)
+      )
+   )
+)</f>
+        <v/>
+      </c>
+      <c r="G12" s="136" t="str">
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(F12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F12,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F12,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H12" s="99" t="str">
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="I12" s="138" t="str">
-        <f>IFERROR(
+      <c r="I12" s="137" t="str">
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(
    IF(AND(H12&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H12,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H12,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H12,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H12,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="110" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J12" s="109" t="str">
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="K12" s="139" t="str">
-        <f>IFERROR(IF(AND(J12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J12,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J12,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
-        <v/>
-      </c>
-      <c r="L12" s="119" t="str">
+      <c r="K12" s="138" t="str">
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(J12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J12,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J12,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L12" s="118" t="str">
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="M12" s="140" t="str">
-        <f>IFERROR(IF(AND(L12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L12,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L12,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="N12" s="71" t="str">
+      <c r="M12" s="139" t="str">
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(L12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L12,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L12,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N12" s="70" t="str">
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="O12" s="141" t="str">
-        <f>IFERROR(IF(AND(N12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="P12" s="71" t="str">
+      <c r="O12" s="140" t="str">
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(N12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P12" s="70" t="str">
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="Q12" s="142" t="str">
-        <f>IFERROR(IF(AND(P12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
-      <c r="R12" s="71" t="str">
+      <c r="Q12" s="141" t="str">
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(P12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R12" s="70" t="str">
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
       <c r="S12" s="37" t="str">
-        <f>IFERROR(IF(AND(R12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(R12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="185"/>
-      <c r="B13" s="135" t="str" cm="1">
+      <c r="A13" s="211"/>
+      <c r="B13" s="134" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
       </c>
-      <c r="C13" s="136" t="str">
+      <c r="C13" s="135" t="str">
         <f>IF(D13="buc",IF(B13&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B13,Deco!$Y$2:$Y$99,0)),""),IF(B13&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B13,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3015,76 +3042,92 @@
         <v>mp</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="87" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="137" t="str">
-        <f>IFERROR(IF(AND(F13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F13,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F13,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="100" t="str">
+      <c r="F13" s="86" t="str">
+        <f t="shared" ref="F13:F22" si="0">IF(
+   OR(
+      ISNUMBER(--RIGHT(B13,1)),
+      RIGHT(B13,2)="SM",
+      RIGHT(B13,2)="PM",
+      RIGHT(B13,2)="PG",
+      RIGHT(B13,2)="PA",
+      RIGHT(B13,2)="MP"
+   ),
+   B13,
+   IF(
+      OR(RIGHT(B13,4)="16mm",RIGHT(B13,4)="10mm"),
+      LEFT(B13,LEN(B13)-5),
+      IF(
+         RIGHT(B13,4)=" 8mm",
+         LEFT(B13,LEN(B13)-4),
+         LEFT(B13,7)
+      )
+   )
+)</f>
+        <v/>
+      </c>
+      <c r="G13" s="136" t="str">
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(F13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F13,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F13,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H13" s="99" t="str">
         <f t="shared" ref="H13:H22" si="1">CONCATENATE(F13)</f>
         <v/>
       </c>
-      <c r="I13" s="138" t="str">
-        <f>IFERROR(
+      <c r="I13" s="137" t="str">
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(
    IF(AND(H13&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H13,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H13,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H13,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H13,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="110" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J13" s="109" t="str">
         <f t="shared" ref="J13:J22" si="2">CONCATENATE(F13)</f>
         <v/>
       </c>
-      <c r="K13" s="139" t="str">
-        <f>IFERROR(IF(AND(J13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J13,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J13,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
-        <v/>
-      </c>
-      <c r="L13" s="119" t="str">
+      <c r="K13" s="138" t="str">
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(J13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J13,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J13,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L13" s="118" t="str">
         <f t="shared" ref="L13:L23" si="3">CONCATENATE(F13)</f>
         <v/>
       </c>
-      <c r="M13" s="140" t="str">
-        <f>IFERROR(IF(AND(L13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L13,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L13,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="N13" s="71" t="str">
+      <c r="M13" s="139" t="str">
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(L13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L13,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L13,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N13" s="70" t="str">
         <f t="shared" ref="N13:N23" si="4">CONCATENATE(F13)</f>
         <v/>
       </c>
-      <c r="O13" s="141" t="str">
-        <f>IFERROR(IF(AND(N13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="P13" s="71" t="str">
+      <c r="O13" s="140" t="str">
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(N13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P13" s="70" t="str">
         <f t="shared" ref="P13:P21" si="5">CONCATENATE(F13)</f>
         <v/>
       </c>
-      <c r="Q13" s="142" t="str">
-        <f>IFERROR(IF(AND(P13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
-      <c r="R13" s="71" t="str">
+      <c r="Q13" s="141" t="str">
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(P13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R13" s="70" t="str">
         <f t="shared" ref="R13:R23" si="6">CONCATENATE(F13)</f>
         <v/>
       </c>
       <c r="S13" s="37" t="str">
-        <f>IFERROR(IF(AND(R13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R13,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R13,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(R13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R13,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R13,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="185"/>
-      <c r="B14" s="135" t="str" cm="1">
-        <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
-        <v/>
-      </c>
-      <c r="C14" s="136" t="str">
+      <c r="A14" s="211"/>
+      <c r="B14" s="134"/>
+      <c r="C14" s="135" t="str">
         <f>IF(D14="buc",IF(B14&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B14,Deco!$Y$2:$Y$99,0)),""),IF(B14&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B14,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3093,76 +3136,73 @@
         <v>mp</v>
       </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="87" t="str">
+      <c r="F14" s="86" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G14" s="137" t="str">
-        <f>IFERROR(IF(AND(F14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F14,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F14,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="100" t="str">
+      <c r="G14" s="136" t="str">
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(F14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F14,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F14,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H14" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I14" s="138" t="str">
-        <f>IFERROR(
+      <c r="I14" s="137" t="str">
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(
    IF(AND(H14&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H14,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H14,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H14,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H14,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K14" s="139" t="str">
-        <f>IFERROR(IF(AND(J14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J14,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J14,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
-        <v/>
-      </c>
-      <c r="L14" s="119" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J14" s="109" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K14" s="138" t="str">
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(J14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J14,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J14,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L14" s="118" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M14" s="140" t="str">
-        <f>IFERROR(IF(AND(L14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L14,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L14,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="N14" s="71" t="str">
+      <c r="M14" s="139" t="str">
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(L14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L14,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L14,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N14" s="70" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O14" s="141" t="str">
-        <f>IFERROR(IF(AND(N14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="P14" s="71" t="str">
+      <c r="O14" s="140" t="str">
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(N14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P14" s="70" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q14" s="142" t="str">
-        <f>IFERROR(IF(AND(P14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
-      <c r="R14" s="71" t="str">
+      <c r="Q14" s="141" t="str">
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(P14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R14" s="70" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S14" s="37" t="str">
-        <f>IFERROR(IF(AND(R14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R14,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R14,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(R14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R14,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R14,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="185"/>
-      <c r="B15" s="135" t="str" cm="1">
-        <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
-        <v/>
-      </c>
-      <c r="C15" s="136" t="str">
+      <c r="A15" s="211"/>
+      <c r="B15" s="134"/>
+      <c r="C15" s="135" t="str">
         <f>IF(D15="buc",IF(B15&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B15,Deco!$Y$2:$Y$99,0)),""),IF(B15&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B15,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3171,76 +3211,76 @@
         <v>mp</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="87" t="str">
+      <c r="F15" s="86" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G15" s="137" t="str">
-        <f>IFERROR(IF(AND(F15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F15,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F15,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="100" t="str">
+      <c r="G15" s="136" t="str">
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(F15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F15,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F15,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H15" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I15" s="138" t="str">
-        <f>IFERROR(
+      <c r="I15" s="137" t="str">
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(
    IF(AND(H15&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H15,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H15,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H15,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H15,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K15" s="139" t="str">
-        <f>IFERROR(IF(AND(J15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J15,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J15,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
-        <v/>
-      </c>
-      <c r="L15" s="119" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J15" s="109" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K15" s="138" t="str">
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(J15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J15,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J15,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L15" s="118" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M15" s="140" t="str">
-        <f>IFERROR(IF(AND(L15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L15,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L15,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="N15" s="71" t="str">
+      <c r="M15" s="139" t="str">
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(L15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L15,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L15,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N15" s="70" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O15" s="141" t="str">
-        <f>IFERROR(IF(AND(N15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="P15" s="71" t="str">
+      <c r="O15" s="140" t="str">
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(N15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P15" s="70" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q15" s="142" t="str">
-        <f>IFERROR(IF(AND(P15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
-      <c r="R15" s="71" t="str">
+      <c r="Q15" s="141" t="str">
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(P15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R15" s="70" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S15" s="37" t="str">
-        <f>IFERROR(IF(AND(R15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R15,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R15,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(R15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R15,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R15,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="185"/>
-      <c r="B16" s="135" t="str" cm="1">
+      <c r="A16" s="211"/>
+      <c r="B16" s="134" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
       </c>
-      <c r="C16" s="136" t="str">
+      <c r="C16" s="135" t="str">
         <f>IF(D16="buc",IF(B16&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B16,Deco!$Y$2:$Y$99,0)),""),IF(B16&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B16,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3249,76 +3289,76 @@
         <v>mp</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="87" t="str">
+      <c r="F16" s="86" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G16" s="137" t="str">
-        <f>IFERROR(IF(AND(F16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F16,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F16,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="100" t="str">
+      <c r="G16" s="136" t="str">
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(F16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F16,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F16,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H16" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I16" s="138" t="str">
-        <f>IFERROR(
+      <c r="I16" s="137" t="str">
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(
    IF(AND(H16&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H16,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H16,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H16,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H16,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K16" s="139" t="str">
-        <f>IFERROR(IF(AND(J16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J16,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J16,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
-        <v/>
-      </c>
-      <c r="L16" s="119" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J16" s="109" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K16" s="138" t="str">
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(J16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J16,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J16,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L16" s="118" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M16" s="140" t="str">
-        <f>IFERROR(IF(AND(L16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L16,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L16,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="N16" s="71" t="str">
+      <c r="M16" s="139" t="str">
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(L16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L16,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L16,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N16" s="70" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O16" s="141" t="str">
-        <f>IFERROR(IF(AND(N16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="P16" s="71" t="str">
+      <c r="O16" s="140" t="str">
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(N16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P16" s="70" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q16" s="142" t="str">
-        <f>IFERROR(IF(AND(P16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
-      <c r="R16" s="71" t="str">
+      <c r="Q16" s="141" t="str">
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(P16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R16" s="70" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S16" s="37" t="str">
-        <f>IFERROR(IF(AND(R16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R16,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R16,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(R16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R16,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R16,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="185"/>
-      <c r="B17" s="135" t="str" cm="1">
+      <c r="A17" s="211"/>
+      <c r="B17" s="134" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
       </c>
-      <c r="C17" s="136" t="str">
+      <c r="C17" s="135" t="str">
         <f>IF(D17="buc",IF(B17&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B17,Deco!$Y$2:$Y$99,0)),""),IF(B17&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B17,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3327,76 +3367,76 @@
         <v>mp</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="87" t="str">
+      <c r="F17" s="86" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G17" s="137" t="str">
-        <f>IFERROR(IF(AND(F17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F17,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F17,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="100" t="str">
+      <c r="G17" s="136" t="str">
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(F17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F17,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F17,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H17" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I17" s="138" t="str">
-        <f>IFERROR(
+      <c r="I17" s="137" t="str">
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(
    IF(AND(H17&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H17,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H17,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H17,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H17,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K17" s="139" t="str">
-        <f>IFERROR(IF(AND(J17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J17,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J17,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
-        <v/>
-      </c>
-      <c r="L17" s="119" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J17" s="109" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K17" s="138" t="str">
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(J17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J17,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J17,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L17" s="118" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M17" s="140" t="str">
-        <f>IFERROR(IF(AND(L17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L17,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L17,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="N17" s="71" t="str">
+      <c r="M17" s="139" t="str">
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(L17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L17,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L17,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N17" s="70" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O17" s="141" t="str">
-        <f>IFERROR(IF(AND(N17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="P17" s="71" t="str">
+      <c r="O17" s="140" t="str">
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(N17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P17" s="70" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q17" s="142" t="str">
-        <f>IFERROR(IF(AND(P17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
-      <c r="R17" s="71" t="str">
+      <c r="Q17" s="141" t="str">
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(P17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R17" s="70" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S17" s="37" t="str">
-        <f>IFERROR(IF(AND(R17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R17,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R17,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(R17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R17,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R17,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="185"/>
-      <c r="B18" s="135" t="str" cm="1">
+      <c r="A18" s="211"/>
+      <c r="B18" s="134" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
       </c>
-      <c r="C18" s="136" t="str">
+      <c r="C18" s="135" t="str">
         <f>IF(D18="buc",IF(B18&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B18,Deco!$Y$2:$Y$99,0)),""),IF(B18&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B18,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3405,76 +3445,76 @@
         <v>mp</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="87" t="str">
+      <c r="F18" s="86" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G18" s="137" t="str">
-        <f>IFERROR(IF(AND(F18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F18,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F18,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="100" t="str">
+      <c r="G18" s="136" t="str">
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(F18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F18,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F18,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H18" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I18" s="138" t="str">
-        <f>IFERROR(
+      <c r="I18" s="137" t="str">
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(
    IF(AND(H18&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H18,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H18,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H18,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H18,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K18" s="139" t="str">
-        <f>IFERROR(IF(AND(J18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J18,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J18,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
-        <v/>
-      </c>
-      <c r="L18" s="119" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J18" s="109" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K18" s="138" t="str">
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(J18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J18,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J18,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L18" s="118" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M18" s="140" t="str">
-        <f>IFERROR(IF(AND(L18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L18,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L18,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="N18" s="71" t="str">
+      <c r="M18" s="139" t="str">
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(L18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L18,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L18,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N18" s="70" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O18" s="141" t="str">
-        <f>IFERROR(IF(AND(N18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="P18" s="71" t="str">
+      <c r="O18" s="140" t="str">
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(N18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P18" s="70" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q18" s="142" t="str">
-        <f>IFERROR(IF(AND(P18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
-      <c r="R18" s="71" t="str">
+      <c r="Q18" s="141" t="str">
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(P18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R18" s="70" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S18" s="37" t="str">
-        <f>IFERROR(IF(AND(R18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R18,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R18,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(R18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R18,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R18,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="185"/>
-      <c r="B19" s="135" t="str" cm="1">
+      <c r="A19" s="211"/>
+      <c r="B19" s="134" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
       </c>
-      <c r="C19" s="136" t="str">
+      <c r="C19" s="135" t="str">
         <f>IF(D19="buc",IF(B19&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B19,Deco!$Y$2:$Y$99,0)),""),IF(B19&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B19,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3483,76 +3523,76 @@
         <v>mp</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="87" t="str">
+      <c r="F19" s="86" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G19" s="137" t="str">
-        <f>IFERROR(IF(AND(F19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F19,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F19,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="100" t="str">
+      <c r="G19" s="136" t="str">
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(F19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F19,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F19,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H19" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I19" s="138" t="str">
-        <f>IFERROR(
+      <c r="I19" s="137" t="str">
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(
    IF(AND(H19&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H19,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H19,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H19,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H19,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K19" s="139" t="str">
-        <f>IFERROR(IF(AND(J19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J19,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J19,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
-        <v/>
-      </c>
-      <c r="L19" s="119" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J19" s="109" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K19" s="138" t="str">
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(J19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J19,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J19,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L19" s="118" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M19" s="140" t="str">
-        <f>IFERROR(IF(AND(L19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L19,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L19,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="N19" s="71" t="str">
+      <c r="M19" s="139" t="str">
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(L19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L19,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L19,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N19" s="70" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O19" s="141" t="str">
-        <f>IFERROR(IF(AND(N19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="P19" s="71" t="str">
+      <c r="O19" s="140" t="str">
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(N19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P19" s="70" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q19" s="142" t="str">
-        <f>IFERROR(IF(AND(P19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
-      <c r="R19" s="71" t="str">
+      <c r="Q19" s="141" t="str">
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(P19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R19" s="70" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S19" s="37" t="str">
-        <f>IFERROR(IF(AND(R19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R19,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R19,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(R19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R19,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R19,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="185"/>
-      <c r="B20" s="135" t="str" cm="1">
+      <c r="A20" s="211"/>
+      <c r="B20" s="134" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
       </c>
-      <c r="C20" s="136" t="str">
+      <c r="C20" s="135" t="str">
         <f>IF(D20="buc",IF(B20&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B20,Deco!$Y$2:$Y$99,0)),""),IF(B20&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B20,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3561,76 +3601,76 @@
         <v>mp</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="87" t="str">
+      <c r="F20" s="86" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G20" s="137" t="str">
-        <f>IFERROR(IF(AND(F20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F20,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F20,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="100" t="str">
+      <c r="G20" s="136" t="str">
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(F20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F20,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F20,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H20" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I20" s="138" t="str">
-        <f>IFERROR(
+      <c r="I20" s="137" t="str">
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(
    IF(AND(H20&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H20,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H20,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H20,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H20,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J20" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K20" s="139" t="str">
-        <f>IFERROR(IF(AND(J20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J20,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J20,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
-        <v/>
-      </c>
-      <c r="L20" s="119" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J20" s="109" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K20" s="138" t="str">
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(J20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J20,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J20,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L20" s="118" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M20" s="140" t="str">
-        <f>IFERROR(IF(AND(L20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L20,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L20,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="N20" s="71" t="str">
+      <c r="M20" s="139" t="str">
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(L20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L20,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L20,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N20" s="70" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O20" s="141" t="str">
-        <f>IFERROR(IF(AND(N20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="P20" s="71" t="str">
+      <c r="O20" s="140" t="str">
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(N20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P20" s="70" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q20" s="142" t="str">
-        <f>IFERROR(IF(AND(P20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
-      <c r="R20" s="71" t="str">
+      <c r="Q20" s="141" t="str">
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(P20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R20" s="70" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S20" s="37" t="str">
-        <f>IFERROR(IF(AND(R20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R20,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R20,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(R20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R20,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R20,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="185"/>
-      <c r="B21" s="135" t="str" cm="1">
+      <c r="A21" s="211"/>
+      <c r="B21" s="134" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
       </c>
-      <c r="C21" s="136" t="str">
+      <c r="C21" s="135" t="str">
         <f>IF(D21="buc",IF(B21&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B21,Deco!$Y$2:$Y$99,0)),""),IF(B21&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B21,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3639,144 +3679,144 @@
         <v>mp</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="87" t="str">
+      <c r="F21" s="86" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G21" s="137" t="str">
-        <f>IFERROR(IF(AND(F21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F21,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F21,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="100" t="str">
+      <c r="G21" s="136" t="str">
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(F21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F21,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F21,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H21" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I21" s="138" t="str">
-        <f>IFERROR(
+      <c r="I21" s="137" t="str">
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(
    IF(AND(H21&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H21,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H21,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H21,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H21,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K21" s="139" t="str">
-        <f>IFERROR(IF(AND(J21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J21,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J21,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
-        <v/>
-      </c>
-      <c r="L21" s="119" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J21" s="109" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K21" s="138" t="str">
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(J21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J21,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J21,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L21" s="118" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M21" s="140" t="str">
-        <f>IFERROR(IF(AND(L21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L21,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L21,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="N21" s="71" t="str">
+      <c r="M21" s="139" t="str">
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(L21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L21,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L21,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N21" s="70" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O21" s="141" t="str">
-        <f>IFERROR(IF(AND(N21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="P21" s="71" t="str">
+      <c r="O21" s="140" t="str">
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(N21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P21" s="70" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q21" s="142" t="str">
-        <f>IFERROR(IF(AND(P21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
-      <c r="R21" s="71" t="str">
+      <c r="Q21" s="141" t="str">
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(P21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R21" s="70" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S21" s="37" t="str">
-        <f>IFERROR(IF(AND(R21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R21,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R21,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(R21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R21,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R21,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="247"/>
-      <c r="B22" s="135" t="str" cm="1">
+      <c r="A22" s="212"/>
+      <c r="B22" s="134" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
       </c>
-      <c r="C22" s="136" t="str">
+      <c r="C22" s="135" t="str">
         <f>IF(D22="buc",IF(B22&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B22,Deco!$Y$2:$Y$99,0)),""),IF(B22&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B22,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
-      <c r="D22" s="128" t="str" cm="1">
+      <c r="D22" s="127" t="str" cm="1">
         <f t="array" ref="D22">IF(I3="Debitare căntuire", IF(OR(RIGHT(B22,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(B22,2)="SM",RIGHT(B22,2)="PM",RIGHT(B22,2)="PG",RIGHT(B22,2)="mm",RIGHT(B22,2)="mp",RIGHT(B22,2)="PA",RIGHT(B22,2)="3D"),"buc","mp"), "mp")</f>
         <v>mp</v>
       </c>
-      <c r="E22" s="79"/>
-      <c r="F22" s="87" t="str">
+      <c r="E22" s="78"/>
+      <c r="F22" s="86" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G22" s="137" t="str">
-        <f>IFERROR(IF(AND(F22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F22,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F22,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="100" t="str">
+      <c r="G22" s="136" t="str">
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(F22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F22,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F22,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H22" s="99" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I22" s="138" t="str">
-        <f>IFERROR(
+      <c r="I22" s="137" t="str">
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(
    IF(AND(H22&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H22,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H22,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H22,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H22,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="110" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K22" s="139" t="str">
-        <f>IFERROR(IF(AND(J22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J22,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J22,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
-        <v/>
-      </c>
-      <c r="L22" s="119" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J22" s="109" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K22" s="138" t="str">
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(J22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J22,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J22,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L22" s="118" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M22" s="140" t="str">
-        <f>IFERROR(IF(AND(L22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L22,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L22,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="N22" s="71" t="str">
+      <c r="M22" s="139" t="str">
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(L22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L22,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L22,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N22" s="70" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O22" s="141" t="str">
-        <f>IFERROR(IF(AND(N22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
-        <v/>
-      </c>
-      <c r="P22" s="71" t="str">
+      <c r="O22" s="140" t="str">
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(N22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P22" s="70" t="str">
         <f>CONCATENATE(F22)</f>
         <v/>
       </c>
-      <c r="Q22" s="142" t="str">
-        <f>IFERROR(IF(AND(P22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
-        <v/>
-      </c>
-      <c r="R22" s="71" t="str">
+      <c r="Q22" s="141" t="str">
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(P22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R22" s="70" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="S22" s="37" t="str">
-        <f>IFERROR(IF(AND(R22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R22,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R22,Cant!$J$2:$J$99,"43/2.0"),""),"")</f>
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(R22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R22,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R22,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3789,13 +3829,21 @@
         <v>mp</v>
       </c>
       <c r="E23" s="49"/>
-      <c r="F23" s="87" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G23" s="90"/>
-      <c r="H23" s="102"/>
-      <c r="I23" s="148" t="str">
+      <c r="F23" s="86" t="str">
+        <f t="shared" ref="F23" si="7" xml:space="preserve"> IF(OR(
+      ISNUMBER(--RIGHT(B23,1)),
+      RIGHT(B23,2)="SM",
+      RIGHT(B23,2)="PM",
+      RIGHT(B23,2)="PG", RIGHT(B23,2)="PA",
+      RIGHT(B23,2)="mm",
+      RIGHT(B23,2)="mp"
+   ),B23,
+   LEFT(B23,7))</f>
+        <v/>
+      </c>
+      <c r="G23" s="89"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="147" t="str">
         <f>IFERROR(
    IF(AND(H23&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H23,Cant!$J$2:$J$99,"22/1.0")
@@ -3805,35 +3853,38 @@
    ""),"")</f>
         <v/>
       </c>
-      <c r="J23" s="112"/>
-      <c r="K23" s="112"/>
-      <c r="L23" s="153" t="str">
+      <c r="J23" s="111"/>
+      <c r="K23" s="111"/>
+      <c r="L23" s="150" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M23" s="121"/>
-      <c r="N23" s="156" t="str">
+      <c r="M23" s="120"/>
+      <c r="N23" s="152" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O23" s="49"/>
       <c r="P23" s="49"/>
       <c r="Q23" s="49"/>
-      <c r="R23" s="156" t="str">
+      <c r="R23" s="152" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="S23" s="60"/>
+      <c r="S23" s="37" t="str">
+        <f>IF(AND(F23&lt;&gt;"",COUNTIF($F$11:F22,F23)&gt;0),"",IFERROR(IF(AND(R23&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R23,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R23,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="246" t="s">
+      <c r="A24" s="210" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),1)),"")</f>
         <v/>
       </c>
-      <c r="C24" s="62" t="str">
+      <c r="C24" s="61" t="str">
         <f>IF(D24="buc",IF(B24&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B24,Deco!$Y$2:$Y$99,0)),""),IF(B24&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B24,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3841,51 +3892,62 @@
         <f t="array" ref="D24">IF(I3="Debitare căntuire", IF(OR(RIGHT(B24,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(B24,2)="SM",RIGHT(B24,2)="PM",RIGHT(B24,2)="PG",RIGHT(B24,2)="mm",RIGHT(B24,2)="mp",RIGHT(B24,2)="PA",RIGHT(B24,2)="3D"),"buc","mp"), "mp")</f>
         <v>mp</v>
       </c>
-      <c r="E24" s="79"/>
-      <c r="F24" s="91" t="str">
-        <f xml:space="preserve"> IF(OR(
+      <c r="E24" s="78"/>
+      <c r="F24" s="90" t="str">
+        <f>IF(
+   OR(
       ISNUMBER(--RIGHT(B24,1)),
       RIGHT(B24,2)="SM",
       RIGHT(B24,2)="PM",
-      RIGHT(B24,2)="PG",RIGHT(B24,2)="PA",
-      RIGHT(B24,2)="mm",
-      RIGHT(B24,2)="mp"
-   ),B24,
-   LEFT(B24,7))</f>
-        <v/>
-      </c>
-      <c r="G24" s="92" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,F24)&gt;0,"",IF(AND(F24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F24,Cant!$J$2:$J$100,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F24,Cant!$J$2:$J$100,"22/0.4"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="99" t="str">
+      RIGHT(B24,2)="PG",
+      RIGHT(B24,2)="PA",
+      RIGHT(B24,2)="MP"
+   ),
+   B24,
+   IF(
+      OR(RIGHT(B24,4)="16mm",RIGHT(B24,4)="10mm"),
+      LEFT(B24,LEN(B24)-5),
+      IF(
+         RIGHT(B24,4)=" 8mm",
+         LEFT(B24,LEN(B24)-4),
+         LEFT(B24,7)
+      )
+   )
+)</f>
+        <v/>
+      </c>
+      <c r="G24" s="91" t="str">
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(F24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F24,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F24,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H24" s="98" t="str">
         <f>CONCATENATE(F24)</f>
         <v/>
       </c>
-      <c r="I24" s="103" t="str">
-        <f>IFERROR(
+      <c r="I24" s="102" t="str">
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(
    IF(AND(H24&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H24,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H24,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H24,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H24,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="109" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J24" s="108" t="str">
         <f>CONCATENATE(F24)</f>
         <v/>
       </c>
-      <c r="K24" s="113" t="str">
-        <f>IFERROR(IF(COUNTIF(J$11:J$22,J24)&gt;0,"",IF(AND(J24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J24,Cant!$J$2:$J$100,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J24,Cant!$J$2:$J$100,"23/0.8"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="L24" s="118" t="str">
+      <c r="K24" s="112" t="str">
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(J24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J24,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J24,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L24" s="117" t="str">
         <f>CONCATENATE(F24)</f>
         <v/>
       </c>
-      <c r="M24" s="122" t="str">
-        <f>IFERROR(IF(COUNTIF(L$11:L$22,L24)&gt;0,"",IF(AND(L24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L24,Cant!$J$2:$J$100,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L24,Cant!$J$2:$J$100,"23/2.0"),"")),"")</f>
+      <c r="M24" s="121" t="str">
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(L24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L24,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L24,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
       <c r="N24" s="57" t="str">
@@ -3893,33 +3955,33 @@
         <v/>
       </c>
       <c r="O24" s="29" t="str">
-        <f>IFERROR(IF(COUNTIF(N$11:N$22,N24)&gt;0,"",IF(AND(N24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N24,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N24,Cant!$J$2:$J$100,"43/1.0"),"")),"")</f>
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(N24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="P24" s="57" t="str">
         <f>CONCATENATE(F24)</f>
         <v/>
       </c>
-      <c r="Q24" s="29" t="str">
-        <f>IFERROR(IF(COUNTIF(P$11:P$22,P24)&gt;0,"",IF(AND(P24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P24,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P24,Cant!$J$2:$J$100,"43/1.5"),"")),"")</f>
+      <c r="Q24" s="262" t="str">
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(P24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
       <c r="R24" s="57" t="str">
         <f>CONCATENATE(F24)</f>
         <v/>
       </c>
-      <c r="S24" s="29" t="str">
-        <f>IFERROR(IF(COUNTIF(R$11:R$22,R24)&gt;0,"",IF(AND(R24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R24,Cant!$J$2:$J$100,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R24,Cant!$J$2:$J$100,"43/2.0"),"")),"")</f>
+      <c r="S24" s="262" t="str">
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(R24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R24,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R24,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="185"/>
-      <c r="B25" s="71" t="str">
+      <c r="A25" s="211"/>
+      <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="136" t="str">
+      <c r="C25" s="135" t="str">
         <f>IF(D25="buc",IF(B25&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B25,Deco!$Y$2:$Y$99,0)),""),IF(B25&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B25,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3928,84 +3990,95 @@
         <v>mp</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="87" t="str">
-        <f xml:space="preserve"> IF(OR(
+      <c r="F25" s="86" t="str">
+        <f>IF(
+   OR(
       ISNUMBER(--RIGHT(B25,1)),
       RIGHT(B25,2)="SM",
       RIGHT(B25,2)="PM",
-      RIGHT(B25,2)="PG",RIGHT(B25,2)="PA",
-      RIGHT(B25,2)="mm",
-      RIGHT(B25,2)="mp"
-   ),B25,
-   LEFT(B25,7))</f>
-        <v/>
-      </c>
-      <c r="G25" s="88" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,F25)&gt;0,"",IF(AND(F25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F25,Cant!$J$2:$J$100,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F25,Cant!$J$2:$J$100,"22/0.4"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="100" t="str">
+      RIGHT(B25,2)="PG",
+      RIGHT(B25,2)="PA",
+      RIGHT(B25,2)="MP"
+   ),
+   B25,
+   IF(
+      OR(RIGHT(B25,4)="16mm",RIGHT(B25,4)="10mm"),
+      LEFT(B25,LEN(B25)-5),
+      IF(
+         RIGHT(B25,4)=" 8mm",
+         LEFT(B25,LEN(B25)-4),
+         LEFT(B25,7)
+      )
+   )
+)</f>
+        <v/>
+      </c>
+      <c r="G25" s="87" t="str">
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(F25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F25,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F25,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H25" s="99" t="str">
         <f>CONCATENATE(F25)</f>
         <v/>
       </c>
-      <c r="I25" s="149" t="str">
-        <f>IFERROR(
+      <c r="I25" s="148" t="str">
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(
    IF(AND(H25&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H25,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H25,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H25,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H25,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="110" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J25" s="109" t="str">
         <f>CONCATENATE(F25)</f>
         <v/>
       </c>
-      <c r="K25" s="151" t="str">
-        <f>IFERROR(IF(COUNTIF(J$11:J$22,J25)&gt;0,"",IF(AND(J25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J25,Cant!$J$2:$J$100,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J25,Cant!$J$2:$J$100,"23/0.8"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="L25" s="119" t="str">
+      <c r="K25" s="149" t="str">
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(J25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J25,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J25,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L25" s="118" t="str">
         <f>CONCATENATE(F25)</f>
         <v/>
       </c>
-      <c r="M25" s="154" t="str">
-        <f>IFERROR(IF(COUNTIF(L$11:L$22,L25)&gt;0,"",IF(AND(L25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L25,Cant!$J$2:$J$100,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L25,Cant!$J$2:$J$100,"23/2.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="N25" s="71" t="str">
+      <c r="M25" s="151" t="str">
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(L25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L25,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L25,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N25" s="70" t="str">
         <f>CONCATENATE(F25)</f>
         <v/>
       </c>
       <c r="O25" s="37" t="str">
-        <f>IFERROR(IF(COUNTIF(N$11:N$22,N25)&gt;0,"",IF(AND(N25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N25,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N25,Cant!$J$2:$J$100,"43/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="P25" s="71" t="str">
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(N25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N25,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P25" s="70" t="str">
         <f>CONCATENATE(F25)</f>
         <v/>
       </c>
-      <c r="Q25" s="37" t="str">
-        <f>IFERROR(IF(COUNTIF(P$11:P$22,P25)&gt;0,"",IF(AND(P25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P25,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P25,Cant!$J$2:$J$100,"43/1.5"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="R25" s="71" t="str">
+      <c r="Q25" s="263" t="str">
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(P25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R25" s="70" t="str">
         <f>CONCATENATE(F25)</f>
         <v/>
       </c>
-      <c r="S25" s="37" t="str">
-        <f>IFERROR(IF(COUNTIF(R$11:R$22,R25)&gt;0,"",IF(AND(R25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R25,Cant!$J$2:$J$100,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R25,Cant!$J$2:$J$100,"43/2.0"),"")),"")</f>
+      <c r="S25" s="263" t="str">
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(R25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R25,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R25,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="185"/>
-      <c r="B26" s="71" t="str" cm="1">
+      <c r="A26" s="211"/>
+      <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
       </c>
-      <c r="C26" s="136" t="str">
+      <c r="C26" s="135" t="str">
         <f>IF(D26="buc",IF(B26&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B26,Deco!$Y$2:$Y$99,0)),""),IF(B26&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B26,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4014,84 +4087,95 @@
         <v>mp</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="87" t="str">
-        <f t="shared" ref="F26:F28" si="7" xml:space="preserve"> IF(OR(
+      <c r="F26" s="86" t="str">
+        <f t="shared" ref="F26:F28" si="8">IF(
+   OR(
       ISNUMBER(--RIGHT(B26,1)),
       RIGHT(B26,2)="SM",
       RIGHT(B26,2)="PM",
-      RIGHT(B26,2)="PG",RIGHT(B26,2)="PA",
-      RIGHT(B26,2)="mm",
-      RIGHT(B26,2)="mp"
-   ),B26,
-   LEFT(B26,7))</f>
-        <v/>
-      </c>
-      <c r="G26" s="88" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,F26)&gt;0,"",IF(AND(F26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F26,Cant!$J$2:$J$100,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F26,Cant!$J$2:$J$100,"22/0.4"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="100" t="str">
+      RIGHT(B26,2)="PG",
+      RIGHT(B26,2)="PA",
+      RIGHT(B26,2)="MP"
+   ),
+   B26,
+   IF(
+      OR(RIGHT(B26,4)="16mm",RIGHT(B26,4)="10mm"),
+      LEFT(B26,LEN(B26)-5),
+      IF(
+         RIGHT(B26,4)=" 8mm",
+         LEFT(B26,LEN(B26)-4),
+         LEFT(B26,7)
+      )
+   )
+)</f>
+        <v/>
+      </c>
+      <c r="G26" s="87" t="str">
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(F26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F26,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F26,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H26" s="99" t="str">
         <f>CONCATENATE(F26)</f>
         <v/>
       </c>
-      <c r="I26" s="149" t="str">
-        <f>IFERROR(
+      <c r="I26" s="148" t="str">
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(
    IF(AND(H26&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H26,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H26,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H26,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H26,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="110" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J26" s="109" t="str">
         <f>CONCATENATE(F26)</f>
         <v/>
       </c>
-      <c r="K26" s="151" t="str">
-        <f>IFERROR(IF(COUNTIF(J$11:J$22,J26)&gt;0,"",IF(AND(J26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J26,Cant!$J$2:$J$100,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J26,Cant!$J$2:$J$100,"23/0.8"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="L26" s="119" t="str">
+      <c r="K26" s="149" t="str">
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(J26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J26,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J26,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L26" s="118" t="str">
         <f>CONCATENATE(F26)</f>
         <v/>
       </c>
-      <c r="M26" s="154" t="str">
-        <f>IFERROR(IF(COUNTIF(L$11:L$22,L26)&gt;0,"",IF(AND(L26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L26,Cant!$J$2:$J$100,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L26,Cant!$J$2:$J$100,"23/2.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="N26" s="71" t="str">
+      <c r="M26" s="151" t="str">
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(L26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L26,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L26,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N26" s="70" t="str">
         <f>CONCATENATE(F26)</f>
         <v/>
       </c>
       <c r="O26" s="37" t="str">
-        <f>IFERROR(IF(COUNTIF(N$11:N$22,N26)&gt;0,"",IF(AND(N26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N26,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N26,Cant!$J$2:$J$100,"43/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="P26" s="71" t="str">
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(N26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N26,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P26" s="70" t="str">
         <f>CONCATENATE(F26)</f>
         <v/>
       </c>
-      <c r="Q26" s="37" t="str">
-        <f>IFERROR(IF(COUNTIF(P$11:P$22,P26)&gt;0,"",IF(AND(P26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P26,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P26,Cant!$J$2:$J$100,"43/1.5"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="R26" s="71" t="str">
+      <c r="Q26" s="263" t="str">
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(P26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R26" s="70" t="str">
         <f>CONCATENATE(F26)</f>
         <v/>
       </c>
-      <c r="S26" s="37" t="str">
-        <f>IFERROR(IF(COUNTIF(R$11:R$22,R26)&gt;0,"",IF(AND(R26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R26,Cant!$J$2:$J$100,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R26,Cant!$J$2:$J$100,"43/2.0"),"")),"")</f>
+      <c r="S26" s="263" t="str">
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(R26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R26,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R26,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="185"/>
-      <c r="B27" s="71" t="str" cm="1">
+      <c r="A27" s="211"/>
+      <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
       </c>
-      <c r="C27" s="136" t="str">
+      <c r="C27" s="135" t="str">
         <f>IF(D27="buc",IF(B27&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B27,Deco!$Y$2:$Y$99,0)),""),IF(B27&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B27,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4100,76 +4184,76 @@
         <v>mp</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="87" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="G27" s="88" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,F27)&gt;0,"",IF(AND(F27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F27,Cant!$J$2:$J$100,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F27,Cant!$J$2:$J$100,"22/0.4"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="100" t="str">
+      <c r="F27" s="86" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="G27" s="87" t="str">
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(F27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F27,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F27,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H27" s="99" t="str">
         <f>CONCATENATE(F27)</f>
         <v/>
       </c>
-      <c r="I27" s="149" t="str">
-        <f>IFERROR(
+      <c r="I27" s="148" t="str">
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(
    IF(AND(H27&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H27,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H27,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H27,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H27,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="110" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J27" s="109" t="str">
         <f>CONCATENATE(F27)</f>
         <v/>
       </c>
-      <c r="K27" s="151" t="str">
-        <f>IFERROR(IF(COUNTIF(J$11:J$22,J27)&gt;0,"",IF(AND(J27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J27,Cant!$J$2:$J$100,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J27,Cant!$J$2:$J$100,"23/0.8"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="L27" s="119" t="str">
+      <c r="K27" s="149" t="str">
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(J27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J27,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J27,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L27" s="118" t="str">
         <f>CONCATENATE(F27)</f>
         <v/>
       </c>
-      <c r="M27" s="154" t="str">
-        <f>IFERROR(IF(COUNTIF(L$11:L$22,L27)&gt;0,"",IF(AND(L27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L27,Cant!$J$2:$J$100,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L27,Cant!$J$2:$J$100,"23/2.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="N27" s="71" t="str">
+      <c r="M27" s="151" t="str">
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(L27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L27,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L27,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N27" s="70" t="str">
         <f>CONCATENATE(F27)</f>
         <v/>
       </c>
       <c r="O27" s="37" t="str">
-        <f>IFERROR(IF(COUNTIF(N$11:N$22,N27)&gt;0,"",IF(AND(N27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N27,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N27,Cant!$J$2:$J$100,"43/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="P27" s="71" t="str">
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(N27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N27,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P27" s="70" t="str">
         <f>CONCATENATE(F27)</f>
         <v/>
       </c>
-      <c r="Q27" s="37" t="str">
-        <f>IFERROR(IF(COUNTIF(P$11:P$22,P27)&gt;0,"",IF(AND(P27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P27,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P27,Cant!$J$2:$J$100,"43/1.5"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="R27" s="71" t="str">
+      <c r="Q27" s="263" t="str">
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(P27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R27" s="70" t="str">
         <f>CONCATENATE(F27)</f>
         <v/>
       </c>
-      <c r="S27" s="37" t="str">
-        <f>IFERROR(IF(COUNTIF(R$11:R$22,R27)&gt;0,"",IF(AND(R27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R27,Cant!$J$2:$J$100,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R27,Cant!$J$2:$J$100,"43/2.0"),"")),"")</f>
+      <c r="S27" s="263" t="str">
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(R27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R27,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R27,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="186"/>
-      <c r="B28" s="71" t="str" cm="1">
+      <c r="A28" s="213"/>
+      <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
       </c>
-      <c r="C28" s="136" t="str">
+      <c r="C28" s="135" t="str">
         <f>IF(D28="buc",IF(B28&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B28,Deco!$Y$2:$Y$99,0)),""),IF(B28&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B28,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4177,101 +4261,101 @@
         <f t="array" ref="D28">IF(I3="Debitare căntuire", IF(OR(RIGHT(B28,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(B28,2)="SM",RIGHT(B28,2)="PM",RIGHT(B28,2)="PG",RIGHT(B28,2)="mm",RIGHT(B28,2)="mp",RIGHT(B28,2)="PA",RIGHT(B28,2)="3D"),"buc","mp"), "mp")</f>
         <v>mp</v>
       </c>
-      <c r="E28" s="79"/>
-      <c r="F28" s="87" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="G28" s="143" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,F28)&gt;0,"",IF(AND(F28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F28,Cant!$J$2:$J$100,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F28,Cant!$J$2:$J$100,"22/0.4"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="104" t="str">
+      <c r="E28" s="78"/>
+      <c r="F28" s="261" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="G28" s="142" t="str">
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(F28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F28,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F28,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H28" s="103" t="str">
         <f>CONCATENATE(F28)</f>
         <v/>
       </c>
-      <c r="I28" s="150" t="str">
-        <f>IFERROR(
+      <c r="I28" s="143" t="str">
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(
    IF(AND(H28&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H28,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H28,Cant!$J$2:$J$99,"23/1.0")&gt;0),
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H28,Cant!$J$2:$J$99,"22/1.0")
      +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H28,Cant!$J$2:$J$99,"23/1.0"),
-   ""),"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="114" t="str">
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J28" s="113" t="str">
         <f>CONCATENATE(F28)</f>
         <v/>
       </c>
-      <c r="K28" s="152" t="str">
-        <f>IFERROR(IF(COUNTIF(J$11:J$22,J28)&gt;0,"",IF(AND(J28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J28,Cant!$J$2:$J$100,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J28,Cant!$J$2:$J$100,"23/0.8"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="L28" s="123" t="str">
+      <c r="K28" s="144" t="str">
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(J28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J28,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J28,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L28" s="122" t="str">
         <f>CONCATENATE(F28)</f>
         <v/>
       </c>
-      <c r="M28" s="155" t="str">
-        <f>IFERROR(IF(COUNTIF(L$11:L$22,L28)&gt;0,"",IF(AND(L28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L28,Cant!$J$2:$J$100,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L28,Cant!$J$2:$J$100,"23/2.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="N28" s="72" t="str">
+      <c r="M28" s="145" t="str">
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(L28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L28,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L28,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N28" s="71" t="str">
         <f>CONCATENATE(F28)</f>
         <v/>
       </c>
-      <c r="O28" s="128" t="str">
-        <f>IFERROR(IF(COUNTIF(N$11:N$22,N28)&gt;0,"",IF(AND(N28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N28,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N28,Cant!$J$2:$J$100,"43/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="P28" s="72" t="str">
+      <c r="O28" s="31" t="str">
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(N28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N28,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="P28" s="71" t="str">
         <f>CONCATENATE(F28)</f>
         <v/>
       </c>
-      <c r="Q28" s="128" t="str">
-        <f>IFERROR(IF(COUNTIF(P$11:P$22,P28)&gt;0,"",IF(AND(P28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P28,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P28,Cant!$J$2:$J$100,"43/1.5"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="R28" s="72" t="str">
+      <c r="Q28" s="31" t="str">
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(P28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="R28" s="71" t="str">
         <f>CONCATENATE(F28)</f>
         <v/>
       </c>
-      <c r="S28" s="128" t="str">
-        <f>IFERROR(IF(COUNTIF(R$11:R$22,R28)&gt;0,"",IF(AND(R28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R28,Cant!$J$2:$J$100,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R28,Cant!$J$2:$J$100,"43/2.0"),"")),"")</f>
+      <c r="S28" s="31" t="str">
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(R28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R28,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R28,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:19" s="51" customFormat="1" ht="15.75" hidden="1" customHeight="1" thickBot="1">
       <c r="A29" s="54"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="80"/>
+      <c r="B29" s="79"/>
+      <c r="C29" s="79"/>
       <c r="D29" s="37" t="str" cm="1">
         <f t="array" ref="D29">IF(I20="Mobilier în Roomdesigner", IF(OR(RIGHT(B29,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(B29,2)="SM",RIGHT(B29,2)="PM",RIGHT(B29,2)="PG",RIGHT(B29,2)="mm"),"buc","mp"), "mp")</f>
         <v>mp</v>
       </c>
       <c r="E29" s="49"/>
-      <c r="F29" s="94"/>
-      <c r="G29" s="95"/>
-      <c r="H29" s="105"/>
-      <c r="I29" s="105"/>
-      <c r="J29" s="115"/>
-      <c r="K29" s="115"/>
-      <c r="L29" s="124"/>
-      <c r="M29" s="124"/>
-      <c r="N29" s="80"/>
-      <c r="O29" s="80"/>
-      <c r="P29" s="80"/>
-      <c r="Q29" s="80"/>
+      <c r="F29" s="93"/>
+      <c r="G29" s="94"/>
+      <c r="H29" s="104"/>
+      <c r="I29" s="104"/>
+      <c r="J29" s="114"/>
+      <c r="K29" s="114"/>
+      <c r="L29" s="123"/>
+      <c r="M29" s="123"/>
+      <c r="N29" s="79"/>
+      <c r="O29" s="79"/>
+      <c r="P29" s="79"/>
+      <c r="Q29" s="79"/>
     </row>
     <row r="30" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A30" s="63" t="s">
+      <c r="A30" s="62" t="s">
         <v>67</v>
       </c>
       <c r="B30" s="57" t="str" cm="1">
         <f t="array" ref="B30">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="HDF"),1))),"")</f>
         <v/>
       </c>
-      <c r="C30" s="62" t="str">
+      <c r="C30" s="61" t="str">
         <f>IF(D30="buc",IF(B30&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B30,Deco!$Y$2:$Y$99,0)),""),IF(B30&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B30,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4280,14 +4364,14 @@
         <v>mp</v>
       </c>
       <c r="E30" s="49"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="90"/>
-      <c r="H30" s="102"/>
-      <c r="I30" s="102"/>
-      <c r="J30" s="112"/>
-      <c r="K30" s="112"/>
-      <c r="L30" s="121"/>
-      <c r="M30" s="121"/>
+      <c r="F30" s="88"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="101"/>
+      <c r="I30" s="101"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="120"/>
+      <c r="M30" s="120"/>
       <c r="N30" s="49"/>
       <c r="O30" s="49"/>
       <c r="P30" s="49"/>
@@ -4297,34 +4381,34 @@
     </row>
     <row r="31" spans="1:19" ht="2.1" hidden="1" customHeight="1" thickBot="1">
       <c r="A31" s="55"/>
-      <c r="B31" s="66"/>
+      <c r="B31" s="65"/>
       <c r="C31" s="49"/>
-      <c r="D31" s="67"/>
+      <c r="D31" s="66"/>
       <c r="E31" s="49"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="106"/>
-      <c r="I31" s="106"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="116"/>
-      <c r="L31" s="125"/>
-      <c r="M31" s="125"/>
+      <c r="F31" s="95"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="105"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="115"/>
+      <c r="L31" s="124"/>
+      <c r="M31" s="124"/>
       <c r="N31" s="59"/>
       <c r="O31" s="59"/>
       <c r="P31" s="59"/>
       <c r="Q31" s="59"/>
-      <c r="R31" s="81"/>
-      <c r="S31" s="81"/>
+      <c r="R31" s="80"/>
+      <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="210" t="s">
+      <c r="A32" s="243" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
         <f t="array" ref="B32">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),1))),"")</f>
         <v/>
       </c>
-      <c r="C32" s="62" t="str">
+      <c r="C32" s="61" t="str">
         <f>IF(D32="buc",IF(B32&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B32,Deco!$Y$2:$Y$99,0)),""),IF(B32&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B32,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4332,36 +4416,42 @@
         <v>55</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="91" t="str">
+      <c r="F32" s="90" t="str">
         <f>IF(B32&lt;&gt;"",TRIM(LEFT(B32,LEN(B32)-4)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="92" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,F32)&gt;0,"",IF(AND(F32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F32,Cant!$J$2:$J$100,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F32,Cant!$J$2:$J$100,"22/0.4"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="99" t="str">
+      <c r="G32" s="91" t="str">
+        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(AND(F32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F32,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F32,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H32" s="98" t="str">
         <f>CONCATENATE(F32)</f>
         <v/>
       </c>
-      <c r="I32" s="103" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,H32)&gt;0,"",IF(AND(H32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H32,Cant!$J$2:$J$100,"22/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H32,Cant!$J$2:$J$100,"22/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="109" t="str">
+      <c r="I32" s="264" t="str">
+        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(
+   IF(AND(H32&lt;&gt;"",
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H32,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H32,Cant!$J$2:$J$99,"23/1.0")&gt;0),
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H32,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H32,Cant!$J$2:$J$99,"23/1.0"),
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J32" s="108" t="str">
         <f>CONCATENATE(F32)</f>
         <v/>
       </c>
-      <c r="K32" s="113" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,J32)&gt;0,"",IF(AND(J32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J32,Cant!$J$2:$J$100,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J32,Cant!$J$2:$J$100,"23/0.8"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="L32" s="118" t="str">
+      <c r="K32" s="112" t="str">
+        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(AND(J32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J32,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J32,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L32" s="117" t="str">
         <f>CONCATENATE(F32)</f>
         <v/>
       </c>
-      <c r="M32" s="122" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,L32)&gt;0,"",IF(AND(L32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L32,Cant!$J$2:$J$100,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L32,Cant!$J$2:$J$100,"23/2.0"),"")),"")</f>
+      <c r="M32" s="121" t="str">
+        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(AND(L32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L32,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L32,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
       <c r="N32" s="57" t="str">
@@ -4369,33 +4459,33 @@
         <v/>
       </c>
       <c r="O32" s="29" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,N32)&gt;0,"",IF(AND(N32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0"),"")),"")</f>
+        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N32)&gt;0,"",IF(AND(N32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N32,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
         <v/>
       </c>
       <c r="P32" s="57" t="str">
         <f>CONCATENATE(F32)</f>
         <v/>
       </c>
-      <c r="Q32" s="29" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,P32)&gt;0,"",IF(AND(P32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"43/1.5"),"")),"")</f>
+      <c r="Q32" s="262" t="str">
+        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P32)&gt;0,"",IF(AND(P32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
         <v/>
       </c>
       <c r="R32" s="57" t="str">
         <f>CONCATENATE(F32)</f>
         <v/>
       </c>
-      <c r="S32" s="29" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,R32)&gt;0,"",IF(AND(R32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R32,Cant!$J$2:$J$100,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R32,Cant!$J$2:$J$100,"43/2.0"),"")),"")</f>
+      <c r="S32" s="262" t="str">
+        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(AND(R32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R32,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R32,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="211"/>
-      <c r="B33" s="71" t="str" cm="1">
+      <c r="A33" s="244"/>
+      <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
       </c>
-      <c r="C33" s="136" t="str">
+      <c r="C33" s="135" t="str">
         <f>IF(D33="buc",IF(B33&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B33,Deco!$Y$2:$Y$99,0)),""),IF(B33&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B33,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4403,70 +4493,76 @@
         <v>55</v>
       </c>
       <c r="E33" s="2"/>
-      <c r="F33" s="87" t="str">
+      <c r="F33" s="86" t="str">
         <f>IF(B33&lt;&gt;"",TRIM(LEFT(B33,LEN(B33)-4)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="88" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,F33)&gt;0,"",IF(AND(F33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F33,Cant!$J$2:$J$100,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F33,Cant!$J$2:$J$100,"22/0.4"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="100" t="str">
+      <c r="G33" s="87" t="str">
+        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(AND(F33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F33,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F33,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H33" s="99" t="str">
         <f>CONCATENATE(F33)</f>
         <v/>
       </c>
-      <c r="I33" s="101" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,H33)&gt;0,"",IF(AND(H33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H33,Cant!$J$2:$J$100,"22/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H33,Cant!$J$2:$J$100,"22/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="110" t="str">
+      <c r="I33" s="265" t="str">
+        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(
+   IF(AND(H33&lt;&gt;"",
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H33,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H33,Cant!$J$2:$J$99,"23/1.0")&gt;0),
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H33,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H33,Cant!$J$2:$J$99,"23/1.0"),
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J33" s="109" t="str">
         <f>CONCATENATE(F33)</f>
         <v/>
       </c>
-      <c r="K33" s="111" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,J33)&gt;0,"",IF(AND(J33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J33,Cant!$J$2:$J$100,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J33,Cant!$J$2:$J$100,"23/0.8"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="L33" s="119" t="str">
+      <c r="K33" s="110" t="str">
+        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(AND(J33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J33,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J33,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L33" s="118" t="str">
         <f>CONCATENATE(F33)</f>
         <v/>
       </c>
-      <c r="M33" s="120" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,L33)&gt;0,"",IF(AND(L33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L33,Cant!$J$2:$J$100,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L33,Cant!$J$2:$J$100,"23/2.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="N33" s="71" t="str">
+      <c r="M33" s="119" t="str">
+        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(AND(L33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L33,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L33,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N33" s="70" t="str">
         <f>CONCATENATE(F33)</f>
         <v/>
       </c>
       <c r="O33" s="30" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,N33)&gt;0,"",IF(AND(N33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="P33" s="71" t="str">
+        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N33)&gt;0,"",IF(AND(N33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N33,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
+        <v/>
+      </c>
+      <c r="P33" s="70" t="str">
         <f>CONCATENATE(F33)</f>
         <v/>
       </c>
-      <c r="Q33" s="30" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,P33)&gt;0,"",IF(AND(P33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"43/1.5"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="R33" s="71" t="str">
+      <c r="Q33" s="263" t="str">
+        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P33)&gt;0,"",IF(AND(P33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
+        <v/>
+      </c>
+      <c r="R33" s="70" t="str">
         <f>CONCATENATE(F33)</f>
         <v/>
       </c>
-      <c r="S33" s="30" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,R33)&gt;0,"",IF(AND(R33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R33,Cant!$J$2:$J$100,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R33,Cant!$J$2:$J$100,"43/2.0"),"")),"")</f>
+      <c r="S33" s="263" t="str">
+        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(AND(R33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R33,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R33,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="212"/>
-      <c r="B34" s="71" t="str" cm="1">
+      <c r="A34" s="245"/>
+      <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
       </c>
-      <c r="C34" s="136" t="str">
+      <c r="C34" s="135" t="str">
         <f>IF(D34="buc",IF(B34&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B34,Deco!$Y$2:$Y$99,0)),""),IF(B34&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B34,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4474,77 +4570,83 @@
         <v>55</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="87" t="str">
+      <c r="F34" s="86" t="str">
         <f>IF(B34&lt;&gt;"",TRIM(LEFT(B34,LEN(B34)-4)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="88" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,F34)&gt;0,"",IF(AND(F34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F34,Cant!$J$2:$J$100,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F34,Cant!$J$2:$J$100,"22/0.4"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="100" t="str">
+      <c r="G34" s="87" t="str">
+        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(AND(F34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F34,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F34,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H34" s="99" t="str">
         <f>CONCATENATE(F34)</f>
         <v/>
       </c>
-      <c r="I34" s="101" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,H34)&gt;0,"",IF(AND(H34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H34,Cant!$J$2:$J$100,"22/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H34,Cant!$J$2:$J$100,"22/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="110" t="str">
+      <c r="I34" s="100" t="str">
+        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(
+   IF(AND(H34&lt;&gt;"",
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H34,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H34,Cant!$J$2:$J$99,"23/1.0")&gt;0),
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H34,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H34,Cant!$J$2:$J$99,"23/1.0"),
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J34" s="109" t="str">
         <f>CONCATENATE(F34)</f>
         <v/>
       </c>
-      <c r="K34" s="111" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,J34)&gt;0,"",IF(AND(J34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J34,Cant!$J$2:$J$100,"22/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J34,Cant!$J$2:$J$100,"22/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="L34" s="119" t="str">
+      <c r="K34" s="110" t="str">
+        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(AND(J34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J34,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J34,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L34" s="118" t="str">
         <f>CONCATENATE(F34)</f>
         <v/>
       </c>
-      <c r="M34" s="120" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,L34)&gt;0,"",IF(AND(L34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L34,Cant!$J$2:$J$100,"22/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L34,Cant!$J$2:$J$100,"22/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="N34" s="71" t="str">
+      <c r="M34" s="119" t="str">
+        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(AND(L34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L34,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L34,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N34" s="70" t="str">
         <f>CONCATENATE(F34)</f>
         <v/>
       </c>
       <c r="O34" s="30" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,N34)&gt;0,"",IF(AND(N34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"22/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"22/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="P34" s="71" t="str">
+        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,N34)&gt;0,"",IF(AND(N34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N34,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
+        <v/>
+      </c>
+      <c r="P34" s="70" t="str">
         <f>CONCATENATE(F34)</f>
         <v/>
       </c>
       <c r="Q34" s="30" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,P34)&gt;0,"",IF(AND(P34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P34,Cant!$J$2:$J$100,"22/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P34,Cant!$J$2:$J$100,"22/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="R34" s="71" t="str">
+        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P34)&gt;0,"",IF(AND(P34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P34,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P34,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
+        <v/>
+      </c>
+      <c r="R34" s="70" t="str">
         <f>CONCATENATE(F34)</f>
         <v/>
       </c>
       <c r="S34" s="30" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,R34)&gt;0,"",IF(AND(R34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R34,Cant!$J$2:$J$100,"22/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R34,Cant!$J$2:$J$100,"22/1.0"),"")),"")</f>
+        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(AND(R34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R34,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R34,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1">
       <c r="A35" s="56"/>
-      <c r="B35" s="66"/>
+      <c r="B35" s="65"/>
       <c r="C35" s="49"/>
-      <c r="D35" s="67"/>
+      <c r="D35" s="66"/>
       <c r="E35" s="49"/>
-      <c r="F35" s="90"/>
-      <c r="G35" s="90"/>
-      <c r="H35" s="102"/>
-      <c r="I35" s="102"/>
-      <c r="J35" s="112"/>
-      <c r="K35" s="112"/>
-      <c r="L35" s="121"/>
-      <c r="M35" s="121"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="89"/>
+      <c r="H35" s="101"/>
+      <c r="I35" s="101"/>
+      <c r="J35" s="111"/>
+      <c r="K35" s="111"/>
+      <c r="L35" s="120"/>
+      <c r="M35" s="120"/>
       <c r="N35" s="49"/>
       <c r="O35" s="49"/>
       <c r="P35" s="49"/>
@@ -4553,14 +4655,14 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="210" t="s">
+      <c r="A36" s="243" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
         <f t="array" ref="B36">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),1))),"")</f>
         <v/>
       </c>
-      <c r="C36" s="62" t="str">
+      <c r="C36" s="61" t="str">
         <f>IF(D36="buc",IF(B36&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B36,Deco!$Y$2:$Y$99,0)),""),IF(B36&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B36,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4568,36 +4670,42 @@
         <v>55</v>
       </c>
       <c r="E36" s="2"/>
-      <c r="F36" s="91" t="str">
+      <c r="F36" s="90" t="str">
         <f>IF(B36&lt;&gt;"",TRIM(LEFT(B36,LEN(B36)-3)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="92" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,F36)&gt;0,"",IF(AND(F36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F36,Cant!$J$2:$J$100,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F36,Cant!$J$2:$J$100,"22/0.4"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="99" t="str">
+      <c r="G36" s="91" t="str">
+        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(AND(F36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F36,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F36,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H36" s="98" t="str">
         <f>CONCATENATE(F36)</f>
         <v/>
       </c>
-      <c r="I36" s="103" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,H36)&gt;0,"",IF(AND(H36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H36,Cant!$J$2:$J$100,"22/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H36,Cant!$J$2:$J$100,"22/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="109" t="str">
+      <c r="I36" s="264" t="str">
+        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(
+   IF(AND(H36&lt;&gt;"",
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H36,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H36,Cant!$J$2:$J$99,"23/1.0")&gt;0),
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H36,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H36,Cant!$J$2:$J$99,"23/1.0"),
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J36" s="108" t="str">
         <f>CONCATENATE(F36)</f>
         <v/>
       </c>
-      <c r="K36" s="113" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,J36)&gt;0,"",IF(AND(J36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J36,Cant!$J$2:$J$100,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J36,Cant!$J$2:$J$100,"23/0.8"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="L36" s="118" t="str">
+      <c r="K36" s="112" t="str">
+        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(AND(J36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J36,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J36,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L36" s="117" t="str">
         <f>CONCATENATE(F36)</f>
         <v/>
       </c>
-      <c r="M36" s="122" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,L36)&gt;0,"",IF(AND(L36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L36,Cant!$J$2:$J$100,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L36,Cant!$J$2:$J$100,"23/2.0"),"")),"")</f>
+      <c r="M36" s="121" t="str">
+        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(AND(L36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L36,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L36,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
       <c r="N36" s="57" t="str">
@@ -4605,33 +4713,33 @@
         <v/>
       </c>
       <c r="O36" s="29" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,N36)&gt;0,"",IF(AND(N36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0"),"")),"")</f>
+        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N36)&gt;0,"",IF(AND(N36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N36,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
         <v/>
       </c>
       <c r="P36" s="57" t="str">
         <f>CONCATENATE(F36)</f>
         <v/>
       </c>
-      <c r="Q36" s="29" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,P36)&gt;0,"",IF(AND(P36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"43/1.5"),"")),"")</f>
+      <c r="Q36" s="262" t="str">
+        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P36)&gt;0,"",IF(AND(P36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
         <v/>
       </c>
       <c r="R36" s="57" t="str">
         <f>CONCATENATE(F36)</f>
         <v/>
       </c>
-      <c r="S36" s="29" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,R36)&gt;0,"",IF(AND(R36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R36,Cant!$J$2:$J$100,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R36,Cant!$J$2:$J$100,"43/2.0"),"")),"")</f>
+      <c r="S36" s="262" t="str">
+        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(AND(R36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R36,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R36,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="211"/>
-      <c r="B37" s="71" t="str" cm="1">
+      <c r="A37" s="244"/>
+      <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
       </c>
-      <c r="C37" s="136" t="str">
+      <c r="C37" s="135" t="str">
         <f>IF(D37="buc",IF(B37&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B37,Deco!$Y$2:$Y$99,0)),""),IF(B37&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B37,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4639,70 +4747,76 @@
         <v>55</v>
       </c>
       <c r="E37" s="2"/>
-      <c r="F37" s="87" t="str">
+      <c r="F37" s="86" t="str">
         <f>IF(B37&lt;&gt;"",TRIM(LEFT(B37,LEN(B37)-3)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="88" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,F37)&gt;0,"",IF(AND(F37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F37,Cant!$J$2:$J$100,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F37,Cant!$J$2:$J$100,"22/0.4"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="107" t="str">
+      <c r="G37" s="87" t="str">
+        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(AND(F37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F37,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F37,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H37" s="106" t="str">
         <f>CONCATENATE(F37)</f>
         <v/>
       </c>
-      <c r="I37" s="101" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,H37)&gt;0,"",IF(AND(H37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H37,Cant!$J$2:$J$100,"22/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H37,Cant!$J$2:$J$100,"22/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="110" t="str">
+      <c r="I37" s="265" t="str">
+        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(
+   IF(AND(H37&lt;&gt;"",
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H37,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H37,Cant!$J$2:$J$99,"23/1.0")&gt;0),
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H37,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H37,Cant!$J$2:$J$99,"23/1.0"),
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J37" s="109" t="str">
         <f>CONCATENATE(F37)</f>
         <v/>
       </c>
-      <c r="K37" s="111" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,J37)&gt;0,"",IF(AND(J37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J37,Cant!$J$2:$J$100,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J37,Cant!$J$2:$J$100,"23/0.8"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="L37" s="119" t="str">
+      <c r="K37" s="110" t="str">
+        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(AND(J37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J37,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J37,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L37" s="118" t="str">
         <f>CONCATENATE(F37)</f>
         <v/>
       </c>
-      <c r="M37" s="120" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,L37)&gt;0,"",IF(AND(L37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L37,Cant!$J$2:$J$100,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L37,Cant!$J$2:$J$100,"23/2.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="N37" s="71" t="str">
+      <c r="M37" s="119" t="str">
+        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(AND(L37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L37,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L37,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N37" s="70" t="str">
         <f>CONCATENATE(F37)</f>
         <v/>
       </c>
       <c r="O37" s="30" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,N37)&gt;0,"",IF(AND(N37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="P37" s="71" t="str">
+        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N37)&gt;0,"",IF(AND(N37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N37,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
+        <v/>
+      </c>
+      <c r="P37" s="70" t="str">
         <f>CONCATENATE(F37)</f>
         <v/>
       </c>
-      <c r="Q37" s="30" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,P37)&gt;0,"",IF(AND(P37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"43/1.5"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="R37" s="71" t="str">
+      <c r="Q37" s="263" t="str">
+        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P37)&gt;0,"",IF(AND(P37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
+        <v/>
+      </c>
+      <c r="R37" s="70" t="str">
         <f>CONCATENATE(F37)</f>
         <v/>
       </c>
-      <c r="S37" s="30" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,R37)&gt;0,"",IF(AND(R37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R37,Cant!$J$2:$J$100,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R37,Cant!$J$2:$J$100,"43/2.0"),"")),"")</f>
+      <c r="S37" s="263" t="str">
+        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(AND(R37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R37,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R37,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="212"/>
-      <c r="B38" s="72" t="str" cm="1">
+      <c r="A38" s="245"/>
+      <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
       </c>
-      <c r="C38" s="136" t="str">
+      <c r="C38" s="135" t="str">
         <f>IF(D38="buc",IF(B38&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B38,Deco!$Y$2:$Y$99,0)),""),IF(B38&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B38,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4710,79 +4824,85 @@
         <v>55</v>
       </c>
       <c r="E38" s="2"/>
-      <c r="F38" s="93" t="str">
+      <c r="F38" s="92" t="str">
         <f>IF(B38&lt;&gt;"",TRIM(LEFT(B38,LEN(B38)-3)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="143" t="str">
-        <f>IFERROR(IF(COUNTIF(F$11:F$22,F38)&gt;0,"",IF(AND(F38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F38,Cant!$J$2:$J$100,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,F38,Cant!$J$2:$J$100,"22/0.4"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="104" t="str">
+      <c r="G38" s="142" t="str">
+        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(AND(F38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F38,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F38,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
+        <v/>
+      </c>
+      <c r="H38" s="103" t="str">
         <f>CONCATENATE(F38)</f>
         <v/>
       </c>
-      <c r="I38" s="144" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,H38)&gt;0,"",IF(AND(H38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H38,Cant!$J$2:$J$100,"22/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,H38,Cant!$J$2:$J$100,"22/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="114" t="str">
+      <c r="I38" s="100" t="str">
+        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(
+   IF(AND(H38&lt;&gt;"",
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H38,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H38,Cant!$J$2:$J$99,"23/1.0")&gt;0),
+      SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H38,Cant!$J$2:$J$99,"22/1.0")
+     +SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H38,Cant!$J$2:$J$99,"23/1.0"),
+   ""),""))</f>
+        <v/>
+      </c>
+      <c r="J38" s="113" t="str">
         <f>CONCATENATE(F38)</f>
         <v/>
       </c>
-      <c r="K38" s="145" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,J38)&gt;0,"",IF(AND(J38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J38,Cant!$J$2:$J$100,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,J38,Cant!$J$2:$J$100,"23/0.8"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="L38" s="123" t="str">
+      <c r="K38" s="144" t="str">
+        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(AND(J38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J38,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J38,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
+        <v/>
+      </c>
+      <c r="L38" s="122" t="str">
         <f>CONCATENATE(F38)</f>
         <v/>
       </c>
-      <c r="M38" s="146" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,L38)&gt;0,"",IF(AND(L38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L38,Cant!$J$2:$J$100,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,L38,Cant!$J$2:$J$100,"23/2.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="N38" s="72" t="str">
+      <c r="M38" s="145" t="str">
+        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(AND(L38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L38,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L38,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
+        <v/>
+      </c>
+      <c r="N38" s="71" t="str">
         <f>CONCATENATE(F38)</f>
         <v/>
       </c>
-      <c r="O38" s="31" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,N38)&gt;0,"",IF(AND(N38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="P38" s="72" t="str">
+      <c r="O38" s="30" t="str">
+        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(COUNTIF(H$11:H$22,N38)&gt;0,"",IF(AND(N38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,N38,Cant!$J$2:$J$100,"43/1.0"),"")),""))</f>
+        <v/>
+      </c>
+      <c r="P38" s="71" t="str">
         <f>CONCATENATE(F38)</f>
         <v/>
       </c>
-      <c r="Q38" s="31" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,P38)&gt;0,"",IF(AND(P38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P38,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P38,Cant!$J$2:$J$100,"43/1.5"),"")),"")</f>
-        <v/>
-      </c>
-      <c r="R38" s="72" t="str">
+      <c r="Q38" s="30" t="str">
+        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P38)&gt;0,"",IF(AND(P38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P38,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P38,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
+        <v/>
+      </c>
+      <c r="R38" s="71" t="str">
         <f>CONCATENATE(F38)</f>
         <v/>
       </c>
-      <c r="S38" s="31" t="str">
-        <f>IFERROR(IF(COUNTIF(H$11:H$22,R38)&gt;0,"",IF(AND(R38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R38,Cant!$J$2:$J$100,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,R38,Cant!$J$2:$J$100,"43/2.0"),"")),"")</f>
+      <c r="S38" s="263" t="str">
+        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(AND(R38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R38,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R38,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="39" spans="1:19" ht="2.1" hidden="1" customHeight="1">
-      <c r="F39" s="64"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="64"/>
-      <c r="I39" s="64"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="64"/>
-      <c r="L39" s="64"/>
-      <c r="M39" s="64"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="64"/>
-      <c r="P39" s="64"/>
-      <c r="Q39" s="65"/>
+      <c r="F39" s="63"/>
+      <c r="G39" s="63"/>
+      <c r="H39" s="63"/>
+      <c r="I39" s="63"/>
+      <c r="J39" s="63"/>
+      <c r="K39" s="63"/>
+      <c r="L39" s="63"/>
+      <c r="M39" s="63"/>
+      <c r="N39" s="63"/>
+      <c r="O39" s="63"/>
+      <c r="P39" s="63"/>
+      <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="246" t="s">
+      <c r="A40" s="210" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4794,25 +4914,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="237" t="s">
+      <c r="F40" s="203" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="238"/>
-      <c r="H40" s="238"/>
-      <c r="I40" s="238"/>
-      <c r="J40" s="238"/>
-      <c r="K40" s="238"/>
-      <c r="L40" s="238"/>
-      <c r="M40" s="238"/>
-      <c r="N40" s="238"/>
-      <c r="O40" s="238"/>
-      <c r="P40" s="238"/>
-      <c r="Q40" s="238"/>
-      <c r="R40" s="238"/>
-      <c r="S40" s="239"/>
+      <c r="G40" s="204"/>
+      <c r="H40" s="204"/>
+      <c r="I40" s="204"/>
+      <c r="J40" s="204"/>
+      <c r="K40" s="204"/>
+      <c r="L40" s="204"/>
+      <c r="M40" s="204"/>
+      <c r="N40" s="204"/>
+      <c r="O40" s="204"/>
+      <c r="P40" s="204"/>
+      <c r="Q40" s="204"/>
+      <c r="R40" s="204"/>
+      <c r="S40" s="205"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="185"/>
+      <c r="A41" s="211"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -4820,62 +4940,62 @@
         <f>SUMIF(Taiere!I2:I99, "PAL", Taiere!C2:C99)</f>
         <v>0</v>
       </c>
-      <c r="D41" s="74" t="s">
+      <c r="D41" s="73" t="s">
         <v>54</v>
       </c>
       <c r="E41" s="2"/>
-      <c r="F41" s="76" t="s">
+      <c r="F41" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="G41" s="61">
+      <c r="G41" s="60">
         <f>SUM(G11:G29)+SUM(G32:G38)</f>
         <v>0</v>
       </c>
       <c r="H41" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="I41" s="61">
+      <c r="I41" s="60">
         <f>SUM(I11:I29)+SUM(I32:I38)</f>
         <v>0</v>
       </c>
       <c r="J41" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="K41" s="61">
+      <c r="K41" s="60">
         <f>SUM(K11:K29)+SUM(K32:K38)</f>
         <v>0</v>
       </c>
       <c r="L41" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="M41" s="61">
+      <c r="M41" s="60">
         <f>SUM(M11:M29)+SUM(M32:M38)</f>
         <v>0</v>
       </c>
       <c r="N41" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="O41" s="61">
+      <c r="O41" s="60">
         <f>SUM(O11:O29)+SUM(O32:O38)</f>
         <v>0</v>
       </c>
       <c r="P41" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="Q41" s="61">
+      <c r="Q41" s="60">
         <f>SUM(Q11:Q29)+SUM(Q32:Q38)</f>
         <v>0</v>
       </c>
       <c r="R41" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="S41" s="61">
+      <c r="S41" s="60">
         <f>SUM(S11:S29)+SUM(S32:S38)</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="185"/>
+      <c r="A42" s="211"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -4883,27 +5003,27 @@
         <f>SUMIF(Taiere!I2:I99, "CLEAF", Taiere!C2:C99)</f>
         <v>0</v>
       </c>
-      <c r="D42" s="75" t="s">
+      <c r="D42" s="74" t="s">
         <v>54</v>
       </c>
       <c r="E42" s="2"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="82"/>
-      <c r="H42" s="69"/>
-      <c r="I42" s="82"/>
-      <c r="J42" s="70"/>
-      <c r="K42" s="82"/>
-      <c r="L42" s="69"/>
-      <c r="M42" s="82"/>
-      <c r="N42" s="70"/>
-      <c r="O42" s="82"/>
-      <c r="P42" s="70"/>
-      <c r="Q42" s="82"/>
-      <c r="R42" s="83"/>
-      <c r="S42" s="84"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="68"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="69"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="68"/>
+      <c r="M42" s="81"/>
+      <c r="N42" s="69"/>
+      <c r="O42" s="81"/>
+      <c r="P42" s="69"/>
+      <c r="Q42" s="81"/>
+      <c r="R42" s="82"/>
+      <c r="S42" s="83"/>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="185"/>
+      <c r="A43" s="211"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -4911,30 +5031,30 @@
         <f>SUMIF(B32:B34, "*/600", C32:C34) + SUMIF(B32:B34, "*/650", C32:C34)</f>
         <v>0</v>
       </c>
-      <c r="D43" s="75" t="s">
+      <c r="D43" s="74" t="s">
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="234" t="str">
+      <c r="F43" s="190" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="235"/>
-      <c r="H43" s="235"/>
-      <c r="I43" s="235"/>
-      <c r="J43" s="235"/>
-      <c r="K43" s="235"/>
-      <c r="L43" s="235"/>
-      <c r="M43" s="235"/>
-      <c r="N43" s="235"/>
-      <c r="O43" s="235"/>
-      <c r="P43" s="235"/>
-      <c r="Q43" s="235"/>
-      <c r="R43" s="235"/>
-      <c r="S43" s="236"/>
+      <c r="G43" s="191"/>
+      <c r="H43" s="191"/>
+      <c r="I43" s="191"/>
+      <c r="J43" s="191"/>
+      <c r="K43" s="191"/>
+      <c r="L43" s="191"/>
+      <c r="M43" s="191"/>
+      <c r="N43" s="191"/>
+      <c r="O43" s="191"/>
+      <c r="P43" s="191"/>
+      <c r="Q43" s="191"/>
+      <c r="R43" s="191"/>
+      <c r="S43" s="192"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="185"/>
+      <c r="A44" s="211"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -4942,7 +5062,7 @@
         <f>SUMIF(B32:B34, "*/920", C32:C34)</f>
         <v>0</v>
       </c>
-      <c r="D44" s="75" t="s">
+      <c r="D44" s="74" t="s">
         <v>55</v>
       </c>
       <c r="E44" s="2"/>
@@ -4990,7 +5110,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="185"/>
+      <c r="A45" s="211"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -4998,7 +5118,7 @@
         <f>SUM(C36:C38)</f>
         <v>0</v>
       </c>
-      <c r="D45" s="75" t="str">
+      <c r="D45" s="74" t="str">
         <f>IF(I3="Mobilier în Roomdesigner", "ml", "buc")</f>
         <v>buc</v>
       </c>
@@ -5019,7 +5139,7 @@
         <f>IFERROR(IF(H45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(H45,Deco!$Z$2:$Z$100,0)),""),"")</f>
         <v/>
       </c>
-      <c r="J45" s="72" t="str" cm="1">
+      <c r="J45" s="71" t="str" cm="1">
         <f t="array" ref="J45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),3))),"")</f>
         <v/>
       </c>
@@ -5027,7 +5147,7 @@
         <f>IFERROR(IF(J45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(J45,Deco!$Z$2:$Z$100,0)),""),"")</f>
         <v/>
       </c>
-      <c r="L45" s="72" t="str" cm="1">
+      <c r="L45" s="71" t="str" cm="1">
         <f t="array" ref="L45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),4))),"")</f>
         <v/>
       </c>
@@ -5035,7 +5155,7 @@
         <f>IFERROR(IF(L45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(L45,Deco!$Z$2:$Z$100,0)),""),"")</f>
         <v/>
       </c>
-      <c r="N45" s="72" t="str" cm="1">
+      <c r="N45" s="71" t="str" cm="1">
         <f t="array" ref="N45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),5))),"")</f>
         <v/>
       </c>
@@ -5043,7 +5163,7 @@
         <f>IFERROR(IF(N45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(N45,Deco!$Z$2:$Z$100,0)),""),"")</f>
         <v/>
       </c>
-      <c r="P45" s="72" t="str" cm="1">
+      <c r="P45" s="71" t="str" cm="1">
         <f t="array" ref="P45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),6))),"")</f>
         <v/>
       </c>
@@ -5051,7 +5171,7 @@
         <f>IFERROR(IF(P45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(P45,Deco!$Z$2:$Z$100,0)),""),"")</f>
         <v/>
       </c>
-      <c r="R45" s="72" t="str" cm="1">
+      <c r="R45" s="71" t="str" cm="1">
         <f t="array" ref="R45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),7))),"")</f>
         <v/>
       </c>
@@ -5061,7 +5181,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="185"/>
+      <c r="A46" s="211"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5069,13 +5189,13 @@
         <f>IF(B30&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B30,Deco!$Y$2:$Y$99,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="75" t="s">
+      <c r="D46" s="74" t="s">
         <v>55</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="185"/>
+      <c r="A47" s="211"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5083,37 +5203,37 @@
         <f>SUMIF(Taiere!I2:I99, "MDF", Taiere!C2:C99)</f>
         <v>0</v>
       </c>
-      <c r="D47" s="75" t="s">
+      <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="204" t="s">
+      <c r="F47" s="171" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="217" t="str">
+      <c r="G47" s="250" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="204" t="s">
+      <c r="J47" s="171" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="206">
+      <c r="K47" s="239">
         <v>1</v>
       </c>
-      <c r="N47" s="204" t="s">
+      <c r="N47" s="171" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="252"/>
-      <c r="P47" s="253"/>
-      <c r="R47" s="204" t="s">
+      <c r="O47" s="173"/>
+      <c r="P47" s="174"/>
+      <c r="R47" s="171" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="204" t="e">
+      <c r="S47" s="171" t="e">
         <f>IF(#REF!=2,"O","X")</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="186"/>
+      <c r="A48" s="213"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5121,18 +5241,18 @@
         <f>SUM(F45:S45)</f>
         <v>0</v>
       </c>
-      <c r="D48" s="73" t="s">
+      <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="205"/>
-      <c r="G48" s="218"/>
-      <c r="J48" s="205"/>
-      <c r="K48" s="207"/>
-      <c r="N48" s="251"/>
-      <c r="O48" s="254"/>
-      <c r="P48" s="255"/>
-      <c r="R48" s="251"/>
-      <c r="S48" s="205"/>
+      <c r="F48" s="219"/>
+      <c r="G48" s="251"/>
+      <c r="J48" s="219"/>
+      <c r="K48" s="240"/>
+      <c r="N48" s="172"/>
+      <c r="O48" s="175"/>
+      <c r="P48" s="176"/>
+      <c r="R48" s="172"/>
+      <c r="S48" s="219"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5141,186 +5261,193 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="184" t="s">
+      <c r="A50" s="223" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="195"/>
-      <c r="C50" s="196"/>
-      <c r="D50" s="196"/>
-      <c r="E50" s="196"/>
-      <c r="F50" s="196"/>
-      <c r="G50" s="196"/>
-      <c r="H50" s="196"/>
-      <c r="I50" s="196"/>
-      <c r="J50" s="196"/>
-      <c r="K50" s="196"/>
-      <c r="L50" s="196"/>
-      <c r="M50" s="196"/>
-      <c r="N50" s="196"/>
-      <c r="O50" s="196"/>
-      <c r="P50" s="196"/>
-      <c r="Q50" s="196"/>
-      <c r="R50" s="196"/>
-      <c r="S50" s="197"/>
+      <c r="B50" s="230"/>
+      <c r="C50" s="231"/>
+      <c r="D50" s="231"/>
+      <c r="E50" s="231"/>
+      <c r="F50" s="231"/>
+      <c r="G50" s="231"/>
+      <c r="H50" s="231"/>
+      <c r="I50" s="231"/>
+      <c r="J50" s="231"/>
+      <c r="K50" s="231"/>
+      <c r="L50" s="231"/>
+      <c r="M50" s="231"/>
+      <c r="N50" s="231"/>
+      <c r="O50" s="231"/>
+      <c r="P50" s="231"/>
+      <c r="Q50" s="231"/>
+      <c r="R50" s="231"/>
+      <c r="S50" s="232"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="185"/>
-      <c r="B51" s="198"/>
-      <c r="C51" s="199"/>
-      <c r="D51" s="199"/>
-      <c r="E51" s="199"/>
-      <c r="F51" s="199"/>
-      <c r="G51" s="199"/>
-      <c r="H51" s="199"/>
-      <c r="I51" s="199"/>
-      <c r="J51" s="199"/>
-      <c r="K51" s="199"/>
-      <c r="L51" s="199"/>
-      <c r="M51" s="199"/>
-      <c r="N51" s="199"/>
-      <c r="O51" s="199"/>
-      <c r="P51" s="199"/>
-      <c r="Q51" s="199"/>
-      <c r="R51" s="199"/>
-      <c r="S51" s="200"/>
+      <c r="A51" s="211"/>
+      <c r="B51" s="233"/>
+      <c r="C51" s="234"/>
+      <c r="D51" s="234"/>
+      <c r="E51" s="234"/>
+      <c r="F51" s="234"/>
+      <c r="G51" s="234"/>
+      <c r="H51" s="234"/>
+      <c r="I51" s="234"/>
+      <c r="J51" s="234"/>
+      <c r="K51" s="234"/>
+      <c r="L51" s="234"/>
+      <c r="M51" s="234"/>
+      <c r="N51" s="234"/>
+      <c r="O51" s="234"/>
+      <c r="P51" s="234"/>
+      <c r="Q51" s="234"/>
+      <c r="R51" s="234"/>
+      <c r="S51" s="235"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="185"/>
-      <c r="B52" s="198"/>
-      <c r="C52" s="199"/>
-      <c r="D52" s="199"/>
-      <c r="E52" s="199"/>
-      <c r="F52" s="199"/>
-      <c r="G52" s="199"/>
-      <c r="H52" s="199"/>
-      <c r="I52" s="199"/>
-      <c r="J52" s="199"/>
-      <c r="K52" s="199"/>
-      <c r="L52" s="199"/>
-      <c r="M52" s="199"/>
-      <c r="N52" s="199"/>
-      <c r="O52" s="199"/>
-      <c r="P52" s="199"/>
-      <c r="Q52" s="199"/>
-      <c r="R52" s="199"/>
-      <c r="S52" s="200"/>
+      <c r="A52" s="211"/>
+      <c r="B52" s="233"/>
+      <c r="C52" s="234"/>
+      <c r="D52" s="234"/>
+      <c r="E52" s="234"/>
+      <c r="F52" s="234"/>
+      <c r="G52" s="234"/>
+      <c r="H52" s="234"/>
+      <c r="I52" s="234"/>
+      <c r="J52" s="234"/>
+      <c r="K52" s="234"/>
+      <c r="L52" s="234"/>
+      <c r="M52" s="234"/>
+      <c r="N52" s="234"/>
+      <c r="O52" s="234"/>
+      <c r="P52" s="234"/>
+      <c r="Q52" s="234"/>
+      <c r="R52" s="234"/>
+      <c r="S52" s="235"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="185"/>
-      <c r="B53" s="198"/>
-      <c r="C53" s="199"/>
-      <c r="D53" s="199"/>
-      <c r="E53" s="199"/>
-      <c r="F53" s="199"/>
-      <c r="G53" s="199"/>
-      <c r="H53" s="199"/>
-      <c r="I53" s="199"/>
-      <c r="J53" s="199"/>
-      <c r="K53" s="199"/>
-      <c r="L53" s="199"/>
-      <c r="M53" s="199"/>
-      <c r="N53" s="199"/>
-      <c r="O53" s="199"/>
-      <c r="P53" s="199"/>
-      <c r="Q53" s="199"/>
-      <c r="R53" s="199"/>
-      <c r="S53" s="200"/>
+      <c r="A53" s="211"/>
+      <c r="B53" s="233"/>
+      <c r="C53" s="234"/>
+      <c r="D53" s="234"/>
+      <c r="E53" s="234"/>
+      <c r="F53" s="234"/>
+      <c r="G53" s="234"/>
+      <c r="H53" s="234"/>
+      <c r="I53" s="234"/>
+      <c r="J53" s="234"/>
+      <c r="K53" s="234"/>
+      <c r="L53" s="234"/>
+      <c r="M53" s="234"/>
+      <c r="N53" s="234"/>
+      <c r="O53" s="234"/>
+      <c r="P53" s="234"/>
+      <c r="Q53" s="234"/>
+      <c r="R53" s="234"/>
+      <c r="S53" s="235"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="185"/>
-      <c r="B54" s="198"/>
-      <c r="C54" s="199"/>
-      <c r="D54" s="199"/>
-      <c r="E54" s="199"/>
-      <c r="F54" s="199"/>
-      <c r="G54" s="199"/>
-      <c r="H54" s="199"/>
-      <c r="I54" s="199"/>
-      <c r="J54" s="199"/>
-      <c r="K54" s="199"/>
-      <c r="L54" s="199"/>
-      <c r="M54" s="199"/>
-      <c r="N54" s="199"/>
-      <c r="O54" s="199"/>
-      <c r="P54" s="199"/>
-      <c r="Q54" s="199"/>
-      <c r="R54" s="199"/>
-      <c r="S54" s="200"/>
+      <c r="A54" s="211"/>
+      <c r="B54" s="233"/>
+      <c r="C54" s="234"/>
+      <c r="D54" s="234"/>
+      <c r="E54" s="234"/>
+      <c r="F54" s="234"/>
+      <c r="G54" s="234"/>
+      <c r="H54" s="234"/>
+      <c r="I54" s="234"/>
+      <c r="J54" s="234"/>
+      <c r="K54" s="234"/>
+      <c r="L54" s="234"/>
+      <c r="M54" s="234"/>
+      <c r="N54" s="234"/>
+      <c r="O54" s="234"/>
+      <c r="P54" s="234"/>
+      <c r="Q54" s="234"/>
+      <c r="R54" s="234"/>
+      <c r="S54" s="235"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="185"/>
-      <c r="B55" s="198"/>
-      <c r="C55" s="199"/>
-      <c r="D55" s="199"/>
-      <c r="E55" s="199"/>
-      <c r="F55" s="199"/>
-      <c r="G55" s="199"/>
-      <c r="H55" s="199"/>
-      <c r="I55" s="199"/>
-      <c r="J55" s="199"/>
-      <c r="K55" s="199"/>
-      <c r="L55" s="199"/>
-      <c r="M55" s="199"/>
-      <c r="N55" s="199"/>
-      <c r="O55" s="199"/>
-      <c r="P55" s="199"/>
-      <c r="Q55" s="199"/>
-      <c r="R55" s="199"/>
-      <c r="S55" s="200"/>
+      <c r="A55" s="211"/>
+      <c r="B55" s="233"/>
+      <c r="C55" s="234"/>
+      <c r="D55" s="234"/>
+      <c r="E55" s="234"/>
+      <c r="F55" s="234"/>
+      <c r="G55" s="234"/>
+      <c r="H55" s="234"/>
+      <c r="I55" s="234"/>
+      <c r="J55" s="234"/>
+      <c r="K55" s="234"/>
+      <c r="L55" s="234"/>
+      <c r="M55" s="234"/>
+      <c r="N55" s="234"/>
+      <c r="O55" s="234"/>
+      <c r="P55" s="234"/>
+      <c r="Q55" s="234"/>
+      <c r="R55" s="234"/>
+      <c r="S55" s="235"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="185"/>
-      <c r="B56" s="198"/>
-      <c r="C56" s="199"/>
-      <c r="D56" s="199"/>
-      <c r="E56" s="199"/>
-      <c r="F56" s="199"/>
-      <c r="G56" s="199"/>
-      <c r="H56" s="199"/>
-      <c r="I56" s="199"/>
-      <c r="J56" s="199"/>
-      <c r="K56" s="199"/>
-      <c r="L56" s="199"/>
-      <c r="M56" s="199"/>
-      <c r="N56" s="199"/>
-      <c r="O56" s="199"/>
-      <c r="P56" s="199"/>
-      <c r="Q56" s="199"/>
-      <c r="R56" s="199"/>
-      <c r="S56" s="200"/>
+      <c r="A56" s="211"/>
+      <c r="B56" s="233"/>
+      <c r="C56" s="234"/>
+      <c r="D56" s="234"/>
+      <c r="E56" s="234"/>
+      <c r="F56" s="234"/>
+      <c r="G56" s="234"/>
+      <c r="H56" s="234"/>
+      <c r="I56" s="234"/>
+      <c r="J56" s="234"/>
+      <c r="K56" s="234"/>
+      <c r="L56" s="234"/>
+      <c r="M56" s="234"/>
+      <c r="N56" s="234"/>
+      <c r="O56" s="234"/>
+      <c r="P56" s="234"/>
+      <c r="Q56" s="234"/>
+      <c r="R56" s="234"/>
+      <c r="S56" s="235"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="186"/>
-      <c r="B57" s="201"/>
-      <c r="C57" s="202"/>
-      <c r="D57" s="202"/>
-      <c r="E57" s="202"/>
-      <c r="F57" s="202"/>
-      <c r="G57" s="202"/>
-      <c r="H57" s="202"/>
-      <c r="I57" s="202"/>
-      <c r="J57" s="202"/>
-      <c r="K57" s="202"/>
-      <c r="L57" s="202"/>
-      <c r="M57" s="202"/>
-      <c r="N57" s="202"/>
-      <c r="O57" s="202"/>
-      <c r="P57" s="202"/>
-      <c r="Q57" s="202"/>
-      <c r="R57" s="202"/>
-      <c r="S57" s="203"/>
+      <c r="A57" s="213"/>
+      <c r="B57" s="236"/>
+      <c r="C57" s="237"/>
+      <c r="D57" s="237"/>
+      <c r="E57" s="237"/>
+      <c r="F57" s="237"/>
+      <c r="G57" s="237"/>
+      <c r="H57" s="237"/>
+      <c r="I57" s="237"/>
+      <c r="J57" s="237"/>
+      <c r="K57" s="237"/>
+      <c r="L57" s="237"/>
+      <c r="M57" s="237"/>
+      <c r="N57" s="237"/>
+      <c r="O57" s="237"/>
+      <c r="P57" s="237"/>
+      <c r="Q57" s="237"/>
+      <c r="R57" s="237"/>
+      <c r="S57" s="238"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="F43:S43"/>
-    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B50:S57"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="O6:S6"/>
@@ -5337,22 +5464,15 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="R47:R48"/>
     <mergeCell ref="S47:S48"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="B50:S57"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="F43:S43"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5403,7 +5523,7 @@
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="129"/>
+    <col min="5" max="5" width="9.140625" style="128"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5431,7 +5551,7 @@
         <f>CONCATENATE(A2," ",F2)</f>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E2" s="129" t="str" cm="1">
+      <c r="E2" s="128" t="str" cm="1">
         <f t="array" ref="E2">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B11,3)="AGT",B2*3.416, IF(OR(RIGHT(Fisa!B11,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B11,2)="SM",RIGHT(Fisa!B11,2)="PM",RIGHT(Fisa!B11,2)="PG",RIGHT(Fisa!B11,2)="mm"), B2*5.796, B2)),B2)</f>
         <v/>
       </c>
@@ -5456,7 +5576,7 @@
         <f t="shared" ref="D3:D24" si="0">CONCATENATE(A3," ",F3)</f>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E3" s="129" t="str" cm="1">
+      <c r="E3" s="128" t="str" cm="1">
         <f t="array" ref="E3">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B12,3)="AGT",B3*3.416, IF(OR(RIGHT(Fisa!B12,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B12,2)="SM",RIGHT(Fisa!B12,2)="PM",RIGHT(Fisa!B12,2)="PG",RIGHT(Fisa!B12,2)="mm"), B3*5.796, B3)),B3)</f>
         <v/>
       </c>
@@ -5481,7 +5601,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E4" s="129" t="str" cm="1">
+      <c r="E4" s="128" t="str" cm="1">
         <f t="array" ref="E4">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B13,3)="AGT",B4*3.416, IF(OR(RIGHT(Fisa!B13,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B13,2)="SM",RIGHT(Fisa!B13,2)="PM",RIGHT(Fisa!B13,2)="PG",RIGHT(Fisa!B13,2)="mm"), B4*5.796, B4)),B4)</f>
         <v/>
       </c>
@@ -5490,9 +5610,9 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" t="str">
+      <c r="A5">
         <f>Fisa!B14</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B5" t="str">
         <f>Fisa!C14</f>
@@ -5504,9 +5624,9 @@
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> mp</v>
-      </c>
-      <c r="E5" s="129" t="str" cm="1">
+        <v>0 mp</v>
+      </c>
+      <c r="E5" s="128" t="str" cm="1">
         <f t="array" ref="E5">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B14,3)="AGT",B5*3.416, IF(OR(RIGHT(Fisa!B14,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B14,2)="SM",RIGHT(Fisa!B14,2)="PM",RIGHT(Fisa!B14,2)="PG",RIGHT(Fisa!B14,2)="mm"), B5*5.796, B5)),B5)</f>
         <v/>
       </c>
@@ -5515,9 +5635,9 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" t="str">
+      <c r="A6">
         <f>Fisa!B15</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="B6" t="str">
         <f>Fisa!C15</f>
@@ -5529,9 +5649,9 @@
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> mp</v>
-      </c>
-      <c r="E6" s="129" t="str" cm="1">
+        <v>0 mp</v>
+      </c>
+      <c r="E6" s="128" t="str" cm="1">
         <f t="array" ref="E6">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B15,3)="AGT",B6*3.416, IF(OR(RIGHT(Fisa!B15,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B15,2)="SM",RIGHT(Fisa!B15,2)="PM",RIGHT(Fisa!B15,2)="PG",RIGHT(Fisa!B15,2)="mm"), B6*5.796, B6)),B6)</f>
         <v/>
       </c>
@@ -5556,7 +5676,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E7" s="129" t="str" cm="1">
+      <c r="E7" s="128" t="str" cm="1">
         <f t="array" ref="E7">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B16,3)="AGT",B7*3.416, IF(OR(RIGHT(Fisa!B16,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B16,2)="SM",RIGHT(Fisa!B16,2)="PM",RIGHT(Fisa!B16,2)="PG",RIGHT(Fisa!B16,2)="mm"), B7*5.796, B7)),B7)</f>
         <v/>
       </c>
@@ -5581,7 +5701,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E8" s="129" t="str" cm="1">
+      <c r="E8" s="128" t="str" cm="1">
         <f t="array" ref="E8">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B17,3)="AGT",B8*3.416, IF(OR(RIGHT(Fisa!B17,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B17,2)="SM",RIGHT(Fisa!B17,2)="PM",RIGHT(Fisa!B17,2)="PG",RIGHT(Fisa!B17,2)="mm"), B8*5.796, B8)),B8)</f>
         <v/>
       </c>
@@ -5606,7 +5726,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E9" s="129" t="str" cm="1">
+      <c r="E9" s="128" t="str" cm="1">
         <f t="array" ref="E9">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B18,3)="AGT",B9*3.416, IF(OR(RIGHT(Fisa!B18,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B18,2)="SM",RIGHT(Fisa!B18,2)="PM",RIGHT(Fisa!B18,2)="PG",RIGHT(Fisa!B18,2)="mm"), B9*5.796, B9)),B9)</f>
         <v/>
       </c>
@@ -5631,7 +5751,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E10" s="129" t="str" cm="1">
+      <c r="E10" s="128" t="str" cm="1">
         <f t="array" ref="E10">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B19,3)="AGT",B10*3.416, IF(OR(RIGHT(Fisa!B19,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B19,2)="SM",RIGHT(Fisa!B19,2)="PM",RIGHT(Fisa!B19,2)="PG",RIGHT(Fisa!B19,2)="mm"), B10*5.796, B10)),B10)</f>
         <v/>
       </c>
@@ -5656,7 +5776,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E11" s="129" t="str" cm="1">
+      <c r="E11" s="128" t="str" cm="1">
         <f t="array" ref="E11">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B20,3)="AGT",B11*3.416, IF(OR(RIGHT(Fisa!B20,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B20,2)="SM",RIGHT(Fisa!B20,2)="PM",RIGHT(Fisa!B20,2)="PG",RIGHT(Fisa!B20,2)="mm"), B11*5.796, B11)),B11)</f>
         <v/>
       </c>
@@ -5681,7 +5801,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E12" s="129" t="str" cm="1">
+      <c r="E12" s="128" t="str" cm="1">
         <f t="array" ref="E12">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B21,3)="AGT",B12*3.416, IF(OR(RIGHT(Fisa!B21,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B21,2)="SM",RIGHT(Fisa!B21,2)="PM",RIGHT(Fisa!B21,2)="PG",RIGHT(Fisa!B21,2)="mm"), B12*5.796, B12)),B12)</f>
         <v/>
       </c>
@@ -5706,7 +5826,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E13" s="129" t="str" cm="1">
+      <c r="E13" s="128" t="str" cm="1">
         <f t="array" ref="E13">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B22,3)="AGT",B13*3.416, IF(OR(RIGHT(Fisa!B22,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B22,2)="SM",RIGHT(Fisa!B22,2)="PM",RIGHT(Fisa!B22,2)="PG",RIGHT(Fisa!B22,2)="mm"), B13*5.796, B13)),B13)</f>
         <v/>
       </c>
@@ -5731,7 +5851,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E14" s="129" t="str" cm="1">
+      <c r="E14" s="128" t="str" cm="1">
         <f t="array" ref="E14">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B24,3)="AGT",B14*3.416, IF(OR(RIGHT(Fisa!B24,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B24,2)="SM",RIGHT(Fisa!B24,2)="PM",RIGHT(Fisa!B24,2)="PG",RIGHT(Fisa!B24,2)="mm"), B14*5.796, B14)),B14)</f>
         <v/>
       </c>
@@ -5756,7 +5876,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E15" s="129" t="str" cm="1">
+      <c r="E15" s="128" t="str" cm="1">
         <f t="array" ref="E15">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B25,3)="AGT",B15*3.416, IF(OR(RIGHT(Fisa!B25,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B25,2)="SM",RIGHT(Fisa!B25,2)="PM",RIGHT(Fisa!B25,2)="PG",RIGHT(Fisa!B25,2)="mm"), B15*5.796, B15)),B15)</f>
         <v/>
       </c>
@@ -5781,7 +5901,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E16" s="129" t="str" cm="1">
+      <c r="E16" s="128" t="str" cm="1">
         <f t="array" ref="E16">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B26,3)="AGT",B16*3.416, IF(OR(RIGHT(Fisa!B26,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B26,2)="SM",RIGHT(Fisa!B26,2)="PM",RIGHT(Fisa!B26,2)="PG",RIGHT(Fisa!B26,2)="mm"), B16*5.796, B16)),B16)</f>
         <v/>
       </c>
@@ -5806,7 +5926,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E17" s="129" t="str" cm="1">
+      <c r="E17" s="128" t="str" cm="1">
         <f t="array" ref="E17">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B27,3)="AGT",B17*3.416, IF(OR(RIGHT(Fisa!B27,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B27,2)="SM",RIGHT(Fisa!B27,2)="PM",RIGHT(Fisa!B27,2)="PG",RIGHT(Fisa!B27,2)="mm"), B17*5.796, B17)),B17)</f>
         <v/>
       </c>
@@ -5831,7 +5951,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E18" s="129" t="str" cm="1">
+      <c r="E18" s="128" t="str" cm="1">
         <f t="array" ref="E18">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B28,3)="AGT",B18*3.416, IF(OR(RIGHT(Fisa!B28,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B28,2)="SM",RIGHT(Fisa!B28,2)="PM",RIGHT(Fisa!B28,2)="PG",RIGHT(Fisa!B28,2)="mm"), B18*5.796, B18)),B18)</f>
         <v/>
       </c>
@@ -5856,7 +5976,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E19" s="129" t="str">
+      <c r="E19" s="128" t="str">
         <f>IFERROR(B19*4.1, "")</f>
         <v/>
       </c>
@@ -5881,7 +6001,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E20" s="129" t="str">
+      <c r="E20" s="128" t="str">
         <f>IFERROR(B20*4.1, "")</f>
         <v/>
       </c>
@@ -5906,7 +6026,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E21" s="129" t="str">
+      <c r="E21" s="128" t="str">
         <f>IFERROR(B21*4.1, "")</f>
         <v/>
       </c>
@@ -5931,7 +6051,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E22" s="129" t="str">
+      <c r="E22" s="128" t="str">
         <f t="shared" ref="E22:E24" si="1">IFERROR(B22*4.1, "")</f>
         <v/>
       </c>
@@ -5956,7 +6076,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E23" s="129" t="str">
+      <c r="E23" s="128" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5981,7 +6101,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E24" s="129" t="str">
+      <c r="E24" s="128" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8515,18 +8635,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customFormat="1">
-      <c r="A1" s="268" t="s">
+      <c r="A1" s="258" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="268"/>
-      <c r="C1" s="268"/>
-      <c r="D1" s="268"/>
-      <c r="E1" s="268"/>
-      <c r="F1" s="268"/>
-      <c r="G1" s="268"/>
-      <c r="H1" s="268"/>
-      <c r="I1" s="268"/>
-      <c r="J1" s="268"/>
+      <c r="B1" s="258"/>
+      <c r="C1" s="258"/>
+      <c r="D1" s="258"/>
+      <c r="E1" s="258"/>
+      <c r="F1" s="258"/>
+      <c r="G1" s="258"/>
+      <c r="H1" s="258"/>
+      <c r="I1" s="258"/>
+      <c r="J1" s="258"/>
       <c r="K1" s="12"/>
       <c r="L1" s="5"/>
     </row>
@@ -8547,15 +8667,15 @@
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="269">
+      <c r="B3" s="259">
         <f>Fisa!B3:D3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="269"/>
-      <c r="D3" s="269"/>
-      <c r="E3" s="269"/>
-      <c r="F3" s="269"/>
-      <c r="G3" s="269"/>
+      <c r="C3" s="259"/>
+      <c r="D3" s="259"/>
+      <c r="E3" s="259"/>
+      <c r="F3" s="259"/>
+      <c r="G3" s="259"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -8566,11 +8686,11 @@
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="270">
+      <c r="B4" s="260">
         <f>Fisa!B6</f>
         <v>0</v>
       </c>
-      <c r="C4" s="270"/>
+      <c r="C4" s="260"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -8698,9 +8818,9 @@
       <c r="L10" s="5"/>
     </row>
     <row r="11" spans="1:12" customFormat="1">
-      <c r="B11" s="8" t="str">
+      <c r="B11" s="8">
         <f>Fisa!B14</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C11" s="8" t="str">
         <f>Fisa!C14</f>
@@ -8717,9 +8837,9 @@
       <c r="L11" s="5"/>
     </row>
     <row r="12" spans="1:12" customFormat="1">
-      <c r="B12" s="8" t="str">
+      <c r="B12" s="8">
         <f>Fisa!B15</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C12" s="8" t="str">
         <f>Fisa!C15</f>
@@ -10018,7 +10138,7 @@
       <c r="L60" s="5"/>
     </row>
     <row r="61" spans="1:29" customFormat="1">
-      <c r="A61" s="126"/>
+      <c r="A61" s="125"/>
       <c r="B61" s="10" t="str">
         <f>Fisa!B37</f>
         <v/>
@@ -10038,7 +10158,7 @@
       <c r="L61" s="5"/>
     </row>
     <row r="62" spans="1:29" customFormat="1">
-      <c r="A62" s="127"/>
+      <c r="A62" s="126"/>
       <c r="B62" s="10" t="str">
         <f>Fisa!B38</f>
         <v/>
@@ -10563,12 +10683,12 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="177"/>
+    <col min="18" max="18" width="9.140625" style="167"/>
     <col min="20" max="20" width="9.140625" customWidth="1"/>
     <col min="21" max="21" width="4.140625" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" style="180"/>
-    <col min="24" max="24" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" style="170"/>
+    <col min="24" max="24" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
@@ -10587,7 +10707,7 @@
       <c r="E1" t="s">
         <v>103</v>
       </c>
-      <c r="V1" s="180" t="s">
+      <c r="V1" s="170" t="s">
         <v>3</v>
       </c>
       <c r="W1" t="s">
@@ -10607,28 +10727,11 @@
       </c>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="160"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="175"/>
-      <c r="M2" s="158"/>
-      <c r="N2" s="158"/>
-      <c r="O2" s="158"/>
-      <c r="P2" s="158"/>
-      <c r="Q2" s="171"/>
-      <c r="R2" s="178"/>
-      <c r="S2" s="173"/>
-      <c r="T2" s="147"/>
-      <c r="U2" s="147"/>
-      <c r="V2" s="180">
+      <c r="R2" s="168"/>
+      <c r="S2" s="165"/>
+      <c r="T2" s="146"/>
+      <c r="U2" s="146"/>
+      <c r="V2" s="170">
         <f>IFERROR(IF(W2="DB",Q2/13.5, ROUND(Q2/P2,2)),"")</f>
         <v>0</v>
       </c>
@@ -10647,7 +10750,7 @@
 "AGT "&amp;TRIM(MID(A2,FIND("-",A2)+1,50)),
 TRIM(MID(A2,FIND("-",A2)+1,50)))
 &amp;IF(OR(E2=600,E2=650,E2=920)," /"&amp;E2,"")
-&amp;IF(E2=640," "&amp;"PS",""),"")</f>
+&amp;IF(E2=640," "&amp;"PS",""),"")&amp;IF(AND(OR(B2=8,B2=10,B2=16),D2=2800,E2=2070)," "&amp;B2&amp;"mm","")</f>
         <v/>
       </c>
       <c r="Y2" t="str">
@@ -10664,28 +10767,11 @@
       </c>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="159"/>
-      <c r="B3" s="157"/>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="157"/>
-      <c r="I3" s="157"/>
-      <c r="J3" s="157"/>
-      <c r="K3" s="157"/>
-      <c r="L3" s="176"/>
-      <c r="M3" s="157"/>
-      <c r="N3" s="157"/>
-      <c r="O3" s="157"/>
-      <c r="P3" s="157"/>
-      <c r="Q3" s="170"/>
-      <c r="R3" s="178"/>
-      <c r="S3" s="173"/>
-      <c r="T3" s="133"/>
-      <c r="U3" s="147"/>
-      <c r="V3" s="180">
+      <c r="R3" s="168"/>
+      <c r="S3" s="165"/>
+      <c r="T3" s="132"/>
+      <c r="U3" s="146"/>
+      <c r="V3" s="170">
         <f t="shared" ref="V3:V34" si="1">IFERROR(IF(W3="DB",Q3/13.5, ROUND(Q3/P3,2)),"")</f>
         <v>0</v>
       </c>
@@ -10704,7 +10790,7 @@
 "AGT "&amp;TRIM(MID(A3,FIND("-",A3)+1,50)),
 TRIM(MID(A3,FIND("-",A3)+1,50)))
 &amp;IF(OR(E3=600,E3=650,E3=920)," /"&amp;E3,"")
-&amp;IF(E3=640," "&amp;"PS",""),"")</f>
+&amp;IF(E3=640," "&amp;"PS",""),"")&amp;IF(AND(OR(B3=8,B3=10,B3=16),D3=2800,E3=2070)," "&amp;B3&amp;"mm","")</f>
         <v/>
       </c>
       <c r="Y3" t="str">
@@ -10721,28 +10807,11 @@
       </c>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="160"/>
-      <c r="B4" s="158"/>
-      <c r="C4" s="158"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="158"/>
-      <c r="F4" s="158"/>
-      <c r="G4" s="158"/>
-      <c r="H4" s="158"/>
-      <c r="I4" s="158"/>
-      <c r="J4" s="158"/>
-      <c r="K4" s="158"/>
-      <c r="L4" s="176"/>
-      <c r="M4" s="158"/>
-      <c r="N4" s="158"/>
-      <c r="O4" s="158"/>
-      <c r="P4" s="158"/>
-      <c r="Q4" s="171"/>
-      <c r="R4" s="178"/>
-      <c r="S4" s="173"/>
-      <c r="T4" s="147"/>
-      <c r="U4" s="133"/>
-      <c r="V4" s="180">
+      <c r="R4" s="168"/>
+      <c r="S4" s="165"/>
+      <c r="T4" s="146"/>
+      <c r="U4" s="132"/>
+      <c r="V4" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10768,28 +10837,11 @@
       </c>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="159"/>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="157"/>
-      <c r="H5" s="157"/>
-      <c r="I5" s="157"/>
-      <c r="J5" s="157"/>
-      <c r="K5" s="157"/>
-      <c r="L5" s="176"/>
-      <c r="M5" s="157"/>
-      <c r="N5" s="157"/>
-      <c r="O5" s="157"/>
-      <c r="P5" s="157"/>
-      <c r="Q5" s="170"/>
-      <c r="R5" s="178"/>
-      <c r="S5" s="173"/>
-      <c r="T5" s="147"/>
-      <c r="U5" s="133"/>
-      <c r="V5" s="180">
+      <c r="R5" s="168"/>
+      <c r="S5" s="165"/>
+      <c r="T5" s="146"/>
+      <c r="U5" s="132"/>
+      <c r="V5" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10815,28 +10867,11 @@
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="159"/>
-      <c r="B6" s="157"/>
-      <c r="C6" s="157"/>
-      <c r="D6" s="157"/>
-      <c r="E6" s="157"/>
-      <c r="F6" s="157"/>
-      <c r="G6" s="157"/>
-      <c r="H6" s="157"/>
-      <c r="I6" s="157"/>
-      <c r="J6" s="157"/>
-      <c r="K6" s="157"/>
-      <c r="L6" s="176"/>
-      <c r="M6" s="157"/>
-      <c r="N6" s="157"/>
-      <c r="O6" s="157"/>
-      <c r="P6" s="157"/>
-      <c r="Q6" s="170"/>
-      <c r="R6" s="178"/>
-      <c r="S6" s="173"/>
-      <c r="T6" s="147"/>
-      <c r="U6" s="133"/>
-      <c r="V6" s="180">
+      <c r="R6" s="168"/>
+      <c r="S6" s="165"/>
+      <c r="T6" s="146"/>
+      <c r="U6" s="132"/>
+      <c r="V6" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10862,28 +10897,11 @@
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="160"/>
-      <c r="B7" s="158"/>
-      <c r="C7" s="158"/>
-      <c r="D7" s="158"/>
-      <c r="E7" s="158"/>
-      <c r="F7" s="158"/>
-      <c r="G7" s="158"/>
-      <c r="H7" s="158"/>
-      <c r="I7" s="158"/>
-      <c r="J7" s="158"/>
-      <c r="K7" s="158"/>
-      <c r="L7" s="176"/>
-      <c r="M7" s="158"/>
-      <c r="N7" s="158"/>
-      <c r="O7" s="158"/>
-      <c r="P7" s="158"/>
-      <c r="Q7" s="171"/>
-      <c r="R7" s="178"/>
-      <c r="S7" s="173"/>
-      <c r="T7" s="133"/>
-      <c r="U7" s="133"/>
-      <c r="V7" s="180">
+      <c r="R7" s="168"/>
+      <c r="S7" s="165"/>
+      <c r="T7" s="132"/>
+      <c r="U7" s="132"/>
+      <c r="V7" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10909,28 +10927,11 @@
       </c>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="159"/>
-      <c r="B8" s="157"/>
-      <c r="C8" s="157"/>
-      <c r="D8" s="157"/>
-      <c r="E8" s="157"/>
-      <c r="F8" s="157"/>
-      <c r="G8" s="157"/>
-      <c r="H8" s="157"/>
-      <c r="I8" s="157"/>
-      <c r="J8" s="157"/>
-      <c r="K8" s="157"/>
-      <c r="L8" s="176"/>
-      <c r="M8" s="157"/>
-      <c r="N8" s="157"/>
-      <c r="O8" s="157"/>
-      <c r="P8" s="157"/>
-      <c r="Q8" s="170"/>
-      <c r="R8" s="178"/>
-      <c r="S8" s="173"/>
-      <c r="T8" s="147"/>
-      <c r="U8" s="133"/>
-      <c r="V8" s="180">
+      <c r="R8" s="168"/>
+      <c r="S8" s="165"/>
+      <c r="T8" s="146"/>
+      <c r="U8" s="132"/>
+      <c r="V8" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10956,28 +10957,11 @@
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="160"/>
-      <c r="B9" s="158"/>
-      <c r="C9" s="158"/>
-      <c r="D9" s="158"/>
-      <c r="E9" s="158"/>
-      <c r="F9" s="158"/>
-      <c r="G9" s="158"/>
-      <c r="H9" s="158"/>
-      <c r="I9" s="158"/>
-      <c r="J9" s="158"/>
-      <c r="K9" s="158"/>
-      <c r="L9" s="175"/>
-      <c r="M9" s="158"/>
-      <c r="N9" s="158"/>
-      <c r="O9" s="158"/>
-      <c r="P9" s="158"/>
-      <c r="Q9" s="171"/>
-      <c r="R9" s="178"/>
-      <c r="S9" s="173"/>
-      <c r="T9" s="147"/>
-      <c r="U9" s="131"/>
-      <c r="V9" s="180">
+      <c r="R9" s="168"/>
+      <c r="S9" s="165"/>
+      <c r="T9" s="146"/>
+      <c r="U9" s="130"/>
+      <c r="V9" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11003,28 +10987,11 @@
       </c>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="159"/>
-      <c r="B10" s="157"/>
-      <c r="C10" s="157"/>
-      <c r="D10" s="157"/>
-      <c r="E10" s="157"/>
-      <c r="F10" s="157"/>
-      <c r="G10" s="157"/>
-      <c r="H10" s="157"/>
-      <c r="I10" s="157"/>
-      <c r="J10" s="157"/>
-      <c r="K10" s="157"/>
-      <c r="L10" s="176"/>
-      <c r="M10" s="157"/>
-      <c r="N10" s="157"/>
-      <c r="O10" s="157"/>
-      <c r="P10" s="157"/>
-      <c r="Q10" s="170"/>
-      <c r="R10" s="178"/>
-      <c r="S10" s="173"/>
-      <c r="T10" s="147"/>
-      <c r="U10" s="147"/>
-      <c r="V10" s="180">
+      <c r="R10" s="168"/>
+      <c r="S10" s="165"/>
+      <c r="T10" s="146"/>
+      <c r="U10" s="146"/>
+      <c r="V10" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11050,28 +11017,11 @@
       </c>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="160"/>
-      <c r="B11" s="158"/>
-      <c r="C11" s="158"/>
-      <c r="D11" s="158"/>
-      <c r="E11" s="158"/>
-      <c r="F11" s="158"/>
-      <c r="G11" s="158"/>
-      <c r="H11" s="158"/>
-      <c r="I11" s="158"/>
-      <c r="J11" s="158"/>
-      <c r="K11" s="158"/>
-      <c r="L11" s="176"/>
-      <c r="M11" s="158"/>
-      <c r="N11" s="158"/>
-      <c r="O11" s="158"/>
-      <c r="P11" s="158"/>
-      <c r="Q11" s="171"/>
-      <c r="R11" s="178"/>
-      <c r="S11" s="173"/>
-      <c r="T11" s="147"/>
-      <c r="U11" s="147"/>
-      <c r="V11" s="180">
+      <c r="R11" s="168"/>
+      <c r="S11" s="165"/>
+      <c r="T11" s="146"/>
+      <c r="U11" s="146"/>
+      <c r="V11" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11097,28 +11047,11 @@
       </c>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="161"/>
-      <c r="B12" s="162"/>
-      <c r="C12" s="163"/>
-      <c r="D12" s="164"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="165"/>
-      <c r="G12" s="162"/>
-      <c r="H12" s="166"/>
-      <c r="I12" s="162"/>
-      <c r="J12" s="166"/>
-      <c r="K12" s="172"/>
-      <c r="L12" s="172"/>
-      <c r="M12" s="168"/>
-      <c r="N12" s="172"/>
-      <c r="O12" s="172"/>
-      <c r="P12" s="167"/>
-      <c r="Q12" s="172"/>
-      <c r="R12" s="178"/>
-      <c r="S12" s="134"/>
-      <c r="T12" s="134"/>
-      <c r="U12" s="134"/>
-      <c r="V12" s="180">
+      <c r="R12" s="168"/>
+      <c r="S12" s="133"/>
+      <c r="T12" s="133"/>
+      <c r="U12" s="133"/>
+      <c r="V12" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11144,28 +11077,11 @@
       </c>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="161"/>
-      <c r="B13" s="162"/>
-      <c r="C13" s="163"/>
-      <c r="D13" s="164"/>
-      <c r="E13" s="164"/>
-      <c r="F13" s="169"/>
-      <c r="G13" s="162"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="162"/>
-      <c r="J13" s="167"/>
-      <c r="K13" s="172"/>
-      <c r="L13" s="172"/>
-      <c r="M13" s="168"/>
-      <c r="N13" s="172"/>
-      <c r="O13" s="172"/>
-      <c r="P13" s="166"/>
-      <c r="Q13" s="172"/>
-      <c r="R13" s="178"/>
-      <c r="S13" s="167"/>
-      <c r="T13" s="166"/>
-      <c r="U13" s="174"/>
-      <c r="V13" s="180">
+      <c r="R13" s="168"/>
+      <c r="S13" s="161"/>
+      <c r="T13" s="160"/>
+      <c r="U13" s="166"/>
+      <c r="V13" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11191,28 +11107,11 @@
       </c>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="161"/>
-      <c r="B14" s="162"/>
-      <c r="C14" s="163"/>
-      <c r="D14" s="164"/>
-      <c r="E14" s="164"/>
-      <c r="F14" s="165"/>
-      <c r="G14" s="162"/>
-      <c r="H14" s="167"/>
-      <c r="I14" s="162"/>
-      <c r="J14" s="167"/>
-      <c r="K14" s="172"/>
-      <c r="L14" s="172"/>
-      <c r="M14" s="167"/>
-      <c r="N14" s="172"/>
-      <c r="O14" s="172"/>
-      <c r="P14" s="167"/>
-      <c r="Q14" s="172"/>
-      <c r="R14" s="178"/>
-      <c r="S14" s="166"/>
-      <c r="T14" s="167"/>
-      <c r="U14" s="174"/>
-      <c r="V14" s="180">
+      <c r="R14" s="168"/>
+      <c r="S14" s="160"/>
+      <c r="T14" s="161"/>
+      <c r="U14" s="166"/>
+      <c r="V14" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11238,11 +11137,11 @@
       </c>
     </row>
     <row r="15" spans="1:27">
-      <c r="R15" s="178"/>
-      <c r="S15" s="167"/>
-      <c r="T15" s="167"/>
-      <c r="U15" s="134"/>
-      <c r="V15" s="180">
+      <c r="R15" s="168"/>
+      <c r="S15" s="161"/>
+      <c r="T15" s="161"/>
+      <c r="U15" s="133"/>
+      <c r="V15" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11268,11 +11167,11 @@
       </c>
     </row>
     <row r="16" spans="1:27">
-      <c r="R16" s="179"/>
-      <c r="S16" s="167"/>
-      <c r="T16" s="167"/>
-      <c r="U16" s="133"/>
-      <c r="V16" s="180">
+      <c r="R16" s="169"/>
+      <c r="S16" s="161"/>
+      <c r="T16" s="161"/>
+      <c r="U16" s="132"/>
+      <c r="V16" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11298,28 +11197,11 @@
       </c>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="159"/>
-      <c r="B17" s="157"/>
-      <c r="C17" s="157"/>
-      <c r="D17" s="157"/>
-      <c r="E17" s="157"/>
-      <c r="F17" s="157"/>
-      <c r="G17" s="157"/>
-      <c r="H17" s="157"/>
-      <c r="I17" s="157"/>
-      <c r="J17" s="157"/>
-      <c r="K17" s="157"/>
-      <c r="L17" s="176"/>
-      <c r="M17" s="157"/>
-      <c r="N17" s="157"/>
-      <c r="O17" s="157"/>
-      <c r="P17" s="157"/>
-      <c r="Q17" s="170"/>
-      <c r="R17" s="179"/>
-      <c r="S17" s="167"/>
-      <c r="T17" s="167"/>
-      <c r="U17" s="133"/>
-      <c r="V17" s="180">
+      <c r="R17" s="169"/>
+      <c r="S17" s="161"/>
+      <c r="T17" s="161"/>
+      <c r="U17" s="132"/>
+      <c r="V17" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11345,28 +11227,28 @@
       </c>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="161"/>
-      <c r="B18" s="162"/>
-      <c r="C18" s="163"/>
-      <c r="D18" s="164"/>
-      <c r="E18" s="164"/>
-      <c r="F18" s="165"/>
-      <c r="G18" s="162"/>
-      <c r="H18" s="166"/>
-      <c r="I18" s="162"/>
-      <c r="J18" s="167"/>
-      <c r="K18" s="172"/>
-      <c r="L18" s="172"/>
-      <c r="M18" s="166"/>
-      <c r="N18" s="172"/>
-      <c r="O18" s="172"/>
-      <c r="P18" s="166"/>
-      <c r="Q18" s="172"/>
-      <c r="R18" s="179"/>
-      <c r="S18" s="167"/>
-      <c r="T18" s="167"/>
-      <c r="U18" s="133"/>
-      <c r="V18" s="180">
+      <c r="A18" s="155"/>
+      <c r="B18" s="156"/>
+      <c r="C18" s="157"/>
+      <c r="D18" s="158"/>
+      <c r="E18" s="158"/>
+      <c r="F18" s="159"/>
+      <c r="G18" s="156"/>
+      <c r="H18" s="160"/>
+      <c r="I18" s="156"/>
+      <c r="J18" s="161"/>
+      <c r="K18" s="164"/>
+      <c r="L18" s="164"/>
+      <c r="M18" s="160"/>
+      <c r="N18" s="164"/>
+      <c r="O18" s="164"/>
+      <c r="P18" s="160"/>
+      <c r="Q18" s="164"/>
+      <c r="R18" s="169"/>
+      <c r="S18" s="161"/>
+      <c r="T18" s="161"/>
+      <c r="U18" s="132"/>
+      <c r="V18" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11392,27 +11274,27 @@
       </c>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="161"/>
-      <c r="B19" s="162"/>
-      <c r="C19" s="163"/>
-      <c r="D19" s="164"/>
-      <c r="E19" s="164"/>
-      <c r="F19" s="165"/>
-      <c r="G19" s="162"/>
-      <c r="H19" s="166"/>
-      <c r="I19" s="162"/>
-      <c r="J19" s="166"/>
-      <c r="K19" s="172"/>
-      <c r="L19" s="172"/>
-      <c r="M19" s="168"/>
-      <c r="N19" s="172"/>
-      <c r="O19" s="172"/>
-      <c r="P19" s="167"/>
-      <c r="Q19" s="172"/>
-      <c r="R19" s="179"/>
-      <c r="S19" s="167"/>
-      <c r="T19" s="167"/>
-      <c r="V19" s="180">
+      <c r="A19" s="155"/>
+      <c r="B19" s="156"/>
+      <c r="C19" s="157"/>
+      <c r="D19" s="158"/>
+      <c r="E19" s="158"/>
+      <c r="F19" s="159"/>
+      <c r="G19" s="156"/>
+      <c r="H19" s="160"/>
+      <c r="I19" s="156"/>
+      <c r="J19" s="160"/>
+      <c r="K19" s="164"/>
+      <c r="L19" s="164"/>
+      <c r="M19" s="162"/>
+      <c r="N19" s="164"/>
+      <c r="O19" s="164"/>
+      <c r="P19" s="161"/>
+      <c r="Q19" s="164"/>
+      <c r="R19" s="169"/>
+      <c r="S19" s="161"/>
+      <c r="T19" s="161"/>
+      <c r="V19" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11438,27 +11320,27 @@
       </c>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="161"/>
-      <c r="B20" s="162"/>
-      <c r="C20" s="163"/>
-      <c r="D20" s="164"/>
-      <c r="E20" s="164"/>
-      <c r="F20" s="169"/>
-      <c r="G20" s="162"/>
-      <c r="H20" s="166"/>
-      <c r="I20" s="162"/>
-      <c r="J20" s="167"/>
-      <c r="K20" s="172"/>
-      <c r="L20" s="172"/>
-      <c r="M20" s="168"/>
-      <c r="N20" s="172"/>
-      <c r="O20" s="172"/>
-      <c r="P20" s="166"/>
-      <c r="Q20" s="172"/>
-      <c r="R20" s="179"/>
-      <c r="S20" s="166"/>
-      <c r="T20" s="162"/>
-      <c r="V20" s="180">
+      <c r="A20" s="155"/>
+      <c r="B20" s="156"/>
+      <c r="C20" s="157"/>
+      <c r="D20" s="158"/>
+      <c r="E20" s="158"/>
+      <c r="F20" s="163"/>
+      <c r="G20" s="156"/>
+      <c r="H20" s="160"/>
+      <c r="I20" s="156"/>
+      <c r="J20" s="161"/>
+      <c r="K20" s="164"/>
+      <c r="L20" s="164"/>
+      <c r="M20" s="162"/>
+      <c r="N20" s="164"/>
+      <c r="O20" s="164"/>
+      <c r="P20" s="160"/>
+      <c r="Q20" s="164"/>
+      <c r="R20" s="169"/>
+      <c r="S20" s="160"/>
+      <c r="T20" s="156"/>
+      <c r="V20" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11484,27 +11366,27 @@
       </c>
     </row>
     <row r="21" spans="1:27">
-      <c r="A21" s="161"/>
-      <c r="B21" s="162"/>
-      <c r="C21" s="163"/>
-      <c r="D21" s="164"/>
-      <c r="E21" s="164"/>
-      <c r="F21" s="165"/>
-      <c r="G21" s="162"/>
-      <c r="H21" s="167"/>
-      <c r="I21" s="162"/>
-      <c r="J21" s="167"/>
-      <c r="K21" s="172"/>
-      <c r="L21" s="172"/>
-      <c r="M21" s="167"/>
-      <c r="N21" s="172"/>
-      <c r="O21" s="172"/>
-      <c r="P21" s="167"/>
-      <c r="Q21" s="172"/>
-      <c r="R21" s="179"/>
-      <c r="S21" s="167"/>
-      <c r="T21" s="166"/>
-      <c r="V21" s="180">
+      <c r="A21" s="155"/>
+      <c r="B21" s="156"/>
+      <c r="C21" s="157"/>
+      <c r="D21" s="158"/>
+      <c r="E21" s="158"/>
+      <c r="F21" s="159"/>
+      <c r="G21" s="156"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="156"/>
+      <c r="J21" s="161"/>
+      <c r="K21" s="164"/>
+      <c r="L21" s="164"/>
+      <c r="M21" s="161"/>
+      <c r="N21" s="164"/>
+      <c r="O21" s="164"/>
+      <c r="P21" s="161"/>
+      <c r="Q21" s="164"/>
+      <c r="R21" s="169"/>
+      <c r="S21" s="161"/>
+      <c r="T21" s="160"/>
+      <c r="V21" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11530,7 +11412,7 @@
       </c>
     </row>
     <row r="22" spans="1:27">
-      <c r="V22" s="180">
+      <c r="V22" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11556,7 +11438,7 @@
       </c>
     </row>
     <row r="23" spans="1:27">
-      <c r="V23" s="180">
+      <c r="V23" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11582,7 +11464,7 @@
       </c>
     </row>
     <row r="24" spans="1:27">
-      <c r="V24" s="180">
+      <c r="V24" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11608,7 +11490,7 @@
       </c>
     </row>
     <row r="25" spans="1:27">
-      <c r="V25" s="180">
+      <c r="V25" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11630,7 +11512,7 @@
       </c>
     </row>
     <row r="26" spans="1:27">
-      <c r="V26" s="180">
+      <c r="V26" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11652,7 +11534,7 @@
       </c>
     </row>
     <row r="27" spans="1:27">
-      <c r="V27" s="180">
+      <c r="V27" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11674,7 +11556,7 @@
       </c>
     </row>
     <row r="28" spans="1:27">
-      <c r="V28" s="180">
+      <c r="V28" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11696,7 +11578,7 @@
       </c>
     </row>
     <row r="29" spans="1:27">
-      <c r="V29" s="180">
+      <c r="V29" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11718,7 +11600,7 @@
       </c>
     </row>
     <row r="30" spans="1:27">
-      <c r="V30" s="180">
+      <c r="V30" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11740,7 +11622,7 @@
       </c>
     </row>
     <row r="31" spans="1:27">
-      <c r="V31" s="180">
+      <c r="V31" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11762,7 +11644,7 @@
       </c>
     </row>
     <row r="32" spans="1:27">
-      <c r="V32" s="180">
+      <c r="V32" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11784,7 +11666,7 @@
       </c>
     </row>
     <row r="33" spans="22:27">
-      <c r="V33" s="180">
+      <c r="V33" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11806,7 +11688,7 @@
       </c>
     </row>
     <row r="34" spans="22:27">
-      <c r="V34" s="180">
+      <c r="V34" s="170">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11873,69 +11755,84 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="160"/>
-      <c r="B2" s="158"/>
-      <c r="C2" s="158"/>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
+      <c r="A2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2">
+        <v>43</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>75</v>
+      </c>
+      <c r="E2">
+        <v>3.9</v>
+      </c>
       <c r="H2" t="str">
         <f>RIGHT(A2,3)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="I2">
         <f>ROUNDUP(E2*1.03,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J23" si="0">CONCATENATE(B2,"/",H2)</f>
-        <v>/</v>
+        <v>43/2.0</v>
       </c>
       <c r="L2" t="str">
         <f>IFERROR(IF(ISNUMBER(VALUE(MID(A2,FIND("-",A2)+1,1))),
 "AGT "&amp;TRIM(MID(A2,FIND("-",A2)+1,FIND("@",SUBSTITUTE(A2,"-","@",LEN(A2)-LEN(SUBSTITUTE(A2,"-",""))))-FIND("-",A2)-1)),
 TRIM(MID(A2,FIND("-",A2)+1,FIND("@",SUBSTITUTE(A2,"-","@",LEN(A2)-LEN(SUBSTITUTE(A2,"-",""))))-FIND("-",A2)-1))),"")</f>
-        <v/>
+        <v>W 960 ST7</v>
       </c>
       <c r="M2" t="str">
         <f>IF(OR(ISNUMBER(FIND(" ST",L2)),ISNUMBER(FIND(" SM",L2)),ISNUMBER(FIND(" PM",L2)),ISNUMBER(FIND(" TM",L2)),ISNUMBER(FIND(" PG",L2)),ISNUMBER(FIND(" PA",L2))),SUBSTITUTE(L2," ","",1),L2)</f>
-        <v/>
+        <v>W960 ST7</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="159"/>
-      <c r="B3" s="157"/>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
+      <c r="A3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>75</v>
+      </c>
+      <c r="E3">
+        <v>4.7</v>
+      </c>
       <c r="H3" t="str">
         <f t="shared" ref="H3:H17" si="1">RIGHT(A3,3)</f>
-        <v/>
+        <v>2.0</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I23" si="2">ROUNDUP(E3*1.03,0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="0"/>
-        <v>/</v>
+        <v>23/2.0</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L23" si="3">IFERROR(IF(ISNUMBER(VALUE(MID(A3,FIND("-",A3)+1,1))),
 "AGT "&amp;TRIM(MID(A3,FIND("-",A3)+1,FIND("@",SUBSTITUTE(A3,"-","@",LEN(A3)-LEN(SUBSTITUTE(A3,"-",""))))-FIND("-",A3)-1)),
 TRIM(MID(A3,FIND("-",A3)+1,FIND("@",SUBSTITUTE(A3,"-","@",LEN(A3)-LEN(SUBSTITUTE(A3,"-",""))))-FIND("-",A3)-1))),"")</f>
-        <v/>
+        <v>W 960 ST7</v>
       </c>
       <c r="M3" t="str">
         <f t="shared" ref="M3:M23" si="4">IF(OR(ISNUMBER(FIND(" ST",L3)),ISNUMBER(FIND(" SM",L3)),ISNUMBER(FIND(" PM",L3)),ISNUMBER(FIND(" TM",L3)),ISNUMBER(FIND(" PG",L3)),ISNUMBER(FIND(" PA",L3))),SUBSTITUTE(L3," ","",1),L3)</f>
-        <v/>
+        <v>W960 ST7</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="160"/>
-      <c r="B4" s="158"/>
-      <c r="C4" s="158"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="158"/>
       <c r="H4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -11958,11 +11855,6 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="159"/>
-      <c r="B5" s="157"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="157"/>
-      <c r="E5" s="157"/>
       <c r="H5" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -11985,11 +11877,6 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="160"/>
-      <c r="B6" s="158"/>
-      <c r="C6" s="158"/>
-      <c r="D6" s="158"/>
-      <c r="E6" s="158"/>
       <c r="H6" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12012,11 +11899,6 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="159"/>
-      <c r="B7" s="157"/>
-      <c r="C7" s="157"/>
-      <c r="D7" s="157"/>
-      <c r="E7" s="157"/>
       <c r="H7" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12039,11 +11921,6 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="160"/>
-      <c r="B8" s="158"/>
-      <c r="C8" s="158"/>
-      <c r="D8" s="158"/>
-      <c r="E8" s="158"/>
       <c r="H8" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12066,11 +11943,6 @@
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="159"/>
-      <c r="B9" s="157"/>
-      <c r="C9" s="157"/>
-      <c r="D9" s="157"/>
-      <c r="E9" s="157"/>
       <c r="H9" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12093,11 +11965,6 @@
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="160"/>
-      <c r="B10" s="158"/>
-      <c r="C10" s="158"/>
-      <c r="D10" s="158"/>
-      <c r="E10" s="158"/>
       <c r="H10" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12120,11 +11987,6 @@
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="159"/>
-      <c r="B11" s="157"/>
-      <c r="C11" s="157"/>
-      <c r="D11" s="157"/>
-      <c r="E11" s="157"/>
       <c r="H11" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12147,11 +12009,11 @@
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="130"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="132"/>
-      <c r="D12" s="132"/>
-      <c r="E12" s="133"/>
+      <c r="A12" s="129"/>
+      <c r="B12" s="130"/>
+      <c r="C12" s="131"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="132"/>
       <c r="H12" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12174,11 +12036,11 @@
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="130"/>
-      <c r="B13" s="131"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="133"/>
+      <c r="A13" s="129"/>
+      <c r="B13" s="130"/>
+      <c r="C13" s="131"/>
+      <c r="D13" s="131"/>
+      <c r="E13" s="132"/>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12201,11 +12063,11 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="130"/>
-      <c r="B14" s="131"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="133"/>
+      <c r="A14" s="129"/>
+      <c r="B14" s="130"/>
+      <c r="C14" s="131"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="132"/>
       <c r="H14" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12228,11 +12090,11 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="160"/>
-      <c r="B15" s="158"/>
-      <c r="C15" s="158"/>
-      <c r="D15" s="158"/>
-      <c r="E15" s="158"/>
+      <c r="A15" s="154"/>
+      <c r="B15" s="153"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153"/>
+      <c r="E15" s="153"/>
       <c r="H15" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12413,136 +12275,97 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E513F1B3-515F-4901-AFA8-22A8293C50FF}">
-  <dimension ref="A2:I335"/>
+  <dimension ref="I2:I335"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9">
-      <c r="A2" s="159"/>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
+    <row r="2" spans="9:9">
       <c r="I2" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A2)), "CLEAF", Deco!W2)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="160"/>
-      <c r="B3" s="158"/>
-      <c r="C3" s="158"/>
+    <row r="3" spans="9:9">
       <c r="I3" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A3)), "CLEAF", Deco!W3)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="159"/>
-      <c r="B4" s="157"/>
-      <c r="C4" s="157"/>
+    <row r="4" spans="9:9">
       <c r="I4" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A4)), "CLEAF", Deco!W4)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="160"/>
-      <c r="B5" s="158"/>
-      <c r="C5" s="158"/>
+    <row r="5" spans="9:9">
       <c r="I5" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A5)), "CLEAF", Deco!W5)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="159"/>
-      <c r="B6" s="157"/>
-      <c r="C6" s="157"/>
+    <row r="6" spans="9:9">
       <c r="I6" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A6)), "CLEAF", Deco!W6)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="160"/>
-      <c r="B7" s="158"/>
-      <c r="C7" s="158"/>
+    <row r="7" spans="9:9">
       <c r="I7" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A7)), "CLEAF", Deco!W7)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="159"/>
-      <c r="B8" s="157"/>
-      <c r="C8" s="157"/>
+    <row r="8" spans="9:9">
       <c r="I8" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A8)), "CLEAF", Deco!W8)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="160"/>
-      <c r="B9" s="158"/>
-      <c r="C9" s="158"/>
+    <row r="9" spans="9:9">
       <c r="I9" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A9)), "CLEAF", Deco!W9)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="159"/>
-      <c r="B10" s="157"/>
-      <c r="C10" s="157"/>
-      <c r="D10" s="157"/>
+    <row r="10" spans="9:9">
       <c r="I10" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A10)), "CLEAF", Deco!W10)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="160"/>
-      <c r="B11" s="158"/>
-      <c r="C11" s="158"/>
-      <c r="D11" s="158"/>
+    <row r="11" spans="9:9">
       <c r="I11" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A11)), "CLEAF", Deco!W11)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="159"/>
-      <c r="B12" s="157"/>
-      <c r="C12" s="157"/>
+    <row r="12" spans="9:9">
       <c r="I12" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A12)), "CLEAF", Deco!W12)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="159"/>
-      <c r="B13" s="157"/>
-      <c r="C13" s="157"/>
-      <c r="D13" s="157"/>
+    <row r="13" spans="9:9">
       <c r="I13" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A13)), "CLEAF", Deco!W13)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="9:9">
       <c r="I14" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A14)), "CLEAF", Deco!W14)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="9:9">
       <c r="I15" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A15)), "CLEAF", Deco!W15)</f>
         <v>DB</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="9:9">
       <c r="I16" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A16)), "CLEAF", Deco!W16)</f>
         <v>DB</v>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E95382-2466-4C7B-BAEC-C6BFE40F2221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6A4074-81E8-45B4-9023-B522BC72D6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -1300,7 +1300,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="266">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1543,7 +1543,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1793,8 +1792,244 @@
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1850,230 +2085,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2081,21 +2095,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2574,33 +2573,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="234" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
-      <c r="F1" s="207"/>
-      <c r="G1" s="207"/>
-      <c r="H1" s="207"/>
-      <c r="I1" s="207"/>
-      <c r="J1" s="207"/>
-      <c r="K1" s="207"/>
-      <c r="L1" s="208"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
+      <c r="L1" s="236"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="196" t="s">
+      <c r="O1" s="219" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="197"/>
-      <c r="Q1" s="197"/>
-      <c r="R1" s="197"/>
-      <c r="S1" s="198"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="221"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2618,166 +2617,166 @@
       <c r="M2" s="42">
         <v>1</v>
       </c>
-      <c r="N2" s="84"/>
-      <c r="O2" s="199"/>
-      <c r="P2" s="200"/>
-      <c r="Q2" s="200"/>
-      <c r="R2" s="200"/>
-      <c r="S2" s="201"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="222"/>
+      <c r="P2" s="223"/>
+      <c r="Q2" s="223"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="224"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="216"/>
-      <c r="C3" s="217"/>
-      <c r="D3" s="218"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="244"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="220"/>
-      <c r="J3" s="221"/>
-      <c r="K3" s="222"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="177"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="209"/>
-      <c r="P3" s="194"/>
-      <c r="Q3" s="194"/>
-      <c r="R3" s="194"/>
-      <c r="S3" s="195"/>
+      <c r="O3" s="237"/>
+      <c r="P3" s="238"/>
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="239"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="252"/>
-      <c r="C4" s="253"/>
-      <c r="D4" s="254"/>
+      <c r="B4" s="213"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="215"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="255"/>
-      <c r="J4" s="256"/>
-      <c r="K4" s="257"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="218"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="209"/>
-      <c r="P4" s="194"/>
-      <c r="Q4" s="194"/>
-      <c r="R4" s="194"/>
-      <c r="S4" s="195"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="238"/>
+      <c r="Q4" s="238"/>
+      <c r="R4" s="238"/>
+      <c r="S4" s="239"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="179"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="181"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="254"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="193"/>
-      <c r="J5" s="194"/>
-      <c r="K5" s="195"/>
+      <c r="I5" s="261"/>
+      <c r="J5" s="238"/>
+      <c r="K5" s="239"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="209"/>
-      <c r="P5" s="194"/>
-      <c r="Q5" s="194"/>
-      <c r="R5" s="194"/>
-      <c r="S5" s="195"/>
+      <c r="O5" s="237"/>
+      <c r="P5" s="238"/>
+      <c r="Q5" s="238"/>
+      <c r="R5" s="238"/>
+      <c r="S5" s="239"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="184"/>
-      <c r="C6" s="185"/>
-      <c r="D6" s="186"/>
+      <c r="B6" s="257"/>
+      <c r="C6" s="258"/>
+      <c r="D6" s="259"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="187"/>
-      <c r="J6" s="188"/>
-      <c r="K6" s="189"/>
+      <c r="I6" s="260"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="227"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="202"/>
-      <c r="P6" s="188"/>
-      <c r="Q6" s="188"/>
-      <c r="R6" s="188"/>
-      <c r="S6" s="189"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="226"/>
+      <c r="Q6" s="226"/>
+      <c r="R6" s="226"/>
+      <c r="S6" s="227"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="224" t="s">
+      <c r="A8" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="225"/>
-      <c r="C8" s="225"/>
-      <c r="D8" s="226"/>
-      <c r="F8" s="190" t="s">
+      <c r="B8" s="182"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="183"/>
+      <c r="F8" s="228" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="191"/>
-      <c r="H8" s="191"/>
-      <c r="I8" s="191"/>
-      <c r="J8" s="191"/>
-      <c r="K8" s="191"/>
-      <c r="L8" s="191"/>
-      <c r="M8" s="191"/>
-      <c r="N8" s="191"/>
-      <c r="O8" s="191"/>
-      <c r="P8" s="191"/>
-      <c r="Q8" s="191"/>
-      <c r="R8" s="191"/>
-      <c r="S8" s="192"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="229"/>
+      <c r="P8" s="229"/>
+      <c r="Q8" s="229"/>
+      <c r="R8" s="229"/>
+      <c r="S8" s="230"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="227"/>
-      <c r="B9" s="228"/>
-      <c r="C9" s="228"/>
-      <c r="D9" s="229"/>
-      <c r="F9" s="248" t="s">
+      <c r="A9" s="184"/>
+      <c r="B9" s="185"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="186"/>
+      <c r="F9" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="249"/>
-      <c r="H9" s="182" t="s">
+      <c r="G9" s="210"/>
+      <c r="H9" s="255" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="183"/>
-      <c r="J9" s="246" t="s">
+      <c r="I9" s="256"/>
+      <c r="J9" s="207" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="247"/>
-      <c r="L9" s="177" t="s">
+      <c r="K9" s="208"/>
+      <c r="L9" s="250" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="178"/>
-      <c r="N9" s="214" t="s">
+      <c r="M9" s="251"/>
+      <c r="N9" s="187" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="215"/>
-      <c r="P9" s="241" t="s">
+      <c r="O9" s="188"/>
+      <c r="P9" s="202" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="242"/>
-      <c r="R9" s="214" t="s">
+      <c r="Q9" s="203"/>
+      <c r="R9" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="215"/>
+      <c r="S9" s="188"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="210" t="s">
+      <c r="A10" s="240" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2790,28 +2789,28 @@
         <v>52</v>
       </c>
       <c r="E10" s="2"/>
-      <c r="F10" s="85" t="s">
+      <c r="F10" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="85" t="s">
+      <c r="G10" s="84" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="97" t="s">
+      <c r="H10" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="97" t="s">
+      <c r="I10" s="96" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="107" t="s">
+      <c r="J10" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="K10" s="107" t="s">
+      <c r="K10" s="106" t="s">
         <v>72</v>
       </c>
-      <c r="L10" s="116" t="s">
+      <c r="L10" s="115" t="s">
         <v>64</v>
       </c>
-      <c r="M10" s="116" t="s">
+      <c r="M10" s="115" t="s">
         <v>72</v>
       </c>
       <c r="N10" s="23" t="s">
@@ -2834,7 +2833,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="211"/>
+      <c r="A11" s="179"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2848,7 +2847,7 @@
         <v>mp</v>
       </c>
       <c r="E11" s="2"/>
-      <c r="F11" s="86" t="str">
+      <c r="F11" s="85" t="str">
         <f>IF(
    OR(
       ISNUMBER(--RIGHT(B11,1)),
@@ -2871,15 +2870,15 @@
 )</f>
         <v/>
       </c>
-      <c r="G11" s="136" t="str">
+      <c r="G11" s="135" t="str">
         <f>IFERROR(IF(AND(F11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F11,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F11,Cant!$J$2:$J$99,"22/0.4"),""),"")</f>
         <v/>
       </c>
-      <c r="H11" s="98" t="str">
+      <c r="H11" s="97" t="str">
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="I11" s="137" t="str">
+      <c r="I11" s="136" t="str">
         <f>IFERROR(
    IF(AND(H11&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H11,Cant!$J$2:$J$99,"22/1.0")
@@ -2889,19 +2888,19 @@
    ""),"")</f>
         <v/>
       </c>
-      <c r="J11" s="108" t="str">
+      <c r="J11" s="107" t="str">
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="K11" s="138" t="str">
+      <c r="K11" s="137" t="str">
         <f>IFERROR(IF(AND(J11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J11,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J11,Cant!$J$2:$J$99,"23/0.8"),""),"")</f>
         <v/>
       </c>
-      <c r="L11" s="117" t="str">
+      <c r="L11" s="116" t="str">
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="M11" s="139" t="str">
+      <c r="M11" s="138" t="str">
         <f>IFERROR(IF(AND(L11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L11,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L11,Cant!$J$2:$J$99,"23/2.0"),""),"")</f>
         <v/>
       </c>
@@ -2909,7 +2908,7 @@
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="O11" s="140" t="str">
+      <c r="O11" s="139" t="str">
         <f>IFERROR(IF(AND(N11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N11,Cant!$J$2:$J$99,"43/1.0"),""),"")</f>
         <v/>
       </c>
@@ -2917,7 +2916,7 @@
         <f>CONCATENATE(F11)</f>
         <v/>
       </c>
-      <c r="Q11" s="141" t="str">
+      <c r="Q11" s="140" t="str">
         <f>IFERROR(IF(AND(P11&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P11,Cant!$J$2:$J$99,"43/1.5"),""),"")</f>
         <v/>
       </c>
@@ -2931,12 +2930,12 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="211"/>
-      <c r="B12" s="134" t="str" cm="1">
+      <c r="A12" s="179"/>
+      <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
       </c>
-      <c r="C12" s="135" t="str">
+      <c r="C12" s="134" t="str">
         <f>IF(D12="buc",IF(B12&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B12,Deco!$Y$2:$Y$99,0)),""),IF(B12&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B12,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -2945,7 +2944,7 @@
         <v>mp</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="86" t="str">
+      <c r="F12" s="85" t="str">
         <f>IF(
    OR(
       ISNUMBER(--RIGHT(B12,1)),
@@ -2968,15 +2967,15 @@
 )</f>
         <v/>
       </c>
-      <c r="G12" s="136" t="str">
+      <c r="G12" s="135" t="str">
         <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(F12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F12,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F12,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H12" s="99" t="str">
+      <c r="H12" s="98" t="str">
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="I12" s="137" t="str">
+      <c r="I12" s="136" t="str">
         <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(
    IF(AND(H12&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H12,Cant!$J$2:$J$99,"22/1.0")
@@ -2986,19 +2985,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J12" s="109" t="str">
+      <c r="J12" s="108" t="str">
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="K12" s="138" t="str">
+      <c r="K12" s="137" t="str">
         <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(J12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J12,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J12,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L12" s="118" t="str">
+      <c r="L12" s="117" t="str">
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="M12" s="139" t="str">
+      <c r="M12" s="138" t="str">
         <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(L12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L12,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L12,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3006,7 +3005,7 @@
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="O12" s="140" t="str">
+      <c r="O12" s="139" t="str">
         <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(N12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N12,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3014,7 +3013,7 @@
         <f>CONCATENATE(F12)</f>
         <v/>
       </c>
-      <c r="Q12" s="141" t="str">
+      <c r="Q12" s="140" t="str">
         <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(P12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3028,12 +3027,12 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="211"/>
-      <c r="B13" s="134" t="str" cm="1">
+      <c r="A13" s="179"/>
+      <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
       </c>
-      <c r="C13" s="135" t="str">
+      <c r="C13" s="134" t="str">
         <f>IF(D13="buc",IF(B13&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B13,Deco!$Y$2:$Y$99,0)),""),IF(B13&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B13,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3042,7 +3041,7 @@
         <v>mp</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="86" t="str">
+      <c r="F13" s="85" t="str">
         <f t="shared" ref="F13:F22" si="0">IF(
    OR(
       ISNUMBER(--RIGHT(B13,1)),
@@ -3065,15 +3064,15 @@
 )</f>
         <v/>
       </c>
-      <c r="G13" s="136" t="str">
+      <c r="G13" s="135" t="str">
         <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(F13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F13,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F13,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H13" s="99" t="str">
+      <c r="H13" s="98" t="str">
         <f t="shared" ref="H13:H22" si="1">CONCATENATE(F13)</f>
         <v/>
       </c>
-      <c r="I13" s="137" t="str">
+      <c r="I13" s="136" t="str">
         <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(
    IF(AND(H13&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H13,Cant!$J$2:$J$99,"22/1.0")
@@ -3083,19 +3082,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J13" s="109" t="str">
+      <c r="J13" s="108" t="str">
         <f t="shared" ref="J13:J22" si="2">CONCATENATE(F13)</f>
         <v/>
       </c>
-      <c r="K13" s="138" t="str">
+      <c r="K13" s="137" t="str">
         <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(J13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J13,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J13,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L13" s="118" t="str">
+      <c r="L13" s="117" t="str">
         <f t="shared" ref="L13:L23" si="3">CONCATENATE(F13)</f>
         <v/>
       </c>
-      <c r="M13" s="139" t="str">
+      <c r="M13" s="138" t="str">
         <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(L13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L13,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L13,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3103,7 +3102,7 @@
         <f t="shared" ref="N13:N23" si="4">CONCATENATE(F13)</f>
         <v/>
       </c>
-      <c r="O13" s="140" t="str">
+      <c r="O13" s="139" t="str">
         <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(N13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N13,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3111,7 +3110,7 @@
         <f t="shared" ref="P13:P21" si="5">CONCATENATE(F13)</f>
         <v/>
       </c>
-      <c r="Q13" s="141" t="str">
+      <c r="Q13" s="140" t="str">
         <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(P13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3125,9 +3124,9 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="211"/>
-      <c r="B14" s="134"/>
-      <c r="C14" s="135" t="str">
+      <c r="A14" s="179"/>
+      <c r="B14" s="133"/>
+      <c r="C14" s="134" t="str">
         <f>IF(D14="buc",IF(B14&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B14,Deco!$Y$2:$Y$99,0)),""),IF(B14&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B14,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3136,19 +3135,19 @@
         <v>mp</v>
       </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="86" t="str">
+      <c r="F14" s="85" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G14" s="136" t="str">
+      <c r="G14" s="135" t="str">
         <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(F14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F14,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F14,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H14" s="99" t="str">
+      <c r="H14" s="98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I14" s="137" t="str">
+      <c r="I14" s="136" t="str">
         <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(
    IF(AND(H14&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H14,Cant!$J$2:$J$99,"22/1.0")
@@ -3158,19 +3157,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J14" s="109" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K14" s="138" t="str">
+      <c r="J14" s="108" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K14" s="137" t="str">
         <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(J14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J14,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J14,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L14" s="118" t="str">
+      <c r="L14" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M14" s="139" t="str">
+      <c r="M14" s="138" t="str">
         <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(L14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L14,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L14,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3178,7 +3177,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O14" s="140" t="str">
+      <c r="O14" s="139" t="str">
         <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(N14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N14,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3186,7 +3185,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q14" s="141" t="str">
+      <c r="Q14" s="140" t="str">
         <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(P14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3200,9 +3199,9 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="211"/>
-      <c r="B15" s="134"/>
-      <c r="C15" s="135" t="str">
+      <c r="A15" s="179"/>
+      <c r="B15" s="133"/>
+      <c r="C15" s="134" t="str">
         <f>IF(D15="buc",IF(B15&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B15,Deco!$Y$2:$Y$99,0)),""),IF(B15&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B15,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3211,19 +3210,19 @@
         <v>mp</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="86" t="str">
+      <c r="F15" s="85" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G15" s="136" t="str">
+      <c r="G15" s="135" t="str">
         <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(F15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F15,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F15,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H15" s="99" t="str">
+      <c r="H15" s="98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I15" s="137" t="str">
+      <c r="I15" s="136" t="str">
         <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(
    IF(AND(H15&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H15,Cant!$J$2:$J$99,"22/1.0")
@@ -3233,19 +3232,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J15" s="109" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K15" s="138" t="str">
+      <c r="J15" s="108" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K15" s="137" t="str">
         <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(J15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J15,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J15,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L15" s="118" t="str">
+      <c r="L15" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M15" s="139" t="str">
+      <c r="M15" s="138" t="str">
         <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(L15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L15,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L15,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3253,7 +3252,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O15" s="140" t="str">
+      <c r="O15" s="139" t="str">
         <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(N15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N15,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3261,7 +3260,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q15" s="141" t="str">
+      <c r="Q15" s="140" t="str">
         <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(P15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3275,12 +3274,12 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="211"/>
-      <c r="B16" s="134" t="str" cm="1">
+      <c r="A16" s="179"/>
+      <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
       </c>
-      <c r="C16" s="135" t="str">
+      <c r="C16" s="134" t="str">
         <f>IF(D16="buc",IF(B16&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B16,Deco!$Y$2:$Y$99,0)),""),IF(B16&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B16,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3289,19 +3288,19 @@
         <v>mp</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="86" t="str">
+      <c r="F16" s="85" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G16" s="136" t="str">
+      <c r="G16" s="135" t="str">
         <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(F16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F16,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F16,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H16" s="99" t="str">
+      <c r="H16" s="98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I16" s="137" t="str">
+      <c r="I16" s="136" t="str">
         <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(
    IF(AND(H16&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H16,Cant!$J$2:$J$99,"22/1.0")
@@ -3311,19 +3310,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J16" s="109" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K16" s="138" t="str">
+      <c r="J16" s="108" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K16" s="137" t="str">
         <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(J16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J16,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J16,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L16" s="118" t="str">
+      <c r="L16" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M16" s="139" t="str">
+      <c r="M16" s="138" t="str">
         <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(L16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L16,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L16,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3331,7 +3330,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O16" s="140" t="str">
+      <c r="O16" s="139" t="str">
         <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(N16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N16,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3339,7 +3338,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q16" s="141" t="str">
+      <c r="Q16" s="140" t="str">
         <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(P16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3353,12 +3352,12 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="211"/>
-      <c r="B17" s="134" t="str" cm="1">
+      <c r="A17" s="179"/>
+      <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
       </c>
-      <c r="C17" s="135" t="str">
+      <c r="C17" s="134" t="str">
         <f>IF(D17="buc",IF(B17&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B17,Deco!$Y$2:$Y$99,0)),""),IF(B17&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B17,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3367,19 +3366,19 @@
         <v>mp</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="86" t="str">
+      <c r="F17" s="85" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G17" s="136" t="str">
+      <c r="G17" s="135" t="str">
         <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(F17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F17,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F17,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H17" s="99" t="str">
+      <c r="H17" s="98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I17" s="137" t="str">
+      <c r="I17" s="136" t="str">
         <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(
    IF(AND(H17&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H17,Cant!$J$2:$J$99,"22/1.0")
@@ -3389,19 +3388,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J17" s="109" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K17" s="138" t="str">
+      <c r="J17" s="108" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K17" s="137" t="str">
         <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(J17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J17,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J17,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L17" s="118" t="str">
+      <c r="L17" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M17" s="139" t="str">
+      <c r="M17" s="138" t="str">
         <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(L17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L17,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L17,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3409,7 +3408,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O17" s="140" t="str">
+      <c r="O17" s="139" t="str">
         <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(N17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N17,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3417,7 +3416,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q17" s="141" t="str">
+      <c r="Q17" s="140" t="str">
         <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(P17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3431,12 +3430,12 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="211"/>
-      <c r="B18" s="134" t="str" cm="1">
+      <c r="A18" s="179"/>
+      <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
       </c>
-      <c r="C18" s="135" t="str">
+      <c r="C18" s="134" t="str">
         <f>IF(D18="buc",IF(B18&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B18,Deco!$Y$2:$Y$99,0)),""),IF(B18&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B18,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3445,19 +3444,19 @@
         <v>mp</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="86" t="str">
+      <c r="F18" s="85" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G18" s="136" t="str">
+      <c r="G18" s="135" t="str">
         <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(F18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F18,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F18,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H18" s="99" t="str">
+      <c r="H18" s="98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I18" s="137" t="str">
+      <c r="I18" s="136" t="str">
         <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(
    IF(AND(H18&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H18,Cant!$J$2:$J$99,"22/1.0")
@@ -3467,19 +3466,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J18" s="109" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K18" s="138" t="str">
+      <c r="J18" s="108" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K18" s="137" t="str">
         <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(J18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J18,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J18,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L18" s="118" t="str">
+      <c r="L18" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M18" s="139" t="str">
+      <c r="M18" s="138" t="str">
         <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(L18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L18,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L18,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3487,7 +3486,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O18" s="140" t="str">
+      <c r="O18" s="139" t="str">
         <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(N18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N18,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3495,7 +3494,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q18" s="141" t="str">
+      <c r="Q18" s="140" t="str">
         <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(P18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3509,12 +3508,12 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="211"/>
-      <c r="B19" s="134" t="str" cm="1">
+      <c r="A19" s="179"/>
+      <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
       </c>
-      <c r="C19" s="135" t="str">
+      <c r="C19" s="134" t="str">
         <f>IF(D19="buc",IF(B19&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B19,Deco!$Y$2:$Y$99,0)),""),IF(B19&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B19,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3523,19 +3522,19 @@
         <v>mp</v>
       </c>
       <c r="E19" s="2"/>
-      <c r="F19" s="86" t="str">
+      <c r="F19" s="85" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G19" s="136" t="str">
+      <c r="G19" s="135" t="str">
         <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(F19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F19,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F19,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H19" s="99" t="str">
+      <c r="H19" s="98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I19" s="137" t="str">
+      <c r="I19" s="136" t="str">
         <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(
    IF(AND(H19&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H19,Cant!$J$2:$J$99,"22/1.0")
@@ -3545,19 +3544,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J19" s="109" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K19" s="138" t="str">
+      <c r="J19" s="108" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K19" s="137" t="str">
         <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(J19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J19,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J19,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L19" s="118" t="str">
+      <c r="L19" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M19" s="139" t="str">
+      <c r="M19" s="138" t="str">
         <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(L19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L19,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L19,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3565,7 +3564,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O19" s="140" t="str">
+      <c r="O19" s="139" t="str">
         <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(N19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N19,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3573,7 +3572,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q19" s="141" t="str">
+      <c r="Q19" s="140" t="str">
         <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(P19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3587,12 +3586,12 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="211"/>
-      <c r="B20" s="134" t="str" cm="1">
+      <c r="A20" s="179"/>
+      <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
       </c>
-      <c r="C20" s="135" t="str">
+      <c r="C20" s="134" t="str">
         <f>IF(D20="buc",IF(B20&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B20,Deco!$Y$2:$Y$99,0)),""),IF(B20&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B20,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3601,19 +3600,19 @@
         <v>mp</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="86" t="str">
+      <c r="F20" s="85" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G20" s="136" t="str">
+      <c r="G20" s="135" t="str">
         <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(F20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F20,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F20,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H20" s="99" t="str">
+      <c r="H20" s="98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I20" s="137" t="str">
+      <c r="I20" s="136" t="str">
         <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(
    IF(AND(H20&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H20,Cant!$J$2:$J$99,"22/1.0")
@@ -3623,19 +3622,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J20" s="109" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K20" s="138" t="str">
+      <c r="J20" s="108" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K20" s="137" t="str">
         <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(J20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J20,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J20,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L20" s="118" t="str">
+      <c r="L20" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M20" s="139" t="str">
+      <c r="M20" s="138" t="str">
         <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(L20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L20,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L20,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3643,7 +3642,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O20" s="140" t="str">
+      <c r="O20" s="139" t="str">
         <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(N20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N20,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3651,7 +3650,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q20" s="141" t="str">
+      <c r="Q20" s="140" t="str">
         <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(P20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3665,12 +3664,12 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="211"/>
-      <c r="B21" s="134" t="str" cm="1">
+      <c r="A21" s="179"/>
+      <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
       </c>
-      <c r="C21" s="135" t="str">
+      <c r="C21" s="134" t="str">
         <f>IF(D21="buc",IF(B21&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B21,Deco!$Y$2:$Y$99,0)),""),IF(B21&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B21,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3679,19 +3678,19 @@
         <v>mp</v>
       </c>
       <c r="E21" s="2"/>
-      <c r="F21" s="86" t="str">
+      <c r="F21" s="85" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G21" s="136" t="str">
+      <c r="G21" s="135" t="str">
         <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(F21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F21,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F21,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H21" s="99" t="str">
+      <c r="H21" s="98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I21" s="137" t="str">
+      <c r="I21" s="136" t="str">
         <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(
    IF(AND(H21&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H21,Cant!$J$2:$J$99,"22/1.0")
@@ -3701,19 +3700,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J21" s="109" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K21" s="138" t="str">
+      <c r="J21" s="108" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K21" s="137" t="str">
         <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(J21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J21,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J21,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L21" s="118" t="str">
+      <c r="L21" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M21" s="139" t="str">
+      <c r="M21" s="138" t="str">
         <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(L21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L21,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L21,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3721,7 +3720,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O21" s="140" t="str">
+      <c r="O21" s="139" t="str">
         <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(N21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N21,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3729,7 +3728,7 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="Q21" s="141" t="str">
+      <c r="Q21" s="140" t="str">
         <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(P21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3743,33 +3742,33 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="212"/>
-      <c r="B22" s="134" t="str" cm="1">
+      <c r="A22" s="241"/>
+      <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
       </c>
-      <c r="C22" s="135" t="str">
+      <c r="C22" s="134" t="str">
         <f>IF(D22="buc",IF(B22&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B22,Deco!$Y$2:$Y$99,0)),""),IF(B22&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B22,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
-      <c r="D22" s="127" t="str" cm="1">
+      <c r="D22" s="126" t="str" cm="1">
         <f t="array" ref="D22">IF(I3="Debitare căntuire", IF(OR(RIGHT(B22,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(B22,2)="SM",RIGHT(B22,2)="PM",RIGHT(B22,2)="PG",RIGHT(B22,2)="mm",RIGHT(B22,2)="mp",RIGHT(B22,2)="PA",RIGHT(B22,2)="3D"),"buc","mp"), "mp")</f>
         <v>mp</v>
       </c>
       <c r="E22" s="78"/>
-      <c r="F22" s="86" t="str">
+      <c r="F22" s="85" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G22" s="136" t="str">
+      <c r="G22" s="135" t="str">
         <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(F22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F22,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F22,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H22" s="99" t="str">
+      <c r="H22" s="98" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I22" s="137" t="str">
+      <c r="I22" s="136" t="str">
         <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(
    IF(AND(H22&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H22,Cant!$J$2:$J$99,"22/1.0")
@@ -3779,19 +3778,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J22" s="109" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K22" s="138" t="str">
+      <c r="J22" s="108" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="K22" s="137" t="str">
         <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(J22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J22,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J22,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L22" s="118" t="str">
+      <c r="L22" s="117" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M22" s="139" t="str">
+      <c r="M22" s="138" t="str">
         <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(L22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L22,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L22,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3799,7 +3798,7 @@
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="O22" s="140" t="str">
+      <c r="O22" s="139" t="str">
         <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(N22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,N22,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3807,7 +3806,7 @@
         <f>CONCATENATE(F22)</f>
         <v/>
       </c>
-      <c r="Q22" s="141" t="str">
+      <c r="Q22" s="140" t="str">
         <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(P22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3829,7 +3828,7 @@
         <v>mp</v>
       </c>
       <c r="E23" s="49"/>
-      <c r="F23" s="86" t="str">
+      <c r="F23" s="85" t="str">
         <f t="shared" ref="F23" si="7" xml:space="preserve"> IF(OR(
       ISNUMBER(--RIGHT(B23,1)),
       RIGHT(B23,2)="SM",
@@ -3841,9 +3840,9 @@
    LEFT(B23,7))</f>
         <v/>
       </c>
-      <c r="G23" s="89"/>
-      <c r="H23" s="101"/>
-      <c r="I23" s="147" t="str">
+      <c r="G23" s="88"/>
+      <c r="H23" s="100"/>
+      <c r="I23" s="146" t="str">
         <f>IFERROR(
    IF(AND(H23&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H23,Cant!$J$2:$J$99,"22/1.0")
@@ -3853,21 +3852,21 @@
    ""),"")</f>
         <v/>
       </c>
-      <c r="J23" s="111"/>
-      <c r="K23" s="111"/>
-      <c r="L23" s="150" t="str">
+      <c r="J23" s="110"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="149" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M23" s="120"/>
-      <c r="N23" s="152" t="str">
+      <c r="M23" s="119"/>
+      <c r="N23" s="151" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O23" s="49"/>
       <c r="P23" s="49"/>
       <c r="Q23" s="49"/>
-      <c r="R23" s="152" t="str">
+      <c r="R23" s="151" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -3877,7 +3876,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="210" t="s">
+      <c r="A24" s="240" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3893,7 +3892,7 @@
         <v>mp</v>
       </c>
       <c r="E24" s="78"/>
-      <c r="F24" s="90" t="str">
+      <c r="F24" s="89" t="str">
         <f>IF(
    OR(
       ISNUMBER(--RIGHT(B24,1)),
@@ -3916,15 +3915,15 @@
 )</f>
         <v/>
       </c>
-      <c r="G24" s="91" t="str">
+      <c r="G24" s="90" t="str">
         <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(F24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F24,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F24,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H24" s="98" t="str">
+      <c r="H24" s="97" t="str">
         <f>CONCATENATE(F24)</f>
         <v/>
       </c>
-      <c r="I24" s="102" t="str">
+      <c r="I24" s="101" t="str">
         <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(
    IF(AND(H24&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H24,Cant!$J$2:$J$99,"22/1.0")
@@ -3934,19 +3933,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J24" s="108" t="str">
+      <c r="J24" s="107" t="str">
         <f>CONCATENATE(F24)</f>
         <v/>
       </c>
-      <c r="K24" s="112" t="str">
+      <c r="K24" s="111" t="str">
         <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(J24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J24,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J24,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L24" s="117" t="str">
+      <c r="L24" s="116" t="str">
         <f>CONCATENATE(F24)</f>
         <v/>
       </c>
-      <c r="M24" s="121" t="str">
+      <c r="M24" s="120" t="str">
         <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(L24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L24,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L24,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -3962,7 +3961,7 @@
         <f>CONCATENATE(F24)</f>
         <v/>
       </c>
-      <c r="Q24" s="262" t="str">
+      <c r="Q24" s="171" t="str">
         <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(P24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -3970,18 +3969,18 @@
         <f>CONCATENATE(F24)</f>
         <v/>
       </c>
-      <c r="S24" s="262" t="str">
+      <c r="S24" s="171" t="str">
         <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(R24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R24,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R24,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="211"/>
+      <c r="A25" s="179"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="135" t="str">
+      <c r="C25" s="134" t="str">
         <f>IF(D25="buc",IF(B25&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B25,Deco!$Y$2:$Y$99,0)),""),IF(B25&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B25,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -3990,7 +3989,7 @@
         <v>mp</v>
       </c>
       <c r="E25" s="2"/>
-      <c r="F25" s="86" t="str">
+      <c r="F25" s="85" t="str">
         <f>IF(
    OR(
       ISNUMBER(--RIGHT(B25,1)),
@@ -4013,15 +4012,15 @@
 )</f>
         <v/>
       </c>
-      <c r="G25" s="87" t="str">
+      <c r="G25" s="86" t="str">
         <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(F25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F25,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F25,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H25" s="99" t="str">
+      <c r="H25" s="98" t="str">
         <f>CONCATENATE(F25)</f>
         <v/>
       </c>
-      <c r="I25" s="148" t="str">
+      <c r="I25" s="147" t="str">
         <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(
    IF(AND(H25&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H25,Cant!$J$2:$J$99,"22/1.0")
@@ -4031,19 +4030,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J25" s="109" t="str">
+      <c r="J25" s="108" t="str">
         <f>CONCATENATE(F25)</f>
         <v/>
       </c>
-      <c r="K25" s="149" t="str">
+      <c r="K25" s="148" t="str">
         <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(J25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J25,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J25,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L25" s="118" t="str">
+      <c r="L25" s="117" t="str">
         <f>CONCATENATE(F25)</f>
         <v/>
       </c>
-      <c r="M25" s="151" t="str">
+      <c r="M25" s="150" t="str">
         <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(L25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L25,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L25,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -4059,7 +4058,7 @@
         <f>CONCATENATE(F25)</f>
         <v/>
       </c>
-      <c r="Q25" s="263" t="str">
+      <c r="Q25" s="172" t="str">
         <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(P25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -4067,18 +4066,18 @@
         <f>CONCATENATE(F25)</f>
         <v/>
       </c>
-      <c r="S25" s="263" t="str">
+      <c r="S25" s="172" t="str">
         <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(R25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R25,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R25,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="211"/>
+      <c r="A26" s="179"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
       </c>
-      <c r="C26" s="135" t="str">
+      <c r="C26" s="134" t="str">
         <f>IF(D26="buc",IF(B26&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B26,Deco!$Y$2:$Y$99,0)),""),IF(B26&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B26,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4087,7 +4086,7 @@
         <v>mp</v>
       </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="86" t="str">
+      <c r="F26" s="85" t="str">
         <f t="shared" ref="F26:F28" si="8">IF(
    OR(
       ISNUMBER(--RIGHT(B26,1)),
@@ -4110,15 +4109,15 @@
 )</f>
         <v/>
       </c>
-      <c r="G26" s="87" t="str">
+      <c r="G26" s="86" t="str">
         <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(F26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F26,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F26,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H26" s="99" t="str">
+      <c r="H26" s="98" t="str">
         <f>CONCATENATE(F26)</f>
         <v/>
       </c>
-      <c r="I26" s="148" t="str">
+      <c r="I26" s="147" t="str">
         <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(
    IF(AND(H26&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H26,Cant!$J$2:$J$99,"22/1.0")
@@ -4128,19 +4127,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J26" s="109" t="str">
+      <c r="J26" s="108" t="str">
         <f>CONCATENATE(F26)</f>
         <v/>
       </c>
-      <c r="K26" s="149" t="str">
+      <c r="K26" s="148" t="str">
         <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(J26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J26,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J26,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L26" s="118" t="str">
+      <c r="L26" s="117" t="str">
         <f>CONCATENATE(F26)</f>
         <v/>
       </c>
-      <c r="M26" s="151" t="str">
+      <c r="M26" s="150" t="str">
         <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(L26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L26,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L26,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -4156,7 +4155,7 @@
         <f>CONCATENATE(F26)</f>
         <v/>
       </c>
-      <c r="Q26" s="263" t="str">
+      <c r="Q26" s="172" t="str">
         <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(P26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -4164,18 +4163,18 @@
         <f>CONCATENATE(F26)</f>
         <v/>
       </c>
-      <c r="S26" s="263" t="str">
+      <c r="S26" s="172" t="str">
         <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(R26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R26,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R26,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="211"/>
+      <c r="A27" s="179"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
       </c>
-      <c r="C27" s="135" t="str">
+      <c r="C27" s="134" t="str">
         <f>IF(D27="buc",IF(B27&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B27,Deco!$Y$2:$Y$99,0)),""),IF(B27&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B27,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4184,19 +4183,19 @@
         <v>mp</v>
       </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="86" t="str">
+      <c r="F27" s="85" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G27" s="87" t="str">
+      <c r="G27" s="86" t="str">
         <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(F27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F27,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F27,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H27" s="99" t="str">
+      <c r="H27" s="98" t="str">
         <f>CONCATENATE(F27)</f>
         <v/>
       </c>
-      <c r="I27" s="148" t="str">
+      <c r="I27" s="147" t="str">
         <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(
    IF(AND(H27&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H27,Cant!$J$2:$J$99,"22/1.0")
@@ -4206,19 +4205,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J27" s="109" t="str">
+      <c r="J27" s="108" t="str">
         <f>CONCATENATE(F27)</f>
         <v/>
       </c>
-      <c r="K27" s="149" t="str">
+      <c r="K27" s="148" t="str">
         <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(J27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J27,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J27,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L27" s="118" t="str">
+      <c r="L27" s="117" t="str">
         <f>CONCATENATE(F27)</f>
         <v/>
       </c>
-      <c r="M27" s="151" t="str">
+      <c r="M27" s="150" t="str">
         <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(L27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L27,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L27,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -4234,7 +4233,7 @@
         <f>CONCATENATE(F27)</f>
         <v/>
       </c>
-      <c r="Q27" s="263" t="str">
+      <c r="Q27" s="172" t="str">
         <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(P27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -4242,18 +4241,18 @@
         <f>CONCATENATE(F27)</f>
         <v/>
       </c>
-      <c r="S27" s="263" t="str">
+      <c r="S27" s="172" t="str">
         <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(R27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R27,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R27,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="213"/>
+      <c r="A28" s="180"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
       </c>
-      <c r="C28" s="135" t="str">
+      <c r="C28" s="134" t="str">
         <f>IF(D28="buc",IF(B28&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B28,Deco!$Y$2:$Y$99,0)),""),IF(B28&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B28,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4262,19 +4261,19 @@
         <v>mp</v>
       </c>
       <c r="E28" s="78"/>
-      <c r="F28" s="261" t="str">
+      <c r="F28" s="170" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G28" s="142" t="str">
+      <c r="G28" s="141" t="str">
         <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(F28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F28,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F28,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H28" s="103" t="str">
+      <c r="H28" s="102" t="str">
         <f>CONCATENATE(F28)</f>
         <v/>
       </c>
-      <c r="I28" s="143" t="str">
+      <c r="I28" s="142" t="str">
         <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(
    IF(AND(H28&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H28,Cant!$J$2:$J$99,"22/1.0")
@@ -4284,19 +4283,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J28" s="113" t="str">
+      <c r="J28" s="112" t="str">
         <f>CONCATENATE(F28)</f>
         <v/>
       </c>
-      <c r="K28" s="144" t="str">
+      <c r="K28" s="143" t="str">
         <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(J28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J28,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J28,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L28" s="122" t="str">
+      <c r="L28" s="121" t="str">
         <f>CONCATENATE(F28)</f>
         <v/>
       </c>
-      <c r="M28" s="145" t="str">
+      <c r="M28" s="144" t="str">
         <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(L28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L28,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L28,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -4334,14 +4333,14 @@
         <v>mp</v>
       </c>
       <c r="E29" s="49"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="94"/>
-      <c r="H29" s="104"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="114"/>
-      <c r="K29" s="114"/>
-      <c r="L29" s="123"/>
-      <c r="M29" s="123"/>
+      <c r="F29" s="92"/>
+      <c r="G29" s="93"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="103"/>
+      <c r="J29" s="113"/>
+      <c r="K29" s="113"/>
+      <c r="L29" s="122"/>
+      <c r="M29" s="122"/>
       <c r="N29" s="79"/>
       <c r="O29" s="79"/>
       <c r="P29" s="79"/>
@@ -4364,14 +4363,14 @@
         <v>mp</v>
       </c>
       <c r="E30" s="49"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="101"/>
-      <c r="I30" s="101"/>
-      <c r="J30" s="111"/>
-      <c r="K30" s="111"/>
-      <c r="L30" s="120"/>
-      <c r="M30" s="120"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="100"/>
+      <c r="I30" s="100"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="110"/>
+      <c r="L30" s="119"/>
+      <c r="M30" s="119"/>
       <c r="N30" s="49"/>
       <c r="O30" s="49"/>
       <c r="P30" s="49"/>
@@ -4385,14 +4384,14 @@
       <c r="C31" s="49"/>
       <c r="D31" s="66"/>
       <c r="E31" s="49"/>
-      <c r="F31" s="95"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="105"/>
-      <c r="I31" s="105"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="115"/>
-      <c r="L31" s="124"/>
-      <c r="M31" s="124"/>
+      <c r="F31" s="94"/>
+      <c r="G31" s="95"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="114"/>
+      <c r="K31" s="114"/>
+      <c r="L31" s="123"/>
+      <c r="M31" s="123"/>
       <c r="N31" s="59"/>
       <c r="O31" s="59"/>
       <c r="P31" s="59"/>
@@ -4401,7 +4400,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="243" t="s">
+      <c r="A32" s="204" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4416,19 +4415,19 @@
         <v>55</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="90" t="str">
+      <c r="F32" s="89" t="str">
         <f>IF(B32&lt;&gt;"",TRIM(LEFT(B32,LEN(B32)-4)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="91" t="str">
+      <c r="G32" s="90" t="str">
         <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(AND(F32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F32,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F32,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H32" s="98" t="str">
+      <c r="H32" s="97" t="str">
         <f>CONCATENATE(F32)</f>
         <v/>
       </c>
-      <c r="I32" s="264" t="str">
+      <c r="I32" s="173" t="str">
         <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(
    IF(AND(H32&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H32,Cant!$J$2:$J$99,"22/1.0")
@@ -4438,19 +4437,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J32" s="108" t="str">
+      <c r="J32" s="107" t="str">
         <f>CONCATENATE(F32)</f>
         <v/>
       </c>
-      <c r="K32" s="112" t="str">
+      <c r="K32" s="111" t="str">
         <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(AND(J32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J32,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J32,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L32" s="117" t="str">
+      <c r="L32" s="116" t="str">
         <f>CONCATENATE(F32)</f>
         <v/>
       </c>
-      <c r="M32" s="121" t="str">
+      <c r="M32" s="120" t="str">
         <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(AND(L32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L32,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L32,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -4466,7 +4465,7 @@
         <f>CONCATENATE(F32)</f>
         <v/>
       </c>
-      <c r="Q32" s="262" t="str">
+      <c r="Q32" s="171" t="str">
         <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P32)&gt;0,"",IF(AND(P32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P32,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
         <v/>
       </c>
@@ -4474,18 +4473,18 @@
         <f>CONCATENATE(F32)</f>
         <v/>
       </c>
-      <c r="S32" s="262" t="str">
+      <c r="S32" s="171" t="str">
         <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(AND(R32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R32,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R32,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="244"/>
+      <c r="A33" s="205"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
       </c>
-      <c r="C33" s="135" t="str">
+      <c r="C33" s="134" t="str">
         <f>IF(D33="buc",IF(B33&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B33,Deco!$Y$2:$Y$99,0)),""),IF(B33&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B33,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4493,19 +4492,19 @@
         <v>55</v>
       </c>
       <c r="E33" s="2"/>
-      <c r="F33" s="86" t="str">
+      <c r="F33" s="85" t="str">
         <f>IF(B33&lt;&gt;"",TRIM(LEFT(B33,LEN(B33)-4)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="87" t="str">
+      <c r="G33" s="86" t="str">
         <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(AND(F33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F33,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F33,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H33" s="99" t="str">
+      <c r="H33" s="98" t="str">
         <f>CONCATENATE(F33)</f>
         <v/>
       </c>
-      <c r="I33" s="265" t="str">
+      <c r="I33" s="174" t="str">
         <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(
    IF(AND(H33&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H33,Cant!$J$2:$J$99,"22/1.0")
@@ -4515,19 +4514,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J33" s="109" t="str">
+      <c r="J33" s="108" t="str">
         <f>CONCATENATE(F33)</f>
         <v/>
       </c>
-      <c r="K33" s="110" t="str">
+      <c r="K33" s="109" t="str">
         <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(AND(J33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J33,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J33,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L33" s="118" t="str">
+      <c r="L33" s="117" t="str">
         <f>CONCATENATE(F33)</f>
         <v/>
       </c>
-      <c r="M33" s="119" t="str">
+      <c r="M33" s="118" t="str">
         <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(AND(L33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L33,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L33,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -4543,7 +4542,7 @@
         <f>CONCATENATE(F33)</f>
         <v/>
       </c>
-      <c r="Q33" s="263" t="str">
+      <c r="Q33" s="172" t="str">
         <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P33)&gt;0,"",IF(AND(P33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P33,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
         <v/>
       </c>
@@ -4551,18 +4550,18 @@
         <f>CONCATENATE(F33)</f>
         <v/>
       </c>
-      <c r="S33" s="263" t="str">
+      <c r="S33" s="172" t="str">
         <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(AND(R33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R33,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R33,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="245"/>
+      <c r="A34" s="206"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
       </c>
-      <c r="C34" s="135" t="str">
+      <c r="C34" s="134" t="str">
         <f>IF(D34="buc",IF(B34&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B34,Deco!$Y$2:$Y$99,0)),""),IF(B34&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B34,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4570,19 +4569,19 @@
         <v>55</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="86" t="str">
+      <c r="F34" s="85" t="str">
         <f>IF(B34&lt;&gt;"",TRIM(LEFT(B34,LEN(B34)-4)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="87" t="str">
+      <c r="G34" s="86" t="str">
         <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(AND(F34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F34,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F34,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H34" s="99" t="str">
+      <c r="H34" s="98" t="str">
         <f>CONCATENATE(F34)</f>
         <v/>
       </c>
-      <c r="I34" s="100" t="str">
+      <c r="I34" s="99" t="str">
         <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(
    IF(AND(H34&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H34,Cant!$J$2:$J$99,"22/1.0")
@@ -4592,19 +4591,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J34" s="109" t="str">
+      <c r="J34" s="108" t="str">
         <f>CONCATENATE(F34)</f>
         <v/>
       </c>
-      <c r="K34" s="110" t="str">
+      <c r="K34" s="109" t="str">
         <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(AND(J34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J34,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J34,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L34" s="118" t="str">
+      <c r="L34" s="117" t="str">
         <f>CONCATENATE(F34)</f>
         <v/>
       </c>
-      <c r="M34" s="119" t="str">
+      <c r="M34" s="118" t="str">
         <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(AND(L34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L34,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L34,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -4639,14 +4638,14 @@
       <c r="C35" s="49"/>
       <c r="D35" s="66"/>
       <c r="E35" s="49"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="89"/>
-      <c r="H35" s="101"/>
-      <c r="I35" s="101"/>
-      <c r="J35" s="111"/>
-      <c r="K35" s="111"/>
-      <c r="L35" s="120"/>
-      <c r="M35" s="120"/>
+      <c r="F35" s="88"/>
+      <c r="G35" s="88"/>
+      <c r="H35" s="100"/>
+      <c r="I35" s="100"/>
+      <c r="J35" s="110"/>
+      <c r="K35" s="110"/>
+      <c r="L35" s="119"/>
+      <c r="M35" s="119"/>
       <c r="N35" s="49"/>
       <c r="O35" s="49"/>
       <c r="P35" s="49"/>
@@ -4655,7 +4654,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="243" t="s">
+      <c r="A36" s="204" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4670,19 +4669,19 @@
         <v>55</v>
       </c>
       <c r="E36" s="2"/>
-      <c r="F36" s="90" t="str">
+      <c r="F36" s="89" t="str">
         <f>IF(B36&lt;&gt;"",TRIM(LEFT(B36,LEN(B36)-3)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="91" t="str">
+      <c r="G36" s="90" t="str">
         <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(AND(F36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F36,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F36,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H36" s="98" t="str">
+      <c r="H36" s="97" t="str">
         <f>CONCATENATE(F36)</f>
         <v/>
       </c>
-      <c r="I36" s="264" t="str">
+      <c r="I36" s="173" t="str">
         <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(
    IF(AND(H36&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H36,Cant!$J$2:$J$99,"22/1.0")
@@ -4692,19 +4691,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J36" s="108" t="str">
+      <c r="J36" s="107" t="str">
         <f>CONCATENATE(F36)</f>
         <v/>
       </c>
-      <c r="K36" s="112" t="str">
+      <c r="K36" s="111" t="str">
         <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(AND(J36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J36,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J36,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L36" s="117" t="str">
+      <c r="L36" s="116" t="str">
         <f>CONCATENATE(F36)</f>
         <v/>
       </c>
-      <c r="M36" s="121" t="str">
+      <c r="M36" s="120" t="str">
         <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(AND(L36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L36,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L36,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -4720,7 +4719,7 @@
         <f>CONCATENATE(F36)</f>
         <v/>
       </c>
-      <c r="Q36" s="262" t="str">
+      <c r="Q36" s="171" t="str">
         <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P36)&gt;0,"",IF(AND(P36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P36,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
         <v/>
       </c>
@@ -4728,18 +4727,18 @@
         <f>CONCATENATE(F36)</f>
         <v/>
       </c>
-      <c r="S36" s="262" t="str">
+      <c r="S36" s="171" t="str">
         <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(AND(R36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R36,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R36,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="244"/>
+      <c r="A37" s="205"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
       </c>
-      <c r="C37" s="135" t="str">
+      <c r="C37" s="134" t="str">
         <f>IF(D37="buc",IF(B37&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B37,Deco!$Y$2:$Y$99,0)),""),IF(B37&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B37,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4747,19 +4746,19 @@
         <v>55</v>
       </c>
       <c r="E37" s="2"/>
-      <c r="F37" s="86" t="str">
+      <c r="F37" s="85" t="str">
         <f>IF(B37&lt;&gt;"",TRIM(LEFT(B37,LEN(B37)-3)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="87" t="str">
+      <c r="G37" s="86" t="str">
         <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(AND(F37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F37,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F37,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H37" s="106" t="str">
+      <c r="H37" s="105" t="str">
         <f>CONCATENATE(F37)</f>
         <v/>
       </c>
-      <c r="I37" s="265" t="str">
+      <c r="I37" s="174" t="str">
         <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(
    IF(AND(H37&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H37,Cant!$J$2:$J$99,"22/1.0")
@@ -4769,19 +4768,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J37" s="109" t="str">
+      <c r="J37" s="108" t="str">
         <f>CONCATENATE(F37)</f>
         <v/>
       </c>
-      <c r="K37" s="110" t="str">
+      <c r="K37" s="109" t="str">
         <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(AND(J37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J37,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J37,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L37" s="118" t="str">
+      <c r="L37" s="117" t="str">
         <f>CONCATENATE(F37)</f>
         <v/>
       </c>
-      <c r="M37" s="119" t="str">
+      <c r="M37" s="118" t="str">
         <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(AND(L37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L37,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L37,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -4797,7 +4796,7 @@
         <f>CONCATENATE(F37)</f>
         <v/>
       </c>
-      <c r="Q37" s="263" t="str">
+      <c r="Q37" s="172" t="str">
         <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(COUNTIF(F$11:F$22,P37)&gt;0,"",IF(AND(P37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$100,Cant!$M$2:$M$100,P37,Cant!$J$2:$J$100,"43/1.5"),"")),""))</f>
         <v/>
       </c>
@@ -4805,18 +4804,18 @@
         <f>CONCATENATE(F37)</f>
         <v/>
       </c>
-      <c r="S37" s="263" t="str">
+      <c r="S37" s="172" t="str">
         <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(AND(R37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R37,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R37,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="245"/>
+      <c r="A38" s="206"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
       </c>
-      <c r="C38" s="135" t="str">
+      <c r="C38" s="134" t="str">
         <f>IF(D38="buc",IF(B38&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B38,Deco!$Y$2:$Y$99,0)),""),IF(B38&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B38,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
       </c>
@@ -4824,19 +4823,19 @@
         <v>55</v>
       </c>
       <c r="E38" s="2"/>
-      <c r="F38" s="92" t="str">
+      <c r="F38" s="91" t="str">
         <f>IF(B38&lt;&gt;"",TRIM(LEFT(B38,LEN(B38)-3)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="142" t="str">
+      <c r="G38" s="141" t="str">
         <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(AND(F38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F38,Cant!$J$2:$J$99,"22/0.4")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,F38,Cant!$J$2:$J$99,"22/0.4"),""),""))</f>
         <v/>
       </c>
-      <c r="H38" s="103" t="str">
+      <c r="H38" s="102" t="str">
         <f>CONCATENATE(F38)</f>
         <v/>
       </c>
-      <c r="I38" s="100" t="str">
+      <c r="I38" s="99" t="str">
         <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(
    IF(AND(H38&lt;&gt;"",
       SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,H38,Cant!$J$2:$J$99,"22/1.0")
@@ -4846,19 +4845,19 @@
    ""),""))</f>
         <v/>
       </c>
-      <c r="J38" s="113" t="str">
+      <c r="J38" s="112" t="str">
         <f>CONCATENATE(F38)</f>
         <v/>
       </c>
-      <c r="K38" s="144" t="str">
+      <c r="K38" s="143" t="str">
         <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(AND(J38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J38,Cant!$J$2:$J$99,"23/0.8")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,J38,Cant!$J$2:$J$99,"23/0.8"),""),""))</f>
         <v/>
       </c>
-      <c r="L38" s="122" t="str">
+      <c r="L38" s="121" t="str">
         <f>CONCATENATE(F38)</f>
         <v/>
       </c>
-      <c r="M38" s="145" t="str">
+      <c r="M38" s="144" t="str">
         <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(AND(L38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L38,Cant!$J$2:$J$99,"23/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,L38,Cant!$J$2:$J$99,"23/2.0"),""),""))</f>
         <v/>
       </c>
@@ -4882,7 +4881,7 @@
         <f>CONCATENATE(F38)</f>
         <v/>
       </c>
-      <c r="S38" s="263" t="str">
+      <c r="S38" s="172" t="str">
         <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(AND(R38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R38,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R38,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
         <v/>
       </c>
@@ -4902,7 +4901,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="210" t="s">
+      <c r="A40" s="240" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4914,25 +4913,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="203" t="s">
+      <c r="F40" s="231" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="204"/>
-      <c r="H40" s="204"/>
-      <c r="I40" s="204"/>
-      <c r="J40" s="204"/>
-      <c r="K40" s="204"/>
-      <c r="L40" s="204"/>
-      <c r="M40" s="204"/>
-      <c r="N40" s="204"/>
-      <c r="O40" s="204"/>
-      <c r="P40" s="204"/>
-      <c r="Q40" s="204"/>
-      <c r="R40" s="204"/>
-      <c r="S40" s="205"/>
+      <c r="G40" s="232"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="232"/>
+      <c r="O40" s="232"/>
+      <c r="P40" s="232"/>
+      <c r="Q40" s="232"/>
+      <c r="R40" s="232"/>
+      <c r="S40" s="233"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="211"/>
+      <c r="A41" s="179"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -4995,7 +4994,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="211"/>
+      <c r="A42" s="179"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5020,10 +5019,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="83"/>
+      <c r="S42" s="198">
+        <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="211"/>
+      <c r="A43" s="179"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5035,26 +5037,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="190" t="str">
+      <c r="F43" s="228" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="191"/>
-      <c r="H43" s="191"/>
-      <c r="I43" s="191"/>
-      <c r="J43" s="191"/>
-      <c r="K43" s="191"/>
-      <c r="L43" s="191"/>
-      <c r="M43" s="191"/>
-      <c r="N43" s="191"/>
-      <c r="O43" s="191"/>
-      <c r="P43" s="191"/>
-      <c r="Q43" s="191"/>
-      <c r="R43" s="191"/>
-      <c r="S43" s="192"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="229"/>
+      <c r="J43" s="229"/>
+      <c r="K43" s="229"/>
+      <c r="L43" s="229"/>
+      <c r="M43" s="229"/>
+      <c r="N43" s="229"/>
+      <c r="O43" s="229"/>
+      <c r="P43" s="229"/>
+      <c r="Q43" s="229"/>
+      <c r="R43" s="229"/>
+      <c r="S43" s="245"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="211"/>
+      <c r="A44" s="179"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5110,7 +5112,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="211"/>
+      <c r="A45" s="179"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5181,7 +5183,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="211"/>
+      <c r="A46" s="179"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5195,7 +5197,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="211"/>
+      <c r="A47" s="179"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5206,34 +5208,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="171" t="s">
+      <c r="F47" s="198" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="250" t="str">
+      <c r="G47" s="211" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="171" t="s">
+      <c r="J47" s="198" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="239">
+      <c r="K47" s="200">
         <v>1</v>
       </c>
-      <c r="N47" s="171" t="s">
+      <c r="N47" s="198" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="173"/>
-      <c r="P47" s="174"/>
-      <c r="R47" s="171" t="s">
+      <c r="O47" s="246"/>
+      <c r="P47" s="247"/>
+      <c r="R47" s="198" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="171" t="e">
-        <f>IF(#REF!=2,"O","X")</f>
-        <v>#REF!</v>
-      </c>
+      <c r="S47" s="198"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="213"/>
+      <c r="A48" s="180"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5244,15 +5243,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="219"/>
-      <c r="G48" s="251"/>
-      <c r="J48" s="219"/>
-      <c r="K48" s="240"/>
-      <c r="N48" s="172"/>
-      <c r="O48" s="175"/>
-      <c r="P48" s="176"/>
-      <c r="R48" s="172"/>
-      <c r="S48" s="219"/>
+      <c r="F48" s="199"/>
+      <c r="G48" s="212"/>
+      <c r="J48" s="199"/>
+      <c r="K48" s="201"/>
+      <c r="N48" s="245"/>
+      <c r="O48" s="248"/>
+      <c r="P48" s="249"/>
+      <c r="R48" s="245"/>
+      <c r="S48" s="199"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5261,177 +5260,203 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="223" t="s">
+      <c r="A50" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="230"/>
-      <c r="C50" s="231"/>
-      <c r="D50" s="231"/>
-      <c r="E50" s="231"/>
-      <c r="F50" s="231"/>
-      <c r="G50" s="231"/>
-      <c r="H50" s="231"/>
-      <c r="I50" s="231"/>
-      <c r="J50" s="231"/>
-      <c r="K50" s="231"/>
-      <c r="L50" s="231"/>
-      <c r="M50" s="231"/>
-      <c r="N50" s="231"/>
-      <c r="O50" s="231"/>
-      <c r="P50" s="231"/>
-      <c r="Q50" s="231"/>
-      <c r="R50" s="231"/>
-      <c r="S50" s="232"/>
+      <c r="B50" s="189"/>
+      <c r="C50" s="190"/>
+      <c r="D50" s="190"/>
+      <c r="E50" s="190"/>
+      <c r="F50" s="190"/>
+      <c r="G50" s="190"/>
+      <c r="H50" s="190"/>
+      <c r="I50" s="190"/>
+      <c r="J50" s="190"/>
+      <c r="K50" s="190"/>
+      <c r="L50" s="190"/>
+      <c r="M50" s="190"/>
+      <c r="N50" s="190"/>
+      <c r="O50" s="190"/>
+      <c r="P50" s="190"/>
+      <c r="Q50" s="190"/>
+      <c r="R50" s="190"/>
+      <c r="S50" s="191"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="211"/>
-      <c r="B51" s="233"/>
-      <c r="C51" s="234"/>
-      <c r="D51" s="234"/>
-      <c r="E51" s="234"/>
-      <c r="F51" s="234"/>
-      <c r="G51" s="234"/>
-      <c r="H51" s="234"/>
-      <c r="I51" s="234"/>
-      <c r="J51" s="234"/>
-      <c r="K51" s="234"/>
-      <c r="L51" s="234"/>
-      <c r="M51" s="234"/>
-      <c r="N51" s="234"/>
-      <c r="O51" s="234"/>
-      <c r="P51" s="234"/>
-      <c r="Q51" s="234"/>
-      <c r="R51" s="234"/>
-      <c r="S51" s="235"/>
+      <c r="A51" s="179"/>
+      <c r="B51" s="192"/>
+      <c r="C51" s="193"/>
+      <c r="D51" s="193"/>
+      <c r="E51" s="193"/>
+      <c r="F51" s="193"/>
+      <c r="G51" s="193"/>
+      <c r="H51" s="193"/>
+      <c r="I51" s="193"/>
+      <c r="J51" s="193"/>
+      <c r="K51" s="193"/>
+      <c r="L51" s="193"/>
+      <c r="M51" s="193"/>
+      <c r="N51" s="193"/>
+      <c r="O51" s="193"/>
+      <c r="P51" s="193"/>
+      <c r="Q51" s="193"/>
+      <c r="R51" s="193"/>
+      <c r="S51" s="194"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="211"/>
-      <c r="B52" s="233"/>
-      <c r="C52" s="234"/>
-      <c r="D52" s="234"/>
-      <c r="E52" s="234"/>
-      <c r="F52" s="234"/>
-      <c r="G52" s="234"/>
-      <c r="H52" s="234"/>
-      <c r="I52" s="234"/>
-      <c r="J52" s="234"/>
-      <c r="K52" s="234"/>
-      <c r="L52" s="234"/>
-      <c r="M52" s="234"/>
-      <c r="N52" s="234"/>
-      <c r="O52" s="234"/>
-      <c r="P52" s="234"/>
-      <c r="Q52" s="234"/>
-      <c r="R52" s="234"/>
-      <c r="S52" s="235"/>
+      <c r="A52" s="179"/>
+      <c r="B52" s="192"/>
+      <c r="C52" s="193"/>
+      <c r="D52" s="193"/>
+      <c r="E52" s="193"/>
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="193"/>
+      <c r="J52" s="193"/>
+      <c r="K52" s="193"/>
+      <c r="L52" s="193"/>
+      <c r="M52" s="193"/>
+      <c r="N52" s="193"/>
+      <c r="O52" s="193"/>
+      <c r="P52" s="193"/>
+      <c r="Q52" s="193"/>
+      <c r="R52" s="193"/>
+      <c r="S52" s="194"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="211"/>
-      <c r="B53" s="233"/>
-      <c r="C53" s="234"/>
-      <c r="D53" s="234"/>
-      <c r="E53" s="234"/>
-      <c r="F53" s="234"/>
-      <c r="G53" s="234"/>
-      <c r="H53" s="234"/>
-      <c r="I53" s="234"/>
-      <c r="J53" s="234"/>
-      <c r="K53" s="234"/>
-      <c r="L53" s="234"/>
-      <c r="M53" s="234"/>
-      <c r="N53" s="234"/>
-      <c r="O53" s="234"/>
-      <c r="P53" s="234"/>
-      <c r="Q53" s="234"/>
-      <c r="R53" s="234"/>
-      <c r="S53" s="235"/>
+      <c r="A53" s="179"/>
+      <c r="B53" s="192"/>
+      <c r="C53" s="193"/>
+      <c r="D53" s="193"/>
+      <c r="E53" s="193"/>
+      <c r="F53" s="193"/>
+      <c r="G53" s="193"/>
+      <c r="H53" s="193"/>
+      <c r="I53" s="193"/>
+      <c r="J53" s="193"/>
+      <c r="K53" s="193"/>
+      <c r="L53" s="193"/>
+      <c r="M53" s="193"/>
+      <c r="N53" s="193"/>
+      <c r="O53" s="193"/>
+      <c r="P53" s="193"/>
+      <c r="Q53" s="193"/>
+      <c r="R53" s="193"/>
+      <c r="S53" s="194"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="211"/>
-      <c r="B54" s="233"/>
-      <c r="C54" s="234"/>
-      <c r="D54" s="234"/>
-      <c r="E54" s="234"/>
-      <c r="F54" s="234"/>
-      <c r="G54" s="234"/>
-      <c r="H54" s="234"/>
-      <c r="I54" s="234"/>
-      <c r="J54" s="234"/>
-      <c r="K54" s="234"/>
-      <c r="L54" s="234"/>
-      <c r="M54" s="234"/>
-      <c r="N54" s="234"/>
-      <c r="O54" s="234"/>
-      <c r="P54" s="234"/>
-      <c r="Q54" s="234"/>
-      <c r="R54" s="234"/>
-      <c r="S54" s="235"/>
+      <c r="A54" s="179"/>
+      <c r="B54" s="192"/>
+      <c r="C54" s="193"/>
+      <c r="D54" s="193"/>
+      <c r="E54" s="193"/>
+      <c r="F54" s="193"/>
+      <c r="G54" s="193"/>
+      <c r="H54" s="193"/>
+      <c r="I54" s="193"/>
+      <c r="J54" s="193"/>
+      <c r="K54" s="193"/>
+      <c r="L54" s="193"/>
+      <c r="M54" s="193"/>
+      <c r="N54" s="193"/>
+      <c r="O54" s="193"/>
+      <c r="P54" s="193"/>
+      <c r="Q54" s="193"/>
+      <c r="R54" s="193"/>
+      <c r="S54" s="194"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="211"/>
-      <c r="B55" s="233"/>
-      <c r="C55" s="234"/>
-      <c r="D55" s="234"/>
-      <c r="E55" s="234"/>
-      <c r="F55" s="234"/>
-      <c r="G55" s="234"/>
-      <c r="H55" s="234"/>
-      <c r="I55" s="234"/>
-      <c r="J55" s="234"/>
-      <c r="K55" s="234"/>
-      <c r="L55" s="234"/>
-      <c r="M55" s="234"/>
-      <c r="N55" s="234"/>
-      <c r="O55" s="234"/>
-      <c r="P55" s="234"/>
-      <c r="Q55" s="234"/>
-      <c r="R55" s="234"/>
-      <c r="S55" s="235"/>
+      <c r="A55" s="179"/>
+      <c r="B55" s="192"/>
+      <c r="C55" s="193"/>
+      <c r="D55" s="193"/>
+      <c r="E55" s="193"/>
+      <c r="F55" s="193"/>
+      <c r="G55" s="193"/>
+      <c r="H55" s="193"/>
+      <c r="I55" s="193"/>
+      <c r="J55" s="193"/>
+      <c r="K55" s="193"/>
+      <c r="L55" s="193"/>
+      <c r="M55" s="193"/>
+      <c r="N55" s="193"/>
+      <c r="O55" s="193"/>
+      <c r="P55" s="193"/>
+      <c r="Q55" s="193"/>
+      <c r="R55" s="193"/>
+      <c r="S55" s="194"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="211"/>
-      <c r="B56" s="233"/>
-      <c r="C56" s="234"/>
-      <c r="D56" s="234"/>
-      <c r="E56" s="234"/>
-      <c r="F56" s="234"/>
-      <c r="G56" s="234"/>
-      <c r="H56" s="234"/>
-      <c r="I56" s="234"/>
-      <c r="J56" s="234"/>
-      <c r="K56" s="234"/>
-      <c r="L56" s="234"/>
-      <c r="M56" s="234"/>
-      <c r="N56" s="234"/>
-      <c r="O56" s="234"/>
-      <c r="P56" s="234"/>
-      <c r="Q56" s="234"/>
-      <c r="R56" s="234"/>
-      <c r="S56" s="235"/>
+      <c r="A56" s="179"/>
+      <c r="B56" s="192"/>
+      <c r="C56" s="193"/>
+      <c r="D56" s="193"/>
+      <c r="E56" s="193"/>
+      <c r="F56" s="193"/>
+      <c r="G56" s="193"/>
+      <c r="H56" s="193"/>
+      <c r="I56" s="193"/>
+      <c r="J56" s="193"/>
+      <c r="K56" s="193"/>
+      <c r="L56" s="193"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="193"/>
+      <c r="O56" s="193"/>
+      <c r="P56" s="193"/>
+      <c r="Q56" s="193"/>
+      <c r="R56" s="193"/>
+      <c r="S56" s="194"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="213"/>
-      <c r="B57" s="236"/>
-      <c r="C57" s="237"/>
-      <c r="D57" s="237"/>
-      <c r="E57" s="237"/>
-      <c r="F57" s="237"/>
-      <c r="G57" s="237"/>
-      <c r="H57" s="237"/>
-      <c r="I57" s="237"/>
-      <c r="J57" s="237"/>
-      <c r="K57" s="237"/>
-      <c r="L57" s="237"/>
-      <c r="M57" s="237"/>
-      <c r="N57" s="237"/>
-      <c r="O57" s="237"/>
-      <c r="P57" s="237"/>
-      <c r="Q57" s="237"/>
-      <c r="R57" s="237"/>
-      <c r="S57" s="238"/>
+      <c r="A57" s="180"/>
+      <c r="B57" s="195"/>
+      <c r="C57" s="196"/>
+      <c r="D57" s="196"/>
+      <c r="E57" s="196"/>
+      <c r="F57" s="196"/>
+      <c r="G57" s="196"/>
+      <c r="H57" s="196"/>
+      <c r="I57" s="196"/>
+      <c r="J57" s="196"/>
+      <c r="K57" s="196"/>
+      <c r="L57" s="196"/>
+      <c r="M57" s="196"/>
+      <c r="N57" s="196"/>
+      <c r="O57" s="196"/>
+      <c r="P57" s="196"/>
+      <c r="Q57" s="196"/>
+      <c r="R57" s="196"/>
+      <c r="S57" s="197"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="42">
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="F40:S40"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="A10:A22"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="S47:S48"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A57"/>
     <mergeCell ref="A8:D9"/>
@@ -5448,38 +5473,36 @@
     <mergeCell ref="G47:G48"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="F40:S40"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="A10:A22"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="F43:S43"/>
-    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{C6EF9909-F153-4D59-8F12-E8C9F6355E3F}">
+            <x14:iconSet showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3Symbols2" iconId="0"/>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>S42</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8352AD92-AE48-443F-8268-FEC6552ABA57}">
           <x14:formula1>
             <xm:f>Parametri!$A:$A</xm:f>
@@ -5523,7 +5546,7 @@
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.42578125" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="128"/>
+    <col min="5" max="5" width="9.140625" style="127"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5551,7 +5574,7 @@
         <f>CONCATENATE(A2," ",F2)</f>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E2" s="128" t="str" cm="1">
+      <c r="E2" s="127" t="str" cm="1">
         <f t="array" ref="E2">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B11,3)="AGT",B2*3.416, IF(OR(RIGHT(Fisa!B11,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B11,2)="SM",RIGHT(Fisa!B11,2)="PM",RIGHT(Fisa!B11,2)="PG",RIGHT(Fisa!B11,2)="mm"), B2*5.796, B2)),B2)</f>
         <v/>
       </c>
@@ -5576,7 +5599,7 @@
         <f t="shared" ref="D3:D24" si="0">CONCATENATE(A3," ",F3)</f>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E3" s="128" t="str" cm="1">
+      <c r="E3" s="127" t="str" cm="1">
         <f t="array" ref="E3">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B12,3)="AGT",B3*3.416, IF(OR(RIGHT(Fisa!B12,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B12,2)="SM",RIGHT(Fisa!B12,2)="PM",RIGHT(Fisa!B12,2)="PG",RIGHT(Fisa!B12,2)="mm"), B3*5.796, B3)),B3)</f>
         <v/>
       </c>
@@ -5601,7 +5624,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E4" s="128" t="str" cm="1">
+      <c r="E4" s="127" t="str" cm="1">
         <f t="array" ref="E4">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B13,3)="AGT",B4*3.416, IF(OR(RIGHT(Fisa!B13,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B13,2)="SM",RIGHT(Fisa!B13,2)="PM",RIGHT(Fisa!B13,2)="PG",RIGHT(Fisa!B13,2)="mm"), B4*5.796, B4)),B4)</f>
         <v/>
       </c>
@@ -5626,7 +5649,7 @@
         <f t="shared" si="0"/>
         <v>0 mp</v>
       </c>
-      <c r="E5" s="128" t="str" cm="1">
+      <c r="E5" s="127" t="str" cm="1">
         <f t="array" ref="E5">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B14,3)="AGT",B5*3.416, IF(OR(RIGHT(Fisa!B14,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B14,2)="SM",RIGHT(Fisa!B14,2)="PM",RIGHT(Fisa!B14,2)="PG",RIGHT(Fisa!B14,2)="mm"), B5*5.796, B5)),B5)</f>
         <v/>
       </c>
@@ -5651,7 +5674,7 @@
         <f t="shared" si="0"/>
         <v>0 mp</v>
       </c>
-      <c r="E6" s="128" t="str" cm="1">
+      <c r="E6" s="127" t="str" cm="1">
         <f t="array" ref="E6">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B15,3)="AGT",B6*3.416, IF(OR(RIGHT(Fisa!B15,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B15,2)="SM",RIGHT(Fisa!B15,2)="PM",RIGHT(Fisa!B15,2)="PG",RIGHT(Fisa!B15,2)="mm"), B6*5.796, B6)),B6)</f>
         <v/>
       </c>
@@ -5676,7 +5699,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E7" s="128" t="str" cm="1">
+      <c r="E7" s="127" t="str" cm="1">
         <f t="array" ref="E7">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B16,3)="AGT",B7*3.416, IF(OR(RIGHT(Fisa!B16,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B16,2)="SM",RIGHT(Fisa!B16,2)="PM",RIGHT(Fisa!B16,2)="PG",RIGHT(Fisa!B16,2)="mm"), B7*5.796, B7)),B7)</f>
         <v/>
       </c>
@@ -5701,7 +5724,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E8" s="128" t="str" cm="1">
+      <c r="E8" s="127" t="str" cm="1">
         <f t="array" ref="E8">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B17,3)="AGT",B8*3.416, IF(OR(RIGHT(Fisa!B17,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B17,2)="SM",RIGHT(Fisa!B17,2)="PM",RIGHT(Fisa!B17,2)="PG",RIGHT(Fisa!B17,2)="mm"), B8*5.796, B8)),B8)</f>
         <v/>
       </c>
@@ -5726,7 +5749,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E9" s="128" t="str" cm="1">
+      <c r="E9" s="127" t="str" cm="1">
         <f t="array" ref="E9">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B18,3)="AGT",B9*3.416, IF(OR(RIGHT(Fisa!B18,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B18,2)="SM",RIGHT(Fisa!B18,2)="PM",RIGHT(Fisa!B18,2)="PG",RIGHT(Fisa!B18,2)="mm"), B9*5.796, B9)),B9)</f>
         <v/>
       </c>
@@ -5751,7 +5774,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E10" s="128" t="str" cm="1">
+      <c r="E10" s="127" t="str" cm="1">
         <f t="array" ref="E10">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B19,3)="AGT",B10*3.416, IF(OR(RIGHT(Fisa!B19,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B19,2)="SM",RIGHT(Fisa!B19,2)="PM",RIGHT(Fisa!B19,2)="PG",RIGHT(Fisa!B19,2)="mm"), B10*5.796, B10)),B10)</f>
         <v/>
       </c>
@@ -5776,7 +5799,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E11" s="128" t="str" cm="1">
+      <c r="E11" s="127" t="str" cm="1">
         <f t="array" ref="E11">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B20,3)="AGT",B11*3.416, IF(OR(RIGHT(Fisa!B20,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B20,2)="SM",RIGHT(Fisa!B20,2)="PM",RIGHT(Fisa!B20,2)="PG",RIGHT(Fisa!B20,2)="mm"), B11*5.796, B11)),B11)</f>
         <v/>
       </c>
@@ -5801,7 +5824,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E12" s="128" t="str" cm="1">
+      <c r="E12" s="127" t="str" cm="1">
         <f t="array" ref="E12">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B21,3)="AGT",B12*3.416, IF(OR(RIGHT(Fisa!B21,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B21,2)="SM",RIGHT(Fisa!B21,2)="PM",RIGHT(Fisa!B21,2)="PG",RIGHT(Fisa!B21,2)="mm"), B12*5.796, B12)),B12)</f>
         <v/>
       </c>
@@ -5826,7 +5849,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E13" s="128" t="str" cm="1">
+      <c r="E13" s="127" t="str" cm="1">
         <f t="array" ref="E13">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B22,3)="AGT",B13*3.416, IF(OR(RIGHT(Fisa!B22,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B22,2)="SM",RIGHT(Fisa!B22,2)="PM",RIGHT(Fisa!B22,2)="PG",RIGHT(Fisa!B22,2)="mm"), B13*5.796, B13)),B13)</f>
         <v/>
       </c>
@@ -5851,7 +5874,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E14" s="128" t="str" cm="1">
+      <c r="E14" s="127" t="str" cm="1">
         <f t="array" ref="E14">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B24,3)="AGT",B14*3.416, IF(OR(RIGHT(Fisa!B24,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B24,2)="SM",RIGHT(Fisa!B24,2)="PM",RIGHT(Fisa!B24,2)="PG",RIGHT(Fisa!B24,2)="mm"), B14*5.796, B14)),B14)</f>
         <v/>
       </c>
@@ -5876,7 +5899,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E15" s="128" t="str" cm="1">
+      <c r="E15" s="127" t="str" cm="1">
         <f t="array" ref="E15">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B25,3)="AGT",B15*3.416, IF(OR(RIGHT(Fisa!B25,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B25,2)="SM",RIGHT(Fisa!B25,2)="PM",RIGHT(Fisa!B25,2)="PG",RIGHT(Fisa!B25,2)="mm"), B15*5.796, B15)),B15)</f>
         <v/>
       </c>
@@ -5901,7 +5924,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E16" s="128" t="str" cm="1">
+      <c r="E16" s="127" t="str" cm="1">
         <f t="array" ref="E16">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B26,3)="AGT",B16*3.416, IF(OR(RIGHT(Fisa!B26,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B26,2)="SM",RIGHT(Fisa!B26,2)="PM",RIGHT(Fisa!B26,2)="PG",RIGHT(Fisa!B26,2)="mm"), B16*5.796, B16)),B16)</f>
         <v/>
       </c>
@@ -5926,7 +5949,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E17" s="128" t="str" cm="1">
+      <c r="E17" s="127" t="str" cm="1">
         <f t="array" ref="E17">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B27,3)="AGT",B17*3.416, IF(OR(RIGHT(Fisa!B27,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B27,2)="SM",RIGHT(Fisa!B27,2)="PM",RIGHT(Fisa!B27,2)="PG",RIGHT(Fisa!B27,2)="mm"), B17*5.796, B17)),B17)</f>
         <v/>
       </c>
@@ -5951,7 +5974,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> mp</v>
       </c>
-      <c r="E18" s="128" t="str" cm="1">
+      <c r="E18" s="127" t="str" cm="1">
         <f t="array" ref="E18">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B28,3)="AGT",B18*3.416, IF(OR(RIGHT(Fisa!B28,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B28,2)="SM",RIGHT(Fisa!B28,2)="PM",RIGHT(Fisa!B28,2)="PG",RIGHT(Fisa!B28,2)="mm"), B18*5.796, B18)),B18)</f>
         <v/>
       </c>
@@ -5976,7 +5999,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E19" s="128" t="str">
+      <c r="E19" s="127" t="str">
         <f>IFERROR(B19*4.1, "")</f>
         <v/>
       </c>
@@ -6001,7 +6024,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E20" s="128" t="str">
+      <c r="E20" s="127" t="str">
         <f>IFERROR(B20*4.1, "")</f>
         <v/>
       </c>
@@ -6026,7 +6049,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E21" s="128" t="str">
+      <c r="E21" s="127" t="str">
         <f>IFERROR(B21*4.1, "")</f>
         <v/>
       </c>
@@ -6051,7 +6074,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E22" s="128" t="str">
+      <c r="E22" s="127" t="str">
         <f t="shared" ref="E22:E24" si="1">IFERROR(B22*4.1, "")</f>
         <v/>
       </c>
@@ -6076,7 +6099,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E23" s="128" t="str">
+      <c r="E23" s="127" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6101,7 +6124,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve"> ml</v>
       </c>
-      <c r="E24" s="128" t="str">
+      <c r="E24" s="127" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -8635,18 +8658,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customFormat="1">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="262" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="258"/>
-      <c r="E1" s="258"/>
-      <c r="F1" s="258"/>
-      <c r="G1" s="258"/>
-      <c r="H1" s="258"/>
-      <c r="I1" s="258"/>
-      <c r="J1" s="258"/>
+      <c r="B1" s="262"/>
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="262"/>
+      <c r="G1" s="262"/>
+      <c r="H1" s="262"/>
+      <c r="I1" s="262"/>
+      <c r="J1" s="262"/>
       <c r="K1" s="12"/>
       <c r="L1" s="5"/>
     </row>
@@ -8667,15 +8690,15 @@
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="259">
+      <c r="B3" s="263">
         <f>Fisa!B3:D3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="259"/>
-      <c r="D3" s="259"/>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="259"/>
+      <c r="C3" s="263"/>
+      <c r="D3" s="263"/>
+      <c r="E3" s="263"/>
+      <c r="F3" s="263"/>
+      <c r="G3" s="263"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -8686,11 +8709,11 @@
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="260">
+      <c r="B4" s="264">
         <f>Fisa!B6</f>
         <v>0</v>
       </c>
-      <c r="C4" s="260"/>
+      <c r="C4" s="264"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -10138,7 +10161,7 @@
       <c r="L60" s="5"/>
     </row>
     <row r="61" spans="1:29" customFormat="1">
-      <c r="A61" s="125"/>
+      <c r="A61" s="124"/>
       <c r="B61" s="10" t="str">
         <f>Fisa!B37</f>
         <v/>
@@ -10158,7 +10181,7 @@
       <c r="L61" s="5"/>
     </row>
     <row r="62" spans="1:29" customFormat="1">
-      <c r="A62" s="126"/>
+      <c r="A62" s="125"/>
       <c r="B62" s="10" t="str">
         <f>Fisa!B38</f>
         <v/>
@@ -10683,10 +10706,10 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="167"/>
+    <col min="18" max="18" width="9.140625" style="166"/>
     <col min="20" max="20" width="9.140625" customWidth="1"/>
     <col min="21" max="21" width="4.140625" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" style="170"/>
+    <col min="22" max="22" width="9.140625" style="169"/>
     <col min="24" max="24" width="19.5703125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -10707,7 +10730,7 @@
       <c r="E1" t="s">
         <v>103</v>
       </c>
-      <c r="V1" s="170" t="s">
+      <c r="V1" s="169" t="s">
         <v>3</v>
       </c>
       <c r="W1" t="s">
@@ -10727,11 +10750,11 @@
       </c>
     </row>
     <row r="2" spans="1:27">
-      <c r="R2" s="168"/>
-      <c r="S2" s="165"/>
-      <c r="T2" s="146"/>
-      <c r="U2" s="146"/>
-      <c r="V2" s="170">
+      <c r="R2" s="167"/>
+      <c r="S2" s="164"/>
+      <c r="T2" s="145"/>
+      <c r="U2" s="145"/>
+      <c r="V2" s="169">
         <f>IFERROR(IF(W2="DB",Q2/13.5, ROUND(Q2/P2,2)),"")</f>
         <v>0</v>
       </c>
@@ -10767,11 +10790,11 @@
       </c>
     </row>
     <row r="3" spans="1:27">
-      <c r="R3" s="168"/>
-      <c r="S3" s="165"/>
-      <c r="T3" s="132"/>
-      <c r="U3" s="146"/>
-      <c r="V3" s="170">
+      <c r="R3" s="167"/>
+      <c r="S3" s="164"/>
+      <c r="T3" s="131"/>
+      <c r="U3" s="145"/>
+      <c r="V3" s="169">
         <f t="shared" ref="V3:V34" si="1">IFERROR(IF(W3="DB",Q3/13.5, ROUND(Q3/P3,2)),"")</f>
         <v>0</v>
       </c>
@@ -10807,11 +10830,11 @@
       </c>
     </row>
     <row r="4" spans="1:27">
-      <c r="R4" s="168"/>
-      <c r="S4" s="165"/>
-      <c r="T4" s="146"/>
-      <c r="U4" s="132"/>
-      <c r="V4" s="170">
+      <c r="R4" s="167"/>
+      <c r="S4" s="164"/>
+      <c r="T4" s="145"/>
+      <c r="U4" s="131"/>
+      <c r="V4" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10837,11 +10860,11 @@
       </c>
     </row>
     <row r="5" spans="1:27">
-      <c r="R5" s="168"/>
-      <c r="S5" s="165"/>
-      <c r="T5" s="146"/>
-      <c r="U5" s="132"/>
-      <c r="V5" s="170">
+      <c r="R5" s="167"/>
+      <c r="S5" s="164"/>
+      <c r="T5" s="145"/>
+      <c r="U5" s="131"/>
+      <c r="V5" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10867,11 +10890,11 @@
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="R6" s="168"/>
-      <c r="S6" s="165"/>
-      <c r="T6" s="146"/>
-      <c r="U6" s="132"/>
-      <c r="V6" s="170">
+      <c r="R6" s="167"/>
+      <c r="S6" s="164"/>
+      <c r="T6" s="145"/>
+      <c r="U6" s="131"/>
+      <c r="V6" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10897,11 +10920,11 @@
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="R7" s="168"/>
-      <c r="S7" s="165"/>
-      <c r="T7" s="132"/>
-      <c r="U7" s="132"/>
-      <c r="V7" s="170">
+      <c r="R7" s="167"/>
+      <c r="S7" s="164"/>
+      <c r="T7" s="131"/>
+      <c r="U7" s="131"/>
+      <c r="V7" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10927,11 +10950,11 @@
       </c>
     </row>
     <row r="8" spans="1:27">
-      <c r="R8" s="168"/>
-      <c r="S8" s="165"/>
-      <c r="T8" s="146"/>
-      <c r="U8" s="132"/>
-      <c r="V8" s="170">
+      <c r="R8" s="167"/>
+      <c r="S8" s="164"/>
+      <c r="T8" s="145"/>
+      <c r="U8" s="131"/>
+      <c r="V8" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10957,11 +10980,11 @@
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="R9" s="168"/>
-      <c r="S9" s="165"/>
-      <c r="T9" s="146"/>
-      <c r="U9" s="130"/>
-      <c r="V9" s="170">
+      <c r="R9" s="167"/>
+      <c r="S9" s="164"/>
+      <c r="T9" s="145"/>
+      <c r="U9" s="129"/>
+      <c r="V9" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -10987,11 +11010,11 @@
       </c>
     </row>
     <row r="10" spans="1:27">
-      <c r="R10" s="168"/>
-      <c r="S10" s="165"/>
-      <c r="T10" s="146"/>
-      <c r="U10" s="146"/>
-      <c r="V10" s="170">
+      <c r="R10" s="167"/>
+      <c r="S10" s="164"/>
+      <c r="T10" s="145"/>
+      <c r="U10" s="145"/>
+      <c r="V10" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11017,11 +11040,11 @@
       </c>
     </row>
     <row r="11" spans="1:27">
-      <c r="R11" s="168"/>
-      <c r="S11" s="165"/>
-      <c r="T11" s="146"/>
-      <c r="U11" s="146"/>
-      <c r="V11" s="170">
+      <c r="R11" s="167"/>
+      <c r="S11" s="164"/>
+      <c r="T11" s="145"/>
+      <c r="U11" s="145"/>
+      <c r="V11" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11047,11 +11070,11 @@
       </c>
     </row>
     <row r="12" spans="1:27">
-      <c r="R12" s="168"/>
-      <c r="S12" s="133"/>
-      <c r="T12" s="133"/>
-      <c r="U12" s="133"/>
-      <c r="V12" s="170">
+      <c r="R12" s="167"/>
+      <c r="S12" s="132"/>
+      <c r="T12" s="132"/>
+      <c r="U12" s="132"/>
+      <c r="V12" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11077,11 +11100,11 @@
       </c>
     </row>
     <row r="13" spans="1:27">
-      <c r="R13" s="168"/>
-      <c r="S13" s="161"/>
-      <c r="T13" s="160"/>
-      <c r="U13" s="166"/>
-      <c r="V13" s="170">
+      <c r="R13" s="167"/>
+      <c r="S13" s="160"/>
+      <c r="T13" s="159"/>
+      <c r="U13" s="165"/>
+      <c r="V13" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11107,11 +11130,11 @@
       </c>
     </row>
     <row r="14" spans="1:27">
-      <c r="R14" s="168"/>
-      <c r="S14" s="160"/>
-      <c r="T14" s="161"/>
-      <c r="U14" s="166"/>
-      <c r="V14" s="170">
+      <c r="R14" s="167"/>
+      <c r="S14" s="159"/>
+      <c r="T14" s="160"/>
+      <c r="U14" s="165"/>
+      <c r="V14" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11137,11 +11160,11 @@
       </c>
     </row>
     <row r="15" spans="1:27">
-      <c r="R15" s="168"/>
-      <c r="S15" s="161"/>
-      <c r="T15" s="161"/>
-      <c r="U15" s="133"/>
-      <c r="V15" s="170">
+      <c r="R15" s="167"/>
+      <c r="S15" s="160"/>
+      <c r="T15" s="160"/>
+      <c r="U15" s="132"/>
+      <c r="V15" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11167,11 +11190,11 @@
       </c>
     </row>
     <row r="16" spans="1:27">
-      <c r="R16" s="169"/>
-      <c r="S16" s="161"/>
-      <c r="T16" s="161"/>
-      <c r="U16" s="132"/>
-      <c r="V16" s="170">
+      <c r="R16" s="168"/>
+      <c r="S16" s="160"/>
+      <c r="T16" s="160"/>
+      <c r="U16" s="131"/>
+      <c r="V16" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11197,11 +11220,11 @@
       </c>
     </row>
     <row r="17" spans="1:27">
-      <c r="R17" s="169"/>
-      <c r="S17" s="161"/>
-      <c r="T17" s="161"/>
-      <c r="U17" s="132"/>
-      <c r="V17" s="170">
+      <c r="R17" s="168"/>
+      <c r="S17" s="160"/>
+      <c r="T17" s="160"/>
+      <c r="U17" s="131"/>
+      <c r="V17" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11227,28 +11250,28 @@
       </c>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="155"/>
-      <c r="B18" s="156"/>
-      <c r="C18" s="157"/>
-      <c r="D18" s="158"/>
-      <c r="E18" s="158"/>
-      <c r="F18" s="159"/>
-      <c r="G18" s="156"/>
-      <c r="H18" s="160"/>
-      <c r="I18" s="156"/>
-      <c r="J18" s="161"/>
-      <c r="K18" s="164"/>
-      <c r="L18" s="164"/>
-      <c r="M18" s="160"/>
-      <c r="N18" s="164"/>
-      <c r="O18" s="164"/>
-      <c r="P18" s="160"/>
-      <c r="Q18" s="164"/>
-      <c r="R18" s="169"/>
-      <c r="S18" s="161"/>
-      <c r="T18" s="161"/>
-      <c r="U18" s="132"/>
-      <c r="V18" s="170">
+      <c r="A18" s="154"/>
+      <c r="B18" s="155"/>
+      <c r="C18" s="156"/>
+      <c r="D18" s="157"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="158"/>
+      <c r="G18" s="155"/>
+      <c r="H18" s="159"/>
+      <c r="I18" s="155"/>
+      <c r="J18" s="160"/>
+      <c r="K18" s="163"/>
+      <c r="L18" s="163"/>
+      <c r="M18" s="159"/>
+      <c r="N18" s="163"/>
+      <c r="O18" s="163"/>
+      <c r="P18" s="159"/>
+      <c r="Q18" s="163"/>
+      <c r="R18" s="168"/>
+      <c r="S18" s="160"/>
+      <c r="T18" s="160"/>
+      <c r="U18" s="131"/>
+      <c r="V18" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11274,27 +11297,27 @@
       </c>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="155"/>
-      <c r="B19" s="156"/>
-      <c r="C19" s="157"/>
-      <c r="D19" s="158"/>
-      <c r="E19" s="158"/>
-      <c r="F19" s="159"/>
-      <c r="G19" s="156"/>
-      <c r="H19" s="160"/>
-      <c r="I19" s="156"/>
-      <c r="J19" s="160"/>
-      <c r="K19" s="164"/>
-      <c r="L19" s="164"/>
-      <c r="M19" s="162"/>
-      <c r="N19" s="164"/>
-      <c r="O19" s="164"/>
-      <c r="P19" s="161"/>
-      <c r="Q19" s="164"/>
-      <c r="R19" s="169"/>
-      <c r="S19" s="161"/>
-      <c r="T19" s="161"/>
-      <c r="V19" s="170">
+      <c r="A19" s="154"/>
+      <c r="B19" s="155"/>
+      <c r="C19" s="156"/>
+      <c r="D19" s="157"/>
+      <c r="E19" s="157"/>
+      <c r="F19" s="158"/>
+      <c r="G19" s="155"/>
+      <c r="H19" s="159"/>
+      <c r="I19" s="155"/>
+      <c r="J19" s="159"/>
+      <c r="K19" s="163"/>
+      <c r="L19" s="163"/>
+      <c r="M19" s="161"/>
+      <c r="N19" s="163"/>
+      <c r="O19" s="163"/>
+      <c r="P19" s="160"/>
+      <c r="Q19" s="163"/>
+      <c r="R19" s="168"/>
+      <c r="S19" s="160"/>
+      <c r="T19" s="160"/>
+      <c r="V19" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11320,27 +11343,27 @@
       </c>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="155"/>
-      <c r="B20" s="156"/>
-      <c r="C20" s="157"/>
-      <c r="D20" s="158"/>
-      <c r="E20" s="158"/>
-      <c r="F20" s="163"/>
-      <c r="G20" s="156"/>
-      <c r="H20" s="160"/>
-      <c r="I20" s="156"/>
-      <c r="J20" s="161"/>
-      <c r="K20" s="164"/>
-      <c r="L20" s="164"/>
-      <c r="M20" s="162"/>
-      <c r="N20" s="164"/>
-      <c r="O20" s="164"/>
-      <c r="P20" s="160"/>
-      <c r="Q20" s="164"/>
-      <c r="R20" s="169"/>
-      <c r="S20" s="160"/>
-      <c r="T20" s="156"/>
-      <c r="V20" s="170">
+      <c r="A20" s="154"/>
+      <c r="B20" s="155"/>
+      <c r="C20" s="156"/>
+      <c r="D20" s="157"/>
+      <c r="E20" s="157"/>
+      <c r="F20" s="162"/>
+      <c r="G20" s="155"/>
+      <c r="H20" s="159"/>
+      <c r="I20" s="155"/>
+      <c r="J20" s="160"/>
+      <c r="K20" s="163"/>
+      <c r="L20" s="163"/>
+      <c r="M20" s="161"/>
+      <c r="N20" s="163"/>
+      <c r="O20" s="163"/>
+      <c r="P20" s="159"/>
+      <c r="Q20" s="163"/>
+      <c r="R20" s="168"/>
+      <c r="S20" s="159"/>
+      <c r="T20" s="155"/>
+      <c r="V20" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11366,27 +11389,27 @@
       </c>
     </row>
     <row r="21" spans="1:27">
-      <c r="A21" s="155"/>
-      <c r="B21" s="156"/>
-      <c r="C21" s="157"/>
-      <c r="D21" s="158"/>
-      <c r="E21" s="158"/>
-      <c r="F21" s="159"/>
-      <c r="G21" s="156"/>
-      <c r="H21" s="161"/>
-      <c r="I21" s="156"/>
-      <c r="J21" s="161"/>
-      <c r="K21" s="164"/>
-      <c r="L21" s="164"/>
-      <c r="M21" s="161"/>
-      <c r="N21" s="164"/>
-      <c r="O21" s="164"/>
-      <c r="P21" s="161"/>
-      <c r="Q21" s="164"/>
-      <c r="R21" s="169"/>
-      <c r="S21" s="161"/>
-      <c r="T21" s="160"/>
-      <c r="V21" s="170">
+      <c r="A21" s="154"/>
+      <c r="B21" s="155"/>
+      <c r="C21" s="156"/>
+      <c r="D21" s="157"/>
+      <c r="E21" s="157"/>
+      <c r="F21" s="158"/>
+      <c r="G21" s="155"/>
+      <c r="H21" s="160"/>
+      <c r="I21" s="155"/>
+      <c r="J21" s="160"/>
+      <c r="K21" s="163"/>
+      <c r="L21" s="163"/>
+      <c r="M21" s="160"/>
+      <c r="N21" s="163"/>
+      <c r="O21" s="163"/>
+      <c r="P21" s="160"/>
+      <c r="Q21" s="163"/>
+      <c r="R21" s="168"/>
+      <c r="S21" s="160"/>
+      <c r="T21" s="159"/>
+      <c r="V21" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11412,7 +11435,7 @@
       </c>
     </row>
     <row r="22" spans="1:27">
-      <c r="V22" s="170">
+      <c r="V22" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11438,7 +11461,7 @@
       </c>
     </row>
     <row r="23" spans="1:27">
-      <c r="V23" s="170">
+      <c r="V23" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11464,7 +11487,7 @@
       </c>
     </row>
     <row r="24" spans="1:27">
-      <c r="V24" s="170">
+      <c r="V24" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11490,7 +11513,7 @@
       </c>
     </row>
     <row r="25" spans="1:27">
-      <c r="V25" s="170">
+      <c r="V25" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11512,7 +11535,7 @@
       </c>
     </row>
     <row r="26" spans="1:27">
-      <c r="V26" s="170">
+      <c r="V26" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11534,7 +11557,7 @@
       </c>
     </row>
     <row r="27" spans="1:27">
-      <c r="V27" s="170">
+      <c r="V27" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11556,7 +11579,7 @@
       </c>
     </row>
     <row r="28" spans="1:27">
-      <c r="V28" s="170">
+      <c r="V28" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11578,7 +11601,7 @@
       </c>
     </row>
     <row r="29" spans="1:27">
-      <c r="V29" s="170">
+      <c r="V29" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11600,7 +11623,7 @@
       </c>
     </row>
     <row r="30" spans="1:27">
-      <c r="V30" s="170">
+      <c r="V30" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11622,7 +11645,7 @@
       </c>
     </row>
     <row r="31" spans="1:27">
-      <c r="V31" s="170">
+      <c r="V31" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11644,7 +11667,7 @@
       </c>
     </row>
     <row r="32" spans="1:27">
-      <c r="V32" s="170">
+      <c r="V32" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11666,7 +11689,7 @@
       </c>
     </row>
     <row r="33" spans="22:27">
-      <c r="V33" s="170">
+      <c r="V33" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11688,7 +11711,7 @@
       </c>
     </row>
     <row r="34" spans="22:27">
-      <c r="V34" s="170">
+      <c r="V34" s="169">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -12009,11 +12032,11 @@
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="129"/>
-      <c r="B12" s="130"/>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="132"/>
+      <c r="A12" s="128"/>
+      <c r="B12" s="129"/>
+      <c r="C12" s="130"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="131"/>
       <c r="H12" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12036,11 +12059,11 @@
       </c>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="129"/>
-      <c r="B13" s="130"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="131"/>
-      <c r="E13" s="132"/>
+      <c r="A13" s="128"/>
+      <c r="B13" s="129"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="131"/>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12063,11 +12086,11 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="129"/>
-      <c r="B14" s="130"/>
-      <c r="C14" s="131"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="132"/>
+      <c r="A14" s="128"/>
+      <c r="B14" s="129"/>
+      <c r="C14" s="130"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="131"/>
       <c r="H14" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -12090,11 +12113,11 @@
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="154"/>
-      <c r="B15" s="153"/>
-      <c r="C15" s="153"/>
-      <c r="D15" s="153"/>
-      <c r="E15" s="153"/>
+      <c r="A15" s="153"/>
+      <c r="B15" s="152"/>
+      <c r="C15" s="152"/>
+      <c r="D15" s="152"/>
+      <c r="E15" s="152"/>
       <c r="H15" t="str">
         <f t="shared" si="1"/>
         <v/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6A4074-81E8-45B4-9023-B522BC72D6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548CDB13-BEA5-46F1-B1A1-EF9CD361BDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -1807,6 +1807,162 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1822,12 +1978,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1846,12 +1996,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1878,12 +2022,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1949,144 +2087,6 @@
     <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2573,33 +2573,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="210" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="235"/>
-      <c r="K1" s="235"/>
-      <c r="L1" s="236"/>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="212"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="219" t="s">
+      <c r="O1" s="199" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="221"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="201"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2618,165 +2618,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="222"/>
-      <c r="P2" s="223"/>
-      <c r="Q2" s="223"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="224"/>
+      <c r="O2" s="202"/>
+      <c r="P2" s="203"/>
+      <c r="Q2" s="203"/>
+      <c r="R2" s="203"/>
+      <c r="S2" s="204"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="242"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="244"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="175"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="177"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="225"/>
+      <c r="K3" s="226"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="237"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="239"/>
+      <c r="O3" s="213"/>
+      <c r="P3" s="195"/>
+      <c r="Q3" s="195"/>
+      <c r="R3" s="195"/>
+      <c r="S3" s="196"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="215"/>
+      <c r="B4" s="256"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="258"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="216"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="218"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="261"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="237"/>
-      <c r="P4" s="238"/>
-      <c r="Q4" s="238"/>
-      <c r="R4" s="238"/>
-      <c r="S4" s="239"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="195"/>
+      <c r="Q4" s="195"/>
+      <c r="R4" s="195"/>
+      <c r="S4" s="196"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="252"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="254"/>
+      <c r="B5" s="183"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="185"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="261"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="239"/>
+      <c r="I5" s="194"/>
+      <c r="J5" s="195"/>
+      <c r="K5" s="196"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="237"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="238"/>
-      <c r="R5" s="238"/>
-      <c r="S5" s="239"/>
+      <c r="O5" s="213"/>
+      <c r="P5" s="195"/>
+      <c r="Q5" s="195"/>
+      <c r="R5" s="195"/>
+      <c r="S5" s="196"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="257"/>
-      <c r="C6" s="258"/>
-      <c r="D6" s="259"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="190"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="260"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="227"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="192"/>
+      <c r="K6" s="193"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="225"/>
-      <c r="P6" s="226"/>
-      <c r="Q6" s="226"/>
-      <c r="R6" s="226"/>
-      <c r="S6" s="227"/>
+      <c r="O6" s="205"/>
+      <c r="P6" s="192"/>
+      <c r="Q6" s="192"/>
+      <c r="R6" s="192"/>
+      <c r="S6" s="193"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="181" t="s">
+      <c r="A8" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="182"/>
-      <c r="C8" s="182"/>
-      <c r="D8" s="183"/>
-      <c r="F8" s="228" t="s">
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="230"/>
+      <c r="F8" s="197" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="229"/>
-      <c r="Q8" s="229"/>
-      <c r="R8" s="229"/>
-      <c r="S8" s="230"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="198"/>
+      <c r="I8" s="198"/>
+      <c r="J8" s="198"/>
+      <c r="K8" s="198"/>
+      <c r="L8" s="198"/>
+      <c r="M8" s="198"/>
+      <c r="N8" s="198"/>
+      <c r="O8" s="198"/>
+      <c r="P8" s="198"/>
+      <c r="Q8" s="198"/>
+      <c r="R8" s="198"/>
+      <c r="S8" s="206"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="184"/>
-      <c r="B9" s="185"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="186"/>
-      <c r="F9" s="209" t="s">
+      <c r="A9" s="231"/>
+      <c r="B9" s="232"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="233"/>
+      <c r="F9" s="252" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="210"/>
-      <c r="H9" s="255" t="s">
+      <c r="G9" s="253"/>
+      <c r="H9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="256"/>
-      <c r="J9" s="207" t="s">
+      <c r="I9" s="187"/>
+      <c r="J9" s="250" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="208"/>
-      <c r="L9" s="250" t="s">
+      <c r="K9" s="251"/>
+      <c r="L9" s="181" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="251"/>
-      <c r="N9" s="187" t="s">
+      <c r="M9" s="182"/>
+      <c r="N9" s="218" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="188"/>
-      <c r="P9" s="202" t="s">
+      <c r="O9" s="219"/>
+      <c r="P9" s="245" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="203"/>
-      <c r="R9" s="187" t="s">
+      <c r="Q9" s="246"/>
+      <c r="R9" s="218" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="188"/>
+      <c r="S9" s="219"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="240" t="s">
+      <c r="A10" s="214" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2833,7 +2833,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="179"/>
+      <c r="A11" s="215"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2930,7 +2930,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="179"/>
+      <c r="A12" s="215"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3027,7 +3027,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="179"/>
+      <c r="A13" s="215"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3124,8 +3124,11 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="179"/>
-      <c r="B14" s="133"/>
+      <c r="A14" s="215"/>
+      <c r="B14" s="133" t="str" cm="1">
+        <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
+        <v/>
+      </c>
       <c r="C14" s="134" t="str">
         <f>IF(D14="buc",IF(B14&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B14,Deco!$Y$2:$Y$99,0)),""),IF(B14&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B14,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
@@ -3199,8 +3202,11 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="179"/>
-      <c r="B15" s="133"/>
+      <c r="A15" s="215"/>
+      <c r="B15" s="133" t="str" cm="1">
+        <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
+        <v/>
+      </c>
       <c r="C15" s="134" t="str">
         <f>IF(D15="buc",IF(B15&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B15,Deco!$Y$2:$Y$99,0)),""),IF(B15&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B15,Deco!$Y$2:$Y$99,0)),""))</f>
         <v/>
@@ -3274,7 +3280,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="179"/>
+      <c r="A16" s="215"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3352,7 +3358,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="179"/>
+      <c r="A17" s="215"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3430,7 +3436,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="179"/>
+      <c r="A18" s="215"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3508,7 +3514,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="179"/>
+      <c r="A19" s="215"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3586,7 +3592,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="179"/>
+      <c r="A20" s="215"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3664,7 +3670,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="179"/>
+      <c r="A21" s="215"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3742,7 +3748,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="241"/>
+      <c r="A22" s="216"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3876,7 +3882,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="240" t="s">
+      <c r="A24" s="214" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3975,7 +3981,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="179"/>
+      <c r="A25" s="215"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4072,7 +4078,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="179"/>
+      <c r="A26" s="215"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4169,7 +4175,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="179"/>
+      <c r="A27" s="215"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4247,7 +4253,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="180"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4400,7 +4406,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="204" t="s">
+      <c r="A32" s="247" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4479,7 +4485,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="205"/>
+      <c r="A33" s="248"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4556,7 +4562,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="206"/>
+      <c r="A34" s="249"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4654,7 +4660,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="204" t="s">
+      <c r="A36" s="247" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4733,7 +4739,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="205"/>
+      <c r="A37" s="248"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4810,7 +4816,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="206"/>
+      <c r="A38" s="249"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4901,7 +4907,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="240" t="s">
+      <c r="A40" s="214" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4913,25 +4919,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="231" t="s">
+      <c r="F40" s="207" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="232"/>
-      <c r="H40" s="232"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="232"/>
-      <c r="O40" s="232"/>
-      <c r="P40" s="232"/>
-      <c r="Q40" s="232"/>
-      <c r="R40" s="232"/>
-      <c r="S40" s="233"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
+      <c r="N40" s="208"/>
+      <c r="O40" s="208"/>
+      <c r="P40" s="208"/>
+      <c r="Q40" s="208"/>
+      <c r="R40" s="208"/>
+      <c r="S40" s="209"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="179"/>
+      <c r="A41" s="215"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -4994,7 +5000,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="179"/>
+      <c r="A42" s="215"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5019,13 +5025,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="198">
+      <c r="S42" s="175">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="179"/>
+      <c r="A43" s="215"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5037,26 +5043,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="228" t="str">
+      <c r="F43" s="197" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="229"/>
-      <c r="H43" s="229"/>
-      <c r="I43" s="229"/>
-      <c r="J43" s="229"/>
-      <c r="K43" s="229"/>
-      <c r="L43" s="229"/>
-      <c r="M43" s="229"/>
-      <c r="N43" s="229"/>
-      <c r="O43" s="229"/>
-      <c r="P43" s="229"/>
-      <c r="Q43" s="229"/>
-      <c r="R43" s="229"/>
-      <c r="S43" s="245"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="198"/>
+      <c r="N43" s="198"/>
+      <c r="O43" s="198"/>
+      <c r="P43" s="198"/>
+      <c r="Q43" s="198"/>
+      <c r="R43" s="198"/>
+      <c r="S43" s="176"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="179"/>
+      <c r="A44" s="215"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5112,7 +5118,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="179"/>
+      <c r="A45" s="215"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5183,7 +5189,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="179"/>
+      <c r="A46" s="215"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5197,7 +5203,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="179"/>
+      <c r="A47" s="215"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5208,31 +5214,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="198" t="s">
+      <c r="F47" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="211" t="str">
+      <c r="G47" s="254" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="198" t="s">
+      <c r="J47" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="200">
+      <c r="K47" s="243">
         <v>1</v>
       </c>
-      <c r="N47" s="198" t="s">
+      <c r="N47" s="175" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="246"/>
-      <c r="P47" s="247"/>
-      <c r="R47" s="198" t="s">
+      <c r="O47" s="177"/>
+      <c r="P47" s="178"/>
+      <c r="R47" s="175" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="198"/>
+      <c r="S47" s="175"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="180"/>
+      <c r="A48" s="217"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5243,15 +5249,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="199"/>
-      <c r="G48" s="212"/>
-      <c r="J48" s="199"/>
-      <c r="K48" s="201"/>
-      <c r="N48" s="245"/>
-      <c r="O48" s="248"/>
-      <c r="P48" s="249"/>
-      <c r="R48" s="245"/>
-      <c r="S48" s="199"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="255"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="244"/>
+      <c r="N48" s="176"/>
+      <c r="O48" s="179"/>
+      <c r="P48" s="180"/>
+      <c r="R48" s="176"/>
+      <c r="S48" s="223"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5260,187 +5266,193 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="178" t="s">
+      <c r="A50" s="227" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="189"/>
-      <c r="C50" s="190"/>
-      <c r="D50" s="190"/>
-      <c r="E50" s="190"/>
-      <c r="F50" s="190"/>
-      <c r="G50" s="190"/>
-      <c r="H50" s="190"/>
-      <c r="I50" s="190"/>
-      <c r="J50" s="190"/>
-      <c r="K50" s="190"/>
-      <c r="L50" s="190"/>
-      <c r="M50" s="190"/>
-      <c r="N50" s="190"/>
-      <c r="O50" s="190"/>
-      <c r="P50" s="190"/>
-      <c r="Q50" s="190"/>
-      <c r="R50" s="190"/>
-      <c r="S50" s="191"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="235"/>
+      <c r="D50" s="235"/>
+      <c r="E50" s="235"/>
+      <c r="F50" s="235"/>
+      <c r="G50" s="235"/>
+      <c r="H50" s="235"/>
+      <c r="I50" s="235"/>
+      <c r="J50" s="235"/>
+      <c r="K50" s="235"/>
+      <c r="L50" s="235"/>
+      <c r="M50" s="235"/>
+      <c r="N50" s="235"/>
+      <c r="O50" s="235"/>
+      <c r="P50" s="235"/>
+      <c r="Q50" s="235"/>
+      <c r="R50" s="235"/>
+      <c r="S50" s="236"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="179"/>
-      <c r="B51" s="192"/>
-      <c r="C51" s="193"/>
-      <c r="D51" s="193"/>
-      <c r="E51" s="193"/>
-      <c r="F51" s="193"/>
-      <c r="G51" s="193"/>
-      <c r="H51" s="193"/>
-      <c r="I51" s="193"/>
-      <c r="J51" s="193"/>
-      <c r="K51" s="193"/>
-      <c r="L51" s="193"/>
-      <c r="M51" s="193"/>
-      <c r="N51" s="193"/>
-      <c r="O51" s="193"/>
-      <c r="P51" s="193"/>
-      <c r="Q51" s="193"/>
-      <c r="R51" s="193"/>
-      <c r="S51" s="194"/>
+      <c r="A51" s="215"/>
+      <c r="B51" s="237"/>
+      <c r="C51" s="238"/>
+      <c r="D51" s="238"/>
+      <c r="E51" s="238"/>
+      <c r="F51" s="238"/>
+      <c r="G51" s="238"/>
+      <c r="H51" s="238"/>
+      <c r="I51" s="238"/>
+      <c r="J51" s="238"/>
+      <c r="K51" s="238"/>
+      <c r="L51" s="238"/>
+      <c r="M51" s="238"/>
+      <c r="N51" s="238"/>
+      <c r="O51" s="238"/>
+      <c r="P51" s="238"/>
+      <c r="Q51" s="238"/>
+      <c r="R51" s="238"/>
+      <c r="S51" s="239"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="179"/>
-      <c r="B52" s="192"/>
-      <c r="C52" s="193"/>
-      <c r="D52" s="193"/>
-      <c r="E52" s="193"/>
-      <c r="F52" s="193"/>
-      <c r="G52" s="193"/>
-      <c r="H52" s="193"/>
-      <c r="I52" s="193"/>
-      <c r="J52" s="193"/>
-      <c r="K52" s="193"/>
-      <c r="L52" s="193"/>
-      <c r="M52" s="193"/>
-      <c r="N52" s="193"/>
-      <c r="O52" s="193"/>
-      <c r="P52" s="193"/>
-      <c r="Q52" s="193"/>
-      <c r="R52" s="193"/>
-      <c r="S52" s="194"/>
+      <c r="A52" s="215"/>
+      <c r="B52" s="237"/>
+      <c r="C52" s="238"/>
+      <c r="D52" s="238"/>
+      <c r="E52" s="238"/>
+      <c r="F52" s="238"/>
+      <c r="G52" s="238"/>
+      <c r="H52" s="238"/>
+      <c r="I52" s="238"/>
+      <c r="J52" s="238"/>
+      <c r="K52" s="238"/>
+      <c r="L52" s="238"/>
+      <c r="M52" s="238"/>
+      <c r="N52" s="238"/>
+      <c r="O52" s="238"/>
+      <c r="P52" s="238"/>
+      <c r="Q52" s="238"/>
+      <c r="R52" s="238"/>
+      <c r="S52" s="239"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="179"/>
-      <c r="B53" s="192"/>
-      <c r="C53" s="193"/>
-      <c r="D53" s="193"/>
-      <c r="E53" s="193"/>
-      <c r="F53" s="193"/>
-      <c r="G53" s="193"/>
-      <c r="H53" s="193"/>
-      <c r="I53" s="193"/>
-      <c r="J53" s="193"/>
-      <c r="K53" s="193"/>
-      <c r="L53" s="193"/>
-      <c r="M53" s="193"/>
-      <c r="N53" s="193"/>
-      <c r="O53" s="193"/>
-      <c r="P53" s="193"/>
-      <c r="Q53" s="193"/>
-      <c r="R53" s="193"/>
-      <c r="S53" s="194"/>
+      <c r="A53" s="215"/>
+      <c r="B53" s="237"/>
+      <c r="C53" s="238"/>
+      <c r="D53" s="238"/>
+      <c r="E53" s="238"/>
+      <c r="F53" s="238"/>
+      <c r="G53" s="238"/>
+      <c r="H53" s="238"/>
+      <c r="I53" s="238"/>
+      <c r="J53" s="238"/>
+      <c r="K53" s="238"/>
+      <c r="L53" s="238"/>
+      <c r="M53" s="238"/>
+      <c r="N53" s="238"/>
+      <c r="O53" s="238"/>
+      <c r="P53" s="238"/>
+      <c r="Q53" s="238"/>
+      <c r="R53" s="238"/>
+      <c r="S53" s="239"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="179"/>
-      <c r="B54" s="192"/>
-      <c r="C54" s="193"/>
-      <c r="D54" s="193"/>
-      <c r="E54" s="193"/>
-      <c r="F54" s="193"/>
-      <c r="G54" s="193"/>
-      <c r="H54" s="193"/>
-      <c r="I54" s="193"/>
-      <c r="J54" s="193"/>
-      <c r="K54" s="193"/>
-      <c r="L54" s="193"/>
-      <c r="M54" s="193"/>
-      <c r="N54" s="193"/>
-      <c r="O54" s="193"/>
-      <c r="P54" s="193"/>
-      <c r="Q54" s="193"/>
-      <c r="R54" s="193"/>
-      <c r="S54" s="194"/>
+      <c r="A54" s="215"/>
+      <c r="B54" s="237"/>
+      <c r="C54" s="238"/>
+      <c r="D54" s="238"/>
+      <c r="E54" s="238"/>
+      <c r="F54" s="238"/>
+      <c r="G54" s="238"/>
+      <c r="H54" s="238"/>
+      <c r="I54" s="238"/>
+      <c r="J54" s="238"/>
+      <c r="K54" s="238"/>
+      <c r="L54" s="238"/>
+      <c r="M54" s="238"/>
+      <c r="N54" s="238"/>
+      <c r="O54" s="238"/>
+      <c r="P54" s="238"/>
+      <c r="Q54" s="238"/>
+      <c r="R54" s="238"/>
+      <c r="S54" s="239"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="179"/>
-      <c r="B55" s="192"/>
-      <c r="C55" s="193"/>
-      <c r="D55" s="193"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
-      <c r="G55" s="193"/>
-      <c r="H55" s="193"/>
-      <c r="I55" s="193"/>
-      <c r="J55" s="193"/>
-      <c r="K55" s="193"/>
-      <c r="L55" s="193"/>
-      <c r="M55" s="193"/>
-      <c r="N55" s="193"/>
-      <c r="O55" s="193"/>
-      <c r="P55" s="193"/>
-      <c r="Q55" s="193"/>
-      <c r="R55" s="193"/>
-      <c r="S55" s="194"/>
+      <c r="A55" s="215"/>
+      <c r="B55" s="237"/>
+      <c r="C55" s="238"/>
+      <c r="D55" s="238"/>
+      <c r="E55" s="238"/>
+      <c r="F55" s="238"/>
+      <c r="G55" s="238"/>
+      <c r="H55" s="238"/>
+      <c r="I55" s="238"/>
+      <c r="J55" s="238"/>
+      <c r="K55" s="238"/>
+      <c r="L55" s="238"/>
+      <c r="M55" s="238"/>
+      <c r="N55" s="238"/>
+      <c r="O55" s="238"/>
+      <c r="P55" s="238"/>
+      <c r="Q55" s="238"/>
+      <c r="R55" s="238"/>
+      <c r="S55" s="239"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="179"/>
-      <c r="B56" s="192"/>
-      <c r="C56" s="193"/>
-      <c r="D56" s="193"/>
-      <c r="E56" s="193"/>
-      <c r="F56" s="193"/>
-      <c r="G56" s="193"/>
-      <c r="H56" s="193"/>
-      <c r="I56" s="193"/>
-      <c r="J56" s="193"/>
-      <c r="K56" s="193"/>
-      <c r="L56" s="193"/>
-      <c r="M56" s="193"/>
-      <c r="N56" s="193"/>
-      <c r="O56" s="193"/>
-      <c r="P56" s="193"/>
-      <c r="Q56" s="193"/>
-      <c r="R56" s="193"/>
-      <c r="S56" s="194"/>
+      <c r="A56" s="215"/>
+      <c r="B56" s="237"/>
+      <c r="C56" s="238"/>
+      <c r="D56" s="238"/>
+      <c r="E56" s="238"/>
+      <c r="F56" s="238"/>
+      <c r="G56" s="238"/>
+      <c r="H56" s="238"/>
+      <c r="I56" s="238"/>
+      <c r="J56" s="238"/>
+      <c r="K56" s="238"/>
+      <c r="L56" s="238"/>
+      <c r="M56" s="238"/>
+      <c r="N56" s="238"/>
+      <c r="O56" s="238"/>
+      <c r="P56" s="238"/>
+      <c r="Q56" s="238"/>
+      <c r="R56" s="238"/>
+      <c r="S56" s="239"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="180"/>
-      <c r="B57" s="195"/>
-      <c r="C57" s="196"/>
-      <c r="D57" s="196"/>
-      <c r="E57" s="196"/>
-      <c r="F57" s="196"/>
-      <c r="G57" s="196"/>
-      <c r="H57" s="196"/>
-      <c r="I57" s="196"/>
-      <c r="J57" s="196"/>
-      <c r="K57" s="196"/>
-      <c r="L57" s="196"/>
-      <c r="M57" s="196"/>
-      <c r="N57" s="196"/>
-      <c r="O57" s="196"/>
-      <c r="P57" s="196"/>
-      <c r="Q57" s="196"/>
-      <c r="R57" s="196"/>
-      <c r="S57" s="197"/>
+      <c r="A57" s="217"/>
+      <c r="B57" s="240"/>
+      <c r="C57" s="241"/>
+      <c r="D57" s="241"/>
+      <c r="E57" s="241"/>
+      <c r="F57" s="241"/>
+      <c r="G57" s="241"/>
+      <c r="H57" s="241"/>
+      <c r="I57" s="241"/>
+      <c r="J57" s="241"/>
+      <c r="K57" s="241"/>
+      <c r="L57" s="241"/>
+      <c r="M57" s="241"/>
+      <c r="N57" s="241"/>
+      <c r="O57" s="241"/>
+      <c r="P57" s="241"/>
+      <c r="Q57" s="241"/>
+      <c r="R57" s="241"/>
+      <c r="S57" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B50:S57"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="O6:S6"/>
@@ -5457,22 +5469,16 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="R47:R48"/>
     <mergeCell ref="S47:S48"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="B50:S57"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5633,9 +5639,9 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5">
+      <c r="A5" t="str">
         <f>Fisa!B14</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="B5" t="str">
         <f>Fisa!C14</f>
@@ -5647,7 +5653,7 @@
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
-        <v>0 mp</v>
+        <v xml:space="preserve"> mp</v>
       </c>
       <c r="E5" s="127" t="str" cm="1">
         <f t="array" ref="E5">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B14,3)="AGT",B5*3.416, IF(OR(RIGHT(Fisa!B14,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B14,2)="SM",RIGHT(Fisa!B14,2)="PM",RIGHT(Fisa!B14,2)="PG",RIGHT(Fisa!B14,2)="mm"), B5*5.796, B5)),B5)</f>
@@ -5658,9 +5664,9 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6">
+      <c r="A6" t="str">
         <f>Fisa!B15</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="B6" t="str">
         <f>Fisa!C15</f>
@@ -5672,7 +5678,7 @@
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
-        <v>0 mp</v>
+        <v xml:space="preserve"> mp</v>
       </c>
       <c r="E6" s="127" t="str" cm="1">
         <f t="array" ref="E6">IF(Fisa!I3="Debitare căntuire",IF(LEFT(Fisa!B15,3)="AGT",B6*3.416, IF(OR(RIGHT(Fisa!B15,1)={"0","1","2","3","4","5","6","7","8","9"},RIGHT(Fisa!B15,2)="SM",RIGHT(Fisa!B15,2)="PM",RIGHT(Fisa!B15,2)="PG",RIGHT(Fisa!B15,2)="mm"), B6*5.796, B6)),B6)</f>
@@ -8841,9 +8847,9 @@
       <c r="L10" s="5"/>
     </row>
     <row r="11" spans="1:12" customFormat="1">
-      <c r="B11" s="8">
+      <c r="B11" s="8" t="str">
         <f>Fisa!B14</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C11" s="8" t="str">
         <f>Fisa!C14</f>
@@ -8860,9 +8866,9 @@
       <c r="L11" s="5"/>
     </row>
     <row r="12" spans="1:12" customFormat="1">
-      <c r="B12" s="8">
+      <c r="B12" s="8" t="str">
         <f>Fisa!B15</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="C12" s="8" t="str">
         <f>Fisa!C15</f>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548CDB13-BEA5-46F1-B1A1-EF9CD361BDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729C0399-119A-46F6-8779-9CA8349BF9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -91,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="118">
   <si>
     <t>FIRMA:</t>
   </si>
@@ -446,9 +446,6 @@
   <si>
     <t>Status  Dublaj</t>
   </si>
-  <si>
-    <t>SHK-W 960 ST7-2.0</t>
-  </si>
 </sst>
 </file>
 
@@ -1300,7 +1297,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="270">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1807,8 +1804,229 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1864,230 +2082,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2097,6 +2094,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2573,33 +2575,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="234" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="212"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
+      <c r="L1" s="236"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="199" t="s">
+      <c r="O1" s="219" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="201"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="221"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2618,165 +2620,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="202"/>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="203"/>
-      <c r="R2" s="203"/>
-      <c r="S2" s="204"/>
+      <c r="O2" s="222"/>
+      <c r="P2" s="223"/>
+      <c r="Q2" s="223"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="224"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="220"/>
-      <c r="C3" s="221"/>
-      <c r="D3" s="222"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="244"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="225"/>
-      <c r="K3" s="226"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="177"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="195"/>
-      <c r="Q3" s="195"/>
-      <c r="R3" s="195"/>
-      <c r="S3" s="196"/>
+      <c r="O3" s="237"/>
+      <c r="P3" s="238"/>
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="239"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="256"/>
-      <c r="C4" s="257"/>
-      <c r="D4" s="258"/>
+      <c r="B4" s="213"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="215"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="259"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="261"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="218"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="195"/>
-      <c r="Q4" s="195"/>
-      <c r="R4" s="195"/>
-      <c r="S4" s="196"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="238"/>
+      <c r="Q4" s="238"/>
+      <c r="R4" s="238"/>
+      <c r="S4" s="239"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="185"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="254"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="194"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="196"/>
+      <c r="I5" s="261"/>
+      <c r="J5" s="238"/>
+      <c r="K5" s="239"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="213"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="195"/>
-      <c r="R5" s="195"/>
-      <c r="S5" s="196"/>
+      <c r="O5" s="237"/>
+      <c r="P5" s="238"/>
+      <c r="Q5" s="238"/>
+      <c r="R5" s="238"/>
+      <c r="S5" s="239"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="188"/>
-      <c r="C6" s="189"/>
-      <c r="D6" s="190"/>
+      <c r="B6" s="257"/>
+      <c r="C6" s="258"/>
+      <c r="D6" s="259"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="191"/>
-      <c r="J6" s="192"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="260"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="227"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="205"/>
-      <c r="P6" s="192"/>
-      <c r="Q6" s="192"/>
-      <c r="R6" s="192"/>
-      <c r="S6" s="193"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="226"/>
+      <c r="Q6" s="226"/>
+      <c r="R6" s="226"/>
+      <c r="S6" s="227"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="228" t="s">
+      <c r="A8" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="230"/>
-      <c r="F8" s="197" t="s">
+      <c r="B8" s="182"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="183"/>
+      <c r="F8" s="228" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="198"/>
-      <c r="H8" s="198"/>
-      <c r="I8" s="198"/>
-      <c r="J8" s="198"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="198"/>
-      <c r="O8" s="198"/>
-      <c r="P8" s="198"/>
-      <c r="Q8" s="198"/>
-      <c r="R8" s="198"/>
-      <c r="S8" s="206"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="229"/>
+      <c r="P8" s="229"/>
+      <c r="Q8" s="229"/>
+      <c r="R8" s="229"/>
+      <c r="S8" s="230"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="231"/>
-      <c r="B9" s="232"/>
-      <c r="C9" s="232"/>
-      <c r="D9" s="233"/>
-      <c r="F9" s="252" t="s">
+      <c r="A9" s="184"/>
+      <c r="B9" s="185"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="186"/>
+      <c r="F9" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="253"/>
-      <c r="H9" s="186" t="s">
+      <c r="G9" s="210"/>
+      <c r="H9" s="255" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="187"/>
-      <c r="J9" s="250" t="s">
+      <c r="I9" s="256"/>
+      <c r="J9" s="207" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="251"/>
-      <c r="L9" s="181" t="s">
+      <c r="K9" s="208"/>
+      <c r="L9" s="250" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="182"/>
-      <c r="N9" s="218" t="s">
+      <c r="M9" s="251"/>
+      <c r="N9" s="187" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="219"/>
-      <c r="P9" s="245" t="s">
+      <c r="O9" s="188"/>
+      <c r="P9" s="202" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="218" t="s">
+      <c r="Q9" s="203"/>
+      <c r="R9" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="219"/>
+      <c r="S9" s="188"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="214" t="s">
+      <c r="A10" s="240" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2833,7 +2835,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="215"/>
+      <c r="A11" s="179"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2930,7 +2932,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="215"/>
+      <c r="A12" s="179"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3027,7 +3029,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="215"/>
+      <c r="A13" s="179"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3124,7 +3126,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="215"/>
+      <c r="A14" s="179"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3202,7 +3204,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="215"/>
+      <c r="A15" s="179"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3280,7 +3282,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="215"/>
+      <c r="A16" s="179"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3358,7 +3360,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="215"/>
+      <c r="A17" s="179"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3436,7 +3438,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="215"/>
+      <c r="A18" s="179"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3514,7 +3516,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="215"/>
+      <c r="A19" s="179"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3592,7 +3594,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="215"/>
+      <c r="A20" s="179"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3670,7 +3672,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="215"/>
+      <c r="A21" s="179"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3748,7 +3750,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="216"/>
+      <c r="A22" s="241"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3882,7 +3884,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="214" t="s">
+      <c r="A24" s="240" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3981,7 +3983,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="215"/>
+      <c r="A25" s="179"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4078,7 +4080,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="215"/>
+      <c r="A26" s="179"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4175,7 +4177,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="215"/>
+      <c r="A27" s="179"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4253,7 +4255,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="217"/>
+      <c r="A28" s="180"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4406,7 +4408,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="247" t="s">
+      <c r="A32" s="204" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4485,7 +4487,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="248"/>
+      <c r="A33" s="205"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4562,7 +4564,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="249"/>
+      <c r="A34" s="206"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4660,7 +4662,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="247" t="s">
+      <c r="A36" s="204" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4739,7 +4741,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="248"/>
+      <c r="A37" s="205"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4816,7 +4818,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="249"/>
+      <c r="A38" s="206"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4907,7 +4909,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="214" t="s">
+      <c r="A40" s="240" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4919,25 +4921,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="207" t="s">
+      <c r="F40" s="231" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="208"/>
-      <c r="L40" s="208"/>
-      <c r="M40" s="208"/>
-      <c r="N40" s="208"/>
-      <c r="O40" s="208"/>
-      <c r="P40" s="208"/>
-      <c r="Q40" s="208"/>
-      <c r="R40" s="208"/>
-      <c r="S40" s="209"/>
+      <c r="G40" s="232"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="232"/>
+      <c r="O40" s="232"/>
+      <c r="P40" s="232"/>
+      <c r="Q40" s="232"/>
+      <c r="R40" s="232"/>
+      <c r="S40" s="233"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="215"/>
+      <c r="A41" s="179"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -5000,7 +5002,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="215"/>
+      <c r="A42" s="179"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5025,13 +5027,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="175">
+      <c r="S42" s="198">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="215"/>
+      <c r="A43" s="179"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5043,26 +5045,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="197" t="str">
+      <c r="F43" s="228" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="198"/>
-      <c r="H43" s="198"/>
-      <c r="I43" s="198"/>
-      <c r="J43" s="198"/>
-      <c r="K43" s="198"/>
-      <c r="L43" s="198"/>
-      <c r="M43" s="198"/>
-      <c r="N43" s="198"/>
-      <c r="O43" s="198"/>
-      <c r="P43" s="198"/>
-      <c r="Q43" s="198"/>
-      <c r="R43" s="198"/>
-      <c r="S43" s="176"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="229"/>
+      <c r="J43" s="229"/>
+      <c r="K43" s="229"/>
+      <c r="L43" s="229"/>
+      <c r="M43" s="229"/>
+      <c r="N43" s="229"/>
+      <c r="O43" s="229"/>
+      <c r="P43" s="229"/>
+      <c r="Q43" s="229"/>
+      <c r="R43" s="229"/>
+      <c r="S43" s="245"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="215"/>
+      <c r="A44" s="179"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5118,7 +5120,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="215"/>
+      <c r="A45" s="179"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5189,7 +5191,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="215"/>
+      <c r="A46" s="179"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5203,7 +5205,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="215"/>
+      <c r="A47" s="179"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5214,31 +5216,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="175" t="s">
+      <c r="F47" s="198" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="254" t="str">
+      <c r="G47" s="211" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="175" t="s">
+      <c r="J47" s="198" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="243">
+      <c r="K47" s="200">
         <v>1</v>
       </c>
-      <c r="N47" s="175" t="s">
+      <c r="N47" s="198" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="177"/>
-      <c r="P47" s="178"/>
-      <c r="R47" s="175" t="s">
+      <c r="O47" s="246"/>
+      <c r="P47" s="247"/>
+      <c r="R47" s="198" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="175"/>
+      <c r="S47" s="198"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="217"/>
+      <c r="A48" s="180"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5249,15 +5251,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="223"/>
-      <c r="G48" s="255"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="244"/>
-      <c r="N48" s="176"/>
-      <c r="O48" s="179"/>
-      <c r="P48" s="180"/>
-      <c r="R48" s="176"/>
-      <c r="S48" s="223"/>
+      <c r="F48" s="199"/>
+      <c r="G48" s="212"/>
+      <c r="J48" s="199"/>
+      <c r="K48" s="201"/>
+      <c r="N48" s="245"/>
+      <c r="O48" s="248"/>
+      <c r="P48" s="249"/>
+      <c r="R48" s="245"/>
+      <c r="S48" s="199"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5266,177 +5268,203 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="227" t="s">
+      <c r="A50" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="234"/>
-      <c r="C50" s="235"/>
-      <c r="D50" s="235"/>
-      <c r="E50" s="235"/>
-      <c r="F50" s="235"/>
-      <c r="G50" s="235"/>
-      <c r="H50" s="235"/>
-      <c r="I50" s="235"/>
-      <c r="J50" s="235"/>
-      <c r="K50" s="235"/>
-      <c r="L50" s="235"/>
-      <c r="M50" s="235"/>
-      <c r="N50" s="235"/>
-      <c r="O50" s="235"/>
-      <c r="P50" s="235"/>
-      <c r="Q50" s="235"/>
-      <c r="R50" s="235"/>
-      <c r="S50" s="236"/>
+      <c r="B50" s="189"/>
+      <c r="C50" s="190"/>
+      <c r="D50" s="190"/>
+      <c r="E50" s="190"/>
+      <c r="F50" s="190"/>
+      <c r="G50" s="190"/>
+      <c r="H50" s="190"/>
+      <c r="I50" s="190"/>
+      <c r="J50" s="190"/>
+      <c r="K50" s="190"/>
+      <c r="L50" s="190"/>
+      <c r="M50" s="190"/>
+      <c r="N50" s="190"/>
+      <c r="O50" s="190"/>
+      <c r="P50" s="190"/>
+      <c r="Q50" s="190"/>
+      <c r="R50" s="190"/>
+      <c r="S50" s="191"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="215"/>
-      <c r="B51" s="237"/>
-      <c r="C51" s="238"/>
-      <c r="D51" s="238"/>
-      <c r="E51" s="238"/>
-      <c r="F51" s="238"/>
-      <c r="G51" s="238"/>
-      <c r="H51" s="238"/>
-      <c r="I51" s="238"/>
-      <c r="J51" s="238"/>
-      <c r="K51" s="238"/>
-      <c r="L51" s="238"/>
-      <c r="M51" s="238"/>
-      <c r="N51" s="238"/>
-      <c r="O51" s="238"/>
-      <c r="P51" s="238"/>
-      <c r="Q51" s="238"/>
-      <c r="R51" s="238"/>
-      <c r="S51" s="239"/>
+      <c r="A51" s="179"/>
+      <c r="B51" s="192"/>
+      <c r="C51" s="193"/>
+      <c r="D51" s="193"/>
+      <c r="E51" s="193"/>
+      <c r="F51" s="193"/>
+      <c r="G51" s="193"/>
+      <c r="H51" s="193"/>
+      <c r="I51" s="193"/>
+      <c r="J51" s="193"/>
+      <c r="K51" s="193"/>
+      <c r="L51" s="193"/>
+      <c r="M51" s="193"/>
+      <c r="N51" s="193"/>
+      <c r="O51" s="193"/>
+      <c r="P51" s="193"/>
+      <c r="Q51" s="193"/>
+      <c r="R51" s="193"/>
+      <c r="S51" s="194"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="215"/>
-      <c r="B52" s="237"/>
-      <c r="C52" s="238"/>
-      <c r="D52" s="238"/>
-      <c r="E52" s="238"/>
-      <c r="F52" s="238"/>
-      <c r="G52" s="238"/>
-      <c r="H52" s="238"/>
-      <c r="I52" s="238"/>
-      <c r="J52" s="238"/>
-      <c r="K52" s="238"/>
-      <c r="L52" s="238"/>
-      <c r="M52" s="238"/>
-      <c r="N52" s="238"/>
-      <c r="O52" s="238"/>
-      <c r="P52" s="238"/>
-      <c r="Q52" s="238"/>
-      <c r="R52" s="238"/>
-      <c r="S52" s="239"/>
+      <c r="A52" s="179"/>
+      <c r="B52" s="192"/>
+      <c r="C52" s="193"/>
+      <c r="D52" s="193"/>
+      <c r="E52" s="193"/>
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="193"/>
+      <c r="J52" s="193"/>
+      <c r="K52" s="193"/>
+      <c r="L52" s="193"/>
+      <c r="M52" s="193"/>
+      <c r="N52" s="193"/>
+      <c r="O52" s="193"/>
+      <c r="P52" s="193"/>
+      <c r="Q52" s="193"/>
+      <c r="R52" s="193"/>
+      <c r="S52" s="194"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="215"/>
-      <c r="B53" s="237"/>
-      <c r="C53" s="238"/>
-      <c r="D53" s="238"/>
-      <c r="E53" s="238"/>
-      <c r="F53" s="238"/>
-      <c r="G53" s="238"/>
-      <c r="H53" s="238"/>
-      <c r="I53" s="238"/>
-      <c r="J53" s="238"/>
-      <c r="K53" s="238"/>
-      <c r="L53" s="238"/>
-      <c r="M53" s="238"/>
-      <c r="N53" s="238"/>
-      <c r="O53" s="238"/>
-      <c r="P53" s="238"/>
-      <c r="Q53" s="238"/>
-      <c r="R53" s="238"/>
-      <c r="S53" s="239"/>
+      <c r="A53" s="179"/>
+      <c r="B53" s="192"/>
+      <c r="C53" s="193"/>
+      <c r="D53" s="193"/>
+      <c r="E53" s="193"/>
+      <c r="F53" s="193"/>
+      <c r="G53" s="193"/>
+      <c r="H53" s="193"/>
+      <c r="I53" s="193"/>
+      <c r="J53" s="193"/>
+      <c r="K53" s="193"/>
+      <c r="L53" s="193"/>
+      <c r="M53" s="193"/>
+      <c r="N53" s="193"/>
+      <c r="O53" s="193"/>
+      <c r="P53" s="193"/>
+      <c r="Q53" s="193"/>
+      <c r="R53" s="193"/>
+      <c r="S53" s="194"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="215"/>
-      <c r="B54" s="237"/>
-      <c r="C54" s="238"/>
-      <c r="D54" s="238"/>
-      <c r="E54" s="238"/>
-      <c r="F54" s="238"/>
-      <c r="G54" s="238"/>
-      <c r="H54" s="238"/>
-      <c r="I54" s="238"/>
-      <c r="J54" s="238"/>
-      <c r="K54" s="238"/>
-      <c r="L54" s="238"/>
-      <c r="M54" s="238"/>
-      <c r="N54" s="238"/>
-      <c r="O54" s="238"/>
-      <c r="P54" s="238"/>
-      <c r="Q54" s="238"/>
-      <c r="R54" s="238"/>
-      <c r="S54" s="239"/>
+      <c r="A54" s="179"/>
+      <c r="B54" s="192"/>
+      <c r="C54" s="193"/>
+      <c r="D54" s="193"/>
+      <c r="E54" s="193"/>
+      <c r="F54" s="193"/>
+      <c r="G54" s="193"/>
+      <c r="H54" s="193"/>
+      <c r="I54" s="193"/>
+      <c r="J54" s="193"/>
+      <c r="K54" s="193"/>
+      <c r="L54" s="193"/>
+      <c r="M54" s="193"/>
+      <c r="N54" s="193"/>
+      <c r="O54" s="193"/>
+      <c r="P54" s="193"/>
+      <c r="Q54" s="193"/>
+      <c r="R54" s="193"/>
+      <c r="S54" s="194"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="215"/>
-      <c r="B55" s="237"/>
-      <c r="C55" s="238"/>
-      <c r="D55" s="238"/>
-      <c r="E55" s="238"/>
-      <c r="F55" s="238"/>
-      <c r="G55" s="238"/>
-      <c r="H55" s="238"/>
-      <c r="I55" s="238"/>
-      <c r="J55" s="238"/>
-      <c r="K55" s="238"/>
-      <c r="L55" s="238"/>
-      <c r="M55" s="238"/>
-      <c r="N55" s="238"/>
-      <c r="O55" s="238"/>
-      <c r="P55" s="238"/>
-      <c r="Q55" s="238"/>
-      <c r="R55" s="238"/>
-      <c r="S55" s="239"/>
+      <c r="A55" s="179"/>
+      <c r="B55" s="192"/>
+      <c r="C55" s="193"/>
+      <c r="D55" s="193"/>
+      <c r="E55" s="193"/>
+      <c r="F55" s="193"/>
+      <c r="G55" s="193"/>
+      <c r="H55" s="193"/>
+      <c r="I55" s="193"/>
+      <c r="J55" s="193"/>
+      <c r="K55" s="193"/>
+      <c r="L55" s="193"/>
+      <c r="M55" s="193"/>
+      <c r="N55" s="193"/>
+      <c r="O55" s="193"/>
+      <c r="P55" s="193"/>
+      <c r="Q55" s="193"/>
+      <c r="R55" s="193"/>
+      <c r="S55" s="194"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="215"/>
-      <c r="B56" s="237"/>
-      <c r="C56" s="238"/>
-      <c r="D56" s="238"/>
-      <c r="E56" s="238"/>
-      <c r="F56" s="238"/>
-      <c r="G56" s="238"/>
-      <c r="H56" s="238"/>
-      <c r="I56" s="238"/>
-      <c r="J56" s="238"/>
-      <c r="K56" s="238"/>
-      <c r="L56" s="238"/>
-      <c r="M56" s="238"/>
-      <c r="N56" s="238"/>
-      <c r="O56" s="238"/>
-      <c r="P56" s="238"/>
-      <c r="Q56" s="238"/>
-      <c r="R56" s="238"/>
-      <c r="S56" s="239"/>
+      <c r="A56" s="179"/>
+      <c r="B56" s="192"/>
+      <c r="C56" s="193"/>
+      <c r="D56" s="193"/>
+      <c r="E56" s="193"/>
+      <c r="F56" s="193"/>
+      <c r="G56" s="193"/>
+      <c r="H56" s="193"/>
+      <c r="I56" s="193"/>
+      <c r="J56" s="193"/>
+      <c r="K56" s="193"/>
+      <c r="L56" s="193"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="193"/>
+      <c r="O56" s="193"/>
+      <c r="P56" s="193"/>
+      <c r="Q56" s="193"/>
+      <c r="R56" s="193"/>
+      <c r="S56" s="194"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="217"/>
-      <c r="B57" s="240"/>
-      <c r="C57" s="241"/>
-      <c r="D57" s="241"/>
-      <c r="E57" s="241"/>
-      <c r="F57" s="241"/>
-      <c r="G57" s="241"/>
-      <c r="H57" s="241"/>
-      <c r="I57" s="241"/>
-      <c r="J57" s="241"/>
-      <c r="K57" s="241"/>
-      <c r="L57" s="241"/>
-      <c r="M57" s="241"/>
-      <c r="N57" s="241"/>
-      <c r="O57" s="241"/>
-      <c r="P57" s="241"/>
-      <c r="Q57" s="241"/>
-      <c r="R57" s="241"/>
-      <c r="S57" s="242"/>
+      <c r="A57" s="180"/>
+      <c r="B57" s="195"/>
+      <c r="C57" s="196"/>
+      <c r="D57" s="196"/>
+      <c r="E57" s="196"/>
+      <c r="F57" s="196"/>
+      <c r="G57" s="196"/>
+      <c r="H57" s="196"/>
+      <c r="I57" s="196"/>
+      <c r="J57" s="196"/>
+      <c r="K57" s="196"/>
+      <c r="L57" s="196"/>
+      <c r="M57" s="196"/>
+      <c r="N57" s="196"/>
+      <c r="O57" s="196"/>
+      <c r="P57" s="196"/>
+      <c r="Q57" s="196"/>
+      <c r="R57" s="196"/>
+      <c r="S57" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="F40:S40"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="A10:A22"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="S47:S48"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A57"/>
     <mergeCell ref="A8:D9"/>
@@ -5453,32 +5481,6 @@
     <mergeCell ref="G47:G48"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="F40:S40"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="A10:A22"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5508,7 +5510,7 @@
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8352AD92-AE48-443F-8268-FEC6552ABA57}">
           <x14:formula1>
             <xm:f>Parametri!$A:$A</xm:f>
@@ -10756,6 +10758,23 @@
       </c>
     </row>
     <row r="2" spans="1:27">
+      <c r="A2" s="268"/>
+      <c r="B2" s="268"/>
+      <c r="C2" s="268"/>
+      <c r="D2" s="268"/>
+      <c r="E2" s="268"/>
+      <c r="F2" s="268"/>
+      <c r="G2" s="268"/>
+      <c r="H2" s="268"/>
+      <c r="I2" s="268"/>
+      <c r="J2" s="268"/>
+      <c r="K2" s="268"/>
+      <c r="L2" s="268"/>
+      <c r="M2" s="268"/>
+      <c r="N2" s="268"/>
+      <c r="O2" s="268"/>
+      <c r="P2" s="268"/>
+      <c r="Q2" s="268"/>
       <c r="R2" s="167"/>
       <c r="S2" s="164"/>
       <c r="T2" s="145"/>
@@ -10765,13 +10784,33 @@
         <v>0</v>
       </c>
       <c r="W2" t="str">
-        <f>IF(AND(D2=2800, E2=2070, OR(B2=18, B2=18.6, B2=8, B2=10, B2=16)), "PAL",
-  IF(OR(AND(D2=2800, E2=2070, OR(B2=19, B2=19.3)),
-        AND(D2=2800, E2=1220, B2=18),
-        AND(D2=3050, E2=1300, B2=19.3)), "MDF",
-    IF(AND(D2=4100, OR(E2=600, E2=650, E2=920), OR(B2=38, B2=20)), "BLAT",
-      IF(AND(D2=4100, E2=640, OR(B2=9.2, B2=8)), "PS",
-        IF(B2=2.7, "HDF", "DB")))))</f>
+        <f>IF(
+    OR(
+        AND(D2=2800,E2=2070,OR(B2=19,B2=19.3)),
+        AND(D2=2800,E2=1220,B2=18),
+        AND(D2=3050,E2=1300,B2=19.3),
+        RIGHT(A2,6)="MDF 3D"
+    ),
+    "MDF",
+    IF(
+        AND(
+            D2=2800,
+            E2=2070,
+            OR(B2=18,B2=18.6,B2=8,B2=10,B2=16),
+            RIGHT(A2,6)&lt;&gt;"MDF 3D"
+        ),
+        "PAL",
+        IF(
+            AND(D2=4100,OR(E2=600,E2=650,E2=920),OR(B2=38,B2=20)),
+            "BLAT",
+            IF(
+                AND(D2=4100,E2=640,OR(B2=9.2,B2=8)),
+                "PS",
+                IF(B2=2.7,"HDF","DB")
+            )
+        )
+    )
+)</f>
         <v>DB</v>
       </c>
       <c r="X2" t="str">
@@ -10796,6 +10835,23 @@
       </c>
     </row>
     <row r="3" spans="1:27">
+      <c r="A3" s="269"/>
+      <c r="B3" s="269"/>
+      <c r="C3" s="269"/>
+      <c r="D3" s="269"/>
+      <c r="E3" s="269"/>
+      <c r="F3" s="269"/>
+      <c r="G3" s="269"/>
+      <c r="H3" s="269"/>
+      <c r="I3" s="269"/>
+      <c r="J3" s="269"/>
+      <c r="K3" s="269"/>
+      <c r="L3" s="269"/>
+      <c r="M3" s="269"/>
+      <c r="N3" s="269"/>
+      <c r="O3" s="269"/>
+      <c r="P3" s="269"/>
+      <c r="Q3" s="269"/>
       <c r="R3" s="167"/>
       <c r="S3" s="164"/>
       <c r="T3" s="131"/>
@@ -10804,14 +10860,34 @@
         <f t="shared" ref="V3:V34" si="1">IFERROR(IF(W3="DB",Q3/13.5, ROUND(Q3/P3,2)),"")</f>
         <v>0</v>
       </c>
-      <c r="W3" t="str">
-        <f t="shared" ref="W3:W34" si="2">IF(AND(D3=2800, E3=2070, OR(B3=18, B3=18.6, B3=8, B3=10, B3=16)), "PAL",
-  IF(OR(AND(D3=2800, E3=2070, OR(B3=19, B3=19.3)),
-        AND(D3=2800, E3=1220, B3=18),
-        AND(D3=3050, E3=1300, B3=19.3)), "MDF",
-    IF(AND(D3=4100, OR(E3=600, E3=650, E3=920), OR(B3=38, B3=20)), "BLAT",
-      IF(AND(D3=4100, E3=640, OR(B3=9.2, B3=8)), "PS",
-        IF(B3=2.7, "HDF", "DB")))))</f>
+      <c r="W3" s="267" t="str">
+        <f t="shared" ref="W3:W34" si="2">IF(
+    OR(
+        AND(D3=2800,E3=2070,OR(B3=19,B3=19.3)),
+        AND(D3=2800,E3=1220,B3=18),
+        AND(D3=3050,E3=1300,B3=19.3),
+        RIGHT(A3,6)="MDF 3D"
+    ),
+    "MDF",
+    IF(
+        AND(
+            D3=2800,
+            E3=2070,
+            OR(B3=18,B3=18.6,B3=8,B3=10,B3=16),
+            RIGHT(A3,6)&lt;&gt;"MDF 3D"
+        ),
+        "PAL",
+        IF(
+            AND(D3=4100,OR(E3=600,E3=650,E3=920),OR(B3=38,B3=20)),
+            "BLAT",
+            IF(
+                AND(D3=4100,E3=640,OR(B3=9.2,B3=8)),
+                "PS",
+                IF(B3=2.7,"HDF","DB")
+            )
+        )
+    )
+)</f>
         <v>DB</v>
       </c>
       <c r="X3" t="str">
@@ -10836,6 +10912,23 @@
       </c>
     </row>
     <row r="4" spans="1:27">
+      <c r="A4" s="265"/>
+      <c r="B4" s="265"/>
+      <c r="C4" s="265"/>
+      <c r="D4" s="265"/>
+      <c r="E4" s="265"/>
+      <c r="F4" s="265"/>
+      <c r="G4" s="265"/>
+      <c r="H4" s="265"/>
+      <c r="I4" s="265"/>
+      <c r="J4" s="265"/>
+      <c r="K4" s="265"/>
+      <c r="L4" s="265"/>
+      <c r="M4" s="265"/>
+      <c r="N4" s="265"/>
+      <c r="O4" s="265"/>
+      <c r="P4" s="265"/>
+      <c r="Q4" s="265"/>
       <c r="R4" s="167"/>
       <c r="S4" s="164"/>
       <c r="T4" s="145"/>
@@ -10844,7 +10937,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W4" t="str">
+      <c r="W4" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -10866,6 +10959,23 @@
       </c>
     </row>
     <row r="5" spans="1:27">
+      <c r="A5" s="266"/>
+      <c r="B5" s="266"/>
+      <c r="C5" s="266"/>
+      <c r="D5" s="266"/>
+      <c r="E5" s="266"/>
+      <c r="F5" s="266"/>
+      <c r="G5" s="266"/>
+      <c r="H5" s="266"/>
+      <c r="I5" s="266"/>
+      <c r="J5" s="266"/>
+      <c r="K5" s="266"/>
+      <c r="L5" s="266"/>
+      <c r="M5" s="266"/>
+      <c r="N5" s="266"/>
+      <c r="O5" s="266"/>
+      <c r="P5" s="266"/>
+      <c r="Q5" s="266"/>
       <c r="R5" s="167"/>
       <c r="S5" s="164"/>
       <c r="T5" s="145"/>
@@ -10874,7 +10984,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W5" t="str">
+      <c r="W5" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -10896,6 +11006,23 @@
       </c>
     </row>
     <row r="6" spans="1:27">
+      <c r="A6" s="266"/>
+      <c r="B6" s="266"/>
+      <c r="C6" s="266"/>
+      <c r="D6" s="266"/>
+      <c r="E6" s="266"/>
+      <c r="F6" s="266"/>
+      <c r="G6" s="266"/>
+      <c r="H6" s="266"/>
+      <c r="I6" s="266"/>
+      <c r="J6" s="266"/>
+      <c r="K6" s="266"/>
+      <c r="L6" s="266"/>
+      <c r="M6" s="266"/>
+      <c r="N6" s="266"/>
+      <c r="O6" s="266"/>
+      <c r="P6" s="266"/>
+      <c r="Q6" s="266"/>
       <c r="R6" s="167"/>
       <c r="S6" s="164"/>
       <c r="T6" s="145"/>
@@ -10904,7 +11031,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W6" t="str">
+      <c r="W6" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -10926,6 +11053,23 @@
       </c>
     </row>
     <row r="7" spans="1:27">
+      <c r="A7" s="267"/>
+      <c r="B7" s="267"/>
+      <c r="C7" s="267"/>
+      <c r="D7" s="267"/>
+      <c r="E7" s="267"/>
+      <c r="F7" s="267"/>
+      <c r="G7" s="267"/>
+      <c r="H7" s="267"/>
+      <c r="I7" s="267"/>
+      <c r="J7" s="267"/>
+      <c r="K7" s="267"/>
+      <c r="L7" s="267"/>
+      <c r="M7" s="267"/>
+      <c r="N7" s="267"/>
+      <c r="O7" s="267"/>
+      <c r="P7" s="267"/>
+      <c r="Q7" s="267"/>
       <c r="R7" s="167"/>
       <c r="S7" s="164"/>
       <c r="T7" s="131"/>
@@ -10934,7 +11078,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W7" t="str">
+      <c r="W7" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -10956,6 +11100,23 @@
       </c>
     </row>
     <row r="8" spans="1:27">
+      <c r="A8" s="267"/>
+      <c r="B8" s="267"/>
+      <c r="C8" s="267"/>
+      <c r="D8" s="267"/>
+      <c r="E8" s="267"/>
+      <c r="F8" s="267"/>
+      <c r="G8" s="267"/>
+      <c r="H8" s="267"/>
+      <c r="I8" s="267"/>
+      <c r="J8" s="267"/>
+      <c r="K8" s="267"/>
+      <c r="L8" s="267"/>
+      <c r="M8" s="267"/>
+      <c r="N8" s="267"/>
+      <c r="O8" s="267"/>
+      <c r="P8" s="267"/>
+      <c r="Q8" s="267"/>
       <c r="R8" s="167"/>
       <c r="S8" s="164"/>
       <c r="T8" s="145"/>
@@ -10964,7 +11125,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W8" t="str">
+      <c r="W8" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -10986,6 +11147,23 @@
       </c>
     </row>
     <row r="9" spans="1:27">
+      <c r="A9" s="267"/>
+      <c r="B9" s="267"/>
+      <c r="C9" s="267"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
+      <c r="M9" s="267"/>
+      <c r="N9" s="267"/>
+      <c r="O9" s="267"/>
+      <c r="P9" s="267"/>
+      <c r="Q9" s="267"/>
       <c r="R9" s="167"/>
       <c r="S9" s="164"/>
       <c r="T9" s="145"/>
@@ -10994,7 +11172,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W9" t="str">
+      <c r="W9" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11024,7 +11202,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" t="str">
+      <c r="W10" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11054,7 +11232,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" t="str">
+      <c r="W11" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11084,7 +11262,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" t="str">
+      <c r="W12" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11114,7 +11292,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" t="str">
+      <c r="W13" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11144,7 +11322,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W14" t="str">
+      <c r="W14" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11174,7 +11352,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W15" t="str">
+      <c r="W15" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11204,7 +11382,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W16" t="str">
+      <c r="W16" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11234,7 +11412,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W17" t="str">
+      <c r="W17" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11281,7 +11459,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W18" t="str">
+      <c r="W18" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11327,7 +11505,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W19" t="str">
+      <c r="W19" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11373,7 +11551,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W20" t="str">
+      <c r="W20" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11419,7 +11597,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W21" t="str">
+      <c r="W21" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11445,7 +11623,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W22" t="str">
+      <c r="W22" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11471,7 +11649,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W23" t="str">
+      <c r="W23" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11497,7 +11675,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W24" t="str">
+      <c r="W24" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11523,7 +11701,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W25" t="str">
+      <c r="W25" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11545,7 +11723,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W26" t="str">
+      <c r="W26" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11567,7 +11745,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W27" t="str">
+      <c r="W27" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11589,7 +11767,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W28" t="str">
+      <c r="W28" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11611,7 +11789,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W29" t="str">
+      <c r="W29" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11633,7 +11811,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W30" t="str">
+      <c r="W30" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11655,7 +11833,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W31" t="str">
+      <c r="W31" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11677,7 +11855,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W32" t="str">
+      <c r="W32" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11699,7 +11877,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W33" t="str">
+      <c r="W33" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11721,7 +11899,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W34" t="str">
+      <c r="W34" s="267" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11784,81 +11962,51 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2">
-        <v>43</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>75</v>
-      </c>
-      <c r="E2">
-        <v>3.9</v>
-      </c>
       <c r="H2" t="str">
         <f>RIGHT(A2,3)</f>
-        <v>2.0</v>
+        <v/>
       </c>
       <c r="I2">
         <f>ROUNDUP(E2*1.03,0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J23" si="0">CONCATENATE(B2,"/",H2)</f>
-        <v>43/2.0</v>
+        <v>/</v>
       </c>
       <c r="L2" t="str">
         <f>IFERROR(IF(ISNUMBER(VALUE(MID(A2,FIND("-",A2)+1,1))),
 "AGT "&amp;TRIM(MID(A2,FIND("-",A2)+1,FIND("@",SUBSTITUTE(A2,"-","@",LEN(A2)-LEN(SUBSTITUTE(A2,"-",""))))-FIND("-",A2)-1)),
 TRIM(MID(A2,FIND("-",A2)+1,FIND("@",SUBSTITUTE(A2,"-","@",LEN(A2)-LEN(SUBSTITUTE(A2,"-",""))))-FIND("-",A2)-1))),"")</f>
-        <v>W 960 ST7</v>
+        <v/>
       </c>
       <c r="M2" t="str">
         <f>IF(OR(ISNUMBER(FIND(" ST",L2)),ISNUMBER(FIND(" SM",L2)),ISNUMBER(FIND(" PM",L2)),ISNUMBER(FIND(" TM",L2)),ISNUMBER(FIND(" PG",L2)),ISNUMBER(FIND(" PA",L2))),SUBSTITUTE(L2," ","",1),L2)</f>
-        <v>W960 ST7</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3">
-        <v>23</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>75</v>
-      </c>
-      <c r="E3">
-        <v>4.7</v>
-      </c>
       <c r="H3" t="str">
         <f t="shared" ref="H3:H17" si="1">RIGHT(A3,3)</f>
-        <v>2.0</v>
+        <v/>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I23" si="2">ROUNDUP(E3*1.03,0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="0"/>
-        <v>23/2.0</v>
+        <v>/</v>
       </c>
       <c r="L3" t="str">
         <f t="shared" ref="L3:L23" si="3">IFERROR(IF(ISNUMBER(VALUE(MID(A3,FIND("-",A3)+1,1))),
 "AGT "&amp;TRIM(MID(A3,FIND("-",A3)+1,FIND("@",SUBSTITUTE(A3,"-","@",LEN(A3)-LEN(SUBSTITUTE(A3,"-",""))))-FIND("-",A3)-1)),
 TRIM(MID(A3,FIND("-",A3)+1,FIND("@",SUBSTITUTE(A3,"-","@",LEN(A3)-LEN(SUBSTITUTE(A3,"-",""))))-FIND("-",A3)-1))),"")</f>
-        <v>W 960 ST7</v>
+        <v/>
       </c>
       <c r="M3" t="str">
         <f t="shared" ref="M3:M23" si="4">IF(OR(ISNUMBER(FIND(" ST",L3)),ISNUMBER(FIND(" SM",L3)),ISNUMBER(FIND(" PM",L3)),ISNUMBER(FIND(" TM",L3)),ISNUMBER(FIND(" PG",L3)),ISNUMBER(FIND(" PA",L3))),SUBSTITUTE(L3," ","",1),L3)</f>
-        <v>W960 ST7</v>
+        <v/>
       </c>
     </row>
     <row r="4" spans="1:13">

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729C0399-119A-46F6-8779-9CA8349BF9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78D4CE1-C844-4287-BFEE-D0BC6C8F7A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -1297,7 +1297,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="270">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1804,6 +1804,162 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1819,12 +1975,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1843,12 +1993,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1875,12 +2019,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1947,144 +2085,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2094,11 +2094,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2575,33 +2570,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="210" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="235"/>
-      <c r="K1" s="235"/>
-      <c r="L1" s="236"/>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="212"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="219" t="s">
+      <c r="O1" s="199" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="221"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="201"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2620,165 +2615,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="222"/>
-      <c r="P2" s="223"/>
-      <c r="Q2" s="223"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="224"/>
+      <c r="O2" s="202"/>
+      <c r="P2" s="203"/>
+      <c r="Q2" s="203"/>
+      <c r="R2" s="203"/>
+      <c r="S2" s="204"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="242"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="244"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="175"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="177"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="225"/>
+      <c r="K3" s="226"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="237"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="239"/>
+      <c r="O3" s="213"/>
+      <c r="P3" s="195"/>
+      <c r="Q3" s="195"/>
+      <c r="R3" s="195"/>
+      <c r="S3" s="196"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="215"/>
+      <c r="B4" s="256"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="258"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="216"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="218"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="261"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="237"/>
-      <c r="P4" s="238"/>
-      <c r="Q4" s="238"/>
-      <c r="R4" s="238"/>
-      <c r="S4" s="239"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="195"/>
+      <c r="Q4" s="195"/>
+      <c r="R4" s="195"/>
+      <c r="S4" s="196"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="252"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="254"/>
+      <c r="B5" s="183"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="185"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="261"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="239"/>
+      <c r="I5" s="194"/>
+      <c r="J5" s="195"/>
+      <c r="K5" s="196"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="237"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="238"/>
-      <c r="R5" s="238"/>
-      <c r="S5" s="239"/>
+      <c r="O5" s="213"/>
+      <c r="P5" s="195"/>
+      <c r="Q5" s="195"/>
+      <c r="R5" s="195"/>
+      <c r="S5" s="196"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="257"/>
-      <c r="C6" s="258"/>
-      <c r="D6" s="259"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="190"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="260"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="227"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="192"/>
+      <c r="K6" s="193"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="225"/>
-      <c r="P6" s="226"/>
-      <c r="Q6" s="226"/>
-      <c r="R6" s="226"/>
-      <c r="S6" s="227"/>
+      <c r="O6" s="205"/>
+      <c r="P6" s="192"/>
+      <c r="Q6" s="192"/>
+      <c r="R6" s="192"/>
+      <c r="S6" s="193"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="181" t="s">
+      <c r="A8" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="182"/>
-      <c r="C8" s="182"/>
-      <c r="D8" s="183"/>
-      <c r="F8" s="228" t="s">
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="230"/>
+      <c r="F8" s="197" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="229"/>
-      <c r="Q8" s="229"/>
-      <c r="R8" s="229"/>
-      <c r="S8" s="230"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="198"/>
+      <c r="I8" s="198"/>
+      <c r="J8" s="198"/>
+      <c r="K8" s="198"/>
+      <c r="L8" s="198"/>
+      <c r="M8" s="198"/>
+      <c r="N8" s="198"/>
+      <c r="O8" s="198"/>
+      <c r="P8" s="198"/>
+      <c r="Q8" s="198"/>
+      <c r="R8" s="198"/>
+      <c r="S8" s="206"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="184"/>
-      <c r="B9" s="185"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="186"/>
-      <c r="F9" s="209" t="s">
+      <c r="A9" s="231"/>
+      <c r="B9" s="232"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="233"/>
+      <c r="F9" s="252" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="210"/>
-      <c r="H9" s="255" t="s">
+      <c r="G9" s="253"/>
+      <c r="H9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="256"/>
-      <c r="J9" s="207" t="s">
+      <c r="I9" s="187"/>
+      <c r="J9" s="250" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="208"/>
-      <c r="L9" s="250" t="s">
+      <c r="K9" s="251"/>
+      <c r="L9" s="181" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="251"/>
-      <c r="N9" s="187" t="s">
+      <c r="M9" s="182"/>
+      <c r="N9" s="218" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="188"/>
-      <c r="P9" s="202" t="s">
+      <c r="O9" s="219"/>
+      <c r="P9" s="245" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="203"/>
-      <c r="R9" s="187" t="s">
+      <c r="Q9" s="246"/>
+      <c r="R9" s="218" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="188"/>
+      <c r="S9" s="219"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="240" t="s">
+      <c r="A10" s="214" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2835,7 +2830,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="179"/>
+      <c r="A11" s="215"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2932,7 +2927,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="179"/>
+      <c r="A12" s="215"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3029,7 +3024,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="179"/>
+      <c r="A13" s="215"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3126,7 +3121,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="179"/>
+      <c r="A14" s="215"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3204,7 +3199,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="179"/>
+      <c r="A15" s="215"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3282,7 +3277,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="179"/>
+      <c r="A16" s="215"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3360,7 +3355,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="179"/>
+      <c r="A17" s="215"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3438,7 +3433,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="179"/>
+      <c r="A18" s="215"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3516,7 +3511,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="179"/>
+      <c r="A19" s="215"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3594,7 +3589,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="179"/>
+      <c r="A20" s="215"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3672,7 +3667,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="179"/>
+      <c r="A21" s="215"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3750,7 +3745,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="241"/>
+      <c r="A22" s="216"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3884,7 +3879,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="240" t="s">
+      <c r="A24" s="214" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3983,7 +3978,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="179"/>
+      <c r="A25" s="215"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4080,7 +4075,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="179"/>
+      <c r="A26" s="215"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4177,7 +4172,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="179"/>
+      <c r="A27" s="215"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4255,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="180"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4408,7 +4403,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="204" t="s">
+      <c r="A32" s="247" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4487,7 +4482,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="205"/>
+      <c r="A33" s="248"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4564,7 +4559,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="206"/>
+      <c r="A34" s="249"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4662,7 +4657,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="204" t="s">
+      <c r="A36" s="247" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4741,7 +4736,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="205"/>
+      <c r="A37" s="248"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4818,7 +4813,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="206"/>
+      <c r="A38" s="249"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4909,7 +4904,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="240" t="s">
+      <c r="A40" s="214" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4921,25 +4916,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="231" t="s">
+      <c r="F40" s="207" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="232"/>
-      <c r="H40" s="232"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="232"/>
-      <c r="O40" s="232"/>
-      <c r="P40" s="232"/>
-      <c r="Q40" s="232"/>
-      <c r="R40" s="232"/>
-      <c r="S40" s="233"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
+      <c r="N40" s="208"/>
+      <c r="O40" s="208"/>
+      <c r="P40" s="208"/>
+      <c r="Q40" s="208"/>
+      <c r="R40" s="208"/>
+      <c r="S40" s="209"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="179"/>
+      <c r="A41" s="215"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -5002,7 +4997,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="179"/>
+      <c r="A42" s="215"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5027,13 +5022,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="198">
+      <c r="S42" s="175">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="179"/>
+      <c r="A43" s="215"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5045,26 +5040,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="228" t="str">
+      <c r="F43" s="197" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="229"/>
-      <c r="H43" s="229"/>
-      <c r="I43" s="229"/>
-      <c r="J43" s="229"/>
-      <c r="K43" s="229"/>
-      <c r="L43" s="229"/>
-      <c r="M43" s="229"/>
-      <c r="N43" s="229"/>
-      <c r="O43" s="229"/>
-      <c r="P43" s="229"/>
-      <c r="Q43" s="229"/>
-      <c r="R43" s="229"/>
-      <c r="S43" s="245"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="198"/>
+      <c r="N43" s="198"/>
+      <c r="O43" s="198"/>
+      <c r="P43" s="198"/>
+      <c r="Q43" s="198"/>
+      <c r="R43" s="198"/>
+      <c r="S43" s="176"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="179"/>
+      <c r="A44" s="215"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5120,7 +5115,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="179"/>
+      <c r="A45" s="215"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5191,7 +5186,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="179"/>
+      <c r="A46" s="215"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5205,7 +5200,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="179"/>
+      <c r="A47" s="215"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5216,31 +5211,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="198" t="s">
+      <c r="F47" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="211" t="str">
+      <c r="G47" s="254" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="198" t="s">
+      <c r="J47" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="200">
+      <c r="K47" s="243">
         <v>1</v>
       </c>
-      <c r="N47" s="198" t="s">
+      <c r="N47" s="175" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="246"/>
-      <c r="P47" s="247"/>
-      <c r="R47" s="198" t="s">
+      <c r="O47" s="177"/>
+      <c r="P47" s="178"/>
+      <c r="R47" s="175" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="198"/>
+      <c r="S47" s="175"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="180"/>
+      <c r="A48" s="217"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5251,15 +5246,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="199"/>
-      <c r="G48" s="212"/>
-      <c r="J48" s="199"/>
-      <c r="K48" s="201"/>
-      <c r="N48" s="245"/>
-      <c r="O48" s="248"/>
-      <c r="P48" s="249"/>
-      <c r="R48" s="245"/>
-      <c r="S48" s="199"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="255"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="244"/>
+      <c r="N48" s="176"/>
+      <c r="O48" s="179"/>
+      <c r="P48" s="180"/>
+      <c r="R48" s="176"/>
+      <c r="S48" s="223"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5268,187 +5263,193 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="178" t="s">
+      <c r="A50" s="227" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="189"/>
-      <c r="C50" s="190"/>
-      <c r="D50" s="190"/>
-      <c r="E50" s="190"/>
-      <c r="F50" s="190"/>
-      <c r="G50" s="190"/>
-      <c r="H50" s="190"/>
-      <c r="I50" s="190"/>
-      <c r="J50" s="190"/>
-      <c r="K50" s="190"/>
-      <c r="L50" s="190"/>
-      <c r="M50" s="190"/>
-      <c r="N50" s="190"/>
-      <c r="O50" s="190"/>
-      <c r="P50" s="190"/>
-      <c r="Q50" s="190"/>
-      <c r="R50" s="190"/>
-      <c r="S50" s="191"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="235"/>
+      <c r="D50" s="235"/>
+      <c r="E50" s="235"/>
+      <c r="F50" s="235"/>
+      <c r="G50" s="235"/>
+      <c r="H50" s="235"/>
+      <c r="I50" s="235"/>
+      <c r="J50" s="235"/>
+      <c r="K50" s="235"/>
+      <c r="L50" s="235"/>
+      <c r="M50" s="235"/>
+      <c r="N50" s="235"/>
+      <c r="O50" s="235"/>
+      <c r="P50" s="235"/>
+      <c r="Q50" s="235"/>
+      <c r="R50" s="235"/>
+      <c r="S50" s="236"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="179"/>
-      <c r="B51" s="192"/>
-      <c r="C51" s="193"/>
-      <c r="D51" s="193"/>
-      <c r="E51" s="193"/>
-      <c r="F51" s="193"/>
-      <c r="G51" s="193"/>
-      <c r="H51" s="193"/>
-      <c r="I51" s="193"/>
-      <c r="J51" s="193"/>
-      <c r="K51" s="193"/>
-      <c r="L51" s="193"/>
-      <c r="M51" s="193"/>
-      <c r="N51" s="193"/>
-      <c r="O51" s="193"/>
-      <c r="P51" s="193"/>
-      <c r="Q51" s="193"/>
-      <c r="R51" s="193"/>
-      <c r="S51" s="194"/>
+      <c r="A51" s="215"/>
+      <c r="B51" s="237"/>
+      <c r="C51" s="238"/>
+      <c r="D51" s="238"/>
+      <c r="E51" s="238"/>
+      <c r="F51" s="238"/>
+      <c r="G51" s="238"/>
+      <c r="H51" s="238"/>
+      <c r="I51" s="238"/>
+      <c r="J51" s="238"/>
+      <c r="K51" s="238"/>
+      <c r="L51" s="238"/>
+      <c r="M51" s="238"/>
+      <c r="N51" s="238"/>
+      <c r="O51" s="238"/>
+      <c r="P51" s="238"/>
+      <c r="Q51" s="238"/>
+      <c r="R51" s="238"/>
+      <c r="S51" s="239"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="179"/>
-      <c r="B52" s="192"/>
-      <c r="C52" s="193"/>
-      <c r="D52" s="193"/>
-      <c r="E52" s="193"/>
-      <c r="F52" s="193"/>
-      <c r="G52" s="193"/>
-      <c r="H52" s="193"/>
-      <c r="I52" s="193"/>
-      <c r="J52" s="193"/>
-      <c r="K52" s="193"/>
-      <c r="L52" s="193"/>
-      <c r="M52" s="193"/>
-      <c r="N52" s="193"/>
-      <c r="O52" s="193"/>
-      <c r="P52" s="193"/>
-      <c r="Q52" s="193"/>
-      <c r="R52" s="193"/>
-      <c r="S52" s="194"/>
+      <c r="A52" s="215"/>
+      <c r="B52" s="237"/>
+      <c r="C52" s="238"/>
+      <c r="D52" s="238"/>
+      <c r="E52" s="238"/>
+      <c r="F52" s="238"/>
+      <c r="G52" s="238"/>
+      <c r="H52" s="238"/>
+      <c r="I52" s="238"/>
+      <c r="J52" s="238"/>
+      <c r="K52" s="238"/>
+      <c r="L52" s="238"/>
+      <c r="M52" s="238"/>
+      <c r="N52" s="238"/>
+      <c r="O52" s="238"/>
+      <c r="P52" s="238"/>
+      <c r="Q52" s="238"/>
+      <c r="R52" s="238"/>
+      <c r="S52" s="239"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="179"/>
-      <c r="B53" s="192"/>
-      <c r="C53" s="193"/>
-      <c r="D53" s="193"/>
-      <c r="E53" s="193"/>
-      <c r="F53" s="193"/>
-      <c r="G53" s="193"/>
-      <c r="H53" s="193"/>
-      <c r="I53" s="193"/>
-      <c r="J53" s="193"/>
-      <c r="K53" s="193"/>
-      <c r="L53" s="193"/>
-      <c r="M53" s="193"/>
-      <c r="N53" s="193"/>
-      <c r="O53" s="193"/>
-      <c r="P53" s="193"/>
-      <c r="Q53" s="193"/>
-      <c r="R53" s="193"/>
-      <c r="S53" s="194"/>
+      <c r="A53" s="215"/>
+      <c r="B53" s="237"/>
+      <c r="C53" s="238"/>
+      <c r="D53" s="238"/>
+      <c r="E53" s="238"/>
+      <c r="F53" s="238"/>
+      <c r="G53" s="238"/>
+      <c r="H53" s="238"/>
+      <c r="I53" s="238"/>
+      <c r="J53" s="238"/>
+      <c r="K53" s="238"/>
+      <c r="L53" s="238"/>
+      <c r="M53" s="238"/>
+      <c r="N53" s="238"/>
+      <c r="O53" s="238"/>
+      <c r="P53" s="238"/>
+      <c r="Q53" s="238"/>
+      <c r="R53" s="238"/>
+      <c r="S53" s="239"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="179"/>
-      <c r="B54" s="192"/>
-      <c r="C54" s="193"/>
-      <c r="D54" s="193"/>
-      <c r="E54" s="193"/>
-      <c r="F54" s="193"/>
-      <c r="G54" s="193"/>
-      <c r="H54" s="193"/>
-      <c r="I54" s="193"/>
-      <c r="J54" s="193"/>
-      <c r="K54" s="193"/>
-      <c r="L54" s="193"/>
-      <c r="M54" s="193"/>
-      <c r="N54" s="193"/>
-      <c r="O54" s="193"/>
-      <c r="P54" s="193"/>
-      <c r="Q54" s="193"/>
-      <c r="R54" s="193"/>
-      <c r="S54" s="194"/>
+      <c r="A54" s="215"/>
+      <c r="B54" s="237"/>
+      <c r="C54" s="238"/>
+      <c r="D54" s="238"/>
+      <c r="E54" s="238"/>
+      <c r="F54" s="238"/>
+      <c r="G54" s="238"/>
+      <c r="H54" s="238"/>
+      <c r="I54" s="238"/>
+      <c r="J54" s="238"/>
+      <c r="K54" s="238"/>
+      <c r="L54" s="238"/>
+      <c r="M54" s="238"/>
+      <c r="N54" s="238"/>
+      <c r="O54" s="238"/>
+      <c r="P54" s="238"/>
+      <c r="Q54" s="238"/>
+      <c r="R54" s="238"/>
+      <c r="S54" s="239"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="179"/>
-      <c r="B55" s="192"/>
-      <c r="C55" s="193"/>
-      <c r="D55" s="193"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
-      <c r="G55" s="193"/>
-      <c r="H55" s="193"/>
-      <c r="I55" s="193"/>
-      <c r="J55" s="193"/>
-      <c r="K55" s="193"/>
-      <c r="L55" s="193"/>
-      <c r="M55" s="193"/>
-      <c r="N55" s="193"/>
-      <c r="O55" s="193"/>
-      <c r="P55" s="193"/>
-      <c r="Q55" s="193"/>
-      <c r="R55" s="193"/>
-      <c r="S55" s="194"/>
+      <c r="A55" s="215"/>
+      <c r="B55" s="237"/>
+      <c r="C55" s="238"/>
+      <c r="D55" s="238"/>
+      <c r="E55" s="238"/>
+      <c r="F55" s="238"/>
+      <c r="G55" s="238"/>
+      <c r="H55" s="238"/>
+      <c r="I55" s="238"/>
+      <c r="J55" s="238"/>
+      <c r="K55" s="238"/>
+      <c r="L55" s="238"/>
+      <c r="M55" s="238"/>
+      <c r="N55" s="238"/>
+      <c r="O55" s="238"/>
+      <c r="P55" s="238"/>
+      <c r="Q55" s="238"/>
+      <c r="R55" s="238"/>
+      <c r="S55" s="239"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="179"/>
-      <c r="B56" s="192"/>
-      <c r="C56" s="193"/>
-      <c r="D56" s="193"/>
-      <c r="E56" s="193"/>
-      <c r="F56" s="193"/>
-      <c r="G56" s="193"/>
-      <c r="H56" s="193"/>
-      <c r="I56" s="193"/>
-      <c r="J56" s="193"/>
-      <c r="K56" s="193"/>
-      <c r="L56" s="193"/>
-      <c r="M56" s="193"/>
-      <c r="N56" s="193"/>
-      <c r="O56" s="193"/>
-      <c r="P56" s="193"/>
-      <c r="Q56" s="193"/>
-      <c r="R56" s="193"/>
-      <c r="S56" s="194"/>
+      <c r="A56" s="215"/>
+      <c r="B56" s="237"/>
+      <c r="C56" s="238"/>
+      <c r="D56" s="238"/>
+      <c r="E56" s="238"/>
+      <c r="F56" s="238"/>
+      <c r="G56" s="238"/>
+      <c r="H56" s="238"/>
+      <c r="I56" s="238"/>
+      <c r="J56" s="238"/>
+      <c r="K56" s="238"/>
+      <c r="L56" s="238"/>
+      <c r="M56" s="238"/>
+      <c r="N56" s="238"/>
+      <c r="O56" s="238"/>
+      <c r="P56" s="238"/>
+      <c r="Q56" s="238"/>
+      <c r="R56" s="238"/>
+      <c r="S56" s="239"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="180"/>
-      <c r="B57" s="195"/>
-      <c r="C57" s="196"/>
-      <c r="D57" s="196"/>
-      <c r="E57" s="196"/>
-      <c r="F57" s="196"/>
-      <c r="G57" s="196"/>
-      <c r="H57" s="196"/>
-      <c r="I57" s="196"/>
-      <c r="J57" s="196"/>
-      <c r="K57" s="196"/>
-      <c r="L57" s="196"/>
-      <c r="M57" s="196"/>
-      <c r="N57" s="196"/>
-      <c r="O57" s="196"/>
-      <c r="P57" s="196"/>
-      <c r="Q57" s="196"/>
-      <c r="R57" s="196"/>
-      <c r="S57" s="197"/>
+      <c r="A57" s="217"/>
+      <c r="B57" s="240"/>
+      <c r="C57" s="241"/>
+      <c r="D57" s="241"/>
+      <c r="E57" s="241"/>
+      <c r="F57" s="241"/>
+      <c r="G57" s="241"/>
+      <c r="H57" s="241"/>
+      <c r="I57" s="241"/>
+      <c r="J57" s="241"/>
+      <c r="K57" s="241"/>
+      <c r="L57" s="241"/>
+      <c r="M57" s="241"/>
+      <c r="N57" s="241"/>
+      <c r="O57" s="241"/>
+      <c r="P57" s="241"/>
+      <c r="Q57" s="241"/>
+      <c r="R57" s="241"/>
+      <c r="S57" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B50:S57"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="O6:S6"/>
@@ -5465,22 +5466,16 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="R47:R48"/>
     <mergeCell ref="S47:S48"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="B50:S57"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10758,23 +10753,6 @@
       </c>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="268"/>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="268"/>
-      <c r="E2" s="268"/>
-      <c r="F2" s="268"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="268"/>
-      <c r="I2" s="268"/>
-      <c r="J2" s="268"/>
-      <c r="K2" s="268"/>
-      <c r="L2" s="268"/>
-      <c r="M2" s="268"/>
-      <c r="N2" s="268"/>
-      <c r="O2" s="268"/>
-      <c r="P2" s="268"/>
-      <c r="Q2" s="268"/>
       <c r="R2" s="167"/>
       <c r="S2" s="164"/>
       <c r="T2" s="145"/>
@@ -10789,6 +10767,8 @@
         AND(D2=2800,E2=2070,OR(B2=19,B2=19.3)),
         AND(D2=2800,E2=1220,B2=18),
         AND(D2=3050,E2=1300,B2=19.3),
+        AND(D2=2800, E2=1300,B2=17.5),
+        AND(D2=2800, E2=1300,B2=19),
         RIGHT(A2,6)="MDF 3D"
     ),
     "MDF",
@@ -10835,23 +10815,6 @@
       </c>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="269"/>
-      <c r="B3" s="269"/>
-      <c r="C3" s="269"/>
-      <c r="D3" s="269"/>
-      <c r="E3" s="269"/>
-      <c r="F3" s="269"/>
-      <c r="G3" s="269"/>
-      <c r="H3" s="269"/>
-      <c r="I3" s="269"/>
-      <c r="J3" s="269"/>
-      <c r="K3" s="269"/>
-      <c r="L3" s="269"/>
-      <c r="M3" s="269"/>
-      <c r="N3" s="269"/>
-      <c r="O3" s="269"/>
-      <c r="P3" s="269"/>
-      <c r="Q3" s="269"/>
       <c r="R3" s="167"/>
       <c r="S3" s="164"/>
       <c r="T3" s="131"/>
@@ -10860,12 +10823,14 @@
         <f t="shared" ref="V3:V34" si="1">IFERROR(IF(W3="DB",Q3/13.5, ROUND(Q3/P3,2)),"")</f>
         <v>0</v>
       </c>
-      <c r="W3" s="267" t="str">
+      <c r="W3" t="str">
         <f t="shared" ref="W3:W34" si="2">IF(
     OR(
         AND(D3=2800,E3=2070,OR(B3=19,B3=19.3)),
         AND(D3=2800,E3=1220,B3=18),
         AND(D3=3050,E3=1300,B3=19.3),
+        AND(D3=2800, E3=1300,B3=17.5),
+        AND(D3=2800, E3=1300,B3=19),
         RIGHT(A3,6)="MDF 3D"
     ),
     "MDF",
@@ -10912,23 +10877,6 @@
       </c>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="265"/>
-      <c r="B4" s="265"/>
-      <c r="C4" s="265"/>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
-      <c r="L4" s="265"/>
-      <c r="M4" s="265"/>
-      <c r="N4" s="265"/>
-      <c r="O4" s="265"/>
-      <c r="P4" s="265"/>
-      <c r="Q4" s="265"/>
       <c r="R4" s="167"/>
       <c r="S4" s="164"/>
       <c r="T4" s="145"/>
@@ -10937,7 +10885,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W4" s="267" t="str">
+      <c r="W4" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -10959,23 +10907,6 @@
       </c>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="266"/>
-      <c r="B5" s="266"/>
-      <c r="C5" s="266"/>
-      <c r="D5" s="266"/>
-      <c r="E5" s="266"/>
-      <c r="F5" s="266"/>
-      <c r="G5" s="266"/>
-      <c r="H5" s="266"/>
-      <c r="I5" s="266"/>
-      <c r="J5" s="266"/>
-      <c r="K5" s="266"/>
-      <c r="L5" s="266"/>
-      <c r="M5" s="266"/>
-      <c r="N5" s="266"/>
-      <c r="O5" s="266"/>
-      <c r="P5" s="266"/>
-      <c r="Q5" s="266"/>
       <c r="R5" s="167"/>
       <c r="S5" s="164"/>
       <c r="T5" s="145"/>
@@ -10984,7 +10915,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W5" s="267" t="str">
+      <c r="W5" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11006,23 +10937,6 @@
       </c>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="266"/>
-      <c r="B6" s="266"/>
-      <c r="C6" s="266"/>
-      <c r="D6" s="266"/>
-      <c r="E6" s="266"/>
-      <c r="F6" s="266"/>
-      <c r="G6" s="266"/>
-      <c r="H6" s="266"/>
-      <c r="I6" s="266"/>
-      <c r="J6" s="266"/>
-      <c r="K6" s="266"/>
-      <c r="L6" s="266"/>
-      <c r="M6" s="266"/>
-      <c r="N6" s="266"/>
-      <c r="O6" s="266"/>
-      <c r="P6" s="266"/>
-      <c r="Q6" s="266"/>
       <c r="R6" s="167"/>
       <c r="S6" s="164"/>
       <c r="T6" s="145"/>
@@ -11031,7 +10945,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W6" s="267" t="str">
+      <c r="W6" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11053,23 +10967,6 @@
       </c>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="267"/>
-      <c r="B7" s="267"/>
-      <c r="C7" s="267"/>
-      <c r="D7" s="267"/>
-      <c r="E7" s="267"/>
-      <c r="F7" s="267"/>
-      <c r="G7" s="267"/>
-      <c r="H7" s="267"/>
-      <c r="I7" s="267"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="267"/>
-      <c r="M7" s="267"/>
-      <c r="N7" s="267"/>
-      <c r="O7" s="267"/>
-      <c r="P7" s="267"/>
-      <c r="Q7" s="267"/>
       <c r="R7" s="167"/>
       <c r="S7" s="164"/>
       <c r="T7" s="131"/>
@@ -11078,7 +10975,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W7" s="267" t="str">
+      <c r="W7" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11100,23 +10997,6 @@
       </c>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="267"/>
-      <c r="B8" s="267"/>
-      <c r="C8" s="267"/>
-      <c r="D8" s="267"/>
-      <c r="E8" s="267"/>
-      <c r="F8" s="267"/>
-      <c r="G8" s="267"/>
-      <c r="H8" s="267"/>
-      <c r="I8" s="267"/>
-      <c r="J8" s="267"/>
-      <c r="K8" s="267"/>
-      <c r="L8" s="267"/>
-      <c r="M8" s="267"/>
-      <c r="N8" s="267"/>
-      <c r="O8" s="267"/>
-      <c r="P8" s="267"/>
-      <c r="Q8" s="267"/>
       <c r="R8" s="167"/>
       <c r="S8" s="164"/>
       <c r="T8" s="145"/>
@@ -11125,7 +11005,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W8" s="267" t="str">
+      <c r="W8" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11147,23 +11027,6 @@
       </c>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="267"/>
-      <c r="B9" s="267"/>
-      <c r="C9" s="267"/>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
-      <c r="M9" s="267"/>
-      <c r="N9" s="267"/>
-      <c r="O9" s="267"/>
-      <c r="P9" s="267"/>
-      <c r="Q9" s="267"/>
       <c r="R9" s="167"/>
       <c r="S9" s="164"/>
       <c r="T9" s="145"/>
@@ -11172,7 +11035,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W9" s="267" t="str">
+      <c r="W9" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11202,7 +11065,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W10" s="267" t="str">
+      <c r="W10" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11232,7 +11095,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="267" t="str">
+      <c r="W11" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11262,7 +11125,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W12" s="267" t="str">
+      <c r="W12" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11292,7 +11155,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W13" s="267" t="str">
+      <c r="W13" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11322,7 +11185,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W14" s="267" t="str">
+      <c r="W14" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11352,7 +11215,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W15" s="267" t="str">
+      <c r="W15" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11382,7 +11245,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W16" s="267" t="str">
+      <c r="W16" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11412,7 +11275,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W17" s="267" t="str">
+      <c r="W17" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11459,7 +11322,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W18" s="267" t="str">
+      <c r="W18" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11505,7 +11368,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W19" s="267" t="str">
+      <c r="W19" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11551,7 +11414,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W20" s="267" t="str">
+      <c r="W20" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11597,7 +11460,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W21" s="267" t="str">
+      <c r="W21" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11623,7 +11486,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W22" s="267" t="str">
+      <c r="W22" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11649,7 +11512,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W23" s="267" t="str">
+      <c r="W23" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11675,7 +11538,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W24" s="267" t="str">
+      <c r="W24" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11701,7 +11564,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W25" s="267" t="str">
+      <c r="W25" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11723,7 +11586,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W26" s="267" t="str">
+      <c r="W26" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11745,7 +11608,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W27" s="267" t="str">
+      <c r="W27" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11767,7 +11630,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W28" s="267" t="str">
+      <c r="W28" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11789,7 +11652,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W29" s="267" t="str">
+      <c r="W29" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11811,7 +11674,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W30" s="267" t="str">
+      <c r="W30" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11833,7 +11696,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W31" s="267" t="str">
+      <c r="W31" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11855,7 +11718,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W32" s="267" t="str">
+      <c r="W32" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11877,7 +11740,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W33" s="267" t="str">
+      <c r="W33" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>
@@ -11899,7 +11762,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W34" s="267" t="str">
+      <c r="W34" t="str">
         <f t="shared" si="2"/>
         <v>DB</v>
       </c>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78D4CE1-C844-4287-BFEE-D0BC6C8F7A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7610AB4-4EDF-44DA-BDE3-D1793F947693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -3011,7 +3011,7 @@
         <v/>
       </c>
       <c r="Q12" s="140" t="str">
-        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(P12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(P12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P12,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R12" s="70" t="str">
@@ -3019,7 +3019,7 @@
         <v/>
       </c>
       <c r="S12" s="37" t="str">
-        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(R12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F12&lt;&gt;"",COUNTIF($F$11:F11,F12)&gt;0),"",IFERROR(IF(AND(R12&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R12,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
         <v/>
       </c>
       <c r="Q13" s="140" t="str">
-        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(P13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(P13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P13,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R13" s="70" t="str">
@@ -3116,7 +3116,7 @@
         <v/>
       </c>
       <c r="S13" s="37" t="str">
-        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(R13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R13,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R13,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F13&lt;&gt;"",COUNTIF($F$11:F12,F13)&gt;0),"",IFERROR(IF(AND(R13&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R13,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R13,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
         <v/>
       </c>
       <c r="Q14" s="140" t="str">
-        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(P14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(P14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P14,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R14" s="70" t="str">
@@ -3194,7 +3194,7 @@
         <v/>
       </c>
       <c r="S14" s="37" t="str">
-        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(R14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R14,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R14,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F14&lt;&gt;"",COUNTIF($F$11:F13,F14)&gt;0),"",IFERROR(IF(AND(R14&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R14,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R14,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
         <v/>
       </c>
       <c r="Q15" s="140" t="str">
-        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(P15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(P15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P15,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R15" s="70" t="str">
@@ -3272,7 +3272,7 @@
         <v/>
       </c>
       <c r="S15" s="37" t="str">
-        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(R15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R15,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R15,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F15&lt;&gt;"",COUNTIF($F$11:F14,F15)&gt;0),"",IFERROR(IF(AND(R15&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R15,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R15,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
         <v/>
       </c>
       <c r="Q16" s="140" t="str">
-        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(P16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(P16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P16,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R16" s="70" t="str">
@@ -3350,7 +3350,7 @@
         <v/>
       </c>
       <c r="S16" s="37" t="str">
-        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(R16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R16,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R16,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F16&lt;&gt;"",COUNTIF($F$11:F15,F16)&gt;0),"",IFERROR(IF(AND(R16&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R16,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R16,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
         <v/>
       </c>
       <c r="Q17" s="140" t="str">
-        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(P17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(P17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P17,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R17" s="70" t="str">
@@ -3428,7 +3428,7 @@
         <v/>
       </c>
       <c r="S17" s="37" t="str">
-        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(R17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R17,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R17,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F17&lt;&gt;"",COUNTIF($F$11:F16,F17)&gt;0),"",IFERROR(IF(AND(R17&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R17,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R17,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
         <v/>
       </c>
       <c r="Q18" s="140" t="str">
-        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(P18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(P18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P18,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R18" s="70" t="str">
@@ -3506,7 +3506,7 @@
         <v/>
       </c>
       <c r="S18" s="37" t="str">
-        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(R18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R18,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R18,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F18&lt;&gt;"",COUNTIF($F$11:F17,F18)&gt;0),"",IFERROR(IF(AND(R18&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R18,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R18,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
         <v/>
       </c>
       <c r="Q19" s="140" t="str">
-        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(P19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(P19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P19,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R19" s="70" t="str">
@@ -3584,7 +3584,7 @@
         <v/>
       </c>
       <c r="S19" s="37" t="str">
-        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(R19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R19,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R19,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F19&lt;&gt;"",COUNTIF($F$11:F18,F19)&gt;0),"",IFERROR(IF(AND(R19&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R19,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R19,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v/>
       </c>
       <c r="Q20" s="140" t="str">
-        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(P20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(P20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P20,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R20" s="70" t="str">
@@ -3662,7 +3662,7 @@
         <v/>
       </c>
       <c r="S20" s="37" t="str">
-        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(R20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R20,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R20,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F20&lt;&gt;"",COUNTIF($F$11:F19,F20)&gt;0),"",IFERROR(IF(AND(R20&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R20,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R20,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
         <v/>
       </c>
       <c r="Q21" s="140" t="str">
-        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(P21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(P21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P21,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R21" s="70" t="str">
@@ -3740,7 +3740,7 @@
         <v/>
       </c>
       <c r="S21" s="37" t="str">
-        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(R21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R21,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R21,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F21&lt;&gt;"",COUNTIF($F$11:F20,F21)&gt;0),"",IFERROR(IF(AND(R21&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R21,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R21,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
         <v/>
       </c>
       <c r="Q22" s="140" t="str">
-        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(P22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(P22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P22,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R22" s="70" t="str">
@@ -3818,7 +3818,7 @@
         <v/>
       </c>
       <c r="S22" s="37" t="str">
-        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(R22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R22,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R22,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F22&lt;&gt;"",COUNTIF($F$11:F21,F22)&gt;0),"",IFERROR(IF(AND(R22&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R22,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R22,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
         <v/>
       </c>
       <c r="S23" s="37" t="str">
-        <f>IF(AND(F23&lt;&gt;"",COUNTIF($F$11:F22,F23)&gt;0),"",IFERROR(IF(AND(R23&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R23,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R23,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F23&lt;&gt;"",COUNTIF($F$11:F22,F23)&gt;0),"",IFERROR(IF(AND(R23&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R23,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R23,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
         <v/>
       </c>
       <c r="Q24" s="171" t="str">
-        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(P24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(P24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P24,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R24" s="57" t="str">
@@ -3973,7 +3973,7 @@
         <v/>
       </c>
       <c r="S24" s="171" t="str">
-        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(R24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R24,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R24,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F24&lt;&gt;"",COUNTIF($F$11:F23,F24)&gt;0),"",IFERROR(IF(AND(R24&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R24,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R24,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
         <v/>
       </c>
       <c r="Q25" s="172" t="str">
-        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(P25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(P25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P25,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R25" s="70" t="str">
@@ -4070,7 +4070,7 @@
         <v/>
       </c>
       <c r="S25" s="172" t="str">
-        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(R25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R25,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R25,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F25&lt;&gt;"",COUNTIF($F$11:F24,F25)&gt;0),"",IFERROR(IF(AND(R25&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R25,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R25,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
         <v/>
       </c>
       <c r="Q26" s="172" t="str">
-        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(P26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(P26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P26,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R26" s="70" t="str">
@@ -4167,7 +4167,7 @@
         <v/>
       </c>
       <c r="S26" s="172" t="str">
-        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(R26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R26,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R26,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F26&lt;&gt;"",COUNTIF($F$11:F25,F26)&gt;0),"",IFERROR(IF(AND(R26&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R26,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R26,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
         <v/>
       </c>
       <c r="Q27" s="172" t="str">
-        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(P27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(P27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P27,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R27" s="70" t="str">
@@ -4245,7 +4245,7 @@
         <v/>
       </c>
       <c r="S27" s="172" t="str">
-        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(R27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R27,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R27,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F27&lt;&gt;"",COUNTIF($F$11:F26,F27)&gt;0),"",IFERROR(IF(AND(R27&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R27,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R27,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
         <v/>
       </c>
       <c r="Q28" s="31" t="str">
-        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(P28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(P28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"43/1.5")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,P28,Cant!$J$2:$J$99,"43/1.5"),""),""))</f>
         <v/>
       </c>
       <c r="R28" s="71" t="str">
@@ -4323,7 +4323,7 @@
         <v/>
       </c>
       <c r="S28" s="31" t="str">
-        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(R28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R28,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R28,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F28&lt;&gt;"",COUNTIF($F$11:F27,F28)&gt;0),"",IFERROR(IF(AND(R28&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R28,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R28,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
         <v/>
       </c>
       <c r="S32" s="171" t="str">
-        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(AND(R32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R32,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R32,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F32&lt;&gt;"",COUNTIF($F$11:F31,F32)&gt;0),"",IFERROR(IF(AND(R32&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R32,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R32,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -4554,7 +4554,7 @@
         <v/>
       </c>
       <c r="S33" s="172" t="str">
-        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(AND(R33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R33,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R33,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F33&lt;&gt;"",COUNTIF($F$11:F32,F33)&gt;0),"",IFERROR(IF(AND(R33&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R33,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R33,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
         <v/>
       </c>
       <c r="S34" s="30" t="str">
-        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(AND(R34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R34,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R34,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F34&lt;&gt;"",COUNTIF($F$11:F33,F34)&gt;0),"",IFERROR(IF(AND(R34&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R34,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R34,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -4731,7 +4731,7 @@
         <v/>
       </c>
       <c r="S36" s="171" t="str">
-        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(AND(R36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R36,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R36,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F36&lt;&gt;"",COUNTIF($F$11:F35,F36)&gt;0),"",IFERROR(IF(AND(R36&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R36,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R36,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
         <v/>
       </c>
       <c r="S37" s="172" t="str">
-        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(AND(R37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R37,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R37,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F37&lt;&gt;"",COUNTIF($F$11:F36,F37)&gt;0),"",IFERROR(IF(AND(R37&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R37,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R37,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
         <v/>
       </c>
       <c r="S38" s="172" t="str">
-        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(AND(R38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R38,Cant!$J$2:$J$99,"43/1.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R38,Cant!$J$2:$J$99,"43/1.0"),""),""))</f>
+        <f>IF(AND(F38&lt;&gt;"",COUNTIF($F$11:F37,F38)&gt;0),"",IFERROR(IF(AND(R38&lt;&gt;"",SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R38,Cant!$J$2:$J$99,"43/2.0")&gt;0),SUMIFS(Cant!$I$2:$I$99,Cant!$M$2:$M$99,R38,Cant!$J$2:$J$99,"43/2.0"),""),""))</f>
         <v/>
       </c>
     </row>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7610AB4-4EDF-44DA-BDE3-D1793F947693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46699E1F-26F1-4BDD-A64B-6881C6F92CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1804,8 +1804,229 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1861,229 +2082,8 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2570,33 +2570,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="234" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="212"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
+      <c r="L1" s="236"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="199" t="s">
+      <c r="O1" s="219" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="201"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="221"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2615,165 +2615,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="202"/>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="203"/>
-      <c r="R2" s="203"/>
-      <c r="S2" s="204"/>
+      <c r="O2" s="222"/>
+      <c r="P2" s="223"/>
+      <c r="Q2" s="223"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="224"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="220"/>
-      <c r="C3" s="221"/>
-      <c r="D3" s="222"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="244"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="225"/>
-      <c r="K3" s="226"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="177"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="195"/>
-      <c r="Q3" s="195"/>
-      <c r="R3" s="195"/>
-      <c r="S3" s="196"/>
+      <c r="O3" s="237"/>
+      <c r="P3" s="238"/>
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="239"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="256"/>
-      <c r="C4" s="257"/>
-      <c r="D4" s="258"/>
+      <c r="B4" s="213"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="215"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="259"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="261"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="218"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="195"/>
-      <c r="Q4" s="195"/>
-      <c r="R4" s="195"/>
-      <c r="S4" s="196"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="238"/>
+      <c r="Q4" s="238"/>
+      <c r="R4" s="238"/>
+      <c r="S4" s="239"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="185"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="254"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="194"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="196"/>
+      <c r="I5" s="261"/>
+      <c r="J5" s="238"/>
+      <c r="K5" s="239"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="213"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="195"/>
-      <c r="R5" s="195"/>
-      <c r="S5" s="196"/>
+      <c r="O5" s="237"/>
+      <c r="P5" s="238"/>
+      <c r="Q5" s="238"/>
+      <c r="R5" s="238"/>
+      <c r="S5" s="239"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="188"/>
-      <c r="C6" s="189"/>
-      <c r="D6" s="190"/>
+      <c r="B6" s="257"/>
+      <c r="C6" s="258"/>
+      <c r="D6" s="259"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="191"/>
-      <c r="J6" s="192"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="260"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="227"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="205"/>
-      <c r="P6" s="192"/>
-      <c r="Q6" s="192"/>
-      <c r="R6" s="192"/>
-      <c r="S6" s="193"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="226"/>
+      <c r="Q6" s="226"/>
+      <c r="R6" s="226"/>
+      <c r="S6" s="227"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="228" t="s">
+      <c r="A8" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="230"/>
-      <c r="F8" s="197" t="s">
+      <c r="B8" s="182"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="183"/>
+      <c r="F8" s="228" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="198"/>
-      <c r="H8" s="198"/>
-      <c r="I8" s="198"/>
-      <c r="J8" s="198"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="198"/>
-      <c r="O8" s="198"/>
-      <c r="P8" s="198"/>
-      <c r="Q8" s="198"/>
-      <c r="R8" s="198"/>
-      <c r="S8" s="206"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="229"/>
+      <c r="P8" s="229"/>
+      <c r="Q8" s="229"/>
+      <c r="R8" s="229"/>
+      <c r="S8" s="230"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="231"/>
-      <c r="B9" s="232"/>
-      <c r="C9" s="232"/>
-      <c r="D9" s="233"/>
-      <c r="F9" s="252" t="s">
+      <c r="A9" s="184"/>
+      <c r="B9" s="185"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="186"/>
+      <c r="F9" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="253"/>
-      <c r="H9" s="186" t="s">
+      <c r="G9" s="210"/>
+      <c r="H9" s="255" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="187"/>
-      <c r="J9" s="250" t="s">
+      <c r="I9" s="256"/>
+      <c r="J9" s="207" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="251"/>
-      <c r="L9" s="181" t="s">
+      <c r="K9" s="208"/>
+      <c r="L9" s="250" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="182"/>
-      <c r="N9" s="218" t="s">
+      <c r="M9" s="251"/>
+      <c r="N9" s="187" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="219"/>
-      <c r="P9" s="245" t="s">
+      <c r="O9" s="188"/>
+      <c r="P9" s="202" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="218" t="s">
+      <c r="Q9" s="203"/>
+      <c r="R9" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="219"/>
+      <c r="S9" s="188"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="214" t="s">
+      <c r="A10" s="240" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2830,7 +2830,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="215"/>
+      <c r="A11" s="179"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2927,7 +2927,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="215"/>
+      <c r="A12" s="179"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3024,7 +3024,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="215"/>
+      <c r="A13" s="179"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3121,7 +3121,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="215"/>
+      <c r="A14" s="179"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3199,7 +3199,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="215"/>
+      <c r="A15" s="179"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3277,7 +3277,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="215"/>
+      <c r="A16" s="179"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3355,7 +3355,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="215"/>
+      <c r="A17" s="179"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3433,7 +3433,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="215"/>
+      <c r="A18" s="179"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="215"/>
+      <c r="A19" s="179"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3589,7 +3589,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="215"/>
+      <c r="A20" s="179"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3667,7 +3667,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="215"/>
+      <c r="A21" s="179"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="216"/>
+      <c r="A22" s="241"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3879,7 +3879,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="214" t="s">
+      <c r="A24" s="240" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3978,7 +3978,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="215"/>
+      <c r="A25" s="179"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4075,7 +4075,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="215"/>
+      <c r="A26" s="179"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4172,7 +4172,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="215"/>
+      <c r="A27" s="179"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="217"/>
+      <c r="A28" s="180"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4403,7 +4403,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="247" t="s">
+      <c r="A32" s="204" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4482,7 +4482,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="248"/>
+      <c r="A33" s="205"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4559,7 +4559,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="249"/>
+      <c r="A34" s="206"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4657,7 +4657,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="247" t="s">
+      <c r="A36" s="204" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4736,7 +4736,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="248"/>
+      <c r="A37" s="205"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4813,7 +4813,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="249"/>
+      <c r="A38" s="206"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4904,7 +4904,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="214" t="s">
+      <c r="A40" s="240" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4916,25 +4916,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="207" t="s">
+      <c r="F40" s="231" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="208"/>
-      <c r="L40" s="208"/>
-      <c r="M40" s="208"/>
-      <c r="N40" s="208"/>
-      <c r="O40" s="208"/>
-      <c r="P40" s="208"/>
-      <c r="Q40" s="208"/>
-      <c r="R40" s="208"/>
-      <c r="S40" s="209"/>
+      <c r="G40" s="232"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="232"/>
+      <c r="O40" s="232"/>
+      <c r="P40" s="232"/>
+      <c r="Q40" s="232"/>
+      <c r="R40" s="232"/>
+      <c r="S40" s="233"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="215"/>
+      <c r="A41" s="179"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -4997,7 +4997,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="215"/>
+      <c r="A42" s="179"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5022,13 +5022,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="175">
+      <c r="S42" s="198">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="215"/>
+      <c r="A43" s="179"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5040,26 +5040,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="197" t="str">
+      <c r="F43" s="228" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="198"/>
-      <c r="H43" s="198"/>
-      <c r="I43" s="198"/>
-      <c r="J43" s="198"/>
-      <c r="K43" s="198"/>
-      <c r="L43" s="198"/>
-      <c r="M43" s="198"/>
-      <c r="N43" s="198"/>
-      <c r="O43" s="198"/>
-      <c r="P43" s="198"/>
-      <c r="Q43" s="198"/>
-      <c r="R43" s="198"/>
-      <c r="S43" s="176"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="229"/>
+      <c r="J43" s="229"/>
+      <c r="K43" s="229"/>
+      <c r="L43" s="229"/>
+      <c r="M43" s="229"/>
+      <c r="N43" s="229"/>
+      <c r="O43" s="229"/>
+      <c r="P43" s="229"/>
+      <c r="Q43" s="229"/>
+      <c r="R43" s="229"/>
+      <c r="S43" s="245"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="215"/>
+      <c r="A44" s="179"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5115,7 +5115,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="215"/>
+      <c r="A45" s="179"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5186,7 +5186,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="215"/>
+      <c r="A46" s="179"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5200,7 +5200,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="215"/>
+      <c r="A47" s="179"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5211,31 +5211,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="175" t="s">
+      <c r="F47" s="198" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="254" t="str">
+      <c r="G47" s="211" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="175" t="s">
+      <c r="J47" s="198" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="243">
+      <c r="K47" s="200">
         <v>1</v>
       </c>
-      <c r="N47" s="175" t="s">
+      <c r="N47" s="198" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="177"/>
-      <c r="P47" s="178"/>
-      <c r="R47" s="175" t="s">
+      <c r="O47" s="246"/>
+      <c r="P47" s="247"/>
+      <c r="R47" s="198" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="175"/>
+      <c r="S47" s="198"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="217"/>
+      <c r="A48" s="180"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5246,15 +5246,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="223"/>
-      <c r="G48" s="255"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="244"/>
-      <c r="N48" s="176"/>
-      <c r="O48" s="179"/>
-      <c r="P48" s="180"/>
-      <c r="R48" s="176"/>
-      <c r="S48" s="223"/>
+      <c r="F48" s="199"/>
+      <c r="G48" s="212"/>
+      <c r="J48" s="199"/>
+      <c r="K48" s="201"/>
+      <c r="N48" s="245"/>
+      <c r="O48" s="248"/>
+      <c r="P48" s="249"/>
+      <c r="R48" s="245"/>
+      <c r="S48" s="199"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5263,177 +5263,203 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="227" t="s">
+      <c r="A50" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="234"/>
-      <c r="C50" s="235"/>
-      <c r="D50" s="235"/>
-      <c r="E50" s="235"/>
-      <c r="F50" s="235"/>
-      <c r="G50" s="235"/>
-      <c r="H50" s="235"/>
-      <c r="I50" s="235"/>
-      <c r="J50" s="235"/>
-      <c r="K50" s="235"/>
-      <c r="L50" s="235"/>
-      <c r="M50" s="235"/>
-      <c r="N50" s="235"/>
-      <c r="O50" s="235"/>
-      <c r="P50" s="235"/>
-      <c r="Q50" s="235"/>
-      <c r="R50" s="235"/>
-      <c r="S50" s="236"/>
+      <c r="B50" s="189"/>
+      <c r="C50" s="190"/>
+      <c r="D50" s="190"/>
+      <c r="E50" s="190"/>
+      <c r="F50" s="190"/>
+      <c r="G50" s="190"/>
+      <c r="H50" s="190"/>
+      <c r="I50" s="190"/>
+      <c r="J50" s="190"/>
+      <c r="K50" s="190"/>
+      <c r="L50" s="190"/>
+      <c r="M50" s="190"/>
+      <c r="N50" s="190"/>
+      <c r="O50" s="190"/>
+      <c r="P50" s="190"/>
+      <c r="Q50" s="190"/>
+      <c r="R50" s="190"/>
+      <c r="S50" s="191"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="215"/>
-      <c r="B51" s="237"/>
-      <c r="C51" s="238"/>
-      <c r="D51" s="238"/>
-      <c r="E51" s="238"/>
-      <c r="F51" s="238"/>
-      <c r="G51" s="238"/>
-      <c r="H51" s="238"/>
-      <c r="I51" s="238"/>
-      <c r="J51" s="238"/>
-      <c r="K51" s="238"/>
-      <c r="L51" s="238"/>
-      <c r="M51" s="238"/>
-      <c r="N51" s="238"/>
-      <c r="O51" s="238"/>
-      <c r="P51" s="238"/>
-      <c r="Q51" s="238"/>
-      <c r="R51" s="238"/>
-      <c r="S51" s="239"/>
+      <c r="A51" s="179"/>
+      <c r="B51" s="192"/>
+      <c r="C51" s="193"/>
+      <c r="D51" s="193"/>
+      <c r="E51" s="193"/>
+      <c r="F51" s="193"/>
+      <c r="G51" s="193"/>
+      <c r="H51" s="193"/>
+      <c r="I51" s="193"/>
+      <c r="J51" s="193"/>
+      <c r="K51" s="193"/>
+      <c r="L51" s="193"/>
+      <c r="M51" s="193"/>
+      <c r="N51" s="193"/>
+      <c r="O51" s="193"/>
+      <c r="P51" s="193"/>
+      <c r="Q51" s="193"/>
+      <c r="R51" s="193"/>
+      <c r="S51" s="194"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="215"/>
-      <c r="B52" s="237"/>
-      <c r="C52" s="238"/>
-      <c r="D52" s="238"/>
-      <c r="E52" s="238"/>
-      <c r="F52" s="238"/>
-      <c r="G52" s="238"/>
-      <c r="H52" s="238"/>
-      <c r="I52" s="238"/>
-      <c r="J52" s="238"/>
-      <c r="K52" s="238"/>
-      <c r="L52" s="238"/>
-      <c r="M52" s="238"/>
-      <c r="N52" s="238"/>
-      <c r="O52" s="238"/>
-      <c r="P52" s="238"/>
-      <c r="Q52" s="238"/>
-      <c r="R52" s="238"/>
-      <c r="S52" s="239"/>
+      <c r="A52" s="179"/>
+      <c r="B52" s="192"/>
+      <c r="C52" s="193"/>
+      <c r="D52" s="193"/>
+      <c r="E52" s="193"/>
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="193"/>
+      <c r="J52" s="193"/>
+      <c r="K52" s="193"/>
+      <c r="L52" s="193"/>
+      <c r="M52" s="193"/>
+      <c r="N52" s="193"/>
+      <c r="O52" s="193"/>
+      <c r="P52" s="193"/>
+      <c r="Q52" s="193"/>
+      <c r="R52" s="193"/>
+      <c r="S52" s="194"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="215"/>
-      <c r="B53" s="237"/>
-      <c r="C53" s="238"/>
-      <c r="D53" s="238"/>
-      <c r="E53" s="238"/>
-      <c r="F53" s="238"/>
-      <c r="G53" s="238"/>
-      <c r="H53" s="238"/>
-      <c r="I53" s="238"/>
-      <c r="J53" s="238"/>
-      <c r="K53" s="238"/>
-      <c r="L53" s="238"/>
-      <c r="M53" s="238"/>
-      <c r="N53" s="238"/>
-      <c r="O53" s="238"/>
-      <c r="P53" s="238"/>
-      <c r="Q53" s="238"/>
-      <c r="R53" s="238"/>
-      <c r="S53" s="239"/>
+      <c r="A53" s="179"/>
+      <c r="B53" s="192"/>
+      <c r="C53" s="193"/>
+      <c r="D53" s="193"/>
+      <c r="E53" s="193"/>
+      <c r="F53" s="193"/>
+      <c r="G53" s="193"/>
+      <c r="H53" s="193"/>
+      <c r="I53" s="193"/>
+      <c r="J53" s="193"/>
+      <c r="K53" s="193"/>
+      <c r="L53" s="193"/>
+      <c r="M53" s="193"/>
+      <c r="N53" s="193"/>
+      <c r="O53" s="193"/>
+      <c r="P53" s="193"/>
+      <c r="Q53" s="193"/>
+      <c r="R53" s="193"/>
+      <c r="S53" s="194"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="215"/>
-      <c r="B54" s="237"/>
-      <c r="C54" s="238"/>
-      <c r="D54" s="238"/>
-      <c r="E54" s="238"/>
-      <c r="F54" s="238"/>
-      <c r="G54" s="238"/>
-      <c r="H54" s="238"/>
-      <c r="I54" s="238"/>
-      <c r="J54" s="238"/>
-      <c r="K54" s="238"/>
-      <c r="L54" s="238"/>
-      <c r="M54" s="238"/>
-      <c r="N54" s="238"/>
-      <c r="O54" s="238"/>
-      <c r="P54" s="238"/>
-      <c r="Q54" s="238"/>
-      <c r="R54" s="238"/>
-      <c r="S54" s="239"/>
+      <c r="A54" s="179"/>
+      <c r="B54" s="192"/>
+      <c r="C54" s="193"/>
+      <c r="D54" s="193"/>
+      <c r="E54" s="193"/>
+      <c r="F54" s="193"/>
+      <c r="G54" s="193"/>
+      <c r="H54" s="193"/>
+      <c r="I54" s="193"/>
+      <c r="J54" s="193"/>
+      <c r="K54" s="193"/>
+      <c r="L54" s="193"/>
+      <c r="M54" s="193"/>
+      <c r="N54" s="193"/>
+      <c r="O54" s="193"/>
+      <c r="P54" s="193"/>
+      <c r="Q54" s="193"/>
+      <c r="R54" s="193"/>
+      <c r="S54" s="194"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="215"/>
-      <c r="B55" s="237"/>
-      <c r="C55" s="238"/>
-      <c r="D55" s="238"/>
-      <c r="E55" s="238"/>
-      <c r="F55" s="238"/>
-      <c r="G55" s="238"/>
-      <c r="H55" s="238"/>
-      <c r="I55" s="238"/>
-      <c r="J55" s="238"/>
-      <c r="K55" s="238"/>
-      <c r="L55" s="238"/>
-      <c r="M55" s="238"/>
-      <c r="N55" s="238"/>
-      <c r="O55" s="238"/>
-      <c r="P55" s="238"/>
-      <c r="Q55" s="238"/>
-      <c r="R55" s="238"/>
-      <c r="S55" s="239"/>
+      <c r="A55" s="179"/>
+      <c r="B55" s="192"/>
+      <c r="C55" s="193"/>
+      <c r="D55" s="193"/>
+      <c r="E55" s="193"/>
+      <c r="F55" s="193"/>
+      <c r="G55" s="193"/>
+      <c r="H55" s="193"/>
+      <c r="I55" s="193"/>
+      <c r="J55" s="193"/>
+      <c r="K55" s="193"/>
+      <c r="L55" s="193"/>
+      <c r="M55" s="193"/>
+      <c r="N55" s="193"/>
+      <c r="O55" s="193"/>
+      <c r="P55" s="193"/>
+      <c r="Q55" s="193"/>
+      <c r="R55" s="193"/>
+      <c r="S55" s="194"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="215"/>
-      <c r="B56" s="237"/>
-      <c r="C56" s="238"/>
-      <c r="D56" s="238"/>
-      <c r="E56" s="238"/>
-      <c r="F56" s="238"/>
-      <c r="G56" s="238"/>
-      <c r="H56" s="238"/>
-      <c r="I56" s="238"/>
-      <c r="J56" s="238"/>
-      <c r="K56" s="238"/>
-      <c r="L56" s="238"/>
-      <c r="M56" s="238"/>
-      <c r="N56" s="238"/>
-      <c r="O56" s="238"/>
-      <c r="P56" s="238"/>
-      <c r="Q56" s="238"/>
-      <c r="R56" s="238"/>
-      <c r="S56" s="239"/>
+      <c r="A56" s="179"/>
+      <c r="B56" s="192"/>
+      <c r="C56" s="193"/>
+      <c r="D56" s="193"/>
+      <c r="E56" s="193"/>
+      <c r="F56" s="193"/>
+      <c r="G56" s="193"/>
+      <c r="H56" s="193"/>
+      <c r="I56" s="193"/>
+      <c r="J56" s="193"/>
+      <c r="K56" s="193"/>
+      <c r="L56" s="193"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="193"/>
+      <c r="O56" s="193"/>
+      <c r="P56" s="193"/>
+      <c r="Q56" s="193"/>
+      <c r="R56" s="193"/>
+      <c r="S56" s="194"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="217"/>
-      <c r="B57" s="240"/>
-      <c r="C57" s="241"/>
-      <c r="D57" s="241"/>
-      <c r="E57" s="241"/>
-      <c r="F57" s="241"/>
-      <c r="G57" s="241"/>
-      <c r="H57" s="241"/>
-      <c r="I57" s="241"/>
-      <c r="J57" s="241"/>
-      <c r="K57" s="241"/>
-      <c r="L57" s="241"/>
-      <c r="M57" s="241"/>
-      <c r="N57" s="241"/>
-      <c r="O57" s="241"/>
-      <c r="P57" s="241"/>
-      <c r="Q57" s="241"/>
-      <c r="R57" s="241"/>
-      <c r="S57" s="242"/>
+      <c r="A57" s="180"/>
+      <c r="B57" s="195"/>
+      <c r="C57" s="196"/>
+      <c r="D57" s="196"/>
+      <c r="E57" s="196"/>
+      <c r="F57" s="196"/>
+      <c r="G57" s="196"/>
+      <c r="H57" s="196"/>
+      <c r="I57" s="196"/>
+      <c r="J57" s="196"/>
+      <c r="K57" s="196"/>
+      <c r="L57" s="196"/>
+      <c r="M57" s="196"/>
+      <c r="N57" s="196"/>
+      <c r="O57" s="196"/>
+      <c r="P57" s="196"/>
+      <c r="Q57" s="196"/>
+      <c r="R57" s="196"/>
+      <c r="S57" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="F40:S40"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="A10:A22"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="S47:S48"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A57"/>
     <mergeCell ref="A8:D9"/>
@@ -5450,32 +5476,6 @@
     <mergeCell ref="G47:G48"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="F40:S40"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="A10:A22"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10794,11 +10794,15 @@
         <v>DB</v>
       </c>
       <c r="X2" t="str">
-        <f>IFERROR(IF(ISNUMBER(--LEFT(TRIM(MID(A2,FIND("-",A2)+1,50)),1)),
-"AGT "&amp;TRIM(MID(A2,FIND("-",A2)+1,50)),
-TRIM(MID(A2,FIND("-",A2)+1,50)))
+        <f>IFERROR(
+IF(
+ISNUMBER(--LEFT(SUBSTITUTE(TRIM(MID(A2,FIND("-",A2)+1,50)),"LR ","LR"),1)),
+"AGT "&amp;SUBSTITUTE(TRIM(MID(A2,FIND("-",A2)+1,50)),"LR ","LR"),
+SUBSTITUTE(TRIM(MID(A2,FIND("-",A2)+1,50)),"LR ","LR")
+)
 &amp;IF(OR(E2=600,E2=650,E2=920)," /"&amp;E2,"")
-&amp;IF(E2=640," "&amp;"PS",""),"")&amp;IF(AND(OR(B2=8,B2=10,B2=16),D2=2800,E2=2070)," "&amp;B2&amp;"mm","")</f>
+&amp;IF(E2=640," PS",""),"")
+&amp;IF(AND(OR(B2=8,B2=10,B2=16),D2=2800,E2=2070)," "&amp;B2&amp;"mm","")</f>
         <v/>
       </c>
       <c r="Y2" t="str">
@@ -10856,11 +10860,15 @@
         <v>DB</v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" ref="X3:X34" si="3">IFERROR(IF(ISNUMBER(--LEFT(TRIM(MID(A3,FIND("-",A3)+1,50)),1)),
-"AGT "&amp;TRIM(MID(A3,FIND("-",A3)+1,50)),
-TRIM(MID(A3,FIND("-",A3)+1,50)))
+        <f t="shared" ref="X3:X34" si="3">IFERROR(
+IF(
+ISNUMBER(--LEFT(SUBSTITUTE(TRIM(MID(A3,FIND("-",A3)+1,50)),"LR ","LR"),1)),
+"AGT "&amp;SUBSTITUTE(TRIM(MID(A3,FIND("-",A3)+1,50)),"LR ","LR"),
+SUBSTITUTE(TRIM(MID(A3,FIND("-",A3)+1,50)),"LR ","LR")
+)
 &amp;IF(OR(E3=600,E3=650,E3=920)," /"&amp;E3,"")
-&amp;IF(E3=640," "&amp;"PS",""),"")&amp;IF(AND(OR(B3=8,B3=10,B3=16),D3=2800,E3=2070)," "&amp;B3&amp;"mm","")</f>
+&amp;IF(E3=640," PS",""),"")
+&amp;IF(AND(OR(B3=8,B3=10,B3=16),D3=2800,E3=2070)," "&amp;B3&amp;"mm","")</f>
         <v/>
       </c>
       <c r="Y3" t="str">

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46699E1F-26F1-4BDD-A64B-6881C6F92CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D14CE0-D54A-4C88-93C8-B1EFDC145833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1804,6 +1804,162 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1819,12 +1975,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1843,12 +1993,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1875,12 +2019,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1946,144 +2084,6 @@
     <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2570,33 +2570,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="210" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="235"/>
-      <c r="K1" s="235"/>
-      <c r="L1" s="236"/>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="212"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="219" t="s">
+      <c r="O1" s="199" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="221"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="201"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2615,165 +2615,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="222"/>
-      <c r="P2" s="223"/>
-      <c r="Q2" s="223"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="224"/>
+      <c r="O2" s="202"/>
+      <c r="P2" s="203"/>
+      <c r="Q2" s="203"/>
+      <c r="R2" s="203"/>
+      <c r="S2" s="204"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="242"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="244"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="175"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="177"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="225"/>
+      <c r="K3" s="226"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="237"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="239"/>
+      <c r="O3" s="213"/>
+      <c r="P3" s="195"/>
+      <c r="Q3" s="195"/>
+      <c r="R3" s="195"/>
+      <c r="S3" s="196"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="215"/>
+      <c r="B4" s="256"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="258"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="216"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="218"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="261"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="237"/>
-      <c r="P4" s="238"/>
-      <c r="Q4" s="238"/>
-      <c r="R4" s="238"/>
-      <c r="S4" s="239"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="195"/>
+      <c r="Q4" s="195"/>
+      <c r="R4" s="195"/>
+      <c r="S4" s="196"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="252"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="254"/>
+      <c r="B5" s="183"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="185"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="261"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="239"/>
+      <c r="I5" s="194"/>
+      <c r="J5" s="195"/>
+      <c r="K5" s="196"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="237"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="238"/>
-      <c r="R5" s="238"/>
-      <c r="S5" s="239"/>
+      <c r="O5" s="213"/>
+      <c r="P5" s="195"/>
+      <c r="Q5" s="195"/>
+      <c r="R5" s="195"/>
+      <c r="S5" s="196"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="257"/>
-      <c r="C6" s="258"/>
-      <c r="D6" s="259"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="190"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="260"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="227"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="192"/>
+      <c r="K6" s="193"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="225"/>
-      <c r="P6" s="226"/>
-      <c r="Q6" s="226"/>
-      <c r="R6" s="226"/>
-      <c r="S6" s="227"/>
+      <c r="O6" s="205"/>
+      <c r="P6" s="192"/>
+      <c r="Q6" s="192"/>
+      <c r="R6" s="192"/>
+      <c r="S6" s="193"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="181" t="s">
+      <c r="A8" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="182"/>
-      <c r="C8" s="182"/>
-      <c r="D8" s="183"/>
-      <c r="F8" s="228" t="s">
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="230"/>
+      <c r="F8" s="197" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="229"/>
-      <c r="Q8" s="229"/>
-      <c r="R8" s="229"/>
-      <c r="S8" s="230"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="198"/>
+      <c r="I8" s="198"/>
+      <c r="J8" s="198"/>
+      <c r="K8" s="198"/>
+      <c r="L8" s="198"/>
+      <c r="M8" s="198"/>
+      <c r="N8" s="198"/>
+      <c r="O8" s="198"/>
+      <c r="P8" s="198"/>
+      <c r="Q8" s="198"/>
+      <c r="R8" s="198"/>
+      <c r="S8" s="206"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="184"/>
-      <c r="B9" s="185"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="186"/>
-      <c r="F9" s="209" t="s">
+      <c r="A9" s="231"/>
+      <c r="B9" s="232"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="233"/>
+      <c r="F9" s="252" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="210"/>
-      <c r="H9" s="255" t="s">
+      <c r="G9" s="253"/>
+      <c r="H9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="256"/>
-      <c r="J9" s="207" t="s">
+      <c r="I9" s="187"/>
+      <c r="J9" s="250" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="208"/>
-      <c r="L9" s="250" t="s">
+      <c r="K9" s="251"/>
+      <c r="L9" s="181" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="251"/>
-      <c r="N9" s="187" t="s">
+      <c r="M9" s="182"/>
+      <c r="N9" s="218" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="188"/>
-      <c r="P9" s="202" t="s">
+      <c r="O9" s="219"/>
+      <c r="P9" s="245" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="203"/>
-      <c r="R9" s="187" t="s">
+      <c r="Q9" s="246"/>
+      <c r="R9" s="218" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="188"/>
+      <c r="S9" s="219"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="240" t="s">
+      <c r="A10" s="214" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2830,7 +2830,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="179"/>
+      <c r="A11" s="215"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2927,7 +2927,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="179"/>
+      <c r="A12" s="215"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3024,7 +3024,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="179"/>
+      <c r="A13" s="215"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3121,7 +3121,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="179"/>
+      <c r="A14" s="215"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3199,7 +3199,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="179"/>
+      <c r="A15" s="215"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3277,7 +3277,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="179"/>
+      <c r="A16" s="215"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3355,7 +3355,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="179"/>
+      <c r="A17" s="215"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3433,7 +3433,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="179"/>
+      <c r="A18" s="215"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="179"/>
+      <c r="A19" s="215"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3589,7 +3589,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="179"/>
+      <c r="A20" s="215"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3667,7 +3667,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="179"/>
+      <c r="A21" s="215"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="241"/>
+      <c r="A22" s="216"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3879,7 +3879,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="240" t="s">
+      <c r="A24" s="214" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3978,7 +3978,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="179"/>
+      <c r="A25" s="215"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4075,7 +4075,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="179"/>
+      <c r="A26" s="215"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4172,7 +4172,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="179"/>
+      <c r="A27" s="215"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="180"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4403,7 +4403,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="204" t="s">
+      <c r="A32" s="247" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4482,7 +4482,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="205"/>
+      <c r="A33" s="248"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4559,7 +4559,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="206"/>
+      <c r="A34" s="249"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4657,7 +4657,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="204" t="s">
+      <c r="A36" s="247" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4736,7 +4736,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="205"/>
+      <c r="A37" s="248"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4813,7 +4813,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="206"/>
+      <c r="A38" s="249"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4904,7 +4904,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="240" t="s">
+      <c r="A40" s="214" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4916,30 +4916,30 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="231" t="s">
+      <c r="F40" s="207" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="232"/>
-      <c r="H40" s="232"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="232"/>
-      <c r="O40" s="232"/>
-      <c r="P40" s="232"/>
-      <c r="Q40" s="232"/>
-      <c r="R40" s="232"/>
-      <c r="S40" s="233"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
+      <c r="N40" s="208"/>
+      <c r="O40" s="208"/>
+      <c r="P40" s="208"/>
+      <c r="Q40" s="208"/>
+      <c r="R40" s="208"/>
+      <c r="S40" s="209"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="179"/>
+      <c r="A41" s="215"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
       <c r="C41" s="29">
-        <f>SUMIF(Taiere!I2:I99, "PAL", Taiere!C2:C99)</f>
+        <f>SUMIF(Taiere!I2:I99, "PAL", Taiere!C2:C99)+SUMIF(Taiere!I2:I99, "DB", Taiere!C2:C99)</f>
         <v>0</v>
       </c>
       <c r="D41" s="73" t="s">
@@ -4997,7 +4997,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="179"/>
+      <c r="A42" s="215"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5022,13 +5022,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="198">
+      <c r="S42" s="175">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="179"/>
+      <c r="A43" s="215"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5040,26 +5040,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="228" t="str">
+      <c r="F43" s="197" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="229"/>
-      <c r="H43" s="229"/>
-      <c r="I43" s="229"/>
-      <c r="J43" s="229"/>
-      <c r="K43" s="229"/>
-      <c r="L43" s="229"/>
-      <c r="M43" s="229"/>
-      <c r="N43" s="229"/>
-      <c r="O43" s="229"/>
-      <c r="P43" s="229"/>
-      <c r="Q43" s="229"/>
-      <c r="R43" s="229"/>
-      <c r="S43" s="245"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="198"/>
+      <c r="N43" s="198"/>
+      <c r="O43" s="198"/>
+      <c r="P43" s="198"/>
+      <c r="Q43" s="198"/>
+      <c r="R43" s="198"/>
+      <c r="S43" s="176"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="179"/>
+      <c r="A44" s="215"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5115,7 +5115,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="179"/>
+      <c r="A45" s="215"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5186,7 +5186,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="179"/>
+      <c r="A46" s="215"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5200,7 +5200,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="179"/>
+      <c r="A47" s="215"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5211,31 +5211,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="198" t="s">
+      <c r="F47" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="211" t="str">
+      <c r="G47" s="254" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="198" t="s">
+      <c r="J47" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="200">
+      <c r="K47" s="243">
         <v>1</v>
       </c>
-      <c r="N47" s="198" t="s">
+      <c r="N47" s="175" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="246"/>
-      <c r="P47" s="247"/>
-      <c r="R47" s="198" t="s">
+      <c r="O47" s="177"/>
+      <c r="P47" s="178"/>
+      <c r="R47" s="175" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="198"/>
+      <c r="S47" s="175"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="180"/>
+      <c r="A48" s="217"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5246,15 +5246,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="199"/>
-      <c r="G48" s="212"/>
-      <c r="J48" s="199"/>
-      <c r="K48" s="201"/>
-      <c r="N48" s="245"/>
-      <c r="O48" s="248"/>
-      <c r="P48" s="249"/>
-      <c r="R48" s="245"/>
-      <c r="S48" s="199"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="255"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="244"/>
+      <c r="N48" s="176"/>
+      <c r="O48" s="179"/>
+      <c r="P48" s="180"/>
+      <c r="R48" s="176"/>
+      <c r="S48" s="223"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5263,187 +5263,193 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="178" t="s">
+      <c r="A50" s="227" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="189"/>
-      <c r="C50" s="190"/>
-      <c r="D50" s="190"/>
-      <c r="E50" s="190"/>
-      <c r="F50" s="190"/>
-      <c r="G50" s="190"/>
-      <c r="H50" s="190"/>
-      <c r="I50" s="190"/>
-      <c r="J50" s="190"/>
-      <c r="K50" s="190"/>
-      <c r="L50" s="190"/>
-      <c r="M50" s="190"/>
-      <c r="N50" s="190"/>
-      <c r="O50" s="190"/>
-      <c r="P50" s="190"/>
-      <c r="Q50" s="190"/>
-      <c r="R50" s="190"/>
-      <c r="S50" s="191"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="235"/>
+      <c r="D50" s="235"/>
+      <c r="E50" s="235"/>
+      <c r="F50" s="235"/>
+      <c r="G50" s="235"/>
+      <c r="H50" s="235"/>
+      <c r="I50" s="235"/>
+      <c r="J50" s="235"/>
+      <c r="K50" s="235"/>
+      <c r="L50" s="235"/>
+      <c r="M50" s="235"/>
+      <c r="N50" s="235"/>
+      <c r="O50" s="235"/>
+      <c r="P50" s="235"/>
+      <c r="Q50" s="235"/>
+      <c r="R50" s="235"/>
+      <c r="S50" s="236"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="179"/>
-      <c r="B51" s="192"/>
-      <c r="C51" s="193"/>
-      <c r="D51" s="193"/>
-      <c r="E51" s="193"/>
-      <c r="F51" s="193"/>
-      <c r="G51" s="193"/>
-      <c r="H51" s="193"/>
-      <c r="I51" s="193"/>
-      <c r="J51" s="193"/>
-      <c r="K51" s="193"/>
-      <c r="L51" s="193"/>
-      <c r="M51" s="193"/>
-      <c r="N51" s="193"/>
-      <c r="O51" s="193"/>
-      <c r="P51" s="193"/>
-      <c r="Q51" s="193"/>
-      <c r="R51" s="193"/>
-      <c r="S51" s="194"/>
+      <c r="A51" s="215"/>
+      <c r="B51" s="237"/>
+      <c r="C51" s="238"/>
+      <c r="D51" s="238"/>
+      <c r="E51" s="238"/>
+      <c r="F51" s="238"/>
+      <c r="G51" s="238"/>
+      <c r="H51" s="238"/>
+      <c r="I51" s="238"/>
+      <c r="J51" s="238"/>
+      <c r="K51" s="238"/>
+      <c r="L51" s="238"/>
+      <c r="M51" s="238"/>
+      <c r="N51" s="238"/>
+      <c r="O51" s="238"/>
+      <c r="P51" s="238"/>
+      <c r="Q51" s="238"/>
+      <c r="R51" s="238"/>
+      <c r="S51" s="239"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="179"/>
-      <c r="B52" s="192"/>
-      <c r="C52" s="193"/>
-      <c r="D52" s="193"/>
-      <c r="E52" s="193"/>
-      <c r="F52" s="193"/>
-      <c r="G52" s="193"/>
-      <c r="H52" s="193"/>
-      <c r="I52" s="193"/>
-      <c r="J52" s="193"/>
-      <c r="K52" s="193"/>
-      <c r="L52" s="193"/>
-      <c r="M52" s="193"/>
-      <c r="N52" s="193"/>
-      <c r="O52" s="193"/>
-      <c r="P52" s="193"/>
-      <c r="Q52" s="193"/>
-      <c r="R52" s="193"/>
-      <c r="S52" s="194"/>
+      <c r="A52" s="215"/>
+      <c r="B52" s="237"/>
+      <c r="C52" s="238"/>
+      <c r="D52" s="238"/>
+      <c r="E52" s="238"/>
+      <c r="F52" s="238"/>
+      <c r="G52" s="238"/>
+      <c r="H52" s="238"/>
+      <c r="I52" s="238"/>
+      <c r="J52" s="238"/>
+      <c r="K52" s="238"/>
+      <c r="L52" s="238"/>
+      <c r="M52" s="238"/>
+      <c r="N52" s="238"/>
+      <c r="O52" s="238"/>
+      <c r="P52" s="238"/>
+      <c r="Q52" s="238"/>
+      <c r="R52" s="238"/>
+      <c r="S52" s="239"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="179"/>
-      <c r="B53" s="192"/>
-      <c r="C53" s="193"/>
-      <c r="D53" s="193"/>
-      <c r="E53" s="193"/>
-      <c r="F53" s="193"/>
-      <c r="G53" s="193"/>
-      <c r="H53" s="193"/>
-      <c r="I53" s="193"/>
-      <c r="J53" s="193"/>
-      <c r="K53" s="193"/>
-      <c r="L53" s="193"/>
-      <c r="M53" s="193"/>
-      <c r="N53" s="193"/>
-      <c r="O53" s="193"/>
-      <c r="P53" s="193"/>
-      <c r="Q53" s="193"/>
-      <c r="R53" s="193"/>
-      <c r="S53" s="194"/>
+      <c r="A53" s="215"/>
+      <c r="B53" s="237"/>
+      <c r="C53" s="238"/>
+      <c r="D53" s="238"/>
+      <c r="E53" s="238"/>
+      <c r="F53" s="238"/>
+      <c r="G53" s="238"/>
+      <c r="H53" s="238"/>
+      <c r="I53" s="238"/>
+      <c r="J53" s="238"/>
+      <c r="K53" s="238"/>
+      <c r="L53" s="238"/>
+      <c r="M53" s="238"/>
+      <c r="N53" s="238"/>
+      <c r="O53" s="238"/>
+      <c r="P53" s="238"/>
+      <c r="Q53" s="238"/>
+      <c r="R53" s="238"/>
+      <c r="S53" s="239"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="179"/>
-      <c r="B54" s="192"/>
-      <c r="C54" s="193"/>
-      <c r="D54" s="193"/>
-      <c r="E54" s="193"/>
-      <c r="F54" s="193"/>
-      <c r="G54" s="193"/>
-      <c r="H54" s="193"/>
-      <c r="I54" s="193"/>
-      <c r="J54" s="193"/>
-      <c r="K54" s="193"/>
-      <c r="L54" s="193"/>
-      <c r="M54" s="193"/>
-      <c r="N54" s="193"/>
-      <c r="O54" s="193"/>
-      <c r="P54" s="193"/>
-      <c r="Q54" s="193"/>
-      <c r="R54" s="193"/>
-      <c r="S54" s="194"/>
+      <c r="A54" s="215"/>
+      <c r="B54" s="237"/>
+      <c r="C54" s="238"/>
+      <c r="D54" s="238"/>
+      <c r="E54" s="238"/>
+      <c r="F54" s="238"/>
+      <c r="G54" s="238"/>
+      <c r="H54" s="238"/>
+      <c r="I54" s="238"/>
+      <c r="J54" s="238"/>
+      <c r="K54" s="238"/>
+      <c r="L54" s="238"/>
+      <c r="M54" s="238"/>
+      <c r="N54" s="238"/>
+      <c r="O54" s="238"/>
+      <c r="P54" s="238"/>
+      <c r="Q54" s="238"/>
+      <c r="R54" s="238"/>
+      <c r="S54" s="239"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="179"/>
-      <c r="B55" s="192"/>
-      <c r="C55" s="193"/>
-      <c r="D55" s="193"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
-      <c r="G55" s="193"/>
-      <c r="H55" s="193"/>
-      <c r="I55" s="193"/>
-      <c r="J55" s="193"/>
-      <c r="K55" s="193"/>
-      <c r="L55" s="193"/>
-      <c r="M55" s="193"/>
-      <c r="N55" s="193"/>
-      <c r="O55" s="193"/>
-      <c r="P55" s="193"/>
-      <c r="Q55" s="193"/>
-      <c r="R55" s="193"/>
-      <c r="S55" s="194"/>
+      <c r="A55" s="215"/>
+      <c r="B55" s="237"/>
+      <c r="C55" s="238"/>
+      <c r="D55" s="238"/>
+      <c r="E55" s="238"/>
+      <c r="F55" s="238"/>
+      <c r="G55" s="238"/>
+      <c r="H55" s="238"/>
+      <c r="I55" s="238"/>
+      <c r="J55" s="238"/>
+      <c r="K55" s="238"/>
+      <c r="L55" s="238"/>
+      <c r="M55" s="238"/>
+      <c r="N55" s="238"/>
+      <c r="O55" s="238"/>
+      <c r="P55" s="238"/>
+      <c r="Q55" s="238"/>
+      <c r="R55" s="238"/>
+      <c r="S55" s="239"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="179"/>
-      <c r="B56" s="192"/>
-      <c r="C56" s="193"/>
-      <c r="D56" s="193"/>
-      <c r="E56" s="193"/>
-      <c r="F56" s="193"/>
-      <c r="G56" s="193"/>
-      <c r="H56" s="193"/>
-      <c r="I56" s="193"/>
-      <c r="J56" s="193"/>
-      <c r="K56" s="193"/>
-      <c r="L56" s="193"/>
-      <c r="M56" s="193"/>
-      <c r="N56" s="193"/>
-      <c r="O56" s="193"/>
-      <c r="P56" s="193"/>
-      <c r="Q56" s="193"/>
-      <c r="R56" s="193"/>
-      <c r="S56" s="194"/>
+      <c r="A56" s="215"/>
+      <c r="B56" s="237"/>
+      <c r="C56" s="238"/>
+      <c r="D56" s="238"/>
+      <c r="E56" s="238"/>
+      <c r="F56" s="238"/>
+      <c r="G56" s="238"/>
+      <c r="H56" s="238"/>
+      <c r="I56" s="238"/>
+      <c r="J56" s="238"/>
+      <c r="K56" s="238"/>
+      <c r="L56" s="238"/>
+      <c r="M56" s="238"/>
+      <c r="N56" s="238"/>
+      <c r="O56" s="238"/>
+      <c r="P56" s="238"/>
+      <c r="Q56" s="238"/>
+      <c r="R56" s="238"/>
+      <c r="S56" s="239"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="180"/>
-      <c r="B57" s="195"/>
-      <c r="C57" s="196"/>
-      <c r="D57" s="196"/>
-      <c r="E57" s="196"/>
-      <c r="F57" s="196"/>
-      <c r="G57" s="196"/>
-      <c r="H57" s="196"/>
-      <c r="I57" s="196"/>
-      <c r="J57" s="196"/>
-      <c r="K57" s="196"/>
-      <c r="L57" s="196"/>
-      <c r="M57" s="196"/>
-      <c r="N57" s="196"/>
-      <c r="O57" s="196"/>
-      <c r="P57" s="196"/>
-      <c r="Q57" s="196"/>
-      <c r="R57" s="196"/>
-      <c r="S57" s="197"/>
+      <c r="A57" s="217"/>
+      <c r="B57" s="240"/>
+      <c r="C57" s="241"/>
+      <c r="D57" s="241"/>
+      <c r="E57" s="241"/>
+      <c r="F57" s="241"/>
+      <c r="G57" s="241"/>
+      <c r="H57" s="241"/>
+      <c r="I57" s="241"/>
+      <c r="J57" s="241"/>
+      <c r="K57" s="241"/>
+      <c r="L57" s="241"/>
+      <c r="M57" s="241"/>
+      <c r="N57" s="241"/>
+      <c r="O57" s="241"/>
+      <c r="P57" s="241"/>
+      <c r="Q57" s="241"/>
+      <c r="R57" s="241"/>
+      <c r="S57" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B50:S57"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="O6:S6"/>
@@ -5460,22 +5466,16 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="R47:R48"/>
     <mergeCell ref="S47:S48"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="B50:S57"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10757,9 +10757,9 @@
       <c r="S2" s="164"/>
       <c r="T2" s="145"/>
       <c r="U2" s="145"/>
-      <c r="V2" s="169">
+      <c r="V2" s="169" t="str">
         <f>IFERROR(IF(W2="DB",Q2/13.5, ROUND(Q2/P2,2)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W2" t="str">
         <f>IF(
@@ -10767,8 +10767,8 @@
         AND(D2=2800,E2=2070,OR(B2=19,B2=19.3)),
         AND(D2=2800,E2=1220,B2=18),
         AND(D2=3050,E2=1300,B2=19.3),
-        AND(D2=2800, E2=1300,B2=17.5),
-        AND(D2=2800, E2=1300,B2=19),
+        AND(D2=2800,E2=1300,B2=17.5),
+        AND(D2=2800,E2=1300,B2=19),
         RIGHT(A2,6)="MDF 3D"
     ),
     "MDF",
@@ -10781,17 +10781,45 @@
         ),
         "PAL",
         IF(
-            AND(D2=4100,OR(E2=600,E2=650,E2=920),OR(B2=38,B2=20)),
+            AND(
+                D2=4100,
+                OR(E2=600,E2=650,E2=920),
+                OR(B2=38,B2=20)
+            ),
             "BLAT",
             IF(
-                AND(D2=4100,E2=640,OR(B2=9.2,B2=8)),
+                AND(
+                    D2=4100,
+                    E2=640,
+                    OR(B2=9.2,B2=8)
+                ),
                 "PS",
-                IF(B2=2.7,"HDF","DB")
+                IF(
+                    OR(
+                        AND(D2=2800,E2=2070,OR(B2=38,B2=38.6)),
+                        AND(D2=2800,E2=1220,B2=36),
+                        AND(D2=3050,E2=1300,B2=38.6),
+                        AND(D2=2800,E2=1300,B2=35),
+                        AND(D2=2800,E2=1300,B2=38),
+                        AND(RIGHT(A2,6)="MDF 3D",B2=36)
+                    ),
+                    "DB MDF",
+                    IF(
+                        AND(
+                            D2=2800,
+                            E2=2070,
+                            OR(B2=36,B2=37.2,B2=32),
+                            RIGHT(A2,6)&lt;&gt;"MDF 3D"
+                        ),
+                        "DB PAL",
+                        IF(B2=2.7,"HDF","N/A")
+                    )
+                )
             )
         )
     )
 )</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X2" t="str">
         <f>IFERROR(
@@ -10807,15 +10835,15 @@
       </c>
       <c r="Y2" t="str">
         <f t="shared" ref="Y2:Y15" si="0">IF(W2="DB", " ",IF(OR(ISNUMBER(FIND(" ST",X2)),ISNUMBER(FIND(" SM",X2)),ISNUMBER(FIND(" PM",X2)),ISNUMBER(FIND(" TM",X2)),ISNUMBER(FIND(" PG",X2)),ISNUMBER(FIND(" PA",X2))),SUBSTITUTE(X2," ","",1),X2))</f>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z2" t="str">
         <f>IF(W2="DB",IF(OR(ISNUMBER(FIND(" ST",X2)),ISNUMBER(FIND(" SM",X2)),ISNUMBER(FIND(" PM",X2)),ISNUMBER(FIND("TM/ST7",X2)),ISNUMBER(FIND(" PG",X2)),ISNUMBER(FIND(" PA",X2))),SUBSTITUTE(X2," ","",1),X2)," ")</f>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA2" t="str">
         <f>IF(W2="DB", IF(V2=INT(V2),"OK", "Vezi EK"),"")</f>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -10823,9 +10851,9 @@
       <c r="S3" s="164"/>
       <c r="T3" s="131"/>
       <c r="U3" s="145"/>
-      <c r="V3" s="169">
+      <c r="V3" s="169" t="str">
         <f t="shared" ref="V3:V34" si="1">IFERROR(IF(W3="DB",Q3/13.5, ROUND(Q3/P3,2)),"")</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W3" t="str">
         <f t="shared" ref="W3:W34" si="2">IF(
@@ -10833,8 +10861,8 @@
         AND(D3=2800,E3=2070,OR(B3=19,B3=19.3)),
         AND(D3=2800,E3=1220,B3=18),
         AND(D3=3050,E3=1300,B3=19.3),
-        AND(D3=2800, E3=1300,B3=17.5),
-        AND(D3=2800, E3=1300,B3=19),
+        AND(D3=2800,E3=1300,B3=17.5),
+        AND(D3=2800,E3=1300,B3=19),
         RIGHT(A3,6)="MDF 3D"
     ),
     "MDF",
@@ -10847,17 +10875,45 @@
         ),
         "PAL",
         IF(
-            AND(D3=4100,OR(E3=600,E3=650,E3=920),OR(B3=38,B3=20)),
+            AND(
+                D3=4100,
+                OR(E3=600,E3=650,E3=920),
+                OR(B3=38,B3=20)
+            ),
             "BLAT",
             IF(
-                AND(D3=4100,E3=640,OR(B3=9.2,B3=8)),
+                AND(
+                    D3=4100,
+                    E3=640,
+                    OR(B3=9.2,B3=8)
+                ),
                 "PS",
-                IF(B3=2.7,"HDF","DB")
+                IF(
+                    OR(
+                        AND(D3=2800,E3=2070,OR(B3=38,B3=38.6)),
+                        AND(D3=2800,E3=1220,B3=36),
+                        AND(D3=3050,E3=1300,B3=38.6),
+                        AND(D3=2800,E3=1300,B3=35),
+                        AND(D3=2800,E3=1300,B3=38),
+                        AND(RIGHT(A3,6)="MDF 3D",B3=36)
+                    ),
+                    "DB MDF",
+                    IF(
+                        AND(
+                            D3=2800,
+                            E3=2070,
+                            OR(B3=36,B3=37.2,B3=32),
+                            RIGHT(A3,6)&lt;&gt;"MDF 3D"
+                        ),
+                        "DB PAL",
+                        IF(B3=2.7,"HDF","N/A")
+                    )
+                )
             )
         )
     )
 )</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X3" t="str">
         <f t="shared" ref="X3:X34" si="3">IFERROR(
@@ -10873,15 +10929,15 @@
       </c>
       <c r="Y3" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z3" t="str">
         <f t="shared" ref="Z3:Z34" si="4">IF(W3="DB",IF(OR(ISNUMBER(FIND(" ST",X3)),ISNUMBER(FIND(" SM",X3)),ISNUMBER(FIND(" PM",X3)),ISNUMBER(FIND("TM/ST7",X3)),ISNUMBER(FIND(" PG",X3)),ISNUMBER(FIND(" PA",X3))),SUBSTITUTE(X3," ","",1),X3)," ")</f>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA3" t="str">
         <f t="shared" ref="AA3:AA34" si="5">IF(W3="DB", IF(V3=INT(V3),"OK", "Vezi EK"),"")</f>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -10889,13 +10945,13 @@
       <c r="S4" s="164"/>
       <c r="T4" s="145"/>
       <c r="U4" s="131"/>
-      <c r="V4" s="169">
+      <c r="V4" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W4" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X4" t="str">
         <f t="shared" si="3"/>
@@ -10903,15 +10959,15 @@
       </c>
       <c r="Y4" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z4" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA4" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -10919,13 +10975,13 @@
       <c r="S5" s="164"/>
       <c r="T5" s="145"/>
       <c r="U5" s="131"/>
-      <c r="V5" s="169">
+      <c r="V5" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W5" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X5" t="str">
         <f t="shared" si="3"/>
@@ -10933,15 +10989,15 @@
       </c>
       <c r="Y5" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z5" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA5" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -10949,13 +11005,13 @@
       <c r="S6" s="164"/>
       <c r="T6" s="145"/>
       <c r="U6" s="131"/>
-      <c r="V6" s="169">
+      <c r="V6" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W6" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X6" t="str">
         <f t="shared" si="3"/>
@@ -10963,15 +11019,15 @@
       </c>
       <c r="Y6" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z6" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA6" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -10979,13 +11035,13 @@
       <c r="S7" s="164"/>
       <c r="T7" s="131"/>
       <c r="U7" s="131"/>
-      <c r="V7" s="169">
+      <c r="V7" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W7" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X7" t="str">
         <f t="shared" si="3"/>
@@ -10993,15 +11049,15 @@
       </c>
       <c r="Y7" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z7" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA7" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -11009,13 +11065,13 @@
       <c r="S8" s="164"/>
       <c r="T8" s="145"/>
       <c r="U8" s="131"/>
-      <c r="V8" s="169">
+      <c r="V8" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W8" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X8" t="str">
         <f t="shared" si="3"/>
@@ -11023,15 +11079,15 @@
       </c>
       <c r="Y8" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z8" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA8" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -11039,13 +11095,13 @@
       <c r="S9" s="164"/>
       <c r="T9" s="145"/>
       <c r="U9" s="129"/>
-      <c r="V9" s="169">
+      <c r="V9" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W9" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X9" t="str">
         <f t="shared" si="3"/>
@@ -11053,15 +11109,15 @@
       </c>
       <c r="Y9" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z9" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA9" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -11069,13 +11125,13 @@
       <c r="S10" s="164"/>
       <c r="T10" s="145"/>
       <c r="U10" s="145"/>
-      <c r="V10" s="169">
+      <c r="V10" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W10" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X10" t="str">
         <f t="shared" si="3"/>
@@ -11083,15 +11139,15 @@
       </c>
       <c r="Y10" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z10" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA10" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -11099,13 +11155,13 @@
       <c r="S11" s="164"/>
       <c r="T11" s="145"/>
       <c r="U11" s="145"/>
-      <c r="V11" s="169">
+      <c r="V11" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W11" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X11" t="str">
         <f t="shared" si="3"/>
@@ -11113,15 +11169,15 @@
       </c>
       <c r="Y11" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z11" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA11" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -11129,13 +11185,13 @@
       <c r="S12" s="132"/>
       <c r="T12" s="132"/>
       <c r="U12" s="132"/>
-      <c r="V12" s="169">
+      <c r="V12" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W12" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X12" t="str">
         <f t="shared" si="3"/>
@@ -11143,15 +11199,15 @@
       </c>
       <c r="Y12" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z12" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA12" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -11159,13 +11215,13 @@
       <c r="S13" s="160"/>
       <c r="T13" s="159"/>
       <c r="U13" s="165"/>
-      <c r="V13" s="169">
+      <c r="V13" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W13" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X13" t="str">
         <f t="shared" si="3"/>
@@ -11173,15 +11229,15 @@
       </c>
       <c r="Y13" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z13" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA13" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -11189,13 +11245,13 @@
       <c r="S14" s="159"/>
       <c r="T14" s="160"/>
       <c r="U14" s="165"/>
-      <c r="V14" s="169">
+      <c r="V14" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W14" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X14" t="str">
         <f t="shared" si="3"/>
@@ -11203,15 +11259,15 @@
       </c>
       <c r="Y14" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z14" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA14" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -11219,13 +11275,13 @@
       <c r="S15" s="160"/>
       <c r="T15" s="160"/>
       <c r="U15" s="132"/>
-      <c r="V15" s="169">
+      <c r="V15" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W15" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X15" t="str">
         <f t="shared" si="3"/>
@@ -11233,15 +11289,15 @@
       </c>
       <c r="Y15" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z15" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA15" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -11249,13 +11305,13 @@
       <c r="S16" s="160"/>
       <c r="T16" s="160"/>
       <c r="U16" s="131"/>
-      <c r="V16" s="169">
+      <c r="V16" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W16" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X16" t="str">
         <f t="shared" si="3"/>
@@ -11263,15 +11319,15 @@
       </c>
       <c r="Y16" t="str">
         <f t="shared" ref="Y16:Y24" si="6">IF(W16="DB", " ",IF(OR(ISNUMBER(FIND(" ST",X16)),ISNUMBER(FIND(" SM",X16)),ISNUMBER(FIND(" PM",X16)),ISNUMBER(FIND(" TM",X16)),ISNUMBER(FIND(" PG",X16)),ISNUMBER(FIND(" PA",X16))),SUBSTITUTE(X16," ","",1),X16))</f>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z16" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA16" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -11279,13 +11335,13 @@
       <c r="S17" s="160"/>
       <c r="T17" s="160"/>
       <c r="U17" s="131"/>
-      <c r="V17" s="169">
+      <c r="V17" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W17" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X17" t="str">
         <f t="shared" si="3"/>
@@ -11293,15 +11349,15 @@
       </c>
       <c r="Y17" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z17" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA17" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -11326,13 +11382,13 @@
       <c r="S18" s="160"/>
       <c r="T18" s="160"/>
       <c r="U18" s="131"/>
-      <c r="V18" s="169">
+      <c r="V18" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W18" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X18" t="str">
         <f t="shared" si="3"/>
@@ -11340,15 +11396,15 @@
       </c>
       <c r="Y18" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z18" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA18" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -11372,13 +11428,13 @@
       <c r="R19" s="168"/>
       <c r="S19" s="160"/>
       <c r="T19" s="160"/>
-      <c r="V19" s="169">
+      <c r="V19" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W19" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X19" t="str">
         <f t="shared" si="3"/>
@@ -11386,15 +11442,15 @@
       </c>
       <c r="Y19" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z19" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA19" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -11418,13 +11474,13 @@
       <c r="R20" s="168"/>
       <c r="S20" s="159"/>
       <c r="T20" s="155"/>
-      <c r="V20" s="169">
+      <c r="V20" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W20" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X20" t="str">
         <f t="shared" si="3"/>
@@ -11432,15 +11488,15 @@
       </c>
       <c r="Y20" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z20" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA20" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -11464,13 +11520,13 @@
       <c r="R21" s="168"/>
       <c r="S21" s="160"/>
       <c r="T21" s="159"/>
-      <c r="V21" s="169">
+      <c r="V21" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W21" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X21" t="str">
         <f t="shared" si="3"/>
@@ -11478,25 +11534,25 @@
       </c>
       <c r="Y21" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z21" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA21" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:27">
-      <c r="V22" s="169">
+      <c r="V22" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W22" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X22" t="str">
         <f t="shared" si="3"/>
@@ -11504,25 +11560,25 @@
       </c>
       <c r="Y22" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z22" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA22" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="23" spans="1:27">
-      <c r="V23" s="169">
+      <c r="V23" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W23" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X23" t="str">
         <f t="shared" si="3"/>
@@ -11530,25 +11586,25 @@
       </c>
       <c r="Y23" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z23" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA23" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:27">
-      <c r="V24" s="169">
+      <c r="V24" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W24" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X24" t="str">
         <f t="shared" si="3"/>
@@ -11556,25 +11612,25 @@
       </c>
       <c r="Y24" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve"> </v>
+        <v/>
       </c>
       <c r="Z24" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA24" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="25" spans="1:27">
-      <c r="V25" s="169">
+      <c r="V25" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W25" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X25" t="str">
         <f t="shared" si="3"/>
@@ -11582,21 +11638,21 @@
       </c>
       <c r="Z25" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA25" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="26" spans="1:27">
-      <c r="V26" s="169">
+      <c r="V26" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W26" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X26" t="str">
         <f t="shared" si="3"/>
@@ -11604,21 +11660,21 @@
       </c>
       <c r="Z26" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA26" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="27" spans="1:27">
-      <c r="V27" s="169">
+      <c r="V27" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W27" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X27" t="str">
         <f t="shared" si="3"/>
@@ -11626,21 +11682,21 @@
       </c>
       <c r="Z27" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA27" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:27">
-      <c r="V28" s="169">
+      <c r="V28" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W28" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X28" t="str">
         <f t="shared" si="3"/>
@@ -11648,21 +11704,21 @@
       </c>
       <c r="Z28" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA28" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="29" spans="1:27">
-      <c r="V29" s="169">
+      <c r="V29" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W29" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X29" t="str">
         <f t="shared" si="3"/>
@@ -11670,21 +11726,21 @@
       </c>
       <c r="Z29" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA29" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="30" spans="1:27">
-      <c r="V30" s="169">
+      <c r="V30" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W30" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X30" t="str">
         <f t="shared" si="3"/>
@@ -11692,21 +11748,21 @@
       </c>
       <c r="Z30" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA30" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="31" spans="1:27">
-      <c r="V31" s="169">
+      <c r="V31" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W31" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X31" t="str">
         <f t="shared" si="3"/>
@@ -11714,21 +11770,21 @@
       </c>
       <c r="Z31" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA31" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="32" spans="1:27">
-      <c r="V32" s="169">
+      <c r="V32" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W32" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X32" t="str">
         <f t="shared" si="3"/>
@@ -11736,21 +11792,21 @@
       </c>
       <c r="Z32" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA32" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="33" spans="22:27">
-      <c r="V33" s="169">
+      <c r="V33" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W33" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X33" t="str">
         <f t="shared" si="3"/>
@@ -11758,21 +11814,21 @@
       </c>
       <c r="Z33" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA33" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
     <row r="34" spans="22:27">
-      <c r="V34" s="169">
+      <c r="V34" s="169" t="str">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="W34" t="str">
         <f t="shared" si="2"/>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
       <c r="X34" t="str">
         <f t="shared" si="3"/>
@@ -11780,11 +11836,11 @@
       </c>
       <c r="Z34" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v xml:space="preserve"> </v>
       </c>
       <c r="AA34" t="str">
         <f t="shared" si="5"/>
-        <v>OK</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -12332,163 +12388,163 @@
     <row r="2" spans="9:9">
       <c r="I2" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A2)), "CLEAF", Deco!W2)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="3" spans="9:9">
       <c r="I3" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A3)), "CLEAF", Deco!W3)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="4" spans="9:9">
       <c r="I4" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A4)), "CLEAF", Deco!W4)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="5" spans="9:9">
       <c r="I5" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A5)), "CLEAF", Deco!W5)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="6" spans="9:9">
       <c r="I6" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A6)), "CLEAF", Deco!W6)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="7" spans="9:9">
       <c r="I7" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A7)), "CLEAF", Deco!W7)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="8" spans="9:9">
       <c r="I8" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A8)), "CLEAF", Deco!W8)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="9" spans="9:9">
       <c r="I9" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A9)), "CLEAF", Deco!W9)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="10" spans="9:9">
       <c r="I10" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A10)), "CLEAF", Deco!W10)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="11" spans="9:9">
       <c r="I11" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A11)), "CLEAF", Deco!W11)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="12" spans="9:9">
       <c r="I12" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A12)), "CLEAF", Deco!W12)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="13" spans="9:9">
       <c r="I13" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A13)), "CLEAF", Deco!W13)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="14" spans="9:9">
       <c r="I14" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A14)), "CLEAF", Deco!W14)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="15" spans="9:9">
       <c r="I15" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A15)), "CLEAF", Deco!W15)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="16" spans="9:9">
       <c r="I16" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A16)), "CLEAF", Deco!W16)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="17" spans="9:9">
       <c r="I17" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A17)), "CLEAF", Deco!W17)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="18" spans="9:9">
       <c r="I18" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A18)), "CLEAF", Deco!W18)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="19" spans="9:9">
       <c r="I19" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A19)), "CLEAF", Deco!W19)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="20" spans="9:9">
       <c r="I20" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A20)), "CLEAF", Deco!W20)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="21" spans="9:9">
       <c r="I21" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A21)), "CLEAF", Deco!W21)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="22" spans="9:9">
       <c r="I22" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A22)), "CLEAF", Deco!W22)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="23" spans="9:9">
       <c r="I23" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A23)), "CLEAF", Deco!W23)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="24" spans="9:9">
       <c r="I24" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A24)), "CLEAF", Deco!W24)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="25" spans="9:9">
       <c r="I25" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A25)), "CLEAF", Deco!W25)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="26" spans="9:9">
       <c r="I26" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A26)), "CLEAF", Deco!W26)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="27" spans="9:9">
       <c r="I27" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A27)), "CLEAF", Deco!W27)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="28" spans="9:9">
       <c r="I28" t="str">
         <f>IF(ISNUMBER(SEARCH("CLMEL", A28)), "CLEAF", Deco!W28)</f>
-        <v>DB</v>
+        <v>N/A</v>
       </c>
     </row>
     <row r="335" spans="9:9">

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D14CE0-D54A-4C88-93C8-B1EFDC145833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1FA08F-B3FA-4A50-9CC3-B605343A8F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1804,8 +1804,229 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1861,229 +2082,8 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2570,33 +2570,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="234" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="212"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
+      <c r="L1" s="236"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="199" t="s">
+      <c r="O1" s="219" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="201"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="221"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2615,165 +2615,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="202"/>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="203"/>
-      <c r="R2" s="203"/>
-      <c r="S2" s="204"/>
+      <c r="O2" s="222"/>
+      <c r="P2" s="223"/>
+      <c r="Q2" s="223"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="224"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="220"/>
-      <c r="C3" s="221"/>
-      <c r="D3" s="222"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="244"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="225"/>
-      <c r="K3" s="226"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="177"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="195"/>
-      <c r="Q3" s="195"/>
-      <c r="R3" s="195"/>
-      <c r="S3" s="196"/>
+      <c r="O3" s="237"/>
+      <c r="P3" s="238"/>
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="239"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="256"/>
-      <c r="C4" s="257"/>
-      <c r="D4" s="258"/>
+      <c r="B4" s="213"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="215"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="259"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="261"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="218"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="195"/>
-      <c r="Q4" s="195"/>
-      <c r="R4" s="195"/>
-      <c r="S4" s="196"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="238"/>
+      <c r="Q4" s="238"/>
+      <c r="R4" s="238"/>
+      <c r="S4" s="239"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="185"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="254"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="194"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="196"/>
+      <c r="I5" s="261"/>
+      <c r="J5" s="238"/>
+      <c r="K5" s="239"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="213"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="195"/>
-      <c r="R5" s="195"/>
-      <c r="S5" s="196"/>
+      <c r="O5" s="237"/>
+      <c r="P5" s="238"/>
+      <c r="Q5" s="238"/>
+      <c r="R5" s="238"/>
+      <c r="S5" s="239"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="188"/>
-      <c r="C6" s="189"/>
-      <c r="D6" s="190"/>
+      <c r="B6" s="257"/>
+      <c r="C6" s="258"/>
+      <c r="D6" s="259"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="191"/>
-      <c r="J6" s="192"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="260"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="227"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="205"/>
-      <c r="P6" s="192"/>
-      <c r="Q6" s="192"/>
-      <c r="R6" s="192"/>
-      <c r="S6" s="193"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="226"/>
+      <c r="Q6" s="226"/>
+      <c r="R6" s="226"/>
+      <c r="S6" s="227"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="228" t="s">
+      <c r="A8" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="230"/>
-      <c r="F8" s="197" t="s">
+      <c r="B8" s="182"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="183"/>
+      <c r="F8" s="228" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="198"/>
-      <c r="H8" s="198"/>
-      <c r="I8" s="198"/>
-      <c r="J8" s="198"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="198"/>
-      <c r="O8" s="198"/>
-      <c r="P8" s="198"/>
-      <c r="Q8" s="198"/>
-      <c r="R8" s="198"/>
-      <c r="S8" s="206"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="229"/>
+      <c r="P8" s="229"/>
+      <c r="Q8" s="229"/>
+      <c r="R8" s="229"/>
+      <c r="S8" s="230"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="231"/>
-      <c r="B9" s="232"/>
-      <c r="C9" s="232"/>
-      <c r="D9" s="233"/>
-      <c r="F9" s="252" t="s">
+      <c r="A9" s="184"/>
+      <c r="B9" s="185"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="186"/>
+      <c r="F9" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="253"/>
-      <c r="H9" s="186" t="s">
+      <c r="G9" s="210"/>
+      <c r="H9" s="255" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="187"/>
-      <c r="J9" s="250" t="s">
+      <c r="I9" s="256"/>
+      <c r="J9" s="207" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="251"/>
-      <c r="L9" s="181" t="s">
+      <c r="K9" s="208"/>
+      <c r="L9" s="250" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="182"/>
-      <c r="N9" s="218" t="s">
+      <c r="M9" s="251"/>
+      <c r="N9" s="187" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="219"/>
-      <c r="P9" s="245" t="s">
+      <c r="O9" s="188"/>
+      <c r="P9" s="202" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="218" t="s">
+      <c r="Q9" s="203"/>
+      <c r="R9" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="219"/>
+      <c r="S9" s="188"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="214" t="s">
+      <c r="A10" s="240" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2830,7 +2830,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="215"/>
+      <c r="A11" s="179"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2927,7 +2927,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="215"/>
+      <c r="A12" s="179"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3024,7 +3024,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="215"/>
+      <c r="A13" s="179"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3121,7 +3121,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="215"/>
+      <c r="A14" s="179"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3199,7 +3199,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="215"/>
+      <c r="A15" s="179"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3277,7 +3277,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="215"/>
+      <c r="A16" s="179"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3355,7 +3355,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="215"/>
+      <c r="A17" s="179"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3433,7 +3433,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="215"/>
+      <c r="A18" s="179"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="215"/>
+      <c r="A19" s="179"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3589,7 +3589,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="215"/>
+      <c r="A20" s="179"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3667,7 +3667,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="215"/>
+      <c r="A21" s="179"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="216"/>
+      <c r="A22" s="241"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3879,7 +3879,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="214" t="s">
+      <c r="A24" s="240" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3978,7 +3978,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="215"/>
+      <c r="A25" s="179"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4075,7 +4075,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="215"/>
+      <c r="A26" s="179"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4172,7 +4172,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="215"/>
+      <c r="A27" s="179"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="217"/>
+      <c r="A28" s="180"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4403,7 +4403,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="247" t="s">
+      <c r="A32" s="204" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4482,7 +4482,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="248"/>
+      <c r="A33" s="205"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4559,7 +4559,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="249"/>
+      <c r="A34" s="206"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4657,7 +4657,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="247" t="s">
+      <c r="A36" s="204" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4736,7 +4736,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="248"/>
+      <c r="A37" s="205"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4813,7 +4813,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="249"/>
+      <c r="A38" s="206"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4904,7 +4904,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="214" t="s">
+      <c r="A40" s="240" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4916,30 +4916,30 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="207" t="s">
+      <c r="F40" s="231" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="208"/>
-      <c r="L40" s="208"/>
-      <c r="M40" s="208"/>
-      <c r="N40" s="208"/>
-      <c r="O40" s="208"/>
-      <c r="P40" s="208"/>
-      <c r="Q40" s="208"/>
-      <c r="R40" s="208"/>
-      <c r="S40" s="209"/>
+      <c r="G40" s="232"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="232"/>
+      <c r="O40" s="232"/>
+      <c r="P40" s="232"/>
+      <c r="Q40" s="232"/>
+      <c r="R40" s="232"/>
+      <c r="S40" s="233"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="215"/>
+      <c r="A41" s="179"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
       <c r="C41" s="29">
-        <f>SUMIF(Taiere!I2:I99, "PAL", Taiere!C2:C99)+SUMIF(Taiere!I2:I99, "DB", Taiere!C2:C99)</f>
+        <f>SUMIF(Taiere!I2:I99, "PAL", Taiere!C2:C99)+SUMIF(Taiere!I2:I99, "DB PAL", Taiere!C2:C99)</f>
         <v>0</v>
       </c>
       <c r="D41" s="73" t="s">
@@ -4997,7 +4997,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="215"/>
+      <c r="A42" s="179"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5022,13 +5022,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="175">
+      <c r="S42" s="198">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="215"/>
+      <c r="A43" s="179"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5040,26 +5040,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="197" t="str">
+      <c r="F43" s="228" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="198"/>
-      <c r="H43" s="198"/>
-      <c r="I43" s="198"/>
-      <c r="J43" s="198"/>
-      <c r="K43" s="198"/>
-      <c r="L43" s="198"/>
-      <c r="M43" s="198"/>
-      <c r="N43" s="198"/>
-      <c r="O43" s="198"/>
-      <c r="P43" s="198"/>
-      <c r="Q43" s="198"/>
-      <c r="R43" s="198"/>
-      <c r="S43" s="176"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="229"/>
+      <c r="J43" s="229"/>
+      <c r="K43" s="229"/>
+      <c r="L43" s="229"/>
+      <c r="M43" s="229"/>
+      <c r="N43" s="229"/>
+      <c r="O43" s="229"/>
+      <c r="P43" s="229"/>
+      <c r="Q43" s="229"/>
+      <c r="R43" s="229"/>
+      <c r="S43" s="245"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="215"/>
+      <c r="A44" s="179"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5115,7 +5115,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="215"/>
+      <c r="A45" s="179"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5128,8 +5128,17 @@
         <v>buc</v>
       </c>
       <c r="E45" s="2"/>
-      <c r="F45" s="43" t="str" cm="1">
-        <f t="array" ref="F45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),1))),"")</f>
+      <c r="F45" s="43" t="str">
+        <f>IFERROR(INDEX(
+        Deco!$Z$2:$Z$100,
+        _xlfn.AGGREGATE(
+            15,6,
+            ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/
+            ((Deco!$W$2:$W$100="DB PAL")+(Deco!$W$2:$W$100="DB MDF")),
+            1
+        )
+    ),
+    "")</f>
         <v/>
       </c>
       <c r="G45" s="31" t="str">
@@ -5137,7 +5146,16 @@
         <v/>
       </c>
       <c r="H45" s="43" t="str" cm="1">
-        <f t="array" ref="H45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),2))),"")</f>
+        <f t="array" ref="H45">IFERROR(_xlfn.SINGLE(INDEX(
+        Deco!$Z$2:$Z$100,
+        _xlfn.AGGREGATE(
+            15,6,
+            ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/
+            ((Deco!$W$2:$W$100="DB PAL")+(Deco!$W$2:$W$100="DB MDF")),
+            2
+        )
+    )),
+    "")</f>
         <v/>
       </c>
       <c r="I45" s="31" t="str">
@@ -5145,7 +5163,16 @@
         <v/>
       </c>
       <c r="J45" s="71" t="str" cm="1">
-        <f t="array" ref="J45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),3))),"")</f>
+        <f t="array" ref="J45">IFERROR(_xlfn.SINGLE(INDEX(
+        Deco!$Z$2:$Z$100,
+        _xlfn.AGGREGATE(
+            15,6,
+            ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/
+            ((Deco!$W$2:$W$100="DB PAL")+(Deco!$W$2:$W$100="DB MDF")),
+            3
+        )
+    )),
+    "")</f>
         <v/>
       </c>
       <c r="K45" s="31" t="str">
@@ -5153,7 +5180,16 @@
         <v/>
       </c>
       <c r="L45" s="71" t="str" cm="1">
-        <f t="array" ref="L45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),4))),"")</f>
+        <f t="array" ref="L45">IFERROR(_xlfn.SINGLE(INDEX(
+        Deco!$Z$2:$Z$100,
+        _xlfn.AGGREGATE(
+            15,6,
+            ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/
+            ((Deco!$W$2:$W$100="DB PAL")+(Deco!$W$2:$W$100="DB MDF")),
+            4
+        )
+    )),
+    "")</f>
         <v/>
       </c>
       <c r="M45" s="31" t="str">
@@ -5161,7 +5197,16 @@
         <v/>
       </c>
       <c r="N45" s="71" t="str" cm="1">
-        <f t="array" ref="N45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),5))),"")</f>
+        <f t="array" ref="N45">IFERROR(_xlfn.SINGLE(INDEX(
+        Deco!$Z$2:$Z$100,
+        _xlfn.AGGREGATE(
+            15,6,
+            ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/
+            ((Deco!$W$2:$W$100="DB PAL")+(Deco!$W$2:$W$100="DB MDF")),
+            5
+        )
+    )),
+    "")</f>
         <v/>
       </c>
       <c r="O45" s="31" t="str">
@@ -5169,7 +5214,16 @@
         <v/>
       </c>
       <c r="P45" s="71" t="str" cm="1">
-        <f t="array" ref="P45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),6))),"")</f>
+        <f t="array" ref="P45">IFERROR(_xlfn.SINGLE(INDEX(
+        Deco!$Z$2:$Z$100,
+        _xlfn.AGGREGATE(
+            15,6,
+            ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/
+            ((Deco!$W$2:$W$100="DB PAL")+(Deco!$W$2:$W$100="DB MDF")),
+            6
+        )
+    )),
+    "")</f>
         <v/>
       </c>
       <c r="Q45" s="31" t="str">
@@ -5177,7 +5231,16 @@
         <v/>
       </c>
       <c r="R45" s="71" t="str" cm="1">
-        <f t="array" ref="R45">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Z$2:$Z$100,_xlfn.AGGREGATE(15,6,ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/(Deco!$W$2:$W$100="DB"),7))),"")</f>
+        <f t="array" ref="R45">IFERROR(_xlfn.SINGLE(INDEX(
+        Deco!$Z$2:$Z$100,
+        _xlfn.AGGREGATE(
+            15,6,
+            ROW(Deco!$Z$2:$Z$100)-ROW(Deco!$Z$2)+1/
+            ((Deco!$W$2:$W$100="DB PAL")+(Deco!$W$2:$W$100="DB MDF")),
+            7
+        )
+    )),
+    "")</f>
         <v/>
       </c>
       <c r="S45" s="44" t="str">
@@ -5186,7 +5249,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="215"/>
+      <c r="A46" s="179"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5200,61 +5263,61 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="215"/>
+      <c r="A47" s="179"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
       <c r="C47" s="30">
-        <f>SUMIF(Taiere!I2:I99, "MDF", Taiere!C2:C99)</f>
+        <f>SUMIF(Taiere!I2:I99, "MDF", Taiere!C2:C99)+SUMIF(Taiere!I2:I99, "DB MDF", Taiere!C2:C99)</f>
         <v>0</v>
       </c>
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="175" t="s">
+      <c r="F47" s="198" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="254" t="str">
+      <c r="G47" s="211" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="175" t="s">
+      <c r="J47" s="198" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="243">
+      <c r="K47" s="200">
         <v>1</v>
       </c>
-      <c r="N47" s="175" t="s">
+      <c r="N47" s="198" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="177"/>
-      <c r="P47" s="178"/>
-      <c r="R47" s="175" t="s">
+      <c r="O47" s="246"/>
+      <c r="P47" s="247"/>
+      <c r="R47" s="198" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="175"/>
+      <c r="S47" s="198"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="217"/>
+      <c r="A48" s="180"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
       <c r="C48" s="31">
-        <f>SUM(F45:S45)</f>
+        <f>ROUND(SUM(F45:S45),0)</f>
         <v>0</v>
       </c>
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="223"/>
-      <c r="G48" s="255"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="244"/>
-      <c r="N48" s="176"/>
-      <c r="O48" s="179"/>
-      <c r="P48" s="180"/>
-      <c r="R48" s="176"/>
-      <c r="S48" s="223"/>
+      <c r="F48" s="199"/>
+      <c r="G48" s="212"/>
+      <c r="J48" s="199"/>
+      <c r="K48" s="201"/>
+      <c r="N48" s="245"/>
+      <c r="O48" s="248"/>
+      <c r="P48" s="249"/>
+      <c r="R48" s="245"/>
+      <c r="S48" s="199"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5263,177 +5326,203 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="227" t="s">
+      <c r="A50" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="234"/>
-      <c r="C50" s="235"/>
-      <c r="D50" s="235"/>
-      <c r="E50" s="235"/>
-      <c r="F50" s="235"/>
-      <c r="G50" s="235"/>
-      <c r="H50" s="235"/>
-      <c r="I50" s="235"/>
-      <c r="J50" s="235"/>
-      <c r="K50" s="235"/>
-      <c r="L50" s="235"/>
-      <c r="M50" s="235"/>
-      <c r="N50" s="235"/>
-      <c r="O50" s="235"/>
-      <c r="P50" s="235"/>
-      <c r="Q50" s="235"/>
-      <c r="R50" s="235"/>
-      <c r="S50" s="236"/>
+      <c r="B50" s="189"/>
+      <c r="C50" s="190"/>
+      <c r="D50" s="190"/>
+      <c r="E50" s="190"/>
+      <c r="F50" s="190"/>
+      <c r="G50" s="190"/>
+      <c r="H50" s="190"/>
+      <c r="I50" s="190"/>
+      <c r="J50" s="190"/>
+      <c r="K50" s="190"/>
+      <c r="L50" s="190"/>
+      <c r="M50" s="190"/>
+      <c r="N50" s="190"/>
+      <c r="O50" s="190"/>
+      <c r="P50" s="190"/>
+      <c r="Q50" s="190"/>
+      <c r="R50" s="190"/>
+      <c r="S50" s="191"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="215"/>
-      <c r="B51" s="237"/>
-      <c r="C51" s="238"/>
-      <c r="D51" s="238"/>
-      <c r="E51" s="238"/>
-      <c r="F51" s="238"/>
-      <c r="G51" s="238"/>
-      <c r="H51" s="238"/>
-      <c r="I51" s="238"/>
-      <c r="J51" s="238"/>
-      <c r="K51" s="238"/>
-      <c r="L51" s="238"/>
-      <c r="M51" s="238"/>
-      <c r="N51" s="238"/>
-      <c r="O51" s="238"/>
-      <c r="P51" s="238"/>
-      <c r="Q51" s="238"/>
-      <c r="R51" s="238"/>
-      <c r="S51" s="239"/>
+      <c r="A51" s="179"/>
+      <c r="B51" s="192"/>
+      <c r="C51" s="193"/>
+      <c r="D51" s="193"/>
+      <c r="E51" s="193"/>
+      <c r="F51" s="193"/>
+      <c r="G51" s="193"/>
+      <c r="H51" s="193"/>
+      <c r="I51" s="193"/>
+      <c r="J51" s="193"/>
+      <c r="K51" s="193"/>
+      <c r="L51" s="193"/>
+      <c r="M51" s="193"/>
+      <c r="N51" s="193"/>
+      <c r="O51" s="193"/>
+      <c r="P51" s="193"/>
+      <c r="Q51" s="193"/>
+      <c r="R51" s="193"/>
+      <c r="S51" s="194"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="215"/>
-      <c r="B52" s="237"/>
-      <c r="C52" s="238"/>
-      <c r="D52" s="238"/>
-      <c r="E52" s="238"/>
-      <c r="F52" s="238"/>
-      <c r="G52" s="238"/>
-      <c r="H52" s="238"/>
-      <c r="I52" s="238"/>
-      <c r="J52" s="238"/>
-      <c r="K52" s="238"/>
-      <c r="L52" s="238"/>
-      <c r="M52" s="238"/>
-      <c r="N52" s="238"/>
-      <c r="O52" s="238"/>
-      <c r="P52" s="238"/>
-      <c r="Q52" s="238"/>
-      <c r="R52" s="238"/>
-      <c r="S52" s="239"/>
+      <c r="A52" s="179"/>
+      <c r="B52" s="192"/>
+      <c r="C52" s="193"/>
+      <c r="D52" s="193"/>
+      <c r="E52" s="193"/>
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="193"/>
+      <c r="J52" s="193"/>
+      <c r="K52" s="193"/>
+      <c r="L52" s="193"/>
+      <c r="M52" s="193"/>
+      <c r="N52" s="193"/>
+      <c r="O52" s="193"/>
+      <c r="P52" s="193"/>
+      <c r="Q52" s="193"/>
+      <c r="R52" s="193"/>
+      <c r="S52" s="194"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="215"/>
-      <c r="B53" s="237"/>
-      <c r="C53" s="238"/>
-      <c r="D53" s="238"/>
-      <c r="E53" s="238"/>
-      <c r="F53" s="238"/>
-      <c r="G53" s="238"/>
-      <c r="H53" s="238"/>
-      <c r="I53" s="238"/>
-      <c r="J53" s="238"/>
-      <c r="K53" s="238"/>
-      <c r="L53" s="238"/>
-      <c r="M53" s="238"/>
-      <c r="N53" s="238"/>
-      <c r="O53" s="238"/>
-      <c r="P53" s="238"/>
-      <c r="Q53" s="238"/>
-      <c r="R53" s="238"/>
-      <c r="S53" s="239"/>
+      <c r="A53" s="179"/>
+      <c r="B53" s="192"/>
+      <c r="C53" s="193"/>
+      <c r="D53" s="193"/>
+      <c r="E53" s="193"/>
+      <c r="F53" s="193"/>
+      <c r="G53" s="193"/>
+      <c r="H53" s="193"/>
+      <c r="I53" s="193"/>
+      <c r="J53" s="193"/>
+      <c r="K53" s="193"/>
+      <c r="L53" s="193"/>
+      <c r="M53" s="193"/>
+      <c r="N53" s="193"/>
+      <c r="O53" s="193"/>
+      <c r="P53" s="193"/>
+      <c r="Q53" s="193"/>
+      <c r="R53" s="193"/>
+      <c r="S53" s="194"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="215"/>
-      <c r="B54" s="237"/>
-      <c r="C54" s="238"/>
-      <c r="D54" s="238"/>
-      <c r="E54" s="238"/>
-      <c r="F54" s="238"/>
-      <c r="G54" s="238"/>
-      <c r="H54" s="238"/>
-      <c r="I54" s="238"/>
-      <c r="J54" s="238"/>
-      <c r="K54" s="238"/>
-      <c r="L54" s="238"/>
-      <c r="M54" s="238"/>
-      <c r="N54" s="238"/>
-      <c r="O54" s="238"/>
-      <c r="P54" s="238"/>
-      <c r="Q54" s="238"/>
-      <c r="R54" s="238"/>
-      <c r="S54" s="239"/>
+      <c r="A54" s="179"/>
+      <c r="B54" s="192"/>
+      <c r="C54" s="193"/>
+      <c r="D54" s="193"/>
+      <c r="E54" s="193"/>
+      <c r="F54" s="193"/>
+      <c r="G54" s="193"/>
+      <c r="H54" s="193"/>
+      <c r="I54" s="193"/>
+      <c r="J54" s="193"/>
+      <c r="K54" s="193"/>
+      <c r="L54" s="193"/>
+      <c r="M54" s="193"/>
+      <c r="N54" s="193"/>
+      <c r="O54" s="193"/>
+      <c r="P54" s="193"/>
+      <c r="Q54" s="193"/>
+      <c r="R54" s="193"/>
+      <c r="S54" s="194"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="215"/>
-      <c r="B55" s="237"/>
-      <c r="C55" s="238"/>
-      <c r="D55" s="238"/>
-      <c r="E55" s="238"/>
-      <c r="F55" s="238"/>
-      <c r="G55" s="238"/>
-      <c r="H55" s="238"/>
-      <c r="I55" s="238"/>
-      <c r="J55" s="238"/>
-      <c r="K55" s="238"/>
-      <c r="L55" s="238"/>
-      <c r="M55" s="238"/>
-      <c r="N55" s="238"/>
-      <c r="O55" s="238"/>
-      <c r="P55" s="238"/>
-      <c r="Q55" s="238"/>
-      <c r="R55" s="238"/>
-      <c r="S55" s="239"/>
+      <c r="A55" s="179"/>
+      <c r="B55" s="192"/>
+      <c r="C55" s="193"/>
+      <c r="D55" s="193"/>
+      <c r="E55" s="193"/>
+      <c r="F55" s="193"/>
+      <c r="G55" s="193"/>
+      <c r="H55" s="193"/>
+      <c r="I55" s="193"/>
+      <c r="J55" s="193"/>
+      <c r="K55" s="193"/>
+      <c r="L55" s="193"/>
+      <c r="M55" s="193"/>
+      <c r="N55" s="193"/>
+      <c r="O55" s="193"/>
+      <c r="P55" s="193"/>
+      <c r="Q55" s="193"/>
+      <c r="R55" s="193"/>
+      <c r="S55" s="194"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="215"/>
-      <c r="B56" s="237"/>
-      <c r="C56" s="238"/>
-      <c r="D56" s="238"/>
-      <c r="E56" s="238"/>
-      <c r="F56" s="238"/>
-      <c r="G56" s="238"/>
-      <c r="H56" s="238"/>
-      <c r="I56" s="238"/>
-      <c r="J56" s="238"/>
-      <c r="K56" s="238"/>
-      <c r="L56" s="238"/>
-      <c r="M56" s="238"/>
-      <c r="N56" s="238"/>
-      <c r="O56" s="238"/>
-      <c r="P56" s="238"/>
-      <c r="Q56" s="238"/>
-      <c r="R56" s="238"/>
-      <c r="S56" s="239"/>
+      <c r="A56" s="179"/>
+      <c r="B56" s="192"/>
+      <c r="C56" s="193"/>
+      <c r="D56" s="193"/>
+      <c r="E56" s="193"/>
+      <c r="F56" s="193"/>
+      <c r="G56" s="193"/>
+      <c r="H56" s="193"/>
+      <c r="I56" s="193"/>
+      <c r="J56" s="193"/>
+      <c r="K56" s="193"/>
+      <c r="L56" s="193"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="193"/>
+      <c r="O56" s="193"/>
+      <c r="P56" s="193"/>
+      <c r="Q56" s="193"/>
+      <c r="R56" s="193"/>
+      <c r="S56" s="194"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="217"/>
-      <c r="B57" s="240"/>
-      <c r="C57" s="241"/>
-      <c r="D57" s="241"/>
-      <c r="E57" s="241"/>
-      <c r="F57" s="241"/>
-      <c r="G57" s="241"/>
-      <c r="H57" s="241"/>
-      <c r="I57" s="241"/>
-      <c r="J57" s="241"/>
-      <c r="K57" s="241"/>
-      <c r="L57" s="241"/>
-      <c r="M57" s="241"/>
-      <c r="N57" s="241"/>
-      <c r="O57" s="241"/>
-      <c r="P57" s="241"/>
-      <c r="Q57" s="241"/>
-      <c r="R57" s="241"/>
-      <c r="S57" s="242"/>
+      <c r="A57" s="180"/>
+      <c r="B57" s="195"/>
+      <c r="C57" s="196"/>
+      <c r="D57" s="196"/>
+      <c r="E57" s="196"/>
+      <c r="F57" s="196"/>
+      <c r="G57" s="196"/>
+      <c r="H57" s="196"/>
+      <c r="I57" s="196"/>
+      <c r="J57" s="196"/>
+      <c r="K57" s="196"/>
+      <c r="L57" s="196"/>
+      <c r="M57" s="196"/>
+      <c r="N57" s="196"/>
+      <c r="O57" s="196"/>
+      <c r="P57" s="196"/>
+      <c r="Q57" s="196"/>
+      <c r="R57" s="196"/>
+      <c r="S57" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="F40:S40"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="A10:A22"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="S47:S48"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A57"/>
     <mergeCell ref="A8:D9"/>
@@ -5450,32 +5539,6 @@
     <mergeCell ref="G47:G48"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="F40:S40"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="A10:A22"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10758,7 +10821,7 @@
       <c r="T2" s="145"/>
       <c r="U2" s="145"/>
       <c r="V2" s="169" t="str">
-        <f>IFERROR(IF(W2="DB",Q2/13.5, ROUND(Q2/P2,2)),"")</f>
+        <f>IFERROR(IF(OR(W2="DB PAL",W2="DB MDF"),Q2/13.5, ROUND(Q2/P2,2)),"")</f>
         <v/>
       </c>
       <c r="W2" t="str">
@@ -10838,7 +10901,22 @@
         <v/>
       </c>
       <c r="Z2" t="str">
-        <f>IF(W2="DB",IF(OR(ISNUMBER(FIND(" ST",X2)),ISNUMBER(FIND(" SM",X2)),ISNUMBER(FIND(" PM",X2)),ISNUMBER(FIND("TM/ST7",X2)),ISNUMBER(FIND(" PG",X2)),ISNUMBER(FIND(" PA",X2))),SUBSTITUTE(X2," ","",1),X2)," ")</f>
+        <f>IF(
+    OR(W2="DB PAL",W2="DB MDF"),
+    IF(
+        OR(
+            ISNUMBER(FIND(" ST",X2)),
+            ISNUMBER(FIND(" SM",X2)),
+            ISNUMBER(FIND(" PM",X2)),
+            ISNUMBER(FIND("TM/ST7",X2)),
+            ISNUMBER(FIND(" PG",X2)),
+            ISNUMBER(FIND(" PA",X2))
+        ),
+        SUBSTITUTE(X2," ","",1),
+        X2
+    ),
+    " "
+)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA2" t="str">
@@ -10852,7 +10930,7 @@
       <c r="T3" s="131"/>
       <c r="U3" s="145"/>
       <c r="V3" s="169" t="str">
-        <f t="shared" ref="V3:V34" si="1">IFERROR(IF(W3="DB",Q3/13.5, ROUND(Q3/P3,2)),"")</f>
+        <f t="shared" ref="V3:V34" si="1">IFERROR(IF(OR(W3="DB PAL",W3="DB MDF"),Q3/13.5, ROUND(Q3/P3,2)),"")</f>
         <v/>
       </c>
       <c r="W3" t="str">
@@ -10932,7 +11010,22 @@
         <v/>
       </c>
       <c r="Z3" t="str">
-        <f t="shared" ref="Z3:Z34" si="4">IF(W3="DB",IF(OR(ISNUMBER(FIND(" ST",X3)),ISNUMBER(FIND(" SM",X3)),ISNUMBER(FIND(" PM",X3)),ISNUMBER(FIND("TM/ST7",X3)),ISNUMBER(FIND(" PG",X3)),ISNUMBER(FIND(" PA",X3))),SUBSTITUTE(X3," ","",1),X3)," ")</f>
+        <f t="shared" ref="Z3:Z34" si="4">IF(
+    OR(W3="DB PAL",W3="DB MDF"),
+    IF(
+        OR(
+            ISNUMBER(FIND(" ST",X3)),
+            ISNUMBER(FIND(" SM",X3)),
+            ISNUMBER(FIND(" PM",X3)),
+            ISNUMBER(FIND("TM/ST7",X3)),
+            ISNUMBER(FIND(" PG",X3)),
+            ISNUMBER(FIND(" PA",X3))
+        ),
+        SUBSTITUTE(X3," ","",1),
+        X3
+    ),
+    " "
+)</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA3" t="str">

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1FA08F-B3FA-4A50-9CC3-B605343A8F10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716C2759-50F9-443C-93D2-66C2EC666E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1804,6 +1804,162 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1819,12 +1975,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1843,12 +1993,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1875,12 +2019,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1946,144 +2084,6 @@
     <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2570,33 +2570,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="210" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="235"/>
-      <c r="K1" s="235"/>
-      <c r="L1" s="236"/>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="212"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="219" t="s">
+      <c r="O1" s="199" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="221"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="201"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2615,165 +2615,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="222"/>
-      <c r="P2" s="223"/>
-      <c r="Q2" s="223"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="224"/>
+      <c r="O2" s="202"/>
+      <c r="P2" s="203"/>
+      <c r="Q2" s="203"/>
+      <c r="R2" s="203"/>
+      <c r="S2" s="204"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="242"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="244"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="175"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="177"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="225"/>
+      <c r="K3" s="226"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="237"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="239"/>
+      <c r="O3" s="213"/>
+      <c r="P3" s="195"/>
+      <c r="Q3" s="195"/>
+      <c r="R3" s="195"/>
+      <c r="S3" s="196"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="215"/>
+      <c r="B4" s="256"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="258"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="216"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="218"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="261"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="237"/>
-      <c r="P4" s="238"/>
-      <c r="Q4" s="238"/>
-      <c r="R4" s="238"/>
-      <c r="S4" s="239"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="195"/>
+      <c r="Q4" s="195"/>
+      <c r="R4" s="195"/>
+      <c r="S4" s="196"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="252"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="254"/>
+      <c r="B5" s="183"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="185"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="261"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="239"/>
+      <c r="I5" s="194"/>
+      <c r="J5" s="195"/>
+      <c r="K5" s="196"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="237"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="238"/>
-      <c r="R5" s="238"/>
-      <c r="S5" s="239"/>
+      <c r="O5" s="213"/>
+      <c r="P5" s="195"/>
+      <c r="Q5" s="195"/>
+      <c r="R5" s="195"/>
+      <c r="S5" s="196"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="257"/>
-      <c r="C6" s="258"/>
-      <c r="D6" s="259"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="190"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="260"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="227"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="192"/>
+      <c r="K6" s="193"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="225"/>
-      <c r="P6" s="226"/>
-      <c r="Q6" s="226"/>
-      <c r="R6" s="226"/>
-      <c r="S6" s="227"/>
+      <c r="O6" s="205"/>
+      <c r="P6" s="192"/>
+      <c r="Q6" s="192"/>
+      <c r="R6" s="192"/>
+      <c r="S6" s="193"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="181" t="s">
+      <c r="A8" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="182"/>
-      <c r="C8" s="182"/>
-      <c r="D8" s="183"/>
-      <c r="F8" s="228" t="s">
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="230"/>
+      <c r="F8" s="197" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="229"/>
-      <c r="Q8" s="229"/>
-      <c r="R8" s="229"/>
-      <c r="S8" s="230"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="198"/>
+      <c r="I8" s="198"/>
+      <c r="J8" s="198"/>
+      <c r="K8" s="198"/>
+      <c r="L8" s="198"/>
+      <c r="M8" s="198"/>
+      <c r="N8" s="198"/>
+      <c r="O8" s="198"/>
+      <c r="P8" s="198"/>
+      <c r="Q8" s="198"/>
+      <c r="R8" s="198"/>
+      <c r="S8" s="206"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="184"/>
-      <c r="B9" s="185"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="186"/>
-      <c r="F9" s="209" t="s">
+      <c r="A9" s="231"/>
+      <c r="B9" s="232"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="233"/>
+      <c r="F9" s="252" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="210"/>
-      <c r="H9" s="255" t="s">
+      <c r="G9" s="253"/>
+      <c r="H9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="256"/>
-      <c r="J9" s="207" t="s">
+      <c r="I9" s="187"/>
+      <c r="J9" s="250" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="208"/>
-      <c r="L9" s="250" t="s">
+      <c r="K9" s="251"/>
+      <c r="L9" s="181" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="251"/>
-      <c r="N9" s="187" t="s">
+      <c r="M9" s="182"/>
+      <c r="N9" s="218" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="188"/>
-      <c r="P9" s="202" t="s">
+      <c r="O9" s="219"/>
+      <c r="P9" s="245" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="203"/>
-      <c r="R9" s="187" t="s">
+      <c r="Q9" s="246"/>
+      <c r="R9" s="218" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="188"/>
+      <c r="S9" s="219"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="240" t="s">
+      <c r="A10" s="214" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2830,7 +2830,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="179"/>
+      <c r="A11" s="215"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2927,7 +2927,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="179"/>
+      <c r="A12" s="215"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3024,7 +3024,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="179"/>
+      <c r="A13" s="215"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3121,7 +3121,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="179"/>
+      <c r="A14" s="215"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3199,7 +3199,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="179"/>
+      <c r="A15" s="215"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3277,7 +3277,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="179"/>
+      <c r="A16" s="215"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3355,7 +3355,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="179"/>
+      <c r="A17" s="215"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3433,7 +3433,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="179"/>
+      <c r="A18" s="215"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="179"/>
+      <c r="A19" s="215"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3589,7 +3589,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="179"/>
+      <c r="A20" s="215"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3667,7 +3667,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="179"/>
+      <c r="A21" s="215"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="241"/>
+      <c r="A22" s="216"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3879,7 +3879,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="240" t="s">
+      <c r="A24" s="214" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3978,7 +3978,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="179"/>
+      <c r="A25" s="215"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4075,7 +4075,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="179"/>
+      <c r="A26" s="215"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4172,7 +4172,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="179"/>
+      <c r="A27" s="215"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="180"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4403,7 +4403,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="204" t="s">
+      <c r="A32" s="247" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4482,7 +4482,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="205"/>
+      <c r="A33" s="248"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4559,7 +4559,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="206"/>
+      <c r="A34" s="249"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4657,7 +4657,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="204" t="s">
+      <c r="A36" s="247" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4736,7 +4736,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="205"/>
+      <c r="A37" s="248"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4813,7 +4813,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="206"/>
+      <c r="A38" s="249"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4904,7 +4904,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="240" t="s">
+      <c r="A40" s="214" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4916,25 +4916,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="231" t="s">
+      <c r="F40" s="207" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="232"/>
-      <c r="H40" s="232"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="232"/>
-      <c r="O40" s="232"/>
-      <c r="P40" s="232"/>
-      <c r="Q40" s="232"/>
-      <c r="R40" s="232"/>
-      <c r="S40" s="233"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
+      <c r="N40" s="208"/>
+      <c r="O40" s="208"/>
+      <c r="P40" s="208"/>
+      <c r="Q40" s="208"/>
+      <c r="R40" s="208"/>
+      <c r="S40" s="209"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="179"/>
+      <c r="A41" s="215"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -4997,7 +4997,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="179"/>
+      <c r="A42" s="215"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5022,13 +5022,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="198">
+      <c r="S42" s="175">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="179"/>
+      <c r="A43" s="215"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5040,26 +5040,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="228" t="str">
+      <c r="F43" s="197" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="229"/>
-      <c r="H43" s="229"/>
-      <c r="I43" s="229"/>
-      <c r="J43" s="229"/>
-      <c r="K43" s="229"/>
-      <c r="L43" s="229"/>
-      <c r="M43" s="229"/>
-      <c r="N43" s="229"/>
-      <c r="O43" s="229"/>
-      <c r="P43" s="229"/>
-      <c r="Q43" s="229"/>
-      <c r="R43" s="229"/>
-      <c r="S43" s="245"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="198"/>
+      <c r="N43" s="198"/>
+      <c r="O43" s="198"/>
+      <c r="P43" s="198"/>
+      <c r="Q43" s="198"/>
+      <c r="R43" s="198"/>
+      <c r="S43" s="176"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="179"/>
+      <c r="A44" s="215"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5115,7 +5115,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="179"/>
+      <c r="A45" s="215"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5249,7 +5249,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="179"/>
+      <c r="A46" s="215"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5263,7 +5263,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="179"/>
+      <c r="A47" s="215"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5274,31 +5274,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="198" t="s">
+      <c r="F47" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="211" t="str">
+      <c r="G47" s="254" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="198" t="s">
+      <c r="J47" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="200">
+      <c r="K47" s="243">
         <v>1</v>
       </c>
-      <c r="N47" s="198" t="s">
+      <c r="N47" s="175" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="246"/>
-      <c r="P47" s="247"/>
-      <c r="R47" s="198" t="s">
+      <c r="O47" s="177"/>
+      <c r="P47" s="178"/>
+      <c r="R47" s="175" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="198"/>
+      <c r="S47" s="175"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="180"/>
+      <c r="A48" s="217"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5309,15 +5309,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="199"/>
-      <c r="G48" s="212"/>
-      <c r="J48" s="199"/>
-      <c r="K48" s="201"/>
-      <c r="N48" s="245"/>
-      <c r="O48" s="248"/>
-      <c r="P48" s="249"/>
-      <c r="R48" s="245"/>
-      <c r="S48" s="199"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="255"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="244"/>
+      <c r="N48" s="176"/>
+      <c r="O48" s="179"/>
+      <c r="P48" s="180"/>
+      <c r="R48" s="176"/>
+      <c r="S48" s="223"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5326,187 +5326,193 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="178" t="s">
+      <c r="A50" s="227" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="189"/>
-      <c r="C50" s="190"/>
-      <c r="D50" s="190"/>
-      <c r="E50" s="190"/>
-      <c r="F50" s="190"/>
-      <c r="G50" s="190"/>
-      <c r="H50" s="190"/>
-      <c r="I50" s="190"/>
-      <c r="J50" s="190"/>
-      <c r="K50" s="190"/>
-      <c r="L50" s="190"/>
-      <c r="M50" s="190"/>
-      <c r="N50" s="190"/>
-      <c r="O50" s="190"/>
-      <c r="P50" s="190"/>
-      <c r="Q50" s="190"/>
-      <c r="R50" s="190"/>
-      <c r="S50" s="191"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="235"/>
+      <c r="D50" s="235"/>
+      <c r="E50" s="235"/>
+      <c r="F50" s="235"/>
+      <c r="G50" s="235"/>
+      <c r="H50" s="235"/>
+      <c r="I50" s="235"/>
+      <c r="J50" s="235"/>
+      <c r="K50" s="235"/>
+      <c r="L50" s="235"/>
+      <c r="M50" s="235"/>
+      <c r="N50" s="235"/>
+      <c r="O50" s="235"/>
+      <c r="P50" s="235"/>
+      <c r="Q50" s="235"/>
+      <c r="R50" s="235"/>
+      <c r="S50" s="236"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="179"/>
-      <c r="B51" s="192"/>
-      <c r="C51" s="193"/>
-      <c r="D51" s="193"/>
-      <c r="E51" s="193"/>
-      <c r="F51" s="193"/>
-      <c r="G51" s="193"/>
-      <c r="H51" s="193"/>
-      <c r="I51" s="193"/>
-      <c r="J51" s="193"/>
-      <c r="K51" s="193"/>
-      <c r="L51" s="193"/>
-      <c r="M51" s="193"/>
-      <c r="N51" s="193"/>
-      <c r="O51" s="193"/>
-      <c r="P51" s="193"/>
-      <c r="Q51" s="193"/>
-      <c r="R51" s="193"/>
-      <c r="S51" s="194"/>
+      <c r="A51" s="215"/>
+      <c r="B51" s="237"/>
+      <c r="C51" s="238"/>
+      <c r="D51" s="238"/>
+      <c r="E51" s="238"/>
+      <c r="F51" s="238"/>
+      <c r="G51" s="238"/>
+      <c r="H51" s="238"/>
+      <c r="I51" s="238"/>
+      <c r="J51" s="238"/>
+      <c r="K51" s="238"/>
+      <c r="L51" s="238"/>
+      <c r="M51" s="238"/>
+      <c r="N51" s="238"/>
+      <c r="O51" s="238"/>
+      <c r="P51" s="238"/>
+      <c r="Q51" s="238"/>
+      <c r="R51" s="238"/>
+      <c r="S51" s="239"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="179"/>
-      <c r="B52" s="192"/>
-      <c r="C52" s="193"/>
-      <c r="D52" s="193"/>
-      <c r="E52" s="193"/>
-      <c r="F52" s="193"/>
-      <c r="G52" s="193"/>
-      <c r="H52" s="193"/>
-      <c r="I52" s="193"/>
-      <c r="J52" s="193"/>
-      <c r="K52" s="193"/>
-      <c r="L52" s="193"/>
-      <c r="M52" s="193"/>
-      <c r="N52" s="193"/>
-      <c r="O52" s="193"/>
-      <c r="P52" s="193"/>
-      <c r="Q52" s="193"/>
-      <c r="R52" s="193"/>
-      <c r="S52" s="194"/>
+      <c r="A52" s="215"/>
+      <c r="B52" s="237"/>
+      <c r="C52" s="238"/>
+      <c r="D52" s="238"/>
+      <c r="E52" s="238"/>
+      <c r="F52" s="238"/>
+      <c r="G52" s="238"/>
+      <c r="H52" s="238"/>
+      <c r="I52" s="238"/>
+      <c r="J52" s="238"/>
+      <c r="K52" s="238"/>
+      <c r="L52" s="238"/>
+      <c r="M52" s="238"/>
+      <c r="N52" s="238"/>
+      <c r="O52" s="238"/>
+      <c r="P52" s="238"/>
+      <c r="Q52" s="238"/>
+      <c r="R52" s="238"/>
+      <c r="S52" s="239"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="179"/>
-      <c r="B53" s="192"/>
-      <c r="C53" s="193"/>
-      <c r="D53" s="193"/>
-      <c r="E53" s="193"/>
-      <c r="F53" s="193"/>
-      <c r="G53" s="193"/>
-      <c r="H53" s="193"/>
-      <c r="I53" s="193"/>
-      <c r="J53" s="193"/>
-      <c r="K53" s="193"/>
-      <c r="L53" s="193"/>
-      <c r="M53" s="193"/>
-      <c r="N53" s="193"/>
-      <c r="O53" s="193"/>
-      <c r="P53" s="193"/>
-      <c r="Q53" s="193"/>
-      <c r="R53" s="193"/>
-      <c r="S53" s="194"/>
+      <c r="A53" s="215"/>
+      <c r="B53" s="237"/>
+      <c r="C53" s="238"/>
+      <c r="D53" s="238"/>
+      <c r="E53" s="238"/>
+      <c r="F53" s="238"/>
+      <c r="G53" s="238"/>
+      <c r="H53" s="238"/>
+      <c r="I53" s="238"/>
+      <c r="J53" s="238"/>
+      <c r="K53" s="238"/>
+      <c r="L53" s="238"/>
+      <c r="M53" s="238"/>
+      <c r="N53" s="238"/>
+      <c r="O53" s="238"/>
+      <c r="P53" s="238"/>
+      <c r="Q53" s="238"/>
+      <c r="R53" s="238"/>
+      <c r="S53" s="239"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="179"/>
-      <c r="B54" s="192"/>
-      <c r="C54" s="193"/>
-      <c r="D54" s="193"/>
-      <c r="E54" s="193"/>
-      <c r="F54" s="193"/>
-      <c r="G54" s="193"/>
-      <c r="H54" s="193"/>
-      <c r="I54" s="193"/>
-      <c r="J54" s="193"/>
-      <c r="K54" s="193"/>
-      <c r="L54" s="193"/>
-      <c r="M54" s="193"/>
-      <c r="N54" s="193"/>
-      <c r="O54" s="193"/>
-      <c r="P54" s="193"/>
-      <c r="Q54" s="193"/>
-      <c r="R54" s="193"/>
-      <c r="S54" s="194"/>
+      <c r="A54" s="215"/>
+      <c r="B54" s="237"/>
+      <c r="C54" s="238"/>
+      <c r="D54" s="238"/>
+      <c r="E54" s="238"/>
+      <c r="F54" s="238"/>
+      <c r="G54" s="238"/>
+      <c r="H54" s="238"/>
+      <c r="I54" s="238"/>
+      <c r="J54" s="238"/>
+      <c r="K54" s="238"/>
+      <c r="L54" s="238"/>
+      <c r="M54" s="238"/>
+      <c r="N54" s="238"/>
+      <c r="O54" s="238"/>
+      <c r="P54" s="238"/>
+      <c r="Q54" s="238"/>
+      <c r="R54" s="238"/>
+      <c r="S54" s="239"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="179"/>
-      <c r="B55" s="192"/>
-      <c r="C55" s="193"/>
-      <c r="D55" s="193"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
-      <c r="G55" s="193"/>
-      <c r="H55" s="193"/>
-      <c r="I55" s="193"/>
-      <c r="J55" s="193"/>
-      <c r="K55" s="193"/>
-      <c r="L55" s="193"/>
-      <c r="M55" s="193"/>
-      <c r="N55" s="193"/>
-      <c r="O55" s="193"/>
-      <c r="P55" s="193"/>
-      <c r="Q55" s="193"/>
-      <c r="R55" s="193"/>
-      <c r="S55" s="194"/>
+      <c r="A55" s="215"/>
+      <c r="B55" s="237"/>
+      <c r="C55" s="238"/>
+      <c r="D55" s="238"/>
+      <c r="E55" s="238"/>
+      <c r="F55" s="238"/>
+      <c r="G55" s="238"/>
+      <c r="H55" s="238"/>
+      <c r="I55" s="238"/>
+      <c r="J55" s="238"/>
+      <c r="K55" s="238"/>
+      <c r="L55" s="238"/>
+      <c r="M55" s="238"/>
+      <c r="N55" s="238"/>
+      <c r="O55" s="238"/>
+      <c r="P55" s="238"/>
+      <c r="Q55" s="238"/>
+      <c r="R55" s="238"/>
+      <c r="S55" s="239"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="179"/>
-      <c r="B56" s="192"/>
-      <c r="C56" s="193"/>
-      <c r="D56" s="193"/>
-      <c r="E56" s="193"/>
-      <c r="F56" s="193"/>
-      <c r="G56" s="193"/>
-      <c r="H56" s="193"/>
-      <c r="I56" s="193"/>
-      <c r="J56" s="193"/>
-      <c r="K56" s="193"/>
-      <c r="L56" s="193"/>
-      <c r="M56" s="193"/>
-      <c r="N56" s="193"/>
-      <c r="O56" s="193"/>
-      <c r="P56" s="193"/>
-      <c r="Q56" s="193"/>
-      <c r="R56" s="193"/>
-      <c r="S56" s="194"/>
+      <c r="A56" s="215"/>
+      <c r="B56" s="237"/>
+      <c r="C56" s="238"/>
+      <c r="D56" s="238"/>
+      <c r="E56" s="238"/>
+      <c r="F56" s="238"/>
+      <c r="G56" s="238"/>
+      <c r="H56" s="238"/>
+      <c r="I56" s="238"/>
+      <c r="J56" s="238"/>
+      <c r="K56" s="238"/>
+      <c r="L56" s="238"/>
+      <c r="M56" s="238"/>
+      <c r="N56" s="238"/>
+      <c r="O56" s="238"/>
+      <c r="P56" s="238"/>
+      <c r="Q56" s="238"/>
+      <c r="R56" s="238"/>
+      <c r="S56" s="239"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="180"/>
-      <c r="B57" s="195"/>
-      <c r="C57" s="196"/>
-      <c r="D57" s="196"/>
-      <c r="E57" s="196"/>
-      <c r="F57" s="196"/>
-      <c r="G57" s="196"/>
-      <c r="H57" s="196"/>
-      <c r="I57" s="196"/>
-      <c r="J57" s="196"/>
-      <c r="K57" s="196"/>
-      <c r="L57" s="196"/>
-      <c r="M57" s="196"/>
-      <c r="N57" s="196"/>
-      <c r="O57" s="196"/>
-      <c r="P57" s="196"/>
-      <c r="Q57" s="196"/>
-      <c r="R57" s="196"/>
-      <c r="S57" s="197"/>
+      <c r="A57" s="217"/>
+      <c r="B57" s="240"/>
+      <c r="C57" s="241"/>
+      <c r="D57" s="241"/>
+      <c r="E57" s="241"/>
+      <c r="F57" s="241"/>
+      <c r="G57" s="241"/>
+      <c r="H57" s="241"/>
+      <c r="I57" s="241"/>
+      <c r="J57" s="241"/>
+      <c r="K57" s="241"/>
+      <c r="L57" s="241"/>
+      <c r="M57" s="241"/>
+      <c r="N57" s="241"/>
+      <c r="O57" s="241"/>
+      <c r="P57" s="241"/>
+      <c r="Q57" s="241"/>
+      <c r="R57" s="241"/>
+      <c r="S57" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B50:S57"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="O6:S6"/>
@@ -5523,22 +5529,16 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="R47:R48"/>
     <mergeCell ref="S47:S48"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="B50:S57"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10871,7 +10871,7 @@
                         AND(
                             D2=2800,
                             E2=2070,
-                            OR(B2=36,B2=37.2,B2=32),
+                            OR(B2=36,B2=37.2,B2=32,B2=26, B2=28),
                             RIGHT(A2,6)&lt;&gt;"MDF 3D"
                         ),
                         "DB PAL",
@@ -10980,7 +10980,7 @@
                         AND(
                             D3=2800,
                             E3=2070,
-                            OR(B3=36,B3=37.2,B3=32),
+                            OR(B3=36,B3=37.2,B3=32,B3=26, B3=28),
                             RIGHT(A3,6)&lt;&gt;"MDF 3D"
                         ),
                         "DB PAL",

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716C2759-50F9-443C-93D2-66C2EC666E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF304B4-D3B9-4A67-BF49-D7AFDA3F93EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -1804,8 +1804,229 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1861,229 +2082,8 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2570,33 +2570,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="234" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="212"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
+      <c r="L1" s="236"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="199" t="s">
+      <c r="O1" s="219" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="201"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="221"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2615,165 +2615,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="202"/>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="203"/>
-      <c r="R2" s="203"/>
-      <c r="S2" s="204"/>
+      <c r="O2" s="222"/>
+      <c r="P2" s="223"/>
+      <c r="Q2" s="223"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="224"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="220"/>
-      <c r="C3" s="221"/>
-      <c r="D3" s="222"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="244"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="225"/>
-      <c r="K3" s="226"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="177"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="195"/>
-      <c r="Q3" s="195"/>
-      <c r="R3" s="195"/>
-      <c r="S3" s="196"/>
+      <c r="O3" s="237"/>
+      <c r="P3" s="238"/>
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="239"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="256"/>
-      <c r="C4" s="257"/>
-      <c r="D4" s="258"/>
+      <c r="B4" s="213"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="215"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="259"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="261"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="218"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="195"/>
-      <c r="Q4" s="195"/>
-      <c r="R4" s="195"/>
-      <c r="S4" s="196"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="238"/>
+      <c r="Q4" s="238"/>
+      <c r="R4" s="238"/>
+      <c r="S4" s="239"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="185"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="254"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="194"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="196"/>
+      <c r="I5" s="261"/>
+      <c r="J5" s="238"/>
+      <c r="K5" s="239"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="213"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="195"/>
-      <c r="R5" s="195"/>
-      <c r="S5" s="196"/>
+      <c r="O5" s="237"/>
+      <c r="P5" s="238"/>
+      <c r="Q5" s="238"/>
+      <c r="R5" s="238"/>
+      <c r="S5" s="239"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="188"/>
-      <c r="C6" s="189"/>
-      <c r="D6" s="190"/>
+      <c r="B6" s="257"/>
+      <c r="C6" s="258"/>
+      <c r="D6" s="259"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="191"/>
-      <c r="J6" s="192"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="260"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="227"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="205"/>
-      <c r="P6" s="192"/>
-      <c r="Q6" s="192"/>
-      <c r="R6" s="192"/>
-      <c r="S6" s="193"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="226"/>
+      <c r="Q6" s="226"/>
+      <c r="R6" s="226"/>
+      <c r="S6" s="227"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="228" t="s">
+      <c r="A8" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="230"/>
-      <c r="F8" s="197" t="s">
+      <c r="B8" s="182"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="183"/>
+      <c r="F8" s="228" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="198"/>
-      <c r="H8" s="198"/>
-      <c r="I8" s="198"/>
-      <c r="J8" s="198"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="198"/>
-      <c r="O8" s="198"/>
-      <c r="P8" s="198"/>
-      <c r="Q8" s="198"/>
-      <c r="R8" s="198"/>
-      <c r="S8" s="206"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="229"/>
+      <c r="P8" s="229"/>
+      <c r="Q8" s="229"/>
+      <c r="R8" s="229"/>
+      <c r="S8" s="230"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="231"/>
-      <c r="B9" s="232"/>
-      <c r="C9" s="232"/>
-      <c r="D9" s="233"/>
-      <c r="F9" s="252" t="s">
+      <c r="A9" s="184"/>
+      <c r="B9" s="185"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="186"/>
+      <c r="F9" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="253"/>
-      <c r="H9" s="186" t="s">
+      <c r="G9" s="210"/>
+      <c r="H9" s="255" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="187"/>
-      <c r="J9" s="250" t="s">
+      <c r="I9" s="256"/>
+      <c r="J9" s="207" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="251"/>
-      <c r="L9" s="181" t="s">
+      <c r="K9" s="208"/>
+      <c r="L9" s="250" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="182"/>
-      <c r="N9" s="218" t="s">
+      <c r="M9" s="251"/>
+      <c r="N9" s="187" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="219"/>
-      <c r="P9" s="245" t="s">
+      <c r="O9" s="188"/>
+      <c r="P9" s="202" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="218" t="s">
+      <c r="Q9" s="203"/>
+      <c r="R9" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="219"/>
+      <c r="S9" s="188"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="214" t="s">
+      <c r="A10" s="240" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2830,7 +2830,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="215"/>
+      <c r="A11" s="179"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2927,7 +2927,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="215"/>
+      <c r="A12" s="179"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3024,7 +3024,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="215"/>
+      <c r="A13" s="179"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3121,7 +3121,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="215"/>
+      <c r="A14" s="179"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3199,7 +3199,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="215"/>
+      <c r="A15" s="179"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3277,7 +3277,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="215"/>
+      <c r="A16" s="179"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3355,7 +3355,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="215"/>
+      <c r="A17" s="179"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3433,7 +3433,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="215"/>
+      <c r="A18" s="179"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="215"/>
+      <c r="A19" s="179"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3589,7 +3589,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="215"/>
+      <c r="A20" s="179"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3667,7 +3667,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="215"/>
+      <c r="A21" s="179"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="216"/>
+      <c r="A22" s="241"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3879,7 +3879,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="214" t="s">
+      <c r="A24" s="240" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3978,7 +3978,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="215"/>
+      <c r="A25" s="179"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4075,7 +4075,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="215"/>
+      <c r="A26" s="179"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4172,7 +4172,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="215"/>
+      <c r="A27" s="179"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="217"/>
+      <c r="A28" s="180"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4403,7 +4403,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="247" t="s">
+      <c r="A32" s="204" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4482,7 +4482,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="248"/>
+      <c r="A33" s="205"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4559,7 +4559,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="249"/>
+      <c r="A34" s="206"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4657,7 +4657,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="247" t="s">
+      <c r="A36" s="204" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4736,7 +4736,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="248"/>
+      <c r="A37" s="205"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4813,7 +4813,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="249"/>
+      <c r="A38" s="206"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4904,7 +4904,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="214" t="s">
+      <c r="A40" s="240" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4916,25 +4916,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="207" t="s">
+      <c r="F40" s="231" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="208"/>
-      <c r="L40" s="208"/>
-      <c r="M40" s="208"/>
-      <c r="N40" s="208"/>
-      <c r="O40" s="208"/>
-      <c r="P40" s="208"/>
-      <c r="Q40" s="208"/>
-      <c r="R40" s="208"/>
-      <c r="S40" s="209"/>
+      <c r="G40" s="232"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="232"/>
+      <c r="O40" s="232"/>
+      <c r="P40" s="232"/>
+      <c r="Q40" s="232"/>
+      <c r="R40" s="232"/>
+      <c r="S40" s="233"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="215"/>
+      <c r="A41" s="179"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -4997,7 +4997,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="215"/>
+      <c r="A42" s="179"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5022,13 +5022,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="175">
+      <c r="S42" s="198">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="215"/>
+      <c r="A43" s="179"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5040,26 +5040,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="197" t="str">
+      <c r="F43" s="228" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="198"/>
-      <c r="H43" s="198"/>
-      <c r="I43" s="198"/>
-      <c r="J43" s="198"/>
-      <c r="K43" s="198"/>
-      <c r="L43" s="198"/>
-      <c r="M43" s="198"/>
-      <c r="N43" s="198"/>
-      <c r="O43" s="198"/>
-      <c r="P43" s="198"/>
-      <c r="Q43" s="198"/>
-      <c r="R43" s="198"/>
-      <c r="S43" s="176"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="229"/>
+      <c r="J43" s="229"/>
+      <c r="K43" s="229"/>
+      <c r="L43" s="229"/>
+      <c r="M43" s="229"/>
+      <c r="N43" s="229"/>
+      <c r="O43" s="229"/>
+      <c r="P43" s="229"/>
+      <c r="Q43" s="229"/>
+      <c r="R43" s="229"/>
+      <c r="S43" s="245"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="215"/>
+      <c r="A44" s="179"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5115,7 +5115,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="215"/>
+      <c r="A45" s="179"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5249,7 +5249,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="215"/>
+      <c r="A46" s="179"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5263,7 +5263,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="215"/>
+      <c r="A47" s="179"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5274,31 +5274,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="175" t="s">
+      <c r="F47" s="198" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="254" t="str">
+      <c r="G47" s="211" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="175" t="s">
+      <c r="J47" s="198" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="243">
+      <c r="K47" s="200">
         <v>1</v>
       </c>
-      <c r="N47" s="175" t="s">
+      <c r="N47" s="198" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="177"/>
-      <c r="P47" s="178"/>
-      <c r="R47" s="175" t="s">
+      <c r="O47" s="246"/>
+      <c r="P47" s="247"/>
+      <c r="R47" s="198" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="175"/>
+      <c r="S47" s="198"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="217"/>
+      <c r="A48" s="180"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5309,15 +5309,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="223"/>
-      <c r="G48" s="255"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="244"/>
-      <c r="N48" s="176"/>
-      <c r="O48" s="179"/>
-      <c r="P48" s="180"/>
-      <c r="R48" s="176"/>
-      <c r="S48" s="223"/>
+      <c r="F48" s="199"/>
+      <c r="G48" s="212"/>
+      <c r="J48" s="199"/>
+      <c r="K48" s="201"/>
+      <c r="N48" s="245"/>
+      <c r="O48" s="248"/>
+      <c r="P48" s="249"/>
+      <c r="R48" s="245"/>
+      <c r="S48" s="199"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5326,177 +5326,203 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="227" t="s">
+      <c r="A50" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="234"/>
-      <c r="C50" s="235"/>
-      <c r="D50" s="235"/>
-      <c r="E50" s="235"/>
-      <c r="F50" s="235"/>
-      <c r="G50" s="235"/>
-      <c r="H50" s="235"/>
-      <c r="I50" s="235"/>
-      <c r="J50" s="235"/>
-      <c r="K50" s="235"/>
-      <c r="L50" s="235"/>
-      <c r="M50" s="235"/>
-      <c r="N50" s="235"/>
-      <c r="O50" s="235"/>
-      <c r="P50" s="235"/>
-      <c r="Q50" s="235"/>
-      <c r="R50" s="235"/>
-      <c r="S50" s="236"/>
+      <c r="B50" s="189"/>
+      <c r="C50" s="190"/>
+      <c r="D50" s="190"/>
+      <c r="E50" s="190"/>
+      <c r="F50" s="190"/>
+      <c r="G50" s="190"/>
+      <c r="H50" s="190"/>
+      <c r="I50" s="190"/>
+      <c r="J50" s="190"/>
+      <c r="K50" s="190"/>
+      <c r="L50" s="190"/>
+      <c r="M50" s="190"/>
+      <c r="N50" s="190"/>
+      <c r="O50" s="190"/>
+      <c r="P50" s="190"/>
+      <c r="Q50" s="190"/>
+      <c r="R50" s="190"/>
+      <c r="S50" s="191"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="215"/>
-      <c r="B51" s="237"/>
-      <c r="C51" s="238"/>
-      <c r="D51" s="238"/>
-      <c r="E51" s="238"/>
-      <c r="F51" s="238"/>
-      <c r="G51" s="238"/>
-      <c r="H51" s="238"/>
-      <c r="I51" s="238"/>
-      <c r="J51" s="238"/>
-      <c r="K51" s="238"/>
-      <c r="L51" s="238"/>
-      <c r="M51" s="238"/>
-      <c r="N51" s="238"/>
-      <c r="O51" s="238"/>
-      <c r="P51" s="238"/>
-      <c r="Q51" s="238"/>
-      <c r="R51" s="238"/>
-      <c r="S51" s="239"/>
+      <c r="A51" s="179"/>
+      <c r="B51" s="192"/>
+      <c r="C51" s="193"/>
+      <c r="D51" s="193"/>
+      <c r="E51" s="193"/>
+      <c r="F51" s="193"/>
+      <c r="G51" s="193"/>
+      <c r="H51" s="193"/>
+      <c r="I51" s="193"/>
+      <c r="J51" s="193"/>
+      <c r="K51" s="193"/>
+      <c r="L51" s="193"/>
+      <c r="M51" s="193"/>
+      <c r="N51" s="193"/>
+      <c r="O51" s="193"/>
+      <c r="P51" s="193"/>
+      <c r="Q51" s="193"/>
+      <c r="R51" s="193"/>
+      <c r="S51" s="194"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="215"/>
-      <c r="B52" s="237"/>
-      <c r="C52" s="238"/>
-      <c r="D52" s="238"/>
-      <c r="E52" s="238"/>
-      <c r="F52" s="238"/>
-      <c r="G52" s="238"/>
-      <c r="H52" s="238"/>
-      <c r="I52" s="238"/>
-      <c r="J52" s="238"/>
-      <c r="K52" s="238"/>
-      <c r="L52" s="238"/>
-      <c r="M52" s="238"/>
-      <c r="N52" s="238"/>
-      <c r="O52" s="238"/>
-      <c r="P52" s="238"/>
-      <c r="Q52" s="238"/>
-      <c r="R52" s="238"/>
-      <c r="S52" s="239"/>
+      <c r="A52" s="179"/>
+      <c r="B52" s="192"/>
+      <c r="C52" s="193"/>
+      <c r="D52" s="193"/>
+      <c r="E52" s="193"/>
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="193"/>
+      <c r="J52" s="193"/>
+      <c r="K52" s="193"/>
+      <c r="L52" s="193"/>
+      <c r="M52" s="193"/>
+      <c r="N52" s="193"/>
+      <c r="O52" s="193"/>
+      <c r="P52" s="193"/>
+      <c r="Q52" s="193"/>
+      <c r="R52" s="193"/>
+      <c r="S52" s="194"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="215"/>
-      <c r="B53" s="237"/>
-      <c r="C53" s="238"/>
-      <c r="D53" s="238"/>
-      <c r="E53" s="238"/>
-      <c r="F53" s="238"/>
-      <c r="G53" s="238"/>
-      <c r="H53" s="238"/>
-      <c r="I53" s="238"/>
-      <c r="J53" s="238"/>
-      <c r="K53" s="238"/>
-      <c r="L53" s="238"/>
-      <c r="M53" s="238"/>
-      <c r="N53" s="238"/>
-      <c r="O53" s="238"/>
-      <c r="P53" s="238"/>
-      <c r="Q53" s="238"/>
-      <c r="R53" s="238"/>
-      <c r="S53" s="239"/>
+      <c r="A53" s="179"/>
+      <c r="B53" s="192"/>
+      <c r="C53" s="193"/>
+      <c r="D53" s="193"/>
+      <c r="E53" s="193"/>
+      <c r="F53" s="193"/>
+      <c r="G53" s="193"/>
+      <c r="H53" s="193"/>
+      <c r="I53" s="193"/>
+      <c r="J53" s="193"/>
+      <c r="K53" s="193"/>
+      <c r="L53" s="193"/>
+      <c r="M53" s="193"/>
+      <c r="N53" s="193"/>
+      <c r="O53" s="193"/>
+      <c r="P53" s="193"/>
+      <c r="Q53" s="193"/>
+      <c r="R53" s="193"/>
+      <c r="S53" s="194"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="215"/>
-      <c r="B54" s="237"/>
-      <c r="C54" s="238"/>
-      <c r="D54" s="238"/>
-      <c r="E54" s="238"/>
-      <c r="F54" s="238"/>
-      <c r="G54" s="238"/>
-      <c r="H54" s="238"/>
-      <c r="I54" s="238"/>
-      <c r="J54" s="238"/>
-      <c r="K54" s="238"/>
-      <c r="L54" s="238"/>
-      <c r="M54" s="238"/>
-      <c r="N54" s="238"/>
-      <c r="O54" s="238"/>
-      <c r="P54" s="238"/>
-      <c r="Q54" s="238"/>
-      <c r="R54" s="238"/>
-      <c r="S54" s="239"/>
+      <c r="A54" s="179"/>
+      <c r="B54" s="192"/>
+      <c r="C54" s="193"/>
+      <c r="D54" s="193"/>
+      <c r="E54" s="193"/>
+      <c r="F54" s="193"/>
+      <c r="G54" s="193"/>
+      <c r="H54" s="193"/>
+      <c r="I54" s="193"/>
+      <c r="J54" s="193"/>
+      <c r="K54" s="193"/>
+      <c r="L54" s="193"/>
+      <c r="M54" s="193"/>
+      <c r="N54" s="193"/>
+      <c r="O54" s="193"/>
+      <c r="P54" s="193"/>
+      <c r="Q54" s="193"/>
+      <c r="R54" s="193"/>
+      <c r="S54" s="194"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="215"/>
-      <c r="B55" s="237"/>
-      <c r="C55" s="238"/>
-      <c r="D55" s="238"/>
-      <c r="E55" s="238"/>
-      <c r="F55" s="238"/>
-      <c r="G55" s="238"/>
-      <c r="H55" s="238"/>
-      <c r="I55" s="238"/>
-      <c r="J55" s="238"/>
-      <c r="K55" s="238"/>
-      <c r="L55" s="238"/>
-      <c r="M55" s="238"/>
-      <c r="N55" s="238"/>
-      <c r="O55" s="238"/>
-      <c r="P55" s="238"/>
-      <c r="Q55" s="238"/>
-      <c r="R55" s="238"/>
-      <c r="S55" s="239"/>
+      <c r="A55" s="179"/>
+      <c r="B55" s="192"/>
+      <c r="C55" s="193"/>
+      <c r="D55" s="193"/>
+      <c r="E55" s="193"/>
+      <c r="F55" s="193"/>
+      <c r="G55" s="193"/>
+      <c r="H55" s="193"/>
+      <c r="I55" s="193"/>
+      <c r="J55" s="193"/>
+      <c r="K55" s="193"/>
+      <c r="L55" s="193"/>
+      <c r="M55" s="193"/>
+      <c r="N55" s="193"/>
+      <c r="O55" s="193"/>
+      <c r="P55" s="193"/>
+      <c r="Q55" s="193"/>
+      <c r="R55" s="193"/>
+      <c r="S55" s="194"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="215"/>
-      <c r="B56" s="237"/>
-      <c r="C56" s="238"/>
-      <c r="D56" s="238"/>
-      <c r="E56" s="238"/>
-      <c r="F56" s="238"/>
-      <c r="G56" s="238"/>
-      <c r="H56" s="238"/>
-      <c r="I56" s="238"/>
-      <c r="J56" s="238"/>
-      <c r="K56" s="238"/>
-      <c r="L56" s="238"/>
-      <c r="M56" s="238"/>
-      <c r="N56" s="238"/>
-      <c r="O56" s="238"/>
-      <c r="P56" s="238"/>
-      <c r="Q56" s="238"/>
-      <c r="R56" s="238"/>
-      <c r="S56" s="239"/>
+      <c r="A56" s="179"/>
+      <c r="B56" s="192"/>
+      <c r="C56" s="193"/>
+      <c r="D56" s="193"/>
+      <c r="E56" s="193"/>
+      <c r="F56" s="193"/>
+      <c r="G56" s="193"/>
+      <c r="H56" s="193"/>
+      <c r="I56" s="193"/>
+      <c r="J56" s="193"/>
+      <c r="K56" s="193"/>
+      <c r="L56" s="193"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="193"/>
+      <c r="O56" s="193"/>
+      <c r="P56" s="193"/>
+      <c r="Q56" s="193"/>
+      <c r="R56" s="193"/>
+      <c r="S56" s="194"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="217"/>
-      <c r="B57" s="240"/>
-      <c r="C57" s="241"/>
-      <c r="D57" s="241"/>
-      <c r="E57" s="241"/>
-      <c r="F57" s="241"/>
-      <c r="G57" s="241"/>
-      <c r="H57" s="241"/>
-      <c r="I57" s="241"/>
-      <c r="J57" s="241"/>
-      <c r="K57" s="241"/>
-      <c r="L57" s="241"/>
-      <c r="M57" s="241"/>
-      <c r="N57" s="241"/>
-      <c r="O57" s="241"/>
-      <c r="P57" s="241"/>
-      <c r="Q57" s="241"/>
-      <c r="R57" s="241"/>
-      <c r="S57" s="242"/>
+      <c r="A57" s="180"/>
+      <c r="B57" s="195"/>
+      <c r="C57" s="196"/>
+      <c r="D57" s="196"/>
+      <c r="E57" s="196"/>
+      <c r="F57" s="196"/>
+      <c r="G57" s="196"/>
+      <c r="H57" s="196"/>
+      <c r="I57" s="196"/>
+      <c r="J57" s="196"/>
+      <c r="K57" s="196"/>
+      <c r="L57" s="196"/>
+      <c r="M57" s="196"/>
+      <c r="N57" s="196"/>
+      <c r="O57" s="196"/>
+      <c r="P57" s="196"/>
+      <c r="Q57" s="196"/>
+      <c r="R57" s="196"/>
+      <c r="S57" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="F40:S40"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="A10:A22"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="S47:S48"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A57"/>
     <mergeCell ref="A8:D9"/>
@@ -5513,32 +5539,6 @@
     <mergeCell ref="G47:G48"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="F40:S40"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="A10:A22"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10920,7 +10920,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA2" t="str">
-        <f>IF(W2="DB", IF(V2=INT(V2),"OK", "Vezi EK"),"")</f>
+        <f>IF(OR(W2="DB PAL",W2="DB MDF"), IF(V2=INT(V2),"OK", "Vezi EK"),"")</f>
         <v/>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="AA3" t="str">
-        <f t="shared" ref="AA3:AA34" si="5">IF(W3="DB", IF(V3=INT(V3),"OK", "Vezi EK"),"")</f>
+        <f t="shared" ref="AA3:AA34" si="5">IF(OR(W3="DB PAL",W3="DB MDF"), IF(V3=INT(V3),"OK", "Vezi EK"),"")</f>
         <v/>
       </c>
     </row>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF304B4-D3B9-4A67-BF49-D7AFDA3F93EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065672EA-1C6E-4F2D-ADD4-40FE676DD28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1804,6 +1804,162 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1819,12 +1975,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1843,12 +1993,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1875,12 +2019,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1946,144 +2084,6 @@
     <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2570,33 +2570,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="210" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="235"/>
-      <c r="K1" s="235"/>
-      <c r="L1" s="236"/>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="212"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="219" t="s">
+      <c r="O1" s="199" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="221"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="201"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2615,165 +2615,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="222"/>
-      <c r="P2" s="223"/>
-      <c r="Q2" s="223"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="224"/>
+      <c r="O2" s="202"/>
+      <c r="P2" s="203"/>
+      <c r="Q2" s="203"/>
+      <c r="R2" s="203"/>
+      <c r="S2" s="204"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="242"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="244"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="175"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="177"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="225"/>
+      <c r="K3" s="226"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="237"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="239"/>
+      <c r="O3" s="213"/>
+      <c r="P3" s="195"/>
+      <c r="Q3" s="195"/>
+      <c r="R3" s="195"/>
+      <c r="S3" s="196"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="215"/>
+      <c r="B4" s="256"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="258"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="216"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="218"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="261"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="237"/>
-      <c r="P4" s="238"/>
-      <c r="Q4" s="238"/>
-      <c r="R4" s="238"/>
-      <c r="S4" s="239"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="195"/>
+      <c r="Q4" s="195"/>
+      <c r="R4" s="195"/>
+      <c r="S4" s="196"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="252"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="254"/>
+      <c r="B5" s="183"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="185"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="261"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="239"/>
+      <c r="I5" s="194"/>
+      <c r="J5" s="195"/>
+      <c r="K5" s="196"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="237"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="238"/>
-      <c r="R5" s="238"/>
-      <c r="S5" s="239"/>
+      <c r="O5" s="213"/>
+      <c r="P5" s="195"/>
+      <c r="Q5" s="195"/>
+      <c r="R5" s="195"/>
+      <c r="S5" s="196"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="257"/>
-      <c r="C6" s="258"/>
-      <c r="D6" s="259"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="190"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="260"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="227"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="192"/>
+      <c r="K6" s="193"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="225"/>
-      <c r="P6" s="226"/>
-      <c r="Q6" s="226"/>
-      <c r="R6" s="226"/>
-      <c r="S6" s="227"/>
+      <c r="O6" s="205"/>
+      <c r="P6" s="192"/>
+      <c r="Q6" s="192"/>
+      <c r="R6" s="192"/>
+      <c r="S6" s="193"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="181" t="s">
+      <c r="A8" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="182"/>
-      <c r="C8" s="182"/>
-      <c r="D8" s="183"/>
-      <c r="F8" s="228" t="s">
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="230"/>
+      <c r="F8" s="197" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="229"/>
-      <c r="Q8" s="229"/>
-      <c r="R8" s="229"/>
-      <c r="S8" s="230"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="198"/>
+      <c r="I8" s="198"/>
+      <c r="J8" s="198"/>
+      <c r="K8" s="198"/>
+      <c r="L8" s="198"/>
+      <c r="M8" s="198"/>
+      <c r="N8" s="198"/>
+      <c r="O8" s="198"/>
+      <c r="P8" s="198"/>
+      <c r="Q8" s="198"/>
+      <c r="R8" s="198"/>
+      <c r="S8" s="206"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="184"/>
-      <c r="B9" s="185"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="186"/>
-      <c r="F9" s="209" t="s">
+      <c r="A9" s="231"/>
+      <c r="B9" s="232"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="233"/>
+      <c r="F9" s="252" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="210"/>
-      <c r="H9" s="255" t="s">
+      <c r="G9" s="253"/>
+      <c r="H9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="256"/>
-      <c r="J9" s="207" t="s">
+      <c r="I9" s="187"/>
+      <c r="J9" s="250" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="208"/>
-      <c r="L9" s="250" t="s">
+      <c r="K9" s="251"/>
+      <c r="L9" s="181" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="251"/>
-      <c r="N9" s="187" t="s">
+      <c r="M9" s="182"/>
+      <c r="N9" s="218" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="188"/>
-      <c r="P9" s="202" t="s">
+      <c r="O9" s="219"/>
+      <c r="P9" s="245" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="203"/>
-      <c r="R9" s="187" t="s">
+      <c r="Q9" s="246"/>
+      <c r="R9" s="218" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="188"/>
+      <c r="S9" s="219"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="240" t="s">
+      <c r="A10" s="214" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2830,7 +2830,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="179"/>
+      <c r="A11" s="215"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2927,7 +2927,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="179"/>
+      <c r="A12" s="215"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3024,7 +3024,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="179"/>
+      <c r="A13" s="215"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3121,7 +3121,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="179"/>
+      <c r="A14" s="215"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3199,7 +3199,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="179"/>
+      <c r="A15" s="215"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3277,7 +3277,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="179"/>
+      <c r="A16" s="215"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3355,7 +3355,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="179"/>
+      <c r="A17" s="215"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3433,7 +3433,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="179"/>
+      <c r="A18" s="215"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="179"/>
+      <c r="A19" s="215"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3589,7 +3589,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="179"/>
+      <c r="A20" s="215"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3667,7 +3667,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="179"/>
+      <c r="A21" s="215"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="241"/>
+      <c r="A22" s="216"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3879,7 +3879,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="240" t="s">
+      <c r="A24" s="214" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3978,7 +3978,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="179"/>
+      <c r="A25" s="215"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4075,7 +4075,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="179"/>
+      <c r="A26" s="215"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4172,7 +4172,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="179"/>
+      <c r="A27" s="215"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="180"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4403,7 +4403,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="204" t="s">
+      <c r="A32" s="247" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4482,7 +4482,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="205"/>
+      <c r="A33" s="248"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4559,7 +4559,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="206"/>
+      <c r="A34" s="249"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4657,7 +4657,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="204" t="s">
+      <c r="A36" s="247" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4736,7 +4736,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="205"/>
+      <c r="A37" s="248"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4813,7 +4813,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="206"/>
+      <c r="A38" s="249"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4904,7 +4904,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="240" t="s">
+      <c r="A40" s="214" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4916,25 +4916,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="231" t="s">
+      <c r="F40" s="207" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="232"/>
-      <c r="H40" s="232"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="232"/>
-      <c r="O40" s="232"/>
-      <c r="P40" s="232"/>
-      <c r="Q40" s="232"/>
-      <c r="R40" s="232"/>
-      <c r="S40" s="233"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
+      <c r="N40" s="208"/>
+      <c r="O40" s="208"/>
+      <c r="P40" s="208"/>
+      <c r="Q40" s="208"/>
+      <c r="R40" s="208"/>
+      <c r="S40" s="209"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="179"/>
+      <c r="A41" s="215"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -4997,7 +4997,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="179"/>
+      <c r="A42" s="215"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5022,13 +5022,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="198">
+      <c r="S42" s="175">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="179"/>
+      <c r="A43" s="215"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5040,26 +5040,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="228" t="str">
+      <c r="F43" s="197" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="229"/>
-      <c r="H43" s="229"/>
-      <c r="I43" s="229"/>
-      <c r="J43" s="229"/>
-      <c r="K43" s="229"/>
-      <c r="L43" s="229"/>
-      <c r="M43" s="229"/>
-      <c r="N43" s="229"/>
-      <c r="O43" s="229"/>
-      <c r="P43" s="229"/>
-      <c r="Q43" s="229"/>
-      <c r="R43" s="229"/>
-      <c r="S43" s="245"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="198"/>
+      <c r="N43" s="198"/>
+      <c r="O43" s="198"/>
+      <c r="P43" s="198"/>
+      <c r="Q43" s="198"/>
+      <c r="R43" s="198"/>
+      <c r="S43" s="176"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="179"/>
+      <c r="A44" s="215"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5115,7 +5115,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="179"/>
+      <c r="A45" s="215"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5249,7 +5249,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="179"/>
+      <c r="A46" s="215"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5263,7 +5263,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="179"/>
+      <c r="A47" s="215"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5274,50 +5274,50 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="198" t="s">
+      <c r="F47" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="211" t="str">
+      <c r="G47" s="254" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="198" t="s">
+      <c r="J47" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="200">
+      <c r="K47" s="243">
         <v>1</v>
       </c>
-      <c r="N47" s="198" t="s">
+      <c r="N47" s="175" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="246"/>
-      <c r="P47" s="247"/>
-      <c r="R47" s="198" t="s">
+      <c r="O47" s="177"/>
+      <c r="P47" s="178"/>
+      <c r="R47" s="175" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="198"/>
+      <c r="S47" s="175"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="180"/>
+      <c r="A48" s="217"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
       <c r="C48" s="31">
-        <f>ROUND(SUM(F45:S45),0)</f>
+        <f>ROUND(SUM(F45:S45),0)*2</f>
         <v>0</v>
       </c>
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="199"/>
-      <c r="G48" s="212"/>
-      <c r="J48" s="199"/>
-      <c r="K48" s="201"/>
-      <c r="N48" s="245"/>
-      <c r="O48" s="248"/>
-      <c r="P48" s="249"/>
-      <c r="R48" s="245"/>
-      <c r="S48" s="199"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="255"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="244"/>
+      <c r="N48" s="176"/>
+      <c r="O48" s="179"/>
+      <c r="P48" s="180"/>
+      <c r="R48" s="176"/>
+      <c r="S48" s="223"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5326,187 +5326,193 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="178" t="s">
+      <c r="A50" s="227" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="189"/>
-      <c r="C50" s="190"/>
-      <c r="D50" s="190"/>
-      <c r="E50" s="190"/>
-      <c r="F50" s="190"/>
-      <c r="G50" s="190"/>
-      <c r="H50" s="190"/>
-      <c r="I50" s="190"/>
-      <c r="J50" s="190"/>
-      <c r="K50" s="190"/>
-      <c r="L50" s="190"/>
-      <c r="M50" s="190"/>
-      <c r="N50" s="190"/>
-      <c r="O50" s="190"/>
-      <c r="P50" s="190"/>
-      <c r="Q50" s="190"/>
-      <c r="R50" s="190"/>
-      <c r="S50" s="191"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="235"/>
+      <c r="D50" s="235"/>
+      <c r="E50" s="235"/>
+      <c r="F50" s="235"/>
+      <c r="G50" s="235"/>
+      <c r="H50" s="235"/>
+      <c r="I50" s="235"/>
+      <c r="J50" s="235"/>
+      <c r="K50" s="235"/>
+      <c r="L50" s="235"/>
+      <c r="M50" s="235"/>
+      <c r="N50" s="235"/>
+      <c r="O50" s="235"/>
+      <c r="P50" s="235"/>
+      <c r="Q50" s="235"/>
+      <c r="R50" s="235"/>
+      <c r="S50" s="236"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="179"/>
-      <c r="B51" s="192"/>
-      <c r="C51" s="193"/>
-      <c r="D51" s="193"/>
-      <c r="E51" s="193"/>
-      <c r="F51" s="193"/>
-      <c r="G51" s="193"/>
-      <c r="H51" s="193"/>
-      <c r="I51" s="193"/>
-      <c r="J51" s="193"/>
-      <c r="K51" s="193"/>
-      <c r="L51" s="193"/>
-      <c r="M51" s="193"/>
-      <c r="N51" s="193"/>
-      <c r="O51" s="193"/>
-      <c r="P51" s="193"/>
-      <c r="Q51" s="193"/>
-      <c r="R51" s="193"/>
-      <c r="S51" s="194"/>
+      <c r="A51" s="215"/>
+      <c r="B51" s="237"/>
+      <c r="C51" s="238"/>
+      <c r="D51" s="238"/>
+      <c r="E51" s="238"/>
+      <c r="F51" s="238"/>
+      <c r="G51" s="238"/>
+      <c r="H51" s="238"/>
+      <c r="I51" s="238"/>
+      <c r="J51" s="238"/>
+      <c r="K51" s="238"/>
+      <c r="L51" s="238"/>
+      <c r="M51" s="238"/>
+      <c r="N51" s="238"/>
+      <c r="O51" s="238"/>
+      <c r="P51" s="238"/>
+      <c r="Q51" s="238"/>
+      <c r="R51" s="238"/>
+      <c r="S51" s="239"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="179"/>
-      <c r="B52" s="192"/>
-      <c r="C52" s="193"/>
-      <c r="D52" s="193"/>
-      <c r="E52" s="193"/>
-      <c r="F52" s="193"/>
-      <c r="G52" s="193"/>
-      <c r="H52" s="193"/>
-      <c r="I52" s="193"/>
-      <c r="J52" s="193"/>
-      <c r="K52" s="193"/>
-      <c r="L52" s="193"/>
-      <c r="M52" s="193"/>
-      <c r="N52" s="193"/>
-      <c r="O52" s="193"/>
-      <c r="P52" s="193"/>
-      <c r="Q52" s="193"/>
-      <c r="R52" s="193"/>
-      <c r="S52" s="194"/>
+      <c r="A52" s="215"/>
+      <c r="B52" s="237"/>
+      <c r="C52" s="238"/>
+      <c r="D52" s="238"/>
+      <c r="E52" s="238"/>
+      <c r="F52" s="238"/>
+      <c r="G52" s="238"/>
+      <c r="H52" s="238"/>
+      <c r="I52" s="238"/>
+      <c r="J52" s="238"/>
+      <c r="K52" s="238"/>
+      <c r="L52" s="238"/>
+      <c r="M52" s="238"/>
+      <c r="N52" s="238"/>
+      <c r="O52" s="238"/>
+      <c r="P52" s="238"/>
+      <c r="Q52" s="238"/>
+      <c r="R52" s="238"/>
+      <c r="S52" s="239"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="179"/>
-      <c r="B53" s="192"/>
-      <c r="C53" s="193"/>
-      <c r="D53" s="193"/>
-      <c r="E53" s="193"/>
-      <c r="F53" s="193"/>
-      <c r="G53" s="193"/>
-      <c r="H53" s="193"/>
-      <c r="I53" s="193"/>
-      <c r="J53" s="193"/>
-      <c r="K53" s="193"/>
-      <c r="L53" s="193"/>
-      <c r="M53" s="193"/>
-      <c r="N53" s="193"/>
-      <c r="O53" s="193"/>
-      <c r="P53" s="193"/>
-      <c r="Q53" s="193"/>
-      <c r="R53" s="193"/>
-      <c r="S53" s="194"/>
+      <c r="A53" s="215"/>
+      <c r="B53" s="237"/>
+      <c r="C53" s="238"/>
+      <c r="D53" s="238"/>
+      <c r="E53" s="238"/>
+      <c r="F53" s="238"/>
+      <c r="G53" s="238"/>
+      <c r="H53" s="238"/>
+      <c r="I53" s="238"/>
+      <c r="J53" s="238"/>
+      <c r="K53" s="238"/>
+      <c r="L53" s="238"/>
+      <c r="M53" s="238"/>
+      <c r="N53" s="238"/>
+      <c r="O53" s="238"/>
+      <c r="P53" s="238"/>
+      <c r="Q53" s="238"/>
+      <c r="R53" s="238"/>
+      <c r="S53" s="239"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="179"/>
-      <c r="B54" s="192"/>
-      <c r="C54" s="193"/>
-      <c r="D54" s="193"/>
-      <c r="E54" s="193"/>
-      <c r="F54" s="193"/>
-      <c r="G54" s="193"/>
-      <c r="H54" s="193"/>
-      <c r="I54" s="193"/>
-      <c r="J54" s="193"/>
-      <c r="K54" s="193"/>
-      <c r="L54" s="193"/>
-      <c r="M54" s="193"/>
-      <c r="N54" s="193"/>
-      <c r="O54" s="193"/>
-      <c r="P54" s="193"/>
-      <c r="Q54" s="193"/>
-      <c r="R54" s="193"/>
-      <c r="S54" s="194"/>
+      <c r="A54" s="215"/>
+      <c r="B54" s="237"/>
+      <c r="C54" s="238"/>
+      <c r="D54" s="238"/>
+      <c r="E54" s="238"/>
+      <c r="F54" s="238"/>
+      <c r="G54" s="238"/>
+      <c r="H54" s="238"/>
+      <c r="I54" s="238"/>
+      <c r="J54" s="238"/>
+      <c r="K54" s="238"/>
+      <c r="L54" s="238"/>
+      <c r="M54" s="238"/>
+      <c r="N54" s="238"/>
+      <c r="O54" s="238"/>
+      <c r="P54" s="238"/>
+      <c r="Q54" s="238"/>
+      <c r="R54" s="238"/>
+      <c r="S54" s="239"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="179"/>
-      <c r="B55" s="192"/>
-      <c r="C55" s="193"/>
-      <c r="D55" s="193"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
-      <c r="G55" s="193"/>
-      <c r="H55" s="193"/>
-      <c r="I55" s="193"/>
-      <c r="J55" s="193"/>
-      <c r="K55" s="193"/>
-      <c r="L55" s="193"/>
-      <c r="M55" s="193"/>
-      <c r="N55" s="193"/>
-      <c r="O55" s="193"/>
-      <c r="P55" s="193"/>
-      <c r="Q55" s="193"/>
-      <c r="R55" s="193"/>
-      <c r="S55" s="194"/>
+      <c r="A55" s="215"/>
+      <c r="B55" s="237"/>
+      <c r="C55" s="238"/>
+      <c r="D55" s="238"/>
+      <c r="E55" s="238"/>
+      <c r="F55" s="238"/>
+      <c r="G55" s="238"/>
+      <c r="H55" s="238"/>
+      <c r="I55" s="238"/>
+      <c r="J55" s="238"/>
+      <c r="K55" s="238"/>
+      <c r="L55" s="238"/>
+      <c r="M55" s="238"/>
+      <c r="N55" s="238"/>
+      <c r="O55" s="238"/>
+      <c r="P55" s="238"/>
+      <c r="Q55" s="238"/>
+      <c r="R55" s="238"/>
+      <c r="S55" s="239"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="179"/>
-      <c r="B56" s="192"/>
-      <c r="C56" s="193"/>
-      <c r="D56" s="193"/>
-      <c r="E56" s="193"/>
-      <c r="F56" s="193"/>
-      <c r="G56" s="193"/>
-      <c r="H56" s="193"/>
-      <c r="I56" s="193"/>
-      <c r="J56" s="193"/>
-      <c r="K56" s="193"/>
-      <c r="L56" s="193"/>
-      <c r="M56" s="193"/>
-      <c r="N56" s="193"/>
-      <c r="O56" s="193"/>
-      <c r="P56" s="193"/>
-      <c r="Q56" s="193"/>
-      <c r="R56" s="193"/>
-      <c r="S56" s="194"/>
+      <c r="A56" s="215"/>
+      <c r="B56" s="237"/>
+      <c r="C56" s="238"/>
+      <c r="D56" s="238"/>
+      <c r="E56" s="238"/>
+      <c r="F56" s="238"/>
+      <c r="G56" s="238"/>
+      <c r="H56" s="238"/>
+      <c r="I56" s="238"/>
+      <c r="J56" s="238"/>
+      <c r="K56" s="238"/>
+      <c r="L56" s="238"/>
+      <c r="M56" s="238"/>
+      <c r="N56" s="238"/>
+      <c r="O56" s="238"/>
+      <c r="P56" s="238"/>
+      <c r="Q56" s="238"/>
+      <c r="R56" s="238"/>
+      <c r="S56" s="239"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="180"/>
-      <c r="B57" s="195"/>
-      <c r="C57" s="196"/>
-      <c r="D57" s="196"/>
-      <c r="E57" s="196"/>
-      <c r="F57" s="196"/>
-      <c r="G57" s="196"/>
-      <c r="H57" s="196"/>
-      <c r="I57" s="196"/>
-      <c r="J57" s="196"/>
-      <c r="K57" s="196"/>
-      <c r="L57" s="196"/>
-      <c r="M57" s="196"/>
-      <c r="N57" s="196"/>
-      <c r="O57" s="196"/>
-      <c r="P57" s="196"/>
-      <c r="Q57" s="196"/>
-      <c r="R57" s="196"/>
-      <c r="S57" s="197"/>
+      <c r="A57" s="217"/>
+      <c r="B57" s="240"/>
+      <c r="C57" s="241"/>
+      <c r="D57" s="241"/>
+      <c r="E57" s="241"/>
+      <c r="F57" s="241"/>
+      <c r="G57" s="241"/>
+      <c r="H57" s="241"/>
+      <c r="I57" s="241"/>
+      <c r="J57" s="241"/>
+      <c r="K57" s="241"/>
+      <c r="L57" s="241"/>
+      <c r="M57" s="241"/>
+      <c r="N57" s="241"/>
+      <c r="O57" s="241"/>
+      <c r="P57" s="241"/>
+      <c r="Q57" s="241"/>
+      <c r="R57" s="241"/>
+      <c r="S57" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B50:S57"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="O6:S6"/>
@@ -5523,22 +5529,16 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="R47:R48"/>
     <mergeCell ref="S47:S48"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="B50:S57"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065672EA-1C6E-4F2D-ADD4-40FE676DD28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53A0577-25BB-4076-8817-53515D8636CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1804,8 +1804,229 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1861,229 +2082,8 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2570,33 +2570,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="234" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="212"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
+      <c r="L1" s="236"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="199" t="s">
+      <c r="O1" s="219" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="201"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="221"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2615,165 +2615,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="202"/>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="203"/>
-      <c r="R2" s="203"/>
-      <c r="S2" s="204"/>
+      <c r="O2" s="222"/>
+      <c r="P2" s="223"/>
+      <c r="Q2" s="223"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="224"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="220"/>
-      <c r="C3" s="221"/>
-      <c r="D3" s="222"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="244"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="225"/>
-      <c r="K3" s="226"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="177"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="195"/>
-      <c r="Q3" s="195"/>
-      <c r="R3" s="195"/>
-      <c r="S3" s="196"/>
+      <c r="O3" s="237"/>
+      <c r="P3" s="238"/>
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="239"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="256"/>
-      <c r="C4" s="257"/>
-      <c r="D4" s="258"/>
+      <c r="B4" s="213"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="215"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="259"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="261"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="218"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="195"/>
-      <c r="Q4" s="195"/>
-      <c r="R4" s="195"/>
-      <c r="S4" s="196"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="238"/>
+      <c r="Q4" s="238"/>
+      <c r="R4" s="238"/>
+      <c r="S4" s="239"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="185"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="254"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="194"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="196"/>
+      <c r="I5" s="261"/>
+      <c r="J5" s="238"/>
+      <c r="K5" s="239"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="213"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="195"/>
-      <c r="R5" s="195"/>
-      <c r="S5" s="196"/>
+      <c r="O5" s="237"/>
+      <c r="P5" s="238"/>
+      <c r="Q5" s="238"/>
+      <c r="R5" s="238"/>
+      <c r="S5" s="239"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="188"/>
-      <c r="C6" s="189"/>
-      <c r="D6" s="190"/>
+      <c r="B6" s="257"/>
+      <c r="C6" s="258"/>
+      <c r="D6" s="259"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="191"/>
-      <c r="J6" s="192"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="260"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="227"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="205"/>
-      <c r="P6" s="192"/>
-      <c r="Q6" s="192"/>
-      <c r="R6" s="192"/>
-      <c r="S6" s="193"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="226"/>
+      <c r="Q6" s="226"/>
+      <c r="R6" s="226"/>
+      <c r="S6" s="227"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="228" t="s">
+      <c r="A8" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="230"/>
-      <c r="F8" s="197" t="s">
+      <c r="B8" s="182"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="183"/>
+      <c r="F8" s="228" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="198"/>
-      <c r="H8" s="198"/>
-      <c r="I8" s="198"/>
-      <c r="J8" s="198"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="198"/>
-      <c r="O8" s="198"/>
-      <c r="P8" s="198"/>
-      <c r="Q8" s="198"/>
-      <c r="R8" s="198"/>
-      <c r="S8" s="206"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="229"/>
+      <c r="P8" s="229"/>
+      <c r="Q8" s="229"/>
+      <c r="R8" s="229"/>
+      <c r="S8" s="230"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="231"/>
-      <c r="B9" s="232"/>
-      <c r="C9" s="232"/>
-      <c r="D9" s="233"/>
-      <c r="F9" s="252" t="s">
+      <c r="A9" s="184"/>
+      <c r="B9" s="185"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="186"/>
+      <c r="F9" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="253"/>
-      <c r="H9" s="186" t="s">
+      <c r="G9" s="210"/>
+      <c r="H9" s="255" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="187"/>
-      <c r="J9" s="250" t="s">
+      <c r="I9" s="256"/>
+      <c r="J9" s="207" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="251"/>
-      <c r="L9" s="181" t="s">
+      <c r="K9" s="208"/>
+      <c r="L9" s="250" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="182"/>
-      <c r="N9" s="218" t="s">
+      <c r="M9" s="251"/>
+      <c r="N9" s="187" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="219"/>
-      <c r="P9" s="245" t="s">
+      <c r="O9" s="188"/>
+      <c r="P9" s="202" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="218" t="s">
+      <c r="Q9" s="203"/>
+      <c r="R9" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="219"/>
+      <c r="S9" s="188"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="214" t="s">
+      <c r="A10" s="240" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2830,7 +2830,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="215"/>
+      <c r="A11" s="179"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2927,7 +2927,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="215"/>
+      <c r="A12" s="179"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3024,7 +3024,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="215"/>
+      <c r="A13" s="179"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3121,7 +3121,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="215"/>
+      <c r="A14" s="179"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3199,7 +3199,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="215"/>
+      <c r="A15" s="179"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3277,7 +3277,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="215"/>
+      <c r="A16" s="179"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3355,7 +3355,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="215"/>
+      <c r="A17" s="179"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3433,7 +3433,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="215"/>
+      <c r="A18" s="179"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="215"/>
+      <c r="A19" s="179"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3589,7 +3589,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="215"/>
+      <c r="A20" s="179"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3667,7 +3667,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="215"/>
+      <c r="A21" s="179"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="216"/>
+      <c r="A22" s="241"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3879,7 +3879,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="214" t="s">
+      <c r="A24" s="240" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3978,7 +3978,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="215"/>
+      <c r="A25" s="179"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4075,7 +4075,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="215"/>
+      <c r="A26" s="179"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4172,7 +4172,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="215"/>
+      <c r="A27" s="179"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="217"/>
+      <c r="A28" s="180"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4403,7 +4403,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="247" t="s">
+      <c r="A32" s="204" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4482,7 +4482,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="248"/>
+      <c r="A33" s="205"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4559,7 +4559,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="249"/>
+      <c r="A34" s="206"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4657,7 +4657,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="247" t="s">
+      <c r="A36" s="204" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4736,7 +4736,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="248"/>
+      <c r="A37" s="205"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4813,7 +4813,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="249"/>
+      <c r="A38" s="206"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4904,7 +4904,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="214" t="s">
+      <c r="A40" s="240" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4916,25 +4916,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="207" t="s">
+      <c r="F40" s="231" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="208"/>
-      <c r="L40" s="208"/>
-      <c r="M40" s="208"/>
-      <c r="N40" s="208"/>
-      <c r="O40" s="208"/>
-      <c r="P40" s="208"/>
-      <c r="Q40" s="208"/>
-      <c r="R40" s="208"/>
-      <c r="S40" s="209"/>
+      <c r="G40" s="232"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="232"/>
+      <c r="O40" s="232"/>
+      <c r="P40" s="232"/>
+      <c r="Q40" s="232"/>
+      <c r="R40" s="232"/>
+      <c r="S40" s="233"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="215"/>
+      <c r="A41" s="179"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -4997,7 +4997,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="215"/>
+      <c r="A42" s="179"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5022,13 +5022,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="175">
+      <c r="S42" s="198">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="215"/>
+      <c r="A43" s="179"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5040,26 +5040,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="197" t="str">
+      <c r="F43" s="228" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="198"/>
-      <c r="H43" s="198"/>
-      <c r="I43" s="198"/>
-      <c r="J43" s="198"/>
-      <c r="K43" s="198"/>
-      <c r="L43" s="198"/>
-      <c r="M43" s="198"/>
-      <c r="N43" s="198"/>
-      <c r="O43" s="198"/>
-      <c r="P43" s="198"/>
-      <c r="Q43" s="198"/>
-      <c r="R43" s="198"/>
-      <c r="S43" s="176"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="229"/>
+      <c r="J43" s="229"/>
+      <c r="K43" s="229"/>
+      <c r="L43" s="229"/>
+      <c r="M43" s="229"/>
+      <c r="N43" s="229"/>
+      <c r="O43" s="229"/>
+      <c r="P43" s="229"/>
+      <c r="Q43" s="229"/>
+      <c r="R43" s="229"/>
+      <c r="S43" s="245"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="215"/>
+      <c r="A44" s="179"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5115,7 +5115,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="215"/>
+      <c r="A45" s="179"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v/>
       </c>
       <c r="G45" s="31" t="str">
-        <f>IFERROR(IF(F45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(F45,Deco!$Z$2:$Z$100,0)),""),"")</f>
+        <f>IFERROR(IF(F45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(F45,Deco!$Z$2:$Z$100,0))*2,""),"")</f>
         <v/>
       </c>
       <c r="H45" s="43" t="str" cm="1">
@@ -5159,7 +5159,7 @@
         <v/>
       </c>
       <c r="I45" s="31" t="str">
-        <f>IFERROR(IF(H45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(H45,Deco!$Z$2:$Z$100,0)),""),"")</f>
+        <f>IFERROR(IF(H45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(H45,Deco!$Z$2:$Z$100,0))*2,""),"")</f>
         <v/>
       </c>
       <c r="J45" s="71" t="str" cm="1">
@@ -5176,7 +5176,7 @@
         <v/>
       </c>
       <c r="K45" s="31" t="str">
-        <f>IFERROR(IF(J45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(J45,Deco!$Z$2:$Z$100,0)),""),"")</f>
+        <f>IFERROR(IF(J45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(J45,Deco!$Z$2:$Z$100,0))*2,""),"")</f>
         <v/>
       </c>
       <c r="L45" s="71" t="str" cm="1">
@@ -5193,7 +5193,7 @@
         <v/>
       </c>
       <c r="M45" s="31" t="str">
-        <f>IFERROR(IF(L45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(L45,Deco!$Z$2:$Z$100,0)),""),"")</f>
+        <f>IFERROR(IF(L45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(L45,Deco!$Z$2:$Z$100,0))*2,""),"")</f>
         <v/>
       </c>
       <c r="N45" s="71" t="str" cm="1">
@@ -5210,7 +5210,7 @@
         <v/>
       </c>
       <c r="O45" s="31" t="str">
-        <f>IFERROR(IF(N45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(N45,Deco!$Z$2:$Z$100,0)),""),"")</f>
+        <f>IFERROR(IF(N45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(N45,Deco!$Z$2:$Z$100,0))*2,""),"")</f>
         <v/>
       </c>
       <c r="P45" s="71" t="str" cm="1">
@@ -5227,7 +5227,7 @@
         <v/>
       </c>
       <c r="Q45" s="31" t="str">
-        <f>IFERROR(IF(P45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(P45,Deco!$Z$2:$Z$100,0)),""),"")</f>
+        <f>IFERROR(IF(P45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(P45,Deco!$Z$2:$Z$100,0))*2,""),"")</f>
         <v/>
       </c>
       <c r="R45" s="71" t="str" cm="1">
@@ -5244,12 +5244,12 @@
         <v/>
       </c>
       <c r="S45" s="44" t="str">
-        <f>IFERROR(IF(R45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(R45,Deco!$Z$2:$Z$100,0)),""),"")</f>
+        <f>IFERROR(IF(R45&lt;&gt;"",INDEX(Deco!$V$2:$V$100,MATCH(R45,Deco!$Z$2:$Z$100,0))*2,""),"")</f>
         <v/>
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="215"/>
+      <c r="A46" s="179"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5263,7 +5263,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="215"/>
+      <c r="A47" s="179"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5274,31 +5274,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="175" t="s">
+      <c r="F47" s="198" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="254" t="str">
+      <c r="G47" s="211" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="175" t="s">
+      <c r="J47" s="198" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="243">
+      <c r="K47" s="200">
         <v>1</v>
       </c>
-      <c r="N47" s="175" t="s">
+      <c r="N47" s="198" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="177"/>
-      <c r="P47" s="178"/>
-      <c r="R47" s="175" t="s">
+      <c r="O47" s="246"/>
+      <c r="P47" s="247"/>
+      <c r="R47" s="198" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="175"/>
+      <c r="S47" s="198"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="217"/>
+      <c r="A48" s="180"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5309,15 +5309,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="223"/>
-      <c r="G48" s="255"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="244"/>
-      <c r="N48" s="176"/>
-      <c r="O48" s="179"/>
-      <c r="P48" s="180"/>
-      <c r="R48" s="176"/>
-      <c r="S48" s="223"/>
+      <c r="F48" s="199"/>
+      <c r="G48" s="212"/>
+      <c r="J48" s="199"/>
+      <c r="K48" s="201"/>
+      <c r="N48" s="245"/>
+      <c r="O48" s="248"/>
+      <c r="P48" s="249"/>
+      <c r="R48" s="245"/>
+      <c r="S48" s="199"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5326,177 +5326,203 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="227" t="s">
+      <c r="A50" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="234"/>
-      <c r="C50" s="235"/>
-      <c r="D50" s="235"/>
-      <c r="E50" s="235"/>
-      <c r="F50" s="235"/>
-      <c r="G50" s="235"/>
-      <c r="H50" s="235"/>
-      <c r="I50" s="235"/>
-      <c r="J50" s="235"/>
-      <c r="K50" s="235"/>
-      <c r="L50" s="235"/>
-      <c r="M50" s="235"/>
-      <c r="N50" s="235"/>
-      <c r="O50" s="235"/>
-      <c r="P50" s="235"/>
-      <c r="Q50" s="235"/>
-      <c r="R50" s="235"/>
-      <c r="S50" s="236"/>
+      <c r="B50" s="189"/>
+      <c r="C50" s="190"/>
+      <c r="D50" s="190"/>
+      <c r="E50" s="190"/>
+      <c r="F50" s="190"/>
+      <c r="G50" s="190"/>
+      <c r="H50" s="190"/>
+      <c r="I50" s="190"/>
+      <c r="J50" s="190"/>
+      <c r="K50" s="190"/>
+      <c r="L50" s="190"/>
+      <c r="M50" s="190"/>
+      <c r="N50" s="190"/>
+      <c r="O50" s="190"/>
+      <c r="P50" s="190"/>
+      <c r="Q50" s="190"/>
+      <c r="R50" s="190"/>
+      <c r="S50" s="191"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="215"/>
-      <c r="B51" s="237"/>
-      <c r="C51" s="238"/>
-      <c r="D51" s="238"/>
-      <c r="E51" s="238"/>
-      <c r="F51" s="238"/>
-      <c r="G51" s="238"/>
-      <c r="H51" s="238"/>
-      <c r="I51" s="238"/>
-      <c r="J51" s="238"/>
-      <c r="K51" s="238"/>
-      <c r="L51" s="238"/>
-      <c r="M51" s="238"/>
-      <c r="N51" s="238"/>
-      <c r="O51" s="238"/>
-      <c r="P51" s="238"/>
-      <c r="Q51" s="238"/>
-      <c r="R51" s="238"/>
-      <c r="S51" s="239"/>
+      <c r="A51" s="179"/>
+      <c r="B51" s="192"/>
+      <c r="C51" s="193"/>
+      <c r="D51" s="193"/>
+      <c r="E51" s="193"/>
+      <c r="F51" s="193"/>
+      <c r="G51" s="193"/>
+      <c r="H51" s="193"/>
+      <c r="I51" s="193"/>
+      <c r="J51" s="193"/>
+      <c r="K51" s="193"/>
+      <c r="L51" s="193"/>
+      <c r="M51" s="193"/>
+      <c r="N51" s="193"/>
+      <c r="O51" s="193"/>
+      <c r="P51" s="193"/>
+      <c r="Q51" s="193"/>
+      <c r="R51" s="193"/>
+      <c r="S51" s="194"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="215"/>
-      <c r="B52" s="237"/>
-      <c r="C52" s="238"/>
-      <c r="D52" s="238"/>
-      <c r="E52" s="238"/>
-      <c r="F52" s="238"/>
-      <c r="G52" s="238"/>
-      <c r="H52" s="238"/>
-      <c r="I52" s="238"/>
-      <c r="J52" s="238"/>
-      <c r="K52" s="238"/>
-      <c r="L52" s="238"/>
-      <c r="M52" s="238"/>
-      <c r="N52" s="238"/>
-      <c r="O52" s="238"/>
-      <c r="P52" s="238"/>
-      <c r="Q52" s="238"/>
-      <c r="R52" s="238"/>
-      <c r="S52" s="239"/>
+      <c r="A52" s="179"/>
+      <c r="B52" s="192"/>
+      <c r="C52" s="193"/>
+      <c r="D52" s="193"/>
+      <c r="E52" s="193"/>
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="193"/>
+      <c r="J52" s="193"/>
+      <c r="K52" s="193"/>
+      <c r="L52" s="193"/>
+      <c r="M52" s="193"/>
+      <c r="N52" s="193"/>
+      <c r="O52" s="193"/>
+      <c r="P52" s="193"/>
+      <c r="Q52" s="193"/>
+      <c r="R52" s="193"/>
+      <c r="S52" s="194"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="215"/>
-      <c r="B53" s="237"/>
-      <c r="C53" s="238"/>
-      <c r="D53" s="238"/>
-      <c r="E53" s="238"/>
-      <c r="F53" s="238"/>
-      <c r="G53" s="238"/>
-      <c r="H53" s="238"/>
-      <c r="I53" s="238"/>
-      <c r="J53" s="238"/>
-      <c r="K53" s="238"/>
-      <c r="L53" s="238"/>
-      <c r="M53" s="238"/>
-      <c r="N53" s="238"/>
-      <c r="O53" s="238"/>
-      <c r="P53" s="238"/>
-      <c r="Q53" s="238"/>
-      <c r="R53" s="238"/>
-      <c r="S53" s="239"/>
+      <c r="A53" s="179"/>
+      <c r="B53" s="192"/>
+      <c r="C53" s="193"/>
+      <c r="D53" s="193"/>
+      <c r="E53" s="193"/>
+      <c r="F53" s="193"/>
+      <c r="G53" s="193"/>
+      <c r="H53" s="193"/>
+      <c r="I53" s="193"/>
+      <c r="J53" s="193"/>
+      <c r="K53" s="193"/>
+      <c r="L53" s="193"/>
+      <c r="M53" s="193"/>
+      <c r="N53" s="193"/>
+      <c r="O53" s="193"/>
+      <c r="P53" s="193"/>
+      <c r="Q53" s="193"/>
+      <c r="R53" s="193"/>
+      <c r="S53" s="194"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="215"/>
-      <c r="B54" s="237"/>
-      <c r="C54" s="238"/>
-      <c r="D54" s="238"/>
-      <c r="E54" s="238"/>
-      <c r="F54" s="238"/>
-      <c r="G54" s="238"/>
-      <c r="H54" s="238"/>
-      <c r="I54" s="238"/>
-      <c r="J54" s="238"/>
-      <c r="K54" s="238"/>
-      <c r="L54" s="238"/>
-      <c r="M54" s="238"/>
-      <c r="N54" s="238"/>
-      <c r="O54" s="238"/>
-      <c r="P54" s="238"/>
-      <c r="Q54" s="238"/>
-      <c r="R54" s="238"/>
-      <c r="S54" s="239"/>
+      <c r="A54" s="179"/>
+      <c r="B54" s="192"/>
+      <c r="C54" s="193"/>
+      <c r="D54" s="193"/>
+      <c r="E54" s="193"/>
+      <c r="F54" s="193"/>
+      <c r="G54" s="193"/>
+      <c r="H54" s="193"/>
+      <c r="I54" s="193"/>
+      <c r="J54" s="193"/>
+      <c r="K54" s="193"/>
+      <c r="L54" s="193"/>
+      <c r="M54" s="193"/>
+      <c r="N54" s="193"/>
+      <c r="O54" s="193"/>
+      <c r="P54" s="193"/>
+      <c r="Q54" s="193"/>
+      <c r="R54" s="193"/>
+      <c r="S54" s="194"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="215"/>
-      <c r="B55" s="237"/>
-      <c r="C55" s="238"/>
-      <c r="D55" s="238"/>
-      <c r="E55" s="238"/>
-      <c r="F55" s="238"/>
-      <c r="G55" s="238"/>
-      <c r="H55" s="238"/>
-      <c r="I55" s="238"/>
-      <c r="J55" s="238"/>
-      <c r="K55" s="238"/>
-      <c r="L55" s="238"/>
-      <c r="M55" s="238"/>
-      <c r="N55" s="238"/>
-      <c r="O55" s="238"/>
-      <c r="P55" s="238"/>
-      <c r="Q55" s="238"/>
-      <c r="R55" s="238"/>
-      <c r="S55" s="239"/>
+      <c r="A55" s="179"/>
+      <c r="B55" s="192"/>
+      <c r="C55" s="193"/>
+      <c r="D55" s="193"/>
+      <c r="E55" s="193"/>
+      <c r="F55" s="193"/>
+      <c r="G55" s="193"/>
+      <c r="H55" s="193"/>
+      <c r="I55" s="193"/>
+      <c r="J55" s="193"/>
+      <c r="K55" s="193"/>
+      <c r="L55" s="193"/>
+      <c r="M55" s="193"/>
+      <c r="N55" s="193"/>
+      <c r="O55" s="193"/>
+      <c r="P55" s="193"/>
+      <c r="Q55" s="193"/>
+      <c r="R55" s="193"/>
+      <c r="S55" s="194"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="215"/>
-      <c r="B56" s="237"/>
-      <c r="C56" s="238"/>
-      <c r="D56" s="238"/>
-      <c r="E56" s="238"/>
-      <c r="F56" s="238"/>
-      <c r="G56" s="238"/>
-      <c r="H56" s="238"/>
-      <c r="I56" s="238"/>
-      <c r="J56" s="238"/>
-      <c r="K56" s="238"/>
-      <c r="L56" s="238"/>
-      <c r="M56" s="238"/>
-      <c r="N56" s="238"/>
-      <c r="O56" s="238"/>
-      <c r="P56" s="238"/>
-      <c r="Q56" s="238"/>
-      <c r="R56" s="238"/>
-      <c r="S56" s="239"/>
+      <c r="A56" s="179"/>
+      <c r="B56" s="192"/>
+      <c r="C56" s="193"/>
+      <c r="D56" s="193"/>
+      <c r="E56" s="193"/>
+      <c r="F56" s="193"/>
+      <c r="G56" s="193"/>
+      <c r="H56" s="193"/>
+      <c r="I56" s="193"/>
+      <c r="J56" s="193"/>
+      <c r="K56" s="193"/>
+      <c r="L56" s="193"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="193"/>
+      <c r="O56" s="193"/>
+      <c r="P56" s="193"/>
+      <c r="Q56" s="193"/>
+      <c r="R56" s="193"/>
+      <c r="S56" s="194"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="217"/>
-      <c r="B57" s="240"/>
-      <c r="C57" s="241"/>
-      <c r="D57" s="241"/>
-      <c r="E57" s="241"/>
-      <c r="F57" s="241"/>
-      <c r="G57" s="241"/>
-      <c r="H57" s="241"/>
-      <c r="I57" s="241"/>
-      <c r="J57" s="241"/>
-      <c r="K57" s="241"/>
-      <c r="L57" s="241"/>
-      <c r="M57" s="241"/>
-      <c r="N57" s="241"/>
-      <c r="O57" s="241"/>
-      <c r="P57" s="241"/>
-      <c r="Q57" s="241"/>
-      <c r="R57" s="241"/>
-      <c r="S57" s="242"/>
+      <c r="A57" s="180"/>
+      <c r="B57" s="195"/>
+      <c r="C57" s="196"/>
+      <c r="D57" s="196"/>
+      <c r="E57" s="196"/>
+      <c r="F57" s="196"/>
+      <c r="G57" s="196"/>
+      <c r="H57" s="196"/>
+      <c r="I57" s="196"/>
+      <c r="J57" s="196"/>
+      <c r="K57" s="196"/>
+      <c r="L57" s="196"/>
+      <c r="M57" s="196"/>
+      <c r="N57" s="196"/>
+      <c r="O57" s="196"/>
+      <c r="P57" s="196"/>
+      <c r="Q57" s="196"/>
+      <c r="R57" s="196"/>
+      <c r="S57" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="F40:S40"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="A10:A22"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="S47:S48"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A57"/>
     <mergeCell ref="A8:D9"/>
@@ -5513,32 +5539,6 @@
     <mergeCell ref="G47:G48"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="F40:S40"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="A10:A22"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10821,7 +10821,7 @@
       <c r="T2" s="145"/>
       <c r="U2" s="145"/>
       <c r="V2" s="169" t="str">
-        <f>IFERROR(IF(OR(W2="DB PAL",W2="DB MDF"),Q2/13.5, ROUND(Q2/P2,2)),"")</f>
+        <f>IFERROR(IF(OR(W2="DB PAL",W2="DB MDF"),ROUND(Q2/13.5,0), ROUND(Q2/P2,2)),"")</f>
         <v/>
       </c>
       <c r="W2" t="str">
@@ -10930,7 +10930,7 @@
       <c r="T3" s="131"/>
       <c r="U3" s="145"/>
       <c r="V3" s="169" t="str">
-        <f t="shared" ref="V3:V34" si="1">IFERROR(IF(OR(W3="DB PAL",W3="DB MDF"),Q3/13.5, ROUND(Q3/P3,2)),"")</f>
+        <f t="shared" ref="V3:V34" si="1">IFERROR(IF(OR(W3="DB PAL",W3="DB MDF"),ROUND(Q3/13.5,0), ROUND(Q3/P3,2)),"")</f>
         <v/>
       </c>
       <c r="W3" t="str">

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53A0577-25BB-4076-8817-53515D8636CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB8C11F-8178-47B8-B19D-65806FD6F19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1804,6 +1804,162 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1819,12 +1975,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1843,12 +1993,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1875,12 +2019,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1946,144 +2084,6 @@
     <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2570,33 +2570,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="210" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="235"/>
-      <c r="K1" s="235"/>
-      <c r="L1" s="236"/>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="212"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="219" t="s">
+      <c r="O1" s="199" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="221"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="201"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2615,165 +2615,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="222"/>
-      <c r="P2" s="223"/>
-      <c r="Q2" s="223"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="224"/>
+      <c r="O2" s="202"/>
+      <c r="P2" s="203"/>
+      <c r="Q2" s="203"/>
+      <c r="R2" s="203"/>
+      <c r="S2" s="204"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="242"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="244"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="175"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="177"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="225"/>
+      <c r="K3" s="226"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="237"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="239"/>
+      <c r="O3" s="213"/>
+      <c r="P3" s="195"/>
+      <c r="Q3" s="195"/>
+      <c r="R3" s="195"/>
+      <c r="S3" s="196"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="215"/>
+      <c r="B4" s="256"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="258"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="216"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="218"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="261"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="237"/>
-      <c r="P4" s="238"/>
-      <c r="Q4" s="238"/>
-      <c r="R4" s="238"/>
-      <c r="S4" s="239"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="195"/>
+      <c r="Q4" s="195"/>
+      <c r="R4" s="195"/>
+      <c r="S4" s="196"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="252"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="254"/>
+      <c r="B5" s="183"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="185"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="261"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="239"/>
+      <c r="I5" s="194"/>
+      <c r="J5" s="195"/>
+      <c r="K5" s="196"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="237"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="238"/>
-      <c r="R5" s="238"/>
-      <c r="S5" s="239"/>
+      <c r="O5" s="213"/>
+      <c r="P5" s="195"/>
+      <c r="Q5" s="195"/>
+      <c r="R5" s="195"/>
+      <c r="S5" s="196"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="257"/>
-      <c r="C6" s="258"/>
-      <c r="D6" s="259"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="190"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="260"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="227"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="192"/>
+      <c r="K6" s="193"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="225"/>
-      <c r="P6" s="226"/>
-      <c r="Q6" s="226"/>
-      <c r="R6" s="226"/>
-      <c r="S6" s="227"/>
+      <c r="O6" s="205"/>
+      <c r="P6" s="192"/>
+      <c r="Q6" s="192"/>
+      <c r="R6" s="192"/>
+      <c r="S6" s="193"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="181" t="s">
+      <c r="A8" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="182"/>
-      <c r="C8" s="182"/>
-      <c r="D8" s="183"/>
-      <c r="F8" s="228" t="s">
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="230"/>
+      <c r="F8" s="197" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="229"/>
-      <c r="Q8" s="229"/>
-      <c r="R8" s="229"/>
-      <c r="S8" s="230"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="198"/>
+      <c r="I8" s="198"/>
+      <c r="J8" s="198"/>
+      <c r="K8" s="198"/>
+      <c r="L8" s="198"/>
+      <c r="M8" s="198"/>
+      <c r="N8" s="198"/>
+      <c r="O8" s="198"/>
+      <c r="P8" s="198"/>
+      <c r="Q8" s="198"/>
+      <c r="R8" s="198"/>
+      <c r="S8" s="206"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="184"/>
-      <c r="B9" s="185"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="186"/>
-      <c r="F9" s="209" t="s">
+      <c r="A9" s="231"/>
+      <c r="B9" s="232"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="233"/>
+      <c r="F9" s="252" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="210"/>
-      <c r="H9" s="255" t="s">
+      <c r="G9" s="253"/>
+      <c r="H9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="256"/>
-      <c r="J9" s="207" t="s">
+      <c r="I9" s="187"/>
+      <c r="J9" s="250" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="208"/>
-      <c r="L9" s="250" t="s">
+      <c r="K9" s="251"/>
+      <c r="L9" s="181" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="251"/>
-      <c r="N9" s="187" t="s">
+      <c r="M9" s="182"/>
+      <c r="N9" s="218" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="188"/>
-      <c r="P9" s="202" t="s">
+      <c r="O9" s="219"/>
+      <c r="P9" s="245" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="203"/>
-      <c r="R9" s="187" t="s">
+      <c r="Q9" s="246"/>
+      <c r="R9" s="218" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="188"/>
+      <c r="S9" s="219"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="240" t="s">
+      <c r="A10" s="214" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2830,7 +2830,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="179"/>
+      <c r="A11" s="215"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2927,7 +2927,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="179"/>
+      <c r="A12" s="215"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3024,7 +3024,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="179"/>
+      <c r="A13" s="215"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3121,7 +3121,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="179"/>
+      <c r="A14" s="215"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3199,7 +3199,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="179"/>
+      <c r="A15" s="215"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3277,7 +3277,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="179"/>
+      <c r="A16" s="215"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3355,7 +3355,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="179"/>
+      <c r="A17" s="215"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3433,7 +3433,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="179"/>
+      <c r="A18" s="215"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="179"/>
+      <c r="A19" s="215"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3589,7 +3589,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="179"/>
+      <c r="A20" s="215"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3667,7 +3667,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="179"/>
+      <c r="A21" s="215"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="241"/>
+      <c r="A22" s="216"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3879,7 +3879,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="240" t="s">
+      <c r="A24" s="214" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3978,7 +3978,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="179"/>
+      <c r="A25" s="215"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4075,7 +4075,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="179"/>
+      <c r="A26" s="215"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4172,7 +4172,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="179"/>
+      <c r="A27" s="215"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4250,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="180"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4403,7 +4403,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="204" t="s">
+      <c r="A32" s="247" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4482,7 +4482,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="205"/>
+      <c r="A33" s="248"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4559,7 +4559,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="206"/>
+      <c r="A34" s="249"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4657,7 +4657,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="204" t="s">
+      <c r="A36" s="247" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4736,7 +4736,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="205"/>
+      <c r="A37" s="248"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4813,7 +4813,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="206"/>
+      <c r="A38" s="249"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4904,7 +4904,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="240" t="s">
+      <c r="A40" s="214" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4916,25 +4916,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="231" t="s">
+      <c r="F40" s="207" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="232"/>
-      <c r="H40" s="232"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="232"/>
-      <c r="O40" s="232"/>
-      <c r="P40" s="232"/>
-      <c r="Q40" s="232"/>
-      <c r="R40" s="232"/>
-      <c r="S40" s="233"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
+      <c r="N40" s="208"/>
+      <c r="O40" s="208"/>
+      <c r="P40" s="208"/>
+      <c r="Q40" s="208"/>
+      <c r="R40" s="208"/>
+      <c r="S40" s="209"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="179"/>
+      <c r="A41" s="215"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -4997,7 +4997,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="179"/>
+      <c r="A42" s="215"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5022,13 +5022,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="198">
+      <c r="S42" s="175">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="179"/>
+      <c r="A43" s="215"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5040,26 +5040,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="228" t="str">
+      <c r="F43" s="197" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="229"/>
-      <c r="H43" s="229"/>
-      <c r="I43" s="229"/>
-      <c r="J43" s="229"/>
-      <c r="K43" s="229"/>
-      <c r="L43" s="229"/>
-      <c r="M43" s="229"/>
-      <c r="N43" s="229"/>
-      <c r="O43" s="229"/>
-      <c r="P43" s="229"/>
-      <c r="Q43" s="229"/>
-      <c r="R43" s="229"/>
-      <c r="S43" s="245"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="198"/>
+      <c r="N43" s="198"/>
+      <c r="O43" s="198"/>
+      <c r="P43" s="198"/>
+      <c r="Q43" s="198"/>
+      <c r="R43" s="198"/>
+      <c r="S43" s="176"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="179"/>
+      <c r="A44" s="215"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5115,7 +5115,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="179"/>
+      <c r="A45" s="215"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5249,7 +5249,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="179"/>
+      <c r="A46" s="215"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5263,7 +5263,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="179"/>
+      <c r="A47" s="215"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5274,50 +5274,50 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="198" t="s">
+      <c r="F47" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="211" t="str">
+      <c r="G47" s="254" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="198" t="s">
+      <c r="J47" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="200">
+      <c r="K47" s="243">
         <v>1</v>
       </c>
-      <c r="N47" s="198" t="s">
+      <c r="N47" s="175" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="246"/>
-      <c r="P47" s="247"/>
-      <c r="R47" s="198" t="s">
+      <c r="O47" s="177"/>
+      <c r="P47" s="178"/>
+      <c r="R47" s="175" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="198"/>
+      <c r="S47" s="175"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="180"/>
+      <c r="A48" s="217"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
       <c r="C48" s="31">
-        <f>ROUND(SUM(F45:S45),0)*2</f>
+        <f>SUMIF(Deco!W2:W99, "DB PAL", Taiere!V2:V99)+SUMIF(Deco!W2:W99, "DB MDF", Deco!V2:V99)</f>
         <v>0</v>
       </c>
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="199"/>
-      <c r="G48" s="212"/>
-      <c r="J48" s="199"/>
-      <c r="K48" s="201"/>
-      <c r="N48" s="245"/>
-      <c r="O48" s="248"/>
-      <c r="P48" s="249"/>
-      <c r="R48" s="245"/>
-      <c r="S48" s="199"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="255"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="244"/>
+      <c r="N48" s="176"/>
+      <c r="O48" s="179"/>
+      <c r="P48" s="180"/>
+      <c r="R48" s="176"/>
+      <c r="S48" s="223"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5326,187 +5326,193 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="178" t="s">
+      <c r="A50" s="227" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="189"/>
-      <c r="C50" s="190"/>
-      <c r="D50" s="190"/>
-      <c r="E50" s="190"/>
-      <c r="F50" s="190"/>
-      <c r="G50" s="190"/>
-      <c r="H50" s="190"/>
-      <c r="I50" s="190"/>
-      <c r="J50" s="190"/>
-      <c r="K50" s="190"/>
-      <c r="L50" s="190"/>
-      <c r="M50" s="190"/>
-      <c r="N50" s="190"/>
-      <c r="O50" s="190"/>
-      <c r="P50" s="190"/>
-      <c r="Q50" s="190"/>
-      <c r="R50" s="190"/>
-      <c r="S50" s="191"/>
+      <c r="B50" s="234"/>
+      <c r="C50" s="235"/>
+      <c r="D50" s="235"/>
+      <c r="E50" s="235"/>
+      <c r="F50" s="235"/>
+      <c r="G50" s="235"/>
+      <c r="H50" s="235"/>
+      <c r="I50" s="235"/>
+      <c r="J50" s="235"/>
+      <c r="K50" s="235"/>
+      <c r="L50" s="235"/>
+      <c r="M50" s="235"/>
+      <c r="N50" s="235"/>
+      <c r="O50" s="235"/>
+      <c r="P50" s="235"/>
+      <c r="Q50" s="235"/>
+      <c r="R50" s="235"/>
+      <c r="S50" s="236"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="179"/>
-      <c r="B51" s="192"/>
-      <c r="C51" s="193"/>
-      <c r="D51" s="193"/>
-      <c r="E51" s="193"/>
-      <c r="F51" s="193"/>
-      <c r="G51" s="193"/>
-      <c r="H51" s="193"/>
-      <c r="I51" s="193"/>
-      <c r="J51" s="193"/>
-      <c r="K51" s="193"/>
-      <c r="L51" s="193"/>
-      <c r="M51" s="193"/>
-      <c r="N51" s="193"/>
-      <c r="O51" s="193"/>
-      <c r="P51" s="193"/>
-      <c r="Q51" s="193"/>
-      <c r="R51" s="193"/>
-      <c r="S51" s="194"/>
+      <c r="A51" s="215"/>
+      <c r="B51" s="237"/>
+      <c r="C51" s="238"/>
+      <c r="D51" s="238"/>
+      <c r="E51" s="238"/>
+      <c r="F51" s="238"/>
+      <c r="G51" s="238"/>
+      <c r="H51" s="238"/>
+      <c r="I51" s="238"/>
+      <c r="J51" s="238"/>
+      <c r="K51" s="238"/>
+      <c r="L51" s="238"/>
+      <c r="M51" s="238"/>
+      <c r="N51" s="238"/>
+      <c r="O51" s="238"/>
+      <c r="P51" s="238"/>
+      <c r="Q51" s="238"/>
+      <c r="R51" s="238"/>
+      <c r="S51" s="239"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="179"/>
-      <c r="B52" s="192"/>
-      <c r="C52" s="193"/>
-      <c r="D52" s="193"/>
-      <c r="E52" s="193"/>
-      <c r="F52" s="193"/>
-      <c r="G52" s="193"/>
-      <c r="H52" s="193"/>
-      <c r="I52" s="193"/>
-      <c r="J52" s="193"/>
-      <c r="K52" s="193"/>
-      <c r="L52" s="193"/>
-      <c r="M52" s="193"/>
-      <c r="N52" s="193"/>
-      <c r="O52" s="193"/>
-      <c r="P52" s="193"/>
-      <c r="Q52" s="193"/>
-      <c r="R52" s="193"/>
-      <c r="S52" s="194"/>
+      <c r="A52" s="215"/>
+      <c r="B52" s="237"/>
+      <c r="C52" s="238"/>
+      <c r="D52" s="238"/>
+      <c r="E52" s="238"/>
+      <c r="F52" s="238"/>
+      <c r="G52" s="238"/>
+      <c r="H52" s="238"/>
+      <c r="I52" s="238"/>
+      <c r="J52" s="238"/>
+      <c r="K52" s="238"/>
+      <c r="L52" s="238"/>
+      <c r="M52" s="238"/>
+      <c r="N52" s="238"/>
+      <c r="O52" s="238"/>
+      <c r="P52" s="238"/>
+      <c r="Q52" s="238"/>
+      <c r="R52" s="238"/>
+      <c r="S52" s="239"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="179"/>
-      <c r="B53" s="192"/>
-      <c r="C53" s="193"/>
-      <c r="D53" s="193"/>
-      <c r="E53" s="193"/>
-      <c r="F53" s="193"/>
-      <c r="G53" s="193"/>
-      <c r="H53" s="193"/>
-      <c r="I53" s="193"/>
-      <c r="J53" s="193"/>
-      <c r="K53" s="193"/>
-      <c r="L53" s="193"/>
-      <c r="M53" s="193"/>
-      <c r="N53" s="193"/>
-      <c r="O53" s="193"/>
-      <c r="P53" s="193"/>
-      <c r="Q53" s="193"/>
-      <c r="R53" s="193"/>
-      <c r="S53" s="194"/>
+      <c r="A53" s="215"/>
+      <c r="B53" s="237"/>
+      <c r="C53" s="238"/>
+      <c r="D53" s="238"/>
+      <c r="E53" s="238"/>
+      <c r="F53" s="238"/>
+      <c r="G53" s="238"/>
+      <c r="H53" s="238"/>
+      <c r="I53" s="238"/>
+      <c r="J53" s="238"/>
+      <c r="K53" s="238"/>
+      <c r="L53" s="238"/>
+      <c r="M53" s="238"/>
+      <c r="N53" s="238"/>
+      <c r="O53" s="238"/>
+      <c r="P53" s="238"/>
+      <c r="Q53" s="238"/>
+      <c r="R53" s="238"/>
+      <c r="S53" s="239"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="179"/>
-      <c r="B54" s="192"/>
-      <c r="C54" s="193"/>
-      <c r="D54" s="193"/>
-      <c r="E54" s="193"/>
-      <c r="F54" s="193"/>
-      <c r="G54" s="193"/>
-      <c r="H54" s="193"/>
-      <c r="I54" s="193"/>
-      <c r="J54" s="193"/>
-      <c r="K54" s="193"/>
-      <c r="L54" s="193"/>
-      <c r="M54" s="193"/>
-      <c r="N54" s="193"/>
-      <c r="O54" s="193"/>
-      <c r="P54" s="193"/>
-      <c r="Q54" s="193"/>
-      <c r="R54" s="193"/>
-      <c r="S54" s="194"/>
+      <c r="A54" s="215"/>
+      <c r="B54" s="237"/>
+      <c r="C54" s="238"/>
+      <c r="D54" s="238"/>
+      <c r="E54" s="238"/>
+      <c r="F54" s="238"/>
+      <c r="G54" s="238"/>
+      <c r="H54" s="238"/>
+      <c r="I54" s="238"/>
+      <c r="J54" s="238"/>
+      <c r="K54" s="238"/>
+      <c r="L54" s="238"/>
+      <c r="M54" s="238"/>
+      <c r="N54" s="238"/>
+      <c r="O54" s="238"/>
+      <c r="P54" s="238"/>
+      <c r="Q54" s="238"/>
+      <c r="R54" s="238"/>
+      <c r="S54" s="239"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="179"/>
-      <c r="B55" s="192"/>
-      <c r="C55" s="193"/>
-      <c r="D55" s="193"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
-      <c r="G55" s="193"/>
-      <c r="H55" s="193"/>
-      <c r="I55" s="193"/>
-      <c r="J55" s="193"/>
-      <c r="K55" s="193"/>
-      <c r="L55" s="193"/>
-      <c r="M55" s="193"/>
-      <c r="N55" s="193"/>
-      <c r="O55" s="193"/>
-      <c r="P55" s="193"/>
-      <c r="Q55" s="193"/>
-      <c r="R55" s="193"/>
-      <c r="S55" s="194"/>
+      <c r="A55" s="215"/>
+      <c r="B55" s="237"/>
+      <c r="C55" s="238"/>
+      <c r="D55" s="238"/>
+      <c r="E55" s="238"/>
+      <c r="F55" s="238"/>
+      <c r="G55" s="238"/>
+      <c r="H55" s="238"/>
+      <c r="I55" s="238"/>
+      <c r="J55" s="238"/>
+      <c r="K55" s="238"/>
+      <c r="L55" s="238"/>
+      <c r="M55" s="238"/>
+      <c r="N55" s="238"/>
+      <c r="O55" s="238"/>
+      <c r="P55" s="238"/>
+      <c r="Q55" s="238"/>
+      <c r="R55" s="238"/>
+      <c r="S55" s="239"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="179"/>
-      <c r="B56" s="192"/>
-      <c r="C56" s="193"/>
-      <c r="D56" s="193"/>
-      <c r="E56" s="193"/>
-      <c r="F56" s="193"/>
-      <c r="G56" s="193"/>
-      <c r="H56" s="193"/>
-      <c r="I56" s="193"/>
-      <c r="J56" s="193"/>
-      <c r="K56" s="193"/>
-      <c r="L56" s="193"/>
-      <c r="M56" s="193"/>
-      <c r="N56" s="193"/>
-      <c r="O56" s="193"/>
-      <c r="P56" s="193"/>
-      <c r="Q56" s="193"/>
-      <c r="R56" s="193"/>
-      <c r="S56" s="194"/>
+      <c r="A56" s="215"/>
+      <c r="B56" s="237"/>
+      <c r="C56" s="238"/>
+      <c r="D56" s="238"/>
+      <c r="E56" s="238"/>
+      <c r="F56" s="238"/>
+      <c r="G56" s="238"/>
+      <c r="H56" s="238"/>
+      <c r="I56" s="238"/>
+      <c r="J56" s="238"/>
+      <c r="K56" s="238"/>
+      <c r="L56" s="238"/>
+      <c r="M56" s="238"/>
+      <c r="N56" s="238"/>
+      <c r="O56" s="238"/>
+      <c r="P56" s="238"/>
+      <c r="Q56" s="238"/>
+      <c r="R56" s="238"/>
+      <c r="S56" s="239"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="180"/>
-      <c r="B57" s="195"/>
-      <c r="C57" s="196"/>
-      <c r="D57" s="196"/>
-      <c r="E57" s="196"/>
-      <c r="F57" s="196"/>
-      <c r="G57" s="196"/>
-      <c r="H57" s="196"/>
-      <c r="I57" s="196"/>
-      <c r="J57" s="196"/>
-      <c r="K57" s="196"/>
-      <c r="L57" s="196"/>
-      <c r="M57" s="196"/>
-      <c r="N57" s="196"/>
-      <c r="O57" s="196"/>
-      <c r="P57" s="196"/>
-      <c r="Q57" s="196"/>
-      <c r="R57" s="196"/>
-      <c r="S57" s="197"/>
+      <c r="A57" s="217"/>
+      <c r="B57" s="240"/>
+      <c r="C57" s="241"/>
+      <c r="D57" s="241"/>
+      <c r="E57" s="241"/>
+      <c r="F57" s="241"/>
+      <c r="G57" s="241"/>
+      <c r="H57" s="241"/>
+      <c r="I57" s="241"/>
+      <c r="J57" s="241"/>
+      <c r="K57" s="241"/>
+      <c r="L57" s="241"/>
+      <c r="M57" s="241"/>
+      <c r="N57" s="241"/>
+      <c r="O57" s="241"/>
+      <c r="P57" s="241"/>
+      <c r="Q57" s="241"/>
+      <c r="R57" s="241"/>
+      <c r="S57" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="B50:S57"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="O6:S6"/>
@@ -5523,22 +5529,16 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="R47:R48"/>
     <mergeCell ref="S47:S48"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="B50:S57"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB8C11F-8178-47B8-B19D-65806FD6F19C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA2B1BB-6E4C-46A8-B4A7-7448615B3E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -1804,8 +1804,229 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1861,229 +2082,8 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2121,6 +2121,150 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA66FE0C-65B0-0F7D-1E1D-9715BE537223}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="895350" y="8353425"/>
+          <a:ext cx="14049375" cy="1552575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ro-RO" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>VB35 -</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ro-RO" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> Culori</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ro-RO" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Profile Gola</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="ro-RO" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Rame</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ro-RO" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> aluminiu</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2570,33 +2714,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="234" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="212"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
+      <c r="L1" s="236"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="199" t="s">
+      <c r="O1" s="219" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="201"/>
+      <c r="P1" s="220"/>
+      <c r="Q1" s="220"/>
+      <c r="R1" s="220"/>
+      <c r="S1" s="221"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2615,165 +2759,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="202"/>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="203"/>
-      <c r="R2" s="203"/>
-      <c r="S2" s="204"/>
+      <c r="O2" s="222"/>
+      <c r="P2" s="223"/>
+      <c r="Q2" s="223"/>
+      <c r="R2" s="223"/>
+      <c r="S2" s="224"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="220"/>
-      <c r="C3" s="221"/>
-      <c r="D3" s="222"/>
+      <c r="B3" s="242"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="244"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="225"/>
-      <c r="K3" s="226"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="176"/>
+      <c r="K3" s="177"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="195"/>
-      <c r="Q3" s="195"/>
-      <c r="R3" s="195"/>
-      <c r="S3" s="196"/>
+      <c r="O3" s="237"/>
+      <c r="P3" s="238"/>
+      <c r="Q3" s="238"/>
+      <c r="R3" s="238"/>
+      <c r="S3" s="239"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="256"/>
-      <c r="C4" s="257"/>
-      <c r="D4" s="258"/>
+      <c r="B4" s="213"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="215"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="259"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="261"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="217"/>
+      <c r="K4" s="218"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="195"/>
-      <c r="Q4" s="195"/>
-      <c r="R4" s="195"/>
-      <c r="S4" s="196"/>
+      <c r="O4" s="237"/>
+      <c r="P4" s="238"/>
+      <c r="Q4" s="238"/>
+      <c r="R4" s="238"/>
+      <c r="S4" s="239"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="185"/>
+      <c r="B5" s="252"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="254"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="194"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="196"/>
+      <c r="I5" s="261"/>
+      <c r="J5" s="238"/>
+      <c r="K5" s="239"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="213"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="195"/>
-      <c r="R5" s="195"/>
-      <c r="S5" s="196"/>
+      <c r="O5" s="237"/>
+      <c r="P5" s="238"/>
+      <c r="Q5" s="238"/>
+      <c r="R5" s="238"/>
+      <c r="S5" s="239"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="188"/>
-      <c r="C6" s="189"/>
-      <c r="D6" s="190"/>
+      <c r="B6" s="257"/>
+      <c r="C6" s="258"/>
+      <c r="D6" s="259"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="191"/>
-      <c r="J6" s="192"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="260"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="227"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="205"/>
-      <c r="P6" s="192"/>
-      <c r="Q6" s="192"/>
-      <c r="R6" s="192"/>
-      <c r="S6" s="193"/>
+      <c r="O6" s="225"/>
+      <c r="P6" s="226"/>
+      <c r="Q6" s="226"/>
+      <c r="R6" s="226"/>
+      <c r="S6" s="227"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="228" t="s">
+      <c r="A8" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="230"/>
-      <c r="F8" s="197" t="s">
+      <c r="B8" s="182"/>
+      <c r="C8" s="182"/>
+      <c r="D8" s="183"/>
+      <c r="F8" s="228" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="198"/>
-      <c r="H8" s="198"/>
-      <c r="I8" s="198"/>
-      <c r="J8" s="198"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="198"/>
-      <c r="O8" s="198"/>
-      <c r="P8" s="198"/>
-      <c r="Q8" s="198"/>
-      <c r="R8" s="198"/>
-      <c r="S8" s="206"/>
+      <c r="G8" s="229"/>
+      <c r="H8" s="229"/>
+      <c r="I8" s="229"/>
+      <c r="J8" s="229"/>
+      <c r="K8" s="229"/>
+      <c r="L8" s="229"/>
+      <c r="M8" s="229"/>
+      <c r="N8" s="229"/>
+      <c r="O8" s="229"/>
+      <c r="P8" s="229"/>
+      <c r="Q8" s="229"/>
+      <c r="R8" s="229"/>
+      <c r="S8" s="230"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="231"/>
-      <c r="B9" s="232"/>
-      <c r="C9" s="232"/>
-      <c r="D9" s="233"/>
-      <c r="F9" s="252" t="s">
+      <c r="A9" s="184"/>
+      <c r="B9" s="185"/>
+      <c r="C9" s="185"/>
+      <c r="D9" s="186"/>
+      <c r="F9" s="209" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="253"/>
-      <c r="H9" s="186" t="s">
+      <c r="G9" s="210"/>
+      <c r="H9" s="255" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="187"/>
-      <c r="J9" s="250" t="s">
+      <c r="I9" s="256"/>
+      <c r="J9" s="207" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="251"/>
-      <c r="L9" s="181" t="s">
+      <c r="K9" s="208"/>
+      <c r="L9" s="250" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="182"/>
-      <c r="N9" s="218" t="s">
+      <c r="M9" s="251"/>
+      <c r="N9" s="187" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="219"/>
-      <c r="P9" s="245" t="s">
+      <c r="O9" s="188"/>
+      <c r="P9" s="202" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="218" t="s">
+      <c r="Q9" s="203"/>
+      <c r="R9" s="187" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="219"/>
+      <c r="S9" s="188"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="214" t="s">
+      <c r="A10" s="240" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2830,7 +2974,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="215"/>
+      <c r="A11" s="179"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2927,7 +3071,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="215"/>
+      <c r="A12" s="179"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3024,7 +3168,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="215"/>
+      <c r="A13" s="179"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3121,7 +3265,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="215"/>
+      <c r="A14" s="179"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3199,7 +3343,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="215"/>
+      <c r="A15" s="179"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3277,7 +3421,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="215"/>
+      <c r="A16" s="179"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3355,7 +3499,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="215"/>
+      <c r="A17" s="179"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3433,7 +3577,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="215"/>
+      <c r="A18" s="179"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3511,7 +3655,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="215"/>
+      <c r="A19" s="179"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3589,7 +3733,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="215"/>
+      <c r="A20" s="179"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3667,7 +3811,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="215"/>
+      <c r="A21" s="179"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3745,7 +3889,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="216"/>
+      <c r="A22" s="241"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3879,7 +4023,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="214" t="s">
+      <c r="A24" s="240" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -3978,7 +4122,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="215"/>
+      <c r="A25" s="179"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4075,7 +4219,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="215"/>
+      <c r="A26" s="179"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4172,7 +4316,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="215"/>
+      <c r="A27" s="179"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4250,7 +4394,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="217"/>
+      <c r="A28" s="180"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4403,7 +4547,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="247" t="s">
+      <c r="A32" s="204" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4482,7 +4626,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="248"/>
+      <c r="A33" s="205"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4559,7 +4703,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="249"/>
+      <c r="A34" s="206"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4657,7 +4801,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="247" t="s">
+      <c r="A36" s="204" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4736,7 +4880,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="248"/>
+      <c r="A37" s="205"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4813,7 +4957,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="249"/>
+      <c r="A38" s="206"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4904,7 +5048,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="214" t="s">
+      <c r="A40" s="240" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -4916,25 +5060,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="207" t="s">
+      <c r="F40" s="231" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="208"/>
-      <c r="L40" s="208"/>
-      <c r="M40" s="208"/>
-      <c r="N40" s="208"/>
-      <c r="O40" s="208"/>
-      <c r="P40" s="208"/>
-      <c r="Q40" s="208"/>
-      <c r="R40" s="208"/>
-      <c r="S40" s="209"/>
+      <c r="G40" s="232"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
+      <c r="M40" s="232"/>
+      <c r="N40" s="232"/>
+      <c r="O40" s="232"/>
+      <c r="P40" s="232"/>
+      <c r="Q40" s="232"/>
+      <c r="R40" s="232"/>
+      <c r="S40" s="233"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="215"/>
+      <c r="A41" s="179"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -4997,7 +5141,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="215"/>
+      <c r="A42" s="179"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5022,13 +5166,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="175">
+      <c r="S42" s="198">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="215"/>
+      <c r="A43" s="179"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5040,26 +5184,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="197" t="str">
+      <c r="F43" s="228" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="198"/>
-      <c r="H43" s="198"/>
-      <c r="I43" s="198"/>
-      <c r="J43" s="198"/>
-      <c r="K43" s="198"/>
-      <c r="L43" s="198"/>
-      <c r="M43" s="198"/>
-      <c r="N43" s="198"/>
-      <c r="O43" s="198"/>
-      <c r="P43" s="198"/>
-      <c r="Q43" s="198"/>
-      <c r="R43" s="198"/>
-      <c r="S43" s="176"/>
+      <c r="G43" s="229"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="229"/>
+      <c r="J43" s="229"/>
+      <c r="K43" s="229"/>
+      <c r="L43" s="229"/>
+      <c r="M43" s="229"/>
+      <c r="N43" s="229"/>
+      <c r="O43" s="229"/>
+      <c r="P43" s="229"/>
+      <c r="Q43" s="229"/>
+      <c r="R43" s="229"/>
+      <c r="S43" s="245"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="215"/>
+      <c r="A44" s="179"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5115,7 +5259,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="215"/>
+      <c r="A45" s="179"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5249,7 +5393,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="215"/>
+      <c r="A46" s="179"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5263,7 +5407,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="215"/>
+      <c r="A47" s="179"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5274,50 +5418,50 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="175" t="s">
+      <c r="F47" s="198" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="254" t="str">
+      <c r="G47" s="211" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="175" t="s">
+      <c r="J47" s="198" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="243">
+      <c r="K47" s="200">
         <v>1</v>
       </c>
-      <c r="N47" s="175" t="s">
+      <c r="N47" s="198" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="177"/>
-      <c r="P47" s="178"/>
-      <c r="R47" s="175" t="s">
+      <c r="O47" s="246"/>
+      <c r="P47" s="247"/>
+      <c r="R47" s="198" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="175"/>
+      <c r="S47" s="198"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="217"/>
+      <c r="A48" s="180"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
       <c r="C48" s="31">
-        <f>SUMIF(Deco!W2:W99, "DB PAL", Taiere!V2:V99)+SUMIF(Deco!W2:W99, "DB MDF", Deco!V2:V99)</f>
+        <f>SUMIF(Deco!W2:W99, "DB PAL", Deco!V2:V99)+SUMIF(Deco!W2:W99, "DB MDF", Deco!V2:V99)</f>
         <v>0</v>
       </c>
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="223"/>
-      <c r="G48" s="255"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="244"/>
-      <c r="N48" s="176"/>
-      <c r="O48" s="179"/>
-      <c r="P48" s="180"/>
-      <c r="R48" s="176"/>
-      <c r="S48" s="223"/>
+      <c r="F48" s="199"/>
+      <c r="G48" s="212"/>
+      <c r="J48" s="199"/>
+      <c r="K48" s="201"/>
+      <c r="N48" s="245"/>
+      <c r="O48" s="248"/>
+      <c r="P48" s="249"/>
+      <c r="R48" s="245"/>
+      <c r="S48" s="199"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5326,177 +5470,203 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="227" t="s">
+      <c r="A50" s="178" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="234"/>
-      <c r="C50" s="235"/>
-      <c r="D50" s="235"/>
-      <c r="E50" s="235"/>
-      <c r="F50" s="235"/>
-      <c r="G50" s="235"/>
-      <c r="H50" s="235"/>
-      <c r="I50" s="235"/>
-      <c r="J50" s="235"/>
-      <c r="K50" s="235"/>
-      <c r="L50" s="235"/>
-      <c r="M50" s="235"/>
-      <c r="N50" s="235"/>
-      <c r="O50" s="235"/>
-      <c r="P50" s="235"/>
-      <c r="Q50" s="235"/>
-      <c r="R50" s="235"/>
-      <c r="S50" s="236"/>
+      <c r="B50" s="189"/>
+      <c r="C50" s="190"/>
+      <c r="D50" s="190"/>
+      <c r="E50" s="190"/>
+      <c r="F50" s="190"/>
+      <c r="G50" s="190"/>
+      <c r="H50" s="190"/>
+      <c r="I50" s="190"/>
+      <c r="J50" s="190"/>
+      <c r="K50" s="190"/>
+      <c r="L50" s="190"/>
+      <c r="M50" s="190"/>
+      <c r="N50" s="190"/>
+      <c r="O50" s="190"/>
+      <c r="P50" s="190"/>
+      <c r="Q50" s="190"/>
+      <c r="R50" s="190"/>
+      <c r="S50" s="191"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="215"/>
-      <c r="B51" s="237"/>
-      <c r="C51" s="238"/>
-      <c r="D51" s="238"/>
-      <c r="E51" s="238"/>
-      <c r="F51" s="238"/>
-      <c r="G51" s="238"/>
-      <c r="H51" s="238"/>
-      <c r="I51" s="238"/>
-      <c r="J51" s="238"/>
-      <c r="K51" s="238"/>
-      <c r="L51" s="238"/>
-      <c r="M51" s="238"/>
-      <c r="N51" s="238"/>
-      <c r="O51" s="238"/>
-      <c r="P51" s="238"/>
-      <c r="Q51" s="238"/>
-      <c r="R51" s="238"/>
-      <c r="S51" s="239"/>
+      <c r="A51" s="179"/>
+      <c r="B51" s="192"/>
+      <c r="C51" s="193"/>
+      <c r="D51" s="193"/>
+      <c r="E51" s="193"/>
+      <c r="F51" s="193"/>
+      <c r="G51" s="193"/>
+      <c r="H51" s="193"/>
+      <c r="I51" s="193"/>
+      <c r="J51" s="193"/>
+      <c r="K51" s="193"/>
+      <c r="L51" s="193"/>
+      <c r="M51" s="193"/>
+      <c r="N51" s="193"/>
+      <c r="O51" s="193"/>
+      <c r="P51" s="193"/>
+      <c r="Q51" s="193"/>
+      <c r="R51" s="193"/>
+      <c r="S51" s="194"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="215"/>
-      <c r="B52" s="237"/>
-      <c r="C52" s="238"/>
-      <c r="D52" s="238"/>
-      <c r="E52" s="238"/>
-      <c r="F52" s="238"/>
-      <c r="G52" s="238"/>
-      <c r="H52" s="238"/>
-      <c r="I52" s="238"/>
-      <c r="J52" s="238"/>
-      <c r="K52" s="238"/>
-      <c r="L52" s="238"/>
-      <c r="M52" s="238"/>
-      <c r="N52" s="238"/>
-      <c r="O52" s="238"/>
-      <c r="P52" s="238"/>
-      <c r="Q52" s="238"/>
-      <c r="R52" s="238"/>
-      <c r="S52" s="239"/>
+      <c r="A52" s="179"/>
+      <c r="B52" s="192"/>
+      <c r="C52" s="193"/>
+      <c r="D52" s="193"/>
+      <c r="E52" s="193"/>
+      <c r="F52" s="193"/>
+      <c r="G52" s="193"/>
+      <c r="H52" s="193"/>
+      <c r="I52" s="193"/>
+      <c r="J52" s="193"/>
+      <c r="K52" s="193"/>
+      <c r="L52" s="193"/>
+      <c r="M52" s="193"/>
+      <c r="N52" s="193"/>
+      <c r="O52" s="193"/>
+      <c r="P52" s="193"/>
+      <c r="Q52" s="193"/>
+      <c r="R52" s="193"/>
+      <c r="S52" s="194"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="215"/>
-      <c r="B53" s="237"/>
-      <c r="C53" s="238"/>
-      <c r="D53" s="238"/>
-      <c r="E53" s="238"/>
-      <c r="F53" s="238"/>
-      <c r="G53" s="238"/>
-      <c r="H53" s="238"/>
-      <c r="I53" s="238"/>
-      <c r="J53" s="238"/>
-      <c r="K53" s="238"/>
-      <c r="L53" s="238"/>
-      <c r="M53" s="238"/>
-      <c r="N53" s="238"/>
-      <c r="O53" s="238"/>
-      <c r="P53" s="238"/>
-      <c r="Q53" s="238"/>
-      <c r="R53" s="238"/>
-      <c r="S53" s="239"/>
+      <c r="A53" s="179"/>
+      <c r="B53" s="192"/>
+      <c r="C53" s="193"/>
+      <c r="D53" s="193"/>
+      <c r="E53" s="193"/>
+      <c r="F53" s="193"/>
+      <c r="G53" s="193"/>
+      <c r="H53" s="193"/>
+      <c r="I53" s="193"/>
+      <c r="J53" s="193"/>
+      <c r="K53" s="193"/>
+      <c r="L53" s="193"/>
+      <c r="M53" s="193"/>
+      <c r="N53" s="193"/>
+      <c r="O53" s="193"/>
+      <c r="P53" s="193"/>
+      <c r="Q53" s="193"/>
+      <c r="R53" s="193"/>
+      <c r="S53" s="194"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="215"/>
-      <c r="B54" s="237"/>
-      <c r="C54" s="238"/>
-      <c r="D54" s="238"/>
-      <c r="E54" s="238"/>
-      <c r="F54" s="238"/>
-      <c r="G54" s="238"/>
-      <c r="H54" s="238"/>
-      <c r="I54" s="238"/>
-      <c r="J54" s="238"/>
-      <c r="K54" s="238"/>
-      <c r="L54" s="238"/>
-      <c r="M54" s="238"/>
-      <c r="N54" s="238"/>
-      <c r="O54" s="238"/>
-      <c r="P54" s="238"/>
-      <c r="Q54" s="238"/>
-      <c r="R54" s="238"/>
-      <c r="S54" s="239"/>
+      <c r="A54" s="179"/>
+      <c r="B54" s="192"/>
+      <c r="C54" s="193"/>
+      <c r="D54" s="193"/>
+      <c r="E54" s="193"/>
+      <c r="F54" s="193"/>
+      <c r="G54" s="193"/>
+      <c r="H54" s="193"/>
+      <c r="I54" s="193"/>
+      <c r="J54" s="193"/>
+      <c r="K54" s="193"/>
+      <c r="L54" s="193"/>
+      <c r="M54" s="193"/>
+      <c r="N54" s="193"/>
+      <c r="O54" s="193"/>
+      <c r="P54" s="193"/>
+      <c r="Q54" s="193"/>
+      <c r="R54" s="193"/>
+      <c r="S54" s="194"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="215"/>
-      <c r="B55" s="237"/>
-      <c r="C55" s="238"/>
-      <c r="D55" s="238"/>
-      <c r="E55" s="238"/>
-      <c r="F55" s="238"/>
-      <c r="G55" s="238"/>
-      <c r="H55" s="238"/>
-      <c r="I55" s="238"/>
-      <c r="J55" s="238"/>
-      <c r="K55" s="238"/>
-      <c r="L55" s="238"/>
-      <c r="M55" s="238"/>
-      <c r="N55" s="238"/>
-      <c r="O55" s="238"/>
-      <c r="P55" s="238"/>
-      <c r="Q55" s="238"/>
-      <c r="R55" s="238"/>
-      <c r="S55" s="239"/>
+      <c r="A55" s="179"/>
+      <c r="B55" s="192"/>
+      <c r="C55" s="193"/>
+      <c r="D55" s="193"/>
+      <c r="E55" s="193"/>
+      <c r="F55" s="193"/>
+      <c r="G55" s="193"/>
+      <c r="H55" s="193"/>
+      <c r="I55" s="193"/>
+      <c r="J55" s="193"/>
+      <c r="K55" s="193"/>
+      <c r="L55" s="193"/>
+      <c r="M55" s="193"/>
+      <c r="N55" s="193"/>
+      <c r="O55" s="193"/>
+      <c r="P55" s="193"/>
+      <c r="Q55" s="193"/>
+      <c r="R55" s="193"/>
+      <c r="S55" s="194"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="215"/>
-      <c r="B56" s="237"/>
-      <c r="C56" s="238"/>
-      <c r="D56" s="238"/>
-      <c r="E56" s="238"/>
-      <c r="F56" s="238"/>
-      <c r="G56" s="238"/>
-      <c r="H56" s="238"/>
-      <c r="I56" s="238"/>
-      <c r="J56" s="238"/>
-      <c r="K56" s="238"/>
-      <c r="L56" s="238"/>
-      <c r="M56" s="238"/>
-      <c r="N56" s="238"/>
-      <c r="O56" s="238"/>
-      <c r="P56" s="238"/>
-      <c r="Q56" s="238"/>
-      <c r="R56" s="238"/>
-      <c r="S56" s="239"/>
+      <c r="A56" s="179"/>
+      <c r="B56" s="192"/>
+      <c r="C56" s="193"/>
+      <c r="D56" s="193"/>
+      <c r="E56" s="193"/>
+      <c r="F56" s="193"/>
+      <c r="G56" s="193"/>
+      <c r="H56" s="193"/>
+      <c r="I56" s="193"/>
+      <c r="J56" s="193"/>
+      <c r="K56" s="193"/>
+      <c r="L56" s="193"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="193"/>
+      <c r="O56" s="193"/>
+      <c r="P56" s="193"/>
+      <c r="Q56" s="193"/>
+      <c r="R56" s="193"/>
+      <c r="S56" s="194"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="217"/>
-      <c r="B57" s="240"/>
-      <c r="C57" s="241"/>
-      <c r="D57" s="241"/>
-      <c r="E57" s="241"/>
-      <c r="F57" s="241"/>
-      <c r="G57" s="241"/>
-      <c r="H57" s="241"/>
-      <c r="I57" s="241"/>
-      <c r="J57" s="241"/>
-      <c r="K57" s="241"/>
-      <c r="L57" s="241"/>
-      <c r="M57" s="241"/>
-      <c r="N57" s="241"/>
-      <c r="O57" s="241"/>
-      <c r="P57" s="241"/>
-      <c r="Q57" s="241"/>
-      <c r="R57" s="241"/>
-      <c r="S57" s="242"/>
+      <c r="A57" s="180"/>
+      <c r="B57" s="195"/>
+      <c r="C57" s="196"/>
+      <c r="D57" s="196"/>
+      <c r="E57" s="196"/>
+      <c r="F57" s="196"/>
+      <c r="G57" s="196"/>
+      <c r="H57" s="196"/>
+      <c r="I57" s="196"/>
+      <c r="J57" s="196"/>
+      <c r="K57" s="196"/>
+      <c r="L57" s="196"/>
+      <c r="M57" s="196"/>
+      <c r="N57" s="196"/>
+      <c r="O57" s="196"/>
+      <c r="P57" s="196"/>
+      <c r="Q57" s="196"/>
+      <c r="R57" s="196"/>
+      <c r="S57" s="197"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="F40:S40"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="A10:A22"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="R47:R48"/>
+    <mergeCell ref="S47:S48"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A57"/>
     <mergeCell ref="A8:D9"/>
@@ -5513,36 +5683,11 @@
     <mergeCell ref="G47:G48"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="F40:S40"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="A10:A22"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="R47:R48"/>
-    <mergeCell ref="S47:S48"/>
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA2B1BB-6E4C-46A8-B4A7-7448615B3E4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09274F1D-72A8-4ABC-B199-18626CF49BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -2979,8 +2979,17 @@
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
       </c>
-      <c r="C11" s="61" t="str">
-        <f>IF(D11="buc",IF(B11&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B11,Deco!$Y$2:$Y$99,0)),""),IF(B11&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B11,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C11" s="61" t="str" cm="1">
+        <f t="array" ref="C11">IFERROR(
+  IF(D11="buc",
+    IF(B11&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B11)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B11&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B11)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B11)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D11" s="29" t="str" cm="1">
@@ -3076,8 +3085,17 @@
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
       </c>
-      <c r="C12" s="134" t="str">
-        <f>IF(D12="buc",IF(B12&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B12,Deco!$Y$2:$Y$99,0)),""),IF(B12&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B12,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C12" s="134" t="str" cm="1">
+        <f t="array" ref="C12">IFERROR(
+  IF(D12="buc",
+    IF(B12&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B12)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B12&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B12)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B12)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D12" s="37" t="str" cm="1">
@@ -3173,8 +3191,17 @@
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
       </c>
-      <c r="C13" s="134" t="str">
-        <f>IF(D13="buc",IF(B13&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B13,Deco!$Y$2:$Y$99,0)),""),IF(B13&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B13,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C13" s="134" t="str" cm="1">
+        <f t="array" ref="C13">IFERROR(
+  IF(D13="buc",
+    IF(B13&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B13)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B13&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B13)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B13)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D13" s="37" t="str" cm="1">
@@ -3270,8 +3297,17 @@
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
       </c>
-      <c r="C14" s="134" t="str">
-        <f>IF(D14="buc",IF(B14&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B14,Deco!$Y$2:$Y$99,0)),""),IF(B14&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B14,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C14" s="134" t="str" cm="1">
+        <f t="array" ref="C14">IFERROR(
+  IF(D14="buc",
+    IF(B14&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B14)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B14&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B14)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B14)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D14" s="37" t="str" cm="1">
@@ -3348,8 +3384,17 @@
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
       </c>
-      <c r="C15" s="134" t="str">
-        <f>IF(D15="buc",IF(B15&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B15,Deco!$Y$2:$Y$99,0)),""),IF(B15&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B15,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C15" s="139" t="str" cm="1">
+        <f t="array" ref="C15">IFERROR(
+  IF(D15="buc",
+    IF(B15&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B15)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B15&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B15)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B15)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D15" s="37" t="str" cm="1">
@@ -3426,8 +3471,17 @@
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
       </c>
-      <c r="C16" s="134" t="str">
-        <f>IF(D16="buc",IF(B16&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B16,Deco!$Y$2:$Y$99,0)),""),IF(B16&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B16,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C16" s="134" t="str" cm="1">
+        <f t="array" ref="C16">IFERROR(
+  IF(D16="buc",
+    IF(B16&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B16)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B16&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B16)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B16)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D16" s="37" t="str" cm="1">
@@ -3504,8 +3558,17 @@
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
       </c>
-      <c r="C17" s="134" t="str">
-        <f>IF(D17="buc",IF(B17&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B17,Deco!$Y$2:$Y$99,0)),""),IF(B17&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B17,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C17" s="134" t="str" cm="1">
+        <f t="array" ref="C17">IFERROR(
+  IF(D17="buc",
+    IF(B17&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B17)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B17&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B17)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B17)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D17" s="37" t="str" cm="1">
@@ -3582,8 +3645,17 @@
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
       </c>
-      <c r="C18" s="134" t="str">
-        <f>IF(D18="buc",IF(B18&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B18,Deco!$Y$2:$Y$99,0)),""),IF(B18&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B18,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C18" s="134" t="str" cm="1">
+        <f t="array" ref="C18">IFERROR(
+  IF(D18="buc",
+    IF(B18&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B18)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B18&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B18)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B18)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D18" s="37" t="str" cm="1">
@@ -3660,8 +3732,17 @@
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
       </c>
-      <c r="C19" s="134" t="str">
-        <f>IF(D19="buc",IF(B19&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B19,Deco!$Y$2:$Y$99,0)),""),IF(B19&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B19,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C19" s="134" t="str" cm="1">
+        <f t="array" ref="C19">IFERROR(
+  IF(D19="buc",
+    IF(B19&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B19)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B19&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B19)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B19)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D19" s="37" t="str" cm="1">
@@ -3738,8 +3819,17 @@
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
       </c>
-      <c r="C20" s="134" t="str">
-        <f>IF(D20="buc",IF(B20&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B20,Deco!$Y$2:$Y$99,0)),""),IF(B20&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B20,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C20" s="134" t="str" cm="1">
+        <f t="array" ref="C20">IFERROR(
+  IF(D20="buc",
+    IF(B20&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B20)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B20&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B20)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B20)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D20" s="37" t="str" cm="1">
@@ -3816,8 +3906,17 @@
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
       </c>
-      <c r="C21" s="134" t="str">
-        <f>IF(D21="buc",IF(B21&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B21,Deco!$Y$2:$Y$99,0)),""),IF(B21&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B21,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C21" s="134" t="str" cm="1">
+        <f t="array" ref="C21">IFERROR(
+  IF(D21="buc",
+    IF(B21&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B21)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B21&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B21)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B21)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D21" s="37" t="str" cm="1">
@@ -3894,8 +3993,17 @@
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
       </c>
-      <c r="C22" s="134" t="str">
-        <f>IF(D22="buc",IF(B22&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B22,Deco!$Y$2:$Y$99,0)),""),IF(B22&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B22,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C22" s="139" t="str" cm="1">
+        <f t="array" ref="C22">IFERROR(
+  IF(D22="buc",
+    IF(B22&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B22)*(Deco!$W$2:$W$99="PAL"), 0)),
+    ""),
+    IF(AND(B22&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B22)*(Deco!$W$2:$W$99="PAL"), 0))="PAL"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B22)*(Deco!$W$2:$W$99="PAL"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D22" s="126" t="str" cm="1">
@@ -4030,8 +4138,17 @@
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),1)),"")</f>
         <v/>
       </c>
-      <c r="C24" s="61" t="str">
-        <f>IF(D24="buc",IF(B24&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B24,Deco!$Y$2:$Y$99,0)),""),IF(B24&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B24,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C24" s="61" t="str" cm="1">
+        <f t="array" ref="C24">IFERROR(
+  IF(D24="buc",
+    IF(B24&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B24)*(Deco!$W$2:$W$99="MDF"), 0)),
+    ""),
+    IF(AND(B24&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B24)*(Deco!$W$2:$W$99="MDF"), 0))="MDF"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B24)*(Deco!$W$2:$W$99="MDF"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D24" s="37" t="str" cm="1">
@@ -4127,8 +4244,17 @@
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
       </c>
-      <c r="C25" s="134" t="str">
-        <f>IF(D25="buc",IF(B25&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B25,Deco!$Y$2:$Y$99,0)),""),IF(B25&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B25,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C25" s="134" t="str" cm="1">
+        <f t="array" ref="C25">IFERROR(
+  IF(D25="buc",
+    IF(B25&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B25)*(Deco!$W$2:$W$99="MDF"), 0)),
+    ""),
+    IF(AND(B25&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B25)*(Deco!$W$2:$W$99="MDF"), 0))="MDF"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B25)*(Deco!$W$2:$W$99="MDF"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D25" s="37" t="str" cm="1">
@@ -4224,8 +4350,17 @@
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
       </c>
-      <c r="C26" s="134" t="str">
-        <f>IF(D26="buc",IF(B26&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B26,Deco!$Y$2:$Y$99,0)),""),IF(B26&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B26,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C26" s="134" t="str" cm="1">
+        <f t="array" ref="C26">IFERROR(
+  IF(D26="buc",
+    IF(B26&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B26)*(Deco!$W$2:$W$99="MDF"), 0)),
+    ""),
+    IF(AND(B26&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B26)*(Deco!$W$2:$W$99="MDF"), 0))="MDF"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B26)*(Deco!$W$2:$W$99="MDF"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D26" s="37" t="str" cm="1">
@@ -4321,8 +4456,17 @@
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
       </c>
-      <c r="C27" s="134" t="str">
-        <f>IF(D27="buc",IF(B27&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B27,Deco!$Y$2:$Y$99,0)),""),IF(B27&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B27,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C27" s="134" t="str" cm="1">
+        <f t="array" ref="C27">IFERROR(
+  IF(D27="buc",
+    IF(B27&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B27)*(Deco!$W$2:$W$99="MDF"), 0)),
+    ""),
+    IF(AND(B27&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B27)*(Deco!$W$2:$W$99="MDF"), 0))="MDF"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B27)*(Deco!$W$2:$W$99="MDF"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D27" s="37" t="str" cm="1">
@@ -4399,8 +4543,17 @@
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
       </c>
-      <c r="C28" s="134" t="str">
-        <f>IF(D28="buc",IF(B28&lt;&gt;"",INDEX(Deco!$C$2:$C$99,MATCH(B28,Deco!$Y$2:$Y$99,0)),""),IF(B28&lt;&gt;"",INDEX(Deco!$V$2:$V$99,MATCH(B28,Deco!$Y$2:$Y$99,0)),""))</f>
+      <c r="C28" s="139" t="str" cm="1">
+        <f t="array" ref="C28">IFERROR(
+  IF(D28="buc",
+    IF(B28&lt;&gt;"",
+      INDEX(Deco!$C$2:$C$99, MATCH(1, (Deco!$Y$2:$Y$99=B28)*(Deco!$W$2:$W$99="MDF"), 0)),
+    ""),
+    IF(AND(B28&lt;&gt;"", INDEX(Deco!$W$2:$W$99, MATCH(1, (Deco!$Y$2:$Y$99=B28)*(Deco!$W$2:$W$99="MDF"), 0))="MDF"),
+      INDEX(Deco!$V$2:$V$99, MATCH(1, (Deco!$Y$2:$Y$99=B28)*(Deco!$W$2:$W$99="MDF"), 0)),
+    "")
+  ),
+"")</f>
         <v/>
       </c>
       <c r="D28" s="37" t="str" cm="1">
@@ -5713,7 +5866,7 @@
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8352AD92-AE48-443F-8268-FEC6552ABA57}">
           <x14:formula1>
             <xm:f>Parametri!$A:$A</xm:f>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09274F1D-72A8-4ABC-B199-18626CF49BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9919665A-135A-40C7-AE15-4A793A60FADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -1804,6 +1804,162 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1819,12 +1975,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1842,45 +1992,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1947,144 +2058,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2093,6 +2066,33 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2121,150 +2121,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA66FE0C-65B0-0F7D-1E1D-9715BE537223}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="895350" y="8353425"/>
-          <a:ext cx="14049375" cy="1552575"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ro-RO" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>VB35 -</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ro-RO" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> Culori</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ro-RO" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Profile Gola</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="ro-RO" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Rame</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ro-RO" sz="1100" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> aluminiu</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2714,33 +2570,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="234" t="s">
+      <c r="A1" s="210" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="235"/>
-      <c r="K1" s="235"/>
-      <c r="L1" s="236"/>
+      <c r="B1" s="211"/>
+      <c r="C1" s="211"/>
+      <c r="D1" s="211"/>
+      <c r="E1" s="211"/>
+      <c r="F1" s="211"/>
+      <c r="G1" s="211"/>
+      <c r="H1" s="211"/>
+      <c r="I1" s="211"/>
+      <c r="J1" s="211"/>
+      <c r="K1" s="211"/>
+      <c r="L1" s="212"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="219" t="s">
+      <c r="O1" s="199" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="220"/>
-      <c r="Q1" s="220"/>
-      <c r="R1" s="220"/>
-      <c r="S1" s="221"/>
+      <c r="P1" s="200"/>
+      <c r="Q1" s="200"/>
+      <c r="R1" s="200"/>
+      <c r="S1" s="201"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2759,165 +2615,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="222"/>
-      <c r="P2" s="223"/>
-      <c r="Q2" s="223"/>
-      <c r="R2" s="223"/>
-      <c r="S2" s="224"/>
+      <c r="O2" s="202"/>
+      <c r="P2" s="203"/>
+      <c r="Q2" s="203"/>
+      <c r="R2" s="203"/>
+      <c r="S2" s="204"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="242"/>
-      <c r="C3" s="243"/>
-      <c r="D3" s="244"/>
+      <c r="B3" s="220"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="222"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="175"/>
-      <c r="J3" s="176"/>
-      <c r="K3" s="177"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="225"/>
+      <c r="K3" s="226"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="237"/>
-      <c r="P3" s="238"/>
-      <c r="Q3" s="238"/>
-      <c r="R3" s="238"/>
-      <c r="S3" s="239"/>
+      <c r="O3" s="213"/>
+      <c r="P3" s="195"/>
+      <c r="Q3" s="195"/>
+      <c r="R3" s="195"/>
+      <c r="S3" s="196"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="215"/>
+      <c r="B4" s="247"/>
+      <c r="C4" s="248"/>
+      <c r="D4" s="249"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="216"/>
-      <c r="J4" s="217"/>
-      <c r="K4" s="218"/>
+      <c r="I4" s="250"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="252"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="237"/>
-      <c r="P4" s="238"/>
-      <c r="Q4" s="238"/>
-      <c r="R4" s="238"/>
-      <c r="S4" s="239"/>
+      <c r="O4" s="213"/>
+      <c r="P4" s="195"/>
+      <c r="Q4" s="195"/>
+      <c r="R4" s="195"/>
+      <c r="S4" s="196"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="252"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="254"/>
+      <c r="B5" s="183"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="185"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="261"/>
-      <c r="J5" s="238"/>
-      <c r="K5" s="239"/>
+      <c r="I5" s="194"/>
+      <c r="J5" s="195"/>
+      <c r="K5" s="196"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="237"/>
-      <c r="P5" s="238"/>
-      <c r="Q5" s="238"/>
-      <c r="R5" s="238"/>
-      <c r="S5" s="239"/>
+      <c r="O5" s="213"/>
+      <c r="P5" s="195"/>
+      <c r="Q5" s="195"/>
+      <c r="R5" s="195"/>
+      <c r="S5" s="196"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="257"/>
-      <c r="C6" s="258"/>
-      <c r="D6" s="259"/>
+      <c r="B6" s="188"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="190"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="260"/>
-      <c r="J6" s="226"/>
-      <c r="K6" s="227"/>
+      <c r="I6" s="191"/>
+      <c r="J6" s="192"/>
+      <c r="K6" s="193"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="225"/>
-      <c r="P6" s="226"/>
-      <c r="Q6" s="226"/>
-      <c r="R6" s="226"/>
-      <c r="S6" s="227"/>
+      <c r="O6" s="205"/>
+      <c r="P6" s="192"/>
+      <c r="Q6" s="192"/>
+      <c r="R6" s="192"/>
+      <c r="S6" s="193"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="181" t="s">
+      <c r="A8" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="182"/>
-      <c r="C8" s="182"/>
-      <c r="D8" s="183"/>
-      <c r="F8" s="228" t="s">
+      <c r="B8" s="229"/>
+      <c r="C8" s="229"/>
+      <c r="D8" s="230"/>
+      <c r="F8" s="197" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="229"/>
-      <c r="H8" s="229"/>
-      <c r="I8" s="229"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="229"/>
-      <c r="L8" s="229"/>
-      <c r="M8" s="229"/>
-      <c r="N8" s="229"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="229"/>
-      <c r="Q8" s="229"/>
-      <c r="R8" s="229"/>
-      <c r="S8" s="230"/>
+      <c r="G8" s="198"/>
+      <c r="H8" s="198"/>
+      <c r="I8" s="198"/>
+      <c r="J8" s="198"/>
+      <c r="K8" s="198"/>
+      <c r="L8" s="198"/>
+      <c r="M8" s="198"/>
+      <c r="N8" s="198"/>
+      <c r="O8" s="198"/>
+      <c r="P8" s="198"/>
+      <c r="Q8" s="198"/>
+      <c r="R8" s="198"/>
+      <c r="S8" s="206"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="184"/>
-      <c r="B9" s="185"/>
-      <c r="C9" s="185"/>
-      <c r="D9" s="186"/>
-      <c r="F9" s="209" t="s">
+      <c r="A9" s="231"/>
+      <c r="B9" s="232"/>
+      <c r="C9" s="232"/>
+      <c r="D9" s="233"/>
+      <c r="F9" s="243" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="210"/>
-      <c r="H9" s="255" t="s">
+      <c r="G9" s="244"/>
+      <c r="H9" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="256"/>
-      <c r="J9" s="207" t="s">
+      <c r="I9" s="187"/>
+      <c r="J9" s="241" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="208"/>
-      <c r="L9" s="250" t="s">
+      <c r="K9" s="242"/>
+      <c r="L9" s="181" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="251"/>
-      <c r="N9" s="187" t="s">
+      <c r="M9" s="182"/>
+      <c r="N9" s="218" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="188"/>
-      <c r="P9" s="202" t="s">
+      <c r="O9" s="219"/>
+      <c r="P9" s="236" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="203"/>
-      <c r="R9" s="187" t="s">
+      <c r="Q9" s="237"/>
+      <c r="R9" s="218" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="188"/>
+      <c r="S9" s="219"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="240" t="s">
+      <c r="A10" s="214" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2974,7 +2830,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="179"/>
+      <c r="A11" s="215"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -3080,7 +2936,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="179"/>
+      <c r="A12" s="215"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3186,7 +3042,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="179"/>
+      <c r="A13" s="215"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3292,7 +3148,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="179"/>
+      <c r="A14" s="215"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3379,7 +3235,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="179"/>
+      <c r="A15" s="215"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3466,7 +3322,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="179"/>
+      <c r="A16" s="215"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3553,7 +3409,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="179"/>
+      <c r="A17" s="215"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3640,7 +3496,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="179"/>
+      <c r="A18" s="215"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3727,7 +3583,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="179"/>
+      <c r="A19" s="215"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3814,7 +3670,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="179"/>
+      <c r="A20" s="215"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3901,7 +3757,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="179"/>
+      <c r="A21" s="215"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3988,7 +3844,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="241"/>
+      <c r="A22" s="216"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -4131,7 +3987,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="240" t="s">
+      <c r="A24" s="214" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -4239,7 +4095,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="179"/>
+      <c r="A25" s="215"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4345,7 +4201,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="179"/>
+      <c r="A26" s="215"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4451,7 +4307,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="179"/>
+      <c r="A27" s="215"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4538,7 +4394,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="180"/>
+      <c r="A28" s="217"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4700,7 +4556,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="204" t="s">
+      <c r="A32" s="238" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4779,7 +4635,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="205"/>
+      <c r="A33" s="239"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4856,7 +4712,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="206"/>
+      <c r="A34" s="240"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4954,7 +4810,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="204" t="s">
+      <c r="A36" s="238" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -5033,7 +4889,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="205"/>
+      <c r="A37" s="239"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -5110,7 +4966,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="206"/>
+      <c r="A38" s="240"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5201,7 +5057,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="240" t="s">
+      <c r="A40" s="214" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5213,31 +5069,31 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="231" t="s">
+      <c r="F40" s="207" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="232"/>
-      <c r="H40" s="232"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
-      <c r="M40" s="232"/>
-      <c r="N40" s="232"/>
-      <c r="O40" s="232"/>
-      <c r="P40" s="232"/>
-      <c r="Q40" s="232"/>
-      <c r="R40" s="232"/>
-      <c r="S40" s="233"/>
+      <c r="G40" s="208"/>
+      <c r="H40" s="208"/>
+      <c r="I40" s="208"/>
+      <c r="J40" s="208"/>
+      <c r="K40" s="208"/>
+      <c r="L40" s="208"/>
+      <c r="M40" s="208"/>
+      <c r="N40" s="208"/>
+      <c r="O40" s="208"/>
+      <c r="P40" s="208"/>
+      <c r="Q40" s="208"/>
+      <c r="R40" s="208"/>
+      <c r="S40" s="209"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="179"/>
+      <c r="A41" s="215"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="29">
-        <f>SUMIF(Taiere!I2:I99, "PAL", Taiere!C2:C99)+SUMIF(Taiere!I2:I99, "DB PAL", Taiere!C2:C99)</f>
-        <v>0</v>
+      <c r="C41" s="29" t="str">
+        <f>IF(SUMIF(Taiere!I2:I99,"PAL",Taiere!C2:C99)+SUMIF(Taiere!I2:I99,"DB PAL",Taiere!C2:C99)=0,"",SUMIF(Taiere!I2:I99,"PAL",Taiere!C2:C99)+SUMIF(Taiere!I2:I99,"DB PAL",Taiere!C2:C99))</f>
+        <v/>
       </c>
       <c r="D41" s="73" t="s">
         <v>54</v>
@@ -5294,13 +5150,13 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="179"/>
+      <c r="A42" s="215"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="C42" s="37">
-        <f>SUMIF(Taiere!I2:I99, "CLEAF", Taiere!C2:C99)</f>
-        <v>0</v>
+      <c r="C42" s="37" t="str">
+        <f>IF(SUMIF(Taiere!I2:I99,"CLEAF",Taiere!C2:C99)=0,"",(SUMIF(Taiere!I2:I99,"CLEAF",Taiere!C2:C99)))</f>
+        <v/>
       </c>
       <c r="D42" s="74" t="s">
         <v>54</v>
@@ -5319,50 +5175,50 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="198">
+      <c r="S42" s="175">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="179"/>
+      <c r="A43" s="215"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="30">
-        <f>SUMIF(B32:B34, "*/600", C32:C34) + SUMIF(B32:B34, "*/650", C32:C34)</f>
-        <v>0</v>
+      <c r="C43" s="30" t="str">
+        <f>IF(SUMIF(B32:B34, "*/600", C32:C34) + SUMIF(B32:B34, "*/650", C32:C34)=0, "",SUMIF(B32:B34, "*/600", C32:C34) + SUMIF(B32:B34, "*/650", C32:C34))</f>
+        <v/>
       </c>
       <c r="D43" s="74" t="s">
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="228" t="str">
+      <c r="F43" s="197" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="229"/>
-      <c r="H43" s="229"/>
-      <c r="I43" s="229"/>
-      <c r="J43" s="229"/>
-      <c r="K43" s="229"/>
-      <c r="L43" s="229"/>
-      <c r="M43" s="229"/>
-      <c r="N43" s="229"/>
-      <c r="O43" s="229"/>
-      <c r="P43" s="229"/>
-      <c r="Q43" s="229"/>
-      <c r="R43" s="229"/>
-      <c r="S43" s="245"/>
+      <c r="G43" s="198"/>
+      <c r="H43" s="198"/>
+      <c r="I43" s="198"/>
+      <c r="J43" s="198"/>
+      <c r="K43" s="198"/>
+      <c r="L43" s="198"/>
+      <c r="M43" s="198"/>
+      <c r="N43" s="198"/>
+      <c r="O43" s="198"/>
+      <c r="P43" s="198"/>
+      <c r="Q43" s="198"/>
+      <c r="R43" s="198"/>
+      <c r="S43" s="176"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="179"/>
+      <c r="A44" s="215"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="C44" s="30">
-        <f>SUMIF(B32:B34, "*/920", C32:C34)</f>
-        <v>0</v>
+      <c r="C44" s="30" t="str">
+        <f>IF(SUMIF(B32:B34, "*/920", C32:C34)=0, "",SUMIF(B32:B34, "*/920", C32:C34)=0)</f>
+        <v/>
       </c>
       <c r="D44" s="74" t="s">
         <v>55</v>
@@ -5412,13 +5268,13 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="179"/>
+      <c r="A45" s="215"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="30">
-        <f>SUM(C36:C38)</f>
-        <v>0</v>
+      <c r="C45" s="30" t="str">
+        <f>IF(SUM(C36:C38)=0,"",SUM(C36:C38))</f>
+        <v/>
       </c>
       <c r="D45" s="74" t="str">
         <f>IF(I3="Mobilier în Roomdesigner", "ml", "buc")</f>
@@ -5546,7 +5402,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="179"/>
+      <c r="A46" s="215"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5560,61 +5416,61 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="179"/>
+      <c r="A47" s="215"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C47" s="30">
-        <f>SUMIF(Taiere!I2:I99, "MDF", Taiere!C2:C99)+SUMIF(Taiere!I2:I99, "DB MDF", Taiere!C2:C99)</f>
-        <v>0</v>
+      <c r="C47" s="30" t="str">
+        <f>IF(SUMIF(Taiere!I2:I99, "MDF", Taiere!C2:C99)+SUMIF(Taiere!I2:I99, "DB MDF", Taiere!C2:C99)=0,"",SUMIF(Taiere!I2:I99, "MDF", Taiere!C2:C99)+SUMIF(Taiere!I2:I99, "DB MDF", Taiere!C2:C99))</f>
+        <v/>
       </c>
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="198" t="s">
+      <c r="F47" s="175" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="211" t="str">
+      <c r="G47" s="245" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="198" t="s">
+      <c r="J47" s="175" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="200">
+      <c r="K47" s="234">
         <v>1</v>
       </c>
-      <c r="N47" s="198" t="s">
+      <c r="N47" s="175" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="246"/>
-      <c r="P47" s="247"/>
-      <c r="R47" s="198" t="s">
+      <c r="O47" s="177"/>
+      <c r="P47" s="178"/>
+      <c r="R47" s="175" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="198"/>
+      <c r="S47" s="175"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="180"/>
+      <c r="A48" s="217"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="31">
-        <f>SUMIF(Deco!W2:W99, "DB PAL", Deco!V2:V99)+SUMIF(Deco!W2:W99, "DB MDF", Deco!V2:V99)</f>
-        <v>0</v>
+      <c r="C48" s="31" t="str">
+        <f>IF(SUMIF(Deco!W2:W99, "DB PAL", Deco!V2:V99)+SUMIF(Deco!W2:W99, "DB MDF", Deco!V2:V99)=0, "",SUMIF(Deco!W2:W99, "DB PAL", Deco!V2:V99)+SUMIF(Deco!W2:W99, "DB MDF", Deco!V2:V99))</f>
+        <v/>
       </c>
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="199"/>
-      <c r="G48" s="212"/>
-      <c r="J48" s="199"/>
-      <c r="K48" s="201"/>
-      <c r="N48" s="245"/>
-      <c r="O48" s="248"/>
-      <c r="P48" s="249"/>
-      <c r="R48" s="245"/>
-      <c r="S48" s="199"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="246"/>
+      <c r="J48" s="223"/>
+      <c r="K48" s="235"/>
+      <c r="N48" s="176"/>
+      <c r="O48" s="179"/>
+      <c r="P48" s="180"/>
+      <c r="R48" s="176"/>
+      <c r="S48" s="223"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5623,187 +5479,192 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="178" t="s">
+      <c r="A50" s="227" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="189"/>
-      <c r="C50" s="190"/>
-      <c r="D50" s="190"/>
-      <c r="E50" s="190"/>
-      <c r="F50" s="190"/>
-      <c r="G50" s="190"/>
-      <c r="H50" s="190"/>
-      <c r="I50" s="190"/>
-      <c r="J50" s="190"/>
-      <c r="K50" s="190"/>
-      <c r="L50" s="190"/>
-      <c r="M50" s="190"/>
-      <c r="N50" s="190"/>
-      <c r="O50" s="190"/>
-      <c r="P50" s="190"/>
-      <c r="Q50" s="190"/>
-      <c r="R50" s="190"/>
-      <c r="S50" s="191"/>
+      <c r="B50" s="256"/>
+      <c r="C50" s="257"/>
+      <c r="D50" s="257"/>
+      <c r="E50" s="257"/>
+      <c r="F50" s="257"/>
+      <c r="G50" s="257"/>
+      <c r="H50" s="257"/>
+      <c r="I50" s="257"/>
+      <c r="J50" s="257"/>
+      <c r="K50" s="257"/>
+      <c r="L50" s="257"/>
+      <c r="M50" s="257"/>
+      <c r="N50" s="257"/>
+      <c r="O50" s="257"/>
+      <c r="P50" s="257"/>
+      <c r="Q50" s="257"/>
+      <c r="R50" s="257"/>
+      <c r="S50" s="258"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="179"/>
-      <c r="B51" s="192"/>
-      <c r="C51" s="193"/>
-      <c r="D51" s="193"/>
-      <c r="E51" s="193"/>
-      <c r="F51" s="193"/>
-      <c r="G51" s="193"/>
-      <c r="H51" s="193"/>
-      <c r="I51" s="193"/>
-      <c r="J51" s="193"/>
-      <c r="K51" s="193"/>
-      <c r="L51" s="193"/>
-      <c r="M51" s="193"/>
-      <c r="N51" s="193"/>
-      <c r="O51" s="193"/>
-      <c r="P51" s="193"/>
-      <c r="Q51" s="193"/>
-      <c r="R51" s="193"/>
-      <c r="S51" s="194"/>
+      <c r="A51" s="215"/>
+      <c r="B51" s="259"/>
+      <c r="C51" s="260"/>
+      <c r="D51" s="260"/>
+      <c r="E51" s="260"/>
+      <c r="F51" s="260"/>
+      <c r="G51" s="260"/>
+      <c r="H51" s="260"/>
+      <c r="I51" s="260"/>
+      <c r="J51" s="260"/>
+      <c r="K51" s="260"/>
+      <c r="L51" s="260"/>
+      <c r="M51" s="260"/>
+      <c r="N51" s="260"/>
+      <c r="O51" s="260"/>
+      <c r="P51" s="260"/>
+      <c r="Q51" s="260"/>
+      <c r="R51" s="260"/>
+      <c r="S51" s="261"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="179"/>
-      <c r="B52" s="192"/>
-      <c r="C52" s="193"/>
-      <c r="D52" s="193"/>
-      <c r="E52" s="193"/>
-      <c r="F52" s="193"/>
-      <c r="G52" s="193"/>
-      <c r="H52" s="193"/>
-      <c r="I52" s="193"/>
-      <c r="J52" s="193"/>
-      <c r="K52" s="193"/>
-      <c r="L52" s="193"/>
-      <c r="M52" s="193"/>
-      <c r="N52" s="193"/>
-      <c r="O52" s="193"/>
-      <c r="P52" s="193"/>
-      <c r="Q52" s="193"/>
-      <c r="R52" s="193"/>
-      <c r="S52" s="194"/>
+      <c r="A52" s="215"/>
+      <c r="B52" s="259"/>
+      <c r="C52" s="260"/>
+      <c r="D52" s="260"/>
+      <c r="E52" s="260"/>
+      <c r="F52" s="260"/>
+      <c r="G52" s="260"/>
+      <c r="H52" s="260"/>
+      <c r="I52" s="260"/>
+      <c r="J52" s="260"/>
+      <c r="K52" s="260"/>
+      <c r="L52" s="260"/>
+      <c r="M52" s="260"/>
+      <c r="N52" s="260"/>
+      <c r="O52" s="260"/>
+      <c r="P52" s="260"/>
+      <c r="Q52" s="260"/>
+      <c r="R52" s="260"/>
+      <c r="S52" s="261"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="179"/>
-      <c r="B53" s="192"/>
-      <c r="C53" s="193"/>
-      <c r="D53" s="193"/>
-      <c r="E53" s="193"/>
-      <c r="F53" s="193"/>
-      <c r="G53" s="193"/>
-      <c r="H53" s="193"/>
-      <c r="I53" s="193"/>
-      <c r="J53" s="193"/>
-      <c r="K53" s="193"/>
-      <c r="L53" s="193"/>
-      <c r="M53" s="193"/>
-      <c r="N53" s="193"/>
-      <c r="O53" s="193"/>
-      <c r="P53" s="193"/>
-      <c r="Q53" s="193"/>
-      <c r="R53" s="193"/>
-      <c r="S53" s="194"/>
+      <c r="A53" s="215"/>
+      <c r="B53" s="259"/>
+      <c r="C53" s="260"/>
+      <c r="D53" s="260"/>
+      <c r="E53" s="260"/>
+      <c r="F53" s="260"/>
+      <c r="G53" s="260"/>
+      <c r="H53" s="260"/>
+      <c r="I53" s="260"/>
+      <c r="J53" s="260"/>
+      <c r="K53" s="260"/>
+      <c r="L53" s="260"/>
+      <c r="M53" s="260"/>
+      <c r="N53" s="260"/>
+      <c r="O53" s="260"/>
+      <c r="P53" s="260"/>
+      <c r="Q53" s="260"/>
+      <c r="R53" s="260"/>
+      <c r="S53" s="261"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="179"/>
-      <c r="B54" s="192"/>
-      <c r="C54" s="193"/>
-      <c r="D54" s="193"/>
-      <c r="E54" s="193"/>
-      <c r="F54" s="193"/>
-      <c r="G54" s="193"/>
-      <c r="H54" s="193"/>
-      <c r="I54" s="193"/>
-      <c r="J54" s="193"/>
-      <c r="K54" s="193"/>
-      <c r="L54" s="193"/>
-      <c r="M54" s="193"/>
-      <c r="N54" s="193"/>
-      <c r="O54" s="193"/>
-      <c r="P54" s="193"/>
-      <c r="Q54" s="193"/>
-      <c r="R54" s="193"/>
-      <c r="S54" s="194"/>
+      <c r="A54" s="215"/>
+      <c r="B54" s="259"/>
+      <c r="C54" s="260"/>
+      <c r="D54" s="260"/>
+      <c r="E54" s="260"/>
+      <c r="F54" s="260"/>
+      <c r="G54" s="260"/>
+      <c r="H54" s="260"/>
+      <c r="I54" s="260"/>
+      <c r="J54" s="260"/>
+      <c r="K54" s="260"/>
+      <c r="L54" s="260"/>
+      <c r="M54" s="260"/>
+      <c r="N54" s="260"/>
+      <c r="O54" s="260"/>
+      <c r="P54" s="260"/>
+      <c r="Q54" s="260"/>
+      <c r="R54" s="260"/>
+      <c r="S54" s="261"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="179"/>
-      <c r="B55" s="192"/>
-      <c r="C55" s="193"/>
-      <c r="D55" s="193"/>
-      <c r="E55" s="193"/>
-      <c r="F55" s="193"/>
-      <c r="G55" s="193"/>
-      <c r="H55" s="193"/>
-      <c r="I55" s="193"/>
-      <c r="J55" s="193"/>
-      <c r="K55" s="193"/>
-      <c r="L55" s="193"/>
-      <c r="M55" s="193"/>
-      <c r="N55" s="193"/>
-      <c r="O55" s="193"/>
-      <c r="P55" s="193"/>
-      <c r="Q55" s="193"/>
-      <c r="R55" s="193"/>
-      <c r="S55" s="194"/>
+      <c r="A55" s="215"/>
+      <c r="B55" s="259"/>
+      <c r="C55" s="260"/>
+      <c r="D55" s="260"/>
+      <c r="E55" s="260"/>
+      <c r="F55" s="260"/>
+      <c r="G55" s="260"/>
+      <c r="H55" s="260"/>
+      <c r="I55" s="260"/>
+      <c r="J55" s="260"/>
+      <c r="K55" s="260"/>
+      <c r="L55" s="260"/>
+      <c r="M55" s="260"/>
+      <c r="N55" s="260"/>
+      <c r="O55" s="260"/>
+      <c r="P55" s="260"/>
+      <c r="Q55" s="260"/>
+      <c r="R55" s="260"/>
+      <c r="S55" s="261"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="179"/>
-      <c r="B56" s="192"/>
-      <c r="C56" s="193"/>
-      <c r="D56" s="193"/>
-      <c r="E56" s="193"/>
-      <c r="F56" s="193"/>
-      <c r="G56" s="193"/>
-      <c r="H56" s="193"/>
-      <c r="I56" s="193"/>
-      <c r="J56" s="193"/>
-      <c r="K56" s="193"/>
-      <c r="L56" s="193"/>
-      <c r="M56" s="193"/>
-      <c r="N56" s="193"/>
-      <c r="O56" s="193"/>
-      <c r="P56" s="193"/>
-      <c r="Q56" s="193"/>
-      <c r="R56" s="193"/>
-      <c r="S56" s="194"/>
+      <c r="A56" s="215"/>
+      <c r="B56" s="259"/>
+      <c r="C56" s="260"/>
+      <c r="D56" s="260"/>
+      <c r="E56" s="260"/>
+      <c r="F56" s="260"/>
+      <c r="G56" s="260"/>
+      <c r="H56" s="260"/>
+      <c r="I56" s="260"/>
+      <c r="J56" s="260"/>
+      <c r="K56" s="260"/>
+      <c r="L56" s="260"/>
+      <c r="M56" s="260"/>
+      <c r="N56" s="260"/>
+      <c r="O56" s="260"/>
+      <c r="P56" s="260"/>
+      <c r="Q56" s="260"/>
+      <c r="R56" s="260"/>
+      <c r="S56" s="261"/>
     </row>
     <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="180"/>
-      <c r="B57" s="195"/>
-      <c r="C57" s="196"/>
-      <c r="D57" s="196"/>
-      <c r="E57" s="196"/>
-      <c r="F57" s="196"/>
-      <c r="G57" s="196"/>
-      <c r="H57" s="196"/>
-      <c r="I57" s="196"/>
-      <c r="J57" s="196"/>
-      <c r="K57" s="196"/>
-      <c r="L57" s="196"/>
-      <c r="M57" s="196"/>
-      <c r="N57" s="196"/>
-      <c r="O57" s="196"/>
-      <c r="P57" s="196"/>
-      <c r="Q57" s="196"/>
-      <c r="R57" s="196"/>
-      <c r="S57" s="197"/>
+      <c r="A57" s="217"/>
+      <c r="B57" s="262"/>
+      <c r="C57" s="263"/>
+      <c r="D57" s="263"/>
+      <c r="E57" s="263"/>
+      <c r="F57" s="263"/>
+      <c r="G57" s="263"/>
+      <c r="H57" s="263"/>
+      <c r="I57" s="263"/>
+      <c r="J57" s="263"/>
+      <c r="K57" s="263"/>
+      <c r="L57" s="263"/>
+      <c r="M57" s="263"/>
+      <c r="N57" s="263"/>
+      <c r="O57" s="263"/>
+      <c r="P57" s="263"/>
+      <c r="Q57" s="263"/>
+      <c r="R57" s="263"/>
+      <c r="S57" s="264"/>
     </row>
   </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
+  <mergeCells count="41">
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A50:A57"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="O6:S6"/>
@@ -5820,27 +5681,20 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="R47:R48"/>
     <mergeCell ref="S47:S48"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="B50:S57"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="64" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -8778,9 +8632,9 @@
       <c r="A187" t="s">
         <v>33</v>
       </c>
-      <c r="B187">
+      <c r="B187" t="str">
         <f>Fisa!C43</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D187" t="str">
         <f t="shared" si="4"/>
@@ -8791,9 +8645,9 @@
       <c r="A188" t="s">
         <v>31</v>
       </c>
-      <c r="B188">
+      <c r="B188" t="str">
         <f>Fisa!C44</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D188" t="str">
         <f t="shared" si="4"/>
@@ -8804,9 +8658,9 @@
       <c r="A189" t="s">
         <v>32</v>
       </c>
-      <c r="B189">
+      <c r="B189" t="str">
         <f>Fisa!C45</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D189" t="str">
         <f t="shared" si="4"/>
@@ -8830,9 +8684,9 @@
       <c r="A191" t="s">
         <v>21</v>
       </c>
-      <c r="B191">
+      <c r="B191" t="str">
         <f>Fisa!C47</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D191" t="str">
         <f t="shared" si="4"/>
@@ -8843,9 +8697,9 @@
       <c r="A192" t="s">
         <v>22</v>
       </c>
-      <c r="B192">
+      <c r="B192" t="str">
         <f>Fisa!C41</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D192" t="str">
         <f>CONCATENATE(A192,C192)</f>
@@ -8856,9 +8710,9 @@
       <c r="A193" t="s">
         <v>94</v>
       </c>
-      <c r="B193">
+      <c r="B193" t="str">
         <f>Fisa!C42</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D193" t="str">
         <f t="shared" ref="D193:D194" si="5">CONCATENATE(A193,C193)</f>
@@ -8869,9 +8723,9 @@
       <c r="A194" t="s">
         <v>23</v>
       </c>
-      <c r="B194">
+      <c r="B194" t="str">
         <f>Fisa!C48</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="D194" t="str">
         <f t="shared" si="5"/>
@@ -9022,18 +8876,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customFormat="1">
-      <c r="A1" s="262" t="s">
+      <c r="A1" s="253" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="262"/>
-      <c r="C1" s="262"/>
-      <c r="D1" s="262"/>
-      <c r="E1" s="262"/>
-      <c r="F1" s="262"/>
-      <c r="G1" s="262"/>
-      <c r="H1" s="262"/>
-      <c r="I1" s="262"/>
-      <c r="J1" s="262"/>
+      <c r="B1" s="253"/>
+      <c r="C1" s="253"/>
+      <c r="D1" s="253"/>
+      <c r="E1" s="253"/>
+      <c r="F1" s="253"/>
+      <c r="G1" s="253"/>
+      <c r="H1" s="253"/>
+      <c r="I1" s="253"/>
+      <c r="J1" s="253"/>
       <c r="K1" s="12"/>
       <c r="L1" s="5"/>
     </row>
@@ -9054,15 +8908,15 @@
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="263">
+      <c r="B3" s="254">
         <f>Fisa!B3:D3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="263"/>
-      <c r="D3" s="263"/>
-      <c r="E3" s="263"/>
-      <c r="F3" s="263"/>
-      <c r="G3" s="263"/>
+      <c r="C3" s="254"/>
+      <c r="D3" s="254"/>
+      <c r="E3" s="254"/>
+      <c r="F3" s="254"/>
+      <c r="G3" s="254"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -9073,11 +8927,11 @@
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="264">
+      <c r="B4" s="255">
         <f>Fisa!B6</f>
         <v>0</v>
       </c>
-      <c r="C4" s="264"/>
+      <c r="C4" s="255"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9919665A-135A-40C7-AE15-4A793A60FADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC4E2B6-DBB6-4D55-BDB3-3720058E6DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -599,7 +599,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -1135,19 +1135,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1297,7 +1284,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="265">
+  <cellXfs count="269">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1511,13 +1498,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1664,9 +1651,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1724,7 +1711,7 @@
     <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1734,17 +1721,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
@@ -1782,7 +1769,7 @@
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="52" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="168" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1792,20 +1779,226 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1861,203 +2054,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2067,32 +2066,22 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2545,7 +2534,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S57"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -2570,33 +2559,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="210" t="s">
+      <c r="A1" s="229" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="211"/>
-      <c r="C1" s="211"/>
-      <c r="D1" s="211"/>
-      <c r="E1" s="211"/>
-      <c r="F1" s="211"/>
-      <c r="G1" s="211"/>
-      <c r="H1" s="211"/>
-      <c r="I1" s="211"/>
-      <c r="J1" s="211"/>
-      <c r="K1" s="211"/>
-      <c r="L1" s="212"/>
+      <c r="B1" s="230"/>
+      <c r="C1" s="230"/>
+      <c r="D1" s="230"/>
+      <c r="E1" s="230"/>
+      <c r="F1" s="230"/>
+      <c r="G1" s="230"/>
+      <c r="H1" s="230"/>
+      <c r="I1" s="230"/>
+      <c r="J1" s="230"/>
+      <c r="K1" s="230"/>
+      <c r="L1" s="231"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="199" t="s">
+      <c r="O1" s="214" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="200"/>
-      <c r="Q1" s="200"/>
-      <c r="R1" s="200"/>
-      <c r="S1" s="201"/>
+      <c r="P1" s="215"/>
+      <c r="Q1" s="215"/>
+      <c r="R1" s="215"/>
+      <c r="S1" s="216"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2615,165 +2604,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="202"/>
-      <c r="P2" s="203"/>
-      <c r="Q2" s="203"/>
-      <c r="R2" s="203"/>
-      <c r="S2" s="204"/>
+      <c r="O2" s="217"/>
+      <c r="P2" s="218"/>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="218"/>
+      <c r="S2" s="219"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="220"/>
-      <c r="C3" s="221"/>
-      <c r="D3" s="222"/>
+      <c r="B3" s="237"/>
+      <c r="C3" s="238"/>
+      <c r="D3" s="239"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="225"/>
-      <c r="K3" s="226"/>
+      <c r="I3" s="180"/>
+      <c r="J3" s="181"/>
+      <c r="K3" s="182"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="213"/>
-      <c r="P3" s="195"/>
-      <c r="Q3" s="195"/>
-      <c r="R3" s="195"/>
-      <c r="S3" s="196"/>
+      <c r="O3" s="232"/>
+      <c r="P3" s="233"/>
+      <c r="Q3" s="233"/>
+      <c r="R3" s="233"/>
+      <c r="S3" s="234"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="247"/>
-      <c r="C4" s="248"/>
-      <c r="D4" s="249"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="209"/>
+      <c r="D4" s="210"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="250"/>
-      <c r="J4" s="251"/>
-      <c r="K4" s="252"/>
+      <c r="I4" s="211"/>
+      <c r="J4" s="212"/>
+      <c r="K4" s="213"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="195"/>
-      <c r="Q4" s="195"/>
-      <c r="R4" s="195"/>
-      <c r="S4" s="196"/>
+      <c r="O4" s="232"/>
+      <c r="P4" s="233"/>
+      <c r="Q4" s="233"/>
+      <c r="R4" s="233"/>
+      <c r="S4" s="234"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="185"/>
+      <c r="B5" s="247"/>
+      <c r="C5" s="248"/>
+      <c r="D5" s="249"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="194"/>
-      <c r="J5" s="195"/>
-      <c r="K5" s="196"/>
+      <c r="I5" s="256"/>
+      <c r="J5" s="233"/>
+      <c r="K5" s="234"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="213"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="195"/>
-      <c r="R5" s="195"/>
-      <c r="S5" s="196"/>
+      <c r="O5" s="232"/>
+      <c r="P5" s="233"/>
+      <c r="Q5" s="233"/>
+      <c r="R5" s="233"/>
+      <c r="S5" s="234"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="188"/>
-      <c r="C6" s="189"/>
-      <c r="D6" s="190"/>
+      <c r="B6" s="252"/>
+      <c r="C6" s="253"/>
+      <c r="D6" s="254"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="191"/>
-      <c r="J6" s="192"/>
-      <c r="K6" s="193"/>
+      <c r="I6" s="255"/>
+      <c r="J6" s="221"/>
+      <c r="K6" s="222"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="205"/>
-      <c r="P6" s="192"/>
-      <c r="Q6" s="192"/>
-      <c r="R6" s="192"/>
-      <c r="S6" s="193"/>
+      <c r="O6" s="220"/>
+      <c r="P6" s="221"/>
+      <c r="Q6" s="221"/>
+      <c r="R6" s="221"/>
+      <c r="S6" s="222"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="228" t="s">
+      <c r="A8" s="185" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="229"/>
-      <c r="C8" s="229"/>
-      <c r="D8" s="230"/>
-      <c r="F8" s="197" t="s">
+      <c r="B8" s="186"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="187"/>
+      <c r="F8" s="223" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="198"/>
-      <c r="H8" s="198"/>
-      <c r="I8" s="198"/>
-      <c r="J8" s="198"/>
-      <c r="K8" s="198"/>
-      <c r="L8" s="198"/>
-      <c r="M8" s="198"/>
-      <c r="N8" s="198"/>
-      <c r="O8" s="198"/>
-      <c r="P8" s="198"/>
-      <c r="Q8" s="198"/>
-      <c r="R8" s="198"/>
-      <c r="S8" s="206"/>
+      <c r="G8" s="224"/>
+      <c r="H8" s="224"/>
+      <c r="I8" s="224"/>
+      <c r="J8" s="224"/>
+      <c r="K8" s="224"/>
+      <c r="L8" s="224"/>
+      <c r="M8" s="224"/>
+      <c r="N8" s="224"/>
+      <c r="O8" s="224"/>
+      <c r="P8" s="224"/>
+      <c r="Q8" s="224"/>
+      <c r="R8" s="224"/>
+      <c r="S8" s="225"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="231"/>
-      <c r="B9" s="232"/>
-      <c r="C9" s="232"/>
-      <c r="D9" s="233"/>
-      <c r="F9" s="243" t="s">
+      <c r="A9" s="188"/>
+      <c r="B9" s="189"/>
+      <c r="C9" s="189"/>
+      <c r="D9" s="190"/>
+      <c r="F9" s="204" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="244"/>
-      <c r="H9" s="186" t="s">
+      <c r="G9" s="205"/>
+      <c r="H9" s="250" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="187"/>
-      <c r="J9" s="241" t="s">
+      <c r="I9" s="251"/>
+      <c r="J9" s="202" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="242"/>
-      <c r="L9" s="181" t="s">
+      <c r="K9" s="203"/>
+      <c r="L9" s="245" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="182"/>
-      <c r="N9" s="218" t="s">
+      <c r="M9" s="246"/>
+      <c r="N9" s="191" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="219"/>
-      <c r="P9" s="236" t="s">
+      <c r="O9" s="192"/>
+      <c r="P9" s="197" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="237"/>
-      <c r="R9" s="218" t="s">
+      <c r="Q9" s="198"/>
+      <c r="R9" s="191" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="219"/>
+      <c r="S9" s="192"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="214" t="s">
+      <c r="A10" s="235" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2830,7 +2819,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="215"/>
+      <c r="A11" s="183"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2936,7 +2925,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="215"/>
+      <c r="A12" s="183"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3042,7 +3031,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="215"/>
+      <c r="A13" s="183"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3148,7 +3137,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="215"/>
+      <c r="A14" s="183"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3235,7 +3224,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="215"/>
+      <c r="A15" s="183"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3322,7 +3311,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="215"/>
+      <c r="A16" s="183"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3409,7 +3398,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="215"/>
+      <c r="A17" s="183"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3496,7 +3485,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="215"/>
+      <c r="A18" s="183"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3583,7 +3572,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="215"/>
+      <c r="A19" s="183"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3670,7 +3659,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="215"/>
+      <c r="A20" s="183"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3757,7 +3746,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="215"/>
+      <c r="A21" s="183"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3844,7 +3833,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="216"/>
+      <c r="A22" s="236"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3987,7 +3976,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="214" t="s">
+      <c r="A24" s="235" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -4095,7 +4084,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="215"/>
+      <c r="A25" s="183"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4201,7 +4190,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="215"/>
+      <c r="A26" s="183"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4307,7 +4296,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="215"/>
+      <c r="A27" s="183"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4394,7 +4383,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="217"/>
+      <c r="A28" s="184"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4556,7 +4545,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="238" t="s">
+      <c r="A32" s="199" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4635,7 +4624,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="239"/>
+      <c r="A33" s="200"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4712,7 +4701,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="240"/>
+      <c r="A34" s="201"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4810,7 +4799,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="238" t="s">
+      <c r="A36" s="199" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4889,7 +4878,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="239"/>
+      <c r="A37" s="200"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4966,7 +4955,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="240"/>
+      <c r="A38" s="201"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5057,7 +5046,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="214" t="s">
+      <c r="A40" s="235" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5069,25 +5058,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="207" t="s">
+      <c r="F40" s="226" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="208"/>
-      <c r="H40" s="208"/>
-      <c r="I40" s="208"/>
-      <c r="J40" s="208"/>
-      <c r="K40" s="208"/>
-      <c r="L40" s="208"/>
-      <c r="M40" s="208"/>
-      <c r="N40" s="208"/>
-      <c r="O40" s="208"/>
-      <c r="P40" s="208"/>
-      <c r="Q40" s="208"/>
-      <c r="R40" s="208"/>
-      <c r="S40" s="209"/>
+      <c r="G40" s="227"/>
+      <c r="H40" s="227"/>
+      <c r="I40" s="227"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="227"/>
+      <c r="L40" s="227"/>
+      <c r="M40" s="227"/>
+      <c r="N40" s="227"/>
+      <c r="O40" s="227"/>
+      <c r="P40" s="227"/>
+      <c r="Q40" s="227"/>
+      <c r="R40" s="227"/>
+      <c r="S40" s="228"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="215"/>
+      <c r="A41" s="183"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -5150,7 +5139,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="215"/>
+      <c r="A42" s="183"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5175,13 +5164,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="175">
+      <c r="S42" s="193">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="215"/>
+      <c r="A43" s="183"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5193,26 +5182,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="197" t="str">
+      <c r="F43" s="223" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="198"/>
-      <c r="H43" s="198"/>
-      <c r="I43" s="198"/>
-      <c r="J43" s="198"/>
-      <c r="K43" s="198"/>
-      <c r="L43" s="198"/>
-      <c r="M43" s="198"/>
-      <c r="N43" s="198"/>
-      <c r="O43" s="198"/>
-      <c r="P43" s="198"/>
-      <c r="Q43" s="198"/>
-      <c r="R43" s="198"/>
-      <c r="S43" s="176"/>
+      <c r="G43" s="224"/>
+      <c r="H43" s="224"/>
+      <c r="I43" s="224"/>
+      <c r="J43" s="224"/>
+      <c r="K43" s="224"/>
+      <c r="L43" s="224"/>
+      <c r="M43" s="224"/>
+      <c r="N43" s="224"/>
+      <c r="O43" s="224"/>
+      <c r="P43" s="224"/>
+      <c r="Q43" s="224"/>
+      <c r="R43" s="224"/>
+      <c r="S43" s="240"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="215"/>
+      <c r="A44" s="183"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5268,7 +5257,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="215"/>
+      <c r="A45" s="183"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5402,7 +5391,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="215"/>
+      <c r="A46" s="183"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5416,7 +5405,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="215"/>
+      <c r="A47" s="183"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5427,31 +5416,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="175" t="s">
+      <c r="F47" s="193" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="245" t="str">
+      <c r="G47" s="206" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="175" t="s">
+      <c r="J47" s="193" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="234">
+      <c r="K47" s="195">
         <v>1</v>
       </c>
-      <c r="N47" s="175" t="s">
+      <c r="N47" s="193" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="177"/>
-      <c r="P47" s="178"/>
-      <c r="R47" s="175" t="s">
+      <c r="O47" s="241"/>
+      <c r="P47" s="242"/>
+      <c r="R47" s="193" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="175"/>
+      <c r="S47" s="193"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="217"/>
+      <c r="A48" s="184"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5462,15 +5451,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="223"/>
-      <c r="G48" s="246"/>
-      <c r="J48" s="223"/>
-      <c r="K48" s="235"/>
-      <c r="N48" s="176"/>
-      <c r="O48" s="179"/>
-      <c r="P48" s="180"/>
-      <c r="R48" s="176"/>
-      <c r="S48" s="223"/>
+      <c r="F48" s="194"/>
+      <c r="G48" s="207"/>
+      <c r="J48" s="194"/>
+      <c r="K48" s="196"/>
+      <c r="N48" s="240"/>
+      <c r="O48" s="243"/>
+      <c r="P48" s="244"/>
+      <c r="R48" s="240"/>
+      <c r="S48" s="194"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5479,31 +5468,31 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="227" t="s">
+      <c r="A50" s="267" t="s">
         <v>66</v>
       </c>
-      <c r="B50" s="256"/>
-      <c r="C50" s="257"/>
-      <c r="D50" s="257"/>
-      <c r="E50" s="257"/>
-      <c r="F50" s="257"/>
-      <c r="G50" s="257"/>
-      <c r="H50" s="257"/>
-      <c r="I50" s="257"/>
-      <c r="J50" s="257"/>
-      <c r="K50" s="257"/>
-      <c r="L50" s="257"/>
-      <c r="M50" s="257"/>
-      <c r="N50" s="257"/>
-      <c r="O50" s="257"/>
-      <c r="P50" s="257"/>
-      <c r="Q50" s="257"/>
-      <c r="R50" s="257"/>
-      <c r="S50" s="258"/>
+      <c r="B50" s="175"/>
+      <c r="C50" s="176"/>
+      <c r="D50" s="176"/>
+      <c r="E50" s="176"/>
+      <c r="F50" s="176"/>
+      <c r="G50" s="176"/>
+      <c r="H50" s="176"/>
+      <c r="I50" s="176"/>
+      <c r="J50" s="176"/>
+      <c r="K50" s="176"/>
+      <c r="L50" s="176"/>
+      <c r="M50" s="176"/>
+      <c r="N50" s="176"/>
+      <c r="O50" s="176"/>
+      <c r="P50" s="176"/>
+      <c r="Q50" s="176"/>
+      <c r="R50" s="176"/>
+      <c r="S50" s="177"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="215"/>
-      <c r="B51" s="259"/>
+      <c r="A51" s="266"/>
+      <c r="B51" s="178"/>
       <c r="C51" s="260"/>
       <c r="D51" s="260"/>
       <c r="E51" s="260"/>
@@ -5520,11 +5509,11 @@
       <c r="P51" s="260"/>
       <c r="Q51" s="260"/>
       <c r="R51" s="260"/>
-      <c r="S51" s="261"/>
+      <c r="S51" s="179"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="215"/>
-      <c r="B52" s="259"/>
+      <c r="A52" s="266"/>
+      <c r="B52" s="178"/>
       <c r="C52" s="260"/>
       <c r="D52" s="260"/>
       <c r="E52" s="260"/>
@@ -5541,11 +5530,11 @@
       <c r="P52" s="260"/>
       <c r="Q52" s="260"/>
       <c r="R52" s="260"/>
-      <c r="S52" s="261"/>
+      <c r="S52" s="179"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="215"/>
-      <c r="B53" s="259"/>
+      <c r="A53" s="266"/>
+      <c r="B53" s="178"/>
       <c r="C53" s="260"/>
       <c r="D53" s="260"/>
       <c r="E53" s="260"/>
@@ -5562,11 +5551,11 @@
       <c r="P53" s="260"/>
       <c r="Q53" s="260"/>
       <c r="R53" s="260"/>
-      <c r="S53" s="261"/>
+      <c r="S53" s="179"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="215"/>
-      <c r="B54" s="259"/>
+      <c r="A54" s="266"/>
+      <c r="B54" s="178"/>
       <c r="C54" s="260"/>
       <c r="D54" s="260"/>
       <c r="E54" s="260"/>
@@ -5583,11 +5572,11 @@
       <c r="P54" s="260"/>
       <c r="Q54" s="260"/>
       <c r="R54" s="260"/>
-      <c r="S54" s="261"/>
+      <c r="S54" s="179"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="215"/>
-      <c r="B55" s="259"/>
+      <c r="A55" s="266"/>
+      <c r="B55" s="178"/>
       <c r="C55" s="260"/>
       <c r="D55" s="260"/>
       <c r="E55" s="260"/>
@@ -5604,11 +5593,11 @@
       <c r="P55" s="260"/>
       <c r="Q55" s="260"/>
       <c r="R55" s="260"/>
-      <c r="S55" s="261"/>
+      <c r="S55" s="179"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="215"/>
-      <c r="B56" s="259"/>
+      <c r="A56" s="266"/>
+      <c r="B56" s="178"/>
       <c r="C56" s="260"/>
       <c r="D56" s="260"/>
       <c r="E56" s="260"/>
@@ -5625,46 +5614,209 @@
       <c r="P56" s="260"/>
       <c r="Q56" s="260"/>
       <c r="R56" s="260"/>
-      <c r="S56" s="261"/>
-    </row>
-    <row r="57" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A57" s="217"/>
-      <c r="B57" s="262"/>
-      <c r="C57" s="263"/>
-      <c r="D57" s="263"/>
-      <c r="E57" s="263"/>
-      <c r="F57" s="263"/>
-      <c r="G57" s="263"/>
-      <c r="H57" s="263"/>
-      <c r="I57" s="263"/>
-      <c r="J57" s="263"/>
-      <c r="K57" s="263"/>
-      <c r="L57" s="263"/>
-      <c r="M57" s="263"/>
-      <c r="N57" s="263"/>
-      <c r="O57" s="263"/>
-      <c r="P57" s="263"/>
-      <c r="Q57" s="263"/>
-      <c r="R57" s="263"/>
-      <c r="S57" s="264"/>
+      <c r="S56" s="179"/>
+    </row>
+    <row r="57" spans="1:19">
+      <c r="A57" s="266"/>
+      <c r="B57" s="178"/>
+      <c r="C57" s="260"/>
+      <c r="D57" s="260"/>
+      <c r="E57" s="260"/>
+      <c r="F57" s="260"/>
+      <c r="G57" s="260"/>
+      <c r="H57" s="260"/>
+      <c r="I57" s="260"/>
+      <c r="J57" s="260"/>
+      <c r="K57" s="260"/>
+      <c r="L57" s="260"/>
+      <c r="M57" s="260"/>
+      <c r="N57" s="260"/>
+      <c r="O57" s="260"/>
+      <c r="P57" s="260"/>
+      <c r="Q57" s="260"/>
+      <c r="R57" s="260"/>
+      <c r="S57" s="179"/>
+    </row>
+    <row r="58" spans="1:19">
+      <c r="A58" s="266"/>
+      <c r="B58" s="261"/>
+      <c r="C58" s="262"/>
+      <c r="D58" s="262"/>
+      <c r="E58" s="262"/>
+      <c r="F58" s="262"/>
+      <c r="G58" s="262"/>
+      <c r="H58" s="262"/>
+      <c r="I58" s="262"/>
+      <c r="J58" s="262"/>
+      <c r="K58" s="262"/>
+      <c r="L58" s="262"/>
+      <c r="M58" s="262"/>
+      <c r="N58" s="262"/>
+      <c r="O58" s="262"/>
+      <c r="P58" s="262"/>
+      <c r="Q58" s="262"/>
+      <c r="R58" s="262"/>
+      <c r="S58" s="263"/>
+    </row>
+    <row r="59" spans="1:19">
+      <c r="A59" s="266"/>
+      <c r="B59" s="261"/>
+      <c r="C59" s="262"/>
+      <c r="D59" s="262"/>
+      <c r="E59" s="262"/>
+      <c r="F59" s="262"/>
+      <c r="G59" s="262"/>
+      <c r="H59" s="262"/>
+      <c r="I59" s="262"/>
+      <c r="J59" s="262"/>
+      <c r="K59" s="262"/>
+      <c r="L59" s="262"/>
+      <c r="M59" s="262"/>
+      <c r="N59" s="262"/>
+      <c r="O59" s="262"/>
+      <c r="P59" s="262"/>
+      <c r="Q59" s="262"/>
+      <c r="R59" s="262"/>
+      <c r="S59" s="263"/>
+    </row>
+    <row r="60" spans="1:19">
+      <c r="A60" s="266"/>
+      <c r="B60" s="261"/>
+      <c r="C60" s="262"/>
+      <c r="D60" s="262"/>
+      <c r="E60" s="262"/>
+      <c r="F60" s="262"/>
+      <c r="G60" s="262"/>
+      <c r="H60" s="262"/>
+      <c r="I60" s="262"/>
+      <c r="J60" s="262"/>
+      <c r="K60" s="262"/>
+      <c r="L60" s="262"/>
+      <c r="M60" s="262"/>
+      <c r="N60" s="262"/>
+      <c r="O60" s="262"/>
+      <c r="P60" s="262"/>
+      <c r="Q60" s="262"/>
+      <c r="R60" s="262"/>
+      <c r="S60" s="263"/>
+    </row>
+    <row r="61" spans="1:19">
+      <c r="A61" s="266"/>
+      <c r="B61" s="261"/>
+      <c r="C61" s="262"/>
+      <c r="D61" s="262"/>
+      <c r="E61" s="262"/>
+      <c r="F61" s="262"/>
+      <c r="G61" s="262"/>
+      <c r="H61" s="262"/>
+      <c r="I61" s="262"/>
+      <c r="J61" s="262"/>
+      <c r="K61" s="262"/>
+      <c r="L61" s="262"/>
+      <c r="M61" s="262"/>
+      <c r="N61" s="262"/>
+      <c r="O61" s="262"/>
+      <c r="P61" s="262"/>
+      <c r="Q61" s="262"/>
+      <c r="R61" s="262"/>
+      <c r="S61" s="263"/>
+    </row>
+    <row r="62" spans="1:19">
+      <c r="A62" s="266"/>
+      <c r="B62" s="261"/>
+      <c r="C62" s="262"/>
+      <c r="D62" s="262"/>
+      <c r="E62" s="262"/>
+      <c r="F62" s="262"/>
+      <c r="G62" s="262"/>
+      <c r="H62" s="262"/>
+      <c r="I62" s="262"/>
+      <c r="J62" s="262"/>
+      <c r="K62" s="262"/>
+      <c r="L62" s="262"/>
+      <c r="M62" s="262"/>
+      <c r="N62" s="262"/>
+      <c r="O62" s="262"/>
+      <c r="P62" s="262"/>
+      <c r="Q62" s="262"/>
+      <c r="R62" s="262"/>
+      <c r="S62" s="263"/>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="A63" s="266"/>
+      <c r="B63" s="261"/>
+      <c r="C63" s="262"/>
+      <c r="D63" s="262"/>
+      <c r="E63" s="262"/>
+      <c r="F63" s="262"/>
+      <c r="G63" s="262"/>
+      <c r="H63" s="262"/>
+      <c r="I63" s="262"/>
+      <c r="J63" s="262"/>
+      <c r="K63" s="262"/>
+      <c r="L63" s="262"/>
+      <c r="M63" s="262"/>
+      <c r="N63" s="262"/>
+      <c r="O63" s="262"/>
+      <c r="P63" s="262"/>
+      <c r="Q63" s="262"/>
+      <c r="R63" s="262"/>
+      <c r="S63" s="263"/>
+    </row>
+    <row r="64" spans="1:19">
+      <c r="A64" s="266"/>
+      <c r="B64" s="261"/>
+      <c r="C64" s="262"/>
+      <c r="D64" s="262"/>
+      <c r="E64" s="262"/>
+      <c r="F64" s="262"/>
+      <c r="G64" s="262"/>
+      <c r="H64" s="262"/>
+      <c r="I64" s="262"/>
+      <c r="J64" s="262"/>
+      <c r="K64" s="262"/>
+      <c r="L64" s="262"/>
+      <c r="M64" s="262"/>
+      <c r="N64" s="262"/>
+      <c r="O64" s="262"/>
+      <c r="P64" s="262"/>
+      <c r="Q64" s="262"/>
+      <c r="R64" s="262"/>
+      <c r="S64" s="263"/>
+    </row>
+    <row r="65" spans="1:19" ht="15.75" thickBot="1">
+      <c r="A65" s="268"/>
+      <c r="B65" s="264"/>
+      <c r="C65" s="80"/>
+      <c r="D65" s="80"/>
+      <c r="E65" s="80"/>
+      <c r="F65" s="80"/>
+      <c r="G65" s="80"/>
+      <c r="H65" s="80"/>
+      <c r="I65" s="80"/>
+      <c r="J65" s="80"/>
+      <c r="K65" s="80"/>
+      <c r="L65" s="80"/>
+      <c r="M65" s="80"/>
+      <c r="N65" s="80"/>
+      <c r="O65" s="80"/>
+      <c r="P65" s="80"/>
+      <c r="Q65" s="80"/>
+      <c r="R65" s="80"/>
+      <c r="S65" s="265"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A50:A57"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="O6:S6"/>
@@ -5681,20 +5833,25 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="R47:R48"/>
     <mergeCell ref="S47:S48"/>
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="A50:A65"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="64" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="56" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -8876,18 +9033,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customFormat="1">
-      <c r="A1" s="253" t="s">
+      <c r="A1" s="257" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="253"/>
-      <c r="C1" s="253"/>
-      <c r="D1" s="253"/>
-      <c r="E1" s="253"/>
-      <c r="F1" s="253"/>
-      <c r="G1" s="253"/>
-      <c r="H1" s="253"/>
-      <c r="I1" s="253"/>
-      <c r="J1" s="253"/>
+      <c r="B1" s="257"/>
+      <c r="C1" s="257"/>
+      <c r="D1" s="257"/>
+      <c r="E1" s="257"/>
+      <c r="F1" s="257"/>
+      <c r="G1" s="257"/>
+      <c r="H1" s="257"/>
+      <c r="I1" s="257"/>
+      <c r="J1" s="257"/>
       <c r="K1" s="12"/>
       <c r="L1" s="5"/>
     </row>
@@ -8908,15 +9065,15 @@
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="254">
+      <c r="B3" s="258">
         <f>Fisa!B3:D3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="254"/>
-      <c r="D3" s="254"/>
-      <c r="E3" s="254"/>
-      <c r="F3" s="254"/>
-      <c r="G3" s="254"/>
+      <c r="C3" s="258"/>
+      <c r="D3" s="258"/>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="258"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -8927,11 +9084,11 @@
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="255">
+      <c r="B4" s="259">
         <f>Fisa!B6</f>
         <v>0</v>
       </c>
-      <c r="C4" s="255"/>
+      <c r="C4" s="259"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC4E2B6-DBB6-4D55-BDB3-3720058E6DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78693F5C-D60C-4E8E-84E4-1FD0BFB8B5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -1284,7 +1284,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="269">
+  <cellXfs count="268">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1806,6 +1806,196 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1818,12 +2008,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1841,18 +2025,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1862,33 +2034,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1919,142 +2064,13 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2065,23 +2081,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2559,33 +2558,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="229" t="s">
+      <c r="A1" s="220" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="230"/>
-      <c r="C1" s="230"/>
-      <c r="D1" s="230"/>
-      <c r="E1" s="230"/>
-      <c r="F1" s="230"/>
-      <c r="G1" s="230"/>
-      <c r="H1" s="230"/>
-      <c r="I1" s="230"/>
-      <c r="J1" s="230"/>
-      <c r="K1" s="230"/>
-      <c r="L1" s="231"/>
+      <c r="B1" s="221"/>
+      <c r="C1" s="221"/>
+      <c r="D1" s="221"/>
+      <c r="E1" s="221"/>
+      <c r="F1" s="221"/>
+      <c r="G1" s="221"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="221"/>
+      <c r="J1" s="221"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="222"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="214" t="s">
+      <c r="O1" s="209" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="215"/>
-      <c r="Q1" s="215"/>
-      <c r="R1" s="215"/>
-      <c r="S1" s="216"/>
+      <c r="P1" s="210"/>
+      <c r="Q1" s="210"/>
+      <c r="R1" s="210"/>
+      <c r="S1" s="211"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2604,165 +2603,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="217"/>
-      <c r="P2" s="218"/>
-      <c r="Q2" s="218"/>
-      <c r="R2" s="218"/>
-      <c r="S2" s="219"/>
+      <c r="O2" s="212"/>
+      <c r="P2" s="213"/>
+      <c r="Q2" s="213"/>
+      <c r="R2" s="213"/>
+      <c r="S2" s="214"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="237"/>
-      <c r="C3" s="238"/>
-      <c r="D3" s="239"/>
+      <c r="B3" s="230"/>
+      <c r="C3" s="231"/>
+      <c r="D3" s="232"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="180"/>
-      <c r="J3" s="181"/>
-      <c r="K3" s="182"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="244"/>
+      <c r="K3" s="245"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="232"/>
-      <c r="P3" s="233"/>
-      <c r="Q3" s="233"/>
-      <c r="R3" s="233"/>
-      <c r="S3" s="234"/>
+      <c r="O3" s="223"/>
+      <c r="P3" s="205"/>
+      <c r="Q3" s="205"/>
+      <c r="R3" s="205"/>
+      <c r="S3" s="206"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="208"/>
-      <c r="C4" s="209"/>
-      <c r="D4" s="210"/>
+      <c r="B4" s="256"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="258"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="211"/>
-      <c r="J4" s="212"/>
-      <c r="K4" s="213"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="260"/>
+      <c r="K4" s="261"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="232"/>
-      <c r="P4" s="233"/>
-      <c r="Q4" s="233"/>
-      <c r="R4" s="233"/>
-      <c r="S4" s="234"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="205"/>
+      <c r="Q4" s="205"/>
+      <c r="R4" s="205"/>
+      <c r="S4" s="206"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="247"/>
-      <c r="C5" s="248"/>
-      <c r="D5" s="249"/>
+      <c r="B5" s="193"/>
+      <c r="C5" s="194"/>
+      <c r="D5" s="195"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="256"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="234"/>
+      <c r="I5" s="204"/>
+      <c r="J5" s="205"/>
+      <c r="K5" s="206"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="232"/>
-      <c r="P5" s="233"/>
-      <c r="Q5" s="233"/>
-      <c r="R5" s="233"/>
-      <c r="S5" s="234"/>
+      <c r="O5" s="223"/>
+      <c r="P5" s="205"/>
+      <c r="Q5" s="205"/>
+      <c r="R5" s="205"/>
+      <c r="S5" s="206"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="252"/>
-      <c r="C6" s="253"/>
-      <c r="D6" s="254"/>
+      <c r="B6" s="198"/>
+      <c r="C6" s="199"/>
+      <c r="D6" s="200"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="255"/>
-      <c r="J6" s="221"/>
-      <c r="K6" s="222"/>
+      <c r="I6" s="201"/>
+      <c r="J6" s="202"/>
+      <c r="K6" s="203"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="220"/>
-      <c r="P6" s="221"/>
-      <c r="Q6" s="221"/>
-      <c r="R6" s="221"/>
-      <c r="S6" s="222"/>
+      <c r="O6" s="215"/>
+      <c r="P6" s="202"/>
+      <c r="Q6" s="202"/>
+      <c r="R6" s="202"/>
+      <c r="S6" s="203"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="185" t="s">
+      <c r="A8" s="246" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="186"/>
-      <c r="C8" s="186"/>
-      <c r="D8" s="187"/>
-      <c r="F8" s="223" t="s">
+      <c r="B8" s="247"/>
+      <c r="C8" s="247"/>
+      <c r="D8" s="248"/>
+      <c r="F8" s="207" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="224"/>
-      <c r="H8" s="224"/>
-      <c r="I8" s="224"/>
-      <c r="J8" s="224"/>
-      <c r="K8" s="224"/>
-      <c r="L8" s="224"/>
-      <c r="M8" s="224"/>
-      <c r="N8" s="224"/>
-      <c r="O8" s="224"/>
-      <c r="P8" s="224"/>
-      <c r="Q8" s="224"/>
-      <c r="R8" s="224"/>
-      <c r="S8" s="225"/>
+      <c r="G8" s="208"/>
+      <c r="H8" s="208"/>
+      <c r="I8" s="208"/>
+      <c r="J8" s="208"/>
+      <c r="K8" s="208"/>
+      <c r="L8" s="208"/>
+      <c r="M8" s="208"/>
+      <c r="N8" s="208"/>
+      <c r="O8" s="208"/>
+      <c r="P8" s="208"/>
+      <c r="Q8" s="208"/>
+      <c r="R8" s="208"/>
+      <c r="S8" s="216"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="188"/>
-      <c r="B9" s="189"/>
-      <c r="C9" s="189"/>
-      <c r="D9" s="190"/>
-      <c r="F9" s="204" t="s">
+      <c r="A9" s="249"/>
+      <c r="B9" s="250"/>
+      <c r="C9" s="250"/>
+      <c r="D9" s="251"/>
+      <c r="F9" s="241" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="205"/>
-      <c r="H9" s="250" t="s">
+      <c r="G9" s="242"/>
+      <c r="H9" s="196" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="251"/>
-      <c r="J9" s="202" t="s">
+      <c r="I9" s="197"/>
+      <c r="J9" s="239" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="203"/>
-      <c r="L9" s="245" t="s">
+      <c r="K9" s="240"/>
+      <c r="L9" s="191" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="246"/>
-      <c r="N9" s="191" t="s">
+      <c r="M9" s="192"/>
+      <c r="N9" s="228" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="192"/>
-      <c r="P9" s="197" t="s">
+      <c r="O9" s="229"/>
+      <c r="P9" s="234" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="198"/>
-      <c r="R9" s="191" t="s">
+      <c r="Q9" s="235"/>
+      <c r="R9" s="228" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="192"/>
+      <c r="S9" s="229"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="235" t="s">
+      <c r="A10" s="224" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2819,7 +2818,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="183"/>
+      <c r="A11" s="225"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2925,7 +2924,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="183"/>
+      <c r="A12" s="225"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3031,7 +3030,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="183"/>
+      <c r="A13" s="225"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3137,7 +3136,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="183"/>
+      <c r="A14" s="225"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3224,7 +3223,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="183"/>
+      <c r="A15" s="225"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3311,7 +3310,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="183"/>
+      <c r="A16" s="225"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3398,7 +3397,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="183"/>
+      <c r="A17" s="225"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3485,7 +3484,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="183"/>
+      <c r="A18" s="225"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3572,7 +3571,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="183"/>
+      <c r="A19" s="225"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3659,7 +3658,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="183"/>
+      <c r="A20" s="225"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3746,7 +3745,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="183"/>
+      <c r="A21" s="225"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3833,7 +3832,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="236"/>
+      <c r="A22" s="226"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3976,7 +3975,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="235" t="s">
+      <c r="A24" s="224" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -4084,7 +4083,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="183"/>
+      <c r="A25" s="225"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4190,7 +4189,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="183"/>
+      <c r="A26" s="225"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4296,7 +4295,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="183"/>
+      <c r="A27" s="225"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4383,7 +4382,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="184"/>
+      <c r="A28" s="227"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4545,7 +4544,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="199" t="s">
+      <c r="A32" s="236" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4624,7 +4623,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="200"/>
+      <c r="A33" s="237"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4701,7 +4700,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="201"/>
+      <c r="A34" s="238"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4799,7 +4798,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="199" t="s">
+      <c r="A36" s="236" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4878,7 +4877,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="200"/>
+      <c r="A37" s="237"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4955,7 +4954,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="201"/>
+      <c r="A38" s="238"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5046,7 +5045,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="235" t="s">
+      <c r="A40" s="224" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5058,25 +5057,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="226" t="s">
+      <c r="F40" s="217" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="227"/>
-      <c r="H40" s="227"/>
-      <c r="I40" s="227"/>
-      <c r="J40" s="227"/>
-      <c r="K40" s="227"/>
-      <c r="L40" s="227"/>
-      <c r="M40" s="227"/>
-      <c r="N40" s="227"/>
-      <c r="O40" s="227"/>
-      <c r="P40" s="227"/>
-      <c r="Q40" s="227"/>
-      <c r="R40" s="227"/>
-      <c r="S40" s="228"/>
+      <c r="G40" s="218"/>
+      <c r="H40" s="218"/>
+      <c r="I40" s="218"/>
+      <c r="J40" s="218"/>
+      <c r="K40" s="218"/>
+      <c r="L40" s="218"/>
+      <c r="M40" s="218"/>
+      <c r="N40" s="218"/>
+      <c r="O40" s="218"/>
+      <c r="P40" s="218"/>
+      <c r="Q40" s="218"/>
+      <c r="R40" s="218"/>
+      <c r="S40" s="219"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="183"/>
+      <c r="A41" s="225"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -5139,7 +5138,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="183"/>
+      <c r="A42" s="225"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5164,13 +5163,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="193">
+      <c r="S42" s="185">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="183"/>
+      <c r="A43" s="225"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5182,31 +5181,31 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="223" t="str">
+      <c r="F43" s="207" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="224"/>
-      <c r="H43" s="224"/>
-      <c r="I43" s="224"/>
-      <c r="J43" s="224"/>
-      <c r="K43" s="224"/>
-      <c r="L43" s="224"/>
-      <c r="M43" s="224"/>
-      <c r="N43" s="224"/>
-      <c r="O43" s="224"/>
-      <c r="P43" s="224"/>
-      <c r="Q43" s="224"/>
-      <c r="R43" s="224"/>
-      <c r="S43" s="240"/>
+      <c r="G43" s="208"/>
+      <c r="H43" s="208"/>
+      <c r="I43" s="208"/>
+      <c r="J43" s="208"/>
+      <c r="K43" s="208"/>
+      <c r="L43" s="208"/>
+      <c r="M43" s="208"/>
+      <c r="N43" s="208"/>
+      <c r="O43" s="208"/>
+      <c r="P43" s="208"/>
+      <c r="Q43" s="208"/>
+      <c r="R43" s="208"/>
+      <c r="S43" s="186"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="183"/>
+      <c r="A44" s="225"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
       <c r="C44" s="30" t="str">
-        <f>IF(SUMIF(B32:B34, "*/920", C32:C34)=0, "",SUMIF(B32:B34, "*/920", C32:C34)=0)</f>
+        <f>IF(SUMIF(B32:B34, "*/920", C32:C34)=0, "",SUMIF(B32:B34, "*/920", C32:C34))</f>
         <v/>
       </c>
       <c r="D44" s="74" t="s">
@@ -5257,7 +5256,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="183"/>
+      <c r="A45" s="225"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5391,7 +5390,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="183"/>
+      <c r="A46" s="225"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5405,7 +5404,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="183"/>
+      <c r="A47" s="225"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5416,31 +5415,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="193" t="s">
+      <c r="F47" s="185" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="206" t="str">
+      <c r="G47" s="254" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="193" t="s">
+      <c r="J47" s="185" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="195">
+      <c r="K47" s="252">
         <v>1</v>
       </c>
-      <c r="N47" s="193" t="s">
+      <c r="N47" s="185" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="241"/>
-      <c r="P47" s="242"/>
-      <c r="R47" s="193" t="s">
+      <c r="O47" s="187"/>
+      <c r="P47" s="188"/>
+      <c r="R47" s="185" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="193"/>
+      <c r="S47" s="185"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="184"/>
+      <c r="A48" s="227"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5451,15 +5450,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="194"/>
-      <c r="G48" s="207"/>
-      <c r="J48" s="194"/>
-      <c r="K48" s="196"/>
-      <c r="N48" s="240"/>
-      <c r="O48" s="243"/>
-      <c r="P48" s="244"/>
-      <c r="R48" s="240"/>
-      <c r="S48" s="194"/>
+      <c r="F48" s="233"/>
+      <c r="G48" s="255"/>
+      <c r="J48" s="233"/>
+      <c r="K48" s="253"/>
+      <c r="N48" s="186"/>
+      <c r="O48" s="189"/>
+      <c r="P48" s="190"/>
+      <c r="R48" s="186"/>
+      <c r="S48" s="233"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5468,7 +5467,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="267" t="s">
+      <c r="A50" s="262" t="s">
         <v>66</v>
       </c>
       <c r="B50" s="175"/>
@@ -5491,302 +5490,190 @@
       <c r="S50" s="177"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="266"/>
+      <c r="A51" s="263"/>
       <c r="B51" s="178"/>
-      <c r="C51" s="260"/>
-      <c r="D51" s="260"/>
-      <c r="E51" s="260"/>
-      <c r="F51" s="260"/>
-      <c r="G51" s="260"/>
-      <c r="H51" s="260"/>
-      <c r="I51" s="260"/>
-      <c r="J51" s="260"/>
-      <c r="K51" s="260"/>
-      <c r="L51" s="260"/>
-      <c r="M51" s="260"/>
-      <c r="N51" s="260"/>
-      <c r="O51" s="260"/>
-      <c r="P51" s="260"/>
-      <c r="Q51" s="260"/>
-      <c r="R51" s="260"/>
+      <c r="C51" s="180"/>
+      <c r="D51" s="180"/>
+      <c r="E51" s="180"/>
+      <c r="F51" s="180"/>
+      <c r="G51" s="180"/>
+      <c r="H51" s="180"/>
+      <c r="I51" s="180"/>
+      <c r="J51" s="180"/>
+      <c r="K51" s="180"/>
+      <c r="L51" s="180"/>
+      <c r="M51" s="180"/>
+      <c r="N51" s="180"/>
+      <c r="O51" s="180"/>
+      <c r="P51" s="180"/>
+      <c r="Q51" s="180"/>
+      <c r="R51" s="180"/>
       <c r="S51" s="179"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="266"/>
+      <c r="A52" s="263"/>
       <c r="B52" s="178"/>
-      <c r="C52" s="260"/>
-      <c r="D52" s="260"/>
-      <c r="E52" s="260"/>
-      <c r="F52" s="260"/>
-      <c r="G52" s="260"/>
-      <c r="H52" s="260"/>
-      <c r="I52" s="260"/>
-      <c r="J52" s="260"/>
-      <c r="K52" s="260"/>
-      <c r="L52" s="260"/>
-      <c r="M52" s="260"/>
-      <c r="N52" s="260"/>
-      <c r="O52" s="260"/>
-      <c r="P52" s="260"/>
-      <c r="Q52" s="260"/>
-      <c r="R52" s="260"/>
+      <c r="C52" s="180"/>
+      <c r="D52" s="180"/>
+      <c r="E52" s="180"/>
+      <c r="F52" s="180"/>
+      <c r="G52" s="180"/>
+      <c r="H52" s="180"/>
+      <c r="I52" s="180"/>
+      <c r="J52" s="180"/>
+      <c r="K52" s="180"/>
+      <c r="L52" s="180"/>
+      <c r="M52" s="180"/>
+      <c r="N52" s="180"/>
+      <c r="O52" s="180"/>
+      <c r="P52" s="180"/>
+      <c r="Q52" s="180"/>
+      <c r="R52" s="180"/>
       <c r="S52" s="179"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="266"/>
+      <c r="A53" s="263"/>
       <c r="B53" s="178"/>
-      <c r="C53" s="260"/>
-      <c r="D53" s="260"/>
-      <c r="E53" s="260"/>
-      <c r="F53" s="260"/>
-      <c r="G53" s="260"/>
-      <c r="H53" s="260"/>
-      <c r="I53" s="260"/>
-      <c r="J53" s="260"/>
-      <c r="K53" s="260"/>
-      <c r="L53" s="260"/>
-      <c r="M53" s="260"/>
-      <c r="N53" s="260"/>
-      <c r="O53" s="260"/>
-      <c r="P53" s="260"/>
-      <c r="Q53" s="260"/>
-      <c r="R53" s="260"/>
+      <c r="C53" s="180"/>
+      <c r="D53" s="180"/>
+      <c r="E53" s="180"/>
+      <c r="F53" s="180"/>
+      <c r="G53" s="180"/>
+      <c r="H53" s="180"/>
+      <c r="I53" s="180"/>
+      <c r="J53" s="180"/>
+      <c r="K53" s="180"/>
+      <c r="L53" s="180"/>
+      <c r="M53" s="180"/>
+      <c r="N53" s="180"/>
+      <c r="O53" s="180"/>
+      <c r="P53" s="180"/>
+      <c r="Q53" s="180"/>
+      <c r="R53" s="180"/>
       <c r="S53" s="179"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="266"/>
+      <c r="A54" s="263"/>
       <c r="B54" s="178"/>
-      <c r="C54" s="260"/>
-      <c r="D54" s="260"/>
-      <c r="E54" s="260"/>
-      <c r="F54" s="260"/>
-      <c r="G54" s="260"/>
-      <c r="H54" s="260"/>
-      <c r="I54" s="260"/>
-      <c r="J54" s="260"/>
-      <c r="K54" s="260"/>
-      <c r="L54" s="260"/>
-      <c r="M54" s="260"/>
-      <c r="N54" s="260"/>
-      <c r="O54" s="260"/>
-      <c r="P54" s="260"/>
-      <c r="Q54" s="260"/>
-      <c r="R54" s="260"/>
+      <c r="C54" s="180"/>
+      <c r="D54" s="180"/>
+      <c r="E54" s="180"/>
+      <c r="F54" s="180"/>
+      <c r="G54" s="180"/>
+      <c r="H54" s="180"/>
+      <c r="I54" s="180"/>
+      <c r="J54" s="180"/>
+      <c r="K54" s="180"/>
+      <c r="L54" s="180"/>
+      <c r="M54" s="180"/>
+      <c r="N54" s="180"/>
+      <c r="O54" s="180"/>
+      <c r="P54" s="180"/>
+      <c r="Q54" s="180"/>
+      <c r="R54" s="180"/>
       <c r="S54" s="179"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="266"/>
+      <c r="A55" s="263"/>
       <c r="B55" s="178"/>
-      <c r="C55" s="260"/>
-      <c r="D55" s="260"/>
-      <c r="E55" s="260"/>
-      <c r="F55" s="260"/>
-      <c r="G55" s="260"/>
-      <c r="H55" s="260"/>
-      <c r="I55" s="260"/>
-      <c r="J55" s="260"/>
-      <c r="K55" s="260"/>
-      <c r="L55" s="260"/>
-      <c r="M55" s="260"/>
-      <c r="N55" s="260"/>
-      <c r="O55" s="260"/>
-      <c r="P55" s="260"/>
-      <c r="Q55" s="260"/>
-      <c r="R55" s="260"/>
+      <c r="C55" s="180"/>
+      <c r="D55" s="180"/>
+      <c r="E55" s="180"/>
+      <c r="F55" s="180"/>
+      <c r="G55" s="180"/>
+      <c r="H55" s="180"/>
+      <c r="I55" s="180"/>
+      <c r="J55" s="180"/>
+      <c r="K55" s="180"/>
+      <c r="L55" s="180"/>
+      <c r="M55" s="180"/>
+      <c r="N55" s="180"/>
+      <c r="O55" s="180"/>
+      <c r="P55" s="180"/>
+      <c r="Q55" s="180"/>
+      <c r="R55" s="180"/>
       <c r="S55" s="179"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="266"/>
+      <c r="A56" s="263"/>
       <c r="B56" s="178"/>
-      <c r="C56" s="260"/>
-      <c r="D56" s="260"/>
-      <c r="E56" s="260"/>
-      <c r="F56" s="260"/>
-      <c r="G56" s="260"/>
-      <c r="H56" s="260"/>
-      <c r="I56" s="260"/>
-      <c r="J56" s="260"/>
-      <c r="K56" s="260"/>
-      <c r="L56" s="260"/>
-      <c r="M56" s="260"/>
-      <c r="N56" s="260"/>
-      <c r="O56" s="260"/>
-      <c r="P56" s="260"/>
-      <c r="Q56" s="260"/>
-      <c r="R56" s="260"/>
+      <c r="C56" s="180"/>
+      <c r="D56" s="180"/>
+      <c r="E56" s="180"/>
+      <c r="F56" s="180"/>
+      <c r="G56" s="180"/>
+      <c r="H56" s="180"/>
+      <c r="I56" s="180"/>
+      <c r="J56" s="180"/>
+      <c r="K56" s="180"/>
+      <c r="L56" s="180"/>
+      <c r="M56" s="180"/>
+      <c r="N56" s="180"/>
+      <c r="O56" s="180"/>
+      <c r="P56" s="180"/>
+      <c r="Q56" s="180"/>
+      <c r="R56" s="180"/>
       <c r="S56" s="179"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="266"/>
+      <c r="A57" s="263"/>
       <c r="B57" s="178"/>
-      <c r="C57" s="260"/>
-      <c r="D57" s="260"/>
-      <c r="E57" s="260"/>
-      <c r="F57" s="260"/>
-      <c r="G57" s="260"/>
-      <c r="H57" s="260"/>
-      <c r="I57" s="260"/>
-      <c r="J57" s="260"/>
-      <c r="K57" s="260"/>
-      <c r="L57" s="260"/>
-      <c r="M57" s="260"/>
-      <c r="N57" s="260"/>
-      <c r="O57" s="260"/>
-      <c r="P57" s="260"/>
-      <c r="Q57" s="260"/>
-      <c r="R57" s="260"/>
+      <c r="C57" s="180"/>
+      <c r="D57" s="180"/>
+      <c r="E57" s="180"/>
+      <c r="F57" s="180"/>
+      <c r="G57" s="180"/>
+      <c r="H57" s="180"/>
+      <c r="I57" s="180"/>
+      <c r="J57" s="180"/>
+      <c r="K57" s="180"/>
+      <c r="L57" s="180"/>
+      <c r="M57" s="180"/>
+      <c r="N57" s="180"/>
+      <c r="O57" s="180"/>
+      <c r="P57" s="180"/>
+      <c r="Q57" s="180"/>
+      <c r="R57" s="180"/>
       <c r="S57" s="179"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="266"/>
-      <c r="B58" s="261"/>
-      <c r="C58" s="262"/>
-      <c r="D58" s="262"/>
-      <c r="E58" s="262"/>
-      <c r="F58" s="262"/>
-      <c r="G58" s="262"/>
-      <c r="H58" s="262"/>
-      <c r="I58" s="262"/>
-      <c r="J58" s="262"/>
-      <c r="K58" s="262"/>
-      <c r="L58" s="262"/>
-      <c r="M58" s="262"/>
-      <c r="N58" s="262"/>
-      <c r="O58" s="262"/>
-      <c r="P58" s="262"/>
-      <c r="Q58" s="262"/>
-      <c r="R58" s="262"/>
-      <c r="S58" s="263"/>
+      <c r="A58" s="263"/>
+      <c r="B58" s="181"/>
+      <c r="S58" s="182"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="266"/>
-      <c r="B59" s="261"/>
-      <c r="C59" s="262"/>
-      <c r="D59" s="262"/>
-      <c r="E59" s="262"/>
-      <c r="F59" s="262"/>
-      <c r="G59" s="262"/>
-      <c r="H59" s="262"/>
-      <c r="I59" s="262"/>
-      <c r="J59" s="262"/>
-      <c r="K59" s="262"/>
-      <c r="L59" s="262"/>
-      <c r="M59" s="262"/>
-      <c r="N59" s="262"/>
-      <c r="O59" s="262"/>
-      <c r="P59" s="262"/>
-      <c r="Q59" s="262"/>
-      <c r="R59" s="262"/>
-      <c r="S59" s="263"/>
+      <c r="A59" s="263"/>
+      <c r="B59" s="181"/>
+      <c r="S59" s="182"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="266"/>
-      <c r="B60" s="261"/>
-      <c r="C60" s="262"/>
-      <c r="D60" s="262"/>
-      <c r="E60" s="262"/>
-      <c r="F60" s="262"/>
-      <c r="G60" s="262"/>
-      <c r="H60" s="262"/>
-      <c r="I60" s="262"/>
-      <c r="J60" s="262"/>
-      <c r="K60" s="262"/>
-      <c r="L60" s="262"/>
-      <c r="M60" s="262"/>
-      <c r="N60" s="262"/>
-      <c r="O60" s="262"/>
-      <c r="P60" s="262"/>
-      <c r="Q60" s="262"/>
-      <c r="R60" s="262"/>
-      <c r="S60" s="263"/>
+      <c r="A60" s="263"/>
+      <c r="B60" s="181"/>
+      <c r="S60" s="182"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="266"/>
-      <c r="B61" s="261"/>
-      <c r="C61" s="262"/>
-      <c r="D61" s="262"/>
-      <c r="E61" s="262"/>
-      <c r="F61" s="262"/>
-      <c r="G61" s="262"/>
-      <c r="H61" s="262"/>
-      <c r="I61" s="262"/>
-      <c r="J61" s="262"/>
-      <c r="K61" s="262"/>
-      <c r="L61" s="262"/>
-      <c r="M61" s="262"/>
-      <c r="N61" s="262"/>
-      <c r="O61" s="262"/>
-      <c r="P61" s="262"/>
-      <c r="Q61" s="262"/>
-      <c r="R61" s="262"/>
-      <c r="S61" s="263"/>
+      <c r="A61" s="263"/>
+      <c r="B61" s="181"/>
+      <c r="S61" s="182"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="266"/>
-      <c r="B62" s="261"/>
-      <c r="C62" s="262"/>
-      <c r="D62" s="262"/>
-      <c r="E62" s="262"/>
-      <c r="F62" s="262"/>
-      <c r="G62" s="262"/>
-      <c r="H62" s="262"/>
-      <c r="I62" s="262"/>
-      <c r="J62" s="262"/>
-      <c r="K62" s="262"/>
-      <c r="L62" s="262"/>
-      <c r="M62" s="262"/>
-      <c r="N62" s="262"/>
-      <c r="O62" s="262"/>
-      <c r="P62" s="262"/>
-      <c r="Q62" s="262"/>
-      <c r="R62" s="262"/>
-      <c r="S62" s="263"/>
+      <c r="A62" s="263"/>
+      <c r="B62" s="181"/>
+      <c r="S62" s="182"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="266"/>
-      <c r="B63" s="261"/>
-      <c r="C63" s="262"/>
-      <c r="D63" s="262"/>
-      <c r="E63" s="262"/>
-      <c r="F63" s="262"/>
-      <c r="G63" s="262"/>
-      <c r="H63" s="262"/>
-      <c r="I63" s="262"/>
-      <c r="J63" s="262"/>
-      <c r="K63" s="262"/>
-      <c r="L63" s="262"/>
-      <c r="M63" s="262"/>
-      <c r="N63" s="262"/>
-      <c r="O63" s="262"/>
-      <c r="P63" s="262"/>
-      <c r="Q63" s="262"/>
-      <c r="R63" s="262"/>
-      <c r="S63" s="263"/>
+      <c r="A63" s="263"/>
+      <c r="B63" s="181"/>
+      <c r="S63" s="182"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="266"/>
-      <c r="B64" s="261"/>
-      <c r="C64" s="262"/>
-      <c r="D64" s="262"/>
-      <c r="E64" s="262"/>
-      <c r="F64" s="262"/>
-      <c r="G64" s="262"/>
-      <c r="H64" s="262"/>
-      <c r="I64" s="262"/>
-      <c r="J64" s="262"/>
-      <c r="K64" s="262"/>
-      <c r="L64" s="262"/>
-      <c r="M64" s="262"/>
-      <c r="N64" s="262"/>
-      <c r="O64" s="262"/>
-      <c r="P64" s="262"/>
-      <c r="Q64" s="262"/>
-      <c r="R64" s="262"/>
-      <c r="S64" s="263"/>
+      <c r="A64" s="263"/>
+      <c r="B64" s="181"/>
+      <c r="S64" s="182"/>
     </row>
     <row r="65" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A65" s="268"/>
-      <c r="B65" s="264"/>
+      <c r="A65" s="264"/>
+      <c r="B65" s="183"/>
       <c r="C65" s="80"/>
       <c r="D65" s="80"/>
       <c r="E65" s="80"/>
@@ -5803,20 +5690,19 @@
       <c r="P65" s="80"/>
       <c r="Q65" s="80"/>
       <c r="R65" s="80"/>
-      <c r="S65" s="265"/>
+      <c r="S65" s="184"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="S42:S43"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="A50:A65"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="O6:S6"/>
@@ -5833,21 +5719,22 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="R47:R48"/>
     <mergeCell ref="S47:S48"/>
+    <mergeCell ref="S42:S43"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:P48"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="F43:R43"/>
     <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A8:D9"/>
     <mergeCell ref="N9:O9"/>
     <mergeCell ref="F47:F48"/>
     <mergeCell ref="J47:J48"/>
     <mergeCell ref="K47:K48"/>
     <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="A50:A65"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9033,18 +8920,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customFormat="1">
-      <c r="A1" s="257" t="s">
+      <c r="A1" s="265" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="257"/>
-      <c r="C1" s="257"/>
-      <c r="D1" s="257"/>
-      <c r="E1" s="257"/>
-      <c r="F1" s="257"/>
-      <c r="G1" s="257"/>
-      <c r="H1" s="257"/>
-      <c r="I1" s="257"/>
-      <c r="J1" s="257"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
+      <c r="J1" s="265"/>
       <c r="K1" s="12"/>
       <c r="L1" s="5"/>
     </row>
@@ -9065,15 +8952,15 @@
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="258">
+      <c r="B3" s="266">
         <f>Fisa!B3:D3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="258"/>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="258"/>
+      <c r="C3" s="266"/>
+      <c r="D3" s="266"/>
+      <c r="E3" s="266"/>
+      <c r="F3" s="266"/>
+      <c r="G3" s="266"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -9084,11 +8971,11 @@
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="259">
+      <c r="B4" s="267">
         <f>Fisa!B6</f>
         <v>0</v>
       </c>
-      <c r="C4" s="259"/>
+      <c r="C4" s="267"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78693F5C-D60C-4E8E-84E4-1FD0BFB8B5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFBC939-F878-4B35-9092-FCF4C2E8C88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -1813,12 +1813,66 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1831,11 +1885,92 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1849,11 +1984,61 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1870,144 +2055,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2025,53 +2072,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2533,7 +2533,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -2558,33 +2558,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="220" t="s">
+      <c r="A1" s="226" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="221"/>
-      <c r="C1" s="221"/>
-      <c r="D1" s="221"/>
-      <c r="E1" s="221"/>
-      <c r="F1" s="221"/>
-      <c r="G1" s="221"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="221"/>
-      <c r="J1" s="221"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="222"/>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
+      <c r="I1" s="227"/>
+      <c r="J1" s="227"/>
+      <c r="K1" s="227"/>
+      <c r="L1" s="228"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="209" t="s">
+      <c r="O1" s="217" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="210"/>
-      <c r="Q1" s="210"/>
-      <c r="R1" s="210"/>
-      <c r="S1" s="211"/>
+      <c r="P1" s="218"/>
+      <c r="Q1" s="218"/>
+      <c r="R1" s="218"/>
+      <c r="S1" s="219"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2603,165 +2603,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="212"/>
-      <c r="P2" s="213"/>
-      <c r="Q2" s="213"/>
-      <c r="R2" s="213"/>
-      <c r="S2" s="214"/>
+      <c r="O2" s="220"/>
+      <c r="P2" s="221"/>
+      <c r="Q2" s="221"/>
+      <c r="R2" s="221"/>
+      <c r="S2" s="222"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="230"/>
-      <c r="C3" s="231"/>
-      <c r="D3" s="232"/>
+      <c r="B3" s="232"/>
+      <c r="C3" s="233"/>
+      <c r="D3" s="234"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="243"/>
-      <c r="J3" s="244"/>
-      <c r="K3" s="245"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="247"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="223"/>
-      <c r="P3" s="205"/>
-      <c r="Q3" s="205"/>
-      <c r="R3" s="205"/>
-      <c r="S3" s="206"/>
+      <c r="O3" s="229"/>
+      <c r="P3" s="230"/>
+      <c r="Q3" s="230"/>
+      <c r="R3" s="230"/>
+      <c r="S3" s="231"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="256"/>
-      <c r="C4" s="257"/>
-      <c r="D4" s="258"/>
+      <c r="B4" s="211"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="213"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="259"/>
-      <c r="J4" s="260"/>
-      <c r="K4" s="261"/>
+      <c r="I4" s="214"/>
+      <c r="J4" s="215"/>
+      <c r="K4" s="216"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="205"/>
-      <c r="Q4" s="205"/>
-      <c r="R4" s="205"/>
-      <c r="S4" s="206"/>
+      <c r="O4" s="229"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="231"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="193"/>
-      <c r="C5" s="194"/>
-      <c r="D5" s="195"/>
+      <c r="B5" s="235"/>
+      <c r="C5" s="236"/>
+      <c r="D5" s="237"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="204"/>
-      <c r="J5" s="205"/>
-      <c r="K5" s="206"/>
+      <c r="I5" s="238"/>
+      <c r="J5" s="230"/>
+      <c r="K5" s="231"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="223"/>
-      <c r="P5" s="205"/>
-      <c r="Q5" s="205"/>
-      <c r="R5" s="205"/>
-      <c r="S5" s="206"/>
+      <c r="O5" s="229"/>
+      <c r="P5" s="230"/>
+      <c r="Q5" s="230"/>
+      <c r="R5" s="230"/>
+      <c r="S5" s="231"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="198"/>
-      <c r="C6" s="199"/>
-      <c r="D6" s="200"/>
+      <c r="B6" s="255"/>
+      <c r="C6" s="256"/>
+      <c r="D6" s="257"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="201"/>
-      <c r="J6" s="202"/>
-      <c r="K6" s="203"/>
+      <c r="I6" s="258"/>
+      <c r="J6" s="224"/>
+      <c r="K6" s="225"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="215"/>
-      <c r="P6" s="202"/>
-      <c r="Q6" s="202"/>
-      <c r="R6" s="202"/>
-      <c r="S6" s="203"/>
+      <c r="O6" s="223"/>
+      <c r="P6" s="224"/>
+      <c r="Q6" s="224"/>
+      <c r="R6" s="224"/>
+      <c r="S6" s="225"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="246" t="s">
+      <c r="A8" s="259" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="247"/>
-      <c r="C8" s="247"/>
-      <c r="D8" s="248"/>
-      <c r="F8" s="207" t="s">
+      <c r="B8" s="260"/>
+      <c r="C8" s="260"/>
+      <c r="D8" s="261"/>
+      <c r="F8" s="239" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="208"/>
-      <c r="H8" s="208"/>
-      <c r="I8" s="208"/>
-      <c r="J8" s="208"/>
-      <c r="K8" s="208"/>
-      <c r="L8" s="208"/>
-      <c r="M8" s="208"/>
-      <c r="N8" s="208"/>
-      <c r="O8" s="208"/>
-      <c r="P8" s="208"/>
-      <c r="Q8" s="208"/>
-      <c r="R8" s="208"/>
-      <c r="S8" s="216"/>
+      <c r="G8" s="240"/>
+      <c r="H8" s="240"/>
+      <c r="I8" s="240"/>
+      <c r="J8" s="240"/>
+      <c r="K8" s="240"/>
+      <c r="L8" s="240"/>
+      <c r="M8" s="240"/>
+      <c r="N8" s="240"/>
+      <c r="O8" s="240"/>
+      <c r="P8" s="240"/>
+      <c r="Q8" s="240"/>
+      <c r="R8" s="240"/>
+      <c r="S8" s="248"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="249"/>
-      <c r="B9" s="250"/>
-      <c r="C9" s="250"/>
-      <c r="D9" s="251"/>
-      <c r="F9" s="241" t="s">
+      <c r="A9" s="262"/>
+      <c r="B9" s="263"/>
+      <c r="C9" s="263"/>
+      <c r="D9" s="264"/>
+      <c r="F9" s="193" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="242"/>
-      <c r="H9" s="196" t="s">
+      <c r="G9" s="194"/>
+      <c r="H9" s="209" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="197"/>
-      <c r="J9" s="239" t="s">
+      <c r="I9" s="210"/>
+      <c r="J9" s="191" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="240"/>
-      <c r="L9" s="191" t="s">
+      <c r="K9" s="192"/>
+      <c r="L9" s="249" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="192"/>
-      <c r="N9" s="228" t="s">
+      <c r="M9" s="250"/>
+      <c r="N9" s="243" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="229"/>
-      <c r="P9" s="234" t="s">
+      <c r="O9" s="244"/>
+      <c r="P9" s="241" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="235"/>
-      <c r="R9" s="228" t="s">
+      <c r="Q9" s="242"/>
+      <c r="R9" s="243" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="229"/>
+      <c r="S9" s="244"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="224" t="s">
+      <c r="A10" s="198" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2818,7 +2818,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="225"/>
+      <c r="A11" s="199"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2924,7 +2924,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="225"/>
+      <c r="A12" s="199"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3030,7 +3030,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="225"/>
+      <c r="A13" s="199"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3136,7 +3136,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="225"/>
+      <c r="A14" s="199"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3223,7 +3223,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="225"/>
+      <c r="A15" s="199"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3310,7 +3310,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="225"/>
+      <c r="A16" s="199"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3397,7 +3397,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="225"/>
+      <c r="A17" s="199"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3484,7 +3484,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="225"/>
+      <c r="A18" s="199"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3571,7 +3571,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="225"/>
+      <c r="A19" s="199"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3658,7 +3658,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="225"/>
+      <c r="A20" s="199"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="225"/>
+      <c r="A21" s="199"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3832,7 +3832,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="226"/>
+      <c r="A22" s="200"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3975,7 +3975,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="224" t="s">
+      <c r="A24" s="198" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -4083,7 +4083,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="225"/>
+      <c r="A25" s="199"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4189,7 +4189,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="225"/>
+      <c r="A26" s="199"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4295,7 +4295,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="225"/>
+      <c r="A27" s="199"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4382,7 +4382,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="227"/>
+      <c r="A28" s="201"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4544,7 +4544,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="236" t="s">
+      <c r="A32" s="188" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4623,7 +4623,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="237"/>
+      <c r="A33" s="189"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4700,7 +4700,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="238"/>
+      <c r="A34" s="190"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4798,7 +4798,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="236" t="s">
+      <c r="A36" s="188" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4877,7 +4877,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="237"/>
+      <c r="A37" s="189"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4954,7 +4954,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="238"/>
+      <c r="A38" s="190"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5045,7 +5045,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="224" t="s">
+      <c r="A40" s="198" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5057,25 +5057,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="217" t="s">
+      <c r="F40" s="195" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="218"/>
-      <c r="H40" s="218"/>
-      <c r="I40" s="218"/>
-      <c r="J40" s="218"/>
-      <c r="K40" s="218"/>
-      <c r="L40" s="218"/>
-      <c r="M40" s="218"/>
-      <c r="N40" s="218"/>
-      <c r="O40" s="218"/>
-      <c r="P40" s="218"/>
-      <c r="Q40" s="218"/>
-      <c r="R40" s="218"/>
-      <c r="S40" s="219"/>
+      <c r="G40" s="196"/>
+      <c r="H40" s="196"/>
+      <c r="I40" s="196"/>
+      <c r="J40" s="196"/>
+      <c r="K40" s="196"/>
+      <c r="L40" s="196"/>
+      <c r="M40" s="196"/>
+      <c r="N40" s="196"/>
+      <c r="O40" s="196"/>
+      <c r="P40" s="196"/>
+      <c r="Q40" s="196"/>
+      <c r="R40" s="196"/>
+      <c r="S40" s="197"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="225"/>
+      <c r="A41" s="199"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -5138,7 +5138,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="225"/>
+      <c r="A42" s="199"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5163,13 +5163,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="185">
+      <c r="S42" s="202">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="225"/>
+      <c r="A43" s="199"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5181,26 +5181,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="207" t="str">
+      <c r="F43" s="239" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="208"/>
-      <c r="H43" s="208"/>
-      <c r="I43" s="208"/>
-      <c r="J43" s="208"/>
-      <c r="K43" s="208"/>
-      <c r="L43" s="208"/>
-      <c r="M43" s="208"/>
-      <c r="N43" s="208"/>
-      <c r="O43" s="208"/>
-      <c r="P43" s="208"/>
-      <c r="Q43" s="208"/>
-      <c r="R43" s="208"/>
-      <c r="S43" s="186"/>
+      <c r="G43" s="240"/>
+      <c r="H43" s="240"/>
+      <c r="I43" s="240"/>
+      <c r="J43" s="240"/>
+      <c r="K43" s="240"/>
+      <c r="L43" s="240"/>
+      <c r="M43" s="240"/>
+      <c r="N43" s="240"/>
+      <c r="O43" s="240"/>
+      <c r="P43" s="240"/>
+      <c r="Q43" s="240"/>
+      <c r="R43" s="240"/>
+      <c r="S43" s="203"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="225"/>
+      <c r="A44" s="199"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5256,7 +5256,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="225"/>
+      <c r="A45" s="199"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5390,7 +5390,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="225"/>
+      <c r="A46" s="199"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5404,7 +5404,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="225"/>
+      <c r="A47" s="199"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5415,31 +5415,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="185" t="s">
+      <c r="F47" s="202" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="254" t="str">
+      <c r="G47" s="253" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="185" t="s">
+      <c r="J47" s="202" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="252">
+      <c r="K47" s="251">
         <v>1</v>
       </c>
-      <c r="N47" s="185" t="s">
+      <c r="N47" s="202" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="187"/>
-      <c r="P47" s="188"/>
-      <c r="R47" s="185" t="s">
+      <c r="O47" s="205"/>
+      <c r="P47" s="206"/>
+      <c r="R47" s="202" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="185"/>
+      <c r="S47" s="202"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="227"/>
+      <c r="A48" s="201"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5450,15 +5450,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="233"/>
-      <c r="G48" s="255"/>
-      <c r="J48" s="233"/>
-      <c r="K48" s="253"/>
-      <c r="N48" s="186"/>
-      <c r="O48" s="189"/>
-      <c r="P48" s="190"/>
-      <c r="R48" s="186"/>
-      <c r="S48" s="233"/>
+      <c r="F48" s="204"/>
+      <c r="G48" s="254"/>
+      <c r="J48" s="204"/>
+      <c r="K48" s="252"/>
+      <c r="N48" s="203"/>
+      <c r="O48" s="207"/>
+      <c r="P48" s="208"/>
+      <c r="R48" s="203"/>
+      <c r="S48" s="204"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5467,7 +5467,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="262" t="s">
+      <c r="A50" s="185" t="s">
         <v>66</v>
       </c>
       <c r="B50" s="175"/>
@@ -5490,7 +5490,7 @@
       <c r="S50" s="177"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="263"/>
+      <c r="A51" s="186"/>
       <c r="B51" s="178"/>
       <c r="C51" s="180"/>
       <c r="D51" s="180"/>
@@ -5511,7 +5511,7 @@
       <c r="S51" s="179"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="263"/>
+      <c r="A52" s="186"/>
       <c r="B52" s="178"/>
       <c r="C52" s="180"/>
       <c r="D52" s="180"/>
@@ -5532,7 +5532,7 @@
       <c r="S52" s="179"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="263"/>
+      <c r="A53" s="186"/>
       <c r="B53" s="178"/>
       <c r="C53" s="180"/>
       <c r="D53" s="180"/>
@@ -5553,7 +5553,7 @@
       <c r="S53" s="179"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="263"/>
+      <c r="A54" s="186"/>
       <c r="B54" s="178"/>
       <c r="C54" s="180"/>
       <c r="D54" s="180"/>
@@ -5574,7 +5574,7 @@
       <c r="S54" s="179"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="263"/>
+      <c r="A55" s="186"/>
       <c r="B55" s="178"/>
       <c r="C55" s="180"/>
       <c r="D55" s="180"/>
@@ -5595,7 +5595,7 @@
       <c r="S55" s="179"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="263"/>
+      <c r="A56" s="186"/>
       <c r="B56" s="178"/>
       <c r="C56" s="180"/>
       <c r="D56" s="180"/>
@@ -5616,7 +5616,7 @@
       <c r="S56" s="179"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="263"/>
+      <c r="A57" s="186"/>
       <c r="B57" s="178"/>
       <c r="C57" s="180"/>
       <c r="D57" s="180"/>
@@ -5637,104 +5637,119 @@
       <c r="S57" s="179"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="263"/>
+      <c r="A58" s="186"/>
       <c r="B58" s="181"/>
       <c r="S58" s="182"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="263"/>
+      <c r="A59" s="186"/>
       <c r="B59" s="181"/>
       <c r="S59" s="182"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="263"/>
+      <c r="A60" s="186"/>
       <c r="B60" s="181"/>
       <c r="S60" s="182"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="263"/>
+      <c r="A61" s="186"/>
       <c r="B61" s="181"/>
       <c r="S61" s="182"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="263"/>
+      <c r="A62" s="186"/>
       <c r="B62" s="181"/>
       <c r="S62" s="182"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="263"/>
+      <c r="A63" s="186"/>
       <c r="B63" s="181"/>
       <c r="S63" s="182"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="263"/>
+      <c r="A64" s="186"/>
       <c r="B64" s="181"/>
       <c r="S64" s="182"/>
     </row>
-    <row r="65" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A65" s="264"/>
-      <c r="B65" s="183"/>
-      <c r="C65" s="80"/>
-      <c r="D65" s="80"/>
-      <c r="E65" s="80"/>
-      <c r="F65" s="80"/>
-      <c r="G65" s="80"/>
-      <c r="H65" s="80"/>
-      <c r="I65" s="80"/>
-      <c r="J65" s="80"/>
-      <c r="K65" s="80"/>
-      <c r="L65" s="80"/>
-      <c r="M65" s="80"/>
-      <c r="N65" s="80"/>
-      <c r="O65" s="80"/>
-      <c r="P65" s="80"/>
-      <c r="Q65" s="80"/>
-      <c r="R65" s="80"/>
-      <c r="S65" s="184"/>
+    <row r="65" spans="1:19">
+      <c r="A65" s="186"/>
+      <c r="B65" s="181"/>
+      <c r="S65" s="182"/>
+    </row>
+    <row r="66" spans="1:19">
+      <c r="A66" s="186"/>
+      <c r="B66" s="181"/>
+      <c r="S66" s="182"/>
+    </row>
+    <row r="67" spans="1:19">
+      <c r="A67" s="186"/>
+      <c r="B67" s="181"/>
+      <c r="S67" s="182"/>
+    </row>
+    <row r="68" spans="1:19" ht="15.75" thickBot="1">
+      <c r="A68" s="187"/>
+      <c r="B68" s="183"/>
+      <c r="C68" s="80"/>
+      <c r="D68" s="80"/>
+      <c r="E68" s="80"/>
+      <c r="F68" s="80"/>
+      <c r="G68" s="80"/>
+      <c r="H68" s="80"/>
+      <c r="I68" s="80"/>
+      <c r="J68" s="80"/>
+      <c r="K68" s="80"/>
+      <c r="L68" s="80"/>
+      <c r="M68" s="80"/>
+      <c r="N68" s="80"/>
+      <c r="O68" s="80"/>
+      <c r="P68" s="80"/>
+      <c r="Q68" s="80"/>
+      <c r="R68" s="80"/>
+      <c r="S68" s="184"/>
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="A50:A65"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
     <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="O1:S1"/>
     <mergeCell ref="O2:S2"/>
     <mergeCell ref="O6:S6"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="F40:S40"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="O3:S3"/>
     <mergeCell ref="O4:S4"/>
     <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="A50:A68"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F40:S40"/>
     <mergeCell ref="A10:A22"/>
     <mergeCell ref="A24:A28"/>
-    <mergeCell ref="R9:S9"/>
     <mergeCell ref="A40:A48"/>
-    <mergeCell ref="B3:D3"/>
     <mergeCell ref="R47:R48"/>
     <mergeCell ref="S47:S48"/>
     <mergeCell ref="S42:S43"/>
     <mergeCell ref="N47:N48"/>
     <mergeCell ref="O47:P48"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B5:D5"/>
     <mergeCell ref="H9:I9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
     <mergeCell ref="F47:F48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFBC939-F878-4B35-9092-FCF4C2E8C88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE97CF5-5714-4014-B818-422FD170AA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1813,82 +1813,102 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1936,12 +1956,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1987,91 +2001,77 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2558,33 +2558,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="226" t="s">
+      <c r="A1" s="228" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
-      <c r="K1" s="227"/>
-      <c r="L1" s="228"/>
+      <c r="B1" s="229"/>
+      <c r="C1" s="229"/>
+      <c r="D1" s="229"/>
+      <c r="E1" s="229"/>
+      <c r="F1" s="229"/>
+      <c r="G1" s="229"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
+      <c r="K1" s="229"/>
+      <c r="L1" s="230"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="217" t="s">
+      <c r="O1" s="221" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="218"/>
-      <c r="Q1" s="218"/>
-      <c r="R1" s="218"/>
-      <c r="S1" s="219"/>
+      <c r="P1" s="222"/>
+      <c r="Q1" s="222"/>
+      <c r="R1" s="222"/>
+      <c r="S1" s="223"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2603,165 +2603,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="220"/>
-      <c r="P2" s="221"/>
-      <c r="Q2" s="221"/>
-      <c r="R2" s="221"/>
-      <c r="S2" s="222"/>
+      <c r="O2" s="224"/>
+      <c r="P2" s="225"/>
+      <c r="Q2" s="225"/>
+      <c r="R2" s="225"/>
+      <c r="S2" s="226"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="232"/>
-      <c r="C3" s="233"/>
-      <c r="D3" s="234"/>
+      <c r="B3" s="234"/>
+      <c r="C3" s="235"/>
+      <c r="D3" s="236"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="245"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="247"/>
+      <c r="I3" s="209"/>
+      <c r="J3" s="210"/>
+      <c r="K3" s="211"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="229"/>
-      <c r="P3" s="230"/>
-      <c r="Q3" s="230"/>
-      <c r="R3" s="230"/>
-      <c r="S3" s="231"/>
+      <c r="O3" s="231"/>
+      <c r="P3" s="232"/>
+      <c r="Q3" s="232"/>
+      <c r="R3" s="232"/>
+      <c r="S3" s="233"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="211"/>
-      <c r="C4" s="212"/>
-      <c r="D4" s="213"/>
+      <c r="B4" s="215"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="217"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="214"/>
-      <c r="J4" s="215"/>
-      <c r="K4" s="216"/>
+      <c r="I4" s="218"/>
+      <c r="J4" s="219"/>
+      <c r="K4" s="220"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="229"/>
-      <c r="P4" s="230"/>
-      <c r="Q4" s="230"/>
-      <c r="R4" s="230"/>
-      <c r="S4" s="231"/>
+      <c r="O4" s="231"/>
+      <c r="P4" s="232"/>
+      <c r="Q4" s="232"/>
+      <c r="R4" s="232"/>
+      <c r="S4" s="233"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="235"/>
-      <c r="C5" s="236"/>
-      <c r="D5" s="237"/>
+      <c r="B5" s="237"/>
+      <c r="C5" s="238"/>
+      <c r="D5" s="239"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="238"/>
-      <c r="J5" s="230"/>
-      <c r="K5" s="231"/>
+      <c r="I5" s="240"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="233"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="229"/>
-      <c r="P5" s="230"/>
-      <c r="Q5" s="230"/>
-      <c r="R5" s="230"/>
-      <c r="S5" s="231"/>
+      <c r="O5" s="231"/>
+      <c r="P5" s="232"/>
+      <c r="Q5" s="232"/>
+      <c r="R5" s="232"/>
+      <c r="S5" s="233"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="255"/>
-      <c r="C6" s="256"/>
-      <c r="D6" s="257"/>
+      <c r="B6" s="191"/>
+      <c r="C6" s="192"/>
+      <c r="D6" s="193"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="258"/>
-      <c r="J6" s="224"/>
-      <c r="K6" s="225"/>
+      <c r="I6" s="194"/>
+      <c r="J6" s="195"/>
+      <c r="K6" s="196"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="223"/>
-      <c r="P6" s="224"/>
-      <c r="Q6" s="224"/>
-      <c r="R6" s="224"/>
-      <c r="S6" s="225"/>
+      <c r="O6" s="227"/>
+      <c r="P6" s="195"/>
+      <c r="Q6" s="195"/>
+      <c r="R6" s="195"/>
+      <c r="S6" s="196"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="259" t="s">
+      <c r="A8" s="197" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="260"/>
-      <c r="C8" s="260"/>
-      <c r="D8" s="261"/>
-      <c r="F8" s="239" t="s">
+      <c r="B8" s="198"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="199"/>
+      <c r="F8" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="240"/>
-      <c r="H8" s="240"/>
-      <c r="I8" s="240"/>
-      <c r="J8" s="240"/>
-      <c r="K8" s="240"/>
-      <c r="L8" s="240"/>
-      <c r="M8" s="240"/>
-      <c r="N8" s="240"/>
-      <c r="O8" s="240"/>
-      <c r="P8" s="240"/>
-      <c r="Q8" s="240"/>
-      <c r="R8" s="240"/>
-      <c r="S8" s="248"/>
+      <c r="G8" s="204"/>
+      <c r="H8" s="204"/>
+      <c r="I8" s="204"/>
+      <c r="J8" s="204"/>
+      <c r="K8" s="204"/>
+      <c r="L8" s="204"/>
+      <c r="M8" s="204"/>
+      <c r="N8" s="204"/>
+      <c r="O8" s="204"/>
+      <c r="P8" s="204"/>
+      <c r="Q8" s="204"/>
+      <c r="R8" s="204"/>
+      <c r="S8" s="212"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="262"/>
-      <c r="B9" s="263"/>
-      <c r="C9" s="263"/>
-      <c r="D9" s="264"/>
-      <c r="F9" s="193" t="s">
+      <c r="A9" s="200"/>
+      <c r="B9" s="201"/>
+      <c r="C9" s="201"/>
+      <c r="D9" s="202"/>
+      <c r="F9" s="249" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="194"/>
-      <c r="H9" s="209" t="s">
+      <c r="G9" s="250"/>
+      <c r="H9" s="263" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="210"/>
-      <c r="J9" s="191" t="s">
+      <c r="I9" s="264"/>
+      <c r="J9" s="247" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="192"/>
-      <c r="L9" s="249" t="s">
+      <c r="K9" s="248"/>
+      <c r="L9" s="213" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="250"/>
-      <c r="N9" s="243" t="s">
+      <c r="M9" s="214"/>
+      <c r="N9" s="207" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="244"/>
-      <c r="P9" s="241" t="s">
+      <c r="O9" s="208"/>
+      <c r="P9" s="205" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="242"/>
-      <c r="R9" s="243" t="s">
+      <c r="Q9" s="206"/>
+      <c r="R9" s="207" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="244"/>
+      <c r="S9" s="208"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="198" t="s">
+      <c r="A10" s="254" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2818,7 +2818,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="199"/>
+      <c r="A11" s="255"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2924,7 +2924,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="199"/>
+      <c r="A12" s="255"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3030,7 +3030,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="199"/>
+      <c r="A13" s="255"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3136,7 +3136,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="199"/>
+      <c r="A14" s="255"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3223,7 +3223,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="199"/>
+      <c r="A15" s="255"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3310,7 +3310,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="199"/>
+      <c r="A16" s="255"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3397,7 +3397,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="199"/>
+      <c r="A17" s="255"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3484,7 +3484,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="199"/>
+      <c r="A18" s="255"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3571,7 +3571,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="199"/>
+      <c r="A19" s="255"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3658,7 +3658,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="199"/>
+      <c r="A20" s="255"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="199"/>
+      <c r="A21" s="255"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3832,7 +3832,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="200"/>
+      <c r="A22" s="256"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3975,7 +3975,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="198" t="s">
+      <c r="A24" s="254" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -4083,7 +4083,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="199"/>
+      <c r="A25" s="255"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4189,7 +4189,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="199"/>
+      <c r="A26" s="255"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4295,7 +4295,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="199"/>
+      <c r="A27" s="255"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4382,7 +4382,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="201"/>
+      <c r="A28" s="257"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4544,7 +4544,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="188" t="s">
+      <c r="A32" s="244" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4623,7 +4623,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="189"/>
+      <c r="A33" s="245"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4700,7 +4700,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="190"/>
+      <c r="A34" s="246"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4798,7 +4798,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="188" t="s">
+      <c r="A36" s="244" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4877,7 +4877,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="189"/>
+      <c r="A37" s="245"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4954,7 +4954,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="190"/>
+      <c r="A38" s="246"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5045,7 +5045,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="198" t="s">
+      <c r="A40" s="254" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5057,25 +5057,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="195" t="s">
+      <c r="F40" s="251" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="196"/>
-      <c r="H40" s="196"/>
-      <c r="I40" s="196"/>
-      <c r="J40" s="196"/>
-      <c r="K40" s="196"/>
-      <c r="L40" s="196"/>
-      <c r="M40" s="196"/>
-      <c r="N40" s="196"/>
-      <c r="O40" s="196"/>
-      <c r="P40" s="196"/>
-      <c r="Q40" s="196"/>
-      <c r="R40" s="196"/>
-      <c r="S40" s="197"/>
+      <c r="G40" s="252"/>
+      <c r="H40" s="252"/>
+      <c r="I40" s="252"/>
+      <c r="J40" s="252"/>
+      <c r="K40" s="252"/>
+      <c r="L40" s="252"/>
+      <c r="M40" s="252"/>
+      <c r="N40" s="252"/>
+      <c r="O40" s="252"/>
+      <c r="P40" s="252"/>
+      <c r="Q40" s="252"/>
+      <c r="R40" s="252"/>
+      <c r="S40" s="253"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="199"/>
+      <c r="A41" s="255"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -5138,7 +5138,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="199"/>
+      <c r="A42" s="255"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5163,13 +5163,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="202">
+      <c r="S42" s="185">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="199"/>
+      <c r="A43" s="255"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5181,26 +5181,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="239" t="str">
+      <c r="F43" s="203" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="240"/>
-      <c r="H43" s="240"/>
-      <c r="I43" s="240"/>
-      <c r="J43" s="240"/>
-      <c r="K43" s="240"/>
-      <c r="L43" s="240"/>
-      <c r="M43" s="240"/>
-      <c r="N43" s="240"/>
-      <c r="O43" s="240"/>
-      <c r="P43" s="240"/>
-      <c r="Q43" s="240"/>
-      <c r="R43" s="240"/>
-      <c r="S43" s="203"/>
+      <c r="G43" s="204"/>
+      <c r="H43" s="204"/>
+      <c r="I43" s="204"/>
+      <c r="J43" s="204"/>
+      <c r="K43" s="204"/>
+      <c r="L43" s="204"/>
+      <c r="M43" s="204"/>
+      <c r="N43" s="204"/>
+      <c r="O43" s="204"/>
+      <c r="P43" s="204"/>
+      <c r="Q43" s="204"/>
+      <c r="R43" s="204"/>
+      <c r="S43" s="258"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="199"/>
+      <c r="A44" s="255"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5256,7 +5256,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="199"/>
+      <c r="A45" s="255"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5390,7 +5390,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="199"/>
+      <c r="A46" s="255"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5404,7 +5404,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="199"/>
+      <c r="A47" s="255"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5415,31 +5415,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="202" t="s">
+      <c r="F47" s="185" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="253" t="str">
+      <c r="G47" s="189" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="202" t="s">
+      <c r="J47" s="185" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="251">
+      <c r="K47" s="187">
         <v>1</v>
       </c>
-      <c r="N47" s="202" t="s">
+      <c r="N47" s="185" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="205"/>
-      <c r="P47" s="206"/>
-      <c r="R47" s="202" t="s">
+      <c r="O47" s="259"/>
+      <c r="P47" s="260"/>
+      <c r="R47" s="185" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="202"/>
+      <c r="S47" s="185"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="201"/>
+      <c r="A48" s="257"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5450,15 +5450,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="204"/>
-      <c r="G48" s="254"/>
-      <c r="J48" s="204"/>
-      <c r="K48" s="252"/>
-      <c r="N48" s="203"/>
-      <c r="O48" s="207"/>
-      <c r="P48" s="208"/>
-      <c r="R48" s="203"/>
-      <c r="S48" s="204"/>
+      <c r="F48" s="186"/>
+      <c r="G48" s="190"/>
+      <c r="J48" s="186"/>
+      <c r="K48" s="188"/>
+      <c r="N48" s="258"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
+      <c r="R48" s="258"/>
+      <c r="S48" s="186"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5467,7 +5467,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="185" t="s">
+      <c r="A50" s="241" t="s">
         <v>66</v>
       </c>
       <c r="B50" s="175"/>
@@ -5490,7 +5490,7 @@
       <c r="S50" s="177"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="186"/>
+      <c r="A51" s="242"/>
       <c r="B51" s="178"/>
       <c r="C51" s="180"/>
       <c r="D51" s="180"/>
@@ -5511,7 +5511,7 @@
       <c r="S51" s="179"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="186"/>
+      <c r="A52" s="242"/>
       <c r="B52" s="178"/>
       <c r="C52" s="180"/>
       <c r="D52" s="180"/>
@@ -5532,7 +5532,7 @@
       <c r="S52" s="179"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="186"/>
+      <c r="A53" s="242"/>
       <c r="B53" s="178"/>
       <c r="C53" s="180"/>
       <c r="D53" s="180"/>
@@ -5553,7 +5553,7 @@
       <c r="S53" s="179"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="186"/>
+      <c r="A54" s="242"/>
       <c r="B54" s="178"/>
       <c r="C54" s="180"/>
       <c r="D54" s="180"/>
@@ -5574,7 +5574,7 @@
       <c r="S54" s="179"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="186"/>
+      <c r="A55" s="242"/>
       <c r="B55" s="178"/>
       <c r="C55" s="180"/>
       <c r="D55" s="180"/>
@@ -5595,7 +5595,7 @@
       <c r="S55" s="179"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="186"/>
+      <c r="A56" s="242"/>
       <c r="B56" s="178"/>
       <c r="C56" s="180"/>
       <c r="D56" s="180"/>
@@ -5616,7 +5616,7 @@
       <c r="S56" s="179"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="186"/>
+      <c r="A57" s="242"/>
       <c r="B57" s="178"/>
       <c r="C57" s="180"/>
       <c r="D57" s="180"/>
@@ -5637,57 +5637,57 @@
       <c r="S57" s="179"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="186"/>
+      <c r="A58" s="242"/>
       <c r="B58" s="181"/>
       <c r="S58" s="182"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="186"/>
+      <c r="A59" s="242"/>
       <c r="B59" s="181"/>
       <c r="S59" s="182"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="186"/>
+      <c r="A60" s="242"/>
       <c r="B60" s="181"/>
       <c r="S60" s="182"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="186"/>
+      <c r="A61" s="242"/>
       <c r="B61" s="181"/>
       <c r="S61" s="182"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="186"/>
+      <c r="A62" s="242"/>
       <c r="B62" s="181"/>
       <c r="S62" s="182"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="186"/>
+      <c r="A63" s="242"/>
       <c r="B63" s="181"/>
       <c r="S63" s="182"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="186"/>
+      <c r="A64" s="242"/>
       <c r="B64" s="181"/>
       <c r="S64" s="182"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="186"/>
+      <c r="A65" s="242"/>
       <c r="B65" s="181"/>
       <c r="S65" s="182"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="186"/>
+      <c r="A66" s="242"/>
       <c r="B66" s="181"/>
       <c r="S66" s="182"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="186"/>
+      <c r="A67" s="242"/>
       <c r="B67" s="181"/>
       <c r="S67" s="182"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A68" s="187"/>
+      <c r="A68" s="243"/>
       <c r="B68" s="183"/>
       <c r="C68" s="80"/>
       <c r="D68" s="80"/>
@@ -5709,31 +5709,6 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
     <mergeCell ref="A50:A68"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A38"/>
@@ -5750,6 +5725,31 @@
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F47:F48"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6419,7 +6419,7 @@
         <v/>
       </c>
       <c r="D25" t="str">
-        <f t="shared" ref="D25:D98" si="2">CONCATENATE(A25,C25)</f>
+        <f>IF(A25="43/1.5",CONCATENATE(A26,C25),CONCATENATE(A25,C25))</f>
         <v xml:space="preserve"> 22/0.4</v>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
         <v/>
       </c>
       <c r="D26" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D26:D89" si="2">IF(A26="43/1.5",CONCATENATE(A27,C26),CONCATENATE(A26,C26))</f>
         <v xml:space="preserve"> 22/1</v>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
         <v/>
       </c>
       <c r="D90" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D90:D143" si="3">IF(A90="43/1.5",CONCATENATE(A91,C90),CONCATENATE(A90,C90))</f>
         <v xml:space="preserve"> 23/0.8</v>
       </c>
     </row>
@@ -7343,7 +7343,7 @@
         <v/>
       </c>
       <c r="D91" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> 23/2</v>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
         <v/>
       </c>
       <c r="D92" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> 43/1</v>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
         <v/>
       </c>
       <c r="D93" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> 43/1.5</v>
       </c>
     </row>
@@ -7385,7 +7385,7 @@
         <v/>
       </c>
       <c r="D94" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> 43/2</v>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
         <v/>
       </c>
       <c r="D95" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> 22/0.4</v>
       </c>
     </row>
@@ -7413,7 +7413,7 @@
         <v/>
       </c>
       <c r="D96" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> 22/1</v>
       </c>
     </row>
@@ -7427,7 +7427,7 @@
         <v/>
       </c>
       <c r="D97" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> 23/0.8</v>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
         <v/>
       </c>
       <c r="D98" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> 23/2</v>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
         <v/>
       </c>
       <c r="D99" t="str">
-        <f t="shared" ref="D99:D152" si="3">CONCATENATE(A99,C99)</f>
+        <f t="shared" si="3"/>
         <v xml:space="preserve"> 43/1</v>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
         <v/>
       </c>
       <c r="D145" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A145="43/1.5",CONCATENATE(A146,C145),CONCATENATE(A145,C145))</f>
         <v xml:space="preserve"> 22/0.4</v>
       </c>
     </row>
@@ -8123,7 +8123,7 @@
         <v/>
       </c>
       <c r="D146" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D146:D186" si="4">IF(A146="43/1.5",CONCATENATE(A147,C146),CONCATENATE(A146,C146))</f>
         <v xml:space="preserve"> 22/1</v>
       </c>
     </row>
@@ -8137,7 +8137,7 @@
         <v/>
       </c>
       <c r="D147" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> 23/0.8</v>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
         <v/>
       </c>
       <c r="D148" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> 23/2</v>
       </c>
     </row>
@@ -8165,7 +8165,7 @@
         <v/>
       </c>
       <c r="D149" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> 43/1</v>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
         <v/>
       </c>
       <c r="D150" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> 43/1.5</v>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
         <v/>
       </c>
       <c r="D151" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> 43/2</v>
       </c>
     </row>
@@ -8207,7 +8207,7 @@
         <v/>
       </c>
       <c r="D152" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> 22/0.4</v>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
         <v/>
       </c>
       <c r="D153" t="str">
-        <f t="shared" ref="D153:D191" si="4">CONCATENATE(A153,C153)</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> 22/1</v>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
         <v/>
       </c>
       <c r="D187" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="D153:D191" si="5">CONCATENATE(A187,C187)</f>
         <v>CUT BLAT 600</v>
       </c>
     </row>
@@ -8709,7 +8709,7 @@
         <v/>
       </c>
       <c r="D188" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>CUT BLAT 920</v>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
         <v/>
       </c>
       <c r="D189" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>CUT PS</v>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
         <v/>
       </c>
       <c r="D190" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>CUT HDF</v>
       </c>
     </row>
@@ -8748,7 +8748,7 @@
         <v/>
       </c>
       <c r="D191" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>CUT MDF</v>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
         <v/>
       </c>
       <c r="D193" t="str">
-        <f t="shared" ref="D193:D194" si="5">CONCATENATE(A193,C193)</f>
+        <f t="shared" ref="D193:D194" si="6">CONCATENATE(A193,C193)</f>
         <v>CUT CLEAF</v>
       </c>
     </row>
@@ -8787,7 +8787,7 @@
         <v/>
       </c>
       <c r="D194" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>DUBL_PAL</v>
       </c>
     </row>
@@ -8800,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="D195" t="str">
-        <f t="shared" ref="D195:D201" si="6">CONCATENATE(A195,C195)</f>
+        <f t="shared" ref="D195:D201" si="7">CONCATENATE(A195,C195)</f>
         <v>Cant 22/0.4</v>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
         <v>0</v>
       </c>
       <c r="D196" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Cant 22/1</v>
       </c>
     </row>
@@ -8826,7 +8826,7 @@
         <v>0</v>
       </c>
       <c r="D197" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Cant 23/0.8</v>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
         <v>0</v>
       </c>
       <c r="D198" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Cant 23/2</v>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
         <v>0</v>
       </c>
       <c r="D199" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Cant 43/1</v>
       </c>
     </row>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="D200" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Cant 43/1.5</v>
       </c>
     </row>
@@ -8878,7 +8878,7 @@
         <v>0</v>
       </c>
       <c r="D201" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Cant 43/2</v>
       </c>
     </row>
@@ -11102,7 +11102,7 @@
 "AGT "&amp;SUBSTITUTE(TRIM(MID(A2,FIND("-",A2)+1,50)),"LR ","LR"),
 SUBSTITUTE(TRIM(MID(A2,FIND("-",A2)+1,50)),"LR ","LR")
 )
-&amp;IF(OR(E2=600,E2=650,E2=920)," /"&amp;E2,"")
+&amp;IF(OR(E2=600,E2=650,E2=920),"/"&amp;E2,"")
 &amp;IF(E2=640," PS",""),"")
 &amp;IF(AND(OR(B2=8,B2=10,B2=16),D2=2800,E2=2070)," "&amp;B2&amp;"mm","")</f>
         <v/>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE97CF5-5714-4014-B818-422FD170AA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43559CB7-E9D6-46EC-AC32-EC7F3F709AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -1813,11 +1813,212 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1848,12 +2049,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1872,205 +2067,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2558,33 +2558,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="228" t="s">
+      <c r="A1" s="220" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="229"/>
-      <c r="C1" s="229"/>
-      <c r="D1" s="229"/>
-      <c r="E1" s="229"/>
-      <c r="F1" s="229"/>
-      <c r="G1" s="229"/>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
-      <c r="J1" s="229"/>
-      <c r="K1" s="229"/>
-      <c r="L1" s="230"/>
+      <c r="B1" s="221"/>
+      <c r="C1" s="221"/>
+      <c r="D1" s="221"/>
+      <c r="E1" s="221"/>
+      <c r="F1" s="221"/>
+      <c r="G1" s="221"/>
+      <c r="H1" s="221"/>
+      <c r="I1" s="221"/>
+      <c r="J1" s="221"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="222"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="221" t="s">
+      <c r="O1" s="211" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="222"/>
-      <c r="Q1" s="222"/>
-      <c r="R1" s="222"/>
-      <c r="S1" s="223"/>
+      <c r="P1" s="212"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="212"/>
+      <c r="S1" s="213"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2603,165 +2603,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="224"/>
-      <c r="P2" s="225"/>
-      <c r="Q2" s="225"/>
-      <c r="R2" s="225"/>
-      <c r="S2" s="226"/>
+      <c r="O2" s="214"/>
+      <c r="P2" s="215"/>
+      <c r="Q2" s="215"/>
+      <c r="R2" s="215"/>
+      <c r="S2" s="216"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="234"/>
-      <c r="C3" s="235"/>
-      <c r="D3" s="236"/>
+      <c r="B3" s="226"/>
+      <c r="C3" s="227"/>
+      <c r="D3" s="228"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="209"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="211"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="235"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="231"/>
-      <c r="P3" s="232"/>
-      <c r="Q3" s="232"/>
-      <c r="R3" s="232"/>
-      <c r="S3" s="233"/>
+      <c r="O3" s="223"/>
+      <c r="P3" s="224"/>
+      <c r="Q3" s="224"/>
+      <c r="R3" s="224"/>
+      <c r="S3" s="225"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="215"/>
-      <c r="C4" s="216"/>
-      <c r="D4" s="217"/>
+      <c r="B4" s="243"/>
+      <c r="C4" s="244"/>
+      <c r="D4" s="245"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="218"/>
-      <c r="J4" s="219"/>
-      <c r="K4" s="220"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="247"/>
+      <c r="K4" s="248"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="231"/>
-      <c r="P4" s="232"/>
-      <c r="Q4" s="232"/>
-      <c r="R4" s="232"/>
-      <c r="S4" s="233"/>
+      <c r="O4" s="223"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="225"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="237"/>
-      <c r="C5" s="238"/>
-      <c r="D5" s="239"/>
+      <c r="B5" s="229"/>
+      <c r="C5" s="230"/>
+      <c r="D5" s="231"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="240"/>
-      <c r="J5" s="232"/>
-      <c r="K5" s="233"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="224"/>
+      <c r="K5" s="225"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="231"/>
-      <c r="P5" s="232"/>
-      <c r="Q5" s="232"/>
-      <c r="R5" s="232"/>
-      <c r="S5" s="233"/>
+      <c r="O5" s="223"/>
+      <c r="P5" s="224"/>
+      <c r="Q5" s="224"/>
+      <c r="R5" s="224"/>
+      <c r="S5" s="225"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="191"/>
-      <c r="C6" s="192"/>
-      <c r="D6" s="193"/>
+      <c r="B6" s="253"/>
+      <c r="C6" s="254"/>
+      <c r="D6" s="255"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="194"/>
-      <c r="J6" s="195"/>
-      <c r="K6" s="196"/>
+      <c r="I6" s="256"/>
+      <c r="J6" s="218"/>
+      <c r="K6" s="219"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="227"/>
-      <c r="P6" s="195"/>
-      <c r="Q6" s="195"/>
-      <c r="R6" s="195"/>
-      <c r="S6" s="196"/>
+      <c r="O6" s="217"/>
+      <c r="P6" s="218"/>
+      <c r="Q6" s="218"/>
+      <c r="R6" s="218"/>
+      <c r="S6" s="219"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="197" t="s">
+      <c r="A8" s="257" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="198"/>
-      <c r="C8" s="198"/>
-      <c r="D8" s="199"/>
-      <c r="F8" s="203" t="s">
+      <c r="B8" s="258"/>
+      <c r="C8" s="258"/>
+      <c r="D8" s="259"/>
+      <c r="F8" s="236" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="204"/>
-      <c r="H8" s="204"/>
-      <c r="I8" s="204"/>
-      <c r="J8" s="204"/>
-      <c r="K8" s="204"/>
-      <c r="L8" s="204"/>
-      <c r="M8" s="204"/>
-      <c r="N8" s="204"/>
-      <c r="O8" s="204"/>
-      <c r="P8" s="204"/>
-      <c r="Q8" s="204"/>
-      <c r="R8" s="204"/>
-      <c r="S8" s="212"/>
+      <c r="G8" s="237"/>
+      <c r="H8" s="237"/>
+      <c r="I8" s="237"/>
+      <c r="J8" s="237"/>
+      <c r="K8" s="237"/>
+      <c r="L8" s="237"/>
+      <c r="M8" s="237"/>
+      <c r="N8" s="237"/>
+      <c r="O8" s="237"/>
+      <c r="P8" s="237"/>
+      <c r="Q8" s="237"/>
+      <c r="R8" s="237"/>
+      <c r="S8" s="238"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="200"/>
-      <c r="B9" s="201"/>
-      <c r="C9" s="201"/>
-      <c r="D9" s="202"/>
-      <c r="F9" s="249" t="s">
+      <c r="A9" s="260"/>
+      <c r="B9" s="261"/>
+      <c r="C9" s="261"/>
+      <c r="D9" s="262"/>
+      <c r="F9" s="193" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="250"/>
-      <c r="H9" s="263" t="s">
+      <c r="G9" s="194"/>
+      <c r="H9" s="209" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="264"/>
-      <c r="J9" s="247" t="s">
+      <c r="I9" s="210"/>
+      <c r="J9" s="191" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="248"/>
-      <c r="L9" s="213" t="s">
+      <c r="K9" s="192"/>
+      <c r="L9" s="241" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="214"/>
-      <c r="N9" s="207" t="s">
+      <c r="M9" s="242"/>
+      <c r="N9" s="239" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="208"/>
-      <c r="P9" s="205" t="s">
+      <c r="O9" s="240"/>
+      <c r="P9" s="263" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="206"/>
-      <c r="R9" s="207" t="s">
+      <c r="Q9" s="264"/>
+      <c r="R9" s="239" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="208"/>
+      <c r="S9" s="240"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="254" t="s">
+      <c r="A10" s="198" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2818,7 +2818,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="255"/>
+      <c r="A11" s="199"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2924,7 +2924,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="255"/>
+      <c r="A12" s="199"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3030,7 +3030,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="255"/>
+      <c r="A13" s="199"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3136,7 +3136,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="255"/>
+      <c r="A14" s="199"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3223,7 +3223,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="255"/>
+      <c r="A15" s="199"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3310,7 +3310,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="255"/>
+      <c r="A16" s="199"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3397,7 +3397,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="255"/>
+      <c r="A17" s="199"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3484,7 +3484,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="255"/>
+      <c r="A18" s="199"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3571,7 +3571,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="255"/>
+      <c r="A19" s="199"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3658,7 +3658,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="255"/>
+      <c r="A20" s="199"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="255"/>
+      <c r="A21" s="199"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3832,7 +3832,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="256"/>
+      <c r="A22" s="200"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3975,7 +3975,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="254" t="s">
+      <c r="A24" s="198" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -4083,7 +4083,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="255"/>
+      <c r="A25" s="199"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4189,7 +4189,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="255"/>
+      <c r="A26" s="199"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4295,7 +4295,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="255"/>
+      <c r="A27" s="199"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4382,7 +4382,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="257"/>
+      <c r="A28" s="201"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4544,7 +4544,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="244" t="s">
+      <c r="A32" s="188" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4623,7 +4623,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="245"/>
+      <c r="A33" s="189"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4700,7 +4700,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="246"/>
+      <c r="A34" s="190"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4798,7 +4798,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="244" t="s">
+      <c r="A36" s="188" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="89" t="str">
-        <f>IF(B36&lt;&gt;"",TRIM(LEFT(B36,LEN(B36)-3)),"")</f>
+        <f>IF(B36&lt;&gt;"",TRIM(RIGHT(B36,LEN(B36)-3)),"")</f>
         <v/>
       </c>
       <c r="G36" s="90" t="str">
@@ -4877,7 +4877,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="245"/>
+      <c r="A37" s="189"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="85" t="str">
-        <f>IF(B37&lt;&gt;"",TRIM(LEFT(B37,LEN(B37)-3)),"")</f>
+        <f>IF(B37&lt;&gt;"",TRIM(RIGHT(B37,LEN(B37)-3)),"")</f>
         <v/>
       </c>
       <c r="G37" s="86" t="str">
@@ -4954,7 +4954,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="246"/>
+      <c r="A38" s="190"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="91" t="str">
-        <f>IF(B38&lt;&gt;"",TRIM(LEFT(B38,LEN(B38)-3)),"")</f>
+        <f>IF(B38&lt;&gt;"",TRIM(RIGHT(B38,LEN(B38)-3)),"")</f>
         <v/>
       </c>
       <c r="G38" s="141" t="str">
@@ -5045,7 +5045,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="254" t="s">
+      <c r="A40" s="198" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5057,25 +5057,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="251" t="s">
+      <c r="F40" s="195" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="252"/>
-      <c r="H40" s="252"/>
-      <c r="I40" s="252"/>
-      <c r="J40" s="252"/>
-      <c r="K40" s="252"/>
-      <c r="L40" s="252"/>
-      <c r="M40" s="252"/>
-      <c r="N40" s="252"/>
-      <c r="O40" s="252"/>
-      <c r="P40" s="252"/>
-      <c r="Q40" s="252"/>
-      <c r="R40" s="252"/>
-      <c r="S40" s="253"/>
+      <c r="G40" s="196"/>
+      <c r="H40" s="196"/>
+      <c r="I40" s="196"/>
+      <c r="J40" s="196"/>
+      <c r="K40" s="196"/>
+      <c r="L40" s="196"/>
+      <c r="M40" s="196"/>
+      <c r="N40" s="196"/>
+      <c r="O40" s="196"/>
+      <c r="P40" s="196"/>
+      <c r="Q40" s="196"/>
+      <c r="R40" s="196"/>
+      <c r="S40" s="197"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="255"/>
+      <c r="A41" s="199"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -5138,7 +5138,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="255"/>
+      <c r="A42" s="199"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5163,13 +5163,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="185">
+      <c r="S42" s="202">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="255"/>
+      <c r="A43" s="199"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5181,26 +5181,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="203" t="str">
+      <c r="F43" s="236" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="204"/>
-      <c r="H43" s="204"/>
-      <c r="I43" s="204"/>
-      <c r="J43" s="204"/>
-      <c r="K43" s="204"/>
-      <c r="L43" s="204"/>
-      <c r="M43" s="204"/>
-      <c r="N43" s="204"/>
-      <c r="O43" s="204"/>
-      <c r="P43" s="204"/>
-      <c r="Q43" s="204"/>
-      <c r="R43" s="204"/>
-      <c r="S43" s="258"/>
+      <c r="G43" s="237"/>
+      <c r="H43" s="237"/>
+      <c r="I43" s="237"/>
+      <c r="J43" s="237"/>
+      <c r="K43" s="237"/>
+      <c r="L43" s="237"/>
+      <c r="M43" s="237"/>
+      <c r="N43" s="237"/>
+      <c r="O43" s="237"/>
+      <c r="P43" s="237"/>
+      <c r="Q43" s="237"/>
+      <c r="R43" s="237"/>
+      <c r="S43" s="203"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="255"/>
+      <c r="A44" s="199"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5256,7 +5256,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="255"/>
+      <c r="A45" s="199"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5390,7 +5390,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="255"/>
+      <c r="A46" s="199"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5404,7 +5404,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="255"/>
+      <c r="A47" s="199"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5415,31 +5415,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="185" t="s">
+      <c r="F47" s="202" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="189" t="str">
+      <c r="G47" s="251" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="185" t="s">
+      <c r="J47" s="202" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="187">
+      <c r="K47" s="249">
         <v>1</v>
       </c>
-      <c r="N47" s="185" t="s">
+      <c r="N47" s="202" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="259"/>
-      <c r="P47" s="260"/>
-      <c r="R47" s="185" t="s">
+      <c r="O47" s="205"/>
+      <c r="P47" s="206"/>
+      <c r="R47" s="202" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="185"/>
+      <c r="S47" s="202"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="257"/>
+      <c r="A48" s="201"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5450,15 +5450,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="186"/>
-      <c r="G48" s="190"/>
-      <c r="J48" s="186"/>
-      <c r="K48" s="188"/>
-      <c r="N48" s="258"/>
-      <c r="O48" s="261"/>
-      <c r="P48" s="262"/>
-      <c r="R48" s="258"/>
-      <c r="S48" s="186"/>
+      <c r="F48" s="204"/>
+      <c r="G48" s="252"/>
+      <c r="J48" s="204"/>
+      <c r="K48" s="250"/>
+      <c r="N48" s="203"/>
+      <c r="O48" s="207"/>
+      <c r="P48" s="208"/>
+      <c r="R48" s="203"/>
+      <c r="S48" s="204"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5467,7 +5467,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="241" t="s">
+      <c r="A50" s="185" t="s">
         <v>66</v>
       </c>
       <c r="B50" s="175"/>
@@ -5490,7 +5490,7 @@
       <c r="S50" s="177"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="242"/>
+      <c r="A51" s="186"/>
       <c r="B51" s="178"/>
       <c r="C51" s="180"/>
       <c r="D51" s="180"/>
@@ -5511,7 +5511,7 @@
       <c r="S51" s="179"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="242"/>
+      <c r="A52" s="186"/>
       <c r="B52" s="178"/>
       <c r="C52" s="180"/>
       <c r="D52" s="180"/>
@@ -5532,7 +5532,7 @@
       <c r="S52" s="179"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="242"/>
+      <c r="A53" s="186"/>
       <c r="B53" s="178"/>
       <c r="C53" s="180"/>
       <c r="D53" s="180"/>
@@ -5553,7 +5553,7 @@
       <c r="S53" s="179"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="242"/>
+      <c r="A54" s="186"/>
       <c r="B54" s="178"/>
       <c r="C54" s="180"/>
       <c r="D54" s="180"/>
@@ -5574,7 +5574,7 @@
       <c r="S54" s="179"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="242"/>
+      <c r="A55" s="186"/>
       <c r="B55" s="178"/>
       <c r="C55" s="180"/>
       <c r="D55" s="180"/>
@@ -5595,7 +5595,7 @@
       <c r="S55" s="179"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="242"/>
+      <c r="A56" s="186"/>
       <c r="B56" s="178"/>
       <c r="C56" s="180"/>
       <c r="D56" s="180"/>
@@ -5616,7 +5616,7 @@
       <c r="S56" s="179"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="242"/>
+      <c r="A57" s="186"/>
       <c r="B57" s="178"/>
       <c r="C57" s="180"/>
       <c r="D57" s="180"/>
@@ -5637,57 +5637,57 @@
       <c r="S57" s="179"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="242"/>
+      <c r="A58" s="186"/>
       <c r="B58" s="181"/>
       <c r="S58" s="182"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="242"/>
+      <c r="A59" s="186"/>
       <c r="B59" s="181"/>
       <c r="S59" s="182"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="242"/>
+      <c r="A60" s="186"/>
       <c r="B60" s="181"/>
       <c r="S60" s="182"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="242"/>
+      <c r="A61" s="186"/>
       <c r="B61" s="181"/>
       <c r="S61" s="182"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="242"/>
+      <c r="A62" s="186"/>
       <c r="B62" s="181"/>
       <c r="S62" s="182"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="242"/>
+      <c r="A63" s="186"/>
       <c r="B63" s="181"/>
       <c r="S63" s="182"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="242"/>
+      <c r="A64" s="186"/>
       <c r="B64" s="181"/>
       <c r="S64" s="182"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="242"/>
+      <c r="A65" s="186"/>
       <c r="B65" s="181"/>
       <c r="S65" s="182"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="242"/>
+      <c r="A66" s="186"/>
       <c r="B66" s="181"/>
       <c r="S66" s="182"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="242"/>
+      <c r="A67" s="186"/>
       <c r="B67" s="181"/>
       <c r="S67" s="182"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A68" s="243"/>
+      <c r="A68" s="187"/>
       <c r="B68" s="183"/>
       <c r="C68" s="80"/>
       <c r="D68" s="80"/>
@@ -5709,6 +5709,31 @@
     </row>
   </sheetData>
   <mergeCells count="41">
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A68"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A38"/>
@@ -5725,31 +5750,6 @@
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F47:F48"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8696,7 +8696,7 @@
         <v/>
       </c>
       <c r="D187" t="str">
-        <f t="shared" ref="D153:D191" si="5">CONCATENATE(A187,C187)</f>
+        <f t="shared" ref="D187:D191" si="5">CONCATENATE(A187,C187)</f>
         <v>CUT BLAT 600</v>
       </c>
     </row>
@@ -11108,7 +11108,15 @@
         <v/>
       </c>
       <c r="Y2" t="str">
-        <f t="shared" ref="Y2:Y15" si="0">IF(W2="DB", " ",IF(OR(ISNUMBER(FIND(" ST",X2)),ISNUMBER(FIND(" SM",X2)),ISNUMBER(FIND(" PM",X2)),ISNUMBER(FIND(" TM",X2)),ISNUMBER(FIND(" PG",X2)),ISNUMBER(FIND(" PA",X2))),SUBSTITUTE(X2," ","",1),X2))</f>
+        <f>IF(W2="DB","",
+  IF(RIGHT(TRIM(X2),3)=" PS",
+    "PS "&amp;SUBSTITUTE(LEFT(TRIM(X2),LEN(TRIM(X2))-3)," ","",1),
+    IF(OR(ISNUMBER(FIND(" ST",X2)),ISNUMBER(FIND(" SM",X2)),ISNUMBER(FIND(" PM",X2)),ISNUMBER(FIND(" TM",X2)),ISNUMBER(FIND(" PG",X2)),ISNUMBER(FIND(" PA",X2))),
+      SUBSTITUTE(X2," ","",1),
+      X2
+    )
+  )
+)</f>
         <v/>
       </c>
       <c r="Z2" t="str">
@@ -11141,11 +11149,11 @@
       <c r="T3" s="131"/>
       <c r="U3" s="145"/>
       <c r="V3" s="169" t="str">
-        <f t="shared" ref="V3:V34" si="1">IFERROR(IF(OR(W3="DB PAL",W3="DB MDF"),ROUND(Q3/13.5,0), ROUND(Q3/P3,2)),"")</f>
+        <f t="shared" ref="V3:V34" si="0">IFERROR(IF(OR(W3="DB PAL",W3="DB MDF"),ROUND(Q3/13.5,0), ROUND(Q3/P3,2)),"")</f>
         <v/>
       </c>
       <c r="W3" t="str">
-        <f t="shared" ref="W3:W34" si="2">IF(
+        <f t="shared" ref="W3:W34" si="1">IF(
     OR(
         AND(D3=2800,E3=2070,OR(B3=19,B3=19.3)),
         AND(D3=2800,E3=1220,B3=18),
@@ -11205,7 +11213,7 @@
         <v>N/A</v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" ref="X3:X34" si="3">IFERROR(
+        <f t="shared" ref="X3:X34" si="2">IFERROR(
 IF(
 ISNUMBER(--LEFT(SUBSTITUTE(TRIM(MID(A3,FIND("-",A3)+1,50)),"LR ","LR"),1)),
 "AGT "&amp;SUBSTITUTE(TRIM(MID(A3,FIND("-",A3)+1,50)),"LR ","LR"),
@@ -11217,7 +11225,15 @@
         <v/>
       </c>
       <c r="Y3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="Y3:Y34" si="3">IF(W3="DB","",
+  IF(RIGHT(TRIM(X3),3)=" PS",
+    "PS "&amp;SUBSTITUTE(LEFT(TRIM(X3),LEN(TRIM(X3))-3)," ","",1),
+    IF(OR(ISNUMBER(FIND(" ST",X3)),ISNUMBER(FIND(" SM",X3)),ISNUMBER(FIND(" PM",X3)),ISNUMBER(FIND(" TM",X3)),ISNUMBER(FIND(" PG",X3)),ISNUMBER(FIND(" PA",X3))),
+      SUBSTITUTE(X3," ","",1),
+      X3
+    )
+  )
+)</f>
         <v/>
       </c>
       <c r="Z3" t="str">
@@ -11250,19 +11266,19 @@
       <c r="T4" s="145"/>
       <c r="U4" s="131"/>
       <c r="V4" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W4" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W4" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X4" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y4" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z4" t="str">
@@ -11280,19 +11296,19 @@
       <c r="T5" s="145"/>
       <c r="U5" s="131"/>
       <c r="V5" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W5" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W5" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X5" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y5" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z5" t="str">
@@ -11310,19 +11326,19 @@
       <c r="T6" s="145"/>
       <c r="U6" s="131"/>
       <c r="V6" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W6" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W6" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X6" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X6" t="str">
+        <v/>
+      </c>
+      <c r="Y6" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y6" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z6" t="str">
@@ -11340,19 +11356,19 @@
       <c r="T7" s="131"/>
       <c r="U7" s="131"/>
       <c r="V7" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W7" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W7" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X7" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X7" t="str">
+        <v/>
+      </c>
+      <c r="Y7" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y7" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z7" t="str">
@@ -11370,19 +11386,19 @@
       <c r="T8" s="145"/>
       <c r="U8" s="131"/>
       <c r="V8" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W8" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W8" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X8" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X8" t="str">
+        <v/>
+      </c>
+      <c r="Y8" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y8" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z8" t="str">
@@ -11400,19 +11416,19 @@
       <c r="T9" s="145"/>
       <c r="U9" s="129"/>
       <c r="V9" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W9" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W9" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X9" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X9" t="str">
+        <v/>
+      </c>
+      <c r="Y9" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y9" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z9" t="str">
@@ -11430,19 +11446,19 @@
       <c r="T10" s="145"/>
       <c r="U10" s="145"/>
       <c r="V10" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W10" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W10" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X10" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X10" t="str">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y10" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z10" t="str">
@@ -11460,19 +11476,19 @@
       <c r="T11" s="145"/>
       <c r="U11" s="145"/>
       <c r="V11" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W11" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W11" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X11" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X11" t="str">
+        <v/>
+      </c>
+      <c r="Y11" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y11" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z11" t="str">
@@ -11490,19 +11506,19 @@
       <c r="T12" s="132"/>
       <c r="U12" s="132"/>
       <c r="V12" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W12" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W12" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X12" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X12" t="str">
+        <v/>
+      </c>
+      <c r="Y12" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y12" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z12" t="str">
@@ -11520,19 +11536,19 @@
       <c r="T13" s="159"/>
       <c r="U13" s="165"/>
       <c r="V13" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W13" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W13" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X13" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X13" t="str">
+        <v/>
+      </c>
+      <c r="Y13" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y13" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z13" t="str">
@@ -11550,19 +11566,19 @@
       <c r="T14" s="160"/>
       <c r="U14" s="165"/>
       <c r="V14" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W14" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W14" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X14" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X14" t="str">
+        <v/>
+      </c>
+      <c r="Y14" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y14" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z14" t="str">
@@ -11580,19 +11596,19 @@
       <c r="T15" s="160"/>
       <c r="U15" s="132"/>
       <c r="V15" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W15" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W15" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X15" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X15" t="str">
+        <v/>
+      </c>
+      <c r="Y15" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y15" t="str">
-        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="Z15" t="str">
@@ -11610,19 +11626,19 @@
       <c r="T16" s="160"/>
       <c r="U16" s="131"/>
       <c r="V16" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W16" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W16" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X16" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X16" t="str">
+        <v/>
+      </c>
+      <c r="Y16" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y16" t="str">
-        <f t="shared" ref="Y16:Y24" si="6">IF(W16="DB", " ",IF(OR(ISNUMBER(FIND(" ST",X16)),ISNUMBER(FIND(" SM",X16)),ISNUMBER(FIND(" PM",X16)),ISNUMBER(FIND(" TM",X16)),ISNUMBER(FIND(" PG",X16)),ISNUMBER(FIND(" PA",X16))),SUBSTITUTE(X16," ","",1),X16))</f>
         <v/>
       </c>
       <c r="Z16" t="str">
@@ -11640,19 +11656,19 @@
       <c r="T17" s="160"/>
       <c r="U17" s="131"/>
       <c r="V17" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W17" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W17" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X17" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X17" t="str">
+        <v/>
+      </c>
+      <c r="Y17" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y17" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="Z17" t="str">
@@ -11687,19 +11703,19 @@
       <c r="T18" s="160"/>
       <c r="U18" s="131"/>
       <c r="V18" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W18" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W18" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X18" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X18" t="str">
+        <v/>
+      </c>
+      <c r="Y18" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y18" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="Z18" t="str">
@@ -11733,19 +11749,19 @@
       <c r="S19" s="160"/>
       <c r="T19" s="160"/>
       <c r="V19" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W19" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W19" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X19" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X19" t="str">
+        <v/>
+      </c>
+      <c r="Y19" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y19" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="Z19" t="str">
@@ -11779,19 +11795,19 @@
       <c r="S20" s="159"/>
       <c r="T20" s="155"/>
       <c r="V20" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W20" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W20" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X20" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X20" t="str">
+        <v/>
+      </c>
+      <c r="Y20" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y20" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="Z20" t="str">
@@ -11825,19 +11841,19 @@
       <c r="S21" s="160"/>
       <c r="T21" s="159"/>
       <c r="V21" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W21" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W21" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X21" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X21" t="str">
+        <v/>
+      </c>
+      <c r="Y21" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y21" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="Z21" t="str">
@@ -11851,19 +11867,19 @@
     </row>
     <row r="22" spans="1:27">
       <c r="V22" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W22" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W22" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X22" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X22" t="str">
+        <v/>
+      </c>
+      <c r="Y22" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y22" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="Z22" t="str">
@@ -11877,19 +11893,19 @@
     </row>
     <row r="23" spans="1:27">
       <c r="V23" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W23" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W23" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X23" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X23" t="str">
+        <v/>
+      </c>
+      <c r="Y23" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y23" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="Z23" t="str">
@@ -11903,19 +11919,19 @@
     </row>
     <row r="24" spans="1:27">
       <c r="V24" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W24" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W24" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X24" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X24" t="str">
+        <v/>
+      </c>
+      <c r="Y24" t="str">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Y24" t="str">
-        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="Z24" t="str">
@@ -11929,14 +11945,18 @@
     </row>
     <row r="25" spans="1:27">
       <c r="V25" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W25" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W25" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X25" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X25" t="str">
+        <v/>
+      </c>
+      <c r="Y25" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -11951,14 +11971,18 @@
     </row>
     <row r="26" spans="1:27">
       <c r="V26" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W26" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W26" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X26" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X26" t="str">
+        <v/>
+      </c>
+      <c r="Y26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -11973,14 +11997,18 @@
     </row>
     <row r="27" spans="1:27">
       <c r="V27" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W27" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W27" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X27" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X27" t="str">
+        <v/>
+      </c>
+      <c r="Y27" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -11995,14 +12023,18 @@
     </row>
     <row r="28" spans="1:27">
       <c r="V28" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W28" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W28" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X28" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X28" t="str">
+        <v/>
+      </c>
+      <c r="Y28" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -12017,14 +12049,18 @@
     </row>
     <row r="29" spans="1:27">
       <c r="V29" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W29" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W29" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X29" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X29" t="str">
+        <v/>
+      </c>
+      <c r="Y29" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -12039,14 +12075,18 @@
     </row>
     <row r="30" spans="1:27">
       <c r="V30" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W30" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W30" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X30" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X30" t="str">
+        <v/>
+      </c>
+      <c r="Y30" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -12061,14 +12101,18 @@
     </row>
     <row r="31" spans="1:27">
       <c r="V31" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W31" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W31" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X31" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X31" t="str">
+        <v/>
+      </c>
+      <c r="Y31" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -12083,14 +12127,18 @@
     </row>
     <row r="32" spans="1:27">
       <c r="V32" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W32" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W32" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X32" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X32" t="str">
+        <v/>
+      </c>
+      <c r="Y32" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -12105,14 +12153,18 @@
     </row>
     <row r="33" spans="22:27">
       <c r="V33" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W33" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W33" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X33" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X33" t="str">
+        <v/>
+      </c>
+      <c r="Y33" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -12127,14 +12179,18 @@
     </row>
     <row r="34" spans="22:27">
       <c r="V34" s="169" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W34" t="str">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="W34" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X34" t="str">
         <f t="shared" si="2"/>
-        <v>N/A</v>
-      </c>
-      <c r="X34" t="str">
+        <v/>
+      </c>
+      <c r="Y34" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43559CB7-E9D6-46EC-AC32-EC7F3F709AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B795B75D-9972-45C6-9A81-CC6C9657726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
@@ -1813,83 +1813,115 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1910,12 +1942,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1975,102 +2001,76 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2558,33 +2558,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="27" thickBot="1">
-      <c r="A1" s="220" t="s">
+      <c r="A1" s="225" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="221"/>
-      <c r="C1" s="221"/>
-      <c r="D1" s="221"/>
-      <c r="E1" s="221"/>
-      <c r="F1" s="221"/>
-      <c r="G1" s="221"/>
-      <c r="H1" s="221"/>
-      <c r="I1" s="221"/>
-      <c r="J1" s="221"/>
-      <c r="K1" s="221"/>
-      <c r="L1" s="222"/>
+      <c r="B1" s="226"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
+      <c r="I1" s="226"/>
+      <c r="J1" s="226"/>
+      <c r="K1" s="226"/>
+      <c r="L1" s="227"/>
       <c r="M1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="O1" s="211" t="s">
+      <c r="O1" s="218" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="212"/>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="213"/>
+      <c r="P1" s="219"/>
+      <c r="Q1" s="219"/>
+      <c r="R1" s="219"/>
+      <c r="S1" s="220"/>
     </row>
     <row r="2" spans="1:19" ht="18.75" thickBot="1">
       <c r="A2" s="17" t="s">
@@ -2603,165 +2603,165 @@
         <v>1</v>
       </c>
       <c r="N2" s="83"/>
-      <c r="O2" s="214"/>
-      <c r="P2" s="215"/>
-      <c r="Q2" s="215"/>
-      <c r="R2" s="215"/>
-      <c r="S2" s="216"/>
+      <c r="O2" s="221"/>
+      <c r="P2" s="222"/>
+      <c r="Q2" s="222"/>
+      <c r="R2" s="222"/>
+      <c r="S2" s="223"/>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="226"/>
-      <c r="C3" s="227"/>
-      <c r="D3" s="228"/>
+      <c r="B3" s="231"/>
+      <c r="C3" s="232"/>
+      <c r="D3" s="233"/>
       <c r="H3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="235"/>
+      <c r="I3" s="238"/>
+      <c r="J3" s="239"/>
+      <c r="K3" s="240"/>
       <c r="M3" s="27">
         <v>2</v>
       </c>
       <c r="N3" s="76"/>
-      <c r="O3" s="223"/>
-      <c r="P3" s="224"/>
-      <c r="Q3" s="224"/>
-      <c r="R3" s="224"/>
-      <c r="S3" s="225"/>
+      <c r="O3" s="228"/>
+      <c r="P3" s="229"/>
+      <c r="Q3" s="229"/>
+      <c r="R3" s="229"/>
+      <c r="S3" s="230"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="243"/>
-      <c r="C4" s="244"/>
-      <c r="D4" s="245"/>
+      <c r="B4" s="212"/>
+      <c r="C4" s="213"/>
+      <c r="D4" s="214"/>
       <c r="H4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="246"/>
-      <c r="J4" s="247"/>
-      <c r="K4" s="248"/>
+      <c r="I4" s="215"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="217"/>
       <c r="M4" s="27">
         <v>3</v>
       </c>
       <c r="N4" s="76"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="224"/>
-      <c r="Q4" s="224"/>
-      <c r="R4" s="224"/>
-      <c r="S4" s="225"/>
+      <c r="O4" s="228"/>
+      <c r="P4" s="229"/>
+      <c r="Q4" s="229"/>
+      <c r="R4" s="229"/>
+      <c r="S4" s="230"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="229"/>
-      <c r="C5" s="230"/>
-      <c r="D5" s="231"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="236"/>
       <c r="H5" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="232"/>
-      <c r="J5" s="224"/>
-      <c r="K5" s="225"/>
+      <c r="I5" s="237"/>
+      <c r="J5" s="229"/>
+      <c r="K5" s="230"/>
       <c r="M5" s="27">
         <v>4</v>
       </c>
       <c r="N5" s="76"/>
-      <c r="O5" s="223"/>
-      <c r="P5" s="224"/>
-      <c r="Q5" s="224"/>
-      <c r="R5" s="224"/>
-      <c r="S5" s="225"/>
+      <c r="O5" s="228"/>
+      <c r="P5" s="229"/>
+      <c r="Q5" s="229"/>
+      <c r="R5" s="229"/>
+      <c r="S5" s="230"/>
     </row>
     <row r="6" spans="1:19" ht="15.75" thickBot="1">
       <c r="A6" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="253"/>
-      <c r="C6" s="254"/>
-      <c r="D6" s="255"/>
+      <c r="B6" s="191"/>
+      <c r="C6" s="192"/>
+      <c r="D6" s="193"/>
       <c r="H6" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="256"/>
-      <c r="J6" s="218"/>
-      <c r="K6" s="219"/>
+      <c r="I6" s="194"/>
+      <c r="J6" s="195"/>
+      <c r="K6" s="196"/>
       <c r="M6" s="28">
         <v>5</v>
       </c>
       <c r="N6" s="77"/>
-      <c r="O6" s="217"/>
-      <c r="P6" s="218"/>
-      <c r="Q6" s="218"/>
-      <c r="R6" s="218"/>
-      <c r="S6" s="219"/>
+      <c r="O6" s="224"/>
+      <c r="P6" s="195"/>
+      <c r="Q6" s="195"/>
+      <c r="R6" s="195"/>
+      <c r="S6" s="196"/>
     </row>
     <row r="7" spans="1:19" s="51" customFormat="1" ht="2.1" hidden="1" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A8" s="257" t="s">
+      <c r="A8" s="197" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="258"/>
-      <c r="C8" s="258"/>
-      <c r="D8" s="259"/>
-      <c r="F8" s="236" t="s">
+      <c r="B8" s="198"/>
+      <c r="C8" s="198"/>
+      <c r="D8" s="199"/>
+      <c r="F8" s="203" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="237"/>
-      <c r="H8" s="237"/>
-      <c r="I8" s="237"/>
-      <c r="J8" s="237"/>
-      <c r="K8" s="237"/>
-      <c r="L8" s="237"/>
-      <c r="M8" s="237"/>
-      <c r="N8" s="237"/>
-      <c r="O8" s="237"/>
-      <c r="P8" s="237"/>
-      <c r="Q8" s="237"/>
-      <c r="R8" s="237"/>
-      <c r="S8" s="238"/>
+      <c r="G8" s="204"/>
+      <c r="H8" s="204"/>
+      <c r="I8" s="204"/>
+      <c r="J8" s="204"/>
+      <c r="K8" s="204"/>
+      <c r="L8" s="204"/>
+      <c r="M8" s="204"/>
+      <c r="N8" s="204"/>
+      <c r="O8" s="204"/>
+      <c r="P8" s="204"/>
+      <c r="Q8" s="204"/>
+      <c r="R8" s="204"/>
+      <c r="S8" s="209"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A9" s="260"/>
-      <c r="B9" s="261"/>
-      <c r="C9" s="261"/>
-      <c r="D9" s="262"/>
-      <c r="F9" s="193" t="s">
+      <c r="A9" s="200"/>
+      <c r="B9" s="201"/>
+      <c r="C9" s="201"/>
+      <c r="D9" s="202"/>
+      <c r="F9" s="249" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="194"/>
-      <c r="H9" s="209" t="s">
+      <c r="G9" s="250"/>
+      <c r="H9" s="263" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="210"/>
-      <c r="J9" s="191" t="s">
+      <c r="I9" s="264"/>
+      <c r="J9" s="247" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="192"/>
-      <c r="L9" s="241" t="s">
+      <c r="K9" s="248"/>
+      <c r="L9" s="210" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="242"/>
-      <c r="N9" s="239" t="s">
+      <c r="M9" s="211"/>
+      <c r="N9" s="207" t="s">
         <v>82</v>
       </c>
-      <c r="O9" s="240"/>
-      <c r="P9" s="263" t="s">
+      <c r="O9" s="208"/>
+      <c r="P9" s="205" t="s">
         <v>69</v>
       </c>
-      <c r="Q9" s="264"/>
-      <c r="R9" s="239" t="s">
+      <c r="Q9" s="206"/>
+      <c r="R9" s="207" t="s">
         <v>18</v>
       </c>
-      <c r="S9" s="240"/>
+      <c r="S9" s="208"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A10" s="198" t="s">
+      <c r="A10" s="254" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2818,7 +2818,7 @@
       </c>
     </row>
     <row r="11" spans="1:19">
-      <c r="A11" s="199"/>
+      <c r="A11" s="255"/>
       <c r="B11" s="57" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),1)),"")</f>
         <v/>
@@ -2924,7 +2924,7 @@
       </c>
     </row>
     <row r="12" spans="1:19">
-      <c r="A12" s="199"/>
+      <c r="A12" s="255"/>
       <c r="B12" s="133" t="str" cm="1">
         <f t="array" ref="B12">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),2))),"")</f>
         <v/>
@@ -3030,7 +3030,7 @@
       </c>
     </row>
     <row r="13" spans="1:19">
-      <c r="A13" s="199"/>
+      <c r="A13" s="255"/>
       <c r="B13" s="133" t="str" cm="1">
         <f t="array" ref="B13">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),3))),"")</f>
         <v/>
@@ -3136,7 +3136,7 @@
       </c>
     </row>
     <row r="14" spans="1:19">
-      <c r="A14" s="199"/>
+      <c r="A14" s="255"/>
       <c r="B14" s="133" t="str" cm="1">
         <f t="array" ref="B14">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),4))),"")</f>
         <v/>
@@ -3223,7 +3223,7 @@
       </c>
     </row>
     <row r="15" spans="1:19">
-      <c r="A15" s="199"/>
+      <c r="A15" s="255"/>
       <c r="B15" s="133" t="str" cm="1">
         <f t="array" ref="B15">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),5))),"")</f>
         <v/>
@@ -3310,7 +3310,7 @@
       </c>
     </row>
     <row r="16" spans="1:19">
-      <c r="A16" s="199"/>
+      <c r="A16" s="255"/>
       <c r="B16" s="133" t="str" cm="1">
         <f t="array" ref="B16">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),6))),"")</f>
         <v/>
@@ -3397,7 +3397,7 @@
       </c>
     </row>
     <row r="17" spans="1:19">
-      <c r="A17" s="199"/>
+      <c r="A17" s="255"/>
       <c r="B17" s="133" t="str" cm="1">
         <f t="array" ref="B17">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),7))),"")</f>
         <v/>
@@ -3484,7 +3484,7 @@
       </c>
     </row>
     <row r="18" spans="1:19">
-      <c r="A18" s="199"/>
+      <c r="A18" s="255"/>
       <c r="B18" s="133" t="str" cm="1">
         <f t="array" ref="B18">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),8))),"")</f>
         <v/>
@@ -3571,7 +3571,7 @@
       </c>
     </row>
     <row r="19" spans="1:19">
-      <c r="A19" s="199"/>
+      <c r="A19" s="255"/>
       <c r="B19" s="133" t="str" cm="1">
         <f t="array" ref="B19">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),9))),"")</f>
         <v/>
@@ -3658,7 +3658,7 @@
       </c>
     </row>
     <row r="20" spans="1:19">
-      <c r="A20" s="199"/>
+      <c r="A20" s="255"/>
       <c r="B20" s="133" t="str" cm="1">
         <f t="array" ref="B20">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),10))),"")</f>
         <v/>
@@ -3745,7 +3745,7 @@
       </c>
     </row>
     <row r="21" spans="1:19">
-      <c r="A21" s="199"/>
+      <c r="A21" s="255"/>
       <c r="B21" s="133" t="str" cm="1">
         <f t="array" ref="B21">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),11))),"")</f>
         <v/>
@@ -3832,7 +3832,7 @@
       </c>
     </row>
     <row r="22" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A22" s="200"/>
+      <c r="A22" s="256"/>
       <c r="B22" s="133" t="str" cm="1">
         <f t="array" ref="B22">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PAL"),12))),"")</f>
         <v/>
@@ -3975,7 +3975,7 @@
       </c>
     </row>
     <row r="24" spans="1:19">
-      <c r="A24" s="198" t="s">
+      <c r="A24" s="254" t="s">
         <v>10</v>
       </c>
       <c r="B24" s="57" t="str">
@@ -4083,7 +4083,7 @@
       </c>
     </row>
     <row r="25" spans="1:19">
-      <c r="A25" s="199"/>
+      <c r="A25" s="255"/>
       <c r="B25" s="70" t="str">
         <f>IFERROR(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),2)),"")</f>
         <v/>
@@ -4189,7 +4189,7 @@
       </c>
     </row>
     <row r="26" spans="1:19">
-      <c r="A26" s="199"/>
+      <c r="A26" s="255"/>
       <c r="B26" s="70" t="str" cm="1">
         <f t="array" ref="B26">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),3))),"")</f>
         <v/>
@@ -4295,7 +4295,7 @@
       </c>
     </row>
     <row r="27" spans="1:19">
-      <c r="A27" s="199"/>
+      <c r="A27" s="255"/>
       <c r="B27" s="70" t="str" cm="1">
         <f t="array" ref="B27">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),4))),"")</f>
         <v/>
@@ -4382,7 +4382,7 @@
       </c>
     </row>
     <row r="28" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A28" s="201"/>
+      <c r="A28" s="257"/>
       <c r="B28" s="70" t="str" cm="1">
         <f t="array" ref="B28">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="MDF"),5))),"")</f>
         <v/>
@@ -4544,7 +4544,7 @@
       <c r="S31" s="80"/>
     </row>
     <row r="32" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A32" s="188" t="s">
+      <c r="A32" s="244" t="s">
         <v>80</v>
       </c>
       <c r="B32" s="57" t="str" cm="1">
@@ -4623,7 +4623,7 @@
       </c>
     </row>
     <row r="33" spans="1:19">
-      <c r="A33" s="189"/>
+      <c r="A33" s="245"/>
       <c r="B33" s="70" t="str" cm="1">
         <f t="array" ref="B33">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),2))),"")</f>
         <v/>
@@ -4700,7 +4700,7 @@
       </c>
     </row>
     <row r="34" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A34" s="190"/>
+      <c r="A34" s="246"/>
       <c r="B34" s="70" t="str" cm="1">
         <f t="array" ref="B34">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="Blat"),3))),"")</f>
         <v/>
@@ -4798,7 +4798,7 @@
       <c r="S35" s="58"/>
     </row>
     <row r="36" spans="1:19">
-      <c r="A36" s="188" t="s">
+      <c r="A36" s="244" t="s">
         <v>81</v>
       </c>
       <c r="B36" s="57" t="str" cm="1">
@@ -4877,7 +4877,7 @@
       </c>
     </row>
     <row r="37" spans="1:19">
-      <c r="A37" s="189"/>
+      <c r="A37" s="245"/>
       <c r="B37" s="70" t="str" cm="1">
         <f t="array" ref="B37">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),2))),"")</f>
         <v/>
@@ -4954,7 +4954,7 @@
       </c>
     </row>
     <row r="38" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A38" s="190"/>
+      <c r="A38" s="246"/>
       <c r="B38" s="71" t="str" cm="1">
         <f t="array" ref="B38">IFERROR(_xlfn.SINGLE(INDEX(Deco!$Y$2:$Y$99,_xlfn.AGGREGATE(15,6,ROW(Deco!$Y$2:$Y$99)-ROW(Deco!$Y$2)+1/(Deco!$W$2:$W$99="PS"),3))),"")</f>
         <v/>
@@ -5045,7 +5045,7 @@
       <c r="Q39" s="64"/>
     </row>
     <row r="40" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A40" s="198" t="s">
+      <c r="A40" s="254" t="s">
         <v>51</v>
       </c>
       <c r="B40" s="32" t="s">
@@ -5057,25 +5057,25 @@
       <c r="D40" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="195" t="s">
+      <c r="F40" s="251" t="s">
         <v>73</v>
       </c>
-      <c r="G40" s="196"/>
-      <c r="H40" s="196"/>
-      <c r="I40" s="196"/>
-      <c r="J40" s="196"/>
-      <c r="K40" s="196"/>
-      <c r="L40" s="196"/>
-      <c r="M40" s="196"/>
-      <c r="N40" s="196"/>
-      <c r="O40" s="196"/>
-      <c r="P40" s="196"/>
-      <c r="Q40" s="196"/>
-      <c r="R40" s="196"/>
-      <c r="S40" s="197"/>
+      <c r="G40" s="252"/>
+      <c r="H40" s="252"/>
+      <c r="I40" s="252"/>
+      <c r="J40" s="252"/>
+      <c r="K40" s="252"/>
+      <c r="L40" s="252"/>
+      <c r="M40" s="252"/>
+      <c r="N40" s="252"/>
+      <c r="O40" s="252"/>
+      <c r="P40" s="252"/>
+      <c r="Q40" s="252"/>
+      <c r="R40" s="252"/>
+      <c r="S40" s="253"/>
     </row>
     <row r="41" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A41" s="199"/>
+      <c r="A41" s="255"/>
       <c r="B41" s="35" t="s">
         <v>83</v>
       </c>
@@ -5138,7 +5138,7 @@
       </c>
     </row>
     <row r="42" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A42" s="199"/>
+      <c r="A42" s="255"/>
       <c r="B42" s="50" t="s">
         <v>90</v>
       </c>
@@ -5163,13 +5163,13 @@
       <c r="P42" s="69"/>
       <c r="Q42" s="81"/>
       <c r="R42" s="82"/>
-      <c r="S42" s="202">
+      <c r="S42" s="185">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,0,1)</f>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A43" s="199"/>
+      <c r="A43" s="255"/>
       <c r="B43" s="50" t="s">
         <v>84</v>
       </c>
@@ -5181,26 +5181,26 @@
         <v>55</v>
       </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="236" t="str">
+      <c r="F43" s="203" t="str">
         <f>IF(COUNTIF(Deco!AA2:AA34,"Vezi EK")&gt;0,"Atentie! Verifica EK dublaje","Nr. Piese Dublaje")</f>
         <v>Nr. Piese Dublaje</v>
       </c>
-      <c r="G43" s="237"/>
-      <c r="H43" s="237"/>
-      <c r="I43" s="237"/>
-      <c r="J43" s="237"/>
-      <c r="K43" s="237"/>
-      <c r="L43" s="237"/>
-      <c r="M43" s="237"/>
-      <c r="N43" s="237"/>
-      <c r="O43" s="237"/>
-      <c r="P43" s="237"/>
-      <c r="Q43" s="237"/>
-      <c r="R43" s="237"/>
-      <c r="S43" s="203"/>
+      <c r="G43" s="204"/>
+      <c r="H43" s="204"/>
+      <c r="I43" s="204"/>
+      <c r="J43" s="204"/>
+      <c r="K43" s="204"/>
+      <c r="L43" s="204"/>
+      <c r="M43" s="204"/>
+      <c r="N43" s="204"/>
+      <c r="O43" s="204"/>
+      <c r="P43" s="204"/>
+      <c r="Q43" s="204"/>
+      <c r="R43" s="204"/>
+      <c r="S43" s="258"/>
     </row>
     <row r="44" spans="1:19">
-      <c r="A44" s="199"/>
+      <c r="A44" s="255"/>
       <c r="B44" s="50" t="s">
         <v>89</v>
       </c>
@@ -5256,7 +5256,7 @@
       </c>
     </row>
     <row r="45" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A45" s="199"/>
+      <c r="A45" s="255"/>
       <c r="B45" s="33" t="s">
         <v>91</v>
       </c>
@@ -5390,7 +5390,7 @@
       </c>
     </row>
     <row r="46" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A46" s="199"/>
+      <c r="A46" s="255"/>
       <c r="B46" s="33" t="s">
         <v>85</v>
       </c>
@@ -5404,7 +5404,7 @@
       <c r="E46" s="2"/>
     </row>
     <row r="47" spans="1:19">
-      <c r="A47" s="199"/>
+      <c r="A47" s="255"/>
       <c r="B47" s="33" t="s">
         <v>86</v>
       </c>
@@ -5415,31 +5415,31 @@
       <c r="D47" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="202" t="s">
+      <c r="F47" s="185" t="s">
         <v>34</v>
       </c>
-      <c r="G47" s="251" t="str">
+      <c r="G47" s="189" t="str">
         <f>IF(I6="PLAN M",SUM(C11:C28), "N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="J47" s="202" t="s">
+      <c r="J47" s="185" t="s">
         <v>88</v>
       </c>
-      <c r="K47" s="249">
+      <c r="K47" s="187">
         <v>1</v>
       </c>
-      <c r="N47" s="202" t="s">
+      <c r="N47" s="185" t="s">
         <v>110</v>
       </c>
-      <c r="O47" s="205"/>
-      <c r="P47" s="206"/>
-      <c r="R47" s="202" t="s">
+      <c r="O47" s="259"/>
+      <c r="P47" s="260"/>
+      <c r="R47" s="185" t="s">
         <v>116</v>
       </c>
-      <c r="S47" s="202"/>
+      <c r="S47" s="185"/>
     </row>
     <row r="48" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A48" s="201"/>
+      <c r="A48" s="257"/>
       <c r="B48" s="36" t="s">
         <v>87</v>
       </c>
@@ -5450,15 +5450,15 @@
       <c r="D48" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="F48" s="204"/>
-      <c r="G48" s="252"/>
-      <c r="J48" s="204"/>
-      <c r="K48" s="250"/>
-      <c r="N48" s="203"/>
-      <c r="O48" s="207"/>
-      <c r="P48" s="208"/>
-      <c r="R48" s="203"/>
-      <c r="S48" s="204"/>
+      <c r="F48" s="186"/>
+      <c r="G48" s="190"/>
+      <c r="J48" s="186"/>
+      <c r="K48" s="188"/>
+      <c r="N48" s="258"/>
+      <c r="O48" s="261"/>
+      <c r="P48" s="262"/>
+      <c r="R48" s="258"/>
+      <c r="S48" s="186"/>
     </row>
     <row r="49" spans="1:19" ht="2.1" hidden="1" customHeight="1">
       <c r="A49" s="40"/>
@@ -5467,7 +5467,7 @@
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:19">
-      <c r="A50" s="185" t="s">
+      <c r="A50" s="241" t="s">
         <v>66</v>
       </c>
       <c r="B50" s="175"/>
@@ -5490,7 +5490,7 @@
       <c r="S50" s="177"/>
     </row>
     <row r="51" spans="1:19">
-      <c r="A51" s="186"/>
+      <c r="A51" s="242"/>
       <c r="B51" s="178"/>
       <c r="C51" s="180"/>
       <c r="D51" s="180"/>
@@ -5511,7 +5511,7 @@
       <c r="S51" s="179"/>
     </row>
     <row r="52" spans="1:19">
-      <c r="A52" s="186"/>
+      <c r="A52" s="242"/>
       <c r="B52" s="178"/>
       <c r="C52" s="180"/>
       <c r="D52" s="180"/>
@@ -5532,7 +5532,7 @@
       <c r="S52" s="179"/>
     </row>
     <row r="53" spans="1:19">
-      <c r="A53" s="186"/>
+      <c r="A53" s="242"/>
       <c r="B53" s="178"/>
       <c r="C53" s="180"/>
       <c r="D53" s="180"/>
@@ -5553,7 +5553,7 @@
       <c r="S53" s="179"/>
     </row>
     <row r="54" spans="1:19">
-      <c r="A54" s="186"/>
+      <c r="A54" s="242"/>
       <c r="B54" s="178"/>
       <c r="C54" s="180"/>
       <c r="D54" s="180"/>
@@ -5574,7 +5574,7 @@
       <c r="S54" s="179"/>
     </row>
     <row r="55" spans="1:19">
-      <c r="A55" s="186"/>
+      <c r="A55" s="242"/>
       <c r="B55" s="178"/>
       <c r="C55" s="180"/>
       <c r="D55" s="180"/>
@@ -5595,7 +5595,7 @@
       <c r="S55" s="179"/>
     </row>
     <row r="56" spans="1:19">
-      <c r="A56" s="186"/>
+      <c r="A56" s="242"/>
       <c r="B56" s="178"/>
       <c r="C56" s="180"/>
       <c r="D56" s="180"/>
@@ -5616,7 +5616,7 @@
       <c r="S56" s="179"/>
     </row>
     <row r="57" spans="1:19">
-      <c r="A57" s="186"/>
+      <c r="A57" s="242"/>
       <c r="B57" s="178"/>
       <c r="C57" s="180"/>
       <c r="D57" s="180"/>
@@ -5637,57 +5637,57 @@
       <c r="S57" s="179"/>
     </row>
     <row r="58" spans="1:19">
-      <c r="A58" s="186"/>
+      <c r="A58" s="242"/>
       <c r="B58" s="181"/>
       <c r="S58" s="182"/>
     </row>
     <row r="59" spans="1:19">
-      <c r="A59" s="186"/>
+      <c r="A59" s="242"/>
       <c r="B59" s="181"/>
       <c r="S59" s="182"/>
     </row>
     <row r="60" spans="1:19">
-      <c r="A60" s="186"/>
+      <c r="A60" s="242"/>
       <c r="B60" s="181"/>
       <c r="S60" s="182"/>
     </row>
     <row r="61" spans="1:19">
-      <c r="A61" s="186"/>
+      <c r="A61" s="242"/>
       <c r="B61" s="181"/>
       <c r="S61" s="182"/>
     </row>
     <row r="62" spans="1:19">
-      <c r="A62" s="186"/>
+      <c r="A62" s="242"/>
       <c r="B62" s="181"/>
       <c r="S62" s="182"/>
     </row>
     <row r="63" spans="1:19">
-      <c r="A63" s="186"/>
+      <c r="A63" s="242"/>
       <c r="B63" s="181"/>
       <c r="S63" s="182"/>
     </row>
     <row r="64" spans="1:19">
-      <c r="A64" s="186"/>
+      <c r="A64" s="242"/>
       <c r="B64" s="181"/>
       <c r="S64" s="182"/>
     </row>
     <row r="65" spans="1:19">
-      <c r="A65" s="186"/>
+      <c r="A65" s="242"/>
       <c r="B65" s="181"/>
       <c r="S65" s="182"/>
     </row>
     <row r="66" spans="1:19">
-      <c r="A66" s="186"/>
+      <c r="A66" s="242"/>
       <c r="B66" s="181"/>
       <c r="S66" s="182"/>
     </row>
     <row r="67" spans="1:19">
-      <c r="A67" s="186"/>
+      <c r="A67" s="242"/>
       <c r="B67" s="181"/>
       <c r="S67" s="182"/>
     </row>
     <row r="68" spans="1:19" ht="15.75" thickBot="1">
-      <c r="A68" s="187"/>
+      <c r="A68" s="243"/>
       <c r="B68" s="183"/>
       <c r="C68" s="80"/>
       <c r="D68" s="80"/>
@@ -5709,31 +5709,6 @@
     </row>
   </sheetData>
   <mergeCells count="41">
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="F43:R43"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="O1:S1"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="O4:S4"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A50:A68"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A36:A38"/>
@@ -5750,6 +5725,31 @@
     <mergeCell ref="O47:P48"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="F47:F48"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="O1:S1"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="O4:S4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:D9"/>
+    <mergeCell ref="F43:R43"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="F8:S8"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="L9:M9"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6136,7 +6136,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="str">
-        <f>Fisa!B24</f>
+        <f>IF(Fisa!B24="","", "MDF "&amp;Fisa!B24)</f>
         <v/>
       </c>
       <c r="B14" t="str">
@@ -6161,7 +6161,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="str">
-        <f>Fisa!B25</f>
+        <f>IF(Fisa!B25="","", "MDF "&amp;Fisa!B25)</f>
         <v/>
       </c>
       <c r="B15" t="str">
@@ -6186,7 +6186,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="str">
-        <f>Fisa!B26</f>
+        <f>IF(Fisa!B26="","", "MDF "&amp;Fisa!B26)</f>
         <v/>
       </c>
       <c r="B16" t="str">
@@ -6211,7 +6211,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="str">
-        <f>Fisa!B27</f>
+        <f>IF(Fisa!B27="","", "MDF "&amp;Fisa!B27)</f>
         <v/>
       </c>
       <c r="B17" t="str">
@@ -6236,7 +6236,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="str">
-        <f>Fisa!B28</f>
+        <f>IF(Fisa!B28="","", "MDF "&amp;Fisa!B28)</f>
         <v/>
       </c>
       <c r="B18" t="str">
@@ -11108,14 +11108,25 @@
         <v/>
       </c>
       <c r="Y2" t="str">
-        <f>IF(W2="DB","",
-  IF(RIGHT(TRIM(X2),3)=" PS",
-    "PS "&amp;SUBSTITUTE(LEFT(TRIM(X2),LEN(TRIM(X2))-3)," ","",1),
-    IF(OR(ISNUMBER(FIND(" ST",X2)),ISNUMBER(FIND(" SM",X2)),ISNUMBER(FIND(" PM",X2)),ISNUMBER(FIND(" TM",X2)),ISNUMBER(FIND(" PG",X2)),ISNUMBER(FIND(" PA",X2))),
-      SUBSTITUTE(X2," ","",1),
-      X2
+        <f>IF(W2="","",
+    IF(
+        OR(
+            ISNUMBER(FIND(" ST",X2)),
+            ISNUMBER(FIND(" SM",X2)),
+            ISNUMBER(FIND(" PM",X2)),
+            ISNUMBER(FIND(" TM",X2)),
+            ISNUMBER(FIND(" PG",X2)),
+            ISNUMBER(FIND(" PA",X2))
+        ),
+        IF(OR(E2=600,E2=650,E2=920),
+            SUBSTITUTE(X2," ","",1),
+            IFERROR(LEFT(SUBSTITUTE(X2," ","",1), FIND("/",SUBSTITUTE(X2," ","",1))-1), SUBSTITUTE(X2," ","",1))
+        ),
+        IF(OR(E2=600,E2=650,E2=920),
+            X2,
+            IFERROR(LEFT(X2, FIND("/",X2)-1), X2)
+        )
     )
-  )
 )</f>
         <v/>
       </c>
@@ -11131,8 +11142,8 @@
             ISNUMBER(FIND(" PG",X2)),
             ISNUMBER(FIND(" PA",X2))
         ),
-        SUBSTITUTE(X2," ","",1),
-        X2
+        IFERROR(LEFT(SUBSTITUTE(X2," ","",1), FIND("/",SUBSTITUTE(X2," ","",1))-1), SUBSTITUTE(X2," ","",1)),
+        IFERROR(LEFT(X2, FIND("/",X2)-1), X2)
     ),
     " "
 )</f>
@@ -11225,14 +11236,25 @@
         <v/>
       </c>
       <c r="Y3" t="str">
-        <f t="shared" ref="Y3:Y34" si="3">IF(W3="DB","",
-  IF(RIGHT(TRIM(X3),3)=" PS",
-    "PS "&amp;SUBSTITUTE(LEFT(TRIM(X3),LEN(TRIM(X3))-3)," ","",1),
-    IF(OR(ISNUMBER(FIND(" ST",X3)),ISNUMBER(FIND(" SM",X3)),ISNUMBER(FIND(" PM",X3)),ISNUMBER(FIND(" TM",X3)),ISNUMBER(FIND(" PG",X3)),ISNUMBER(FIND(" PA",X3))),
-      SUBSTITUTE(X3," ","",1),
-      X3
+        <f t="shared" ref="Y3:Y34" si="3">IF(W3="","",
+    IF(
+        OR(
+            ISNUMBER(FIND(" ST",X3)),
+            ISNUMBER(FIND(" SM",X3)),
+            ISNUMBER(FIND(" PM",X3)),
+            ISNUMBER(FIND(" TM",X3)),
+            ISNUMBER(FIND(" PG",X3)),
+            ISNUMBER(FIND(" PA",X3))
+        ),
+        IF(OR(E3=600,E3=650,E3=920),
+            SUBSTITUTE(X3," ","",1),
+            IFERROR(LEFT(SUBSTITUTE(X3," ","",1), FIND("/",SUBSTITUTE(X3," ","",1))-1), SUBSTITUTE(X3," ","",1))
+        ),
+        IF(OR(E3=600,E3=650,E3=920),
+            X3,
+            IFERROR(LEFT(X3, FIND("/",X3)-1), X3)
+        )
     )
-  )
 )</f>
         <v/>
       </c>
@@ -11248,8 +11270,8 @@
             ISNUMBER(FIND(" PG",X3)),
             ISNUMBER(FIND(" PA",X3))
         ),
-        SUBSTITUTE(X3," ","",1),
-        X3
+        IFERROR(LEFT(SUBSTITUTE(X3," ","",1), FIND("/",SUBSTITUTE(X3," ","",1))-1), SUBSTITUTE(X3," ","",1)),
+        IFERROR(LEFT(X3, FIND("/",X3)-1), X3)
     ),
     " "
 )</f>

--- a/_FIsa_Prototip.xlsx
+++ b/_FIsa_Prototip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B795B75D-9972-45C6-9A81-CC6C9657726B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9865FA55-33BB-40C5-A628-91C0683875A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{6BB54F16-2027-48CD-9FB7-F8F825275EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Fisa" sheetId="6" r:id="rId1"/>
@@ -599,7 +599,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="58">
     <border>
       <left/>
       <right/>
@@ -1276,6 +1276,56 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1284,7 +1334,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="268">
+  <cellXfs count="277">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1776,9 +1826,6 @@
       <alignment vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1813,11 +1860,191 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1848,12 +2075,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1899,180 +2120,6 @@
     <xf numFmtId="49" fontId="3" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xf